--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -171,7 +171,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="197">
   <si>
     <t>id</t>
   </si>
@@ -488,7 +488,19 @@
     <t>宙斯vs哈迪斯</t>
   </si>
   <si>
-    <t>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</t>
+    <t>1_9650|2_300|3_50</t>
+  </si>
+  <si>
+    <t>1000000&amp;999999999_4,25-0|26-0|27-0|28-0;5,25-0|26-0|27-0|28-0</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-55000|1&amp;15-10000|15&amp;30-3000|30&amp;45-2200|45&amp;60-1100|60&amp;75-1200|75&amp;90-700|90&amp;105-800|105&amp;120-400|120&amp;135-300|135&amp;150-300|150&amp;180-100|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-100|300&amp;360-100|360&amp;420-100|420&amp;480-40|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-97900|1&amp;15-2000|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-97100|1&amp;15-2800|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-1600|1&amp;15-7000|15&amp;30-4500|30&amp;45-3600|45&amp;60-2800|60&amp;75-2800|75&amp;90-2200|90&amp;105-2000|105&amp;120-1600|120&amp;135-1900|135&amp;150-1400|150&amp;180-2700|180&amp;210-2300|210&amp;240-2000|240&amp;270-1900|270&amp;300-1500|300&amp;360-2800|360&amp;420-2300|420&amp;480-1900|480&amp;540-1700|540&amp;600-1400|600&amp;720-2500|720&amp;840-2100|840&amp;960-1700|960&amp;1080-1500|1080&amp;1200-1500|1200&amp;1440-1500|1440&amp;1680-1000|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-300|1&amp;15-800|15&amp;30-500|30&amp;45-500|45&amp;60-400|60&amp;75-500|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-500|135&amp;150-400|150&amp;180-800|180&amp;210-800|210&amp;240-800|240&amp;270-800|270&amp;300-700|300&amp;360-1500|360&amp;420-1400|420&amp;480-1300|480&amp;540-400|540&amp;600-500|600&amp;720-500|720&amp;840-500|840&amp;960-500|960&amp;1080-100|1080&amp;1200-100|1200&amp;1440-100|1440&amp;1680-100|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9700|2_250|3_50</t>
+  </si>
+  <si>
+    <t>1_9790|2_160|3_50</t>
   </si>
   <si>
     <t>杰克船长</t>
@@ -524,12 +536,6 @@
     <t>1,0&amp;1-70000|1&amp;25-13000|25&amp;50-9000|50&amp;75-4000|75&amp;100-1400|100&amp;125-950|125&amp;150-600|150&amp;175-400|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-50|300&amp;350-10|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-85200|1&amp;25-4700|25&amp;50-2100|50&amp;75-200|75&amp;100-100|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-0|1&amp;25-5000|25&amp;50-2300|50&amp;75-900|75&amp;100-300|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-100|200&amp;225-100|225&amp;250-0|250&amp;300-100|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-5000|300&amp;350-5000|350&amp;400-5000|400&amp;450-5000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-50|6400&amp;7200-50|7200&amp;8000-10|8000&amp;9250-10|9250&amp;10500-10|10500&amp;99999999-0;5,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-2000|175&amp;200-2000|200&amp;225-2000|225&amp;250-5000|250&amp;300-4000|300&amp;350-4000|350&amp;400-4000|400&amp;450-4000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-400|5600&amp;6400-250|6400&amp;7200-150|7200&amp;8000-100|8000&amp;9250-100|9250&amp;10500-50|10500&amp;99999999-0</t>
   </si>
   <si>
-    <t>1_9650|2_300|3_50</t>
-  </si>
-  <si>
-    <t>1_9700|2_250|3_50</t>
-  </si>
-  <si>
     <t>1_9850|2_150|3_0</t>
   </si>
   <si>
@@ -626,9 +632,6 @@
     <t>虎虎生财</t>
   </si>
   <si>
-    <t>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</t>
-  </si>
-  <si>
     <t>金蛇招财</t>
   </si>
   <si>
@@ -737,7 +740,22 @@
     <t>潘金莲</t>
   </si>
   <si>
-    <t>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</t>
+    <t>1000000&amp;999999999_2,27-0|28-0|29-0|30-0|31-0|32-0|33-0|34-0</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-60000|1&amp;40-20000|40&amp;80-6000|80&amp;120-2000|120&amp;160-2800|160&amp;200-1000|200&amp;240-1000|240&amp;280-500|280&amp;320-500|320&amp;360-600|360&amp;400-100|400&amp;480-100|480&amp;560-100|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-200|40&amp;80-400|80&amp;120-500|120&amp;160-600|160&amp;200-700|200&amp;240-700|240&amp;280-800|280&amp;320-900|320&amp;360-900|360&amp;400-1000|400&amp;480-2100|480&amp;560-2300|560&amp;640-2400|640&amp;720-2500|720&amp;800-2600|800&amp;960-5200|960&amp;1120-4000|1120&amp;1280-3000|1280&amp;1440-2000|1440&amp;1600-2000|1600&amp;1920-2000|1920&amp;2240-2000|2240&amp;2560-2000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1100|6400&amp;7680-1000|7680&amp;8960-300|8960&amp;10240-100|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;3,0&amp;1-84600|1&amp;40-13400|40&amp;80-1400|80&amp;120-300|120&amp;160-100|160&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9810|2_140|3_50</t>
+  </si>
+  <si>
+    <t>1_9830|2_120|3_50</t>
+  </si>
+  <si>
+    <t>1_9910|2_40|3_50</t>
+  </si>
+  <si>
+    <t>1_9930|2_20|3_50</t>
   </si>
   <si>
     <t>澳门壕梦</t>
@@ -4134,11 +4152,13 @@
         <v>1</v>
       </c>
       <c r="E68" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="F68" s="24"/>
+        <v>105</v>
+      </c>
+      <c r="F68" s="24" t="s">
+        <v>106</v>
+      </c>
       <c r="G68" s="37" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H68" s="27">
         <v>8000</v>
@@ -4164,12 +4184,15 @@
         <v>2</v>
       </c>
       <c r="E69" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="F69" s="24"/>
+        <v>108</v>
+      </c>
+      <c r="F69" s="24" t="str">
+        <f>F68</f>
+        <v>1000000&amp;999999999_4,25-0|26-0|27-0|28-0;5,25-0|26-0|27-0|28-0</v>
+      </c>
       <c r="G69" s="37" t="str">
         <f t="shared" ref="G69:G74" si="9">G68</f>
-        <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
+        <v>1,0&amp;1-55000|1&amp;15-10000|15&amp;30-3000|30&amp;45-2200|45&amp;60-1100|60&amp;75-1200|75&amp;90-700|90&amp;105-800|105&amp;120-400|120&amp;135-300|135&amp;150-300|150&amp;180-100|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-100|300&amp;360-100|360&amp;420-100|420&amp;480-40|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-97900|1&amp;15-2000|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-97100|1&amp;15-2800|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-1600|1&amp;15-7000|15&amp;30-4500|30&amp;45-3600|45&amp;60-2800|60&amp;75-2800|75&amp;90-2200|90&amp;105-2000|105&amp;120-1600|120&amp;135-1900|135&amp;150-1400|150&amp;180-2700|180&amp;210-2300|210&amp;240-2000|240&amp;270-1900|270&amp;300-1500|300&amp;360-2800|360&amp;420-2300|420&amp;480-1900|480&amp;540-1700|540&amp;600-1400|600&amp;720-2500|720&amp;840-2100|840&amp;960-1700|960&amp;1080-1500|1080&amp;1200-1500|1200&amp;1440-1500|1440&amp;1680-1000|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-300|1&amp;15-800|15&amp;30-500|30&amp;45-500|45&amp;60-400|60&amp;75-500|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-500|135&amp;150-400|150&amp;180-800|180&amp;210-800|210&amp;240-800|240&amp;270-800|270&amp;300-700|300&amp;360-1500|360&amp;420-1400|420&amp;480-1300|480&amp;540-400|540&amp;600-500|600&amp;720-500|720&amp;840-500|840&amp;960-500|960&amp;1080-100|1080&amp;1200-100|1200&amp;1440-100|1440&amp;1680-100|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="H69" s="27">
         <v>6000</v>
@@ -4195,12 +4218,15 @@
         <v>3</v>
       </c>
       <c r="E70" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="F70" s="24"/>
+        <v>68</v>
+      </c>
+      <c r="F70" s="24" t="str">
+        <f>F69</f>
+        <v>1000000&amp;999999999_4,25-0|26-0|27-0|28-0;5,25-0|26-0|27-0|28-0</v>
+      </c>
       <c r="G70" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
+        <v>1,0&amp;1-55000|1&amp;15-10000|15&amp;30-3000|30&amp;45-2200|45&amp;60-1100|60&amp;75-1200|75&amp;90-700|90&amp;105-800|105&amp;120-400|120&amp;135-300|135&amp;150-300|150&amp;180-100|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-100|300&amp;360-100|360&amp;420-100|420&amp;480-40|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-97900|1&amp;15-2000|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-97100|1&amp;15-2800|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-1600|1&amp;15-7000|15&amp;30-4500|30&amp;45-3600|45&amp;60-2800|60&amp;75-2800|75&amp;90-2200|90&amp;105-2000|105&amp;120-1600|120&amp;135-1900|135&amp;150-1400|150&amp;180-2700|180&amp;210-2300|210&amp;240-2000|240&amp;270-1900|270&amp;300-1500|300&amp;360-2800|360&amp;420-2300|420&amp;480-1900|480&amp;540-1700|540&amp;600-1400|600&amp;720-2500|720&amp;840-2100|840&amp;960-1700|960&amp;1080-1500|1080&amp;1200-1500|1200&amp;1440-1500|1440&amp;1680-1000|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-300|1&amp;15-800|15&amp;30-500|30&amp;45-500|45&amp;60-400|60&amp;75-500|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-500|135&amp;150-400|150&amp;180-800|180&amp;210-800|210&amp;240-800|240&amp;270-800|270&amp;300-700|300&amp;360-1500|360&amp;420-1400|420&amp;480-1300|480&amp;540-400|540&amp;600-500|600&amp;720-500|720&amp;840-500|840&amp;960-500|960&amp;1080-100|1080&amp;1200-100|1200&amp;1440-100|1440&amp;1680-100|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="H70" s="27">
         <v>4000</v>
@@ -4226,12 +4252,15 @@
         <v>4</v>
       </c>
       <c r="E71" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="F71" s="24"/>
+        <v>109</v>
+      </c>
+      <c r="F71" s="24" t="str">
+        <f>F70</f>
+        <v>1000000&amp;999999999_4,25-0|26-0|27-0|28-0;5,25-0|26-0|27-0|28-0</v>
+      </c>
       <c r="G71" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
+        <v>1,0&amp;1-55000|1&amp;15-10000|15&amp;30-3000|30&amp;45-2200|45&amp;60-1100|60&amp;75-1200|75&amp;90-700|90&amp;105-800|105&amp;120-400|120&amp;135-300|135&amp;150-300|150&amp;180-100|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-100|300&amp;360-100|360&amp;420-100|420&amp;480-40|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-97900|1&amp;15-2000|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-97100|1&amp;15-2800|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-1600|1&amp;15-7000|15&amp;30-4500|30&amp;45-3600|45&amp;60-2800|60&amp;75-2800|75&amp;90-2200|90&amp;105-2000|105&amp;120-1600|120&amp;135-1900|135&amp;150-1400|150&amp;180-2700|180&amp;210-2300|210&amp;240-2000|240&amp;270-1900|270&amp;300-1500|300&amp;360-2800|360&amp;420-2300|420&amp;480-1900|480&amp;540-1700|540&amp;600-1400|600&amp;720-2500|720&amp;840-2100|840&amp;960-1700|960&amp;1080-1500|1080&amp;1200-1500|1200&amp;1440-1500|1440&amp;1680-1000|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-300|1&amp;15-800|15&amp;30-500|30&amp;45-500|45&amp;60-400|60&amp;75-500|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-500|135&amp;150-400|150&amp;180-800|180&amp;210-800|210&amp;240-800|240&amp;270-800|270&amp;300-700|300&amp;360-1500|360&amp;420-1400|420&amp;480-1300|480&amp;540-400|540&amp;600-500|600&amp;720-500|720&amp;840-500|840&amp;960-500|960&amp;1080-100|1080&amp;1200-100|1200&amp;1440-100|1440&amp;1680-100|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="H71" s="27">
         <v>2000</v>
@@ -4257,12 +4286,15 @@
         <v>5</v>
       </c>
       <c r="E72" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="F72" s="24"/>
+        <v>100</v>
+      </c>
+      <c r="F72" s="24" t="str">
+        <f>F71</f>
+        <v>1000000&amp;999999999_4,25-0|26-0|27-0|28-0;5,25-0|26-0|27-0|28-0</v>
+      </c>
       <c r="G72" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
+        <v>1,0&amp;1-55000|1&amp;15-10000|15&amp;30-3000|30&amp;45-2200|45&amp;60-1100|60&amp;75-1200|75&amp;90-700|90&amp;105-800|105&amp;120-400|120&amp;135-300|135&amp;150-300|150&amp;180-100|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-100|300&amp;360-100|360&amp;420-100|420&amp;480-40|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-97900|1&amp;15-2000|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-97100|1&amp;15-2800|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-1600|1&amp;15-7000|15&amp;30-4500|30&amp;45-3600|45&amp;60-2800|60&amp;75-2800|75&amp;90-2200|90&amp;105-2000|105&amp;120-1600|120&amp;135-1900|135&amp;150-1400|150&amp;180-2700|180&amp;210-2300|210&amp;240-2000|240&amp;270-1900|270&amp;300-1500|300&amp;360-2800|360&amp;420-2300|420&amp;480-1900|480&amp;540-1700|540&amp;600-1400|600&amp;720-2500|720&amp;840-2100|840&amp;960-1700|960&amp;1080-1500|1080&amp;1200-1500|1200&amp;1440-1500|1440&amp;1680-1000|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-300|1&amp;15-800|15&amp;30-500|30&amp;45-500|45&amp;60-400|60&amp;75-500|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-500|135&amp;150-400|150&amp;180-800|180&amp;210-800|210&amp;240-800|240&amp;270-800|270&amp;300-700|300&amp;360-1500|360&amp;420-1400|420&amp;480-1300|480&amp;540-400|540&amp;600-500|600&amp;720-500|720&amp;840-500|840&amp;960-500|960&amp;1080-100|1080&amp;1200-100|1200&amp;1440-100|1440&amp;1680-100|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="H72" s="27">
         <v>0</v>
@@ -4288,12 +4320,15 @@
         <v>6</v>
       </c>
       <c r="E73" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="F73" s="24"/>
+        <v>69</v>
+      </c>
+      <c r="F73" s="24" t="str">
+        <f>F72</f>
+        <v>1000000&amp;999999999_4,25-0|26-0|27-0|28-0;5,25-0|26-0|27-0|28-0</v>
+      </c>
       <c r="G73" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
+        <v>1,0&amp;1-55000|1&amp;15-10000|15&amp;30-3000|30&amp;45-2200|45&amp;60-1100|60&amp;75-1200|75&amp;90-700|90&amp;105-800|105&amp;120-400|120&amp;135-300|135&amp;150-300|150&amp;180-100|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-100|300&amp;360-100|360&amp;420-100|420&amp;480-40|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-97900|1&amp;15-2000|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-97100|1&amp;15-2800|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-1600|1&amp;15-7000|15&amp;30-4500|30&amp;45-3600|45&amp;60-2800|60&amp;75-2800|75&amp;90-2200|90&amp;105-2000|105&amp;120-1600|120&amp;135-1900|135&amp;150-1400|150&amp;180-2700|180&amp;210-2300|210&amp;240-2000|240&amp;270-1900|270&amp;300-1500|300&amp;360-2800|360&amp;420-2300|420&amp;480-1900|480&amp;540-1700|540&amp;600-1400|600&amp;720-2500|720&amp;840-2100|840&amp;960-1700|960&amp;1080-1500|1080&amp;1200-1500|1200&amp;1440-1500|1440&amp;1680-1000|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-300|1&amp;15-800|15&amp;30-500|30&amp;45-500|45&amp;60-400|60&amp;75-500|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-500|135&amp;150-400|150&amp;180-800|180&amp;210-800|210&amp;240-800|240&amp;270-800|270&amp;300-700|300&amp;360-1500|360&amp;420-1400|420&amp;480-1300|480&amp;540-400|540&amp;600-500|600&amp;720-500|720&amp;840-500|840&amp;960-500|960&amp;1080-100|1080&amp;1200-100|1200&amp;1440-100|1440&amp;1680-100|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="H73" s="27">
         <v>-1000</v>
@@ -4319,12 +4354,15 @@
         <v>7</v>
       </c>
       <c r="E74" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="F74" s="24"/>
+        <v>43</v>
+      </c>
+      <c r="F74" s="24" t="str">
+        <f>F73</f>
+        <v>1000000&amp;999999999_4,25-0|26-0|27-0|28-0;5,25-0|26-0|27-0|28-0</v>
+      </c>
       <c r="G74" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
+        <v>1,0&amp;1-55000|1&amp;15-10000|15&amp;30-3000|30&amp;45-2200|45&amp;60-1100|60&amp;75-1200|75&amp;90-700|90&amp;105-800|105&amp;120-400|120&amp;135-300|135&amp;150-300|150&amp;180-100|180&amp;210-100|210&amp;240-100|240&amp;270-100|270&amp;300-100|300&amp;360-100|360&amp;420-100|420&amp;480-40|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-97900|1&amp;15-2000|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-97100|1&amp;15-2800|15&amp;30-100|30&amp;45-0|45&amp;60-0|60&amp;75-0|75&amp;90-0|90&amp;105-0|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-1600|1&amp;15-7000|15&amp;30-4500|30&amp;45-3600|45&amp;60-2800|60&amp;75-2800|75&amp;90-2200|90&amp;105-2000|105&amp;120-1600|120&amp;135-1900|135&amp;150-1400|150&amp;180-2700|180&amp;210-2300|210&amp;240-2000|240&amp;270-1900|270&amp;300-1500|300&amp;360-2800|360&amp;420-2300|420&amp;480-1900|480&amp;540-1700|540&amp;600-1400|600&amp;720-2500|720&amp;840-2100|840&amp;960-1700|960&amp;1080-1500|1080&amp;1200-1500|1200&amp;1440-1500|1440&amp;1680-1000|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;5,0&amp;1-300|1&amp;15-800|15&amp;30-500|30&amp;45-500|45&amp;60-400|60&amp;75-500|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-500|135&amp;150-400|150&amp;180-800|180&amp;210-800|210&amp;240-800|240&amp;270-800|270&amp;300-700|300&amp;360-1500|360&amp;420-1400|420&amp;480-1300|480&amp;540-400|540&amp;600-500|600&amp;720-500|720&amp;840-500|840&amp;960-500|960&amp;1080-100|1080&amp;1200-100|1200&amp;1440-100|1440&amp;1680-100|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0</v>
       </c>
       <c r="H74" s="27">
         <v>-999999</v>
@@ -4344,19 +4382,19 @@
         <v>102100</v>
       </c>
       <c r="C75" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D75" s="46">
         <v>1</v>
       </c>
       <c r="E75" s="47" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F75" s="24" t="s">
         <v>90</v>
       </c>
       <c r="G75" s="26" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H75" s="27">
         <v>8000</v>
@@ -4376,13 +4414,13 @@
         <v>102100</v>
       </c>
       <c r="C76" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D76" s="46">
         <v>2</v>
       </c>
       <c r="E76" s="47" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F76" s="24" t="s">
         <v>90</v>
@@ -4409,13 +4447,13 @@
         <v>102100</v>
       </c>
       <c r="C77" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D77" s="46">
         <v>3</v>
       </c>
       <c r="E77" s="47" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F77" s="24" t="s">
         <v>90</v>
@@ -4442,13 +4480,13 @@
         <v>102100</v>
       </c>
       <c r="C78" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D78" s="46">
         <v>4</v>
       </c>
       <c r="E78" s="47" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F78" s="24" t="s">
         <v>90</v>
@@ -4475,13 +4513,13 @@
         <v>102100</v>
       </c>
       <c r="C79" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D79" s="46">
         <v>5</v>
       </c>
       <c r="E79" s="47" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F79" s="24" t="s">
         <v>90</v>
@@ -4508,13 +4546,13 @@
         <v>102100</v>
       </c>
       <c r="C80" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D80" s="46">
         <v>6</v>
       </c>
       <c r="E80" s="47" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F80" s="24" t="s">
         <v>90</v>
@@ -4541,13 +4579,13 @@
         <v>102100</v>
       </c>
       <c r="C81" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D81" s="46">
         <v>7</v>
       </c>
       <c r="E81" s="47" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F81" s="24" t="s">
         <v>90</v>
@@ -4574,7 +4612,7 @@
         <v>102200</v>
       </c>
       <c r="C82" s="48" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D82" s="48">
         <v>1</v>
@@ -4583,10 +4621,10 @@
         <v>67</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G82" s="26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H82" s="27">
         <v>8000</v>
@@ -4606,16 +4644,16 @@
         <v>102200</v>
       </c>
       <c r="C83" s="48" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D83" s="48">
         <v>2</v>
       </c>
       <c r="E83" s="49" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G83" s="50" t="str">
         <f t="shared" ref="G83:G88" si="11">G82</f>
@@ -4639,16 +4677,16 @@
         <v>102200</v>
       </c>
       <c r="C84" s="48" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D84" s="48">
         <v>3</v>
       </c>
       <c r="E84" s="49" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G84" s="50" t="str">
         <f t="shared" si="11"/>
@@ -4672,7 +4710,7 @@
         <v>102200</v>
       </c>
       <c r="C85" s="48" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D85" s="48">
         <v>4</v>
@@ -4681,7 +4719,7 @@
         <v>68</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G85" s="50" t="str">
         <f t="shared" si="11"/>
@@ -4705,16 +4743,16 @@
         <v>102200</v>
       </c>
       <c r="C86" s="48" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D86" s="48">
         <v>5</v>
       </c>
       <c r="E86" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="F86" s="24" t="s">
         <v>119</v>
-      </c>
-      <c r="F86" s="24" t="s">
-        <v>115</v>
       </c>
       <c r="G86" s="50" t="str">
         <f t="shared" si="11"/>
@@ -4738,7 +4776,7 @@
         <v>102200</v>
       </c>
       <c r="C87" s="48" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D87" s="48">
         <v>6</v>
@@ -4747,7 +4785,7 @@
         <v>43</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G87" s="50" t="str">
         <f t="shared" si="11"/>
@@ -4771,7 +4809,7 @@
         <v>102200</v>
       </c>
       <c r="C88" s="48" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D88" s="48">
         <v>7</v>
@@ -4780,7 +4818,7 @@
         <v>43</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G88" s="50" t="str">
         <f t="shared" si="11"/>
@@ -4804,19 +4842,19 @@
         <v>102300</v>
       </c>
       <c r="C89" s="51" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D89" s="51">
         <v>1</v>
       </c>
       <c r="E89" s="52" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G89" s="26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H89" s="27">
         <v>8000</v>
@@ -4836,16 +4874,16 @@
         <v>102300</v>
       </c>
       <c r="C90" s="51" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D90" s="51">
         <v>2</v>
       </c>
       <c r="E90" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="F90" s="24" t="s">
         <v>124</v>
-      </c>
-      <c r="F90" s="24" t="s">
-        <v>122</v>
       </c>
       <c r="G90" s="53" t="str">
         <f t="shared" ref="G90:G95" si="12">G89</f>
@@ -4869,16 +4907,16 @@
         <v>102300</v>
       </c>
       <c r="C91" s="51" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D91" s="51">
         <v>3</v>
       </c>
       <c r="E91" s="52" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F91" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G91" s="53" t="str">
         <f t="shared" si="12"/>
@@ -4902,16 +4940,16 @@
         <v>102300</v>
       </c>
       <c r="C92" s="51" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D92" s="51">
         <v>4</v>
       </c>
       <c r="E92" s="52" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F92" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G92" s="53" t="str">
         <f t="shared" si="12"/>
@@ -4935,16 +4973,16 @@
         <v>102300</v>
       </c>
       <c r="C93" s="51" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D93" s="51">
         <v>5</v>
       </c>
       <c r="E93" s="52" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F93" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G93" s="53" t="str">
         <f t="shared" si="12"/>
@@ -4968,7 +5006,7 @@
         <v>102300</v>
       </c>
       <c r="C94" s="51" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D94" s="51">
         <v>6</v>
@@ -4977,7 +5015,7 @@
         <v>96</v>
       </c>
       <c r="F94" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G94" s="53" t="str">
         <f t="shared" si="12"/>
@@ -5001,7 +5039,7 @@
         <v>102300</v>
       </c>
       <c r="C95" s="51" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D95" s="51">
         <v>7</v>
@@ -5010,7 +5048,7 @@
         <v>43</v>
       </c>
       <c r="F95" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G95" s="53" t="str">
         <f t="shared" si="12"/>
@@ -5034,7 +5072,7 @@
         <v>102400</v>
       </c>
       <c r="C96" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D96" s="22">
         <v>1</v>
@@ -5064,7 +5102,7 @@
         <v>102400</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D97" s="22">
         <v>2</v>
@@ -5095,7 +5133,7 @@
         <v>102400</v>
       </c>
       <c r="C98" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D98" s="22">
         <v>3</v>
@@ -5126,7 +5164,7 @@
         <v>102400</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D99" s="22">
         <v>4</v>
@@ -5157,7 +5195,7 @@
         <v>102400</v>
       </c>
       <c r="C100" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D100" s="22">
         <v>5</v>
@@ -5188,7 +5226,7 @@
         <v>102400</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D101" s="22">
         <v>6</v>
@@ -5219,7 +5257,7 @@
         <v>102400</v>
       </c>
       <c r="C102" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D102" s="22">
         <v>7</v>
@@ -5250,7 +5288,7 @@
         <v>102500</v>
       </c>
       <c r="C103" s="54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D103" s="54">
         <v>1</v>
@@ -5262,7 +5300,7 @@
         <v>90</v>
       </c>
       <c r="G103" s="26" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H103" s="27">
         <v>8000</v>
@@ -5282,7 +5320,7 @@
         <v>102500</v>
       </c>
       <c r="C104" s="54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D104" s="54">
         <v>2</v>
@@ -5315,7 +5353,7 @@
         <v>102500</v>
       </c>
       <c r="C105" s="54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D105" s="54">
         <v>3</v>
@@ -5348,7 +5386,7 @@
         <v>102500</v>
       </c>
       <c r="C106" s="54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D106" s="54">
         <v>4</v>
@@ -5381,7 +5419,7 @@
         <v>102500</v>
       </c>
       <c r="C107" s="54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D107" s="54">
         <v>5</v>
@@ -5414,7 +5452,7 @@
         <v>102500</v>
       </c>
       <c r="C108" s="54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D108" s="54">
         <v>6</v>
@@ -5447,7 +5485,7 @@
         <v>102500</v>
       </c>
       <c r="C109" s="54" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D109" s="54">
         <v>7</v>
@@ -5480,7 +5518,7 @@
         <v>102600</v>
       </c>
       <c r="C110" s="57" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D110" s="57">
         <v>1</v>
@@ -5510,7 +5548,7 @@
         <v>102600</v>
       </c>
       <c r="C111" s="57" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D111" s="57">
         <v>2</v>
@@ -5541,7 +5579,7 @@
         <v>102600</v>
       </c>
       <c r="C112" s="57" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D112" s="57">
         <v>3</v>
@@ -5572,7 +5610,7 @@
         <v>102600</v>
       </c>
       <c r="C113" s="57" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D113" s="57">
         <v>4</v>
@@ -5603,7 +5641,7 @@
         <v>102600</v>
       </c>
       <c r="C114" s="57" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D114" s="57">
         <v>5</v>
@@ -5634,7 +5672,7 @@
         <v>102600</v>
       </c>
       <c r="C115" s="57" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D115" s="57">
         <v>6</v>
@@ -5665,7 +5703,7 @@
         <v>102600</v>
       </c>
       <c r="C116" s="57" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D116" s="57">
         <v>7</v>
@@ -5696,7 +5734,7 @@
         <v>102700</v>
       </c>
       <c r="C117" s="54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D117" s="54">
         <v>1</v>
@@ -5706,7 +5744,7 @@
       </c>
       <c r="F117" s="24"/>
       <c r="G117" s="56" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H117" s="27">
         <v>8000</v>
@@ -5726,7 +5764,7 @@
         <v>102700</v>
       </c>
       <c r="C118" s="54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D118" s="54">
         <v>2</v>
@@ -5757,7 +5795,7 @@
         <v>102700</v>
       </c>
       <c r="C119" s="54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D119" s="54">
         <v>3</v>
@@ -5788,7 +5826,7 @@
         <v>102700</v>
       </c>
       <c r="C120" s="54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D120" s="54">
         <v>4</v>
@@ -5819,7 +5857,7 @@
         <v>102700</v>
       </c>
       <c r="C121" s="54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D121" s="54">
         <v>5</v>
@@ -5850,7 +5888,7 @@
         <v>102700</v>
       </c>
       <c r="C122" s="54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D122" s="54">
         <v>6</v>
@@ -5881,7 +5919,7 @@
         <v>102700</v>
       </c>
       <c r="C123" s="54" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D123" s="54">
         <v>7</v>
@@ -5912,7 +5950,7 @@
         <v>102800</v>
       </c>
       <c r="C124" s="39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D124" s="39">
         <v>1</v>
@@ -5942,7 +5980,7 @@
         <v>102800</v>
       </c>
       <c r="C125" s="39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D125" s="39">
         <v>2</v>
@@ -5973,7 +6011,7 @@
         <v>102800</v>
       </c>
       <c r="C126" s="39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D126" s="39">
         <v>3</v>
@@ -6004,7 +6042,7 @@
         <v>102800</v>
       </c>
       <c r="C127" s="39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D127" s="39">
         <v>4</v>
@@ -6035,7 +6073,7 @@
         <v>102800</v>
       </c>
       <c r="C128" s="39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D128" s="39">
         <v>5</v>
@@ -6066,7 +6104,7 @@
         <v>102800</v>
       </c>
       <c r="C129" s="39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D129" s="39">
         <v>6</v>
@@ -6097,7 +6135,7 @@
         <v>102800</v>
       </c>
       <c r="C130" s="39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D130" s="39">
         <v>7</v>
@@ -6128,17 +6166,17 @@
         <v>103100</v>
       </c>
       <c r="C131" s="61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D131" s="61">
         <v>1</v>
       </c>
       <c r="E131" s="62" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F131" s="24"/>
       <c r="G131" s="63" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H131" s="27">
         <v>8000</v>
@@ -6158,13 +6196,13 @@
         <v>103100</v>
       </c>
       <c r="C132" s="61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D132" s="61">
         <v>2</v>
       </c>
       <c r="E132" s="62" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F132" s="24"/>
       <c r="G132" s="63" t="str">
@@ -6189,13 +6227,13 @@
         <v>103100</v>
       </c>
       <c r="C133" s="61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D133" s="61">
         <v>3</v>
       </c>
       <c r="E133" s="62" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F133" s="24"/>
       <c r="G133" s="63" t="str">
@@ -6220,13 +6258,13 @@
         <v>103100</v>
       </c>
       <c r="C134" s="61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D134" s="61">
         <v>4</v>
       </c>
       <c r="E134" s="62" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F134" s="24"/>
       <c r="G134" s="63" t="str">
@@ -6251,13 +6289,13 @@
         <v>103100</v>
       </c>
       <c r="C135" s="61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D135" s="61">
         <v>5</v>
       </c>
       <c r="E135" s="62" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F135" s="24"/>
       <c r="G135" s="63" t="str">
@@ -6282,13 +6320,13 @@
         <v>103100</v>
       </c>
       <c r="C136" s="61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D136" s="61">
         <v>6</v>
       </c>
       <c r="E136" s="62" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F136" s="24"/>
       <c r="G136" s="63" t="str">
@@ -6313,13 +6351,13 @@
         <v>103100</v>
       </c>
       <c r="C137" s="61" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D137" s="61">
         <v>7</v>
       </c>
       <c r="E137" s="62" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F137" s="24"/>
       <c r="G137" s="63" t="str">
@@ -6344,17 +6382,17 @@
         <v>103400</v>
       </c>
       <c r="C138" s="65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D138" s="65">
         <v>1</v>
       </c>
       <c r="E138" s="66" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F138" s="24"/>
       <c r="G138" s="26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H138" s="27">
         <v>8000</v>
@@ -6374,13 +6412,13 @@
         <v>103400</v>
       </c>
       <c r="C139" s="65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D139" s="65">
         <v>2</v>
       </c>
       <c r="E139" s="66" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F139" s="24"/>
       <c r="G139" s="67" t="str">
@@ -6405,7 +6443,7 @@
         <v>103400</v>
       </c>
       <c r="C140" s="65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D140" s="65">
         <v>3</v>
@@ -6436,13 +6474,13 @@
         <v>103400</v>
       </c>
       <c r="C141" s="65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D141" s="65">
         <v>4</v>
       </c>
       <c r="E141" s="66" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F141" s="24"/>
       <c r="G141" s="67" t="str">
@@ -6467,13 +6505,13 @@
         <v>103400</v>
       </c>
       <c r="C142" s="65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D142" s="65">
         <v>5</v>
       </c>
       <c r="E142" s="66" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F142" s="24"/>
       <c r="G142" s="67" t="str">
@@ -6498,7 +6536,7 @@
         <v>103400</v>
       </c>
       <c r="C143" s="65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D143" s="65">
         <v>6</v>
@@ -6529,7 +6567,7 @@
         <v>103400</v>
       </c>
       <c r="C144" s="65" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D144" s="65">
         <v>7</v>
@@ -6560,17 +6598,17 @@
         <v>103401</v>
       </c>
       <c r="C145" s="68" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D145" s="68">
         <v>1</v>
       </c>
       <c r="E145" s="69" t="s">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="F145" s="24"/>
       <c r="G145" s="70" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H145" s="27">
         <v>8000</v>
@@ -6590,18 +6628,18 @@
         <v>103401</v>
       </c>
       <c r="C146" s="68" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D146" s="68">
         <v>2</v>
       </c>
       <c r="E146" s="69" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="F146" s="24"/>
       <c r="G146" s="70" t="str">
         <f t="shared" ref="G146:G151" si="20">G145</f>
-        <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
       <c r="H146" s="27">
         <v>6000</v>
@@ -6621,18 +6659,18 @@
         <v>103401</v>
       </c>
       <c r="C147" s="68" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D147" s="68">
         <v>3</v>
       </c>
       <c r="E147" s="69" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F147" s="24"/>
       <c r="G147" s="70" t="str">
         <f t="shared" si="20"/>
-        <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
       <c r="H147" s="27">
         <v>4000</v>
@@ -6652,18 +6690,18 @@
         <v>103401</v>
       </c>
       <c r="C148" s="68" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D148" s="68">
         <v>4</v>
       </c>
       <c r="E148" s="69" t="s">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="F148" s="24"/>
       <c r="G148" s="70" t="str">
         <f t="shared" si="20"/>
-        <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
       <c r="H148" s="27">
         <v>2000</v>
@@ -6683,18 +6721,18 @@
         <v>103401</v>
       </c>
       <c r="C149" s="68" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D149" s="68">
         <v>5</v>
       </c>
       <c r="E149" s="69" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
       <c r="F149" s="24"/>
       <c r="G149" s="70" t="str">
         <f t="shared" si="20"/>
-        <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
       <c r="H149" s="27">
         <v>0</v>
@@ -6714,18 +6752,18 @@
         <v>103401</v>
       </c>
       <c r="C150" s="68" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D150" s="68">
         <v>6</v>
       </c>
       <c r="E150" s="69" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F150" s="24"/>
       <c r="G150" s="70" t="str">
         <f t="shared" si="20"/>
-        <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
       <c r="H150" s="27">
         <v>-1000</v>
@@ -6745,18 +6783,18 @@
         <v>103401</v>
       </c>
       <c r="C151" s="68" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D151" s="68">
         <v>7</v>
       </c>
       <c r="E151" s="69" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F151" s="24"/>
       <c r="G151" s="70" t="str">
         <f t="shared" si="20"/>
-        <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
       <c r="H151" s="27">
         <v>-999999</v>
@@ -6776,7 +6814,7 @@
         <v>103500</v>
       </c>
       <c r="C152" s="72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D152" s="72">
         <v>1</v>
@@ -6786,7 +6824,7 @@
       </c>
       <c r="F152" s="24"/>
       <c r="G152" s="26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H152" s="27">
         <v>8000</v>
@@ -6806,13 +6844,13 @@
         <v>103500</v>
       </c>
       <c r="C153" s="72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D153" s="72">
         <v>2</v>
       </c>
       <c r="E153" s="73" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F153" s="24"/>
       <c r="G153" s="74" t="str">
@@ -6837,13 +6875,13 @@
         <v>103500</v>
       </c>
       <c r="C154" s="72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D154" s="72">
         <v>3</v>
       </c>
       <c r="E154" s="73" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F154" s="24"/>
       <c r="G154" s="74" t="str">
@@ -6868,13 +6906,13 @@
         <v>103500</v>
       </c>
       <c r="C155" s="72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D155" s="72">
         <v>4</v>
       </c>
       <c r="E155" s="73" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F155" s="24"/>
       <c r="G155" s="74" t="str">
@@ -6899,13 +6937,13 @@
         <v>103500</v>
       </c>
       <c r="C156" s="72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D156" s="72">
         <v>5</v>
       </c>
       <c r="E156" s="73" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F156" s="24"/>
       <c r="G156" s="74" t="str">
@@ -6930,7 +6968,7 @@
         <v>103500</v>
       </c>
       <c r="C157" s="72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D157" s="72">
         <v>6</v>
@@ -6961,7 +6999,7 @@
         <v>103500</v>
       </c>
       <c r="C158" s="72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D158" s="72">
         <v>7</v>
@@ -6992,7 +7030,7 @@
         <v>103501</v>
       </c>
       <c r="C159" s="75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D159" s="75">
         <v>1</v>
@@ -7002,7 +7040,7 @@
       </c>
       <c r="F159" s="24"/>
       <c r="G159" s="26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H159" s="27">
         <v>8000</v>
@@ -7022,13 +7060,13 @@
         <v>103501</v>
       </c>
       <c r="C160" s="75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D160" s="75">
         <v>2</v>
       </c>
       <c r="E160" s="76" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F160" s="24"/>
       <c r="G160" s="31" t="str">
@@ -7053,13 +7091,13 @@
         <v>103501</v>
       </c>
       <c r="C161" s="75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D161" s="75">
         <v>3</v>
       </c>
       <c r="E161" s="76" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F161" s="24"/>
       <c r="G161" s="31" t="str">
@@ -7084,13 +7122,13 @@
         <v>103501</v>
       </c>
       <c r="C162" s="75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D162" s="75">
         <v>4</v>
       </c>
       <c r="E162" s="76" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F162" s="24"/>
       <c r="G162" s="31" t="str">
@@ -7115,13 +7153,13 @@
         <v>103501</v>
       </c>
       <c r="C163" s="75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D163" s="75">
         <v>5</v>
       </c>
       <c r="E163" s="76" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F163" s="24"/>
       <c r="G163" s="31" t="str">
@@ -7146,7 +7184,7 @@
         <v>103501</v>
       </c>
       <c r="C164" s="75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D164" s="75">
         <v>6</v>
@@ -7177,7 +7215,7 @@
         <v>103501</v>
       </c>
       <c r="C165" s="75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D165" s="75">
         <v>7</v>
@@ -7208,17 +7246,17 @@
         <v>103600</v>
       </c>
       <c r="C166" s="77" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D166" s="77">
         <v>1</v>
       </c>
       <c r="E166" s="78" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F166" s="24"/>
       <c r="G166" s="79" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H166" s="27">
         <v>8000</v>
@@ -7238,7 +7276,7 @@
         <v>103600</v>
       </c>
       <c r="C167" s="77" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D167" s="77">
         <v>2</v>
@@ -7269,13 +7307,13 @@
         <v>103600</v>
       </c>
       <c r="C168" s="77" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D168" s="77">
         <v>3</v>
       </c>
       <c r="E168" s="78" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F168" s="24"/>
       <c r="G168" s="79" t="str">
@@ -7300,13 +7338,13 @@
         <v>103600</v>
       </c>
       <c r="C169" s="77" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D169" s="77">
         <v>4</v>
       </c>
       <c r="E169" s="78" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F169" s="24"/>
       <c r="G169" s="79" t="str">
@@ -7331,7 +7369,7 @@
         <v>103600</v>
       </c>
       <c r="C170" s="77" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D170" s="77">
         <v>5</v>
@@ -7362,7 +7400,7 @@
         <v>103600</v>
       </c>
       <c r="C171" s="77" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D171" s="77">
         <v>6</v>
@@ -7393,7 +7431,7 @@
         <v>103600</v>
       </c>
       <c r="C172" s="77" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D172" s="77">
         <v>7</v>
@@ -7424,17 +7462,17 @@
         <v>103800</v>
       </c>
       <c r="C173" s="81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D173" s="81">
         <v>1</v>
       </c>
       <c r="E173" s="82" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F173" s="24"/>
       <c r="G173" s="83" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H173" s="27">
         <v>8000</v>
@@ -7454,13 +7492,13 @@
         <v>103800</v>
       </c>
       <c r="C174" s="81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D174" s="81">
         <v>2</v>
       </c>
       <c r="E174" s="82" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F174" s="24"/>
       <c r="G174" s="83" t="str">
@@ -7485,13 +7523,13 @@
         <v>103800</v>
       </c>
       <c r="C175" s="81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D175" s="81">
         <v>3</v>
       </c>
       <c r="E175" s="82" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F175" s="24"/>
       <c r="G175" s="83" t="str">
@@ -7516,13 +7554,13 @@
         <v>103800</v>
       </c>
       <c r="C176" s="81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D176" s="81">
         <v>4</v>
       </c>
       <c r="E176" s="82" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F176" s="24"/>
       <c r="G176" s="83" t="str">
@@ -7547,13 +7585,13 @@
         <v>103800</v>
       </c>
       <c r="C177" s="81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D177" s="81">
         <v>5</v>
       </c>
       <c r="E177" s="82" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F177" s="24"/>
       <c r="G177" s="83" t="str">
@@ -7578,13 +7616,13 @@
         <v>103800</v>
       </c>
       <c r="C178" s="81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D178" s="81">
         <v>6</v>
       </c>
       <c r="E178" s="82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F178" s="24"/>
       <c r="G178" s="83" t="str">
@@ -7609,13 +7647,13 @@
         <v>103800</v>
       </c>
       <c r="C179" s="81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D179" s="81">
         <v>7</v>
       </c>
       <c r="E179" s="82" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F179" s="24"/>
       <c r="G179" s="83" t="str">
@@ -7640,17 +7678,17 @@
         <v>103700</v>
       </c>
       <c r="C180" s="77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D180" s="77">
         <v>1</v>
       </c>
       <c r="E180" s="78" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F180" s="24"/>
       <c r="G180" s="79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H180" s="27">
         <v>8000</v>
@@ -7670,13 +7708,13 @@
         <v>103700</v>
       </c>
       <c r="C181" s="77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D181" s="77">
         <v>2</v>
       </c>
       <c r="E181" s="78" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F181" s="24"/>
       <c r="G181" s="79" t="str">
@@ -7701,13 +7739,13 @@
         <v>103700</v>
       </c>
       <c r="C182" s="77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D182" s="77">
         <v>3</v>
       </c>
       <c r="E182" s="78" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F182" s="24"/>
       <c r="G182" s="79" t="str">
@@ -7732,13 +7770,13 @@
         <v>103700</v>
       </c>
       <c r="C183" s="77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D183" s="77">
         <v>4</v>
       </c>
       <c r="E183" s="78" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F183" s="24"/>
       <c r="G183" s="79" t="str">
@@ -7763,13 +7801,13 @@
         <v>103700</v>
       </c>
       <c r="C184" s="77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D184" s="77">
         <v>5</v>
       </c>
       <c r="E184" s="78" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F184" s="24"/>
       <c r="G184" s="79" t="str">
@@ -7794,7 +7832,7 @@
         <v>103700</v>
       </c>
       <c r="C185" s="77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D185" s="77">
         <v>6</v>
@@ -7825,13 +7863,13 @@
         <v>103700</v>
       </c>
       <c r="C186" s="77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D186" s="77">
         <v>7</v>
       </c>
       <c r="E186" s="78" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F186" s="24"/>
       <c r="G186" s="79" t="str">
@@ -7856,17 +7894,17 @@
         <v>103900</v>
       </c>
       <c r="C187" s="85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D187" s="85">
         <v>1</v>
       </c>
       <c r="E187" s="86" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F187" s="24"/>
       <c r="G187" s="32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H187" s="27">
         <v>8000</v>
@@ -7886,13 +7924,13 @@
         <v>103900</v>
       </c>
       <c r="C188" s="85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D188" s="85">
         <v>2</v>
       </c>
       <c r="E188" s="86" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F188" s="24"/>
       <c r="G188" s="32" t="str">
@@ -7917,13 +7955,13 @@
         <v>103900</v>
       </c>
       <c r="C189" s="85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D189" s="85">
         <v>3</v>
       </c>
       <c r="E189" s="86" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F189" s="24"/>
       <c r="G189" s="32" t="str">
@@ -7948,13 +7986,13 @@
         <v>103900</v>
       </c>
       <c r="C190" s="85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D190" s="85">
         <v>4</v>
       </c>
       <c r="E190" s="86" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F190" s="24"/>
       <c r="G190" s="32" t="str">
@@ -7979,13 +8017,13 @@
         <v>103900</v>
       </c>
       <c r="C191" s="85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D191" s="85">
         <v>5</v>
       </c>
       <c r="E191" s="86" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F191" s="24"/>
       <c r="G191" s="32" t="str">
@@ -8010,13 +8048,13 @@
         <v>103900</v>
       </c>
       <c r="C192" s="85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D192" s="85">
         <v>6</v>
       </c>
       <c r="E192" s="86" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F192" s="24"/>
       <c r="G192" s="32" t="str">
@@ -8041,13 +8079,13 @@
         <v>103900</v>
       </c>
       <c r="C193" s="85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D193" s="85">
         <v>7</v>
       </c>
       <c r="E193" s="86" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F193" s="24"/>
       <c r="G193" s="32" t="str">
@@ -8072,17 +8110,19 @@
         <v>104000</v>
       </c>
       <c r="C194" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D194" s="68">
         <v>1</v>
       </c>
       <c r="E194" s="69" t="s">
-        <v>80</v>
-      </c>
-      <c r="F194" s="24"/>
+        <v>155</v>
+      </c>
+      <c r="F194" s="24" t="s">
+        <v>189</v>
+      </c>
       <c r="G194" s="70" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H194" s="27">
         <v>8000</v>
@@ -8102,18 +8142,21 @@
         <v>104000</v>
       </c>
       <c r="C195" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D195" s="68">
         <v>2</v>
       </c>
       <c r="E195" s="69" t="s">
-        <v>82</v>
-      </c>
-      <c r="F195" s="24"/>
+        <v>191</v>
+      </c>
+      <c r="F195" s="24" t="str">
+        <f t="shared" ref="F195:F200" si="27">F194</f>
+        <v>1000000&amp;999999999_2,27-0|28-0|29-0|30-0|31-0|32-0|33-0|34-0</v>
+      </c>
       <c r="G195" s="70" t="str">
-        <f t="shared" ref="G195:G200" si="27">G194</f>
-        <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
+        <f t="shared" ref="G195:G200" si="28">G194</f>
+        <v>1,0&amp;1-60000|1&amp;40-20000|40&amp;80-6000|80&amp;120-2000|120&amp;160-2800|160&amp;200-1000|200&amp;240-1000|240&amp;280-500|280&amp;320-500|320&amp;360-600|360&amp;400-100|400&amp;480-100|480&amp;560-100|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-200|40&amp;80-400|80&amp;120-500|120&amp;160-600|160&amp;200-700|200&amp;240-700|240&amp;280-800|280&amp;320-900|320&amp;360-900|360&amp;400-1000|400&amp;480-2100|480&amp;560-2300|560&amp;640-2400|640&amp;720-2500|720&amp;800-2600|800&amp;960-5200|960&amp;1120-4000|1120&amp;1280-3000|1280&amp;1440-2000|1440&amp;1600-2000|1600&amp;1920-2000|1920&amp;2240-2000|2240&amp;2560-2000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1100|6400&amp;7680-1000|7680&amp;8960-300|8960&amp;10240-100|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;3,0&amp;1-84600|1&amp;40-13400|40&amp;80-1400|80&amp;120-300|120&amp;160-100|160&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
       <c r="H195" s="27">
         <v>6000</v>
@@ -8133,18 +8176,21 @@
         <v>104000</v>
       </c>
       <c r="C196" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D196" s="68">
         <v>3</v>
       </c>
       <c r="E196" s="69" t="s">
-        <v>83</v>
-      </c>
-      <c r="F196" s="24"/>
+        <v>192</v>
+      </c>
+      <c r="F196" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>1000000&amp;999999999_2,27-0|28-0|29-0|30-0|31-0|32-0|33-0|34-0</v>
+      </c>
       <c r="G196" s="70" t="str">
-        <f t="shared" si="27"/>
-        <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
+        <f t="shared" si="28"/>
+        <v>1,0&amp;1-60000|1&amp;40-20000|40&amp;80-6000|80&amp;120-2000|120&amp;160-2800|160&amp;200-1000|200&amp;240-1000|240&amp;280-500|280&amp;320-500|320&amp;360-600|360&amp;400-100|400&amp;480-100|480&amp;560-100|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-200|40&amp;80-400|80&amp;120-500|120&amp;160-600|160&amp;200-700|200&amp;240-700|240&amp;280-800|280&amp;320-900|320&amp;360-900|360&amp;400-1000|400&amp;480-2100|480&amp;560-2300|560&amp;640-2400|640&amp;720-2500|720&amp;800-2600|800&amp;960-5200|960&amp;1120-4000|1120&amp;1280-3000|1280&amp;1440-2000|1440&amp;1600-2000|1600&amp;1920-2000|1920&amp;2240-2000|2240&amp;2560-2000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1100|6400&amp;7680-1000|7680&amp;8960-300|8960&amp;10240-100|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;3,0&amp;1-84600|1&amp;40-13400|40&amp;80-1400|80&amp;120-300|120&amp;160-100|160&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
       <c r="H196" s="27">
         <v>4000</v>
@@ -8164,18 +8210,21 @@
         <v>104000</v>
       </c>
       <c r="C197" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D197" s="68">
         <v>4</v>
       </c>
       <c r="E197" s="69" t="s">
-        <v>84</v>
-      </c>
-      <c r="F197" s="24"/>
+        <v>89</v>
+      </c>
+      <c r="F197" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>1000000&amp;999999999_2,27-0|28-0|29-0|30-0|31-0|32-0|33-0|34-0</v>
+      </c>
       <c r="G197" s="70" t="str">
-        <f t="shared" si="27"/>
-        <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
+        <f t="shared" si="28"/>
+        <v>1,0&amp;1-60000|1&amp;40-20000|40&amp;80-6000|80&amp;120-2000|120&amp;160-2800|160&amp;200-1000|200&amp;240-1000|240&amp;280-500|280&amp;320-500|320&amp;360-600|360&amp;400-100|400&amp;480-100|480&amp;560-100|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-200|40&amp;80-400|80&amp;120-500|120&amp;160-600|160&amp;200-700|200&amp;240-700|240&amp;280-800|280&amp;320-900|320&amp;360-900|360&amp;400-1000|400&amp;480-2100|480&amp;560-2300|560&amp;640-2400|640&amp;720-2500|720&amp;800-2600|800&amp;960-5200|960&amp;1120-4000|1120&amp;1280-3000|1280&amp;1440-2000|1440&amp;1600-2000|1600&amp;1920-2000|1920&amp;2240-2000|2240&amp;2560-2000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1100|6400&amp;7680-1000|7680&amp;8960-300|8960&amp;10240-100|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;3,0&amp;1-84600|1&amp;40-13400|40&amp;80-1400|80&amp;120-300|120&amp;160-100|160&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
       <c r="H197" s="27">
         <v>2000</v>
@@ -8195,18 +8244,21 @@
         <v>104000</v>
       </c>
       <c r="C198" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D198" s="68">
         <v>5</v>
       </c>
       <c r="E198" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F198" s="24"/>
+        <v>193</v>
+      </c>
+      <c r="F198" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>1000000&amp;999999999_2,27-0|28-0|29-0|30-0|31-0|32-0|33-0|34-0</v>
+      </c>
       <c r="G198" s="70" t="str">
-        <f t="shared" si="27"/>
-        <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
+        <f t="shared" si="28"/>
+        <v>1,0&amp;1-60000|1&amp;40-20000|40&amp;80-6000|80&amp;120-2000|120&amp;160-2800|160&amp;200-1000|200&amp;240-1000|240&amp;280-500|280&amp;320-500|320&amp;360-600|360&amp;400-100|400&amp;480-100|480&amp;560-100|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-200|40&amp;80-400|80&amp;120-500|120&amp;160-600|160&amp;200-700|200&amp;240-700|240&amp;280-800|280&amp;320-900|320&amp;360-900|360&amp;400-1000|400&amp;480-2100|480&amp;560-2300|560&amp;640-2400|640&amp;720-2500|720&amp;800-2600|800&amp;960-5200|960&amp;1120-4000|1120&amp;1280-3000|1280&amp;1440-2000|1440&amp;1600-2000|1600&amp;1920-2000|1920&amp;2240-2000|2240&amp;2560-2000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1100|6400&amp;7680-1000|7680&amp;8960-300|8960&amp;10240-100|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;3,0&amp;1-84600|1&amp;40-13400|40&amp;80-1400|80&amp;120-300|120&amp;160-100|160&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
       <c r="H198" s="27">
         <v>0</v>
@@ -8226,18 +8278,21 @@
         <v>104000</v>
       </c>
       <c r="C199" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D199" s="68">
         <v>6</v>
       </c>
       <c r="E199" s="69" t="s">
-        <v>86</v>
-      </c>
-      <c r="F199" s="24"/>
+        <v>194</v>
+      </c>
+      <c r="F199" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>1000000&amp;999999999_2,27-0|28-0|29-0|30-0|31-0|32-0|33-0|34-0</v>
+      </c>
       <c r="G199" s="70" t="str">
-        <f t="shared" si="27"/>
-        <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
+        <f t="shared" si="28"/>
+        <v>1,0&amp;1-60000|1&amp;40-20000|40&amp;80-6000|80&amp;120-2000|120&amp;160-2800|160&amp;200-1000|200&amp;240-1000|240&amp;280-500|280&amp;320-500|320&amp;360-600|360&amp;400-100|400&amp;480-100|480&amp;560-100|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-200|40&amp;80-400|80&amp;120-500|120&amp;160-600|160&amp;200-700|200&amp;240-700|240&amp;280-800|280&amp;320-900|320&amp;360-900|360&amp;400-1000|400&amp;480-2100|480&amp;560-2300|560&amp;640-2400|640&amp;720-2500|720&amp;800-2600|800&amp;960-5200|960&amp;1120-4000|1120&amp;1280-3000|1280&amp;1440-2000|1440&amp;1600-2000|1600&amp;1920-2000|1920&amp;2240-2000|2240&amp;2560-2000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1100|6400&amp;7680-1000|7680&amp;8960-300|8960&amp;10240-100|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;3,0&amp;1-84600|1&amp;40-13400|40&amp;80-1400|80&amp;120-300|120&amp;160-100|160&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
       <c r="H199" s="27">
         <v>-1000</v>
@@ -8257,18 +8312,21 @@
         <v>104000</v>
       </c>
       <c r="C200" s="68" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D200" s="68">
         <v>7</v>
       </c>
       <c r="E200" s="69" t="s">
-        <v>87</v>
-      </c>
-      <c r="F200" s="24"/>
+        <v>43</v>
+      </c>
+      <c r="F200" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>1000000&amp;999999999_2,27-0|28-0|29-0|30-0|31-0|32-0|33-0|34-0</v>
+      </c>
       <c r="G200" s="70" t="str">
-        <f t="shared" si="27"/>
-        <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
+        <f t="shared" si="28"/>
+        <v>1,0&amp;1-60000|1&amp;40-20000|40&amp;80-6000|80&amp;120-2000|120&amp;160-2800|160&amp;200-1000|200&amp;240-1000|240&amp;280-500|280&amp;320-500|320&amp;360-600|360&amp;400-100|400&amp;480-100|480&amp;560-100|560&amp;640-100|640&amp;720-100|720&amp;800-100|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-200|40&amp;80-400|80&amp;120-500|120&amp;160-600|160&amp;200-700|200&amp;240-700|240&amp;280-800|280&amp;320-900|320&amp;360-900|360&amp;400-1000|400&amp;480-2100|480&amp;560-2300|560&amp;640-2400|640&amp;720-2500|720&amp;800-2600|800&amp;960-5200|960&amp;1120-4000|1120&amp;1280-3000|1280&amp;1440-2000|1440&amp;1600-2000|1600&amp;1920-2000|1920&amp;2240-2000|2240&amp;2560-2000|2560&amp;2880-2000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1100|6400&amp;7680-1000|7680&amp;8960-300|8960&amp;10240-100|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;3,0&amp;1-84600|1&amp;40-13400|40&amp;80-1400|80&amp;120-300|120&amp;160-100|160&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
       <c r="H200" s="27">
         <v>-999999</v>
@@ -8288,7 +8346,7 @@
         <v>105000</v>
       </c>
       <c r="C201" s="77" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D201" s="77">
         <v>1</v>
@@ -8318,7 +8376,7 @@
         <v>105000</v>
       </c>
       <c r="C202" s="77" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D202" s="77">
         <v>2</v>
@@ -8348,7 +8406,7 @@
         <v>105000</v>
       </c>
       <c r="C203" s="77" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D203" s="77">
         <v>3</v>
@@ -8378,7 +8436,7 @@
         <v>105000</v>
       </c>
       <c r="C204" s="77" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D204" s="77">
         <v>4</v>
@@ -8408,7 +8466,7 @@
         <v>105000</v>
       </c>
       <c r="C205" s="77" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D205" s="77">
         <v>5</v>
@@ -8438,7 +8496,7 @@
         <v>105000</v>
       </c>
       <c r="C206" s="77" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D206" s="77">
         <v>6</v>
@@ -8468,7 +8526,7 @@
         <v>105000</v>
       </c>
       <c r="C207" s="77" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D207" s="77">
         <v>7</v>
@@ -8498,7 +8556,7 @@
         <v>105100</v>
       </c>
       <c r="C208" s="88" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D208" s="88">
         <v>1</v>
@@ -8528,7 +8586,7 @@
         <v>105100</v>
       </c>
       <c r="C209" s="88" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D209" s="88">
         <v>2</v>
@@ -8558,7 +8616,7 @@
         <v>105100</v>
       </c>
       <c r="C210" s="88" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D210" s="88">
         <v>3</v>
@@ -8588,7 +8646,7 @@
         <v>105100</v>
       </c>
       <c r="C211" s="88" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D211" s="88">
         <v>4</v>
@@ -8618,7 +8676,7 @@
         <v>105100</v>
       </c>
       <c r="C212" s="88" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D212" s="88">
         <v>5</v>
@@ -8648,7 +8706,7 @@
         <v>105100</v>
       </c>
       <c r="C213" s="88" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D213" s="88">
         <v>6</v>
@@ -8678,7 +8736,7 @@
         <v>105100</v>
       </c>
       <c r="C214" s="88" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D214" s="88">
         <v>7</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -171,7 +171,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="206">
   <si>
     <t>id</t>
   </si>
@@ -771,6 +771,24 @@
   </si>
   <si>
     <t>极速糖果1000</t>
+  </si>
+  <si>
+    <t>伽罗宝石</t>
+  </si>
+  <si>
+    <t>1_8650|2_1300</t>
+  </si>
+  <si>
+    <t>1_8850|2_1100</t>
+  </si>
+  <si>
+    <t>1_9150|2_800</t>
+  </si>
+  <si>
+    <t>1_9500|2_500</t>
+  </si>
+  <si>
+    <t>1_9800|2_200</t>
   </si>
 </sst>
 </file>
@@ -959,7 +977,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="47">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1071,6 +1089,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1361,7 +1385,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1385,16 +1409,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1403,90 +1427,90 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1747,6 +1771,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -2068,7 +2099,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K249"/>
+  <dimension ref="A1:K256"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
@@ -9754,6 +9785,216 @@
         <v>190</v>
       </c>
     </row>
+    <row r="250" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A250" s="103">
+        <v>55001</v>
+      </c>
+      <c r="B250" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C250" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="D250" s="69">
+        <v>1</v>
+      </c>
+      <c r="E250" s="70" t="s">
+        <v>201</v>
+      </c>
+      <c r="F250" s="99"/>
+      <c r="G250" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H250" s="28">
+        <v>8000</v>
+      </c>
+      <c r="I250" s="28">
+        <v>999999</v>
+      </c>
+      <c r="J250" s="105" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="251" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A251" s="103">
+        <v>55002</v>
+      </c>
+      <c r="B251" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C251" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="D251" s="69">
+        <v>2</v>
+      </c>
+      <c r="E251" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="F251" s="99"/>
+      <c r="G251" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H251" s="28">
+        <v>6000</v>
+      </c>
+      <c r="I251" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J251" s="105" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="252" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A252" s="103">
+        <v>55003</v>
+      </c>
+      <c r="B252" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C252" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="D252" s="69">
+        <v>3</v>
+      </c>
+      <c r="E252" s="70" t="s">
+        <v>203</v>
+      </c>
+      <c r="F252" s="99"/>
+      <c r="G252" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H252" s="28">
+        <v>4000</v>
+      </c>
+      <c r="I252" s="28">
+        <v>6000</v>
+      </c>
+      <c r="J252" s="105" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="253" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A253" s="103">
+        <v>55004</v>
+      </c>
+      <c r="B253" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C253" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="D253" s="69">
+        <v>4</v>
+      </c>
+      <c r="E253" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="F253" s="99"/>
+      <c r="G253" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H253" s="28">
+        <v>2000</v>
+      </c>
+      <c r="I253" s="28">
+        <v>4000</v>
+      </c>
+      <c r="J253" s="105" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="254" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A254" s="103">
+        <v>55005</v>
+      </c>
+      <c r="B254" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C254" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="D254" s="69">
+        <v>5</v>
+      </c>
+      <c r="E254" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="F254" s="99"/>
+      <c r="G254" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H254" s="28">
+        <v>0</v>
+      </c>
+      <c r="I254" s="28">
+        <v>2000</v>
+      </c>
+      <c r="J254" s="105" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="255" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A255" s="103">
+        <v>55006</v>
+      </c>
+      <c r="B255" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C255" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="D255" s="69">
+        <v>6</v>
+      </c>
+      <c r="E255" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="F255" s="99"/>
+      <c r="G255" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H255" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="I255" s="28">
+        <v>0</v>
+      </c>
+      <c r="J255" s="105" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="256" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A256" s="103">
+        <v>55007</v>
+      </c>
+      <c r="B256" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C256" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="D256" s="69">
+        <v>7</v>
+      </c>
+      <c r="E256" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="F256" s="99"/>
+      <c r="G256" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H256" s="28">
+        <v>-999999</v>
+      </c>
+      <c r="I256" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="J256" s="105" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -171,7 +171,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="209">
   <si>
     <t>id</t>
   </si>
@@ -731,6 +731,9 @@
     <t>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</t>
   </si>
   <si>
+    <t>超级高尔夫</t>
+  </si>
+  <si>
     <t>澳门壕梦</t>
   </si>
   <si>
@@ -779,6 +782,9 @@
     <t>1_8650|2_1300</t>
   </si>
   <si>
+    <t>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</t>
+  </si>
+  <si>
     <t>1_8850|2_1100</t>
   </si>
   <si>
@@ -789,6 +795,9 @@
   </si>
   <si>
     <t>1_9800|2_200</t>
+  </si>
+  <si>
+    <t>伽罗宝石1</t>
   </si>
 </sst>
 </file>
@@ -2099,7 +2108,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K256"/>
+  <dimension ref="A1:K270"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
@@ -8581,24 +8590,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="208" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A208" s="81">
-        <v>50001</v>
-      </c>
-      <c r="B208" s="81">
-        <v>105000</v>
-      </c>
-      <c r="C208" s="81" t="s">
+    <row r="208" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A208" s="89">
+        <v>48001</v>
+      </c>
+      <c r="B208" s="89">
+        <v>104800</v>
+      </c>
+      <c r="C208" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="D208" s="81">
+      <c r="D208" s="89">
         <v>1</v>
       </c>
-      <c r="E208" s="82" t="s">
+      <c r="E208" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="F208" s="25"/>
-      <c r="G208" s="83" t="s">
+      <c r="F208" s="35"/>
+      <c r="G208" s="37" t="s">
         <v>55</v>
       </c>
       <c r="H208" s="28">
@@ -8607,28 +8616,28 @@
       <c r="I208" s="28">
         <v>999999</v>
       </c>
-      <c r="J208" s="84" t="s">
+      <c r="J208" s="33" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="209" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A209" s="81">
-        <v>50002</v>
-      </c>
-      <c r="B209" s="81">
-        <v>105000</v>
-      </c>
-      <c r="C209" s="81" t="s">
+    <row r="209" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A209" s="89">
+        <v>48002</v>
+      </c>
+      <c r="B209" s="89">
+        <v>104800</v>
+      </c>
+      <c r="C209" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="D209" s="81">
+      <c r="D209" s="89">
         <v>2</v>
       </c>
-      <c r="E209" s="82" t="s">
+      <c r="E209" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F209" s="25"/>
-      <c r="G209" s="83" t="s">
+      <c r="F209" s="35"/>
+      <c r="G209" s="37" t="s">
         <v>55</v>
       </c>
       <c r="H209" s="28">
@@ -8637,28 +8646,28 @@
       <c r="I209" s="28">
         <v>8000</v>
       </c>
-      <c r="J209" s="84" t="s">
+      <c r="J209" s="33" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="210" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A210" s="81">
-        <v>50003</v>
-      </c>
-      <c r="B210" s="81">
-        <v>105000</v>
-      </c>
-      <c r="C210" s="81" t="s">
+    <row r="210" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A210" s="89">
+        <v>48003</v>
+      </c>
+      <c r="B210" s="89">
+        <v>104800</v>
+      </c>
+      <c r="C210" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="D210" s="81">
+      <c r="D210" s="89">
         <v>3</v>
       </c>
-      <c r="E210" s="82" t="s">
+      <c r="E210" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F210" s="25"/>
-      <c r="G210" s="83" t="s">
+      <c r="F210" s="35"/>
+      <c r="G210" s="37" t="s">
         <v>55</v>
       </c>
       <c r="H210" s="28">
@@ -8667,28 +8676,28 @@
       <c r="I210" s="28">
         <v>6000</v>
       </c>
-      <c r="J210" s="84" t="s">
+      <c r="J210" s="33" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="211" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A211" s="81">
-        <v>50004</v>
-      </c>
-      <c r="B211" s="81">
-        <v>105000</v>
-      </c>
-      <c r="C211" s="81" t="s">
+    <row r="211" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A211" s="89">
+        <v>48004</v>
+      </c>
+      <c r="B211" s="89">
+        <v>104800</v>
+      </c>
+      <c r="C211" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="D211" s="81">
+      <c r="D211" s="89">
         <v>4</v>
       </c>
-      <c r="E211" s="82" t="s">
+      <c r="E211" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="F211" s="25"/>
-      <c r="G211" s="83" t="s">
+      <c r="F211" s="35"/>
+      <c r="G211" s="37" t="s">
         <v>55</v>
       </c>
       <c r="H211" s="28">
@@ -8697,28 +8706,28 @@
       <c r="I211" s="28">
         <v>4000</v>
       </c>
-      <c r="J211" s="84" t="s">
+      <c r="J211" s="33" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="212" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A212" s="81">
-        <v>50005</v>
-      </c>
-      <c r="B212" s="81">
-        <v>105000</v>
-      </c>
-      <c r="C212" s="81" t="s">
+    <row r="212" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A212" s="89">
+        <v>48005</v>
+      </c>
+      <c r="B212" s="89">
+        <v>104800</v>
+      </c>
+      <c r="C212" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="D212" s="81">
+      <c r="D212" s="89">
         <v>5</v>
       </c>
-      <c r="E212" s="82" t="s">
+      <c r="E212" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="F212" s="25"/>
-      <c r="G212" s="83" t="s">
+      <c r="F212" s="35"/>
+      <c r="G212" s="37" t="s">
         <v>55</v>
       </c>
       <c r="H212" s="28">
@@ -8727,28 +8736,28 @@
       <c r="I212" s="28">
         <v>2000</v>
       </c>
-      <c r="J212" s="84" t="s">
+      <c r="J212" s="33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="213" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A213" s="81">
-        <v>50006</v>
-      </c>
-      <c r="B213" s="81">
-        <v>105000</v>
-      </c>
-      <c r="C213" s="81" t="s">
+    <row r="213" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A213" s="89">
+        <v>48006</v>
+      </c>
+      <c r="B213" s="89">
+        <v>104800</v>
+      </c>
+      <c r="C213" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="D213" s="81">
+      <c r="D213" s="89">
         <v>6</v>
       </c>
-      <c r="E213" s="82" t="s">
+      <c r="E213" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F213" s="25"/>
-      <c r="G213" s="83" t="s">
+      <c r="F213" s="35"/>
+      <c r="G213" s="37" t="s">
         <v>55</v>
       </c>
       <c r="H213" s="28">
@@ -8757,28 +8766,28 @@
       <c r="I213" s="28">
         <v>0</v>
       </c>
-      <c r="J213" s="84" t="s">
+      <c r="J213" s="33" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="214" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A214" s="81">
-        <v>50007</v>
-      </c>
-      <c r="B214" s="81">
-        <v>105000</v>
-      </c>
-      <c r="C214" s="81" t="s">
+    <row r="214" s="3" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A214" s="89">
+        <v>48007</v>
+      </c>
+      <c r="B214" s="89">
+        <v>104800</v>
+      </c>
+      <c r="C214" s="89" t="s">
         <v>186</v>
       </c>
-      <c r="D214" s="81">
+      <c r="D214" s="89">
         <v>7</v>
       </c>
-      <c r="E214" s="82" t="s">
+      <c r="E214" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F214" s="25"/>
-      <c r="G214" s="83" t="s">
+      <c r="F214" s="35"/>
+      <c r="G214" s="37" t="s">
         <v>55</v>
       </c>
       <c r="H214" s="28">
@@ -8787,28 +8796,28 @@
       <c r="I214" s="28">
         <v>-1000</v>
       </c>
-      <c r="J214" s="84" t="s">
+      <c r="J214" s="33" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="215" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A215" s="90">
-        <v>51001</v>
-      </c>
-      <c r="B215" s="90">
-        <v>105100</v>
-      </c>
-      <c r="C215" s="90" t="s">
+    <row r="215" s="18" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A215" s="81">
+        <v>50001</v>
+      </c>
+      <c r="B215" s="81">
+        <v>105000</v>
+      </c>
+      <c r="C215" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="D215" s="90">
+      <c r="D215" s="81">
         <v>1</v>
       </c>
-      <c r="E215" s="91" t="s">
+      <c r="E215" s="82" t="s">
         <v>54</v>
       </c>
       <c r="F215" s="25"/>
-      <c r="G215" s="92" t="s">
+      <c r="G215" s="83" t="s">
         <v>55</v>
       </c>
       <c r="H215" s="28">
@@ -8817,28 +8826,28 @@
       <c r="I215" s="28">
         <v>999999</v>
       </c>
-      <c r="J215" s="93" t="s">
+      <c r="J215" s="84" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="216" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A216" s="90">
-        <v>51002</v>
-      </c>
-      <c r="B216" s="90">
-        <v>105100</v>
-      </c>
-      <c r="C216" s="90" t="s">
+    <row r="216" s="18" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A216" s="81">
+        <v>50002</v>
+      </c>
+      <c r="B216" s="81">
+        <v>105000</v>
+      </c>
+      <c r="C216" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="D216" s="90">
+      <c r="D216" s="81">
         <v>2</v>
       </c>
-      <c r="E216" s="91" t="s">
+      <c r="E216" s="82" t="s">
         <v>56</v>
       </c>
       <c r="F216" s="25"/>
-      <c r="G216" s="92" t="s">
+      <c r="G216" s="83" t="s">
         <v>55</v>
       </c>
       <c r="H216" s="28">
@@ -8847,28 +8856,28 @@
       <c r="I216" s="28">
         <v>8000</v>
       </c>
-      <c r="J216" s="93" t="s">
+      <c r="J216" s="84" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="217" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A217" s="90">
-        <v>51003</v>
-      </c>
-      <c r="B217" s="90">
-        <v>105100</v>
-      </c>
-      <c r="C217" s="90" t="s">
+    <row r="217" s="18" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A217" s="81">
+        <v>50003</v>
+      </c>
+      <c r="B217" s="81">
+        <v>105000</v>
+      </c>
+      <c r="C217" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="D217" s="90">
+      <c r="D217" s="81">
         <v>3</v>
       </c>
-      <c r="E217" s="91" t="s">
+      <c r="E217" s="82" t="s">
         <v>57</v>
       </c>
       <c r="F217" s="25"/>
-      <c r="G217" s="92" t="s">
+      <c r="G217" s="83" t="s">
         <v>55</v>
       </c>
       <c r="H217" s="28">
@@ -8877,28 +8886,28 @@
       <c r="I217" s="28">
         <v>6000</v>
       </c>
-      <c r="J217" s="93" t="s">
+      <c r="J217" s="84" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="218" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A218" s="90">
-        <v>51004</v>
-      </c>
-      <c r="B218" s="90">
-        <v>105100</v>
-      </c>
-      <c r="C218" s="90" t="s">
+    <row r="218" s="18" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A218" s="81">
+        <v>50004</v>
+      </c>
+      <c r="B218" s="81">
+        <v>105000</v>
+      </c>
+      <c r="C218" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="D218" s="90">
+      <c r="D218" s="81">
         <v>4</v>
       </c>
-      <c r="E218" s="91" t="s">
+      <c r="E218" s="82" t="s">
         <v>58</v>
       </c>
       <c r="F218" s="25"/>
-      <c r="G218" s="92" t="s">
+      <c r="G218" s="83" t="s">
         <v>55</v>
       </c>
       <c r="H218" s="28">
@@ -8907,28 +8916,28 @@
       <c r="I218" s="28">
         <v>4000</v>
       </c>
-      <c r="J218" s="93" t="s">
+      <c r="J218" s="84" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="219" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A219" s="90">
-        <v>51005</v>
-      </c>
-      <c r="B219" s="90">
-        <v>105100</v>
-      </c>
-      <c r="C219" s="90" t="s">
+    <row r="219" s="18" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A219" s="81">
+        <v>50005</v>
+      </c>
+      <c r="B219" s="81">
+        <v>105000</v>
+      </c>
+      <c r="C219" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="D219" s="90">
+      <c r="D219" s="81">
         <v>5</v>
       </c>
-      <c r="E219" s="91" t="s">
+      <c r="E219" s="82" t="s">
         <v>59</v>
       </c>
       <c r="F219" s="25"/>
-      <c r="G219" s="92" t="s">
+      <c r="G219" s="83" t="s">
         <v>55</v>
       </c>
       <c r="H219" s="28">
@@ -8937,28 +8946,28 @@
       <c r="I219" s="28">
         <v>2000</v>
       </c>
-      <c r="J219" s="93" t="s">
+      <c r="J219" s="84" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="220" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A220" s="90">
-        <v>51006</v>
-      </c>
-      <c r="B220" s="90">
-        <v>105100</v>
-      </c>
-      <c r="C220" s="90" t="s">
+    <row r="220" s="18" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A220" s="81">
+        <v>50006</v>
+      </c>
+      <c r="B220" s="81">
+        <v>105000</v>
+      </c>
+      <c r="C220" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="D220" s="90">
+      <c r="D220" s="81">
         <v>6</v>
       </c>
-      <c r="E220" s="91" t="s">
+      <c r="E220" s="82" t="s">
         <v>60</v>
       </c>
       <c r="F220" s="25"/>
-      <c r="G220" s="92" t="s">
+      <c r="G220" s="83" t="s">
         <v>55</v>
       </c>
       <c r="H220" s="28">
@@ -8967,28 +8976,28 @@
       <c r="I220" s="28">
         <v>0</v>
       </c>
-      <c r="J220" s="93" t="s">
+      <c r="J220" s="84" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="221" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A221" s="90">
-        <v>51007</v>
-      </c>
-      <c r="B221" s="90">
-        <v>105100</v>
-      </c>
-      <c r="C221" s="90" t="s">
+    <row r="221" s="18" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A221" s="81">
+        <v>50007</v>
+      </c>
+      <c r="B221" s="81">
+        <v>105000</v>
+      </c>
+      <c r="C221" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="D221" s="90">
+      <c r="D221" s="81">
         <v>7</v>
       </c>
-      <c r="E221" s="91" t="s">
+      <c r="E221" s="82" t="s">
         <v>61</v>
       </c>
       <c r="F221" s="25"/>
-      <c r="G221" s="92" t="s">
+      <c r="G221" s="83" t="s">
         <v>55</v>
       </c>
       <c r="H221" s="28">
@@ -8997,1001 +9006,1427 @@
       <c r="I221" s="28">
         <v>-1000</v>
       </c>
-      <c r="J221" s="93" t="s">
+      <c r="J221" s="84" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="222" s="8" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A222" s="8">
+    <row r="222" s="20" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A222" s="90">
+        <v>51001</v>
+      </c>
+      <c r="B222" s="90">
+        <v>105100</v>
+      </c>
+      <c r="C222" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="D222" s="90">
+        <v>1</v>
+      </c>
+      <c r="E222" s="91" t="s">
+        <v>54</v>
+      </c>
+      <c r="F222" s="25"/>
+      <c r="G222" s="92" t="s">
+        <v>55</v>
+      </c>
+      <c r="H222" s="28">
+        <v>8000</v>
+      </c>
+      <c r="I222" s="28">
+        <v>999999</v>
+      </c>
+      <c r="J222" s="93" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="223" s="20" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A223" s="90">
+        <v>51002</v>
+      </c>
+      <c r="B223" s="90">
+        <v>105100</v>
+      </c>
+      <c r="C223" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="D223" s="90">
+        <v>2</v>
+      </c>
+      <c r="E223" s="91" t="s">
+        <v>56</v>
+      </c>
+      <c r="F223" s="25"/>
+      <c r="G223" s="92" t="s">
+        <v>55</v>
+      </c>
+      <c r="H223" s="28">
+        <v>6000</v>
+      </c>
+      <c r="I223" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J223" s="93" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="224" s="20" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A224" s="90">
+        <v>51003</v>
+      </c>
+      <c r="B224" s="90">
+        <v>105100</v>
+      </c>
+      <c r="C224" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="D224" s="90">
+        <v>3</v>
+      </c>
+      <c r="E224" s="91" t="s">
+        <v>57</v>
+      </c>
+      <c r="F224" s="25"/>
+      <c r="G224" s="92" t="s">
+        <v>55</v>
+      </c>
+      <c r="H224" s="28">
+        <v>4000</v>
+      </c>
+      <c r="I224" s="28">
+        <v>6000</v>
+      </c>
+      <c r="J224" s="93" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="225" s="20" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A225" s="90">
+        <v>51004</v>
+      </c>
+      <c r="B225" s="90">
+        <v>105100</v>
+      </c>
+      <c r="C225" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="D225" s="90">
+        <v>4</v>
+      </c>
+      <c r="E225" s="91" t="s">
+        <v>58</v>
+      </c>
+      <c r="F225" s="25"/>
+      <c r="G225" s="92" t="s">
+        <v>55</v>
+      </c>
+      <c r="H225" s="28">
+        <v>2000</v>
+      </c>
+      <c r="I225" s="28">
+        <v>4000</v>
+      </c>
+      <c r="J225" s="93" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="226" s="20" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A226" s="90">
+        <v>51005</v>
+      </c>
+      <c r="B226" s="90">
+        <v>105100</v>
+      </c>
+      <c r="C226" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="D226" s="90">
+        <v>5</v>
+      </c>
+      <c r="E226" s="91" t="s">
+        <v>59</v>
+      </c>
+      <c r="F226" s="25"/>
+      <c r="G226" s="92" t="s">
+        <v>55</v>
+      </c>
+      <c r="H226" s="28">
+        <v>0</v>
+      </c>
+      <c r="I226" s="28">
+        <v>2000</v>
+      </c>
+      <c r="J226" s="93" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="227" s="20" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A227" s="90">
+        <v>51006</v>
+      </c>
+      <c r="B227" s="90">
+        <v>105100</v>
+      </c>
+      <c r="C227" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="D227" s="90">
+        <v>6</v>
+      </c>
+      <c r="E227" s="91" t="s">
+        <v>60</v>
+      </c>
+      <c r="F227" s="25"/>
+      <c r="G227" s="92" t="s">
+        <v>55</v>
+      </c>
+      <c r="H227" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="I227" s="28">
+        <v>0</v>
+      </c>
+      <c r="J227" s="93" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="228" s="20" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A228" s="90">
+        <v>51007</v>
+      </c>
+      <c r="B228" s="90">
+        <v>105100</v>
+      </c>
+      <c r="C228" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="D228" s="90">
+        <v>7</v>
+      </c>
+      <c r="E228" s="91" t="s">
+        <v>61</v>
+      </c>
+      <c r="F228" s="25"/>
+      <c r="G228" s="92" t="s">
+        <v>55</v>
+      </c>
+      <c r="H228" s="28">
+        <v>-999999</v>
+      </c>
+      <c r="I228" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="J228" s="93" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="229" s="8" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A229" s="8">
         <v>53001</v>
       </c>
-      <c r="B222" s="51">
+      <c r="B229" s="51">
         <v>105300</v>
       </c>
-      <c r="C222" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="D222" s="30">
+      <c r="C229" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="D229" s="30">
         <v>1</v>
       </c>
-      <c r="E222" s="31" t="s">
+      <c r="E229" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="F229" s="52"/>
+      <c r="G229" s="94" t="s">
+        <v>191</v>
+      </c>
+      <c r="H229" s="30">
+        <v>2000</v>
+      </c>
+      <c r="I229" s="30">
+        <v>999999</v>
+      </c>
+      <c r="J229" s="30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="230" s="8" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A230" s="8">
+        <v>53002</v>
+      </c>
+      <c r="B230" s="51">
+        <v>105300</v>
+      </c>
+      <c r="C230" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="F222" s="52"/>
-      <c r="G222" s="94" t="s">
+      <c r="D230" s="30">
+        <v>2</v>
+      </c>
+      <c r="E230" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="F230" s="52"/>
+      <c r="G230" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="H230" s="30">
+        <v>1000</v>
+      </c>
+      <c r="I230" s="30">
+        <v>2000</v>
+      </c>
+      <c r="J230" s="30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="231" s="8" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A231" s="8">
+        <v>53003</v>
+      </c>
+      <c r="B231" s="51">
+        <v>105300</v>
+      </c>
+      <c r="C231" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="D231" s="30">
+        <v>3</v>
+      </c>
+      <c r="E231" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="F231" s="52"/>
+      <c r="G231" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="H231" s="30">
+        <v>500</v>
+      </c>
+      <c r="I231" s="30">
+        <v>1000</v>
+      </c>
+      <c r="J231" s="30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="232" s="8" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A232" s="8">
+        <v>53004</v>
+      </c>
+      <c r="B232" s="51">
+        <v>105300</v>
+      </c>
+      <c r="C232" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="D232" s="30">
+        <v>4</v>
+      </c>
+      <c r="E232" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="F232" s="52"/>
+      <c r="G232" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="H232" s="30">
+        <v>-500</v>
+      </c>
+      <c r="I232" s="30">
+        <v>500</v>
+      </c>
+      <c r="J232" s="30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="233" s="8" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A233" s="8">
+        <v>53005</v>
+      </c>
+      <c r="B233" s="51">
+        <v>105300</v>
+      </c>
+      <c r="C233" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="D233" s="30">
+        <v>5</v>
+      </c>
+      <c r="E233" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="F233" s="52"/>
+      <c r="G233" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="H233" s="30">
+        <v>-1000</v>
+      </c>
+      <c r="I233" s="30">
+        <v>-500</v>
+      </c>
+      <c r="J233" s="30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="234" s="8" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A234" s="8">
+        <v>53006</v>
+      </c>
+      <c r="B234" s="51">
+        <v>105300</v>
+      </c>
+      <c r="C234" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="D234" s="30">
+        <v>6</v>
+      </c>
+      <c r="E234" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="F234" s="52"/>
+      <c r="G234" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="H234" s="30">
+        <v>-2000</v>
+      </c>
+      <c r="I234" s="30">
+        <v>-1000</v>
+      </c>
+      <c r="J234" s="30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="235" s="8" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A235" s="8">
+        <v>53007</v>
+      </c>
+      <c r="B235" s="51">
+        <v>105300</v>
+      </c>
+      <c r="C235" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="D235" s="30">
+        <v>7</v>
+      </c>
+      <c r="E235" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="F235" s="52"/>
+      <c r="G235" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="H235" s="30">
+        <v>-999999</v>
+      </c>
+      <c r="I235" s="30">
+        <v>-2000</v>
+      </c>
+      <c r="J235" s="30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="236" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A236" s="89">
+        <v>54001</v>
+      </c>
+      <c r="B236" s="89">
+        <v>105400</v>
+      </c>
+      <c r="C236" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="D236" s="89">
+        <v>1</v>
+      </c>
+      <c r="E236" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="F236" s="22"/>
+      <c r="G236" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H236" s="33">
+        <v>2000</v>
+      </c>
+      <c r="I236" s="33">
+        <v>999999</v>
+      </c>
+      <c r="J236" s="33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="237" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A237" s="89">
+        <v>54002</v>
+      </c>
+      <c r="B237" s="89">
+        <v>105400</v>
+      </c>
+      <c r="C237" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="D237" s="89">
+        <v>2</v>
+      </c>
+      <c r="E237" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="F237" s="22"/>
+      <c r="G237" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H237" s="33">
+        <v>1000</v>
+      </c>
+      <c r="I237" s="33">
+        <v>2000</v>
+      </c>
+      <c r="J237" s="33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="238" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A238" s="89">
+        <v>54003</v>
+      </c>
+      <c r="B238" s="89">
+        <v>105400</v>
+      </c>
+      <c r="C238" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="D238" s="89">
+        <v>3</v>
+      </c>
+      <c r="E238" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="F238" s="22"/>
+      <c r="G238" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H238" s="33">
+        <v>500</v>
+      </c>
+      <c r="I238" s="33">
+        <v>1000</v>
+      </c>
+      <c r="J238" s="33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="239" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A239" s="89">
+        <v>54004</v>
+      </c>
+      <c r="B239" s="89">
+        <v>105400</v>
+      </c>
+      <c r="C239" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="D239" s="89">
+        <v>4</v>
+      </c>
+      <c r="E239" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="F239" s="22"/>
+      <c r="G239" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H239" s="33">
+        <v>-500</v>
+      </c>
+      <c r="I239" s="33">
+        <v>500</v>
+      </c>
+      <c r="J239" s="33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="240" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A240" s="89">
+        <v>54005</v>
+      </c>
+      <c r="B240" s="89">
+        <v>105400</v>
+      </c>
+      <c r="C240" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="D240" s="89">
+        <v>5</v>
+      </c>
+      <c r="E240" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="F240" s="22"/>
+      <c r="G240" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H240" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="I240" s="33">
+        <v>-500</v>
+      </c>
+      <c r="J240" s="33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="241" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A241" s="89">
+        <v>54006</v>
+      </c>
+      <c r="B241" s="89">
+        <v>105400</v>
+      </c>
+      <c r="C241" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="D241" s="89">
+        <v>6</v>
+      </c>
+      <c r="E241" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="F241" s="22"/>
+      <c r="G241" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H241" s="33">
+        <v>-2000</v>
+      </c>
+      <c r="I241" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="J241" s="33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="242" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A242" s="89">
+        <v>54007</v>
+      </c>
+      <c r="B242" s="89">
+        <v>105400</v>
+      </c>
+      <c r="C242" s="89" t="s">
+        <v>198</v>
+      </c>
+      <c r="D242" s="89">
+        <v>7</v>
+      </c>
+      <c r="E242" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F242" s="22"/>
+      <c r="G242" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H242" s="33">
+        <v>-999999</v>
+      </c>
+      <c r="I242" s="33">
+        <v>-2000</v>
+      </c>
+      <c r="J242" s="33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="243" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A243" s="95">
+        <v>57001</v>
+      </c>
+      <c r="B243" s="96">
+        <v>105700</v>
+      </c>
+      <c r="C243" s="96" t="s">
+        <v>199</v>
+      </c>
+      <c r="D243" s="97">
+        <v>1</v>
+      </c>
+      <c r="E243" s="98" t="s">
+        <v>54</v>
+      </c>
+      <c r="F243" s="99"/>
+      <c r="G243" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="H243" s="93">
+        <v>2000</v>
+      </c>
+      <c r="I243" s="93">
+        <v>999999</v>
+      </c>
+      <c r="J243" s="100" t="s">
+        <v>23</v>
+      </c>
+      <c r="K243" s="101"/>
+    </row>
+    <row r="244" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A244" s="95">
+        <v>57002</v>
+      </c>
+      <c r="B244" s="96">
+        <v>105700</v>
+      </c>
+      <c r="C244" s="96" t="s">
+        <v>199</v>
+      </c>
+      <c r="D244" s="97">
+        <v>2</v>
+      </c>
+      <c r="E244" s="98" t="s">
+        <v>56</v>
+      </c>
+      <c r="F244" s="99"/>
+      <c r="G244" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="H244" s="93">
+        <v>1000</v>
+      </c>
+      <c r="I244" s="93">
+        <v>2000</v>
+      </c>
+      <c r="J244" s="100" t="s">
+        <v>25</v>
+      </c>
+      <c r="K244" s="101"/>
+    </row>
+    <row r="245" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A245" s="95">
+        <v>57003</v>
+      </c>
+      <c r="B245" s="96">
+        <v>105700</v>
+      </c>
+      <c r="C245" s="96" t="s">
+        <v>199</v>
+      </c>
+      <c r="D245" s="97">
+        <v>3</v>
+      </c>
+      <c r="E245" s="98" t="s">
+        <v>57</v>
+      </c>
+      <c r="F245" s="99"/>
+      <c r="G245" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="H245" s="93">
+        <v>500</v>
+      </c>
+      <c r="I245" s="93">
+        <v>1000</v>
+      </c>
+      <c r="J245" s="100" t="s">
+        <v>27</v>
+      </c>
+      <c r="K245" s="101"/>
+    </row>
+    <row r="246" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A246" s="95">
+        <v>57004</v>
+      </c>
+      <c r="B246" s="96">
+        <v>105700</v>
+      </c>
+      <c r="C246" s="96" t="s">
+        <v>199</v>
+      </c>
+      <c r="D246" s="97">
+        <v>4</v>
+      </c>
+      <c r="E246" s="98" t="s">
+        <v>58</v>
+      </c>
+      <c r="F246" s="99"/>
+      <c r="G246" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="H246" s="93">
+        <v>-500</v>
+      </c>
+      <c r="I246" s="93">
+        <v>500</v>
+      </c>
+      <c r="J246" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="K246" s="101"/>
+    </row>
+    <row r="247" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A247" s="95">
+        <v>57005</v>
+      </c>
+      <c r="B247" s="96">
+        <v>105700</v>
+      </c>
+      <c r="C247" s="96" t="s">
+        <v>199</v>
+      </c>
+      <c r="D247" s="97">
+        <v>5</v>
+      </c>
+      <c r="E247" s="98" t="s">
+        <v>59</v>
+      </c>
+      <c r="F247" s="99"/>
+      <c r="G247" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="H247" s="93">
+        <v>-1000</v>
+      </c>
+      <c r="I247" s="93">
+        <v>-500</v>
+      </c>
+      <c r="J247" s="100" t="s">
+        <v>31</v>
+      </c>
+      <c r="K247" s="101"/>
+    </row>
+    <row r="248" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A248" s="95">
+        <v>57006</v>
+      </c>
+      <c r="B248" s="96">
+        <v>105700</v>
+      </c>
+      <c r="C248" s="96" t="s">
+        <v>199</v>
+      </c>
+      <c r="D248" s="97">
+        <v>6</v>
+      </c>
+      <c r="E248" s="98" t="s">
+        <v>60</v>
+      </c>
+      <c r="F248" s="99"/>
+      <c r="G248" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="H248" s="93">
+        <v>-2000</v>
+      </c>
+      <c r="I248" s="93">
+        <v>-1000</v>
+      </c>
+      <c r="J248" s="100" t="s">
+        <v>33</v>
+      </c>
+      <c r="K248" s="101"/>
+    </row>
+    <row r="249" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A249" s="95">
+        <v>57007</v>
+      </c>
+      <c r="B249" s="96">
+        <v>105700</v>
+      </c>
+      <c r="C249" s="96" t="s">
+        <v>199</v>
+      </c>
+      <c r="D249" s="97">
+        <v>7</v>
+      </c>
+      <c r="E249" s="98" t="s">
+        <v>61</v>
+      </c>
+      <c r="F249" s="99"/>
+      <c r="G249" s="100" t="s">
+        <v>55</v>
+      </c>
+      <c r="H249" s="93">
+        <v>-999999</v>
+      </c>
+      <c r="I249" s="93">
+        <v>-2000</v>
+      </c>
+      <c r="J249" s="100" t="s">
+        <v>35</v>
+      </c>
+      <c r="K249" s="101"/>
+    </row>
+    <row r="250" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A250" s="21">
+        <v>58001</v>
+      </c>
+      <c r="B250" s="102">
+        <v>105800</v>
+      </c>
+      <c r="C250" s="102" t="s">
+        <v>200</v>
+      </c>
+      <c r="D250" s="102">
+        <v>1</v>
+      </c>
+      <c r="E250" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="H222" s="30">
+      <c r="F250" s="99"/>
+      <c r="G250" s="27" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="251" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A251" s="21">
+        <v>58002</v>
+      </c>
+      <c r="B251" s="102">
+        <v>105800</v>
+      </c>
+      <c r="C251" s="102" t="s">
+        <v>200</v>
+      </c>
+      <c r="D251" s="102">
+        <v>2</v>
+      </c>
+      <c r="E251" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="F251" s="99"/>
+      <c r="G251" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="252" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A252" s="21">
+        <v>58003</v>
+      </c>
+      <c r="B252" s="102">
+        <v>105800</v>
+      </c>
+      <c r="C252" s="102" t="s">
+        <v>200</v>
+      </c>
+      <c r="D252" s="102">
+        <v>3</v>
+      </c>
+      <c r="E252" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="F252" s="99"/>
+      <c r="G252" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="253" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A253" s="21">
+        <v>58004</v>
+      </c>
+      <c r="B253" s="102">
+        <v>105800</v>
+      </c>
+      <c r="C253" s="102" t="s">
+        <v>200</v>
+      </c>
+      <c r="D253" s="102">
+        <v>4</v>
+      </c>
+      <c r="E253" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="F253" s="99"/>
+      <c r="G253" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="254" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A254" s="21">
+        <v>58005</v>
+      </c>
+      <c r="B254" s="102">
+        <v>105800</v>
+      </c>
+      <c r="C254" s="102" t="s">
+        <v>200</v>
+      </c>
+      <c r="D254" s="102">
+        <v>5</v>
+      </c>
+      <c r="E254" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="F254" s="99"/>
+      <c r="G254" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="255" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A255" s="21">
+        <v>58006</v>
+      </c>
+      <c r="B255" s="102">
+        <v>105800</v>
+      </c>
+      <c r="C255" s="102" t="s">
+        <v>200</v>
+      </c>
+      <c r="D255" s="102">
+        <v>6</v>
+      </c>
+      <c r="E255" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="F255" s="99"/>
+      <c r="G255" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="256" s="21" customFormat="1" ht="16.5" spans="1:11">
+      <c r="A256" s="21">
+        <v>58007</v>
+      </c>
+      <c r="B256" s="102">
+        <v>105800</v>
+      </c>
+      <c r="C256" s="102" t="s">
+        <v>200</v>
+      </c>
+      <c r="D256" s="102">
+        <v>7</v>
+      </c>
+      <c r="E256" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="F256" s="99"/>
+      <c r="G256" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="257" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A257" s="103">
+        <v>55001</v>
+      </c>
+      <c r="B257" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C257" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="D257" s="69">
+        <v>1</v>
+      </c>
+      <c r="E257" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="F257" s="99"/>
+      <c r="G257" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="H257" s="28">
+        <v>8000</v>
+      </c>
+      <c r="I257" s="28">
+        <v>999999</v>
+      </c>
+      <c r="J257" s="105" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="258" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A258" s="103">
+        <v>55002</v>
+      </c>
+      <c r="B258" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C258" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="D258" s="69">
+        <v>2</v>
+      </c>
+      <c r="E258" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="F258" s="99"/>
+      <c r="G258" s="83" t="str">
+        <f>G257</f>
+        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
+      </c>
+      <c r="H258" s="28">
+        <v>6000</v>
+      </c>
+      <c r="I258" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J258" s="105" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A259" s="103">
+        <v>55003</v>
+      </c>
+      <c r="B259" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C259" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="D259" s="69">
+        <v>3</v>
+      </c>
+      <c r="E259" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="F259" s="99"/>
+      <c r="G259" s="83" t="str">
+        <f>G258</f>
+        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
+      </c>
+      <c r="H259" s="28">
+        <v>4000</v>
+      </c>
+      <c r="I259" s="28">
+        <v>6000</v>
+      </c>
+      <c r="J259" s="105" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="260" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A260" s="103">
+        <v>55004</v>
+      </c>
+      <c r="B260" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C260" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="D260" s="69">
+        <v>4</v>
+      </c>
+      <c r="E260" s="70" t="s">
+        <v>206</v>
+      </c>
+      <c r="F260" s="99"/>
+      <c r="G260" s="83" t="str">
+        <f>G259</f>
+        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
+      </c>
+      <c r="H260" s="28">
         <v>2000</v>
       </c>
-      <c r="I222" s="30">
+      <c r="I260" s="28">
+        <v>4000</v>
+      </c>
+      <c r="J260" s="105" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="261" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A261" s="103">
+        <v>55005</v>
+      </c>
+      <c r="B261" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C261" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="D261" s="69">
+        <v>5</v>
+      </c>
+      <c r="E261" s="70" t="s">
+        <v>207</v>
+      </c>
+      <c r="F261" s="99"/>
+      <c r="G261" s="83" t="str">
+        <f>G260</f>
+        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
+      </c>
+      <c r="H261" s="28">
+        <v>0</v>
+      </c>
+      <c r="I261" s="28">
+        <v>2000</v>
+      </c>
+      <c r="J261" s="105" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="262" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A262" s="103">
+        <v>55006</v>
+      </c>
+      <c r="B262" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C262" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="D262" s="69">
+        <v>6</v>
+      </c>
+      <c r="E262" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="F262" s="99"/>
+      <c r="G262" s="83" t="str">
+        <f>G261</f>
+        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
+      </c>
+      <c r="H262" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="I262" s="28">
+        <v>0</v>
+      </c>
+      <c r="J262" s="105" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="263" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A263" s="103">
+        <v>55007</v>
+      </c>
+      <c r="B263" s="104">
+        <v>105500</v>
+      </c>
+      <c r="C263" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="D263" s="69">
+        <v>7</v>
+      </c>
+      <c r="E263" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="F263" s="99"/>
+      <c r="G263" s="83" t="str">
+        <f>G262</f>
+        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
+      </c>
+      <c r="H263" s="28">
+        <v>-999999</v>
+      </c>
+      <c r="I263" s="28">
+        <v>-1000</v>
+      </c>
+      <c r="J263" s="105" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="264" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A264" s="103">
+        <v>55011</v>
+      </c>
+      <c r="B264" s="104">
+        <v>105501</v>
+      </c>
+      <c r="C264" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="D264" s="69">
+        <v>1</v>
+      </c>
+      <c r="E264" s="98" t="s">
+        <v>54</v>
+      </c>
+      <c r="F264" s="99"/>
+      <c r="G264" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="H264" s="28">
+        <v>8000</v>
+      </c>
+      <c r="I264" s="28">
         <v>999999</v>
       </c>
-      <c r="J222" s="30" t="s">
+      <c r="J264" s="105" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="223" s="8" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A223" s="8">
-        <v>53002</v>
-      </c>
-      <c r="B223" s="51">
-        <v>105300</v>
-      </c>
-      <c r="C223" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="D223" s="30">
+    <row r="265" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A265" s="103">
+        <v>55012</v>
+      </c>
+      <c r="B265" s="104">
+        <v>105501</v>
+      </c>
+      <c r="C265" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="D265" s="69">
         <v>2</v>
       </c>
-      <c r="E223" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="F223" s="52"/>
-      <c r="G223" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="H223" s="30">
-        <v>1000</v>
-      </c>
-      <c r="I223" s="30">
+      <c r="E265" s="98" t="s">
+        <v>56</v>
+      </c>
+      <c r="F265" s="99"/>
+      <c r="G265" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H265" s="28">
+        <v>6000</v>
+      </c>
+      <c r="I265" s="28">
+        <v>8000</v>
+      </c>
+      <c r="J265" s="105" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="266" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A266" s="103">
+        <v>55013</v>
+      </c>
+      <c r="B266" s="104">
+        <v>105501</v>
+      </c>
+      <c r="C266" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="D266" s="69">
+        <v>3</v>
+      </c>
+      <c r="E266" s="98" t="s">
+        <v>57</v>
+      </c>
+      <c r="F266" s="99"/>
+      <c r="G266" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H266" s="28">
+        <v>4000</v>
+      </c>
+      <c r="I266" s="28">
+        <v>6000</v>
+      </c>
+      <c r="J266" s="105" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="267" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A267" s="103">
+        <v>55014</v>
+      </c>
+      <c r="B267" s="104">
+        <v>105501</v>
+      </c>
+      <c r="C267" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="D267" s="69">
+        <v>4</v>
+      </c>
+      <c r="E267" s="98" t="s">
+        <v>58</v>
+      </c>
+      <c r="F267" s="99"/>
+      <c r="G267" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H267" s="28">
         <v>2000</v>
       </c>
-      <c r="J223" s="30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="224" s="8" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A224" s="8">
-        <v>53003</v>
-      </c>
-      <c r="B224" s="51">
-        <v>105300</v>
-      </c>
-      <c r="C224" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="D224" s="30">
-        <v>3</v>
-      </c>
-      <c r="E224" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="F224" s="52"/>
-      <c r="G224" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="H224" s="30">
-        <v>500</v>
-      </c>
-      <c r="I224" s="30">
-        <v>1000</v>
-      </c>
-      <c r="J224" s="30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="225" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A225" s="8">
-        <v>53004</v>
-      </c>
-      <c r="B225" s="51">
-        <v>105300</v>
-      </c>
-      <c r="C225" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="D225" s="30">
-        <v>4</v>
-      </c>
-      <c r="E225" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="F225" s="52"/>
-      <c r="G225" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="H225" s="30">
-        <v>-500</v>
-      </c>
-      <c r="I225" s="30">
-        <v>500</v>
-      </c>
-      <c r="J225" s="30" t="s">
+      <c r="I267" s="28">
+        <v>4000</v>
+      </c>
+      <c r="J267" s="105" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="226" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A226" s="8">
-        <v>53005</v>
-      </c>
-      <c r="B226" s="51">
-        <v>105300</v>
-      </c>
-      <c r="C226" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="D226" s="30">
+    <row r="268" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A268" s="103">
+        <v>55015</v>
+      </c>
+      <c r="B268" s="104">
+        <v>105501</v>
+      </c>
+      <c r="C268" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="D268" s="69">
         <v>5</v>
       </c>
-      <c r="E226" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="F226" s="52"/>
-      <c r="G226" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="H226" s="30">
+      <c r="E268" s="98" t="s">
+        <v>59</v>
+      </c>
+      <c r="F268" s="99"/>
+      <c r="G268" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H268" s="28">
+        <v>0</v>
+      </c>
+      <c r="I268" s="28">
+        <v>2000</v>
+      </c>
+      <c r="J268" s="105" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="269" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A269" s="103">
+        <v>55016</v>
+      </c>
+      <c r="B269" s="104">
+        <v>105501</v>
+      </c>
+      <c r="C269" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="D269" s="69">
+        <v>6</v>
+      </c>
+      <c r="E269" s="98" t="s">
+        <v>60</v>
+      </c>
+      <c r="F269" s="99"/>
+      <c r="G269" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H269" s="28">
         <v>-1000</v>
       </c>
-      <c r="I226" s="30">
-        <v>-500</v>
-      </c>
-      <c r="J226" s="30" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="227" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A227" s="8">
-        <v>53006</v>
-      </c>
-      <c r="B227" s="51">
-        <v>105300</v>
-      </c>
-      <c r="C227" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="D227" s="30">
-        <v>6</v>
-      </c>
-      <c r="E227" s="31" t="s">
-        <v>195</v>
-      </c>
-      <c r="F227" s="52"/>
-      <c r="G227" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="H227" s="30">
-        <v>-2000</v>
-      </c>
-      <c r="I227" s="30">
+      <c r="I269" s="28">
+        <v>0</v>
+      </c>
+      <c r="J269" s="105" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="270" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A270" s="103">
+        <v>55017</v>
+      </c>
+      <c r="B270" s="104">
+        <v>105501</v>
+      </c>
+      <c r="C270" s="104" t="s">
+        <v>208</v>
+      </c>
+      <c r="D270" s="69">
+        <v>7</v>
+      </c>
+      <c r="E270" s="98" t="s">
+        <v>61</v>
+      </c>
+      <c r="F270" s="99"/>
+      <c r="G270" s="83" t="s">
+        <v>161</v>
+      </c>
+      <c r="H270" s="28">
+        <v>-999999</v>
+      </c>
+      <c r="I270" s="28">
         <v>-1000</v>
       </c>
-      <c r="J227" s="30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="228" s="8" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A228" s="8">
-        <v>53007</v>
-      </c>
-      <c r="B228" s="51">
-        <v>105300</v>
-      </c>
-      <c r="C228" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="D228" s="30">
-        <v>7</v>
-      </c>
-      <c r="E228" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="F228" s="52"/>
-      <c r="G228" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="H228" s="30">
-        <v>-999999</v>
-      </c>
-      <c r="I228" s="30">
-        <v>-2000</v>
-      </c>
-      <c r="J228" s="30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="229" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A229" s="89">
-        <v>54001</v>
-      </c>
-      <c r="B229" s="89">
-        <v>105400</v>
-      </c>
-      <c r="C229" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="D229" s="89">
-        <v>1</v>
-      </c>
-      <c r="E229" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="F229" s="22"/>
-      <c r="G229" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H229" s="33">
-        <v>2000</v>
-      </c>
-      <c r="I229" s="33">
-        <v>999999</v>
-      </c>
-      <c r="J229" s="33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="230" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A230" s="89">
-        <v>54002</v>
-      </c>
-      <c r="B230" s="89">
-        <v>105400</v>
-      </c>
-      <c r="C230" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="D230" s="89">
-        <v>2</v>
-      </c>
-      <c r="E230" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="F230" s="22"/>
-      <c r="G230" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H230" s="33">
-        <v>1000</v>
-      </c>
-      <c r="I230" s="33">
-        <v>2000</v>
-      </c>
-      <c r="J230" s="33" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="231" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A231" s="89">
-        <v>54003</v>
-      </c>
-      <c r="B231" s="89">
-        <v>105400</v>
-      </c>
-      <c r="C231" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="D231" s="89">
-        <v>3</v>
-      </c>
-      <c r="E231" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F231" s="22"/>
-      <c r="G231" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H231" s="33">
-        <v>500</v>
-      </c>
-      <c r="I231" s="33">
-        <v>1000</v>
-      </c>
-      <c r="J231" s="33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="232" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A232" s="89">
-        <v>54004</v>
-      </c>
-      <c r="B232" s="89">
-        <v>105400</v>
-      </c>
-      <c r="C232" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="D232" s="89">
-        <v>4</v>
-      </c>
-      <c r="E232" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="F232" s="22"/>
-      <c r="G232" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H232" s="33">
-        <v>-500</v>
-      </c>
-      <c r="I232" s="33">
-        <v>500</v>
-      </c>
-      <c r="J232" s="33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="233" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A233" s="89">
-        <v>54005</v>
-      </c>
-      <c r="B233" s="89">
-        <v>105400</v>
-      </c>
-      <c r="C233" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="D233" s="89">
-        <v>5</v>
-      </c>
-      <c r="E233" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="F233" s="22"/>
-      <c r="G233" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H233" s="33">
-        <v>-1000</v>
-      </c>
-      <c r="I233" s="33">
-        <v>-500</v>
-      </c>
-      <c r="J233" s="33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="234" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A234" s="89">
-        <v>54006</v>
-      </c>
-      <c r="B234" s="89">
-        <v>105400</v>
-      </c>
-      <c r="C234" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="D234" s="89">
-        <v>6</v>
-      </c>
-      <c r="E234" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F234" s="22"/>
-      <c r="G234" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H234" s="33">
-        <v>-2000</v>
-      </c>
-      <c r="I234" s="33">
-        <v>-1000</v>
-      </c>
-      <c r="J234" s="33" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="235" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A235" s="89">
-        <v>54007</v>
-      </c>
-      <c r="B235" s="89">
-        <v>105400</v>
-      </c>
-      <c r="C235" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="D235" s="89">
-        <v>7</v>
-      </c>
-      <c r="E235" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F235" s="22"/>
-      <c r="G235" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="H235" s="33">
-        <v>-999999</v>
-      </c>
-      <c r="I235" s="33">
-        <v>-2000</v>
-      </c>
-      <c r="J235" s="33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="236" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A236" s="95">
-        <v>57001</v>
-      </c>
-      <c r="B236" s="96">
-        <v>105700</v>
-      </c>
-      <c r="C236" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="D236" s="97">
-        <v>1</v>
-      </c>
-      <c r="E236" s="98" t="s">
-        <v>54</v>
-      </c>
-      <c r="F236" s="99"/>
-      <c r="G236" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="H236" s="93">
-        <v>2000</v>
-      </c>
-      <c r="I236" s="93">
-        <v>999999</v>
-      </c>
-      <c r="J236" s="100" t="s">
-        <v>23</v>
-      </c>
-      <c r="K236" s="101"/>
-    </row>
-    <row r="237" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A237" s="95">
-        <v>57002</v>
-      </c>
-      <c r="B237" s="96">
-        <v>105700</v>
-      </c>
-      <c r="C237" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="D237" s="97">
-        <v>2</v>
-      </c>
-      <c r="E237" s="98" t="s">
-        <v>56</v>
-      </c>
-      <c r="F237" s="99"/>
-      <c r="G237" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="H237" s="93">
-        <v>1000</v>
-      </c>
-      <c r="I237" s="93">
-        <v>2000</v>
-      </c>
-      <c r="J237" s="100" t="s">
-        <v>25</v>
-      </c>
-      <c r="K237" s="101"/>
-    </row>
-    <row r="238" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A238" s="95">
-        <v>57003</v>
-      </c>
-      <c r="B238" s="96">
-        <v>105700</v>
-      </c>
-      <c r="C238" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="D238" s="97">
-        <v>3</v>
-      </c>
-      <c r="E238" s="98" t="s">
-        <v>57</v>
-      </c>
-      <c r="F238" s="99"/>
-      <c r="G238" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="H238" s="93">
-        <v>500</v>
-      </c>
-      <c r="I238" s="93">
-        <v>1000</v>
-      </c>
-      <c r="J238" s="100" t="s">
-        <v>27</v>
-      </c>
-      <c r="K238" s="101"/>
-    </row>
-    <row r="239" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A239" s="95">
-        <v>57004</v>
-      </c>
-      <c r="B239" s="96">
-        <v>105700</v>
-      </c>
-      <c r="C239" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="D239" s="97">
-        <v>4</v>
-      </c>
-      <c r="E239" s="98" t="s">
-        <v>58</v>
-      </c>
-      <c r="F239" s="99"/>
-      <c r="G239" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="H239" s="93">
-        <v>-500</v>
-      </c>
-      <c r="I239" s="93">
-        <v>500</v>
-      </c>
-      <c r="J239" s="100" t="s">
-        <v>29</v>
-      </c>
-      <c r="K239" s="101"/>
-    </row>
-    <row r="240" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A240" s="95">
-        <v>57005</v>
-      </c>
-      <c r="B240" s="96">
-        <v>105700</v>
-      </c>
-      <c r="C240" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="D240" s="97">
-        <v>5</v>
-      </c>
-      <c r="E240" s="98" t="s">
-        <v>59</v>
-      </c>
-      <c r="F240" s="99"/>
-      <c r="G240" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="H240" s="93">
-        <v>-1000</v>
-      </c>
-      <c r="I240" s="93">
-        <v>-500</v>
-      </c>
-      <c r="J240" s="100" t="s">
-        <v>31</v>
-      </c>
-      <c r="K240" s="101"/>
-    </row>
-    <row r="241" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A241" s="95">
-        <v>57006</v>
-      </c>
-      <c r="B241" s="96">
-        <v>105700</v>
-      </c>
-      <c r="C241" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="D241" s="97">
-        <v>6</v>
-      </c>
-      <c r="E241" s="98" t="s">
-        <v>60</v>
-      </c>
-      <c r="F241" s="99"/>
-      <c r="G241" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="H241" s="93">
-        <v>-2000</v>
-      </c>
-      <c r="I241" s="93">
-        <v>-1000</v>
-      </c>
-      <c r="J241" s="100" t="s">
-        <v>33</v>
-      </c>
-      <c r="K241" s="101"/>
-    </row>
-    <row r="242" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A242" s="95">
-        <v>57007</v>
-      </c>
-      <c r="B242" s="96">
-        <v>105700</v>
-      </c>
-      <c r="C242" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="D242" s="97">
-        <v>7</v>
-      </c>
-      <c r="E242" s="98" t="s">
-        <v>61</v>
-      </c>
-      <c r="F242" s="99"/>
-      <c r="G242" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="H242" s="93">
-        <v>-999999</v>
-      </c>
-      <c r="I242" s="93">
-        <v>-2000</v>
-      </c>
-      <c r="J242" s="100" t="s">
-        <v>35</v>
-      </c>
-      <c r="K242" s="101"/>
-    </row>
-    <row r="243" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A243" s="21">
-        <v>58001</v>
-      </c>
-      <c r="B243" s="102">
-        <v>105800</v>
-      </c>
-      <c r="C243" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="D243" s="102">
-        <v>1</v>
-      </c>
-      <c r="E243" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="F243" s="99"/>
-      <c r="G243" s="27" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="244" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A244" s="21">
-        <v>58002</v>
-      </c>
-      <c r="B244" s="102">
-        <v>105800</v>
-      </c>
-      <c r="C244" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="D244" s="102">
-        <v>2</v>
-      </c>
-      <c r="E244" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="F244" s="99"/>
-      <c r="G244" s="25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="245" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A245" s="21">
-        <v>58003</v>
-      </c>
-      <c r="B245" s="102">
-        <v>105800</v>
-      </c>
-      <c r="C245" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="D245" s="102">
-        <v>3</v>
-      </c>
-      <c r="E245" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="F245" s="99"/>
-      <c r="G245" s="25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="246" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A246" s="21">
-        <v>58004</v>
-      </c>
-      <c r="B246" s="102">
-        <v>105800</v>
-      </c>
-      <c r="C246" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="D246" s="102">
-        <v>4</v>
-      </c>
-      <c r="E246" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="F246" s="99"/>
-      <c r="G246" s="25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="247" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A247" s="21">
-        <v>58005</v>
-      </c>
-      <c r="B247" s="102">
-        <v>105800</v>
-      </c>
-      <c r="C247" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="D247" s="102">
-        <v>5</v>
-      </c>
-      <c r="E247" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="F247" s="99"/>
-      <c r="G247" s="25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="248" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A248" s="21">
-        <v>58006</v>
-      </c>
-      <c r="B248" s="102">
-        <v>105800</v>
-      </c>
-      <c r="C248" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="D248" s="102">
-        <v>6</v>
-      </c>
-      <c r="E248" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="F248" s="99"/>
-      <c r="G248" s="25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="249" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A249" s="21">
-        <v>58007</v>
-      </c>
-      <c r="B249" s="102">
-        <v>105800</v>
-      </c>
-      <c r="C249" s="102" t="s">
-        <v>199</v>
-      </c>
-      <c r="D249" s="102">
-        <v>7</v>
-      </c>
-      <c r="E249" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="F249" s="99"/>
-      <c r="G249" s="25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="250" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A250" s="103">
-        <v>55001</v>
-      </c>
-      <c r="B250" s="104">
-        <v>105500</v>
-      </c>
-      <c r="C250" s="104" t="s">
-        <v>200</v>
-      </c>
-      <c r="D250" s="69">
-        <v>1</v>
-      </c>
-      <c r="E250" s="70" t="s">
-        <v>201</v>
-      </c>
-      <c r="F250" s="99"/>
-      <c r="G250" s="83" t="s">
-        <v>161</v>
-      </c>
-      <c r="H250" s="28">
-        <v>8000</v>
-      </c>
-      <c r="I250" s="28">
-        <v>999999</v>
-      </c>
-      <c r="J250" s="105" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="251" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A251" s="103">
-        <v>55002</v>
-      </c>
-      <c r="B251" s="104">
-        <v>105500</v>
-      </c>
-      <c r="C251" s="104" t="s">
-        <v>200</v>
-      </c>
-      <c r="D251" s="69">
-        <v>2</v>
-      </c>
-      <c r="E251" s="70" t="s">
-        <v>202</v>
-      </c>
-      <c r="F251" s="99"/>
-      <c r="G251" s="83" t="s">
-        <v>161</v>
-      </c>
-      <c r="H251" s="28">
-        <v>6000</v>
-      </c>
-      <c r="I251" s="28">
-        <v>8000</v>
-      </c>
-      <c r="J251" s="105" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="252" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A252" s="103">
-        <v>55003</v>
-      </c>
-      <c r="B252" s="104">
-        <v>105500</v>
-      </c>
-      <c r="C252" s="104" t="s">
-        <v>200</v>
-      </c>
-      <c r="D252" s="69">
-        <v>3</v>
-      </c>
-      <c r="E252" s="70" t="s">
-        <v>203</v>
-      </c>
-      <c r="F252" s="99"/>
-      <c r="G252" s="83" t="s">
-        <v>161</v>
-      </c>
-      <c r="H252" s="28">
-        <v>4000</v>
-      </c>
-      <c r="I252" s="28">
-        <v>6000</v>
-      </c>
-      <c r="J252" s="105" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="253" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A253" s="103">
-        <v>55004</v>
-      </c>
-      <c r="B253" s="104">
-        <v>105500</v>
-      </c>
-      <c r="C253" s="104" t="s">
-        <v>200</v>
-      </c>
-      <c r="D253" s="69">
-        <v>4</v>
-      </c>
-      <c r="E253" s="70" t="s">
-        <v>204</v>
-      </c>
-      <c r="F253" s="99"/>
-      <c r="G253" s="83" t="s">
-        <v>161</v>
-      </c>
-      <c r="H253" s="28">
-        <v>2000</v>
-      </c>
-      <c r="I253" s="28">
-        <v>4000</v>
-      </c>
-      <c r="J253" s="105" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="254" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A254" s="103">
-        <v>55005</v>
-      </c>
-      <c r="B254" s="104">
-        <v>105500</v>
-      </c>
-      <c r="C254" s="104" t="s">
-        <v>200</v>
-      </c>
-      <c r="D254" s="69">
-        <v>5</v>
-      </c>
-      <c r="E254" s="70" t="s">
-        <v>205</v>
-      </c>
-      <c r="F254" s="99"/>
-      <c r="G254" s="83" t="s">
-        <v>161</v>
-      </c>
-      <c r="H254" s="28">
-        <v>0</v>
-      </c>
-      <c r="I254" s="28">
-        <v>2000</v>
-      </c>
-      <c r="J254" s="105" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="255" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A255" s="103">
-        <v>55006</v>
-      </c>
-      <c r="B255" s="104">
-        <v>105500</v>
-      </c>
-      <c r="C255" s="104" t="s">
-        <v>200</v>
-      </c>
-      <c r="D255" s="69">
-        <v>6</v>
-      </c>
-      <c r="E255" s="70" t="s">
-        <v>52</v>
-      </c>
-      <c r="F255" s="99"/>
-      <c r="G255" s="83" t="s">
-        <v>161</v>
-      </c>
-      <c r="H255" s="28">
-        <v>-1000</v>
-      </c>
-      <c r="I255" s="28">
-        <v>0</v>
-      </c>
-      <c r="J255" s="105" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="256" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A256" s="103">
-        <v>55007</v>
-      </c>
-      <c r="B256" s="104">
-        <v>105500</v>
-      </c>
-      <c r="C256" s="104" t="s">
-        <v>200</v>
-      </c>
-      <c r="D256" s="69">
-        <v>7</v>
-      </c>
-      <c r="E256" s="70" t="s">
-        <v>52</v>
-      </c>
-      <c r="F256" s="99"/>
-      <c r="G256" s="83" t="s">
-        <v>161</v>
-      </c>
-      <c r="H256" s="28">
-        <v>-999999</v>
-      </c>
-      <c r="I256" s="28">
-        <v>-1000</v>
-      </c>
-      <c r="J256" s="105" t="s">
+      <c r="J270" s="105" t="s">
         <v>35</v>
       </c>
     </row>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_3789B584A9A1EE387DABE1B383A9EAD968E4F336" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -27,13 +33,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -57,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -83,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -95,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -108,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -141,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0">
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -803,14 +809,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -831,147 +831,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -985,8 +848,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -995,25 +864,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1031,25 +900,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.6"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.4"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.25"/>
+        <fgColor theme="7" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1061,13 +930,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.6"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1097,174 +966,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.4"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1272,254 +985,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1548,7 +1019,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1580,9 +1051,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1777,7 +1245,6 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1789,62 +1256,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 73" xfId="49"/>
+    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2102,27 +1525,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K270"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J270"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="5" width="32.5" style="22" customWidth="1"/>
     <col min="6" max="6" width="77.375" style="22" customWidth="1"/>
-    <col min="7" max="7" width="27.3166666666667" style="22" customWidth="1"/>
+    <col min="7" max="7" width="27.375" style="22" customWidth="1"/>
     <col min="8" max="8" width="15.625" customWidth="1"/>
     <col min="9" max="9" width="15.125" customWidth="1"/>
     <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -2152,7 +1575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:10">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
@@ -2180,7 +1603,7 @@
       </c>
       <c r="J2" s="23"/>
     </row>
-    <row r="3" ht="16.5" spans="1:10">
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
         <v>0</v>
       </c>
@@ -2208,7 +1631,7 @@
       </c>
       <c r="J3" s="23"/>
     </row>
-    <row r="4" ht="16.5" spans="1:10">
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -2220,7 +1643,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="23">
         <v>1001</v>
       </c>
@@ -2250,7 +1673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:10">
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="23">
         <v>1002</v>
       </c>
@@ -2281,7 +1704,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:10">
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="23">
         <v>1003</v>
       </c>
@@ -2312,7 +1735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:10">
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="23">
         <v>1004</v>
       </c>
@@ -2343,7 +1766,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:10">
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="23">
         <v>1005</v>
       </c>
@@ -2374,7 +1797,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:10">
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="23">
         <v>1006</v>
       </c>
@@ -2405,7 +1828,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:10">
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="23">
         <v>1007</v>
       </c>
@@ -2436,7 +1859,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="29">
         <v>3001</v>
       </c>
@@ -2466,7 +1889,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="29">
         <v>3002</v>
       </c>
@@ -2497,7 +1920,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="29">
         <v>3003</v>
       </c>
@@ -2528,7 +1951,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="29">
         <v>3004</v>
       </c>
@@ -2559,7 +1982,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="16" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="29">
         <v>3005</v>
       </c>
@@ -2590,7 +2013,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="17" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="29">
         <v>3006</v>
       </c>
@@ -2621,7 +2044,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="18" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="29">
         <v>3007</v>
       </c>
@@ -2652,7 +2075,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="19" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="23">
         <v>7001</v>
       </c>
@@ -2684,7 +2107,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="23">
         <v>7002</v>
       </c>
@@ -2717,7 +2140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="23">
         <v>7003</v>
       </c>
@@ -2750,7 +2173,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="23">
         <v>7004</v>
       </c>
@@ -2783,7 +2206,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="23">
         <v>7005</v>
       </c>
@@ -2816,7 +2239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="23">
         <v>7006</v>
       </c>
@@ -2849,7 +2272,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="25" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="23">
         <v>7007</v>
       </c>
@@ -2882,7 +2305,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="26" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
         <v>8001</v>
       </c>
@@ -2898,7 +2321,7 @@
       <c r="E26" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="35"/>
+      <c r="F26" s="25"/>
       <c r="G26" s="3" t="s">
         <v>55</v>
       </c>
@@ -2908,11 +2331,11 @@
       <c r="I26" s="28">
         <v>999999</v>
       </c>
-      <c r="J26" s="36" t="s">
+      <c r="J26" s="35" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="27" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>8002</v>
       </c>
@@ -2928,7 +2351,7 @@
       <c r="E27" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="35"/>
+      <c r="F27" s="25"/>
       <c r="G27" s="3" t="s">
         <v>55</v>
       </c>
@@ -2938,11 +2361,11 @@
       <c r="I27" s="28">
         <v>8000</v>
       </c>
-      <c r="J27" s="36" t="s">
+      <c r="J27" s="35" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="28" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
         <v>8003</v>
       </c>
@@ -2958,7 +2381,7 @@
       <c r="E28" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F28" s="35"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="3" t="s">
         <v>55</v>
       </c>
@@ -2968,11 +2391,11 @@
       <c r="I28" s="28">
         <v>6000</v>
       </c>
-      <c r="J28" s="36" t="s">
+      <c r="J28" s="35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="29" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>8004</v>
       </c>
@@ -2988,7 +2411,7 @@
       <c r="E29" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="F29" s="35"/>
+      <c r="F29" s="25"/>
       <c r="G29" s="3" t="s">
         <v>55</v>
       </c>
@@ -2998,11 +2421,11 @@
       <c r="I29" s="28">
         <v>4000</v>
       </c>
-      <c r="J29" s="36" t="s">
+      <c r="J29" s="35" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="30" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
         <v>8005</v>
       </c>
@@ -3018,7 +2441,7 @@
       <c r="E30" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="35"/>
+      <c r="F30" s="25"/>
       <c r="G30" s="3" t="s">
         <v>55</v>
       </c>
@@ -3028,11 +2451,11 @@
       <c r="I30" s="28">
         <v>2000</v>
       </c>
-      <c r="J30" s="36" t="s">
+      <c r="J30" s="35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="31" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>8006</v>
       </c>
@@ -3048,7 +2471,7 @@
       <c r="E31" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="35"/>
+      <c r="F31" s="25"/>
       <c r="G31" s="3" t="s">
         <v>55</v>
       </c>
@@ -3058,11 +2481,11 @@
       <c r="I31" s="28">
         <v>0</v>
       </c>
-      <c r="J31" s="36" t="s">
+      <c r="J31" s="35" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="32" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
         <v>8007</v>
       </c>
@@ -3078,7 +2501,7 @@
       <c r="E32" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F32" s="35"/>
+      <c r="F32" s="25"/>
       <c r="G32" s="3" t="s">
         <v>55</v>
       </c>
@@ -3088,11 +2511,11 @@
       <c r="I32" s="28">
         <v>-1000</v>
       </c>
-      <c r="J32" s="36" t="s">
+      <c r="J32" s="35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="33" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A33" s="29">
         <v>12001</v>
       </c>
@@ -3108,7 +2531,7 @@
       <c r="E33" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="37" t="s">
+      <c r="F33" s="36" t="s">
         <v>64</v>
       </c>
       <c r="G33" s="27" t="s">
@@ -3124,7 +2547,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="34" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A34" s="29">
         <v>12002</v>
       </c>
@@ -3140,7 +2563,7 @@
       <c r="E34" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="F34" s="36" t="s">
         <v>64</v>
       </c>
       <c r="G34" s="25" t="str">
@@ -3157,7 +2580,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="35" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A35" s="29">
         <v>12003</v>
       </c>
@@ -3173,7 +2596,7 @@
       <c r="E35" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="36" t="s">
         <v>64</v>
       </c>
       <c r="G35" s="25" t="str">
@@ -3190,7 +2613,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="36" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A36" s="29">
         <v>12004</v>
       </c>
@@ -3206,7 +2629,7 @@
       <c r="E36" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="F36" s="37" t="s">
+      <c r="F36" s="36" t="s">
         <v>64</v>
       </c>
       <c r="G36" s="25" t="str">
@@ -3223,7 +2646,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="37" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A37" s="29">
         <v>12005</v>
       </c>
@@ -3239,7 +2662,7 @@
       <c r="E37" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="F37" s="37" t="s">
+      <c r="F37" s="36" t="s">
         <v>64</v>
       </c>
       <c r="G37" s="25" t="str">
@@ -3256,7 +2679,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="38" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A38" s="29">
         <v>12006</v>
       </c>
@@ -3272,7 +2695,7 @@
       <c r="E38" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="F38" s="37" t="s">
+      <c r="F38" s="36" t="s">
         <v>64</v>
       </c>
       <c r="G38" s="25" t="str">
@@ -3289,7 +2712,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="39" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A39" s="29">
         <v>12007</v>
       </c>
@@ -3305,7 +2728,7 @@
       <c r="E39" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="36" t="s">
         <v>64</v>
       </c>
       <c r="G39" s="25" t="str">
@@ -3322,20 +2745,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="40" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A40" s="23">
         <v>14001</v>
       </c>
-      <c r="B40" s="38">
+      <c r="B40" s="37">
         <v>101400</v>
       </c>
-      <c r="C40" s="38" t="s">
+      <c r="C40" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D40" s="38">
+      <c r="D40" s="37">
         <v>1</v>
       </c>
-      <c r="E40" s="39" t="s">
+      <c r="E40" s="38" t="s">
         <v>72</v>
       </c>
       <c r="F40" s="25"/>
@@ -3352,20 +2775,20 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="41" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A41" s="23">
         <v>14002</v>
       </c>
-      <c r="B41" s="38">
+      <c r="B41" s="37">
         <v>101400</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D41" s="38">
+      <c r="D41" s="37">
         <v>2</v>
       </c>
-      <c r="E41" s="39" t="s">
+      <c r="E41" s="38" t="s">
         <v>74</v>
       </c>
       <c r="F41" s="25"/>
@@ -3383,20 +2806,20 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="42" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A42" s="23">
         <v>14003</v>
       </c>
-      <c r="B42" s="38">
+      <c r="B42" s="37">
         <v>101400</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="38">
+      <c r="D42" s="37">
         <v>3</v>
       </c>
-      <c r="E42" s="39" t="s">
+      <c r="E42" s="38" t="s">
         <v>75</v>
       </c>
       <c r="F42" s="25"/>
@@ -3414,20 +2837,20 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="43" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A43" s="23">
         <v>14004</v>
       </c>
-      <c r="B43" s="38">
+      <c r="B43" s="37">
         <v>101400</v>
       </c>
-      <c r="C43" s="38" t="s">
+      <c r="C43" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D43" s="38">
+      <c r="D43" s="37">
         <v>4</v>
       </c>
-      <c r="E43" s="39" t="s">
+      <c r="E43" s="38" t="s">
         <v>76</v>
       </c>
       <c r="F43" s="25"/>
@@ -3445,20 +2868,20 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="44" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A44" s="23">
         <v>14005</v>
       </c>
-      <c r="B44" s="38">
+      <c r="B44" s="37">
         <v>101400</v>
       </c>
-      <c r="C44" s="38" t="s">
+      <c r="C44" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D44" s="38">
+      <c r="D44" s="37">
         <v>5</v>
       </c>
-      <c r="E44" s="39" t="s">
+      <c r="E44" s="38" t="s">
         <v>77</v>
       </c>
       <c r="F44" s="25"/>
@@ -3476,20 +2899,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="45" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A45" s="23">
         <v>14006</v>
       </c>
-      <c r="B45" s="38">
+      <c r="B45" s="37">
         <v>101400</v>
       </c>
-      <c r="C45" s="38" t="s">
+      <c r="C45" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D45" s="38">
+      <c r="D45" s="37">
         <v>6</v>
       </c>
-      <c r="E45" s="39" t="s">
+      <c r="E45" s="38" t="s">
         <v>78</v>
       </c>
       <c r="F45" s="25"/>
@@ -3507,20 +2930,20 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="46" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A46" s="23">
         <v>14007</v>
       </c>
-      <c r="B46" s="38">
+      <c r="B46" s="37">
         <v>101400</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="C46" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="D46" s="38">
+      <c r="D46" s="37">
         <v>7</v>
       </c>
-      <c r="E46" s="39" t="s">
+      <c r="E46" s="38" t="s">
         <v>43</v>
       </c>
       <c r="F46" s="25"/>
@@ -3538,24 +2961,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A47" s="40">
+    <row r="47" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A47" s="39">
         <v>15001</v>
       </c>
-      <c r="B47" s="40">
+      <c r="B47" s="39">
         <v>101500</v>
       </c>
-      <c r="C47" s="40" t="s">
+      <c r="C47" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="D47" s="40">
+      <c r="D47" s="39">
         <v>1</v>
       </c>
-      <c r="E47" s="41" t="s">
+      <c r="E47" s="40" t="s">
         <v>80</v>
       </c>
       <c r="F47" s="25"/>
-      <c r="G47" s="42" t="s">
+      <c r="G47" s="41" t="s">
         <v>81</v>
       </c>
       <c r="H47" s="28">
@@ -3564,28 +2987,28 @@
       <c r="I47" s="28">
         <v>999999</v>
       </c>
-      <c r="J47" s="43" t="s">
+      <c r="J47" s="42" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="48" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A48" s="40">
+    <row r="48" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A48" s="39">
         <v>15002</v>
       </c>
-      <c r="B48" s="40">
+      <c r="B48" s="39">
         <v>101500</v>
       </c>
-      <c r="C48" s="40" t="s">
+      <c r="C48" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="D48" s="40">
+      <c r="D48" s="39">
         <v>2</v>
       </c>
-      <c r="E48" s="41" t="s">
+      <c r="E48" s="40" t="s">
         <v>82</v>
       </c>
       <c r="F48" s="25"/>
-      <c r="G48" s="42" t="str">
+      <c r="G48" s="41" t="str">
         <f t="shared" ref="G48:G53" si="5">G47</f>
         <v>1,0&amp;1-64000|1&amp;20-8800|20&amp;40-6800|40&amp;60-3500|60&amp;80-1800|80&amp;100-900|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-500|240&amp;280-200|280&amp;320-200|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-4700|20&amp;40-2100|40&amp;60-200|60&amp;80-100|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-5000|20&amp;40-2300|40&amp;60-900|60&amp;80-300|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-1000|1&amp;20-1000|20&amp;40-3000|40&amp;60-3000|60&amp;80-3500|80&amp;100-3500|100&amp;120-3600|120&amp;140-4000|140&amp;160-3200|160&amp;180-2900|180&amp;200-2700|200&amp;240-300|240&amp;280-5000|280&amp;320-4300|320&amp;360-3900|360&amp;400-3400|400&amp;480-4000|480&amp;560-4600|560&amp;640-3500|640&amp;720-2900|720&amp;800-2200|800&amp;960-3300|960&amp;1120-2300|1120&amp;1280-1500|1280&amp;1440-1200|1440&amp;1600-800|1600&amp;1920-1100|1920&amp;2240-600|2240&amp;2560-400|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3595,28 +3018,28 @@
       <c r="I48" s="28">
         <v>8000</v>
       </c>
-      <c r="J48" s="43" t="s">
+      <c r="J48" s="42" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="49" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A49" s="40">
+    <row r="49" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A49" s="39">
         <v>15003</v>
       </c>
-      <c r="B49" s="40">
+      <c r="B49" s="39">
         <v>101500</v>
       </c>
-      <c r="C49" s="40" t="s">
+      <c r="C49" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="D49" s="40">
+      <c r="D49" s="39">
         <v>3</v>
       </c>
-      <c r="E49" s="41" t="s">
+      <c r="E49" s="40" t="s">
         <v>83</v>
       </c>
       <c r="F49" s="25"/>
-      <c r="G49" s="42" t="str">
+      <c r="G49" s="41" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-64000|1&amp;20-8800|20&amp;40-6800|40&amp;60-3500|60&amp;80-1800|80&amp;100-900|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-500|240&amp;280-200|280&amp;320-200|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-4700|20&amp;40-2100|40&amp;60-200|60&amp;80-100|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-5000|20&amp;40-2300|40&amp;60-900|60&amp;80-300|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-1000|1&amp;20-1000|20&amp;40-3000|40&amp;60-3000|60&amp;80-3500|80&amp;100-3500|100&amp;120-3600|120&amp;140-4000|140&amp;160-3200|160&amp;180-2900|180&amp;200-2700|200&amp;240-300|240&amp;280-5000|280&amp;320-4300|320&amp;360-3900|360&amp;400-3400|400&amp;480-4000|480&amp;560-4600|560&amp;640-3500|640&amp;720-2900|720&amp;800-2200|800&amp;960-3300|960&amp;1120-2300|1120&amp;1280-1500|1280&amp;1440-1200|1440&amp;1600-800|1600&amp;1920-1100|1920&amp;2240-600|2240&amp;2560-400|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3626,28 +3049,28 @@
       <c r="I49" s="28">
         <v>6000</v>
       </c>
-      <c r="J49" s="43" t="s">
+      <c r="J49" s="42" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="50" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A50" s="40">
+    <row r="50" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A50" s="39">
         <v>15004</v>
       </c>
-      <c r="B50" s="40">
+      <c r="B50" s="39">
         <v>101500</v>
       </c>
-      <c r="C50" s="40" t="s">
+      <c r="C50" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="D50" s="40">
+      <c r="D50" s="39">
         <v>4</v>
       </c>
-      <c r="E50" s="41" t="s">
+      <c r="E50" s="40" t="s">
         <v>84</v>
       </c>
       <c r="F50" s="25"/>
-      <c r="G50" s="42" t="str">
+      <c r="G50" s="41" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-64000|1&amp;20-8800|20&amp;40-6800|40&amp;60-3500|60&amp;80-1800|80&amp;100-900|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-500|240&amp;280-200|280&amp;320-200|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-4700|20&amp;40-2100|40&amp;60-200|60&amp;80-100|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-5000|20&amp;40-2300|40&amp;60-900|60&amp;80-300|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-1000|1&amp;20-1000|20&amp;40-3000|40&amp;60-3000|60&amp;80-3500|80&amp;100-3500|100&amp;120-3600|120&amp;140-4000|140&amp;160-3200|160&amp;180-2900|180&amp;200-2700|200&amp;240-300|240&amp;280-5000|280&amp;320-4300|320&amp;360-3900|360&amp;400-3400|400&amp;480-4000|480&amp;560-4600|560&amp;640-3500|640&amp;720-2900|720&amp;800-2200|800&amp;960-3300|960&amp;1120-2300|1120&amp;1280-1500|1280&amp;1440-1200|1440&amp;1600-800|1600&amp;1920-1100|1920&amp;2240-600|2240&amp;2560-400|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3657,28 +3080,28 @@
       <c r="I50" s="28">
         <v>4000</v>
       </c>
-      <c r="J50" s="43" t="s">
+      <c r="J50" s="42" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A51" s="40">
+    <row r="51" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A51" s="39">
         <v>15005</v>
       </c>
-      <c r="B51" s="40">
+      <c r="B51" s="39">
         <v>101500</v>
       </c>
-      <c r="C51" s="40" t="s">
+      <c r="C51" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="D51" s="40">
+      <c r="D51" s="39">
         <v>5</v>
       </c>
-      <c r="E51" s="41" t="s">
+      <c r="E51" s="40" t="s">
         <v>85</v>
       </c>
       <c r="F51" s="25"/>
-      <c r="G51" s="42" t="str">
+      <c r="G51" s="41" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-64000|1&amp;20-8800|20&amp;40-6800|40&amp;60-3500|60&amp;80-1800|80&amp;100-900|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-500|240&amp;280-200|280&amp;320-200|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-4700|20&amp;40-2100|40&amp;60-200|60&amp;80-100|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-5000|20&amp;40-2300|40&amp;60-900|60&amp;80-300|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-1000|1&amp;20-1000|20&amp;40-3000|40&amp;60-3000|60&amp;80-3500|80&amp;100-3500|100&amp;120-3600|120&amp;140-4000|140&amp;160-3200|160&amp;180-2900|180&amp;200-2700|200&amp;240-300|240&amp;280-5000|280&amp;320-4300|320&amp;360-3900|360&amp;400-3400|400&amp;480-4000|480&amp;560-4600|560&amp;640-3500|640&amp;720-2900|720&amp;800-2200|800&amp;960-3300|960&amp;1120-2300|1120&amp;1280-1500|1280&amp;1440-1200|1440&amp;1600-800|1600&amp;1920-1100|1920&amp;2240-600|2240&amp;2560-400|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3688,28 +3111,28 @@
       <c r="I51" s="28">
         <v>2000</v>
       </c>
-      <c r="J51" s="43" t="s">
+      <c r="J51" s="42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A52" s="40">
+    <row r="52" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A52" s="39">
         <v>15006</v>
       </c>
-      <c r="B52" s="40">
+      <c r="B52" s="39">
         <v>101500</v>
       </c>
-      <c r="C52" s="40" t="s">
+      <c r="C52" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="D52" s="40">
+      <c r="D52" s="39">
         <v>6</v>
       </c>
-      <c r="E52" s="41" t="s">
+      <c r="E52" s="40" t="s">
         <v>86</v>
       </c>
       <c r="F52" s="25"/>
-      <c r="G52" s="42" t="str">
+      <c r="G52" s="41" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-64000|1&amp;20-8800|20&amp;40-6800|40&amp;60-3500|60&amp;80-1800|80&amp;100-900|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-500|240&amp;280-200|280&amp;320-200|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-4700|20&amp;40-2100|40&amp;60-200|60&amp;80-100|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-5000|20&amp;40-2300|40&amp;60-900|60&amp;80-300|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-1000|1&amp;20-1000|20&amp;40-3000|40&amp;60-3000|60&amp;80-3500|80&amp;100-3500|100&amp;120-3600|120&amp;140-4000|140&amp;160-3200|160&amp;180-2900|180&amp;200-2700|200&amp;240-300|240&amp;280-5000|280&amp;320-4300|320&amp;360-3900|360&amp;400-3400|400&amp;480-4000|480&amp;560-4600|560&amp;640-3500|640&amp;720-2900|720&amp;800-2200|800&amp;960-3300|960&amp;1120-2300|1120&amp;1280-1500|1280&amp;1440-1200|1440&amp;1600-800|1600&amp;1920-1100|1920&amp;2240-600|2240&amp;2560-400|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3719,28 +3142,28 @@
       <c r="I52" s="28">
         <v>0</v>
       </c>
-      <c r="J52" s="43" t="s">
+      <c r="J52" s="42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="53" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A53" s="40">
+    <row r="53" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A53" s="39">
         <v>15007</v>
       </c>
-      <c r="B53" s="40">
+      <c r="B53" s="39">
         <v>101500</v>
       </c>
-      <c r="C53" s="40" t="s">
+      <c r="C53" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="D53" s="40">
+      <c r="D53" s="39">
         <v>7</v>
       </c>
-      <c r="E53" s="41" t="s">
+      <c r="E53" s="40" t="s">
         <v>87</v>
       </c>
       <c r="F53" s="25"/>
-      <c r="G53" s="42" t="str">
+      <c r="G53" s="41" t="str">
         <f t="shared" si="5"/>
         <v>1,0&amp;1-64000|1&amp;20-8800|20&amp;40-6800|40&amp;60-3500|60&amp;80-1800|80&amp;100-900|100&amp;120-800|120&amp;140-500|140&amp;160-500|160&amp;180-300|180&amp;200-200|200&amp;240-500|240&amp;280-200|280&amp;320-200|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-85200|1&amp;20-4700|20&amp;40-2100|40&amp;60-200|60&amp;80-100|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-5000|20&amp;40-2300|40&amp;60-900|60&amp;80-300|80&amp;100-100|100&amp;120-100|120&amp;140-100|140&amp;160-100|160&amp;180-100|180&amp;200-0|200&amp;240-100|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-1000|1&amp;20-1000|20&amp;40-3000|40&amp;60-3000|60&amp;80-3500|80&amp;100-3500|100&amp;120-3600|120&amp;140-4000|140&amp;160-3200|160&amp;180-2900|180&amp;200-2700|200&amp;240-300|240&amp;280-5000|280&amp;320-4300|320&amp;360-3900|360&amp;400-3400|400&amp;480-4000|480&amp;560-4600|560&amp;640-3500|640&amp;720-2900|720&amp;800-2200|800&amp;960-3300|960&amp;1120-2300|1120&amp;1280-1500|1280&amp;1440-1200|1440&amp;1600-800|1600&amp;1920-1100|1920&amp;2240-600|2240&amp;2560-400|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-1000|1&amp;20-200|20&amp;40-1800|40&amp;60-1400|60&amp;80-2300|80&amp;100-2100|100&amp;120-1300|120&amp;140-2200|140&amp;160-1800|160&amp;180-1200|180&amp;200-2000|200&amp;240-2900|240&amp;280-3400|280&amp;320-2700|320&amp;360-2400|360&amp;400-2900|400&amp;480-4100|480&amp;560-3700|560&amp;640-3200|640&amp;720-2600|720&amp;800-2600|800&amp;960-4100|960&amp;1120-3400|1120&amp;1280-1500|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3750,28 +3173,28 @@
       <c r="I53" s="28">
         <v>-1000</v>
       </c>
-      <c r="J53" s="43" t="s">
+      <c r="J53" s="42" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A54" s="44">
+    <row r="54" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A54" s="43">
         <v>16001</v>
       </c>
-      <c r="B54" s="44">
+      <c r="B54" s="43">
         <v>101600</v>
       </c>
-      <c r="C54" s="44" t="s">
+      <c r="C54" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="44">
+      <c r="D54" s="43">
         <v>1</v>
       </c>
-      <c r="E54" s="45" t="s">
+      <c r="E54" s="44" t="s">
         <v>54</v>
       </c>
       <c r="F54" s="25"/>
-      <c r="G54" s="46" t="s">
+      <c r="G54" s="45" t="s">
         <v>55</v>
       </c>
       <c r="H54" s="28">
@@ -3780,28 +3203,28 @@
       <c r="I54" s="28">
         <v>999999</v>
       </c>
-      <c r="J54" s="47" t="s">
+      <c r="J54" s="46" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="55" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A55" s="44">
+    <row r="55" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A55" s="43">
         <v>16002</v>
       </c>
-      <c r="B55" s="44">
+      <c r="B55" s="43">
         <v>101600</v>
       </c>
-      <c r="C55" s="44" t="s">
+      <c r="C55" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="D55" s="44">
+      <c r="D55" s="43">
         <v>2</v>
       </c>
-      <c r="E55" s="45" t="s">
+      <c r="E55" s="44" t="s">
         <v>56</v>
       </c>
       <c r="F55" s="25"/>
-      <c r="G55" s="46" t="str">
+      <c r="G55" s="45" t="str">
         <f t="shared" ref="G55:G60" si="6">G54</f>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3811,28 +3234,28 @@
       <c r="I55" s="28">
         <v>8000</v>
       </c>
-      <c r="J55" s="47" t="s">
+      <c r="J55" s="46" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="56" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A56" s="44">
+    <row r="56" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A56" s="43">
         <v>16003</v>
       </c>
-      <c r="B56" s="44">
+      <c r="B56" s="43">
         <v>101600</v>
       </c>
-      <c r="C56" s="44" t="s">
+      <c r="C56" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="D56" s="44">
+      <c r="D56" s="43">
         <v>3</v>
       </c>
-      <c r="E56" s="45" t="s">
+      <c r="E56" s="44" t="s">
         <v>57</v>
       </c>
       <c r="F56" s="25"/>
-      <c r="G56" s="46" t="str">
+      <c r="G56" s="45" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3842,28 +3265,28 @@
       <c r="I56" s="28">
         <v>6000</v>
       </c>
-      <c r="J56" s="47" t="s">
+      <c r="J56" s="46" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="57" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A57" s="44">
+    <row r="57" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A57" s="43">
         <v>16004</v>
       </c>
-      <c r="B57" s="44">
+      <c r="B57" s="43">
         <v>101600</v>
       </c>
-      <c r="C57" s="44" t="s">
+      <c r="C57" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="D57" s="44">
+      <c r="D57" s="43">
         <v>4</v>
       </c>
-      <c r="E57" s="45" t="s">
+      <c r="E57" s="44" t="s">
         <v>58</v>
       </c>
       <c r="F57" s="25"/>
-      <c r="G57" s="46" t="str">
+      <c r="G57" s="45" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3873,28 +3296,28 @@
       <c r="I57" s="28">
         <v>4000</v>
       </c>
-      <c r="J57" s="47" t="s">
+      <c r="J57" s="46" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="58" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A58" s="44">
+    <row r="58" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A58" s="43">
         <v>16005</v>
       </c>
-      <c r="B58" s="44">
+      <c r="B58" s="43">
         <v>101600</v>
       </c>
-      <c r="C58" s="44" t="s">
+      <c r="C58" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="D58" s="44">
+      <c r="D58" s="43">
         <v>5</v>
       </c>
-      <c r="E58" s="45" t="s">
+      <c r="E58" s="44" t="s">
         <v>59</v>
       </c>
       <c r="F58" s="25"/>
-      <c r="G58" s="46" t="str">
+      <c r="G58" s="45" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3904,28 +3327,28 @@
       <c r="I58" s="28">
         <v>2000</v>
       </c>
-      <c r="J58" s="47" t="s">
+      <c r="J58" s="46" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="59" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A59" s="44">
+    <row r="59" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A59" s="43">
         <v>16006</v>
       </c>
-      <c r="B59" s="44">
+      <c r="B59" s="43">
         <v>101600</v>
       </c>
-      <c r="C59" s="44" t="s">
+      <c r="C59" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="D59" s="44">
+      <c r="D59" s="43">
         <v>6</v>
       </c>
-      <c r="E59" s="45" t="s">
+      <c r="E59" s="44" t="s">
         <v>60</v>
       </c>
       <c r="F59" s="25"/>
-      <c r="G59" s="46" t="str">
+      <c r="G59" s="45" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3935,28 +3358,28 @@
       <c r="I59" s="28">
         <v>0</v>
       </c>
-      <c r="J59" s="47" t="s">
+      <c r="J59" s="46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="60" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A60" s="44">
+    <row r="60" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A60" s="43">
         <v>16007</v>
       </c>
-      <c r="B60" s="44">
+      <c r="B60" s="43">
         <v>101600</v>
       </c>
-      <c r="C60" s="44" t="s">
+      <c r="C60" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="D60" s="44">
+      <c r="D60" s="43">
         <v>7</v>
       </c>
-      <c r="E60" s="45" t="s">
+      <c r="E60" s="44" t="s">
         <v>61</v>
       </c>
       <c r="F60" s="25"/>
-      <c r="G60" s="46" t="str">
+      <c r="G60" s="45" t="str">
         <f t="shared" si="6"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -3966,11 +3389,11 @@
       <c r="I60" s="28">
         <v>-1000</v>
       </c>
-      <c r="J60" s="47" t="s">
+      <c r="J60" s="46" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="61" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A61" s="23">
         <v>17001</v>
       </c>
@@ -4002,7 +3425,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="62" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A62" s="23">
         <v>17002</v>
       </c>
@@ -4035,7 +3458,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="63" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A63" s="23">
         <v>17003</v>
       </c>
@@ -4068,7 +3491,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="64" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A64" s="23">
         <v>17004</v>
       </c>
@@ -4101,7 +3524,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="65" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A65" s="23">
         <v>17005</v>
       </c>
@@ -4134,7 +3557,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="66" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A66" s="23">
         <v>17006</v>
       </c>
@@ -4167,7 +3590,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="67" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A67" s="23">
         <v>17007</v>
       </c>
@@ -4200,20 +3623,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" s="7" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A68" s="48">
+    <row r="68" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A68" s="47">
         <v>18001</v>
       </c>
-      <c r="B68" s="48">
+      <c r="B68" s="47">
         <v>101800</v>
       </c>
-      <c r="C68" s="48" t="s">
+      <c r="C68" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="D68" s="48">
+      <c r="D68" s="47">
         <v>1</v>
       </c>
-      <c r="E68" s="49" t="s">
+      <c r="E68" s="48" t="s">
         <v>99</v>
       </c>
       <c r="F68" s="25" t="s">
@@ -4232,26 +3655,26 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A69" s="48">
+    <row r="69" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A69" s="47">
         <v>18002</v>
       </c>
-      <c r="B69" s="48">
+      <c r="B69" s="47">
         <v>101800</v>
       </c>
-      <c r="C69" s="48" t="s">
+      <c r="C69" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="D69" s="48">
+      <c r="D69" s="47">
         <v>2</v>
       </c>
-      <c r="E69" s="49" t="s">
+      <c r="E69" s="48" t="s">
         <v>101</v>
       </c>
       <c r="F69" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G69" s="50" t="str">
+      <c r="G69" s="49" t="str">
         <f t="shared" ref="G69:G74" si="8">G68</f>
         <v>1,0&amp;1-74000|1&amp;20-13000|20&amp;40-2000|40&amp;60-1500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1000|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-400|240&amp;280-200|280&amp;320-200|320&amp;360-100|360&amp;400-100|400&amp;480-50|480&amp;560-50|560&amp;640-10|640&amp;720-10|720&amp;800-10|800&amp;960-10|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-4500|240&amp;280-4500|280&amp;320-4500|320&amp;360-4500|360&amp;400-4500|400&amp;480-4500|480&amp;560-4500|560&amp;640-4500|640&amp;720-3500|720&amp;800-3500|800&amp;960-3500|960&amp;1120-3500|1120&amp;1280-3500|1280&amp;1440-3500|1440&amp;1600-2500|1600&amp;1920-2500|1920&amp;2240-2500|2240&amp;2560-2500|2560&amp;2880-1500|2880&amp;3200-1500|3200&amp;3840-1000|3840&amp;4480-500|4480&amp;5120-500|5120&amp;5760-500|5760&amp;6400-500|6400&amp;7400-200|7400&amp;8400-200|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -4265,26 +3688,26 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" s="7" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A70" s="48">
+    <row r="70" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A70" s="47">
         <v>18003</v>
       </c>
-      <c r="B70" s="48">
+      <c r="B70" s="47">
         <v>101800</v>
       </c>
-      <c r="C70" s="48" t="s">
+      <c r="C70" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="D70" s="48">
+      <c r="D70" s="47">
         <v>3</v>
       </c>
-      <c r="E70" s="49" t="s">
+      <c r="E70" s="48" t="s">
         <v>102</v>
       </c>
       <c r="F70" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G70" s="50" t="str">
+      <c r="G70" s="49" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-74000|1&amp;20-13000|20&amp;40-2000|40&amp;60-1500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1000|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-400|240&amp;280-200|280&amp;320-200|320&amp;360-100|360&amp;400-100|400&amp;480-50|480&amp;560-50|560&amp;640-10|640&amp;720-10|720&amp;800-10|800&amp;960-10|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-4500|240&amp;280-4500|280&amp;320-4500|320&amp;360-4500|360&amp;400-4500|400&amp;480-4500|480&amp;560-4500|560&amp;640-4500|640&amp;720-3500|720&amp;800-3500|800&amp;960-3500|960&amp;1120-3500|1120&amp;1280-3500|1280&amp;1440-3500|1440&amp;1600-2500|1600&amp;1920-2500|1920&amp;2240-2500|2240&amp;2560-2500|2560&amp;2880-1500|2880&amp;3200-1500|3200&amp;3840-1000|3840&amp;4480-500|4480&amp;5120-500|5120&amp;5760-500|5760&amp;6400-500|6400&amp;7400-200|7400&amp;8400-200|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -4298,26 +3721,26 @@
         <v>27</v>
       </c>
     </row>
-    <row r="71" s="7" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A71" s="48">
+    <row r="71" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A71" s="47">
         <v>18004</v>
       </c>
-      <c r="B71" s="48">
+      <c r="B71" s="47">
         <v>101800</v>
       </c>
-      <c r="C71" s="48" t="s">
+      <c r="C71" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="D71" s="48">
+      <c r="D71" s="47">
         <v>4</v>
       </c>
-      <c r="E71" s="49" t="s">
+      <c r="E71" s="48" t="s">
         <v>103</v>
       </c>
       <c r="F71" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G71" s="50" t="str">
+      <c r="G71" s="49" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-74000|1&amp;20-13000|20&amp;40-2000|40&amp;60-1500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1000|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-400|240&amp;280-200|280&amp;320-200|320&amp;360-100|360&amp;400-100|400&amp;480-50|480&amp;560-50|560&amp;640-10|640&amp;720-10|720&amp;800-10|800&amp;960-10|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-4500|240&amp;280-4500|280&amp;320-4500|320&amp;360-4500|360&amp;400-4500|400&amp;480-4500|480&amp;560-4500|560&amp;640-4500|640&amp;720-3500|720&amp;800-3500|800&amp;960-3500|960&amp;1120-3500|1120&amp;1280-3500|1280&amp;1440-3500|1440&amp;1600-2500|1600&amp;1920-2500|1920&amp;2240-2500|2240&amp;2560-2500|2560&amp;2880-1500|2880&amp;3200-1500|3200&amp;3840-1000|3840&amp;4480-500|4480&amp;5120-500|5120&amp;5760-500|5760&amp;6400-500|6400&amp;7400-200|7400&amp;8400-200|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -4331,26 +3754,26 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" s="7" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A72" s="48">
+    <row r="72" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A72" s="47">
         <v>18005</v>
       </c>
-      <c r="B72" s="48">
+      <c r="B72" s="47">
         <v>101800</v>
       </c>
-      <c r="C72" s="48" t="s">
+      <c r="C72" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="D72" s="48">
+      <c r="D72" s="47">
         <v>5</v>
       </c>
-      <c r="E72" s="49" t="s">
+      <c r="E72" s="48" t="s">
         <v>104</v>
       </c>
       <c r="F72" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G72" s="50" t="str">
+      <c r="G72" s="49" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-74000|1&amp;20-13000|20&amp;40-2000|40&amp;60-1500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1000|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-400|240&amp;280-200|280&amp;320-200|320&amp;360-100|360&amp;400-100|400&amp;480-50|480&amp;560-50|560&amp;640-10|640&amp;720-10|720&amp;800-10|800&amp;960-10|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-4500|240&amp;280-4500|280&amp;320-4500|320&amp;360-4500|360&amp;400-4500|400&amp;480-4500|480&amp;560-4500|560&amp;640-4500|640&amp;720-3500|720&amp;800-3500|800&amp;960-3500|960&amp;1120-3500|1120&amp;1280-3500|1280&amp;1440-3500|1440&amp;1600-2500|1600&amp;1920-2500|1920&amp;2240-2500|2240&amp;2560-2500|2560&amp;2880-1500|2880&amp;3200-1500|3200&amp;3840-1000|3840&amp;4480-500|4480&amp;5120-500|5120&amp;5760-500|5760&amp;6400-500|6400&amp;7400-200|7400&amp;8400-200|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -4364,26 +3787,26 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" s="7" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A73" s="48">
+    <row r="73" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A73" s="47">
         <v>18006</v>
       </c>
-      <c r="B73" s="48">
+      <c r="B73" s="47">
         <v>101800</v>
       </c>
-      <c r="C73" s="48" t="s">
+      <c r="C73" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="D73" s="48">
+      <c r="D73" s="47">
         <v>6</v>
       </c>
-      <c r="E73" s="49" t="s">
+      <c r="E73" s="48" t="s">
         <v>43</v>
       </c>
       <c r="F73" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G73" s="50" t="str">
+      <c r="G73" s="49" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-74000|1&amp;20-13000|20&amp;40-2000|40&amp;60-1500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1000|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-400|240&amp;280-200|280&amp;320-200|320&amp;360-100|360&amp;400-100|400&amp;480-50|480&amp;560-50|560&amp;640-10|640&amp;720-10|720&amp;800-10|800&amp;960-10|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-4500|240&amp;280-4500|280&amp;320-4500|320&amp;360-4500|360&amp;400-4500|400&amp;480-4500|480&amp;560-4500|560&amp;640-4500|640&amp;720-3500|720&amp;800-3500|800&amp;960-3500|960&amp;1120-3500|1120&amp;1280-3500|1280&amp;1440-3500|1440&amp;1600-2500|1600&amp;1920-2500|1920&amp;2240-2500|2240&amp;2560-2500|2560&amp;2880-1500|2880&amp;3200-1500|3200&amp;3840-1000|3840&amp;4480-500|4480&amp;5120-500|5120&amp;5760-500|5760&amp;6400-500|6400&amp;7400-200|7400&amp;8400-200|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -4397,26 +3820,26 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" s="7" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A74" s="48">
+    <row r="74" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A74" s="47">
         <v>18007</v>
       </c>
-      <c r="B74" s="48">
+      <c r="B74" s="47">
         <v>101800</v>
       </c>
-      <c r="C74" s="48" t="s">
+      <c r="C74" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="D74" s="48">
+      <c r="D74" s="47">
         <v>7</v>
       </c>
-      <c r="E74" s="49" t="s">
+      <c r="E74" s="48" t="s">
         <v>43</v>
       </c>
       <c r="F74" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G74" s="50" t="str">
+      <c r="G74" s="49" t="str">
         <f t="shared" si="8"/>
         <v>1,0&amp;1-74000|1&amp;20-13000|20&amp;40-2000|40&amp;60-1500|60&amp;80-1500|80&amp;100-1000|100&amp;120-1000|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-400|240&amp;280-200|280&amp;320-200|320&amp;360-100|360&amp;400-100|400&amp;480-50|480&amp;560-50|560&amp;640-10|640&amp;720-10|720&amp;800-10|800&amp;960-10|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-0|80&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-4500|240&amp;280-4500|280&amp;320-4500|320&amp;360-4500|360&amp;400-4500|400&amp;480-4500|480&amp;560-4500|560&amp;640-4500|640&amp;720-3500|720&amp;800-3500|800&amp;960-3500|960&amp;1120-3500|1120&amp;1280-3500|1280&amp;1440-3500|1440&amp;1600-2500|1600&amp;1920-2500|1920&amp;2240-2500|2240&amp;2560-2500|2560&amp;2880-1500|2880&amp;3200-1500|3200&amp;3840-1000|3840&amp;4480-500|4480&amp;5120-500|5120&amp;5760-500|5760&amp;6400-500|6400&amp;7400-200|7400&amp;8400-200|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -4430,24 +3853,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A75" s="40">
+    <row r="75" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A75" s="39">
         <v>20001</v>
       </c>
-      <c r="B75" s="40">
+      <c r="B75" s="39">
         <v>102000</v>
       </c>
-      <c r="C75" s="40" t="s">
+      <c r="C75" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="D75" s="40">
+      <c r="D75" s="39">
         <v>1</v>
       </c>
-      <c r="E75" s="41" t="s">
+      <c r="E75" s="40" t="s">
         <v>54</v>
       </c>
       <c r="F75" s="25"/>
-      <c r="G75" s="42" t="s">
+      <c r="G75" s="41" t="s">
         <v>106</v>
       </c>
       <c r="H75" s="28">
@@ -4456,28 +3879,28 @@
       <c r="I75" s="28">
         <v>999999</v>
       </c>
-      <c r="J75" s="43" t="s">
+      <c r="J75" s="42" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="76" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A76" s="40">
+    <row r="76" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A76" s="39">
         <v>20002</v>
       </c>
-      <c r="B76" s="40">
+      <c r="B76" s="39">
         <v>102000</v>
       </c>
-      <c r="C76" s="40" t="s">
+      <c r="C76" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="D76" s="40">
+      <c r="D76" s="39">
         <v>2</v>
       </c>
-      <c r="E76" s="41" t="s">
+      <c r="E76" s="40" t="s">
         <v>56</v>
       </c>
       <c r="F76" s="25"/>
-      <c r="G76" s="42" t="str">
+      <c r="G76" s="41" t="str">
         <f t="shared" ref="G76:G81" si="9">G75</f>
         <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
       </c>
@@ -4487,28 +3910,28 @@
       <c r="I76" s="28">
         <v>8000</v>
       </c>
-      <c r="J76" s="43" t="s">
+      <c r="J76" s="42" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="77" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A77" s="40">
+    <row r="77" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A77" s="39">
         <v>20003</v>
       </c>
-      <c r="B77" s="40">
+      <c r="B77" s="39">
         <v>102000</v>
       </c>
-      <c r="C77" s="40" t="s">
+      <c r="C77" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="D77" s="40">
+      <c r="D77" s="39">
         <v>3</v>
       </c>
-      <c r="E77" s="41" t="s">
+      <c r="E77" s="40" t="s">
         <v>57</v>
       </c>
       <c r="F77" s="25"/>
-      <c r="G77" s="42" t="str">
+      <c r="G77" s="41" t="str">
         <f t="shared" si="9"/>
         <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
       </c>
@@ -4518,28 +3941,28 @@
       <c r="I77" s="28">
         <v>6000</v>
       </c>
-      <c r="J77" s="43" t="s">
+      <c r="J77" s="42" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="78" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A78" s="40">
+    <row r="78" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A78" s="39">
         <v>20004</v>
       </c>
-      <c r="B78" s="40">
+      <c r="B78" s="39">
         <v>102000</v>
       </c>
-      <c r="C78" s="40" t="s">
+      <c r="C78" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="D78" s="40">
+      <c r="D78" s="39">
         <v>4</v>
       </c>
-      <c r="E78" s="41" t="s">
+      <c r="E78" s="40" t="s">
         <v>58</v>
       </c>
       <c r="F78" s="25"/>
-      <c r="G78" s="42" t="str">
+      <c r="G78" s="41" t="str">
         <f t="shared" si="9"/>
         <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
       </c>
@@ -4549,28 +3972,28 @@
       <c r="I78" s="28">
         <v>4000</v>
       </c>
-      <c r="J78" s="43" t="s">
+      <c r="J78" s="42" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="79" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A79" s="40">
+    <row r="79" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A79" s="39">
         <v>20005</v>
       </c>
-      <c r="B79" s="40">
+      <c r="B79" s="39">
         <v>102000</v>
       </c>
-      <c r="C79" s="40" t="s">
+      <c r="C79" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="D79" s="40">
+      <c r="D79" s="39">
         <v>5</v>
       </c>
-      <c r="E79" s="41" t="s">
+      <c r="E79" s="40" t="s">
         <v>59</v>
       </c>
       <c r="F79" s="25"/>
-      <c r="G79" s="42" t="str">
+      <c r="G79" s="41" t="str">
         <f t="shared" si="9"/>
         <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
       </c>
@@ -4580,28 +4003,28 @@
       <c r="I79" s="28">
         <v>2000</v>
       </c>
-      <c r="J79" s="43" t="s">
+      <c r="J79" s="42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="80" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A80" s="40">
+    <row r="80" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A80" s="39">
         <v>20006</v>
       </c>
-      <c r="B80" s="40">
+      <c r="B80" s="39">
         <v>102000</v>
       </c>
-      <c r="C80" s="40" t="s">
+      <c r="C80" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="D80" s="40">
+      <c r="D80" s="39">
         <v>6</v>
       </c>
-      <c r="E80" s="41" t="s">
+      <c r="E80" s="40" t="s">
         <v>60</v>
       </c>
       <c r="F80" s="25"/>
-      <c r="G80" s="42" t="str">
+      <c r="G80" s="41" t="str">
         <f t="shared" si="9"/>
         <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
       </c>
@@ -4611,28 +4034,28 @@
       <c r="I80" s="28">
         <v>0</v>
       </c>
-      <c r="J80" s="43" t="s">
+      <c r="J80" s="42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="81" s="5" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A81" s="40">
+    <row r="81" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A81" s="39">
         <v>20007</v>
       </c>
-      <c r="B81" s="40">
+      <c r="B81" s="39">
         <v>102000</v>
       </c>
-      <c r="C81" s="40" t="s">
+      <c r="C81" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="D81" s="40">
+      <c r="D81" s="39">
         <v>7</v>
       </c>
-      <c r="E81" s="41" t="s">
+      <c r="E81" s="40" t="s">
         <v>61</v>
       </c>
       <c r="F81" s="25"/>
-      <c r="G81" s="42" t="str">
+      <c r="G81" s="41" t="str">
         <f t="shared" si="9"/>
         <v>1,0&amp;1-64000|1&amp;15-8800|15&amp;30-6800|30&amp;45-3500|45&amp;60-1800|60&amp;75-900|75&amp;90-800|90&amp;105-500|105&amp;120-500|120&amp;135-300|135&amp;150-200|150&amp;180-500|180&amp;210-200|210&amp;240-200|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;2,0&amp;1-85200|1&amp;15-4700|15&amp;30-2100|30&amp;45-200|45&amp;60-100|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-0|120&amp;135-0|135&amp;150-0|150&amp;180-0|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;3,0&amp;1-91000|1&amp;15-5000|15&amp;30-2300|30&amp;45-900|45&amp;60-300|60&amp;75-100|75&amp;90-100|90&amp;105-100|105&amp;120-100|120&amp;135-100|135&amp;150-0|150&amp;180-100|180&amp;210-0|210&amp;240-0|240&amp;270-0|270&amp;300-0|300&amp;360-0|360&amp;420-0|420&amp;480-0|480&amp;540-0|540&amp;600-0|600&amp;720-0|720&amp;840-0|840&amp;960-0|960&amp;1080-0|1080&amp;1200-0|1200&amp;1440-0|1440&amp;1680-0|1680&amp;1920-0|1920&amp;2160-0|2160&amp;2400-0|2400&amp;2880-0|2880&amp;3360-0|3360&amp;3840-0|3840&amp;4320-0|4320&amp;4800-0|4800&amp;5550-0|5550&amp;6300-0|6300&amp;99999999-0;4,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400;5,0&amp;1-100|1&amp;15-100|15&amp;30-100|30&amp;45-300|45&amp;60-300|60&amp;75-400|75&amp;90-400|90&amp;105-500|105&amp;120-400|120&amp;135-600|135&amp;150-500|150&amp;180-1200|180&amp;210-1400|210&amp;240-1500|240&amp;270-1800|270&amp;300-1700|300&amp;360-3600|360&amp;420-3700|420&amp;480-3800|480&amp;540-3700|540&amp;600-3700|600&amp;720-6900|720&amp;840-6100|840&amp;960-5900|960&amp;1080-5300|1080&amp;1200-4700|1200&amp;1440-7700|1440&amp;1680-6100|1680&amp;1920-5000|1920&amp;2160-3900|2160&amp;2400-3200|2400&amp;2880-4500|2880&amp;3360-3100|3360&amp;3840-2100|3840&amp;4320-1400|4320&amp;4800-900|4800&amp;5550-1100|5550&amp;6300-700|6300&amp;99999999-1400</v>
       </c>
@@ -4642,24 +4065,24 @@
       <c r="I81" s="28">
         <v>-1000</v>
       </c>
-      <c r="J81" s="43" t="s">
+      <c r="J81" s="42" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="82" s="8" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A82" s="51">
+    <row r="82" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A82" s="50">
         <v>21001</v>
       </c>
-      <c r="B82" s="51">
+      <c r="B82" s="50">
         <v>102100</v>
       </c>
-      <c r="C82" s="51" t="s">
+      <c r="C82" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="D82" s="51">
+      <c r="D82" s="50">
         <v>1</v>
       </c>
-      <c r="E82" s="52" t="s">
+      <c r="E82" s="51" t="s">
         <v>108</v>
       </c>
       <c r="F82" s="25" t="s">
@@ -4678,20 +4101,20 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" s="8" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A83" s="51">
+    <row r="83" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A83" s="50">
         <v>21002</v>
       </c>
-      <c r="B83" s="51">
+      <c r="B83" s="50">
         <v>102100</v>
       </c>
-      <c r="C83" s="51" t="s">
+      <c r="C83" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="D83" s="51">
+      <c r="D83" s="50">
         <v>2</v>
       </c>
-      <c r="E83" s="52" t="s">
+      <c r="E83" s="51" t="s">
         <v>110</v>
       </c>
       <c r="F83" s="25" t="s">
@@ -4711,20 +4134,20 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" s="8" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A84" s="51">
+    <row r="84" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A84" s="50">
         <v>21003</v>
       </c>
-      <c r="B84" s="51">
+      <c r="B84" s="50">
         <v>102100</v>
       </c>
-      <c r="C84" s="51" t="s">
+      <c r="C84" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="D84" s="51">
+      <c r="D84" s="50">
         <v>3</v>
       </c>
-      <c r="E84" s="52" t="s">
+      <c r="E84" s="51" t="s">
         <v>111</v>
       </c>
       <c r="F84" s="25" t="s">
@@ -4744,20 +4167,20 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" s="8" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A85" s="51">
+    <row r="85" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A85" s="50">
         <v>21004</v>
       </c>
-      <c r="B85" s="51">
+      <c r="B85" s="50">
         <v>102100</v>
       </c>
-      <c r="C85" s="51" t="s">
+      <c r="C85" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="D85" s="51">
+      <c r="D85" s="50">
         <v>4</v>
       </c>
-      <c r="E85" s="52" t="s">
+      <c r="E85" s="51" t="s">
         <v>112</v>
       </c>
       <c r="F85" s="25" t="s">
@@ -4777,20 +4200,20 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" s="8" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A86" s="51">
+    <row r="86" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A86" s="50">
         <v>21005</v>
       </c>
-      <c r="B86" s="51">
+      <c r="B86" s="50">
         <v>102100</v>
       </c>
-      <c r="C86" s="51" t="s">
+      <c r="C86" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="D86" s="51">
+      <c r="D86" s="50">
         <v>5</v>
       </c>
-      <c r="E86" s="52" t="s">
+      <c r="E86" s="51" t="s">
         <v>113</v>
       </c>
       <c r="F86" s="25" t="s">
@@ -4810,20 +4233,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" s="8" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A87" s="51">
+    <row r="87" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A87" s="50">
         <v>21006</v>
       </c>
-      <c r="B87" s="51">
+      <c r="B87" s="50">
         <v>102100</v>
       </c>
-      <c r="C87" s="51" t="s">
+      <c r="C87" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="D87" s="51">
+      <c r="D87" s="50">
         <v>6</v>
       </c>
-      <c r="E87" s="52" t="s">
+      <c r="E87" s="51" t="s">
         <v>114</v>
       </c>
       <c r="F87" s="25" t="s">
@@ -4843,20 +4266,20 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" s="8" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A88" s="51">
+    <row r="88" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A88" s="50">
         <v>21007</v>
       </c>
-      <c r="B88" s="51">
+      <c r="B88" s="50">
         <v>102100</v>
       </c>
-      <c r="C88" s="51" t="s">
+      <c r="C88" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="D88" s="51">
+      <c r="D88" s="50">
         <v>7</v>
       </c>
-      <c r="E88" s="52" t="s">
+      <c r="E88" s="51" t="s">
         <v>114</v>
       </c>
       <c r="F88" s="25" t="s">
@@ -4876,20 +4299,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" s="9" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A89" s="53">
+    <row r="89" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A89" s="52">
         <v>22001</v>
       </c>
-      <c r="B89" s="53">
+      <c r="B89" s="52">
         <v>102200</v>
       </c>
-      <c r="C89" s="53" t="s">
+      <c r="C89" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="D89" s="53">
+      <c r="D89" s="52">
         <v>1</v>
       </c>
-      <c r="E89" s="54" t="s">
+      <c r="E89" s="53" t="s">
         <v>76</v>
       </c>
       <c r="F89" s="25" t="s">
@@ -4908,26 +4331,26 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" s="9" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A90" s="53">
+    <row r="90" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A90" s="52">
         <v>22002</v>
       </c>
-      <c r="B90" s="53">
+      <c r="B90" s="52">
         <v>102200</v>
       </c>
-      <c r="C90" s="53" t="s">
+      <c r="C90" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="D90" s="53">
+      <c r="D90" s="52">
         <v>2</v>
       </c>
-      <c r="E90" s="54" t="s">
+      <c r="E90" s="53" t="s">
         <v>118</v>
       </c>
       <c r="F90" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="G90" s="55" t="str">
+      <c r="G90" s="54" t="str">
         <f t="shared" ref="G90:G95" si="11">G89</f>
         <v>1,0&amp;1-70000|1&amp;25-13000|25&amp;50-9000|50&amp;75-4000|75&amp;100-1400|100&amp;125-950|125&amp;150-600|150&amp;175-400|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-50|300&amp;350-10|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-85200|1&amp;25-4700|25&amp;50-2100|50&amp;75-200|75&amp;100-100|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-0|1&amp;25-5000|25&amp;50-2300|50&amp;75-900|75&amp;100-300|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-100|200&amp;225-100|225&amp;250-0|250&amp;300-100|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-5000|300&amp;350-5000|350&amp;400-5000|400&amp;450-5000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-50|6400&amp;7200-50|7200&amp;8000-10|8000&amp;9250-10|9250&amp;10500-10|10500&amp;99999999-0;5,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-2000|175&amp;200-2000|200&amp;225-2000|225&amp;250-5000|250&amp;300-4000|300&amp;350-4000|350&amp;400-4000|400&amp;450-4000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-400|5600&amp;6400-250|6400&amp;7200-150|7200&amp;8000-100|8000&amp;9250-100|9250&amp;10500-50|10500&amp;99999999-0</v>
       </c>
@@ -4941,26 +4364,26 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" s="9" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A91" s="53">
+    <row r="91" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A91" s="52">
         <v>22003</v>
       </c>
-      <c r="B91" s="53">
+      <c r="B91" s="52">
         <v>102200</v>
       </c>
-      <c r="C91" s="53" t="s">
+      <c r="C91" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="D91" s="53">
+      <c r="D91" s="52">
         <v>3</v>
       </c>
-      <c r="E91" s="54" t="s">
+      <c r="E91" s="53" t="s">
         <v>119</v>
       </c>
       <c r="F91" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="G91" s="55" t="str">
+      <c r="G91" s="54" t="str">
         <f t="shared" si="11"/>
         <v>1,0&amp;1-70000|1&amp;25-13000|25&amp;50-9000|50&amp;75-4000|75&amp;100-1400|100&amp;125-950|125&amp;150-600|150&amp;175-400|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-50|300&amp;350-10|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-85200|1&amp;25-4700|25&amp;50-2100|50&amp;75-200|75&amp;100-100|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-0|1&amp;25-5000|25&amp;50-2300|50&amp;75-900|75&amp;100-300|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-100|200&amp;225-100|225&amp;250-0|250&amp;300-100|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-5000|300&amp;350-5000|350&amp;400-5000|400&amp;450-5000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-50|6400&amp;7200-50|7200&amp;8000-10|8000&amp;9250-10|9250&amp;10500-10|10500&amp;99999999-0;5,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-2000|175&amp;200-2000|200&amp;225-2000|225&amp;250-5000|250&amp;300-4000|300&amp;350-4000|350&amp;400-4000|400&amp;450-4000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-400|5600&amp;6400-250|6400&amp;7200-150|7200&amp;8000-100|8000&amp;9250-100|9250&amp;10500-50|10500&amp;99999999-0</v>
       </c>
@@ -4974,26 +4397,26 @@
         <v>27</v>
       </c>
     </row>
-    <row r="92" s="9" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A92" s="53">
+    <row r="92" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A92" s="52">
         <v>22004</v>
       </c>
-      <c r="B92" s="53">
+      <c r="B92" s="52">
         <v>102200</v>
       </c>
-      <c r="C92" s="53" t="s">
+      <c r="C92" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="D92" s="53">
+      <c r="D92" s="52">
         <v>4</v>
       </c>
-      <c r="E92" s="54" t="s">
+      <c r="E92" s="53" t="s">
         <v>77</v>
       </c>
       <c r="F92" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="G92" s="55" t="str">
+      <c r="G92" s="54" t="str">
         <f t="shared" si="11"/>
         <v>1,0&amp;1-70000|1&amp;25-13000|25&amp;50-9000|50&amp;75-4000|75&amp;100-1400|100&amp;125-950|125&amp;150-600|150&amp;175-400|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-50|300&amp;350-10|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-85200|1&amp;25-4700|25&amp;50-2100|50&amp;75-200|75&amp;100-100|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-0|1&amp;25-5000|25&amp;50-2300|50&amp;75-900|75&amp;100-300|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-100|200&amp;225-100|225&amp;250-0|250&amp;300-100|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-5000|300&amp;350-5000|350&amp;400-5000|400&amp;450-5000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-50|6400&amp;7200-50|7200&amp;8000-10|8000&amp;9250-10|9250&amp;10500-10|10500&amp;99999999-0;5,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-2000|175&amp;200-2000|200&amp;225-2000|225&amp;250-5000|250&amp;300-4000|300&amp;350-4000|350&amp;400-4000|400&amp;450-4000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-400|5600&amp;6400-250|6400&amp;7200-150|7200&amp;8000-100|8000&amp;9250-100|9250&amp;10500-50|10500&amp;99999999-0</v>
       </c>
@@ -5007,26 +4430,26 @@
         <v>29</v>
       </c>
     </row>
-    <row r="93" s="9" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A93" s="53">
+    <row r="93" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A93" s="52">
         <v>22005</v>
       </c>
-      <c r="B93" s="53">
+      <c r="B93" s="52">
         <v>102200</v>
       </c>
-      <c r="C93" s="53" t="s">
+      <c r="C93" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="D93" s="53">
+      <c r="D93" s="52">
         <v>5</v>
       </c>
-      <c r="E93" s="54" t="s">
+      <c r="E93" s="53" t="s">
         <v>120</v>
       </c>
       <c r="F93" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="G93" s="55" t="str">
+      <c r="G93" s="54" t="str">
         <f t="shared" si="11"/>
         <v>1,0&amp;1-70000|1&amp;25-13000|25&amp;50-9000|50&amp;75-4000|75&amp;100-1400|100&amp;125-950|125&amp;150-600|150&amp;175-400|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-50|300&amp;350-10|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-85200|1&amp;25-4700|25&amp;50-2100|50&amp;75-200|75&amp;100-100|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-0|1&amp;25-5000|25&amp;50-2300|50&amp;75-900|75&amp;100-300|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-100|200&amp;225-100|225&amp;250-0|250&amp;300-100|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-5000|300&amp;350-5000|350&amp;400-5000|400&amp;450-5000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-50|6400&amp;7200-50|7200&amp;8000-10|8000&amp;9250-10|9250&amp;10500-10|10500&amp;99999999-0;5,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-2000|175&amp;200-2000|200&amp;225-2000|225&amp;250-5000|250&amp;300-4000|300&amp;350-4000|350&amp;400-4000|400&amp;450-4000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-400|5600&amp;6400-250|6400&amp;7200-150|7200&amp;8000-100|8000&amp;9250-100|9250&amp;10500-50|10500&amp;99999999-0</v>
       </c>
@@ -5040,26 +4463,26 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" s="9" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A94" s="53">
+    <row r="94" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A94" s="52">
         <v>22006</v>
       </c>
-      <c r="B94" s="53">
+      <c r="B94" s="52">
         <v>102200</v>
       </c>
-      <c r="C94" s="53" t="s">
+      <c r="C94" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="D94" s="53">
+      <c r="D94" s="52">
         <v>6</v>
       </c>
-      <c r="E94" s="54" t="s">
+      <c r="E94" s="53" t="s">
         <v>43</v>
       </c>
       <c r="F94" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="G94" s="55" t="str">
+      <c r="G94" s="54" t="str">
         <f t="shared" si="11"/>
         <v>1,0&amp;1-70000|1&amp;25-13000|25&amp;50-9000|50&amp;75-4000|75&amp;100-1400|100&amp;125-950|125&amp;150-600|150&amp;175-400|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-50|300&amp;350-10|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-85200|1&amp;25-4700|25&amp;50-2100|50&amp;75-200|75&amp;100-100|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-0|1&amp;25-5000|25&amp;50-2300|50&amp;75-900|75&amp;100-300|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-100|200&amp;225-100|225&amp;250-0|250&amp;300-100|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-5000|300&amp;350-5000|350&amp;400-5000|400&amp;450-5000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-50|6400&amp;7200-50|7200&amp;8000-10|8000&amp;9250-10|9250&amp;10500-10|10500&amp;99999999-0;5,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-2000|175&amp;200-2000|200&amp;225-2000|225&amp;250-5000|250&amp;300-4000|300&amp;350-4000|350&amp;400-4000|400&amp;450-4000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-400|5600&amp;6400-250|6400&amp;7200-150|7200&amp;8000-100|8000&amp;9250-100|9250&amp;10500-50|10500&amp;99999999-0</v>
       </c>
@@ -5073,26 +4496,26 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" s="9" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A95" s="53">
+    <row r="95" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A95" s="52">
         <v>22007</v>
       </c>
-      <c r="B95" s="53">
+      <c r="B95" s="52">
         <v>102200</v>
       </c>
-      <c r="C95" s="53" t="s">
+      <c r="C95" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="D95" s="53">
+      <c r="D95" s="52">
         <v>7</v>
       </c>
-      <c r="E95" s="54" t="s">
+      <c r="E95" s="53" t="s">
         <v>43</v>
       </c>
       <c r="F95" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="G95" s="55" t="str">
+      <c r="G95" s="54" t="str">
         <f t="shared" si="11"/>
         <v>1,0&amp;1-70000|1&amp;25-13000|25&amp;50-9000|50&amp;75-4000|75&amp;100-1400|100&amp;125-950|125&amp;150-600|150&amp;175-400|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-50|300&amp;350-10|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-85200|1&amp;25-4700|25&amp;50-2100|50&amp;75-200|75&amp;100-100|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-0|1&amp;25-5000|25&amp;50-2300|50&amp;75-900|75&amp;100-300|100&amp;125-100|125&amp;150-100|150&amp;175-100|175&amp;200-100|200&amp;225-100|225&amp;250-0|250&amp;300-100|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-5000|300&amp;350-5000|350&amp;400-5000|400&amp;450-5000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-50|6400&amp;7200-50|7200&amp;8000-10|8000&amp;9250-10|9250&amp;10500-10|10500&amp;99999999-0;5,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-2000|175&amp;200-2000|200&amp;225-2000|225&amp;250-5000|250&amp;300-4000|300&amp;350-4000|350&amp;400-4000|400&amp;450-4000|450&amp;500-4000|500&amp;600-4000|600&amp;700-4000|700&amp;800-3500|800&amp;900-3500|900&amp;1000-3000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-1500|1600&amp;1800-1500|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-800|2800&amp;3200-400|3200&amp;3600-200|3600&amp;4000-150|4000&amp;4800-100|4800&amp;5600-400|5600&amp;6400-250|6400&amp;7200-150|7200&amp;8000-100|8000&amp;9250-100|9250&amp;10500-50|10500&amp;99999999-0</v>
       </c>
@@ -5106,20 +4529,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" s="10" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A96" s="56">
+    <row r="96" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A96" s="55">
         <v>23001</v>
       </c>
-      <c r="B96" s="56">
+      <c r="B96" s="55">
         <v>102300</v>
       </c>
-      <c r="C96" s="56" t="s">
+      <c r="C96" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="D96" s="56">
+      <c r="D96" s="55">
         <v>1</v>
       </c>
-      <c r="E96" s="57" t="s">
+      <c r="E96" s="56" t="s">
         <v>122</v>
       </c>
       <c r="F96" s="25" t="s">
@@ -5138,26 +4561,26 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" s="10" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A97" s="56">
+    <row r="97" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A97" s="55">
         <v>23002</v>
       </c>
-      <c r="B97" s="56">
+      <c r="B97" s="55">
         <v>102300</v>
       </c>
-      <c r="C97" s="56" t="s">
+      <c r="C97" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="D97" s="56">
+      <c r="D97" s="55">
         <v>2</v>
       </c>
-      <c r="E97" s="57" t="s">
+      <c r="E97" s="56" t="s">
         <v>125</v>
       </c>
       <c r="F97" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="G97" s="58" t="str">
+      <c r="G97" s="57" t="str">
         <f t="shared" ref="G97:G102" si="12">G96</f>
         <v>1,0&amp;1-75000|1&amp;20-15000|20&amp;40-2000|40&amp;80-1500|80&amp;120-1200|120&amp;160-500|160&amp;200-200|200&amp;280-200|280&amp;360-100|360&amp;440-100|440&amp;520-100|520&amp;600-100|600&amp;800-50|800&amp;1000-50|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-5|1800&amp;2000-5|2000&amp;2600-5|2600&amp;3200-1|3200&amp;3800-1|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-0|80&amp;120-0|120&amp;160-0|160&amp;200-0|200&amp;280-0|280&amp;360-0|360&amp;440-0|440&amp;520-0|520&amp;600-0|600&amp;800-0|800&amp;1000-10000|1000&amp;1200-10000|1200&amp;1400-10000|1400&amp;1600-8000|1600&amp;1800-8000|1800&amp;2000-4000|2000&amp;2600-1000|2600&amp;3200-1000|3200&amp;3800-500|3800&amp;4400-500|4400&amp;5000-500|5000&amp;5600-400|5600&amp;6800-300|6800&amp;8000-200|8000&amp;9200-100|9200&amp;10400-100|10400&amp;11600-50|11600&amp;12800-50|12800&amp;14000-50|14000&amp;15200-10|15200&amp;16400-10|16400&amp;17600-10|17600&amp;18800-5|18800&amp;20000-5|20000&amp;21200-1|21200&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-2800|80&amp;120-1500|120&amp;160-1300|160&amp;200-700|200&amp;280-600|280&amp;360-300|360&amp;440-400|440&amp;520-200|520&amp;600-300|600&amp;800-200|800&amp;1000-100|1000&amp;1200-100|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2600-0|2600&amp;3200-0|3200&amp;3800-0|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0</v>
       </c>
@@ -5171,26 +4594,26 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" s="10" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A98" s="56">
+    <row r="98" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A98" s="55">
         <v>23003</v>
       </c>
-      <c r="B98" s="56">
+      <c r="B98" s="55">
         <v>102300</v>
       </c>
-      <c r="C98" s="56" t="s">
+      <c r="C98" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="D98" s="56">
+      <c r="D98" s="55">
         <v>3</v>
       </c>
-      <c r="E98" s="57" t="s">
+      <c r="E98" s="56" t="s">
         <v>126</v>
       </c>
       <c r="F98" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="G98" s="58" t="str">
+      <c r="G98" s="57" t="str">
         <f t="shared" si="12"/>
         <v>1,0&amp;1-75000|1&amp;20-15000|20&amp;40-2000|40&amp;80-1500|80&amp;120-1200|120&amp;160-500|160&amp;200-200|200&amp;280-200|280&amp;360-100|360&amp;440-100|440&amp;520-100|520&amp;600-100|600&amp;800-50|800&amp;1000-50|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-5|1800&amp;2000-5|2000&amp;2600-5|2600&amp;3200-1|3200&amp;3800-1|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-0|80&amp;120-0|120&amp;160-0|160&amp;200-0|200&amp;280-0|280&amp;360-0|360&amp;440-0|440&amp;520-0|520&amp;600-0|600&amp;800-0|800&amp;1000-10000|1000&amp;1200-10000|1200&amp;1400-10000|1400&amp;1600-8000|1600&amp;1800-8000|1800&amp;2000-4000|2000&amp;2600-1000|2600&amp;3200-1000|3200&amp;3800-500|3800&amp;4400-500|4400&amp;5000-500|5000&amp;5600-400|5600&amp;6800-300|6800&amp;8000-200|8000&amp;9200-100|9200&amp;10400-100|10400&amp;11600-50|11600&amp;12800-50|12800&amp;14000-50|14000&amp;15200-10|15200&amp;16400-10|16400&amp;17600-10|17600&amp;18800-5|18800&amp;20000-5|20000&amp;21200-1|21200&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-2800|80&amp;120-1500|120&amp;160-1300|160&amp;200-700|200&amp;280-600|280&amp;360-300|360&amp;440-400|440&amp;520-200|520&amp;600-300|600&amp;800-200|800&amp;1000-100|1000&amp;1200-100|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2600-0|2600&amp;3200-0|3200&amp;3800-0|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0</v>
       </c>
@@ -5204,26 +4627,26 @@
         <v>27</v>
       </c>
     </row>
-    <row r="99" s="10" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A99" s="56">
+    <row r="99" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A99" s="55">
         <v>23004</v>
       </c>
-      <c r="B99" s="56">
+      <c r="B99" s="55">
         <v>102300</v>
       </c>
-      <c r="C99" s="56" t="s">
+      <c r="C99" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="D99" s="56">
+      <c r="D99" s="55">
         <v>4</v>
       </c>
-      <c r="E99" s="57" t="s">
+      <c r="E99" s="56" t="s">
         <v>127</v>
       </c>
       <c r="F99" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="G99" s="58" t="str">
+      <c r="G99" s="57" t="str">
         <f t="shared" si="12"/>
         <v>1,0&amp;1-75000|1&amp;20-15000|20&amp;40-2000|40&amp;80-1500|80&amp;120-1200|120&amp;160-500|160&amp;200-200|200&amp;280-200|280&amp;360-100|360&amp;440-100|440&amp;520-100|520&amp;600-100|600&amp;800-50|800&amp;1000-50|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-5|1800&amp;2000-5|2000&amp;2600-5|2600&amp;3200-1|3200&amp;3800-1|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-0|80&amp;120-0|120&amp;160-0|160&amp;200-0|200&amp;280-0|280&amp;360-0|360&amp;440-0|440&amp;520-0|520&amp;600-0|600&amp;800-0|800&amp;1000-10000|1000&amp;1200-10000|1200&amp;1400-10000|1400&amp;1600-8000|1600&amp;1800-8000|1800&amp;2000-4000|2000&amp;2600-1000|2600&amp;3200-1000|3200&amp;3800-500|3800&amp;4400-500|4400&amp;5000-500|5000&amp;5600-400|5600&amp;6800-300|6800&amp;8000-200|8000&amp;9200-100|9200&amp;10400-100|10400&amp;11600-50|11600&amp;12800-50|12800&amp;14000-50|14000&amp;15200-10|15200&amp;16400-10|16400&amp;17600-10|17600&amp;18800-5|18800&amp;20000-5|20000&amp;21200-1|21200&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-2800|80&amp;120-1500|120&amp;160-1300|160&amp;200-700|200&amp;280-600|280&amp;360-300|360&amp;440-400|440&amp;520-200|520&amp;600-300|600&amp;800-200|800&amp;1000-100|1000&amp;1200-100|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2600-0|2600&amp;3200-0|3200&amp;3800-0|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0</v>
       </c>
@@ -5237,26 +4660,26 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" s="10" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A100" s="56">
+    <row r="100" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A100" s="55">
         <v>23005</v>
       </c>
-      <c r="B100" s="56">
+      <c r="B100" s="55">
         <v>102300</v>
       </c>
-      <c r="C100" s="56" t="s">
+      <c r="C100" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="D100" s="56">
+      <c r="D100" s="55">
         <v>5</v>
       </c>
-      <c r="E100" s="57" t="s">
+      <c r="E100" s="56" t="s">
         <v>128</v>
       </c>
       <c r="F100" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="G100" s="58" t="str">
+      <c r="G100" s="57" t="str">
         <f t="shared" si="12"/>
         <v>1,0&amp;1-75000|1&amp;20-15000|20&amp;40-2000|40&amp;80-1500|80&amp;120-1200|120&amp;160-500|160&amp;200-200|200&amp;280-200|280&amp;360-100|360&amp;440-100|440&amp;520-100|520&amp;600-100|600&amp;800-50|800&amp;1000-50|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-5|1800&amp;2000-5|2000&amp;2600-5|2600&amp;3200-1|3200&amp;3800-1|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-0|80&amp;120-0|120&amp;160-0|160&amp;200-0|200&amp;280-0|280&amp;360-0|360&amp;440-0|440&amp;520-0|520&amp;600-0|600&amp;800-0|800&amp;1000-10000|1000&amp;1200-10000|1200&amp;1400-10000|1400&amp;1600-8000|1600&amp;1800-8000|1800&amp;2000-4000|2000&amp;2600-1000|2600&amp;3200-1000|3200&amp;3800-500|3800&amp;4400-500|4400&amp;5000-500|5000&amp;5600-400|5600&amp;6800-300|6800&amp;8000-200|8000&amp;9200-100|9200&amp;10400-100|10400&amp;11600-50|11600&amp;12800-50|12800&amp;14000-50|14000&amp;15200-10|15200&amp;16400-10|16400&amp;17600-10|17600&amp;18800-5|18800&amp;20000-5|20000&amp;21200-1|21200&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-2800|80&amp;120-1500|120&amp;160-1300|160&amp;200-700|200&amp;280-600|280&amp;360-300|360&amp;440-400|440&amp;520-200|520&amp;600-300|600&amp;800-200|800&amp;1000-100|1000&amp;1200-100|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2600-0|2600&amp;3200-0|3200&amp;3800-0|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0</v>
       </c>
@@ -5270,26 +4693,26 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" s="10" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A101" s="56">
+    <row r="101" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A101" s="55">
         <v>23006</v>
       </c>
-      <c r="B101" s="56">
+      <c r="B101" s="55">
         <v>102300</v>
       </c>
-      <c r="C101" s="56" t="s">
+      <c r="C101" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="D101" s="56">
+      <c r="D101" s="55">
         <v>6</v>
       </c>
-      <c r="E101" s="57" t="s">
+      <c r="E101" s="56" t="s">
         <v>97</v>
       </c>
       <c r="F101" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="G101" s="58" t="str">
+      <c r="G101" s="57" t="str">
         <f t="shared" si="12"/>
         <v>1,0&amp;1-75000|1&amp;20-15000|20&amp;40-2000|40&amp;80-1500|80&amp;120-1200|120&amp;160-500|160&amp;200-200|200&amp;280-200|280&amp;360-100|360&amp;440-100|440&amp;520-100|520&amp;600-100|600&amp;800-50|800&amp;1000-50|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-5|1800&amp;2000-5|2000&amp;2600-5|2600&amp;3200-1|3200&amp;3800-1|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-0|80&amp;120-0|120&amp;160-0|160&amp;200-0|200&amp;280-0|280&amp;360-0|360&amp;440-0|440&amp;520-0|520&amp;600-0|600&amp;800-0|800&amp;1000-10000|1000&amp;1200-10000|1200&amp;1400-10000|1400&amp;1600-8000|1600&amp;1800-8000|1800&amp;2000-4000|2000&amp;2600-1000|2600&amp;3200-1000|3200&amp;3800-500|3800&amp;4400-500|4400&amp;5000-500|5000&amp;5600-400|5600&amp;6800-300|6800&amp;8000-200|8000&amp;9200-100|9200&amp;10400-100|10400&amp;11600-50|11600&amp;12800-50|12800&amp;14000-50|14000&amp;15200-10|15200&amp;16400-10|16400&amp;17600-10|17600&amp;18800-5|18800&amp;20000-5|20000&amp;21200-1|21200&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-2800|80&amp;120-1500|120&amp;160-1300|160&amp;200-700|200&amp;280-600|280&amp;360-300|360&amp;440-400|440&amp;520-200|520&amp;600-300|600&amp;800-200|800&amp;1000-100|1000&amp;1200-100|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2600-0|2600&amp;3200-0|3200&amp;3800-0|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0</v>
       </c>
@@ -5303,26 +4726,26 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" s="10" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A102" s="56">
+    <row r="102" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A102" s="55">
         <v>23007</v>
       </c>
-      <c r="B102" s="56">
+      <c r="B102" s="55">
         <v>102300</v>
       </c>
-      <c r="C102" s="56" t="s">
+      <c r="C102" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="D102" s="56">
+      <c r="D102" s="55">
         <v>7</v>
       </c>
-      <c r="E102" s="57" t="s">
+      <c r="E102" s="56" t="s">
         <v>43</v>
       </c>
       <c r="F102" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="G102" s="58" t="str">
+      <c r="G102" s="57" t="str">
         <f t="shared" si="12"/>
         <v>1,0&amp;1-75000|1&amp;20-15000|20&amp;40-2000|40&amp;80-1500|80&amp;120-1200|120&amp;160-500|160&amp;200-200|200&amp;280-200|280&amp;360-100|360&amp;440-100|440&amp;520-100|520&amp;600-100|600&amp;800-50|800&amp;1000-50|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-5|1800&amp;2000-5|2000&amp;2600-5|2600&amp;3200-1|3200&amp;3800-1|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-0|80&amp;120-0|120&amp;160-0|160&amp;200-0|200&amp;280-0|280&amp;360-0|360&amp;440-0|440&amp;520-0|520&amp;600-0|600&amp;800-0|800&amp;1000-10000|1000&amp;1200-10000|1200&amp;1400-10000|1400&amp;1600-8000|1600&amp;1800-8000|1800&amp;2000-4000|2000&amp;2600-1000|2600&amp;3200-1000|3200&amp;3800-500|3800&amp;4400-500|4400&amp;5000-500|5000&amp;5600-400|5600&amp;6800-300|6800&amp;8000-200|8000&amp;9200-100|9200&amp;10400-100|10400&amp;11600-50|11600&amp;12800-50|12800&amp;14000-50|14000&amp;15200-10|15200&amp;16400-10|16400&amp;17600-10|17600&amp;18800-5|18800&amp;20000-5|20000&amp;21200-1|21200&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;80-2800|80&amp;120-1500|120&amp;160-1300|160&amp;200-700|200&amp;280-600|280&amp;360-300|360&amp;440-400|440&amp;520-200|520&amp;600-300|600&amp;800-200|800&amp;1000-100|1000&amp;1200-100|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2600-0|2600&amp;3200-0|3200&amp;3800-0|3800&amp;4400-0|4400&amp;5000-0|5000&amp;5600-0|5600&amp;6800-0|6800&amp;8000-0|8000&amp;9200-0|9200&amp;10400-0|10400&amp;11600-0|11600&amp;12800-0|12800&amp;14000-0|14000&amp;15200-0|15200&amp;16400-0|16400&amp;17600-0|17600&amp;18800-0|18800&amp;20000-0|20000&amp;21200-0|21200&amp;99999999-0</v>
       </c>
@@ -5336,7 +4759,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" ht="16.5" spans="1:10">
+    <row r="103" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A103" s="23">
         <v>24001</v>
       </c>
@@ -5366,7 +4789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" ht="16.5" spans="1:10">
+    <row r="104" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A104" s="23">
         <v>24002</v>
       </c>
@@ -5397,7 +4820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" ht="16.5" spans="1:10">
+    <row r="105" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A105" s="23">
         <v>24003</v>
       </c>
@@ -5428,7 +4851,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="106" ht="16.5" spans="1:10">
+    <row r="106" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A106" s="23">
         <v>24004</v>
       </c>
@@ -5459,7 +4882,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="107" ht="16.5" spans="1:10">
+    <row r="107" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A107" s="23">
         <v>24005</v>
       </c>
@@ -5490,7 +4913,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" ht="16.5" spans="1:10">
+    <row r="108" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A108" s="23">
         <v>24006</v>
       </c>
@@ -5521,7 +4944,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="109" ht="16.5" spans="1:10">
+    <row r="109" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A109" s="23">
         <v>24007</v>
       </c>
@@ -5552,20 +4975,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A110" s="59">
+    <row r="110" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A110" s="58">
         <v>25001</v>
       </c>
-      <c r="B110" s="59">
+      <c r="B110" s="58">
         <v>102500</v>
       </c>
-      <c r="C110" s="59" t="s">
+      <c r="C110" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="D110" s="59">
+      <c r="D110" s="58">
         <v>1</v>
       </c>
-      <c r="E110" s="60" t="s">
+      <c r="E110" s="59" t="s">
         <v>101</v>
       </c>
       <c r="F110" s="25" t="s">
@@ -5584,26 +5007,26 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A111" s="59">
+    <row r="111" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A111" s="58">
         <v>25002</v>
       </c>
-      <c r="B111" s="59">
+      <c r="B111" s="58">
         <v>102500</v>
       </c>
-      <c r="C111" s="59" t="s">
+      <c r="C111" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="D111" s="59">
+      <c r="D111" s="58">
         <v>2</v>
       </c>
-      <c r="E111" s="60" t="s">
+      <c r="E111" s="59" t="s">
         <v>102</v>
       </c>
       <c r="F111" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G111" s="61" t="str">
+      <c r="G111" s="60" t="str">
         <f t="shared" ref="G111:G116" si="14">G110</f>
         <v>1,0&amp;1-70000|1&amp;50-12000|50&amp;100-6000|100&amp;150-4000|150&amp;200-3000|200&amp;250-1500|250&amp;300-1000|300&amp;350-700|350&amp;400-200|400&amp;450-100|450&amp;500-10|500&amp;600-10|600&amp;700-10|700&amp;800-10|800&amp;900-10|900&amp;1000-10|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-10|1800&amp;2000-10|2000&amp;2400-10|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0;2,0&amp;1-0|1&amp;50-0|50&amp;100-0|100&amp;150-0|150&amp;200-0|200&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-2001|700&amp;800-2009|800&amp;900-2180|900&amp;1000-2109|1000&amp;1200-4500|1200&amp;1400-4500|1400&amp;1600-4500|1600&amp;1800-4500|1800&amp;2000-4500|2000&amp;2400-7000|2400&amp;2800-6000|2800&amp;3200-6000|3200&amp;3600-4500|3600&amp;4000-4500|4000&amp;4800-4500|4800&amp;5600-4500|5600&amp;6400-4500|6400&amp;7200-3000|7200&amp;8000-3000|8000&amp;9600-3000|9600&amp;11200-2000|11200&amp;12800-1500|12800&amp;14400-1200|14400&amp;16000-900|16000&amp;18500-900|18500&amp;21000-700|21000&amp;99999999-0;3,0&amp;1-0|1&amp;50-0|50&amp;100-4000|100&amp;150-2500|150&amp;200-900|200&amp;250-600|250&amp;300-300|300&amp;350-200|350&amp;400-100|400&amp;450-100|450&amp;500-50|500&amp;600-50|600&amp;700-10|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0</v>
       </c>
@@ -5617,26 +5040,26 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A112" s="59">
+    <row r="112" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A112" s="58">
         <v>25003</v>
       </c>
-      <c r="B112" s="59">
+      <c r="B112" s="58">
         <v>102500</v>
       </c>
-      <c r="C112" s="59" t="s">
+      <c r="C112" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="D112" s="59">
+      <c r="D112" s="58">
         <v>3</v>
       </c>
-      <c r="E112" s="60" t="s">
+      <c r="E112" s="59" t="s">
         <v>103</v>
       </c>
       <c r="F112" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G112" s="61" t="str">
+      <c r="G112" s="60" t="str">
         <f t="shared" si="14"/>
         <v>1,0&amp;1-70000|1&amp;50-12000|50&amp;100-6000|100&amp;150-4000|150&amp;200-3000|200&amp;250-1500|250&amp;300-1000|300&amp;350-700|350&amp;400-200|400&amp;450-100|450&amp;500-10|500&amp;600-10|600&amp;700-10|700&amp;800-10|800&amp;900-10|900&amp;1000-10|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-10|1800&amp;2000-10|2000&amp;2400-10|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0;2,0&amp;1-0|1&amp;50-0|50&amp;100-0|100&amp;150-0|150&amp;200-0|200&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-2001|700&amp;800-2009|800&amp;900-2180|900&amp;1000-2109|1000&amp;1200-4500|1200&amp;1400-4500|1400&amp;1600-4500|1600&amp;1800-4500|1800&amp;2000-4500|2000&amp;2400-7000|2400&amp;2800-6000|2800&amp;3200-6000|3200&amp;3600-4500|3600&amp;4000-4500|4000&amp;4800-4500|4800&amp;5600-4500|5600&amp;6400-4500|6400&amp;7200-3000|7200&amp;8000-3000|8000&amp;9600-3000|9600&amp;11200-2000|11200&amp;12800-1500|12800&amp;14400-1200|14400&amp;16000-900|16000&amp;18500-900|18500&amp;21000-700|21000&amp;99999999-0;3,0&amp;1-0|1&amp;50-0|50&amp;100-4000|100&amp;150-2500|150&amp;200-900|200&amp;250-600|250&amp;300-300|300&amp;350-200|350&amp;400-100|400&amp;450-100|450&amp;500-50|500&amp;600-50|600&amp;700-10|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0</v>
       </c>
@@ -5650,26 +5073,26 @@
         <v>27</v>
       </c>
     </row>
-    <row r="113" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A113" s="59">
+    <row r="113" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A113" s="58">
         <v>25004</v>
       </c>
-      <c r="B113" s="59">
+      <c r="B113" s="58">
         <v>102500</v>
       </c>
-      <c r="C113" s="59" t="s">
+      <c r="C113" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="D113" s="59">
+      <c r="D113" s="58">
         <v>4</v>
       </c>
-      <c r="E113" s="60" t="s">
+      <c r="E113" s="59" t="s">
         <v>95</v>
       </c>
       <c r="F113" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G113" s="61" t="str">
+      <c r="G113" s="60" t="str">
         <f t="shared" si="14"/>
         <v>1,0&amp;1-70000|1&amp;50-12000|50&amp;100-6000|100&amp;150-4000|150&amp;200-3000|200&amp;250-1500|250&amp;300-1000|300&amp;350-700|350&amp;400-200|400&amp;450-100|450&amp;500-10|500&amp;600-10|600&amp;700-10|700&amp;800-10|800&amp;900-10|900&amp;1000-10|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-10|1800&amp;2000-10|2000&amp;2400-10|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0;2,0&amp;1-0|1&amp;50-0|50&amp;100-0|100&amp;150-0|150&amp;200-0|200&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-2001|700&amp;800-2009|800&amp;900-2180|900&amp;1000-2109|1000&amp;1200-4500|1200&amp;1400-4500|1400&amp;1600-4500|1600&amp;1800-4500|1800&amp;2000-4500|2000&amp;2400-7000|2400&amp;2800-6000|2800&amp;3200-6000|3200&amp;3600-4500|3600&amp;4000-4500|4000&amp;4800-4500|4800&amp;5600-4500|5600&amp;6400-4500|6400&amp;7200-3000|7200&amp;8000-3000|8000&amp;9600-3000|9600&amp;11200-2000|11200&amp;12800-1500|12800&amp;14400-1200|14400&amp;16000-900|16000&amp;18500-900|18500&amp;21000-700|21000&amp;99999999-0;3,0&amp;1-0|1&amp;50-0|50&amp;100-4000|100&amp;150-2500|150&amp;200-900|200&amp;250-600|250&amp;300-300|300&amp;350-200|350&amp;400-100|400&amp;450-100|450&amp;500-50|500&amp;600-50|600&amp;700-10|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0</v>
       </c>
@@ -5683,26 +5106,26 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A114" s="59">
+    <row r="114" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A114" s="58">
         <v>25005</v>
       </c>
-      <c r="B114" s="59">
+      <c r="B114" s="58">
         <v>102500</v>
       </c>
-      <c r="C114" s="59" t="s">
+      <c r="C114" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="D114" s="59">
+      <c r="D114" s="58">
         <v>5</v>
       </c>
-      <c r="E114" s="60" t="s">
+      <c r="E114" s="59" t="s">
         <v>104</v>
       </c>
       <c r="F114" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G114" s="61" t="str">
+      <c r="G114" s="60" t="str">
         <f t="shared" si="14"/>
         <v>1,0&amp;1-70000|1&amp;50-12000|50&amp;100-6000|100&amp;150-4000|150&amp;200-3000|200&amp;250-1500|250&amp;300-1000|300&amp;350-700|350&amp;400-200|400&amp;450-100|450&amp;500-10|500&amp;600-10|600&amp;700-10|700&amp;800-10|800&amp;900-10|900&amp;1000-10|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-10|1800&amp;2000-10|2000&amp;2400-10|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0;2,0&amp;1-0|1&amp;50-0|50&amp;100-0|100&amp;150-0|150&amp;200-0|200&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-2001|700&amp;800-2009|800&amp;900-2180|900&amp;1000-2109|1000&amp;1200-4500|1200&amp;1400-4500|1400&amp;1600-4500|1600&amp;1800-4500|1800&amp;2000-4500|2000&amp;2400-7000|2400&amp;2800-6000|2800&amp;3200-6000|3200&amp;3600-4500|3600&amp;4000-4500|4000&amp;4800-4500|4800&amp;5600-4500|5600&amp;6400-4500|6400&amp;7200-3000|7200&amp;8000-3000|8000&amp;9600-3000|9600&amp;11200-2000|11200&amp;12800-1500|12800&amp;14400-1200|14400&amp;16000-900|16000&amp;18500-900|18500&amp;21000-700|21000&amp;99999999-0;3,0&amp;1-0|1&amp;50-0|50&amp;100-4000|100&amp;150-2500|150&amp;200-900|200&amp;250-600|250&amp;300-300|300&amp;350-200|350&amp;400-100|400&amp;450-100|450&amp;500-50|500&amp;600-50|600&amp;700-10|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0</v>
       </c>
@@ -5716,26 +5139,26 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A115" s="59">
+    <row r="115" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A115" s="58">
         <v>25006</v>
       </c>
-      <c r="B115" s="59">
+      <c r="B115" s="58">
         <v>102500</v>
       </c>
-      <c r="C115" s="59" t="s">
+      <c r="C115" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="D115" s="59">
+      <c r="D115" s="58">
         <v>6</v>
       </c>
-      <c r="E115" s="60" t="s">
+      <c r="E115" s="59" t="s">
         <v>43</v>
       </c>
       <c r="F115" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G115" s="61" t="str">
+      <c r="G115" s="60" t="str">
         <f t="shared" si="14"/>
         <v>1,0&amp;1-70000|1&amp;50-12000|50&amp;100-6000|100&amp;150-4000|150&amp;200-3000|200&amp;250-1500|250&amp;300-1000|300&amp;350-700|350&amp;400-200|400&amp;450-100|450&amp;500-10|500&amp;600-10|600&amp;700-10|700&amp;800-10|800&amp;900-10|900&amp;1000-10|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-10|1800&amp;2000-10|2000&amp;2400-10|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0;2,0&amp;1-0|1&amp;50-0|50&amp;100-0|100&amp;150-0|150&amp;200-0|200&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-2001|700&amp;800-2009|800&amp;900-2180|900&amp;1000-2109|1000&amp;1200-4500|1200&amp;1400-4500|1400&amp;1600-4500|1600&amp;1800-4500|1800&amp;2000-4500|2000&amp;2400-7000|2400&amp;2800-6000|2800&amp;3200-6000|3200&amp;3600-4500|3600&amp;4000-4500|4000&amp;4800-4500|4800&amp;5600-4500|5600&amp;6400-4500|6400&amp;7200-3000|7200&amp;8000-3000|8000&amp;9600-3000|9600&amp;11200-2000|11200&amp;12800-1500|12800&amp;14400-1200|14400&amp;16000-900|16000&amp;18500-900|18500&amp;21000-700|21000&amp;99999999-0;3,0&amp;1-0|1&amp;50-0|50&amp;100-4000|100&amp;150-2500|150&amp;200-900|200&amp;250-600|250&amp;300-300|300&amp;350-200|350&amp;400-100|400&amp;450-100|450&amp;500-50|500&amp;600-50|600&amp;700-10|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0</v>
       </c>
@@ -5749,26 +5172,26 @@
         <v>33</v>
       </c>
     </row>
-    <row r="116" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A116" s="59">
+    <row r="116" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A116" s="58">
         <v>25007</v>
       </c>
-      <c r="B116" s="59">
+      <c r="B116" s="58">
         <v>102500</v>
       </c>
-      <c r="C116" s="59" t="s">
+      <c r="C116" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="D116" s="59">
+      <c r="D116" s="58">
         <v>7</v>
       </c>
-      <c r="E116" s="60" t="s">
+      <c r="E116" s="59" t="s">
         <v>43</v>
       </c>
       <c r="F116" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="G116" s="61" t="str">
+      <c r="G116" s="60" t="str">
         <f t="shared" si="14"/>
         <v>1,0&amp;1-70000|1&amp;50-12000|50&amp;100-6000|100&amp;150-4000|150&amp;200-3000|200&amp;250-1500|250&amp;300-1000|300&amp;350-700|350&amp;400-200|400&amp;450-100|450&amp;500-10|500&amp;600-10|600&amp;700-10|700&amp;800-10|800&amp;900-10|900&amp;1000-10|1000&amp;1200-10|1200&amp;1400-10|1400&amp;1600-10|1600&amp;1800-10|1800&amp;2000-10|2000&amp;2400-10|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0;2,0&amp;1-0|1&amp;50-0|50&amp;100-0|100&amp;150-0|150&amp;200-0|200&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-2001|700&amp;800-2009|800&amp;900-2180|900&amp;1000-2109|1000&amp;1200-4500|1200&amp;1400-4500|1400&amp;1600-4500|1600&amp;1800-4500|1800&amp;2000-4500|2000&amp;2400-7000|2400&amp;2800-6000|2800&amp;3200-6000|3200&amp;3600-4500|3600&amp;4000-4500|4000&amp;4800-4500|4800&amp;5600-4500|5600&amp;6400-4500|6400&amp;7200-3000|7200&amp;8000-3000|8000&amp;9600-3000|9600&amp;11200-2000|11200&amp;12800-1500|12800&amp;14400-1200|14400&amp;16000-900|16000&amp;18500-900|18500&amp;21000-700|21000&amp;99999999-0;3,0&amp;1-0|1&amp;50-0|50&amp;100-4000|100&amp;150-2500|150&amp;200-900|200&amp;250-600|250&amp;300-300|300&amp;350-200|350&amp;400-100|400&amp;450-100|450&amp;500-50|500&amp;600-50|600&amp;700-10|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9600-0|9600&amp;11200-0|11200&amp;12800-0|12800&amp;14400-0|14400&amp;16000-0|16000&amp;18500-0|18500&amp;21000-0|21000&amp;99999999-0</v>
       </c>
@@ -5782,24 +5205,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" s="12" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A117" s="62">
+    <row r="117" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A117" s="61">
         <v>26001</v>
       </c>
-      <c r="B117" s="62">
+      <c r="B117" s="61">
         <v>102600</v>
       </c>
-      <c r="C117" s="62" t="s">
+      <c r="C117" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="D117" s="62">
+      <c r="D117" s="61">
         <v>1</v>
       </c>
-      <c r="E117" s="63" t="s">
+      <c r="E117" s="62" t="s">
         <v>54</v>
       </c>
       <c r="F117" s="25"/>
-      <c r="G117" s="64" t="s">
+      <c r="G117" s="63" t="s">
         <v>55</v>
       </c>
       <c r="H117" s="28">
@@ -5808,28 +5231,28 @@
       <c r="I117" s="28">
         <v>999999</v>
       </c>
-      <c r="J117" s="36" t="s">
+      <c r="J117" s="35" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="118" s="12" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A118" s="62">
+    <row r="118" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A118" s="61">
         <v>26002</v>
       </c>
-      <c r="B118" s="62">
+      <c r="B118" s="61">
         <v>102600</v>
       </c>
-      <c r="C118" s="62" t="s">
+      <c r="C118" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="D118" s="62">
+      <c r="D118" s="61">
         <v>2</v>
       </c>
-      <c r="E118" s="63" t="s">
+      <c r="E118" s="62" t="s">
         <v>56</v>
       </c>
       <c r="F118" s="25"/>
-      <c r="G118" s="64" t="str">
+      <c r="G118" s="63" t="str">
         <f t="shared" ref="G118:G123" si="15">G117</f>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -5839,28 +5262,28 @@
       <c r="I118" s="28">
         <v>8000</v>
       </c>
-      <c r="J118" s="36" t="s">
+      <c r="J118" s="35" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="119" s="12" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A119" s="62">
+    <row r="119" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A119" s="61">
         <v>26003</v>
       </c>
-      <c r="B119" s="62">
+      <c r="B119" s="61">
         <v>102600</v>
       </c>
-      <c r="C119" s="62" t="s">
+      <c r="C119" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="D119" s="62">
+      <c r="D119" s="61">
         <v>3</v>
       </c>
-      <c r="E119" s="63" t="s">
+      <c r="E119" s="62" t="s">
         <v>57</v>
       </c>
       <c r="F119" s="25"/>
-      <c r="G119" s="64" t="str">
+      <c r="G119" s="63" t="str">
         <f t="shared" si="15"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -5870,28 +5293,28 @@
       <c r="I119" s="28">
         <v>6000</v>
       </c>
-      <c r="J119" s="36" t="s">
+      <c r="J119" s="35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="120" s="12" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A120" s="62">
+    <row r="120" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A120" s="61">
         <v>26004</v>
       </c>
-      <c r="B120" s="62">
+      <c r="B120" s="61">
         <v>102600</v>
       </c>
-      <c r="C120" s="62" t="s">
+      <c r="C120" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="D120" s="62">
+      <c r="D120" s="61">
         <v>4</v>
       </c>
-      <c r="E120" s="63" t="s">
+      <c r="E120" s="62" t="s">
         <v>58</v>
       </c>
       <c r="F120" s="25"/>
-      <c r="G120" s="64" t="str">
+      <c r="G120" s="63" t="str">
         <f t="shared" si="15"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -5901,28 +5324,28 @@
       <c r="I120" s="28">
         <v>4000</v>
       </c>
-      <c r="J120" s="36" t="s">
+      <c r="J120" s="35" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="121" s="12" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A121" s="62">
+    <row r="121" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A121" s="61">
         <v>26005</v>
       </c>
-      <c r="B121" s="62">
+      <c r="B121" s="61">
         <v>102600</v>
       </c>
-      <c r="C121" s="62" t="s">
+      <c r="C121" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="D121" s="62">
+      <c r="D121" s="61">
         <v>5</v>
       </c>
-      <c r="E121" s="63" t="s">
+      <c r="E121" s="62" t="s">
         <v>59</v>
       </c>
       <c r="F121" s="25"/>
-      <c r="G121" s="64" t="str">
+      <c r="G121" s="63" t="str">
         <f t="shared" si="15"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -5932,28 +5355,28 @@
       <c r="I121" s="28">
         <v>2000</v>
       </c>
-      <c r="J121" s="36" t="s">
+      <c r="J121" s="35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="122" s="12" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A122" s="62">
+    <row r="122" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A122" s="61">
         <v>26006</v>
       </c>
-      <c r="B122" s="62">
+      <c r="B122" s="61">
         <v>102600</v>
       </c>
-      <c r="C122" s="62" t="s">
+      <c r="C122" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="D122" s="62">
+      <c r="D122" s="61">
         <v>6</v>
       </c>
-      <c r="E122" s="63" t="s">
+      <c r="E122" s="62" t="s">
         <v>60</v>
       </c>
       <c r="F122" s="25"/>
-      <c r="G122" s="64" t="str">
+      <c r="G122" s="63" t="str">
         <f t="shared" si="15"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -5963,28 +5386,28 @@
       <c r="I122" s="28">
         <v>0</v>
       </c>
-      <c r="J122" s="36" t="s">
+      <c r="J122" s="35" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="123" s="12" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A123" s="62">
+    <row r="123" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A123" s="61">
         <v>26007</v>
       </c>
-      <c r="B123" s="62">
+      <c r="B123" s="61">
         <v>102600</v>
       </c>
-      <c r="C123" s="62" t="s">
+      <c r="C123" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="D123" s="62">
+      <c r="D123" s="61">
         <v>7</v>
       </c>
-      <c r="E123" s="63" t="s">
+      <c r="E123" s="62" t="s">
         <v>61</v>
       </c>
       <c r="F123" s="25"/>
-      <c r="G123" s="64" t="str">
+      <c r="G123" s="63" t="str">
         <f t="shared" si="15"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -5994,28 +5417,28 @@
       <c r="I123" s="28">
         <v>-1000</v>
       </c>
-      <c r="J123" s="36" t="s">
+      <c r="J123" s="35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="124" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A124" s="59">
+    <row r="124" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A124" s="58">
         <v>27001</v>
       </c>
-      <c r="B124" s="59">
+      <c r="B124" s="58">
         <v>102700</v>
       </c>
-      <c r="C124" s="59" t="s">
+      <c r="C124" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D124" s="59">
+      <c r="D124" s="58">
         <v>1</v>
       </c>
-      <c r="E124" s="60" t="s">
+      <c r="E124" s="59" t="s">
         <v>54</v>
       </c>
       <c r="F124" s="25"/>
-      <c r="G124" s="61" t="s">
+      <c r="G124" s="60" t="s">
         <v>134</v>
       </c>
       <c r="H124" s="28">
@@ -6028,24 +5451,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="125" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A125" s="59">
+    <row r="125" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A125" s="58">
         <v>27002</v>
       </c>
-      <c r="B125" s="59">
+      <c r="B125" s="58">
         <v>102700</v>
       </c>
-      <c r="C125" s="59" t="s">
+      <c r="C125" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D125" s="59">
+      <c r="D125" s="58">
         <v>2</v>
       </c>
-      <c r="E125" s="60" t="s">
+      <c r="E125" s="59" t="s">
         <v>56</v>
       </c>
       <c r="F125" s="25"/>
-      <c r="G125" s="61" t="str">
+      <c r="G125" s="60" t="str">
         <f t="shared" ref="G125:G130" si="16">G124</f>
         <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6059,24 +5482,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A126" s="59">
+    <row r="126" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A126" s="58">
         <v>27003</v>
       </c>
-      <c r="B126" s="59">
+      <c r="B126" s="58">
         <v>102700</v>
       </c>
-      <c r="C126" s="59" t="s">
+      <c r="C126" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D126" s="59">
+      <c r="D126" s="58">
         <v>3</v>
       </c>
-      <c r="E126" s="60" t="s">
+      <c r="E126" s="59" t="s">
         <v>57</v>
       </c>
       <c r="F126" s="25"/>
-      <c r="G126" s="61" t="str">
+      <c r="G126" s="60" t="str">
         <f t="shared" si="16"/>
         <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6090,24 +5513,24 @@
         <v>27</v>
       </c>
     </row>
-    <row r="127" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A127" s="59">
+    <row r="127" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A127" s="58">
         <v>27004</v>
       </c>
-      <c r="B127" s="59">
+      <c r="B127" s="58">
         <v>102700</v>
       </c>
-      <c r="C127" s="59" t="s">
+      <c r="C127" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D127" s="59">
+      <c r="D127" s="58">
         <v>4</v>
       </c>
-      <c r="E127" s="60" t="s">
+      <c r="E127" s="59" t="s">
         <v>58</v>
       </c>
       <c r="F127" s="25"/>
-      <c r="G127" s="61" t="str">
+      <c r="G127" s="60" t="str">
         <f t="shared" si="16"/>
         <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6121,24 +5544,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A128" s="59">
+    <row r="128" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A128" s="58">
         <v>27005</v>
       </c>
-      <c r="B128" s="59">
+      <c r="B128" s="58">
         <v>102700</v>
       </c>
-      <c r="C128" s="59" t="s">
+      <c r="C128" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D128" s="59">
+      <c r="D128" s="58">
         <v>5</v>
       </c>
-      <c r="E128" s="60" t="s">
+      <c r="E128" s="59" t="s">
         <v>59</v>
       </c>
       <c r="F128" s="25"/>
-      <c r="G128" s="61" t="str">
+      <c r="G128" s="60" t="str">
         <f t="shared" si="16"/>
         <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6152,24 +5575,24 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A129" s="59">
+    <row r="129" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A129" s="58">
         <v>27006</v>
       </c>
-      <c r="B129" s="59">
+      <c r="B129" s="58">
         <v>102700</v>
       </c>
-      <c r="C129" s="59" t="s">
+      <c r="C129" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D129" s="59">
+      <c r="D129" s="58">
         <v>6</v>
       </c>
-      <c r="E129" s="60" t="s">
+      <c r="E129" s="59" t="s">
         <v>60</v>
       </c>
       <c r="F129" s="25"/>
-      <c r="G129" s="61" t="str">
+      <c r="G129" s="60" t="str">
         <f t="shared" si="16"/>
         <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6183,24 +5606,24 @@
         <v>33</v>
       </c>
     </row>
-    <row r="130" s="11" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A130" s="59">
+    <row r="130" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A130" s="58">
         <v>27007</v>
       </c>
-      <c r="B130" s="59">
+      <c r="B130" s="58">
         <v>102700</v>
       </c>
-      <c r="C130" s="59" t="s">
+      <c r="C130" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D130" s="59">
+      <c r="D130" s="58">
         <v>7</v>
       </c>
-      <c r="E130" s="60" t="s">
+      <c r="E130" s="59" t="s">
         <v>61</v>
       </c>
       <c r="F130" s="25"/>
-      <c r="G130" s="61" t="str">
+      <c r="G130" s="60" t="str">
         <f t="shared" si="16"/>
         <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6214,24 +5637,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A131" s="44">
+    <row r="131" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A131" s="43">
         <v>28001</v>
       </c>
-      <c r="B131" s="44">
+      <c r="B131" s="43">
         <v>102800</v>
       </c>
-      <c r="C131" s="44" t="s">
+      <c r="C131" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="D131" s="44">
+      <c r="D131" s="43">
         <v>1</v>
       </c>
-      <c r="E131" s="45" t="s">
+      <c r="E131" s="44" t="s">
         <v>54</v>
       </c>
       <c r="F131" s="25"/>
-      <c r="G131" s="46" t="s">
+      <c r="G131" s="45" t="s">
         <v>55</v>
       </c>
       <c r="H131" s="28">
@@ -6240,28 +5663,28 @@
       <c r="I131" s="28">
         <v>999999</v>
       </c>
-      <c r="J131" s="47" t="s">
+      <c r="J131" s="46" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="132" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A132" s="44">
+    <row r="132" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A132" s="43">
         <v>28002</v>
       </c>
-      <c r="B132" s="44">
+      <c r="B132" s="43">
         <v>102800</v>
       </c>
-      <c r="C132" s="44" t="s">
+      <c r="C132" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="D132" s="44">
+      <c r="D132" s="43">
         <v>2</v>
       </c>
-      <c r="E132" s="45" t="s">
+      <c r="E132" s="44" t="s">
         <v>56</v>
       </c>
       <c r="F132" s="25"/>
-      <c r="G132" s="46" t="str">
+      <c r="G132" s="45" t="str">
         <f t="shared" ref="G132:G137" si="17">G131</f>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6271,28 +5694,28 @@
       <c r="I132" s="28">
         <v>8000</v>
       </c>
-      <c r="J132" s="47" t="s">
+      <c r="J132" s="46" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="133" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A133" s="44">
+    <row r="133" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A133" s="43">
         <v>28003</v>
       </c>
-      <c r="B133" s="44">
+      <c r="B133" s="43">
         <v>102800</v>
       </c>
-      <c r="C133" s="44" t="s">
+      <c r="C133" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="D133" s="44">
+      <c r="D133" s="43">
         <v>3</v>
       </c>
-      <c r="E133" s="45" t="s">
+      <c r="E133" s="44" t="s">
         <v>57</v>
       </c>
       <c r="F133" s="25"/>
-      <c r="G133" s="46" t="str">
+      <c r="G133" s="45" t="str">
         <f t="shared" si="17"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6302,28 +5725,28 @@
       <c r="I133" s="28">
         <v>6000</v>
       </c>
-      <c r="J133" s="47" t="s">
+      <c r="J133" s="46" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="134" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A134" s="44">
+    <row r="134" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A134" s="43">
         <v>28004</v>
       </c>
-      <c r="B134" s="44">
+      <c r="B134" s="43">
         <v>102800</v>
       </c>
-      <c r="C134" s="44" t="s">
+      <c r="C134" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="D134" s="44">
+      <c r="D134" s="43">
         <v>4</v>
       </c>
-      <c r="E134" s="45" t="s">
+      <c r="E134" s="44" t="s">
         <v>58</v>
       </c>
       <c r="F134" s="25"/>
-      <c r="G134" s="46" t="str">
+      <c r="G134" s="45" t="str">
         <f t="shared" si="17"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6333,28 +5756,28 @@
       <c r="I134" s="28">
         <v>4000</v>
       </c>
-      <c r="J134" s="47" t="s">
+      <c r="J134" s="46" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="135" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A135" s="44">
+    <row r="135" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A135" s="43">
         <v>28005</v>
       </c>
-      <c r="B135" s="44">
+      <c r="B135" s="43">
         <v>102800</v>
       </c>
-      <c r="C135" s="44" t="s">
+      <c r="C135" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="D135" s="44">
+      <c r="D135" s="43">
         <v>5</v>
       </c>
-      <c r="E135" s="45" t="s">
+      <c r="E135" s="44" t="s">
         <v>59</v>
       </c>
       <c r="F135" s="25"/>
-      <c r="G135" s="46" t="str">
+      <c r="G135" s="45" t="str">
         <f t="shared" si="17"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6364,28 +5787,28 @@
       <c r="I135" s="28">
         <v>2000</v>
       </c>
-      <c r="J135" s="47" t="s">
+      <c r="J135" s="46" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="136" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A136" s="44">
+    <row r="136" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A136" s="43">
         <v>28006</v>
       </c>
-      <c r="B136" s="44">
+      <c r="B136" s="43">
         <v>102800</v>
       </c>
-      <c r="C136" s="44" t="s">
+      <c r="C136" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="D136" s="44">
+      <c r="D136" s="43">
         <v>6</v>
       </c>
-      <c r="E136" s="45" t="s">
+      <c r="E136" s="44" t="s">
         <v>60</v>
       </c>
       <c r="F136" s="25"/>
-      <c r="G136" s="46" t="str">
+      <c r="G136" s="45" t="str">
         <f t="shared" si="17"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6395,28 +5818,28 @@
       <c r="I136" s="28">
         <v>0</v>
       </c>
-      <c r="J136" s="47" t="s">
+      <c r="J136" s="46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="137" s="6" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A137" s="44">
+    <row r="137" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A137" s="43">
         <v>28007</v>
       </c>
-      <c r="B137" s="44">
+      <c r="B137" s="43">
         <v>102800</v>
       </c>
-      <c r="C137" s="44" t="s">
+      <c r="C137" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="D137" s="44">
+      <c r="D137" s="43">
         <v>7</v>
       </c>
-      <c r="E137" s="45" t="s">
+      <c r="E137" s="44" t="s">
         <v>61</v>
       </c>
       <c r="F137" s="25"/>
-      <c r="G137" s="46" t="str">
+      <c r="G137" s="45" t="str">
         <f t="shared" si="17"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
@@ -6426,28 +5849,28 @@
       <c r="I137" s="28">
         <v>-1000</v>
       </c>
-      <c r="J137" s="47" t="s">
+      <c r="J137" s="46" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="138" s="13" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A138" s="65">
+    <row r="138" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A138" s="64">
         <v>31001</v>
       </c>
-      <c r="B138" s="65">
+      <c r="B138" s="64">
         <v>103100</v>
       </c>
-      <c r="C138" s="65" t="s">
+      <c r="C138" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D138" s="65">
+      <c r="D138" s="64">
         <v>1</v>
       </c>
-      <c r="E138" s="66" t="s">
+      <c r="E138" s="65" t="s">
         <v>137</v>
       </c>
       <c r="F138" s="25"/>
-      <c r="G138" s="67" t="s">
+      <c r="G138" s="66" t="s">
         <v>138</v>
       </c>
       <c r="H138" s="28">
@@ -6456,28 +5879,28 @@
       <c r="I138" s="28">
         <v>999999</v>
       </c>
-      <c r="J138" s="68" t="s">
+      <c r="J138" s="67" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="139" s="13" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A139" s="65">
+    <row r="139" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A139" s="64">
         <v>31002</v>
       </c>
-      <c r="B139" s="65">
+      <c r="B139" s="64">
         <v>103100</v>
       </c>
-      <c r="C139" s="65" t="s">
+      <c r="C139" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D139" s="65">
+      <c r="D139" s="64">
         <v>2</v>
       </c>
-      <c r="E139" s="66" t="s">
+      <c r="E139" s="65" t="s">
         <v>139</v>
       </c>
       <c r="F139" s="25"/>
-      <c r="G139" s="67" t="str">
+      <c r="G139" s="66" t="str">
         <f t="shared" ref="G139:G144" si="18">G138</f>
         <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -6487,28 +5910,28 @@
       <c r="I139" s="28">
         <v>8000</v>
       </c>
-      <c r="J139" s="68" t="s">
+      <c r="J139" s="67" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="140" s="13" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A140" s="65">
+    <row r="140" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A140" s="64">
         <v>31003</v>
       </c>
-      <c r="B140" s="65">
+      <c r="B140" s="64">
         <v>103100</v>
       </c>
-      <c r="C140" s="65" t="s">
+      <c r="C140" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D140" s="65">
+      <c r="D140" s="64">
         <v>3</v>
       </c>
-      <c r="E140" s="66" t="s">
+      <c r="E140" s="65" t="s">
         <v>140</v>
       </c>
       <c r="F140" s="25"/>
-      <c r="G140" s="67" t="str">
+      <c r="G140" s="66" t="str">
         <f t="shared" si="18"/>
         <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -6518,28 +5941,28 @@
       <c r="I140" s="28">
         <v>6000</v>
       </c>
-      <c r="J140" s="68" t="s">
+      <c r="J140" s="67" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="141" s="13" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A141" s="65">
+    <row r="141" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A141" s="64">
         <v>31004</v>
       </c>
-      <c r="B141" s="65">
+      <c r="B141" s="64">
         <v>103100</v>
       </c>
-      <c r="C141" s="65" t="s">
+      <c r="C141" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D141" s="65">
+      <c r="D141" s="64">
         <v>4</v>
       </c>
-      <c r="E141" s="66" t="s">
+      <c r="E141" s="65" t="s">
         <v>141</v>
       </c>
       <c r="F141" s="25"/>
-      <c r="G141" s="67" t="str">
+      <c r="G141" s="66" t="str">
         <f t="shared" si="18"/>
         <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -6549,28 +5972,28 @@
       <c r="I141" s="28">
         <v>4000</v>
       </c>
-      <c r="J141" s="68" t="s">
+      <c r="J141" s="67" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="142" s="13" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A142" s="65">
+    <row r="142" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A142" s="64">
         <v>31005</v>
       </c>
-      <c r="B142" s="65">
+      <c r="B142" s="64">
         <v>103100</v>
       </c>
-      <c r="C142" s="65" t="s">
+      <c r="C142" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D142" s="65">
+      <c r="D142" s="64">
         <v>5</v>
       </c>
-      <c r="E142" s="66" t="s">
+      <c r="E142" s="65" t="s">
         <v>142</v>
       </c>
       <c r="F142" s="25"/>
-      <c r="G142" s="67" t="str">
+      <c r="G142" s="66" t="str">
         <f t="shared" si="18"/>
         <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -6580,28 +6003,28 @@
       <c r="I142" s="28">
         <v>2000</v>
       </c>
-      <c r="J142" s="68" t="s">
+      <c r="J142" s="67" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="143" s="13" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A143" s="65">
+    <row r="143" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A143" s="64">
         <v>31006</v>
       </c>
-      <c r="B143" s="65">
+      <c r="B143" s="64">
         <v>103100</v>
       </c>
-      <c r="C143" s="65" t="s">
+      <c r="C143" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D143" s="65">
+      <c r="D143" s="64">
         <v>6</v>
       </c>
-      <c r="E143" s="66" t="s">
+      <c r="E143" s="65" t="s">
         <v>143</v>
       </c>
       <c r="F143" s="25"/>
-      <c r="G143" s="67" t="str">
+      <c r="G143" s="66" t="str">
         <f t="shared" si="18"/>
         <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -6611,28 +6034,28 @@
       <c r="I143" s="28">
         <v>0</v>
       </c>
-      <c r="J143" s="68" t="s">
+      <c r="J143" s="67" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="144" s="13" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A144" s="65">
+    <row r="144" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A144" s="64">
         <v>31007</v>
       </c>
-      <c r="B144" s="65">
+      <c r="B144" s="64">
         <v>103100</v>
       </c>
-      <c r="C144" s="65" t="s">
+      <c r="C144" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D144" s="65">
+      <c r="D144" s="64">
         <v>7</v>
       </c>
-      <c r="E144" s="66" t="s">
+      <c r="E144" s="65" t="s">
         <v>144</v>
       </c>
       <c r="F144" s="25"/>
-      <c r="G144" s="67" t="str">
+      <c r="G144" s="66" t="str">
         <f t="shared" si="18"/>
         <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -6642,24 +6065,24 @@
       <c r="I144" s="28">
         <v>-1000</v>
       </c>
-      <c r="J144" s="68" t="s">
+      <c r="J144" s="67" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="145" s="14" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A145" s="69">
+    <row r="145" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A145" s="68">
         <v>34001</v>
       </c>
-      <c r="B145" s="69">
+      <c r="B145" s="68">
         <v>103400</v>
       </c>
-      <c r="C145" s="69" t="s">
+      <c r="C145" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D145" s="69">
+      <c r="D145" s="68">
         <v>1</v>
       </c>
-      <c r="E145" s="70" t="s">
+      <c r="E145" s="69" t="s">
         <v>146</v>
       </c>
       <c r="F145" s="25"/>
@@ -6676,24 +6099,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" s="14" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A146" s="69">
+    <row r="146" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A146" s="68">
         <v>34002</v>
       </c>
-      <c r="B146" s="69">
+      <c r="B146" s="68">
         <v>103400</v>
       </c>
-      <c r="C146" s="69" t="s">
+      <c r="C146" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D146" s="69">
+      <c r="D146" s="68">
         <v>2</v>
       </c>
-      <c r="E146" s="70" t="s">
+      <c r="E146" s="69" t="s">
         <v>148</v>
       </c>
       <c r="F146" s="25"/>
-      <c r="G146" s="71" t="str">
+      <c r="G146" s="70" t="str">
         <f t="shared" ref="G146:G151" si="19">G145</f>
         <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -6707,24 +6130,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" s="14" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A147" s="69">
+    <row r="147" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A147" s="68">
         <v>34003</v>
       </c>
-      <c r="B147" s="69">
+      <c r="B147" s="68">
         <v>103400</v>
       </c>
-      <c r="C147" s="69" t="s">
+      <c r="C147" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D147" s="69">
+      <c r="D147" s="68">
         <v>3</v>
       </c>
-      <c r="E147" s="70" t="s">
+      <c r="E147" s="69" t="s">
         <v>74</v>
       </c>
       <c r="F147" s="25"/>
-      <c r="G147" s="71" t="str">
+      <c r="G147" s="70" t="str">
         <f t="shared" si="19"/>
         <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -6738,24 +6161,24 @@
         <v>27</v>
       </c>
     </row>
-    <row r="148" s="14" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A148" s="69">
+    <row r="148" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A148" s="68">
         <v>34004</v>
       </c>
-      <c r="B148" s="69">
+      <c r="B148" s="68">
         <v>103400</v>
       </c>
-      <c r="C148" s="69" t="s">
+      <c r="C148" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D148" s="69">
+      <c r="D148" s="68">
         <v>4</v>
       </c>
-      <c r="E148" s="70" t="s">
+      <c r="E148" s="69" t="s">
         <v>149</v>
       </c>
       <c r="F148" s="25"/>
-      <c r="G148" s="71" t="str">
+      <c r="G148" s="70" t="str">
         <f t="shared" si="19"/>
         <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -6769,24 +6192,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="149" s="14" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A149" s="69">
+    <row r="149" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A149" s="68">
         <v>34005</v>
       </c>
-      <c r="B149" s="69">
+      <c r="B149" s="68">
         <v>103400</v>
       </c>
-      <c r="C149" s="69" t="s">
+      <c r="C149" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D149" s="69">
+      <c r="D149" s="68">
         <v>5</v>
       </c>
-      <c r="E149" s="70" t="s">
+      <c r="E149" s="69" t="s">
         <v>150</v>
       </c>
       <c r="F149" s="25"/>
-      <c r="G149" s="71" t="str">
+      <c r="G149" s="70" t="str">
         <f t="shared" si="19"/>
         <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -6800,24 +6223,24 @@
         <v>31</v>
       </c>
     </row>
-    <row r="150" s="14" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A150" s="69">
+    <row r="150" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A150" s="68">
         <v>34006</v>
       </c>
-      <c r="B150" s="69">
+      <c r="B150" s="68">
         <v>103400</v>
       </c>
-      <c r="C150" s="69" t="s">
+      <c r="C150" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D150" s="69">
+      <c r="D150" s="68">
         <v>6</v>
       </c>
-      <c r="E150" s="70" t="s">
+      <c r="E150" s="69" t="s">
         <v>43</v>
       </c>
       <c r="F150" s="25"/>
-      <c r="G150" s="71" t="str">
+      <c r="G150" s="70" t="str">
         <f t="shared" si="19"/>
         <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -6831,24 +6254,24 @@
         <v>33</v>
       </c>
     </row>
-    <row r="151" s="14" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A151" s="69">
+    <row r="151" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A151" s="68">
         <v>34007</v>
       </c>
-      <c r="B151" s="69">
+      <c r="B151" s="68">
         <v>103400</v>
       </c>
-      <c r="C151" s="69" t="s">
+      <c r="C151" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D151" s="69">
+      <c r="D151" s="68">
         <v>7</v>
       </c>
-      <c r="E151" s="70" t="s">
+      <c r="E151" s="69" t="s">
         <v>43</v>
       </c>
       <c r="F151" s="25"/>
-      <c r="G151" s="71" t="str">
+      <c r="G151" s="70" t="str">
         <f t="shared" si="19"/>
         <v>1,0&amp;1-70000|1&amp;5-18000|5&amp;10-5000|10&amp;15-1000|15&amp;20-1000|20&amp;25-800|25&amp;30-800|30&amp;35-500|35&amp;40-100|40&amp;45-50|45&amp;50-50|50&amp;60-50|60&amp;70-50|70&amp;80-50|80&amp;90-0|90&amp;100-0|100&amp;120-50|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-50|280&amp;320-50|320&amp;360-50|360&amp;400-50|400&amp;480-0|480&amp;560-50|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-40000|20&amp;25-10000|25&amp;30-35000|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-10000|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-10000|5&amp;10-10000|10&amp;15-10000|15&amp;20-5000|20&amp;25-1000|25&amp;30-900|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -6862,24 +6285,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="152" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A152" s="72">
+    <row r="152" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A152" s="71">
         <v>34011</v>
       </c>
-      <c r="B152" s="72">
+      <c r="B152" s="71">
         <v>103401</v>
       </c>
-      <c r="C152" s="72" t="s">
+      <c r="C152" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="D152" s="72">
+      <c r="D152" s="71">
         <v>1</v>
       </c>
-      <c r="E152" s="73" t="s">
+      <c r="E152" s="72" t="s">
         <v>54</v>
       </c>
       <c r="F152" s="25"/>
-      <c r="G152" s="74" t="s">
+      <c r="G152" s="73" t="s">
         <v>152</v>
       </c>
       <c r="H152" s="28">
@@ -6888,28 +6311,28 @@
       <c r="I152" s="28">
         <v>999999</v>
       </c>
-      <c r="J152" s="75" t="s">
+      <c r="J152" s="74" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="153" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A153" s="72">
+    <row r="153" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A153" s="71">
         <v>34012</v>
       </c>
-      <c r="B153" s="72">
+      <c r="B153" s="71">
         <v>103401</v>
       </c>
-      <c r="C153" s="72" t="s">
+      <c r="C153" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="D153" s="72">
+      <c r="D153" s="71">
         <v>2</v>
       </c>
-      <c r="E153" s="73" t="s">
+      <c r="E153" s="72" t="s">
         <v>56</v>
       </c>
       <c r="F153" s="25"/>
-      <c r="G153" s="74" t="str">
+      <c r="G153" s="73" t="str">
         <f t="shared" ref="G153:G158" si="20">G152</f>
         <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -6919,28 +6342,28 @@
       <c r="I153" s="28">
         <v>8000</v>
       </c>
-      <c r="J153" s="75" t="s">
+      <c r="J153" s="74" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="154" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A154" s="72">
+    <row r="154" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A154" s="71">
         <v>34013</v>
       </c>
-      <c r="B154" s="72">
+      <c r="B154" s="71">
         <v>103401</v>
       </c>
-      <c r="C154" s="72" t="s">
+      <c r="C154" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="D154" s="72">
+      <c r="D154" s="71">
         <v>3</v>
       </c>
-      <c r="E154" s="73" t="s">
+      <c r="E154" s="72" t="s">
         <v>57</v>
       </c>
       <c r="F154" s="25"/>
-      <c r="G154" s="74" t="str">
+      <c r="G154" s="73" t="str">
         <f t="shared" si="20"/>
         <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -6950,28 +6373,28 @@
       <c r="I154" s="28">
         <v>6000</v>
       </c>
-      <c r="J154" s="75" t="s">
+      <c r="J154" s="74" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="155" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A155" s="72">
+    <row r="155" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A155" s="71">
         <v>34014</v>
       </c>
-      <c r="B155" s="72">
+      <c r="B155" s="71">
         <v>103401</v>
       </c>
-      <c r="C155" s="72" t="s">
+      <c r="C155" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="D155" s="72">
+      <c r="D155" s="71">
         <v>4</v>
       </c>
-      <c r="E155" s="73" t="s">
+      <c r="E155" s="72" t="s">
         <v>58</v>
       </c>
       <c r="F155" s="25"/>
-      <c r="G155" s="74" t="str">
+      <c r="G155" s="73" t="str">
         <f t="shared" si="20"/>
         <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -6981,28 +6404,28 @@
       <c r="I155" s="28">
         <v>4000</v>
       </c>
-      <c r="J155" s="75" t="s">
+      <c r="J155" s="74" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="156" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A156" s="72">
+    <row r="156" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A156" s="71">
         <v>34015</v>
       </c>
-      <c r="B156" s="72">
+      <c r="B156" s="71">
         <v>103401</v>
       </c>
-      <c r="C156" s="72" t="s">
+      <c r="C156" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="D156" s="72">
+      <c r="D156" s="71">
         <v>5</v>
       </c>
-      <c r="E156" s="73" t="s">
+      <c r="E156" s="72" t="s">
         <v>59</v>
       </c>
       <c r="F156" s="25"/>
-      <c r="G156" s="74" t="str">
+      <c r="G156" s="73" t="str">
         <f t="shared" si="20"/>
         <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -7012,28 +6435,28 @@
       <c r="I156" s="28">
         <v>2000</v>
       </c>
-      <c r="J156" s="75" t="s">
+      <c r="J156" s="74" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="157" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A157" s="72">
+    <row r="157" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A157" s="71">
         <v>34016</v>
       </c>
-      <c r="B157" s="72">
+      <c r="B157" s="71">
         <v>103401</v>
       </c>
-      <c r="C157" s="72" t="s">
+      <c r="C157" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="D157" s="72">
+      <c r="D157" s="71">
         <v>6</v>
       </c>
-      <c r="E157" s="73" t="s">
+      <c r="E157" s="72" t="s">
         <v>60</v>
       </c>
       <c r="F157" s="25"/>
-      <c r="G157" s="74" t="str">
+      <c r="G157" s="73" t="str">
         <f t="shared" si="20"/>
         <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -7043,28 +6466,28 @@
       <c r="I157" s="28">
         <v>0</v>
       </c>
-      <c r="J157" s="75" t="s">
+      <c r="J157" s="74" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="158" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A158" s="72">
+    <row r="158" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A158" s="71">
         <v>34017</v>
       </c>
-      <c r="B158" s="72">
+      <c r="B158" s="71">
         <v>103401</v>
       </c>
-      <c r="C158" s="72" t="s">
+      <c r="C158" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="D158" s="72">
+      <c r="D158" s="71">
         <v>7</v>
       </c>
-      <c r="E158" s="73" t="s">
+      <c r="E158" s="72" t="s">
         <v>61</v>
       </c>
       <c r="F158" s="25"/>
-      <c r="G158" s="74" t="str">
+      <c r="G158" s="73" t="str">
         <f t="shared" si="20"/>
         <v>1,0&amp;1-53400|1&amp;5-8200|5&amp;10-17200|10&amp;15-8600|15&amp;20-3900|20&amp;25-1800|25&amp;30-2500|30&amp;35-1200|35&amp;40-600|40&amp;45-300|45&amp;50-100|50&amp;60-300|60&amp;70-100|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-0|1&amp;5-5900|5&amp;10-10000|10&amp;15-2200|15&amp;20-400|20&amp;25-100|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-65500|1&amp;5-29400|5&amp;10-3100|10&amp;15-1000|15&amp;20-500|20&amp;25-300|25&amp;30-0|30&amp;35-100|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -7074,24 +6497,24 @@
       <c r="I158" s="28">
         <v>-1000</v>
       </c>
-      <c r="J158" s="75" t="s">
+      <c r="J158" s="74" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="159" s="16" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A159" s="76">
+    <row r="159" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A159" s="75">
         <v>35001</v>
       </c>
-      <c r="B159" s="76">
+      <c r="B159" s="75">
         <v>103500</v>
       </c>
-      <c r="C159" s="76" t="s">
+      <c r="C159" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="D159" s="76">
+      <c r="D159" s="75">
         <v>1</v>
       </c>
-      <c r="E159" s="77" t="s">
+      <c r="E159" s="76" t="s">
         <v>77</v>
       </c>
       <c r="F159" s="25"/>
@@ -7108,24 +6531,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" s="16" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A160" s="76">
+    <row r="160" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A160" s="75">
         <v>35002</v>
       </c>
-      <c r="B160" s="76">
+      <c r="B160" s="75">
         <v>103500</v>
       </c>
-      <c r="C160" s="76" t="s">
+      <c r="C160" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="D160" s="76">
+      <c r="D160" s="75">
         <v>2</v>
       </c>
-      <c r="E160" s="77" t="s">
+      <c r="E160" s="76" t="s">
         <v>155</v>
       </c>
       <c r="F160" s="25"/>
-      <c r="G160" s="78" t="str">
+      <c r="G160" s="77" t="str">
         <f t="shared" ref="G160:G165" si="21">G159</f>
         <v>1,0&amp;1-70000|1&amp;10-18000|10&amp;20-6000|20&amp;30-1000|30&amp;40-100|40&amp;50-0|50&amp;60-1000|60&amp;70-600|70&amp;80-600|80&amp;90-600|90&amp;100-600|100&amp;120-800|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-10|200&amp;240-10|240&amp;280-1|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-2500|140&amp;160-4000|160&amp;180-4982|180&amp;200-5014|200&amp;240-8228|240&amp;280-8228|280&amp;320-8228|320&amp;360-8228|360&amp;400-8000|400&amp;480-10033|480&amp;560-8000|560&amp;640-5000|640&amp;720-4000|720&amp;800-2500|800&amp;960-2500|960&amp;1120-800|1120&amp;1280-400|1280&amp;1440-50|1440&amp;1600-10|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-2600|20&amp;30-400|30&amp;40-100|40&amp;50-1000|50&amp;60-400|60&amp;70-1000|70&amp;80-800|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
@@ -7139,24 +6562,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" s="16" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A161" s="76">
+    <row r="161" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A161" s="75">
         <v>35003</v>
       </c>
-      <c r="B161" s="76">
+      <c r="B161" s="75">
         <v>103500</v>
       </c>
-      <c r="C161" s="76" t="s">
+      <c r="C161" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="D161" s="76">
+      <c r="D161" s="75">
         <v>3</v>
       </c>
-      <c r="E161" s="77" t="s">
+      <c r="E161" s="76" t="s">
         <v>156</v>
       </c>
       <c r="F161" s="25"/>
-      <c r="G161" s="78" t="str">
+      <c r="G161" s="77" t="str">
         <f t="shared" si="21"/>
         <v>1,0&amp;1-70000|1&amp;10-18000|10&amp;20-6000|20&amp;30-1000|30&amp;40-100|40&amp;50-0|50&amp;60-1000|60&amp;70-600|70&amp;80-600|80&amp;90-600|90&amp;100-600|100&amp;120-800|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-10|200&amp;240-10|240&amp;280-1|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-2500|140&amp;160-4000|160&amp;180-4982|180&amp;200-5014|200&amp;240-8228|240&amp;280-8228|280&amp;320-8228|320&amp;360-8228|360&amp;400-8000|400&amp;480-10033|480&amp;560-8000|560&amp;640-5000|640&amp;720-4000|720&amp;800-2500|800&amp;960-2500|960&amp;1120-800|1120&amp;1280-400|1280&amp;1440-50|1440&amp;1600-10|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-2600|20&amp;30-400|30&amp;40-100|40&amp;50-1000|50&amp;60-400|60&amp;70-1000|70&amp;80-800|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
@@ -7170,24 +6593,24 @@
         <v>27</v>
       </c>
     </row>
-    <row r="162" s="16" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A162" s="76">
+    <row r="162" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A162" s="75">
         <v>35004</v>
       </c>
-      <c r="B162" s="76">
+      <c r="B162" s="75">
         <v>103500</v>
       </c>
-      <c r="C162" s="76" t="s">
+      <c r="C162" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="D162" s="76">
+      <c r="D162" s="75">
         <v>4</v>
       </c>
-      <c r="E162" s="77" t="s">
+      <c r="E162" s="76" t="s">
         <v>157</v>
       </c>
       <c r="F162" s="25"/>
-      <c r="G162" s="78" t="str">
+      <c r="G162" s="77" t="str">
         <f t="shared" si="21"/>
         <v>1,0&amp;1-70000|1&amp;10-18000|10&amp;20-6000|20&amp;30-1000|30&amp;40-100|40&amp;50-0|50&amp;60-1000|60&amp;70-600|70&amp;80-600|80&amp;90-600|90&amp;100-600|100&amp;120-800|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-10|200&amp;240-10|240&amp;280-1|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-2500|140&amp;160-4000|160&amp;180-4982|180&amp;200-5014|200&amp;240-8228|240&amp;280-8228|280&amp;320-8228|320&amp;360-8228|360&amp;400-8000|400&amp;480-10033|480&amp;560-8000|560&amp;640-5000|640&amp;720-4000|720&amp;800-2500|800&amp;960-2500|960&amp;1120-800|1120&amp;1280-400|1280&amp;1440-50|1440&amp;1600-10|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-2600|20&amp;30-400|30&amp;40-100|40&amp;50-1000|50&amp;60-400|60&amp;70-1000|70&amp;80-800|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
@@ -7201,24 +6624,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="163" s="16" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A163" s="76">
+    <row r="163" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A163" s="75">
         <v>35005</v>
       </c>
-      <c r="B163" s="76">
+      <c r="B163" s="75">
         <v>103500</v>
       </c>
-      <c r="C163" s="76" t="s">
+      <c r="C163" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="D163" s="76">
+      <c r="D163" s="75">
         <v>5</v>
       </c>
-      <c r="E163" s="77" t="s">
+      <c r="E163" s="76" t="s">
         <v>158</v>
       </c>
       <c r="F163" s="25"/>
-      <c r="G163" s="78" t="str">
+      <c r="G163" s="77" t="str">
         <f t="shared" si="21"/>
         <v>1,0&amp;1-70000|1&amp;10-18000|10&amp;20-6000|20&amp;30-1000|30&amp;40-100|40&amp;50-0|50&amp;60-1000|60&amp;70-600|70&amp;80-600|80&amp;90-600|90&amp;100-600|100&amp;120-800|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-10|200&amp;240-10|240&amp;280-1|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-2500|140&amp;160-4000|160&amp;180-4982|180&amp;200-5014|200&amp;240-8228|240&amp;280-8228|280&amp;320-8228|320&amp;360-8228|360&amp;400-8000|400&amp;480-10033|480&amp;560-8000|560&amp;640-5000|640&amp;720-4000|720&amp;800-2500|800&amp;960-2500|960&amp;1120-800|1120&amp;1280-400|1280&amp;1440-50|1440&amp;1600-10|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-2600|20&amp;30-400|30&amp;40-100|40&amp;50-1000|50&amp;60-400|60&amp;70-1000|70&amp;80-800|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
@@ -7232,24 +6655,24 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" s="16" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A164" s="76">
+    <row r="164" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A164" s="75">
         <v>35006</v>
       </c>
-      <c r="B164" s="76">
+      <c r="B164" s="75">
         <v>103500</v>
       </c>
-      <c r="C164" s="76" t="s">
+      <c r="C164" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="D164" s="76">
+      <c r="D164" s="75">
         <v>6</v>
       </c>
-      <c r="E164" s="77" t="s">
+      <c r="E164" s="76" t="s">
         <v>43</v>
       </c>
       <c r="F164" s="25"/>
-      <c r="G164" s="78" t="str">
+      <c r="G164" s="77" t="str">
         <f t="shared" si="21"/>
         <v>1,0&amp;1-70000|1&amp;10-18000|10&amp;20-6000|20&amp;30-1000|30&amp;40-100|40&amp;50-0|50&amp;60-1000|60&amp;70-600|70&amp;80-600|80&amp;90-600|90&amp;100-600|100&amp;120-800|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-10|200&amp;240-10|240&amp;280-1|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-2500|140&amp;160-4000|160&amp;180-4982|180&amp;200-5014|200&amp;240-8228|240&amp;280-8228|280&amp;320-8228|320&amp;360-8228|360&amp;400-8000|400&amp;480-10033|480&amp;560-8000|560&amp;640-5000|640&amp;720-4000|720&amp;800-2500|800&amp;960-2500|960&amp;1120-800|1120&amp;1280-400|1280&amp;1440-50|1440&amp;1600-10|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-2600|20&amp;30-400|30&amp;40-100|40&amp;50-1000|50&amp;60-400|60&amp;70-1000|70&amp;80-800|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
@@ -7263,24 +6686,24 @@
         <v>33</v>
       </c>
     </row>
-    <row r="165" s="16" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A165" s="76">
+    <row r="165" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A165" s="75">
         <v>35007</v>
       </c>
-      <c r="B165" s="76">
+      <c r="B165" s="75">
         <v>103500</v>
       </c>
-      <c r="C165" s="76" t="s">
+      <c r="C165" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="D165" s="76">
+      <c r="D165" s="75">
         <v>7</v>
       </c>
-      <c r="E165" s="77" t="s">
+      <c r="E165" s="76" t="s">
         <v>43</v>
       </c>
       <c r="F165" s="25"/>
-      <c r="G165" s="78" t="str">
+      <c r="G165" s="77" t="str">
         <f t="shared" si="21"/>
         <v>1,0&amp;1-70000|1&amp;10-18000|10&amp;20-6000|20&amp;30-1000|30&amp;40-100|40&amp;50-0|50&amp;60-1000|60&amp;70-600|70&amp;80-600|80&amp;90-600|90&amp;100-600|100&amp;120-800|120&amp;140-300|140&amp;160-200|160&amp;180-100|180&amp;200-10|200&amp;240-10|240&amp;280-1|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-0|40&amp;50-0|50&amp;60-0|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-2500|140&amp;160-4000|160&amp;180-4982|180&amp;200-5014|200&amp;240-8228|240&amp;280-8228|280&amp;320-8228|320&amp;360-8228|360&amp;400-8000|400&amp;480-10033|480&amp;560-8000|560&amp;640-5000|640&amp;720-4000|720&amp;800-2500|800&amp;960-2500|960&amp;1120-800|1120&amp;1280-400|1280&amp;1440-50|1440&amp;1600-10|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-2600|20&amp;30-400|30&amp;40-100|40&amp;50-1000|50&amp;60-400|60&amp;70-1000|70&amp;80-800|80&amp;90-0|90&amp;100-0|100&amp;120-100|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
@@ -7294,20 +6717,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="166" s="17" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A166" s="79">
+    <row r="166" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A166" s="78">
         <v>35011</v>
       </c>
-      <c r="B166" s="79">
+      <c r="B166" s="78">
         <v>103501</v>
       </c>
-      <c r="C166" s="79" t="s">
+      <c r="C166" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="D166" s="79">
+      <c r="D166" s="78">
         <v>1</v>
       </c>
-      <c r="E166" s="80" t="s">
+      <c r="E166" s="79" t="s">
         <v>77</v>
       </c>
       <c r="F166" s="25"/>
@@ -7324,20 +6747,20 @@
         <v>23</v>
       </c>
     </row>
-    <row r="167" s="17" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A167" s="79">
+    <row r="167" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A167" s="78">
         <v>35012</v>
       </c>
-      <c r="B167" s="79">
+      <c r="B167" s="78">
         <v>103501</v>
       </c>
-      <c r="C167" s="79" t="s">
+      <c r="C167" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="D167" s="79">
+      <c r="D167" s="78">
         <v>2</v>
       </c>
-      <c r="E167" s="80" t="s">
+      <c r="E167" s="79" t="s">
         <v>155</v>
       </c>
       <c r="F167" s="25"/>
@@ -7355,20 +6778,20 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" s="17" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A168" s="79">
+    <row r="168" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A168" s="78">
         <v>35013</v>
       </c>
-      <c r="B168" s="79">
+      <c r="B168" s="78">
         <v>103501</v>
       </c>
-      <c r="C168" s="79" t="s">
+      <c r="C168" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="D168" s="79">
+      <c r="D168" s="78">
         <v>3</v>
       </c>
-      <c r="E168" s="80" t="s">
+      <c r="E168" s="79" t="s">
         <v>156</v>
       </c>
       <c r="F168" s="25"/>
@@ -7386,20 +6809,20 @@
         <v>27</v>
       </c>
     </row>
-    <row r="169" s="17" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A169" s="79">
+    <row r="169" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A169" s="78">
         <v>35014</v>
       </c>
-      <c r="B169" s="79">
+      <c r="B169" s="78">
         <v>103501</v>
       </c>
-      <c r="C169" s="79" t="s">
+      <c r="C169" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="D169" s="79">
+      <c r="D169" s="78">
         <v>4</v>
       </c>
-      <c r="E169" s="80" t="s">
+      <c r="E169" s="79" t="s">
         <v>157</v>
       </c>
       <c r="F169" s="25"/>
@@ -7417,20 +6840,20 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" s="17" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A170" s="79">
+    <row r="170" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A170" s="78">
         <v>35015</v>
       </c>
-      <c r="B170" s="79">
+      <c r="B170" s="78">
         <v>103501</v>
       </c>
-      <c r="C170" s="79" t="s">
+      <c r="C170" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="D170" s="79">
+      <c r="D170" s="78">
         <v>5</v>
       </c>
-      <c r="E170" s="80" t="s">
+      <c r="E170" s="79" t="s">
         <v>158</v>
       </c>
       <c r="F170" s="25"/>
@@ -7448,20 +6871,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" s="17" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A171" s="79">
+    <row r="171" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A171" s="78">
         <v>35016</v>
       </c>
-      <c r="B171" s="79">
+      <c r="B171" s="78">
         <v>103501</v>
       </c>
-      <c r="C171" s="79" t="s">
+      <c r="C171" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="D171" s="79">
+      <c r="D171" s="78">
         <v>6</v>
       </c>
-      <c r="E171" s="80" t="s">
+      <c r="E171" s="79" t="s">
         <v>43</v>
       </c>
       <c r="F171" s="25"/>
@@ -7479,20 +6902,20 @@
         <v>33</v>
       </c>
     </row>
-    <row r="172" s="17" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A172" s="79">
+    <row r="172" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A172" s="78">
         <v>35017</v>
       </c>
-      <c r="B172" s="79">
+      <c r="B172" s="78">
         <v>103501</v>
       </c>
-      <c r="C172" s="79" t="s">
+      <c r="C172" s="78" t="s">
         <v>159</v>
       </c>
-      <c r="D172" s="79">
+      <c r="D172" s="78">
         <v>7</v>
       </c>
-      <c r="E172" s="80" t="s">
+      <c r="E172" s="79" t="s">
         <v>43</v>
       </c>
       <c r="F172" s="25"/>
@@ -7510,24 +6933,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A173" s="81">
+    <row r="173" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A173" s="80">
         <v>36001</v>
       </c>
-      <c r="B173" s="81">
+      <c r="B173" s="80">
         <v>103600</v>
       </c>
-      <c r="C173" s="81" t="s">
+      <c r="C173" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="D173" s="81">
+      <c r="D173" s="80">
         <v>1</v>
       </c>
-      <c r="E173" s="82" t="s">
+      <c r="E173" s="81" t="s">
         <v>54</v>
       </c>
       <c r="F173" s="25"/>
-      <c r="G173" s="83" t="s">
+      <c r="G173" s="82" t="s">
         <v>161</v>
       </c>
       <c r="H173" s="28">
@@ -7536,28 +6959,28 @@
       <c r="I173" s="28">
         <v>999999</v>
       </c>
-      <c r="J173" s="84" t="s">
+      <c r="J173" s="83" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="174" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A174" s="81">
+    <row r="174" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A174" s="80">
         <v>36002</v>
       </c>
-      <c r="B174" s="81">
+      <c r="B174" s="80">
         <v>103600</v>
       </c>
-      <c r="C174" s="81" t="s">
+      <c r="C174" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="D174" s="81">
+      <c r="D174" s="80">
         <v>2</v>
       </c>
-      <c r="E174" s="82" t="s">
+      <c r="E174" s="81" t="s">
         <v>56</v>
       </c>
       <c r="F174" s="25"/>
-      <c r="G174" s="83" t="str">
+      <c r="G174" s="82" t="str">
         <f t="shared" ref="G174:G179" si="23">G173</f>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -7567,28 +6990,28 @@
       <c r="I174" s="28">
         <v>8000</v>
       </c>
-      <c r="J174" s="84" t="s">
+      <c r="J174" s="83" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="175" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A175" s="81">
+    <row r="175" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A175" s="80">
         <v>36003</v>
       </c>
-      <c r="B175" s="81">
+      <c r="B175" s="80">
         <v>103600</v>
       </c>
-      <c r="C175" s="81" t="s">
+      <c r="C175" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="D175" s="81">
+      <c r="D175" s="80">
         <v>3</v>
       </c>
-      <c r="E175" s="82" t="s">
+      <c r="E175" s="81" t="s">
         <v>57</v>
       </c>
       <c r="F175" s="25"/>
-      <c r="G175" s="83" t="str">
+      <c r="G175" s="82" t="str">
         <f t="shared" si="23"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -7598,28 +7021,28 @@
       <c r="I175" s="28">
         <v>6000</v>
       </c>
-      <c r="J175" s="84" t="s">
+      <c r="J175" s="83" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="176" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A176" s="81">
+    <row r="176" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A176" s="80">
         <v>36004</v>
       </c>
-      <c r="B176" s="81">
+      <c r="B176" s="80">
         <v>103600</v>
       </c>
-      <c r="C176" s="81" t="s">
+      <c r="C176" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="D176" s="81">
+      <c r="D176" s="80">
         <v>4</v>
       </c>
-      <c r="E176" s="82" t="s">
+      <c r="E176" s="81" t="s">
         <v>58</v>
       </c>
       <c r="F176" s="25"/>
-      <c r="G176" s="83" t="str">
+      <c r="G176" s="82" t="str">
         <f t="shared" si="23"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -7629,28 +7052,28 @@
       <c r="I176" s="28">
         <v>4000</v>
       </c>
-      <c r="J176" s="84" t="s">
+      <c r="J176" s="83" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="177" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A177" s="81">
+    <row r="177" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A177" s="80">
         <v>36005</v>
       </c>
-      <c r="B177" s="81">
+      <c r="B177" s="80">
         <v>103600</v>
       </c>
-      <c r="C177" s="81" t="s">
+      <c r="C177" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="D177" s="81">
+      <c r="D177" s="80">
         <v>5</v>
       </c>
-      <c r="E177" s="82" t="s">
+      <c r="E177" s="81" t="s">
         <v>59</v>
       </c>
       <c r="F177" s="25"/>
-      <c r="G177" s="83" t="str">
+      <c r="G177" s="82" t="str">
         <f t="shared" si="23"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -7660,28 +7083,28 @@
       <c r="I177" s="28">
         <v>2000</v>
       </c>
-      <c r="J177" s="84" t="s">
+      <c r="J177" s="83" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="178" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A178" s="81">
+    <row r="178" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A178" s="80">
         <v>36006</v>
       </c>
-      <c r="B178" s="81">
+      <c r="B178" s="80">
         <v>103600</v>
       </c>
-      <c r="C178" s="81" t="s">
+      <c r="C178" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="D178" s="81">
+      <c r="D178" s="80">
         <v>6</v>
       </c>
-      <c r="E178" s="82" t="s">
+      <c r="E178" s="81" t="s">
         <v>60</v>
       </c>
       <c r="F178" s="25"/>
-      <c r="G178" s="83" t="str">
+      <c r="G178" s="82" t="str">
         <f t="shared" si="23"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -7691,28 +7114,28 @@
       <c r="I178" s="28">
         <v>0</v>
       </c>
-      <c r="J178" s="84" t="s">
+      <c r="J178" s="83" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="179" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A179" s="81">
+    <row r="179" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A179" s="80">
         <v>36007</v>
       </c>
-      <c r="B179" s="81">
+      <c r="B179" s="80">
         <v>103600</v>
       </c>
-      <c r="C179" s="81" t="s">
+      <c r="C179" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="D179" s="81">
+      <c r="D179" s="80">
         <v>7</v>
       </c>
-      <c r="E179" s="82" t="s">
+      <c r="E179" s="81" t="s">
         <v>61</v>
       </c>
       <c r="F179" s="25"/>
-      <c r="G179" s="83" t="str">
+      <c r="G179" s="82" t="str">
         <f t="shared" si="23"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -7722,28 +7145,28 @@
       <c r="I179" s="28">
         <v>-1000</v>
       </c>
-      <c r="J179" s="84" t="s">
+      <c r="J179" s="83" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="180" s="19" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A180" s="85">
+    <row r="180" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A180" s="84">
         <v>38001</v>
       </c>
-      <c r="B180" s="85">
+      <c r="B180" s="84">
         <v>103800</v>
       </c>
-      <c r="C180" s="85" t="s">
+      <c r="C180" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="D180" s="85">
+      <c r="D180" s="84">
         <v>1</v>
       </c>
-      <c r="E180" s="86" t="s">
+      <c r="E180" s="85" t="s">
         <v>163</v>
       </c>
       <c r="F180" s="25"/>
-      <c r="G180" s="87" t="s">
+      <c r="G180" s="86" t="s">
         <v>164</v>
       </c>
       <c r="H180" s="28">
@@ -7752,28 +7175,28 @@
       <c r="I180" s="28">
         <v>999999</v>
       </c>
-      <c r="J180" s="88" t="s">
+      <c r="J180" s="87" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="181" s="19" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A181" s="85">
+    <row r="181" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A181" s="84">
         <v>38002</v>
       </c>
-      <c r="B181" s="85">
+      <c r="B181" s="84">
         <v>103800</v>
       </c>
-      <c r="C181" s="85" t="s">
+      <c r="C181" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="D181" s="85">
+      <c r="D181" s="84">
         <v>2</v>
       </c>
-      <c r="E181" s="86" t="s">
+      <c r="E181" s="85" t="s">
         <v>165</v>
       </c>
       <c r="F181" s="25"/>
-      <c r="G181" s="87" t="str">
+      <c r="G181" s="86" t="str">
         <f t="shared" ref="G181:G186" si="24">G180</f>
         <v>1,0&amp;1-55100|1&amp;40-33800|40&amp;80-900|80&amp;120-5900|120&amp;160-200|160&amp;200-1600|200&amp;240-300|240&amp;280-200|280&amp;320-200|320&amp;360-1000|360&amp;400-1000|400&amp;480-800|480&amp;560-100|560&amp;640-100|640&amp;720-1000|720&amp;800-1000|800&amp;960-100|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-100|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-200|1&amp;40-3900|40&amp;80-3800|80&amp;120-4100|120&amp;160-3600|160&amp;200-3400|200&amp;240-3000|240&amp;280-3100|280&amp;320-2700|320&amp;360-2400|360&amp;400-2100|400&amp;480-4300|480&amp;560-3800|560&amp;640-3400|640&amp;720-3100|720&amp;800-2600|800&amp;960-5000|960&amp;1120-4100|1120&amp;1280-3600|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-4200|1920&amp;2240-3500|2240&amp;2560-2800|2560&amp;2880-2300|2880&amp;3200-2000|3200&amp;3840-2900|3840&amp;4480-2300|4480&amp;5120-1800|5120&amp;5760-1400|5760&amp;6400-1300|6400&amp;7680-1700|7680&amp;8960-1200|8960&amp;10240-900|10240&amp;11520-700|11520&amp;12800-500|12800&amp;14800-600|14800&amp;16800-400|16800&amp;99999999-1500;3,0&amp;1-0|1&amp;40-0|40&amp;80-200|80&amp;120-3600|120&amp;160-100|160&amp;200-800|200&amp;240-100|240&amp;280-100|280&amp;320-1000|320&amp;360-0|360&amp;400-0|400&amp;480-400|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-100|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;4,0&amp;1-0|1&amp;40-23300|40&amp;80-100|80&amp;120-1500|120&amp;160-0|160&amp;200-300|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-200|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
@@ -7783,28 +7206,28 @@
       <c r="I181" s="28">
         <v>8000</v>
       </c>
-      <c r="J181" s="88" t="s">
+      <c r="J181" s="87" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="182" s="19" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A182" s="85">
+    <row r="182" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A182" s="84">
         <v>38003</v>
       </c>
-      <c r="B182" s="85">
+      <c r="B182" s="84">
         <v>103800</v>
       </c>
-      <c r="C182" s="85" t="s">
+      <c r="C182" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="D182" s="85">
+      <c r="D182" s="84">
         <v>3</v>
       </c>
-      <c r="E182" s="86" t="s">
+      <c r="E182" s="85" t="s">
         <v>166</v>
       </c>
       <c r="F182" s="25"/>
-      <c r="G182" s="87" t="str">
+      <c r="G182" s="86" t="str">
         <f t="shared" si="24"/>
         <v>1,0&amp;1-55100|1&amp;40-33800|40&amp;80-900|80&amp;120-5900|120&amp;160-200|160&amp;200-1600|200&amp;240-300|240&amp;280-200|280&amp;320-200|320&amp;360-1000|360&amp;400-1000|400&amp;480-800|480&amp;560-100|560&amp;640-100|640&amp;720-1000|720&amp;800-1000|800&amp;960-100|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-100|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-200|1&amp;40-3900|40&amp;80-3800|80&amp;120-4100|120&amp;160-3600|160&amp;200-3400|200&amp;240-3000|240&amp;280-3100|280&amp;320-2700|320&amp;360-2400|360&amp;400-2100|400&amp;480-4300|480&amp;560-3800|560&amp;640-3400|640&amp;720-3100|720&amp;800-2600|800&amp;960-5000|960&amp;1120-4100|1120&amp;1280-3600|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-4200|1920&amp;2240-3500|2240&amp;2560-2800|2560&amp;2880-2300|2880&amp;3200-2000|3200&amp;3840-2900|3840&amp;4480-2300|4480&amp;5120-1800|5120&amp;5760-1400|5760&amp;6400-1300|6400&amp;7680-1700|7680&amp;8960-1200|8960&amp;10240-900|10240&amp;11520-700|11520&amp;12800-500|12800&amp;14800-600|14800&amp;16800-400|16800&amp;99999999-1500;3,0&amp;1-0|1&amp;40-0|40&amp;80-200|80&amp;120-3600|120&amp;160-100|160&amp;200-800|200&amp;240-100|240&amp;280-100|280&amp;320-1000|320&amp;360-0|360&amp;400-0|400&amp;480-400|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-100|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;4,0&amp;1-0|1&amp;40-23300|40&amp;80-100|80&amp;120-1500|120&amp;160-0|160&amp;200-300|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-200|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
@@ -7814,28 +7237,28 @@
       <c r="I182" s="28">
         <v>6000</v>
       </c>
-      <c r="J182" s="88" t="s">
+      <c r="J182" s="87" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="183" s="19" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A183" s="85">
+    <row r="183" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A183" s="84">
         <v>38004</v>
       </c>
-      <c r="B183" s="85">
+      <c r="B183" s="84">
         <v>103800</v>
       </c>
-      <c r="C183" s="85" t="s">
+      <c r="C183" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="D183" s="85">
+      <c r="D183" s="84">
         <v>4</v>
       </c>
-      <c r="E183" s="86" t="s">
+      <c r="E183" s="85" t="s">
         <v>167</v>
       </c>
       <c r="F183" s="25"/>
-      <c r="G183" s="87" t="str">
+      <c r="G183" s="86" t="str">
         <f t="shared" si="24"/>
         <v>1,0&amp;1-55100|1&amp;40-33800|40&amp;80-900|80&amp;120-5900|120&amp;160-200|160&amp;200-1600|200&amp;240-300|240&amp;280-200|280&amp;320-200|320&amp;360-1000|360&amp;400-1000|400&amp;480-800|480&amp;560-100|560&amp;640-100|640&amp;720-1000|720&amp;800-1000|800&amp;960-100|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-100|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-200|1&amp;40-3900|40&amp;80-3800|80&amp;120-4100|120&amp;160-3600|160&amp;200-3400|200&amp;240-3000|240&amp;280-3100|280&amp;320-2700|320&amp;360-2400|360&amp;400-2100|400&amp;480-4300|480&amp;560-3800|560&amp;640-3400|640&amp;720-3100|720&amp;800-2600|800&amp;960-5000|960&amp;1120-4100|1120&amp;1280-3600|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-4200|1920&amp;2240-3500|2240&amp;2560-2800|2560&amp;2880-2300|2880&amp;3200-2000|3200&amp;3840-2900|3840&amp;4480-2300|4480&amp;5120-1800|5120&amp;5760-1400|5760&amp;6400-1300|6400&amp;7680-1700|7680&amp;8960-1200|8960&amp;10240-900|10240&amp;11520-700|11520&amp;12800-500|12800&amp;14800-600|14800&amp;16800-400|16800&amp;99999999-1500;3,0&amp;1-0|1&amp;40-0|40&amp;80-200|80&amp;120-3600|120&amp;160-100|160&amp;200-800|200&amp;240-100|240&amp;280-100|280&amp;320-1000|320&amp;360-0|360&amp;400-0|400&amp;480-400|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-100|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;4,0&amp;1-0|1&amp;40-23300|40&amp;80-100|80&amp;120-1500|120&amp;160-0|160&amp;200-300|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-200|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
@@ -7845,28 +7268,28 @@
       <c r="I183" s="28">
         <v>4000</v>
       </c>
-      <c r="J183" s="88" t="s">
+      <c r="J183" s="87" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="184" s="19" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A184" s="85">
+    <row r="184" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A184" s="84">
         <v>38005</v>
       </c>
-      <c r="B184" s="85">
+      <c r="B184" s="84">
         <v>103800</v>
       </c>
-      <c r="C184" s="85" t="s">
+      <c r="C184" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="D184" s="85">
+      <c r="D184" s="84">
         <v>5</v>
       </c>
-      <c r="E184" s="86" t="s">
+      <c r="E184" s="85" t="s">
         <v>86</v>
       </c>
       <c r="F184" s="25"/>
-      <c r="G184" s="87" t="str">
+      <c r="G184" s="86" t="str">
         <f t="shared" si="24"/>
         <v>1,0&amp;1-55100|1&amp;40-33800|40&amp;80-900|80&amp;120-5900|120&amp;160-200|160&amp;200-1600|200&amp;240-300|240&amp;280-200|280&amp;320-200|320&amp;360-1000|360&amp;400-1000|400&amp;480-800|480&amp;560-100|560&amp;640-100|640&amp;720-1000|720&amp;800-1000|800&amp;960-100|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-100|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-200|1&amp;40-3900|40&amp;80-3800|80&amp;120-4100|120&amp;160-3600|160&amp;200-3400|200&amp;240-3000|240&amp;280-3100|280&amp;320-2700|320&amp;360-2400|360&amp;400-2100|400&amp;480-4300|480&amp;560-3800|560&amp;640-3400|640&amp;720-3100|720&amp;800-2600|800&amp;960-5000|960&amp;1120-4100|1120&amp;1280-3600|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-4200|1920&amp;2240-3500|2240&amp;2560-2800|2560&amp;2880-2300|2880&amp;3200-2000|3200&amp;3840-2900|3840&amp;4480-2300|4480&amp;5120-1800|5120&amp;5760-1400|5760&amp;6400-1300|6400&amp;7680-1700|7680&amp;8960-1200|8960&amp;10240-900|10240&amp;11520-700|11520&amp;12800-500|12800&amp;14800-600|14800&amp;16800-400|16800&amp;99999999-1500;3,0&amp;1-0|1&amp;40-0|40&amp;80-200|80&amp;120-3600|120&amp;160-100|160&amp;200-800|200&amp;240-100|240&amp;280-100|280&amp;320-1000|320&amp;360-0|360&amp;400-0|400&amp;480-400|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-100|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;4,0&amp;1-0|1&amp;40-23300|40&amp;80-100|80&amp;120-1500|120&amp;160-0|160&amp;200-300|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-200|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
@@ -7876,28 +7299,28 @@
       <c r="I184" s="28">
         <v>2000</v>
       </c>
-      <c r="J184" s="88" t="s">
+      <c r="J184" s="87" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="185" s="19" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A185" s="85">
+    <row r="185" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A185" s="84">
         <v>38006</v>
       </c>
-      <c r="B185" s="85">
+      <c r="B185" s="84">
         <v>103800</v>
       </c>
-      <c r="C185" s="85" t="s">
+      <c r="C185" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="D185" s="85">
+      <c r="D185" s="84">
         <v>6</v>
       </c>
-      <c r="E185" s="86" t="s">
+      <c r="E185" s="85" t="s">
         <v>168</v>
       </c>
       <c r="F185" s="25"/>
-      <c r="G185" s="87" t="str">
+      <c r="G185" s="86" t="str">
         <f t="shared" si="24"/>
         <v>1,0&amp;1-55100|1&amp;40-33800|40&amp;80-900|80&amp;120-5900|120&amp;160-200|160&amp;200-1600|200&amp;240-300|240&amp;280-200|280&amp;320-200|320&amp;360-1000|360&amp;400-1000|400&amp;480-800|480&amp;560-100|560&amp;640-100|640&amp;720-1000|720&amp;800-1000|800&amp;960-100|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-100|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-200|1&amp;40-3900|40&amp;80-3800|80&amp;120-4100|120&amp;160-3600|160&amp;200-3400|200&amp;240-3000|240&amp;280-3100|280&amp;320-2700|320&amp;360-2400|360&amp;400-2100|400&amp;480-4300|480&amp;560-3800|560&amp;640-3400|640&amp;720-3100|720&amp;800-2600|800&amp;960-5000|960&amp;1120-4100|1120&amp;1280-3600|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-4200|1920&amp;2240-3500|2240&amp;2560-2800|2560&amp;2880-2300|2880&amp;3200-2000|3200&amp;3840-2900|3840&amp;4480-2300|4480&amp;5120-1800|5120&amp;5760-1400|5760&amp;6400-1300|6400&amp;7680-1700|7680&amp;8960-1200|8960&amp;10240-900|10240&amp;11520-700|11520&amp;12800-500|12800&amp;14800-600|14800&amp;16800-400|16800&amp;99999999-1500;3,0&amp;1-0|1&amp;40-0|40&amp;80-200|80&amp;120-3600|120&amp;160-100|160&amp;200-800|200&amp;240-100|240&amp;280-100|280&amp;320-1000|320&amp;360-0|360&amp;400-0|400&amp;480-400|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-100|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;4,0&amp;1-0|1&amp;40-23300|40&amp;80-100|80&amp;120-1500|120&amp;160-0|160&amp;200-300|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-200|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
@@ -7907,28 +7330,28 @@
       <c r="I185" s="28">
         <v>0</v>
       </c>
-      <c r="J185" s="88" t="s">
+      <c r="J185" s="87" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="186" s="19" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A186" s="85">
+    <row r="186" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A186" s="84">
         <v>38007</v>
       </c>
-      <c r="B186" s="85">
+      <c r="B186" s="84">
         <v>103800</v>
       </c>
-      <c r="C186" s="85" t="s">
+      <c r="C186" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="D186" s="85">
+      <c r="D186" s="84">
         <v>7</v>
       </c>
-      <c r="E186" s="86" t="s">
+      <c r="E186" s="85" t="s">
         <v>169</v>
       </c>
       <c r="F186" s="25"/>
-      <c r="G186" s="87" t="str">
+      <c r="G186" s="86" t="str">
         <f t="shared" si="24"/>
         <v>1,0&amp;1-55100|1&amp;40-33800|40&amp;80-900|80&amp;120-5900|120&amp;160-200|160&amp;200-1600|200&amp;240-300|240&amp;280-200|280&amp;320-200|320&amp;360-1000|360&amp;400-1000|400&amp;480-800|480&amp;560-100|560&amp;640-100|640&amp;720-1000|720&amp;800-1000|800&amp;960-100|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-100|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-200|1&amp;40-3900|40&amp;80-3800|80&amp;120-4100|120&amp;160-3600|160&amp;200-3400|200&amp;240-3000|240&amp;280-3100|280&amp;320-2700|320&amp;360-2400|360&amp;400-2100|400&amp;480-4300|480&amp;560-3800|560&amp;640-3400|640&amp;720-3100|720&amp;800-2600|800&amp;960-5000|960&amp;1120-4100|1120&amp;1280-3600|1280&amp;1440-3200|1440&amp;1600-2600|1600&amp;1920-4200|1920&amp;2240-3500|2240&amp;2560-2800|2560&amp;2880-2300|2880&amp;3200-2000|3200&amp;3840-2900|3840&amp;4480-2300|4480&amp;5120-1800|5120&amp;5760-1400|5760&amp;6400-1300|6400&amp;7680-1700|7680&amp;8960-1200|8960&amp;10240-900|10240&amp;11520-700|11520&amp;12800-500|12800&amp;14800-600|14800&amp;16800-400|16800&amp;99999999-1500;3,0&amp;1-0|1&amp;40-0|40&amp;80-200|80&amp;120-3600|120&amp;160-100|160&amp;200-800|200&amp;240-100|240&amp;280-100|280&amp;320-1000|320&amp;360-0|360&amp;400-0|400&amp;480-400|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-100|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;4,0&amp;1-0|1&amp;40-23300|40&amp;80-100|80&amp;120-1500|120&amp;160-0|160&amp;200-300|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-200|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</v>
       </c>
@@ -7938,28 +7361,28 @@
       <c r="I186" s="28">
         <v>-1000</v>
       </c>
-      <c r="J186" s="88" t="s">
+      <c r="J186" s="87" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="187" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A187" s="81">
+    <row r="187" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A187" s="80">
         <v>37001</v>
       </c>
-      <c r="B187" s="81">
+      <c r="B187" s="80">
         <v>103700</v>
       </c>
-      <c r="C187" s="81" t="s">
+      <c r="C187" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="D187" s="81">
+      <c r="D187" s="80">
         <v>1</v>
       </c>
-      <c r="E187" s="82" t="s">
+      <c r="E187" s="81" t="s">
         <v>171</v>
       </c>
       <c r="F187" s="25"/>
-      <c r="G187" s="83" t="s">
+      <c r="G187" s="82" t="s">
         <v>161</v>
       </c>
       <c r="H187" s="28">
@@ -7968,28 +7391,28 @@
       <c r="I187" s="28">
         <v>999999</v>
       </c>
-      <c r="J187" s="84" t="s">
+      <c r="J187" s="83" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="188" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A188" s="81">
+    <row r="188" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A188" s="80">
         <v>37002</v>
       </c>
-      <c r="B188" s="81">
+      <c r="B188" s="80">
         <v>103700</v>
       </c>
-      <c r="C188" s="81" t="s">
+      <c r="C188" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="D188" s="81">
+      <c r="D188" s="80">
         <v>2</v>
       </c>
-      <c r="E188" s="82" t="s">
+      <c r="E188" s="81" t="s">
         <v>172</v>
       </c>
       <c r="F188" s="25"/>
-      <c r="G188" s="83" t="str">
+      <c r="G188" s="82" t="str">
         <f t="shared" ref="G188:G193" si="25">G187</f>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -7999,28 +7422,28 @@
       <c r="I188" s="28">
         <v>8000</v>
       </c>
-      <c r="J188" s="84" t="s">
+      <c r="J188" s="83" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="189" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A189" s="81">
+    <row r="189" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A189" s="80">
         <v>37003</v>
       </c>
-      <c r="B189" s="81">
+      <c r="B189" s="80">
         <v>103700</v>
       </c>
-      <c r="C189" s="81" t="s">
+      <c r="C189" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="D189" s="81">
+      <c r="D189" s="80">
         <v>3</v>
       </c>
-      <c r="E189" s="82" t="s">
+      <c r="E189" s="81" t="s">
         <v>173</v>
       </c>
       <c r="F189" s="25"/>
-      <c r="G189" s="83" t="str">
+      <c r="G189" s="82" t="str">
         <f t="shared" si="25"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -8030,28 +7453,28 @@
       <c r="I189" s="28">
         <v>6000</v>
       </c>
-      <c r="J189" s="84" t="s">
+      <c r="J189" s="83" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="190" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A190" s="81">
+    <row r="190" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A190" s="80">
         <v>37004</v>
       </c>
-      <c r="B190" s="81">
+      <c r="B190" s="80">
         <v>103700</v>
       </c>
-      <c r="C190" s="81" t="s">
+      <c r="C190" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="D190" s="81">
+      <c r="D190" s="80">
         <v>4</v>
       </c>
-      <c r="E190" s="82" t="s">
+      <c r="E190" s="81" t="s">
         <v>174</v>
       </c>
       <c r="F190" s="25"/>
-      <c r="G190" s="83" t="str">
+      <c r="G190" s="82" t="str">
         <f t="shared" si="25"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -8061,28 +7484,28 @@
       <c r="I190" s="28">
         <v>4000</v>
       </c>
-      <c r="J190" s="84" t="s">
+      <c r="J190" s="83" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="191" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A191" s="81">
+    <row r="191" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A191" s="80">
         <v>37005</v>
       </c>
-      <c r="B191" s="81">
+      <c r="B191" s="80">
         <v>103700</v>
       </c>
-      <c r="C191" s="81" t="s">
+      <c r="C191" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="D191" s="81">
+      <c r="D191" s="80">
         <v>5</v>
       </c>
-      <c r="E191" s="82" t="s">
+      <c r="E191" s="81" t="s">
         <v>175</v>
       </c>
       <c r="F191" s="25"/>
-      <c r="G191" s="83" t="str">
+      <c r="G191" s="82" t="str">
         <f t="shared" si="25"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -8092,28 +7515,28 @@
       <c r="I191" s="28">
         <v>2000</v>
       </c>
-      <c r="J191" s="84" t="s">
+      <c r="J191" s="83" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="192" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A192" s="81">
+    <row r="192" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A192" s="80">
         <v>37006</v>
       </c>
-      <c r="B192" s="81">
+      <c r="B192" s="80">
         <v>103700</v>
       </c>
-      <c r="C192" s="81" t="s">
+      <c r="C192" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="D192" s="81">
+      <c r="D192" s="80">
         <v>6</v>
       </c>
-      <c r="E192" s="82" t="s">
+      <c r="E192" s="81" t="s">
         <v>58</v>
       </c>
       <c r="F192" s="25"/>
-      <c r="G192" s="83" t="str">
+      <c r="G192" s="82" t="str">
         <f t="shared" si="25"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -8123,28 +7546,28 @@
       <c r="I192" s="28">
         <v>0</v>
       </c>
-      <c r="J192" s="84" t="s">
+      <c r="J192" s="83" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="193" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A193" s="81">
+    <row r="193" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A193" s="80">
         <v>37007</v>
       </c>
-      <c r="B193" s="81">
+      <c r="B193" s="80">
         <v>103700</v>
       </c>
-      <c r="C193" s="81" t="s">
+      <c r="C193" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="D193" s="81">
+      <c r="D193" s="80">
         <v>7</v>
       </c>
-      <c r="E193" s="82" t="s">
+      <c r="E193" s="81" t="s">
         <v>176</v>
       </c>
       <c r="F193" s="25"/>
-      <c r="G193" s="83" t="str">
+      <c r="G193" s="82" t="str">
         <f t="shared" si="25"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
       </c>
@@ -8154,28 +7577,28 @@
       <c r="I193" s="28">
         <v>-1000</v>
       </c>
-      <c r="J193" s="84" t="s">
+      <c r="J193" s="83" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="194" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A194" s="89">
+    <row r="194" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A194" s="88">
         <v>39001</v>
       </c>
-      <c r="B194" s="89">
+      <c r="B194" s="88">
         <v>103900</v>
       </c>
-      <c r="C194" s="89" t="s">
+      <c r="C194" s="88" t="s">
         <v>177</v>
       </c>
-      <c r="D194" s="89">
+      <c r="D194" s="88">
         <v>1</v>
       </c>
       <c r="E194" s="34" t="s">
         <v>122</v>
       </c>
       <c r="F194" s="25"/>
-      <c r="G194" s="37" t="s">
+      <c r="G194" s="36" t="s">
         <v>178</v>
       </c>
       <c r="H194" s="28">
@@ -8188,24 +7611,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A195" s="89">
+    <row r="195" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A195" s="88">
         <v>39002</v>
       </c>
-      <c r="B195" s="89">
+      <c r="B195" s="88">
         <v>103900</v>
       </c>
-      <c r="C195" s="89" t="s">
+      <c r="C195" s="88" t="s">
         <v>177</v>
       </c>
-      <c r="D195" s="89">
+      <c r="D195" s="88">
         <v>2</v>
       </c>
       <c r="E195" s="34" t="s">
         <v>179</v>
       </c>
       <c r="F195" s="25"/>
-      <c r="G195" s="37" t="str">
+      <c r="G195" s="36" t="str">
         <f t="shared" ref="G195:G200" si="26">G194</f>
         <v>1,0&amp;1-59200|1&amp;25-7500|25&amp;50-6700|50&amp;75-5700|75&amp;100-3200|100&amp;125-3000|125&amp;150-1800|150&amp;175-1800|175&amp;200-1200|200&amp;225-1300|225&amp;250-900|250&amp;300-1400|300&amp;350-1300|350&amp;400-800|400&amp;450-600|450&amp;500-400|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-6900|1200&amp;1400-6100|1400&amp;1600-5900|1600&amp;1800-5300|1800&amp;2000-4700|2000&amp;2400-7700|2400&amp;2800-6100|2800&amp;3200-5000|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -8219,24 +7642,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A196" s="89">
+    <row r="196" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A196" s="88">
         <v>39003</v>
       </c>
-      <c r="B196" s="89">
+      <c r="B196" s="88">
         <v>103900</v>
       </c>
-      <c r="C196" s="89" t="s">
+      <c r="C196" s="88" t="s">
         <v>177</v>
       </c>
-      <c r="D196" s="89">
+      <c r="D196" s="88">
         <v>3</v>
       </c>
       <c r="E196" s="34" t="s">
         <v>180</v>
       </c>
       <c r="F196" s="25"/>
-      <c r="G196" s="37" t="str">
+      <c r="G196" s="36" t="str">
         <f t="shared" si="26"/>
         <v>1,0&amp;1-59200|1&amp;25-7500|25&amp;50-6700|50&amp;75-5700|75&amp;100-3200|100&amp;125-3000|125&amp;150-1800|150&amp;175-1800|175&amp;200-1200|200&amp;225-1300|225&amp;250-900|250&amp;300-1400|300&amp;350-1300|350&amp;400-800|400&amp;450-600|450&amp;500-400|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-6900|1200&amp;1400-6100|1400&amp;1600-5900|1600&amp;1800-5300|1800&amp;2000-4700|2000&amp;2400-7700|2400&amp;2800-6100|2800&amp;3200-5000|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -8250,24 +7673,24 @@
         <v>27</v>
       </c>
     </row>
-    <row r="197" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A197" s="89">
+    <row r="197" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A197" s="88">
         <v>39004</v>
       </c>
-      <c r="B197" s="89">
+      <c r="B197" s="88">
         <v>103900</v>
       </c>
-      <c r="C197" s="89" t="s">
+      <c r="C197" s="88" t="s">
         <v>177</v>
       </c>
-      <c r="D197" s="89">
+      <c r="D197" s="88">
         <v>4</v>
       </c>
       <c r="E197" s="34" t="s">
         <v>181</v>
       </c>
       <c r="F197" s="25"/>
-      <c r="G197" s="37" t="str">
+      <c r="G197" s="36" t="str">
         <f t="shared" si="26"/>
         <v>1,0&amp;1-59200|1&amp;25-7500|25&amp;50-6700|50&amp;75-5700|75&amp;100-3200|100&amp;125-3000|125&amp;150-1800|150&amp;175-1800|175&amp;200-1200|200&amp;225-1300|225&amp;250-900|250&amp;300-1400|300&amp;350-1300|350&amp;400-800|400&amp;450-600|450&amp;500-400|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-6900|1200&amp;1400-6100|1400&amp;1600-5900|1600&amp;1800-5300|1800&amp;2000-4700|2000&amp;2400-7700|2400&amp;2800-6100|2800&amp;3200-5000|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -8281,24 +7704,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="198" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A198" s="89">
+    <row r="198" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A198" s="88">
         <v>39005</v>
       </c>
-      <c r="B198" s="89">
+      <c r="B198" s="88">
         <v>103900</v>
       </c>
-      <c r="C198" s="89" t="s">
+      <c r="C198" s="88" t="s">
         <v>177</v>
       </c>
-      <c r="D198" s="89">
+      <c r="D198" s="88">
         <v>5</v>
       </c>
       <c r="E198" s="34" t="s">
         <v>182</v>
       </c>
       <c r="F198" s="25"/>
-      <c r="G198" s="37" t="str">
+      <c r="G198" s="36" t="str">
         <f t="shared" si="26"/>
         <v>1,0&amp;1-59200|1&amp;25-7500|25&amp;50-6700|50&amp;75-5700|75&amp;100-3200|100&amp;125-3000|125&amp;150-1800|150&amp;175-1800|175&amp;200-1200|200&amp;225-1300|225&amp;250-900|250&amp;300-1400|300&amp;350-1300|350&amp;400-800|400&amp;450-600|450&amp;500-400|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-6900|1200&amp;1400-6100|1400&amp;1600-5900|1600&amp;1800-5300|1800&amp;2000-4700|2000&amp;2400-7700|2400&amp;2800-6100|2800&amp;3200-5000|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -8312,24 +7735,24 @@
         <v>31</v>
       </c>
     </row>
-    <row r="199" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A199" s="89">
+    <row r="199" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A199" s="88">
         <v>39006</v>
       </c>
-      <c r="B199" s="89">
+      <c r="B199" s="88">
         <v>103900</v>
       </c>
-      <c r="C199" s="89" t="s">
+      <c r="C199" s="88" t="s">
         <v>177</v>
       </c>
-      <c r="D199" s="89">
+      <c r="D199" s="88">
         <v>6</v>
       </c>
       <c r="E199" s="34" t="s">
         <v>176</v>
       </c>
       <c r="F199" s="25"/>
-      <c r="G199" s="37" t="str">
+      <c r="G199" s="36" t="str">
         <f t="shared" si="26"/>
         <v>1,0&amp;1-59200|1&amp;25-7500|25&amp;50-6700|50&amp;75-5700|75&amp;100-3200|100&amp;125-3000|125&amp;150-1800|150&amp;175-1800|175&amp;200-1200|200&amp;225-1300|225&amp;250-900|250&amp;300-1400|300&amp;350-1300|350&amp;400-800|400&amp;450-600|450&amp;500-400|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-6900|1200&amp;1400-6100|1400&amp;1600-5900|1600&amp;1800-5300|1800&amp;2000-4700|2000&amp;2400-7700|2400&amp;2800-6100|2800&amp;3200-5000|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -8343,24 +7766,24 @@
         <v>33</v>
       </c>
     </row>
-    <row r="200" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A200" s="89">
+    <row r="200" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A200" s="88">
         <v>39007</v>
       </c>
-      <c r="B200" s="89">
+      <c r="B200" s="88">
         <v>103900</v>
       </c>
-      <c r="C200" s="89" t="s">
+      <c r="C200" s="88" t="s">
         <v>177</v>
       </c>
-      <c r="D200" s="89">
+      <c r="D200" s="88">
         <v>7</v>
       </c>
       <c r="E200" s="34" t="s">
         <v>183</v>
       </c>
       <c r="F200" s="25"/>
-      <c r="G200" s="37" t="str">
+      <c r="G200" s="36" t="str">
         <f t="shared" si="26"/>
         <v>1,0&amp;1-59200|1&amp;25-7500|25&amp;50-6700|50&amp;75-5700|75&amp;100-3200|100&amp;125-3000|125&amp;150-1800|150&amp;175-1800|175&amp;200-1200|200&amp;225-1300|225&amp;250-900|250&amp;300-1400|300&amp;350-1300|350&amp;400-800|400&amp;450-600|450&amp;500-400|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-6900|1200&amp;1400-6100|1400&amp;1600-5900|1600&amp;1800-5300|1800&amp;2000-4700|2000&amp;2400-7700|2400&amp;2800-6100|2800&amp;3200-5000|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
@@ -8374,24 +7797,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="201" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A201" s="72">
+    <row r="201" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A201" s="71">
         <v>40001</v>
       </c>
-      <c r="B201" s="72">
+      <c r="B201" s="71">
         <v>104000</v>
       </c>
-      <c r="C201" s="72" t="s">
+      <c r="C201" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="D201" s="72">
+      <c r="D201" s="71">
         <v>1</v>
       </c>
-      <c r="E201" s="73" t="s">
+      <c r="E201" s="72" t="s">
         <v>54</v>
       </c>
       <c r="F201" s="25"/>
-      <c r="G201" s="74" t="s">
+      <c r="G201" s="73" t="s">
         <v>185</v>
       </c>
       <c r="H201" s="28">
@@ -8400,28 +7823,28 @@
       <c r="I201" s="28">
         <v>999999</v>
       </c>
-      <c r="J201" s="75" t="s">
+      <c r="J201" s="74" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="202" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A202" s="72">
+    <row r="202" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A202" s="71">
         <v>40002</v>
       </c>
-      <c r="B202" s="72">
+      <c r="B202" s="71">
         <v>104000</v>
       </c>
-      <c r="C202" s="72" t="s">
+      <c r="C202" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="D202" s="72">
+      <c r="D202" s="71">
         <v>2</v>
       </c>
-      <c r="E202" s="73" t="s">
+      <c r="E202" s="72" t="s">
         <v>56</v>
       </c>
       <c r="F202" s="25"/>
-      <c r="G202" s="74" t="str">
+      <c r="G202" s="73" t="str">
         <f t="shared" ref="G202:G207" si="27">G201</f>
         <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
       </c>
@@ -8431,28 +7854,28 @@
       <c r="I202" s="28">
         <v>8000</v>
       </c>
-      <c r="J202" s="75" t="s">
+      <c r="J202" s="74" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="203" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A203" s="72">
+    <row r="203" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A203" s="71">
         <v>40003</v>
       </c>
-      <c r="B203" s="72">
+      <c r="B203" s="71">
         <v>104000</v>
       </c>
-      <c r="C203" s="72" t="s">
+      <c r="C203" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="D203" s="72">
+      <c r="D203" s="71">
         <v>3</v>
       </c>
-      <c r="E203" s="73" t="s">
+      <c r="E203" s="72" t="s">
         <v>57</v>
       </c>
       <c r="F203" s="25"/>
-      <c r="G203" s="74" t="str">
+      <c r="G203" s="73" t="str">
         <f t="shared" si="27"/>
         <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
       </c>
@@ -8462,28 +7885,28 @@
       <c r="I203" s="28">
         <v>6000</v>
       </c>
-      <c r="J203" s="75" t="s">
+      <c r="J203" s="74" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="204" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A204" s="72">
+    <row r="204" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A204" s="71">
         <v>40004</v>
       </c>
-      <c r="B204" s="72">
+      <c r="B204" s="71">
         <v>104000</v>
       </c>
-      <c r="C204" s="72" t="s">
+      <c r="C204" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="D204" s="72">
+      <c r="D204" s="71">
         <v>4</v>
       </c>
-      <c r="E204" s="73" t="s">
+      <c r="E204" s="72" t="s">
         <v>58</v>
       </c>
       <c r="F204" s="25"/>
-      <c r="G204" s="74" t="str">
+      <c r="G204" s="73" t="str">
         <f t="shared" si="27"/>
         <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
       </c>
@@ -8493,28 +7916,28 @@
       <c r="I204" s="28">
         <v>4000</v>
       </c>
-      <c r="J204" s="75" t="s">
+      <c r="J204" s="74" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="205" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A205" s="72">
+    <row r="205" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A205" s="71">
         <v>40005</v>
       </c>
-      <c r="B205" s="72">
+      <c r="B205" s="71">
         <v>104000</v>
       </c>
-      <c r="C205" s="72" t="s">
+      <c r="C205" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="D205" s="72">
+      <c r="D205" s="71">
         <v>5</v>
       </c>
-      <c r="E205" s="73" t="s">
+      <c r="E205" s="72" t="s">
         <v>59</v>
       </c>
       <c r="F205" s="25"/>
-      <c r="G205" s="74" t="str">
+      <c r="G205" s="73" t="str">
         <f t="shared" si="27"/>
         <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
       </c>
@@ -8524,28 +7947,28 @@
       <c r="I205" s="28">
         <v>2000</v>
       </c>
-      <c r="J205" s="75" t="s">
+      <c r="J205" s="74" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="206" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A206" s="72">
+    <row r="206" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A206" s="71">
         <v>40006</v>
       </c>
-      <c r="B206" s="72">
+      <c r="B206" s="71">
         <v>104000</v>
       </c>
-      <c r="C206" s="72" t="s">
+      <c r="C206" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="D206" s="72">
+      <c r="D206" s="71">
         <v>6</v>
       </c>
-      <c r="E206" s="73" t="s">
+      <c r="E206" s="72" t="s">
         <v>60</v>
       </c>
       <c r="F206" s="25"/>
-      <c r="G206" s="74" t="str">
+      <c r="G206" s="73" t="str">
         <f t="shared" si="27"/>
         <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
       </c>
@@ -8555,28 +7978,28 @@
       <c r="I206" s="28">
         <v>0</v>
       </c>
-      <c r="J206" s="75" t="s">
+      <c r="J206" s="74" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="207" s="15" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A207" s="72">
+    <row r="207" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A207" s="71">
         <v>40007</v>
       </c>
-      <c r="B207" s="72">
+      <c r="B207" s="71">
         <v>104000</v>
       </c>
-      <c r="C207" s="72" t="s">
+      <c r="C207" s="71" t="s">
         <v>184</v>
       </c>
-      <c r="D207" s="72">
+      <c r="D207" s="71">
         <v>7</v>
       </c>
-      <c r="E207" s="73" t="s">
+      <c r="E207" s="72" t="s">
         <v>61</v>
       </c>
       <c r="F207" s="25"/>
-      <c r="G207" s="74" t="str">
+      <c r="G207" s="73" t="str">
         <f t="shared" si="27"/>
         <v>1,0&amp;1-63800|1&amp;40-13300|40&amp;80-6600|80&amp;120-3500|120&amp;160-2400|160&amp;200-2200|200&amp;240-700|240&amp;280-1300|280&amp;320-500|320&amp;360-900|360&amp;400-500|400&amp;480-400|480&amp;560-1000|560&amp;640-300|640&amp;720-400|720&amp;800-400|800&amp;960-300|960&amp;1120-400|1120&amp;1280-200|1280&amp;1440-100|1440&amp;1600-100|1600&amp;1920-100|1920&amp;2240-200|2240&amp;2560-100|2560&amp;2880-0|2880&amp;3200-100|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400;3,0&amp;1-100|1&amp;40-100|40&amp;80-100|80&amp;120-300|120&amp;160-300|160&amp;200-400|200&amp;240-400|240&amp;280-500|280&amp;320-400|320&amp;360-600|360&amp;400-500|400&amp;480-1200|480&amp;560-1400|560&amp;640-1500|640&amp;720-1800|720&amp;800-1700|800&amp;960-3600|960&amp;1120-3700|1120&amp;1280-3800|1280&amp;1440-3700|1440&amp;1600-3700|1600&amp;1920-6900|1920&amp;2240-6100|2240&amp;2560-5900|2560&amp;2880-5300|2880&amp;3200-4700|3200&amp;3840-7700|3840&amp;4480-6100|4480&amp;5120-5000|5120&amp;5760-3900|5760&amp;6400-3200|6400&amp;7680-4500|7680&amp;8960-3100|8960&amp;10240-2100|10240&amp;11520-1400|11520&amp;12800-900|12800&amp;14800-1100|14800&amp;16800-700|16800&amp;99999999-1400</v>
       </c>
@@ -8586,28 +8009,28 @@
       <c r="I207" s="28">
         <v>-1000</v>
       </c>
-      <c r="J207" s="75" t="s">
+      <c r="J207" s="74" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="208" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A208" s="89">
+    <row r="208" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A208" s="88">
         <v>48001</v>
       </c>
-      <c r="B208" s="89">
+      <c r="B208" s="88">
         <v>104800</v>
       </c>
-      <c r="C208" s="89" t="s">
+      <c r="C208" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="D208" s="89">
+      <c r="D208" s="88">
         <v>1</v>
       </c>
       <c r="E208" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="F208" s="35"/>
-      <c r="G208" s="37" t="s">
+      <c r="F208" s="25"/>
+      <c r="G208" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H208" s="28">
@@ -8620,24 +8043,24 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A209" s="89">
+    <row r="209" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A209" s="88">
         <v>48002</v>
       </c>
-      <c r="B209" s="89">
+      <c r="B209" s="88">
         <v>104800</v>
       </c>
-      <c r="C209" s="89" t="s">
+      <c r="C209" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="D209" s="89">
+      <c r="D209" s="88">
         <v>2</v>
       </c>
       <c r="E209" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F209" s="35"/>
-      <c r="G209" s="37" t="s">
+      <c r="F209" s="25"/>
+      <c r="G209" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H209" s="28">
@@ -8650,24 +8073,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A210" s="89">
+    <row r="210" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A210" s="88">
         <v>48003</v>
       </c>
-      <c r="B210" s="89">
+      <c r="B210" s="88">
         <v>104800</v>
       </c>
-      <c r="C210" s="89" t="s">
+      <c r="C210" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="D210" s="89">
+      <c r="D210" s="88">
         <v>3</v>
       </c>
       <c r="E210" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F210" s="35"/>
-      <c r="G210" s="37" t="s">
+      <c r="F210" s="25"/>
+      <c r="G210" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H210" s="28">
@@ -8680,24 +8103,24 @@
         <v>27</v>
       </c>
     </row>
-    <row r="211" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A211" s="89">
+    <row r="211" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A211" s="88">
         <v>48004</v>
       </c>
-      <c r="B211" s="89">
+      <c r="B211" s="88">
         <v>104800</v>
       </c>
-      <c r="C211" s="89" t="s">
+      <c r="C211" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="D211" s="89">
+      <c r="D211" s="88">
         <v>4</v>
       </c>
       <c r="E211" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="F211" s="35"/>
-      <c r="G211" s="37" t="s">
+      <c r="F211" s="25"/>
+      <c r="G211" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H211" s="28">
@@ -8710,24 +8133,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="212" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A212" s="89">
+    <row r="212" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A212" s="88">
         <v>48005</v>
       </c>
-      <c r="B212" s="89">
+      <c r="B212" s="88">
         <v>104800</v>
       </c>
-      <c r="C212" s="89" t="s">
+      <c r="C212" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="D212" s="89">
+      <c r="D212" s="88">
         <v>5</v>
       </c>
       <c r="E212" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="F212" s="35"/>
-      <c r="G212" s="37" t="s">
+      <c r="F212" s="25"/>
+      <c r="G212" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H212" s="28">
@@ -8740,24 +8163,24 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A213" s="89">
+    <row r="213" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A213" s="88">
         <v>48006</v>
       </c>
-      <c r="B213" s="89">
+      <c r="B213" s="88">
         <v>104800</v>
       </c>
-      <c r="C213" s="89" t="s">
+      <c r="C213" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="D213" s="89">
+      <c r="D213" s="88">
         <v>6</v>
       </c>
       <c r="E213" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F213" s="35"/>
-      <c r="G213" s="37" t="s">
+      <c r="F213" s="25"/>
+      <c r="G213" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H213" s="28">
@@ -8770,24 +8193,24 @@
         <v>33</v>
       </c>
     </row>
-    <row r="214" s="3" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A214" s="89">
+    <row r="214" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A214" s="88">
         <v>48007</v>
       </c>
-      <c r="B214" s="89">
+      <c r="B214" s="88">
         <v>104800</v>
       </c>
-      <c r="C214" s="89" t="s">
+      <c r="C214" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="D214" s="89">
+      <c r="D214" s="88">
         <v>7</v>
       </c>
       <c r="E214" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F214" s="35"/>
-      <c r="G214" s="37" t="s">
+      <c r="F214" s="25"/>
+      <c r="G214" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H214" s="28">
@@ -8800,24 +8223,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="215" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A215" s="81">
+    <row r="215" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A215" s="80">
         <v>50001</v>
       </c>
-      <c r="B215" s="81">
+      <c r="B215" s="80">
         <v>105000</v>
       </c>
-      <c r="C215" s="81" t="s">
+      <c r="C215" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="D215" s="81">
+      <c r="D215" s="80">
         <v>1</v>
       </c>
-      <c r="E215" s="82" t="s">
+      <c r="E215" s="81" t="s">
         <v>54</v>
       </c>
       <c r="F215" s="25"/>
-      <c r="G215" s="83" t="s">
+      <c r="G215" s="82" t="s">
         <v>55</v>
       </c>
       <c r="H215" s="28">
@@ -8826,28 +8249,28 @@
       <c r="I215" s="28">
         <v>999999</v>
       </c>
-      <c r="J215" s="84" t="s">
+      <c r="J215" s="83" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="216" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A216" s="81">
+    <row r="216" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A216" s="80">
         <v>50002</v>
       </c>
-      <c r="B216" s="81">
+      <c r="B216" s="80">
         <v>105000</v>
       </c>
-      <c r="C216" s="81" t="s">
+      <c r="C216" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="D216" s="81">
+      <c r="D216" s="80">
         <v>2</v>
       </c>
-      <c r="E216" s="82" t="s">
+      <c r="E216" s="81" t="s">
         <v>56</v>
       </c>
       <c r="F216" s="25"/>
-      <c r="G216" s="83" t="s">
+      <c r="G216" s="82" t="s">
         <v>55</v>
       </c>
       <c r="H216" s="28">
@@ -8856,28 +8279,28 @@
       <c r="I216" s="28">
         <v>8000</v>
       </c>
-      <c r="J216" s="84" t="s">
+      <c r="J216" s="83" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="217" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A217" s="81">
+    <row r="217" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A217" s="80">
         <v>50003</v>
       </c>
-      <c r="B217" s="81">
+      <c r="B217" s="80">
         <v>105000</v>
       </c>
-      <c r="C217" s="81" t="s">
+      <c r="C217" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="D217" s="81">
+      <c r="D217" s="80">
         <v>3</v>
       </c>
-      <c r="E217" s="82" t="s">
+      <c r="E217" s="81" t="s">
         <v>57</v>
       </c>
       <c r="F217" s="25"/>
-      <c r="G217" s="83" t="s">
+      <c r="G217" s="82" t="s">
         <v>55</v>
       </c>
       <c r="H217" s="28">
@@ -8886,28 +8309,28 @@
       <c r="I217" s="28">
         <v>6000</v>
       </c>
-      <c r="J217" s="84" t="s">
+      <c r="J217" s="83" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="218" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A218" s="81">
+    <row r="218" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A218" s="80">
         <v>50004</v>
       </c>
-      <c r="B218" s="81">
+      <c r="B218" s="80">
         <v>105000</v>
       </c>
-      <c r="C218" s="81" t="s">
+      <c r="C218" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="D218" s="81">
+      <c r="D218" s="80">
         <v>4</v>
       </c>
-      <c r="E218" s="82" t="s">
+      <c r="E218" s="81" t="s">
         <v>58</v>
       </c>
       <c r="F218" s="25"/>
-      <c r="G218" s="83" t="s">
+      <c r="G218" s="82" t="s">
         <v>55</v>
       </c>
       <c r="H218" s="28">
@@ -8916,28 +8339,28 @@
       <c r="I218" s="28">
         <v>4000</v>
       </c>
-      <c r="J218" s="84" t="s">
+      <c r="J218" s="83" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="219" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A219" s="81">
+    <row r="219" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A219" s="80">
         <v>50005</v>
       </c>
-      <c r="B219" s="81">
+      <c r="B219" s="80">
         <v>105000</v>
       </c>
-      <c r="C219" s="81" t="s">
+      <c r="C219" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="D219" s="81">
+      <c r="D219" s="80">
         <v>5</v>
       </c>
-      <c r="E219" s="82" t="s">
+      <c r="E219" s="81" t="s">
         <v>59</v>
       </c>
       <c r="F219" s="25"/>
-      <c r="G219" s="83" t="s">
+      <c r="G219" s="82" t="s">
         <v>55</v>
       </c>
       <c r="H219" s="28">
@@ -8946,28 +8369,28 @@
       <c r="I219" s="28">
         <v>2000</v>
       </c>
-      <c r="J219" s="84" t="s">
+      <c r="J219" s="83" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="220" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A220" s="81">
+    <row r="220" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A220" s="80">
         <v>50006</v>
       </c>
-      <c r="B220" s="81">
+      <c r="B220" s="80">
         <v>105000</v>
       </c>
-      <c r="C220" s="81" t="s">
+      <c r="C220" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="D220" s="81">
+      <c r="D220" s="80">
         <v>6</v>
       </c>
-      <c r="E220" s="82" t="s">
+      <c r="E220" s="81" t="s">
         <v>60</v>
       </c>
       <c r="F220" s="25"/>
-      <c r="G220" s="83" t="s">
+      <c r="G220" s="82" t="s">
         <v>55</v>
       </c>
       <c r="H220" s="28">
@@ -8976,28 +8399,28 @@
       <c r="I220" s="28">
         <v>0</v>
       </c>
-      <c r="J220" s="84" t="s">
+      <c r="J220" s="83" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="221" s="18" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A221" s="81">
+    <row r="221" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A221" s="80">
         <v>50007</v>
       </c>
-      <c r="B221" s="81">
+      <c r="B221" s="80">
         <v>105000</v>
       </c>
-      <c r="C221" s="81" t="s">
+      <c r="C221" s="80" t="s">
         <v>187</v>
       </c>
-      <c r="D221" s="81">
+      <c r="D221" s="80">
         <v>7</v>
       </c>
-      <c r="E221" s="82" t="s">
+      <c r="E221" s="81" t="s">
         <v>61</v>
       </c>
       <c r="F221" s="25"/>
-      <c r="G221" s="83" t="s">
+      <c r="G221" s="82" t="s">
         <v>55</v>
       </c>
       <c r="H221" s="28">
@@ -9006,28 +8429,28 @@
       <c r="I221" s="28">
         <v>-1000</v>
       </c>
-      <c r="J221" s="84" t="s">
+      <c r="J221" s="83" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="222" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A222" s="90">
+    <row r="222" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A222" s="89">
         <v>51001</v>
       </c>
-      <c r="B222" s="90">
+      <c r="B222" s="89">
         <v>105100</v>
       </c>
-      <c r="C222" s="90" t="s">
+      <c r="C222" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="D222" s="90">
+      <c r="D222" s="89">
         <v>1</v>
       </c>
-      <c r="E222" s="91" t="s">
+      <c r="E222" s="90" t="s">
         <v>54</v>
       </c>
       <c r="F222" s="25"/>
-      <c r="G222" s="92" t="s">
+      <c r="G222" s="91" t="s">
         <v>55</v>
       </c>
       <c r="H222" s="28">
@@ -9036,28 +8459,28 @@
       <c r="I222" s="28">
         <v>999999</v>
       </c>
-      <c r="J222" s="93" t="s">
+      <c r="J222" s="92" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="223" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A223" s="90">
+    <row r="223" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A223" s="89">
         <v>51002</v>
       </c>
-      <c r="B223" s="90">
+      <c r="B223" s="89">
         <v>105100</v>
       </c>
-      <c r="C223" s="90" t="s">
+      <c r="C223" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="D223" s="90">
+      <c r="D223" s="89">
         <v>2</v>
       </c>
-      <c r="E223" s="91" t="s">
+      <c r="E223" s="90" t="s">
         <v>56</v>
       </c>
       <c r="F223" s="25"/>
-      <c r="G223" s="92" t="s">
+      <c r="G223" s="91" t="s">
         <v>55</v>
       </c>
       <c r="H223" s="28">
@@ -9066,28 +8489,28 @@
       <c r="I223" s="28">
         <v>8000</v>
       </c>
-      <c r="J223" s="93" t="s">
+      <c r="J223" s="92" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="224" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A224" s="90">
+    <row r="224" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A224" s="89">
         <v>51003</v>
       </c>
-      <c r="B224" s="90">
+      <c r="B224" s="89">
         <v>105100</v>
       </c>
-      <c r="C224" s="90" t="s">
+      <c r="C224" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="D224" s="90">
+      <c r="D224" s="89">
         <v>3</v>
       </c>
-      <c r="E224" s="91" t="s">
+      <c r="E224" s="90" t="s">
         <v>57</v>
       </c>
       <c r="F224" s="25"/>
-      <c r="G224" s="92" t="s">
+      <c r="G224" s="91" t="s">
         <v>55</v>
       </c>
       <c r="H224" s="28">
@@ -9096,28 +8519,28 @@
       <c r="I224" s="28">
         <v>6000</v>
       </c>
-      <c r="J224" s="93" t="s">
+      <c r="J224" s="92" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="225" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A225" s="90">
+    <row r="225" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A225" s="89">
         <v>51004</v>
       </c>
-      <c r="B225" s="90">
+      <c r="B225" s="89">
         <v>105100</v>
       </c>
-      <c r="C225" s="90" t="s">
+      <c r="C225" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="D225" s="90">
+      <c r="D225" s="89">
         <v>4</v>
       </c>
-      <c r="E225" s="91" t="s">
+      <c r="E225" s="90" t="s">
         <v>58</v>
       </c>
       <c r="F225" s="25"/>
-      <c r="G225" s="92" t="s">
+      <c r="G225" s="91" t="s">
         <v>55</v>
       </c>
       <c r="H225" s="28">
@@ -9126,28 +8549,28 @@
       <c r="I225" s="28">
         <v>4000</v>
       </c>
-      <c r="J225" s="93" t="s">
+      <c r="J225" s="92" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="226" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A226" s="90">
+    <row r="226" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A226" s="89">
         <v>51005</v>
       </c>
-      <c r="B226" s="90">
+      <c r="B226" s="89">
         <v>105100</v>
       </c>
-      <c r="C226" s="90" t="s">
+      <c r="C226" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="D226" s="90">
+      <c r="D226" s="89">
         <v>5</v>
       </c>
-      <c r="E226" s="91" t="s">
+      <c r="E226" s="90" t="s">
         <v>59</v>
       </c>
       <c r="F226" s="25"/>
-      <c r="G226" s="92" t="s">
+      <c r="G226" s="91" t="s">
         <v>55</v>
       </c>
       <c r="H226" s="28">
@@ -9156,28 +8579,28 @@
       <c r="I226" s="28">
         <v>2000</v>
       </c>
-      <c r="J226" s="93" t="s">
+      <c r="J226" s="92" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="227" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A227" s="90">
+    <row r="227" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A227" s="89">
         <v>51006</v>
       </c>
-      <c r="B227" s="90">
+      <c r="B227" s="89">
         <v>105100</v>
       </c>
-      <c r="C227" s="90" t="s">
+      <c r="C227" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="D227" s="90">
+      <c r="D227" s="89">
         <v>6</v>
       </c>
-      <c r="E227" s="91" t="s">
+      <c r="E227" s="90" t="s">
         <v>60</v>
       </c>
       <c r="F227" s="25"/>
-      <c r="G227" s="92" t="s">
+      <c r="G227" s="91" t="s">
         <v>55</v>
       </c>
       <c r="H227" s="28">
@@ -9186,28 +8609,28 @@
       <c r="I227" s="28">
         <v>0</v>
       </c>
-      <c r="J227" s="93" t="s">
+      <c r="J227" s="92" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="228" s="20" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A228" s="90">
+    <row r="228" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A228" s="89">
         <v>51007</v>
       </c>
-      <c r="B228" s="90">
+      <c r="B228" s="89">
         <v>105100</v>
       </c>
-      <c r="C228" s="90" t="s">
+      <c r="C228" s="89" t="s">
         <v>188</v>
       </c>
-      <c r="D228" s="90">
+      <c r="D228" s="89">
         <v>7</v>
       </c>
-      <c r="E228" s="91" t="s">
+      <c r="E228" s="90" t="s">
         <v>61</v>
       </c>
       <c r="F228" s="25"/>
-      <c r="G228" s="92" t="s">
+      <c r="G228" s="91" t="s">
         <v>55</v>
       </c>
       <c r="H228" s="28">
@@ -9216,18 +8639,18 @@
       <c r="I228" s="28">
         <v>-1000</v>
       </c>
-      <c r="J228" s="93" t="s">
+      <c r="J228" s="92" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="229" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="229" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A229" s="8">
         <v>53001</v>
       </c>
-      <c r="B229" s="51">
+      <c r="B229" s="50">
         <v>105300</v>
       </c>
-      <c r="C229" s="51" t="s">
+      <c r="C229" s="50" t="s">
         <v>189</v>
       </c>
       <c r="D229" s="30">
@@ -9236,8 +8659,8 @@
       <c r="E229" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="F229" s="52"/>
-      <c r="G229" s="94" t="s">
+      <c r="F229" s="51"/>
+      <c r="G229" s="93" t="s">
         <v>191</v>
       </c>
       <c r="H229" s="30">
@@ -9250,14 +8673,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="230" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="230" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A230" s="8">
         <v>53002</v>
       </c>
-      <c r="B230" s="51">
+      <c r="B230" s="50">
         <v>105300</v>
       </c>
-      <c r="C230" s="51" t="s">
+      <c r="C230" s="50" t="s">
         <v>189</v>
       </c>
       <c r="D230" s="30">
@@ -9266,7 +8689,7 @@
       <c r="E230" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="F230" s="52"/>
+      <c r="F230" s="51"/>
       <c r="G230" s="31" t="s">
         <v>191</v>
       </c>
@@ -9280,14 +8703,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="231" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A231" s="8">
         <v>53003</v>
       </c>
-      <c r="B231" s="51">
+      <c r="B231" s="50">
         <v>105300</v>
       </c>
-      <c r="C231" s="51" t="s">
+      <c r="C231" s="50" t="s">
         <v>189</v>
       </c>
       <c r="D231" s="30">
@@ -9296,7 +8719,7 @@
       <c r="E231" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="F231" s="52"/>
+      <c r="F231" s="51"/>
       <c r="G231" s="31" t="s">
         <v>191</v>
       </c>
@@ -9310,14 +8733,14 @@
         <v>27</v>
       </c>
     </row>
-    <row r="232" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="232" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A232" s="8">
         <v>53004</v>
       </c>
-      <c r="B232" s="51">
+      <c r="B232" s="50">
         <v>105300</v>
       </c>
-      <c r="C232" s="51" t="s">
+      <c r="C232" s="50" t="s">
         <v>189</v>
       </c>
       <c r="D232" s="30">
@@ -9326,7 +8749,7 @@
       <c r="E232" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="F232" s="52"/>
+      <c r="F232" s="51"/>
       <c r="G232" s="31" t="s">
         <v>191</v>
       </c>
@@ -9340,14 +8763,14 @@
         <v>29</v>
       </c>
     </row>
-    <row r="233" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="233" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A233" s="8">
         <v>53005</v>
       </c>
-      <c r="B233" s="51">
+      <c r="B233" s="50">
         <v>105300</v>
       </c>
-      <c r="C233" s="51" t="s">
+      <c r="C233" s="50" t="s">
         <v>189</v>
       </c>
       <c r="D233" s="30">
@@ -9356,7 +8779,7 @@
       <c r="E233" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="F233" s="52"/>
+      <c r="F233" s="51"/>
       <c r="G233" s="31" t="s">
         <v>191</v>
       </c>
@@ -9370,14 +8793,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="234" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="234" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A234" s="8">
         <v>53006</v>
       </c>
-      <c r="B234" s="51">
+      <c r="B234" s="50">
         <v>105300</v>
       </c>
-      <c r="C234" s="51" t="s">
+      <c r="C234" s="50" t="s">
         <v>189</v>
       </c>
       <c r="D234" s="30">
@@ -9386,7 +8809,7 @@
       <c r="E234" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="F234" s="52"/>
+      <c r="F234" s="51"/>
       <c r="G234" s="31" t="s">
         <v>191</v>
       </c>
@@ -9400,14 +8823,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="235" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="235" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A235" s="8">
         <v>53007</v>
       </c>
-      <c r="B235" s="51">
+      <c r="B235" s="50">
         <v>105300</v>
       </c>
-      <c r="C235" s="51" t="s">
+      <c r="C235" s="50" t="s">
         <v>189</v>
       </c>
       <c r="D235" s="30">
@@ -9416,7 +8839,7 @@
       <c r="E235" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="F235" s="52"/>
+      <c r="F235" s="51"/>
       <c r="G235" s="31" t="s">
         <v>191</v>
       </c>
@@ -9430,24 +8853,23 @@
         <v>35</v>
       </c>
     </row>
-    <row r="236" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A236" s="89">
+    <row r="236" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A236" s="88">
         <v>54001</v>
       </c>
-      <c r="B236" s="89">
+      <c r="B236" s="88">
         <v>105400</v>
       </c>
-      <c r="C236" s="89" t="s">
+      <c r="C236" s="88" t="s">
         <v>198</v>
       </c>
-      <c r="D236" s="89">
+      <c r="D236" s="88">
         <v>1</v>
       </c>
       <c r="E236" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="F236" s="22"/>
-      <c r="G236" s="37" t="s">
+      <c r="G236" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H236" s="33">
@@ -9460,24 +8882,23 @@
         <v>23</v>
       </c>
     </row>
-    <row r="237" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A237" s="89">
+    <row r="237" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A237" s="88">
         <v>54002</v>
       </c>
-      <c r="B237" s="89">
+      <c r="B237" s="88">
         <v>105400</v>
       </c>
-      <c r="C237" s="89" t="s">
+      <c r="C237" s="88" t="s">
         <v>198</v>
       </c>
-      <c r="D237" s="89">
+      <c r="D237" s="88">
         <v>2</v>
       </c>
       <c r="E237" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F237" s="22"/>
-      <c r="G237" s="37" t="s">
+      <c r="G237" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H237" s="33">
@@ -9490,24 +8911,23 @@
         <v>25</v>
       </c>
     </row>
-    <row r="238" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A238" s="89">
+    <row r="238" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A238" s="88">
         <v>54003</v>
       </c>
-      <c r="B238" s="89">
+      <c r="B238" s="88">
         <v>105400</v>
       </c>
-      <c r="C238" s="89" t="s">
+      <c r="C238" s="88" t="s">
         <v>198</v>
       </c>
-      <c r="D238" s="89">
+      <c r="D238" s="88">
         <v>3</v>
       </c>
       <c r="E238" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F238" s="22"/>
-      <c r="G238" s="37" t="s">
+      <c r="G238" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H238" s="33">
@@ -9520,24 +8940,23 @@
         <v>27</v>
       </c>
     </row>
-    <row r="239" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A239" s="89">
+    <row r="239" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A239" s="88">
         <v>54004</v>
       </c>
-      <c r="B239" s="89">
+      <c r="B239" s="88">
         <v>105400</v>
       </c>
-      <c r="C239" s="89" t="s">
+      <c r="C239" s="88" t="s">
         <v>198</v>
       </c>
-      <c r="D239" s="89">
+      <c r="D239" s="88">
         <v>4</v>
       </c>
       <c r="E239" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="F239" s="22"/>
-      <c r="G239" s="37" t="s">
+      <c r="G239" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H239" s="33">
@@ -9550,24 +8969,23 @@
         <v>29</v>
       </c>
     </row>
-    <row r="240" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A240" s="89">
+    <row r="240" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A240" s="88">
         <v>54005</v>
       </c>
-      <c r="B240" s="89">
+      <c r="B240" s="88">
         <v>105400</v>
       </c>
-      <c r="C240" s="89" t="s">
+      <c r="C240" s="88" t="s">
         <v>198</v>
       </c>
-      <c r="D240" s="89">
+      <c r="D240" s="88">
         <v>5</v>
       </c>
       <c r="E240" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="F240" s="22"/>
-      <c r="G240" s="37" t="s">
+      <c r="G240" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H240" s="33">
@@ -9580,24 +8998,23 @@
         <v>31</v>
       </c>
     </row>
-    <row r="241" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A241" s="89">
+    <row r="241" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A241" s="88">
         <v>54006</v>
       </c>
-      <c r="B241" s="89">
+      <c r="B241" s="88">
         <v>105400</v>
       </c>
-      <c r="C241" s="89" t="s">
+      <c r="C241" s="88" t="s">
         <v>198</v>
       </c>
-      <c r="D241" s="89">
+      <c r="D241" s="88">
         <v>6</v>
       </c>
       <c r="E241" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="F241" s="22"/>
-      <c r="G241" s="37" t="s">
+      <c r="G241" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H241" s="33">
@@ -9610,24 +9027,23 @@
         <v>33</v>
       </c>
     </row>
-    <row r="242" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A242" s="89">
+    <row r="242" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A242" s="88">
         <v>54007</v>
       </c>
-      <c r="B242" s="89">
+      <c r="B242" s="88">
         <v>105400</v>
       </c>
-      <c r="C242" s="89" t="s">
+      <c r="C242" s="88" t="s">
         <v>198</v>
       </c>
-      <c r="D242" s="89">
+      <c r="D242" s="88">
         <v>7</v>
       </c>
       <c r="E242" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F242" s="22"/>
-      <c r="G242" s="37" t="s">
+      <c r="G242" s="36" t="s">
         <v>55</v>
       </c>
       <c r="H242" s="33">
@@ -9640,388 +9056,381 @@
         <v>35</v>
       </c>
     </row>
-    <row r="243" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A243" s="95">
+    <row r="243" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A243" s="94">
         <v>57001</v>
       </c>
-      <c r="B243" s="96">
+      <c r="B243" s="95">
         <v>105700</v>
       </c>
-      <c r="C243" s="96" t="s">
+      <c r="C243" s="95" t="s">
         <v>199</v>
       </c>
-      <c r="D243" s="97">
+      <c r="D243" s="96">
         <v>1</v>
       </c>
-      <c r="E243" s="98" t="s">
+      <c r="E243" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="F243" s="99"/>
-      <c r="G243" s="100" t="s">
+      <c r="F243" s="98"/>
+      <c r="G243" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="H243" s="93">
+      <c r="H243" s="92">
         <v>2000</v>
       </c>
-      <c r="I243" s="93">
+      <c r="I243" s="92">
         <v>999999</v>
       </c>
-      <c r="J243" s="100" t="s">
+      <c r="J243" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="K243" s="101"/>
-    </row>
-    <row r="244" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A244" s="95">
+    </row>
+    <row r="244" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A244" s="94">
         <v>57002</v>
       </c>
-      <c r="B244" s="96">
+      <c r="B244" s="95">
         <v>105700</v>
       </c>
-      <c r="C244" s="96" t="s">
+      <c r="C244" s="95" t="s">
         <v>199</v>
       </c>
-      <c r="D244" s="97">
+      <c r="D244" s="96">
         <v>2</v>
       </c>
-      <c r="E244" s="98" t="s">
+      <c r="E244" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="F244" s="99"/>
-      <c r="G244" s="100" t="s">
+      <c r="F244" s="98"/>
+      <c r="G244" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="H244" s="93">
+      <c r="H244" s="92">
         <v>1000</v>
       </c>
-      <c r="I244" s="93">
+      <c r="I244" s="92">
         <v>2000</v>
       </c>
-      <c r="J244" s="100" t="s">
+      <c r="J244" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="K244" s="101"/>
-    </row>
-    <row r="245" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A245" s="95">
+    </row>
+    <row r="245" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A245" s="94">
         <v>57003</v>
       </c>
-      <c r="B245" s="96">
+      <c r="B245" s="95">
         <v>105700</v>
       </c>
-      <c r="C245" s="96" t="s">
+      <c r="C245" s="95" t="s">
         <v>199</v>
       </c>
-      <c r="D245" s="97">
+      <c r="D245" s="96">
         <v>3</v>
       </c>
-      <c r="E245" s="98" t="s">
+      <c r="E245" s="97" t="s">
         <v>57</v>
       </c>
-      <c r="F245" s="99"/>
-      <c r="G245" s="100" t="s">
+      <c r="F245" s="98"/>
+      <c r="G245" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="H245" s="93">
+      <c r="H245" s="92">
         <v>500</v>
       </c>
-      <c r="I245" s="93">
+      <c r="I245" s="92">
         <v>1000</v>
       </c>
-      <c r="J245" s="100" t="s">
+      <c r="J245" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="K245" s="101"/>
-    </row>
-    <row r="246" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A246" s="95">
+    </row>
+    <row r="246" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A246" s="94">
         <v>57004</v>
       </c>
-      <c r="B246" s="96">
+      <c r="B246" s="95">
         <v>105700</v>
       </c>
-      <c r="C246" s="96" t="s">
+      <c r="C246" s="95" t="s">
         <v>199</v>
       </c>
-      <c r="D246" s="97">
+      <c r="D246" s="96">
         <v>4</v>
       </c>
-      <c r="E246" s="98" t="s">
+      <c r="E246" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="F246" s="99"/>
-      <c r="G246" s="100" t="s">
+      <c r="F246" s="98"/>
+      <c r="G246" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="H246" s="93">
+      <c r="H246" s="92">
         <v>-500</v>
       </c>
-      <c r="I246" s="93">
+      <c r="I246" s="92">
         <v>500</v>
       </c>
-      <c r="J246" s="100" t="s">
+      <c r="J246" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="K246" s="101"/>
-    </row>
-    <row r="247" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A247" s="95">
+    </row>
+    <row r="247" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A247" s="94">
         <v>57005</v>
       </c>
-      <c r="B247" s="96">
+      <c r="B247" s="95">
         <v>105700</v>
       </c>
-      <c r="C247" s="96" t="s">
+      <c r="C247" s="95" t="s">
         <v>199</v>
       </c>
-      <c r="D247" s="97">
+      <c r="D247" s="96">
         <v>5</v>
       </c>
-      <c r="E247" s="98" t="s">
+      <c r="E247" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="F247" s="99"/>
-      <c r="G247" s="100" t="s">
+      <c r="F247" s="98"/>
+      <c r="G247" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="H247" s="93">
+      <c r="H247" s="92">
         <v>-1000</v>
       </c>
-      <c r="I247" s="93">
+      <c r="I247" s="92">
         <v>-500</v>
       </c>
-      <c r="J247" s="100" t="s">
+      <c r="J247" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="K247" s="101"/>
-    </row>
-    <row r="248" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A248" s="95">
+    </row>
+    <row r="248" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A248" s="94">
         <v>57006</v>
       </c>
-      <c r="B248" s="96">
+      <c r="B248" s="95">
         <v>105700</v>
       </c>
-      <c r="C248" s="96" t="s">
+      <c r="C248" s="95" t="s">
         <v>199</v>
       </c>
-      <c r="D248" s="97">
+      <c r="D248" s="96">
         <v>6</v>
       </c>
-      <c r="E248" s="98" t="s">
+      <c r="E248" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="F248" s="99"/>
-      <c r="G248" s="100" t="s">
+      <c r="F248" s="98"/>
+      <c r="G248" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="H248" s="93">
+      <c r="H248" s="92">
         <v>-2000</v>
       </c>
-      <c r="I248" s="93">
+      <c r="I248" s="92">
         <v>-1000</v>
       </c>
-      <c r="J248" s="100" t="s">
+      <c r="J248" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="K248" s="101"/>
-    </row>
-    <row r="249" s="21" customFormat="1" ht="16.5" spans="1:11">
-      <c r="A249" s="95">
+    </row>
+    <row r="249" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A249" s="94">
         <v>57007</v>
       </c>
-      <c r="B249" s="96">
+      <c r="B249" s="95">
         <v>105700</v>
       </c>
-      <c r="C249" s="96" t="s">
+      <c r="C249" s="95" t="s">
         <v>199</v>
       </c>
-      <c r="D249" s="97">
+      <c r="D249" s="96">
         <v>7</v>
       </c>
-      <c r="E249" s="98" t="s">
+      <c r="E249" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="F249" s="99"/>
-      <c r="G249" s="100" t="s">
+      <c r="F249" s="98"/>
+      <c r="G249" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="H249" s="93">
+      <c r="H249" s="92">
         <v>-999999</v>
       </c>
-      <c r="I249" s="93">
+      <c r="I249" s="92">
         <v>-2000</v>
       </c>
-      <c r="J249" s="100" t="s">
+      <c r="J249" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="K249" s="101"/>
-    </row>
-    <row r="250" s="21" customFormat="1" ht="16.5" spans="1:11">
+    </row>
+    <row r="250" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A250" s="21">
         <v>58001</v>
       </c>
-      <c r="B250" s="102">
+      <c r="B250" s="100">
         <v>105800</v>
       </c>
-      <c r="C250" s="102" t="s">
+      <c r="C250" s="100" t="s">
         <v>200</v>
       </c>
-      <c r="D250" s="102">
+      <c r="D250" s="100">
         <v>1</v>
       </c>
-      <c r="E250" s="35" t="s">
+      <c r="E250" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="F250" s="99"/>
+      <c r="F250" s="98"/>
       <c r="G250" s="27" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="251" s="21" customFormat="1" ht="16.5" spans="1:11">
+    <row r="251" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A251" s="21">
         <v>58002</v>
       </c>
-      <c r="B251" s="102">
+      <c r="B251" s="100">
         <v>105800</v>
       </c>
-      <c r="C251" s="102" t="s">
+      <c r="C251" s="100" t="s">
         <v>200</v>
       </c>
-      <c r="D251" s="102">
+      <c r="D251" s="100">
         <v>2</v>
       </c>
-      <c r="E251" s="35" t="s">
+      <c r="E251" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="F251" s="99"/>
+      <c r="F251" s="98"/>
       <c r="G251" s="25" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="252" s="21" customFormat="1" ht="16.5" spans="1:11">
+    <row r="252" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A252" s="21">
         <v>58003</v>
       </c>
-      <c r="B252" s="102">
+      <c r="B252" s="100">
         <v>105800</v>
       </c>
-      <c r="C252" s="102" t="s">
+      <c r="C252" s="100" t="s">
         <v>200</v>
       </c>
-      <c r="D252" s="102">
+      <c r="D252" s="100">
         <v>3</v>
       </c>
-      <c r="E252" s="35" t="s">
+      <c r="E252" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="F252" s="99"/>
+      <c r="F252" s="98"/>
       <c r="G252" s="25" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="253" s="21" customFormat="1" ht="16.5" spans="1:11">
+    <row r="253" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A253" s="21">
         <v>58004</v>
       </c>
-      <c r="B253" s="102">
+      <c r="B253" s="100">
         <v>105800</v>
       </c>
-      <c r="C253" s="102" t="s">
+      <c r="C253" s="100" t="s">
         <v>200</v>
       </c>
-      <c r="D253" s="102">
+      <c r="D253" s="100">
         <v>4</v>
       </c>
-      <c r="E253" s="35" t="s">
+      <c r="E253" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="F253" s="99"/>
+      <c r="F253" s="98"/>
       <c r="G253" s="25" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="254" s="21" customFormat="1" ht="16.5" spans="1:11">
+    <row r="254" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A254" s="21">
         <v>58005</v>
       </c>
-      <c r="B254" s="102">
+      <c r="B254" s="100">
         <v>105800</v>
       </c>
-      <c r="C254" s="102" t="s">
+      <c r="C254" s="100" t="s">
         <v>200</v>
       </c>
-      <c r="D254" s="102">
+      <c r="D254" s="100">
         <v>5</v>
       </c>
-      <c r="E254" s="35" t="s">
+      <c r="E254" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="F254" s="99"/>
+      <c r="F254" s="98"/>
       <c r="G254" s="25" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="255" s="21" customFormat="1" ht="16.5" spans="1:11">
+    <row r="255" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A255" s="21">
         <v>58006</v>
       </c>
-      <c r="B255" s="102">
+      <c r="B255" s="100">
         <v>105800</v>
       </c>
-      <c r="C255" s="102" t="s">
+      <c r="C255" s="100" t="s">
         <v>200</v>
       </c>
-      <c r="D255" s="102">
+      <c r="D255" s="100">
         <v>6</v>
       </c>
-      <c r="E255" s="35" t="s">
+      <c r="E255" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="F255" s="99"/>
+      <c r="F255" s="98"/>
       <c r="G255" s="25" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="256" s="21" customFormat="1" ht="16.5" spans="1:11">
+    <row r="256" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A256" s="21">
         <v>58007</v>
       </c>
-      <c r="B256" s="102">
+      <c r="B256" s="100">
         <v>105800</v>
       </c>
-      <c r="C256" s="102" t="s">
+      <c r="C256" s="100" t="s">
         <v>200</v>
       </c>
-      <c r="D256" s="102">
+      <c r="D256" s="100">
         <v>7</v>
       </c>
-      <c r="E256" s="35" t="s">
+      <c r="E256" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="F256" s="99"/>
+      <c r="F256" s="98"/>
       <c r="G256" s="25" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="257" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A257" s="103">
+    <row r="257" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A257" s="101">
         <v>55001</v>
       </c>
-      <c r="B257" s="104">
+      <c r="B257" s="102">
         <v>105500</v>
       </c>
-      <c r="C257" s="104" t="s">
+      <c r="C257" s="102" t="s">
         <v>201</v>
       </c>
-      <c r="D257" s="69">
+      <c r="D257" s="68">
         <v>1</v>
       </c>
-      <c r="E257" s="70" t="s">
+      <c r="E257" s="69" t="s">
         <v>202</v>
       </c>
-      <c r="F257" s="99"/>
-      <c r="G257" s="83" t="s">
+      <c r="F257" s="98"/>
+      <c r="G257" s="82" t="s">
         <v>203</v>
       </c>
       <c r="H257" s="28">
@@ -10030,29 +9439,29 @@
       <c r="I257" s="28">
         <v>999999</v>
       </c>
-      <c r="J257" s="105" t="s">
+      <c r="J257" s="103" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="258" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A258" s="103">
+    <row r="258" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A258" s="101">
         <v>55002</v>
       </c>
-      <c r="B258" s="104">
+      <c r="B258" s="102">
         <v>105500</v>
       </c>
-      <c r="C258" s="104" t="s">
+      <c r="C258" s="102" t="s">
         <v>201</v>
       </c>
-      <c r="D258" s="69">
+      <c r="D258" s="68">
         <v>2</v>
       </c>
-      <c r="E258" s="70" t="s">
+      <c r="E258" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="F258" s="99"/>
-      <c r="G258" s="83" t="str">
-        <f>G257</f>
+      <c r="F258" s="98"/>
+      <c r="G258" s="82" t="str">
+        <f t="shared" ref="G258:G263" si="28">G257</f>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
       <c r="H258" s="28">
@@ -10061,29 +9470,29 @@
       <c r="I258" s="28">
         <v>8000</v>
       </c>
-      <c r="J258" s="105" t="s">
+      <c r="J258" s="103" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="259" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A259" s="103">
+    <row r="259" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A259" s="101">
         <v>55003</v>
       </c>
-      <c r="B259" s="104">
+      <c r="B259" s="102">
         <v>105500</v>
       </c>
-      <c r="C259" s="104" t="s">
+      <c r="C259" s="102" t="s">
         <v>201</v>
       </c>
-      <c r="D259" s="69">
+      <c r="D259" s="68">
         <v>3</v>
       </c>
-      <c r="E259" s="70" t="s">
+      <c r="E259" s="69" t="s">
         <v>205</v>
       </c>
-      <c r="F259" s="99"/>
-      <c r="G259" s="83" t="str">
-        <f>G258</f>
+      <c r="F259" s="98"/>
+      <c r="G259" s="82" t="str">
+        <f t="shared" si="28"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
       <c r="H259" s="28">
@@ -10092,29 +9501,29 @@
       <c r="I259" s="28">
         <v>6000</v>
       </c>
-      <c r="J259" s="105" t="s">
+      <c r="J259" s="103" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="260" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A260" s="103">
+    <row r="260" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A260" s="101">
         <v>55004</v>
       </c>
-      <c r="B260" s="104">
+      <c r="B260" s="102">
         <v>105500</v>
       </c>
-      <c r="C260" s="104" t="s">
+      <c r="C260" s="102" t="s">
         <v>201</v>
       </c>
-      <c r="D260" s="69">
+      <c r="D260" s="68">
         <v>4</v>
       </c>
-      <c r="E260" s="70" t="s">
+      <c r="E260" s="69" t="s">
         <v>206</v>
       </c>
-      <c r="F260" s="99"/>
-      <c r="G260" s="83" t="str">
-        <f>G259</f>
+      <c r="F260" s="98"/>
+      <c r="G260" s="82" t="str">
+        <f t="shared" si="28"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
       <c r="H260" s="28">
@@ -10123,29 +9532,29 @@
       <c r="I260" s="28">
         <v>4000</v>
       </c>
-      <c r="J260" s="105" t="s">
+      <c r="J260" s="103" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="261" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A261" s="103">
+    <row r="261" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A261" s="101">
         <v>55005</v>
       </c>
-      <c r="B261" s="104">
+      <c r="B261" s="102">
         <v>105500</v>
       </c>
-      <c r="C261" s="104" t="s">
+      <c r="C261" s="102" t="s">
         <v>201</v>
       </c>
-      <c r="D261" s="69">
+      <c r="D261" s="68">
         <v>5</v>
       </c>
-      <c r="E261" s="70" t="s">
+      <c r="E261" s="69" t="s">
         <v>207</v>
       </c>
-      <c r="F261" s="99"/>
-      <c r="G261" s="83" t="str">
-        <f>G260</f>
+      <c r="F261" s="98"/>
+      <c r="G261" s="82" t="str">
+        <f t="shared" si="28"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
       <c r="H261" s="28">
@@ -10154,29 +9563,29 @@
       <c r="I261" s="28">
         <v>2000</v>
       </c>
-      <c r="J261" s="105" t="s">
+      <c r="J261" s="103" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="262" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A262" s="103">
+    <row r="262" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A262" s="101">
         <v>55006</v>
       </c>
-      <c r="B262" s="104">
+      <c r="B262" s="102">
         <v>105500</v>
       </c>
-      <c r="C262" s="104" t="s">
+      <c r="C262" s="102" t="s">
         <v>201</v>
       </c>
-      <c r="D262" s="69">
+      <c r="D262" s="68">
         <v>6</v>
       </c>
-      <c r="E262" s="70" t="s">
+      <c r="E262" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="F262" s="99"/>
-      <c r="G262" s="83" t="str">
-        <f>G261</f>
+      <c r="F262" s="98"/>
+      <c r="G262" s="82" t="str">
+        <f t="shared" si="28"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
       <c r="H262" s="28">
@@ -10185,29 +9594,29 @@
       <c r="I262" s="28">
         <v>0</v>
       </c>
-      <c r="J262" s="105" t="s">
+      <c r="J262" s="103" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="263" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A263" s="103">
+    <row r="263" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A263" s="101">
         <v>55007</v>
       </c>
-      <c r="B263" s="104">
+      <c r="B263" s="102">
         <v>105500</v>
       </c>
-      <c r="C263" s="104" t="s">
+      <c r="C263" s="102" t="s">
         <v>201</v>
       </c>
-      <c r="D263" s="69">
+      <c r="D263" s="68">
         <v>7</v>
       </c>
-      <c r="E263" s="70" t="s">
+      <c r="E263" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="F263" s="99"/>
-      <c r="G263" s="83" t="str">
-        <f>G262</f>
+      <c r="F263" s="98"/>
+      <c r="G263" s="82" t="str">
+        <f t="shared" si="28"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
       <c r="H263" s="28">
@@ -10216,28 +9625,28 @@
       <c r="I263" s="28">
         <v>-1000</v>
       </c>
-      <c r="J263" s="105" t="s">
+      <c r="J263" s="103" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="264" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A264" s="103">
+    <row r="264" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A264" s="101">
         <v>55011</v>
       </c>
-      <c r="B264" s="104">
+      <c r="B264" s="102">
         <v>105501</v>
       </c>
-      <c r="C264" s="104" t="s">
+      <c r="C264" s="102" t="s">
         <v>208</v>
       </c>
-      <c r="D264" s="69">
+      <c r="D264" s="68">
         <v>1</v>
       </c>
-      <c r="E264" s="98" t="s">
+      <c r="E264" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="F264" s="99"/>
-      <c r="G264" s="83" t="s">
+      <c r="F264" s="98"/>
+      <c r="G264" s="82" t="s">
         <v>203</v>
       </c>
       <c r="H264" s="28">
@@ -10246,28 +9655,28 @@
       <c r="I264" s="28">
         <v>999999</v>
       </c>
-      <c r="J264" s="105" t="s">
+      <c r="J264" s="103" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="265" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A265" s="103">
+    <row r="265" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A265" s="101">
         <v>55012</v>
       </c>
-      <c r="B265" s="104">
+      <c r="B265" s="102">
         <v>105501</v>
       </c>
-      <c r="C265" s="104" t="s">
+      <c r="C265" s="102" t="s">
         <v>208</v>
       </c>
-      <c r="D265" s="69">
+      <c r="D265" s="68">
         <v>2</v>
       </c>
-      <c r="E265" s="98" t="s">
+      <c r="E265" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="F265" s="99"/>
-      <c r="G265" s="83" t="s">
+      <c r="F265" s="98"/>
+      <c r="G265" s="82" t="s">
         <v>161</v>
       </c>
       <c r="H265" s="28">
@@ -10276,28 +9685,28 @@
       <c r="I265" s="28">
         <v>8000</v>
       </c>
-      <c r="J265" s="105" t="s">
+      <c r="J265" s="103" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="266" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A266" s="103">
+    <row r="266" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A266" s="101">
         <v>55013</v>
       </c>
-      <c r="B266" s="104">
+      <c r="B266" s="102">
         <v>105501</v>
       </c>
-      <c r="C266" s="104" t="s">
+      <c r="C266" s="102" t="s">
         <v>208</v>
       </c>
-      <c r="D266" s="69">
+      <c r="D266" s="68">
         <v>3</v>
       </c>
-      <c r="E266" s="98" t="s">
+      <c r="E266" s="97" t="s">
         <v>57</v>
       </c>
-      <c r="F266" s="99"/>
-      <c r="G266" s="83" t="s">
+      <c r="F266" s="98"/>
+      <c r="G266" s="82" t="s">
         <v>161</v>
       </c>
       <c r="H266" s="28">
@@ -10306,28 +9715,28 @@
       <c r="I266" s="28">
         <v>6000</v>
       </c>
-      <c r="J266" s="105" t="s">
+      <c r="J266" s="103" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="267" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A267" s="103">
+    <row r="267" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A267" s="101">
         <v>55014</v>
       </c>
-      <c r="B267" s="104">
+      <c r="B267" s="102">
         <v>105501</v>
       </c>
-      <c r="C267" s="104" t="s">
+      <c r="C267" s="102" t="s">
         <v>208</v>
       </c>
-      <c r="D267" s="69">
+      <c r="D267" s="68">
         <v>4</v>
       </c>
-      <c r="E267" s="98" t="s">
+      <c r="E267" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="F267" s="99"/>
-      <c r="G267" s="83" t="s">
+      <c r="F267" s="98"/>
+      <c r="G267" s="82" t="s">
         <v>161</v>
       </c>
       <c r="H267" s="28">
@@ -10336,28 +9745,28 @@
       <c r="I267" s="28">
         <v>4000</v>
       </c>
-      <c r="J267" s="105" t="s">
+      <c r="J267" s="103" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="268" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A268" s="103">
+    <row r="268" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A268" s="101">
         <v>55015</v>
       </c>
-      <c r="B268" s="104">
+      <c r="B268" s="102">
         <v>105501</v>
       </c>
-      <c r="C268" s="104" t="s">
+      <c r="C268" s="102" t="s">
         <v>208</v>
       </c>
-      <c r="D268" s="69">
+      <c r="D268" s="68">
         <v>5</v>
       </c>
-      <c r="E268" s="98" t="s">
+      <c r="E268" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="F268" s="99"/>
-      <c r="G268" s="83" t="s">
+      <c r="F268" s="98"/>
+      <c r="G268" s="82" t="s">
         <v>161</v>
       </c>
       <c r="H268" s="28">
@@ -10366,28 +9775,28 @@
       <c r="I268" s="28">
         <v>2000</v>
       </c>
-      <c r="J268" s="105" t="s">
+      <c r="J268" s="103" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="269" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A269" s="103">
+    <row r="269" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A269" s="101">
         <v>55016</v>
       </c>
-      <c r="B269" s="104">
+      <c r="B269" s="102">
         <v>105501</v>
       </c>
-      <c r="C269" s="104" t="s">
+      <c r="C269" s="102" t="s">
         <v>208</v>
       </c>
-      <c r="D269" s="69">
+      <c r="D269" s="68">
         <v>6</v>
       </c>
-      <c r="E269" s="98" t="s">
+      <c r="E269" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="F269" s="99"/>
-      <c r="G269" s="83" t="s">
+      <c r="F269" s="98"/>
+      <c r="G269" s="82" t="s">
         <v>161</v>
       </c>
       <c r="H269" s="28">
@@ -10396,28 +9805,28 @@
       <c r="I269" s="28">
         <v>0</v>
       </c>
-      <c r="J269" s="105" t="s">
+      <c r="J269" s="103" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="270" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A270" s="103">
+    <row r="270" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A270" s="101">
         <v>55017</v>
       </c>
-      <c r="B270" s="104">
+      <c r="B270" s="102">
         <v>105501</v>
       </c>
-      <c r="C270" s="104" t="s">
+      <c r="C270" s="102" t="s">
         <v>208</v>
       </c>
-      <c r="D270" s="69">
+      <c r="D270" s="68">
         <v>7</v>
       </c>
-      <c r="E270" s="98" t="s">
+      <c r="E270" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="F270" s="99"/>
-      <c r="G270" s="83" t="s">
+      <c r="F270" s="98"/>
+      <c r="G270" s="82" t="s">
         <v>161</v>
       </c>
       <c r="H270" s="28">
@@ -10426,13 +9835,13 @@
       <c r="I270" s="28">
         <v>-1000</v>
       </c>
-      <c r="J270" s="105" t="s">
+      <c r="J270" s="103" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3789B584A9A1EE387DABE1B383A9EAD968E4F336" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -33,13 +27,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -63,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -89,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="G1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -101,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -114,7 +108,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -127,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -147,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="F12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -177,7 +171,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="211">
   <si>
     <t>id</t>
   </si>
@@ -744,6 +738,12 @@
   </si>
   <si>
     <t>糖果派对</t>
+  </si>
+  <si>
+    <t>1_9850|2_140|3_10|4_9850|5_140|6_10|7_9850|8_140|9_10</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
   </si>
   <si>
     <t>麻将胡了2</t>
@@ -809,8 +809,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -831,10 +837,147 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -848,14 +991,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="21">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -864,25 +1001,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -900,13 +1037,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -918,7 +1055,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -930,13 +1067,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -966,18 +1103,108 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -985,10 +1212,252 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1019,7 +1488,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1256,18 +1725,62 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1525,14 +2038,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J270"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="3" width="15.25" customWidth="1"/>
@@ -1545,7 +2058,7 @@
     <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1575,7 +2088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
@@ -1603,7 +2116,7 @@
       </c>
       <c r="J2" s="23"/>
     </row>
-    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="23" t="s">
         <v>0</v>
       </c>
@@ -1631,7 +2144,7 @@
       </c>
       <c r="J3" s="23"/>
     </row>
-    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -1643,7 +2156,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="23">
         <v>1001</v>
       </c>
@@ -1673,7 +2186,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="23">
         <v>1002</v>
       </c>
@@ -1704,7 +2217,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="23">
         <v>1003</v>
       </c>
@@ -1735,7 +2248,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="23">
         <v>1004</v>
       </c>
@@ -1766,7 +2279,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="23">
         <v>1005</v>
       </c>
@@ -1797,7 +2310,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="23">
         <v>1006</v>
       </c>
@@ -1828,7 +2341,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="23">
         <v>1007</v>
       </c>
@@ -1859,7 +2372,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A12" s="29">
         <v>3001</v>
       </c>
@@ -1889,7 +2402,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="29">
         <v>3002</v>
       </c>
@@ -1920,7 +2433,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="29">
         <v>3003</v>
       </c>
@@ -1951,7 +2464,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A15" s="29">
         <v>3004</v>
       </c>
@@ -1982,7 +2495,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A16" s="29">
         <v>3005</v>
       </c>
@@ -2013,7 +2526,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A17" s="29">
         <v>3006</v>
       </c>
@@ -2044,7 +2557,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A18" s="29">
         <v>3007</v>
       </c>
@@ -2075,7 +2588,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A19" s="23">
         <v>7001</v>
       </c>
@@ -2107,7 +2620,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A20" s="23">
         <v>7002</v>
       </c>
@@ -2140,7 +2653,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A21" s="23">
         <v>7003</v>
       </c>
@@ -2173,7 +2686,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A22" s="23">
         <v>7004</v>
       </c>
@@ -2206,7 +2719,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A23" s="23">
         <v>7005</v>
       </c>
@@ -2239,7 +2752,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A24" s="23">
         <v>7006</v>
       </c>
@@ -2272,7 +2785,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A25" s="23">
         <v>7007</v>
       </c>
@@ -2305,7 +2818,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A26" s="33">
         <v>8001</v>
       </c>
@@ -2335,7 +2848,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A27" s="33">
         <v>8002</v>
       </c>
@@ -2365,7 +2878,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A28" s="33">
         <v>8003</v>
       </c>
@@ -2395,7 +2908,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A29" s="33">
         <v>8004</v>
       </c>
@@ -2425,7 +2938,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A30" s="33">
         <v>8005</v>
       </c>
@@ -2455,7 +2968,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A31" s="33">
         <v>8006</v>
       </c>
@@ -2485,7 +2998,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A32" s="33">
         <v>8007</v>
       </c>
@@ -2515,7 +3028,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A33" s="29">
         <v>12001</v>
       </c>
@@ -2547,7 +3060,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="34" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A34" s="29">
         <v>12002</v>
       </c>
@@ -2580,7 +3093,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="35" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A35" s="29">
         <v>12003</v>
       </c>
@@ -2613,7 +3126,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A36" s="29">
         <v>12004</v>
       </c>
@@ -2646,7 +3159,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A37" s="29">
         <v>12005</v>
       </c>
@@ -2679,7 +3192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="38" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A38" s="29">
         <v>12006</v>
       </c>
@@ -2712,7 +3225,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A39" s="29">
         <v>12007</v>
       </c>
@@ -2745,7 +3258,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="40" s="4" customFormat="1" ht="16.5" spans="1:10">
       <c r="A40" s="23">
         <v>14001</v>
       </c>
@@ -2775,7 +3288,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:10">
       <c r="A41" s="23">
         <v>14002</v>
       </c>
@@ -2806,7 +3319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:10">
       <c r="A42" s="23">
         <v>14003</v>
       </c>
@@ -2837,7 +3350,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:10">
       <c r="A43" s="23">
         <v>14004</v>
       </c>
@@ -2868,7 +3381,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="44" s="4" customFormat="1" ht="16.5" spans="1:10">
       <c r="A44" s="23">
         <v>14005</v>
       </c>
@@ -2899,7 +3412,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="45" s="4" customFormat="1" ht="16.5" spans="1:10">
       <c r="A45" s="23">
         <v>14006</v>
       </c>
@@ -2930,7 +3443,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="46" s="4" customFormat="1" ht="16.5" spans="1:10">
       <c r="A46" s="23">
         <v>14007</v>
       </c>
@@ -2961,7 +3474,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="47" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A47" s="39">
         <v>15001</v>
       </c>
@@ -2991,7 +3504,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="48" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A48" s="39">
         <v>15002</v>
       </c>
@@ -3022,7 +3535,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="49" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A49" s="39">
         <v>15003</v>
       </c>
@@ -3053,7 +3566,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="50" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A50" s="39">
         <v>15004</v>
       </c>
@@ -3084,7 +3597,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A51" s="39">
         <v>15005</v>
       </c>
@@ -3115,7 +3628,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A52" s="39">
         <v>15006</v>
       </c>
@@ -3146,7 +3659,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A53" s="39">
         <v>15007</v>
       </c>
@@ -3177,7 +3690,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A54" s="43">
         <v>16001</v>
       </c>
@@ -3207,7 +3720,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="55" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A55" s="43">
         <v>16002</v>
       </c>
@@ -3238,7 +3751,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="56" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A56" s="43">
         <v>16003</v>
       </c>
@@ -3269,7 +3782,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="57" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A57" s="43">
         <v>16004</v>
       </c>
@@ -3300,7 +3813,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="58" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A58" s="43">
         <v>16005</v>
       </c>
@@ -3331,7 +3844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="59" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A59" s="43">
         <v>16006</v>
       </c>
@@ -3362,7 +3875,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="60" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A60" s="43">
         <v>16007</v>
       </c>
@@ -3393,7 +3906,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="61" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A61" s="23">
         <v>17001</v>
       </c>
@@ -3425,7 +3938,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="62" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A62" s="23">
         <v>17002</v>
       </c>
@@ -3458,7 +3971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="63" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A63" s="23">
         <v>17003</v>
       </c>
@@ -3491,7 +4004,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="64" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A64" s="23">
         <v>17004</v>
       </c>
@@ -3524,7 +4037,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="65" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A65" s="23">
         <v>17005</v>
       </c>
@@ -3557,7 +4070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="66" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A66" s="23">
         <v>17006</v>
       </c>
@@ -3590,7 +4103,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="67" s="2" customFormat="1" ht="16.5" spans="1:10">
       <c r="A67" s="23">
         <v>17007</v>
       </c>
@@ -3623,7 +4136,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="68" s="7" customFormat="1" ht="16.5" spans="1:10">
       <c r="A68" s="47">
         <v>18001</v>
       </c>
@@ -3655,7 +4168,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:10">
       <c r="A69" s="47">
         <v>18002</v>
       </c>
@@ -3688,7 +4201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="70" s="7" customFormat="1" ht="16.5" spans="1:10">
       <c r="A70" s="47">
         <v>18003</v>
       </c>
@@ -3721,7 +4234,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="71" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="71" s="7" customFormat="1" ht="16.5" spans="1:10">
       <c r="A71" s="47">
         <v>18004</v>
       </c>
@@ -3754,7 +4267,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="72" s="7" customFormat="1" ht="16.5" spans="1:10">
       <c r="A72" s="47">
         <v>18005</v>
       </c>
@@ -3787,7 +4300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="73" s="7" customFormat="1" ht="16.5" spans="1:10">
       <c r="A73" s="47">
         <v>18006</v>
       </c>
@@ -3820,7 +4333,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="74" s="7" customFormat="1" ht="16.5" spans="1:10">
       <c r="A74" s="47">
         <v>18007</v>
       </c>
@@ -3853,7 +4366,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="75" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A75" s="39">
         <v>20001</v>
       </c>
@@ -3883,7 +4396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="76" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A76" s="39">
         <v>20002</v>
       </c>
@@ -3914,7 +4427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="77" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A77" s="39">
         <v>20003</v>
       </c>
@@ -3945,7 +4458,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="78" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="78" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A78" s="39">
         <v>20004</v>
       </c>
@@ -3976,7 +4489,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="79" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="79" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A79" s="39">
         <v>20005</v>
       </c>
@@ -4007,7 +4520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="80" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A80" s="39">
         <v>20006</v>
       </c>
@@ -4038,7 +4551,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="81" s="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A81" s="39">
         <v>20007</v>
       </c>
@@ -4069,7 +4582,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="82" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A82" s="50">
         <v>21001</v>
       </c>
@@ -4101,7 +4614,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="83" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A83" s="50">
         <v>21002</v>
       </c>
@@ -4134,7 +4647,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="84" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A84" s="50">
         <v>21003</v>
       </c>
@@ -4167,7 +4680,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="85" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A85" s="50">
         <v>21004</v>
       </c>
@@ -4200,7 +4713,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="86" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A86" s="50">
         <v>21005</v>
       </c>
@@ -4233,7 +4746,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="87" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A87" s="50">
         <v>21006</v>
       </c>
@@ -4266,7 +4779,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="88" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A88" s="50">
         <v>21007</v>
       </c>
@@ -4299,7 +4812,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="89" s="9" customFormat="1" ht="16.5" spans="1:10">
       <c r="A89" s="52">
         <v>22001</v>
       </c>
@@ -4331,7 +4844,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="90" s="9" customFormat="1" ht="16.5" spans="1:10">
       <c r="A90" s="52">
         <v>22002</v>
       </c>
@@ -4364,7 +4877,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="91" s="9" customFormat="1" ht="16.5" spans="1:10">
       <c r="A91" s="52">
         <v>22003</v>
       </c>
@@ -4397,7 +4910,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="92" s="9" customFormat="1" ht="16.5" spans="1:10">
       <c r="A92" s="52">
         <v>22004</v>
       </c>
@@ -4430,7 +4943,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="93" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="93" s="9" customFormat="1" ht="16.5" spans="1:10">
       <c r="A93" s="52">
         <v>22005</v>
       </c>
@@ -4463,7 +4976,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="94" s="9" customFormat="1" ht="16.5" spans="1:10">
       <c r="A94" s="52">
         <v>22006</v>
       </c>
@@ -4496,7 +5009,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="95" s="9" customFormat="1" ht="16.5" spans="1:10">
       <c r="A95" s="52">
         <v>22007</v>
       </c>
@@ -4529,7 +5042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="96" s="10" customFormat="1" ht="16.5" spans="1:10">
       <c r="A96" s="55">
         <v>23001</v>
       </c>
@@ -4561,7 +5074,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="97" s="10" customFormat="1" ht="16.5" spans="1:10">
       <c r="A97" s="55">
         <v>23002</v>
       </c>
@@ -4594,7 +5107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="98" s="10" customFormat="1" ht="16.5" spans="1:10">
       <c r="A98" s="55">
         <v>23003</v>
       </c>
@@ -4627,7 +5140,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="99" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="99" s="10" customFormat="1" ht="16.5" spans="1:10">
       <c r="A99" s="55">
         <v>23004</v>
       </c>
@@ -4660,7 +5173,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="100" s="10" customFormat="1" ht="16.5" spans="1:10">
       <c r="A100" s="55">
         <v>23005</v>
       </c>
@@ -4693,7 +5206,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="101" s="10" customFormat="1" ht="16.5" spans="1:10">
       <c r="A101" s="55">
         <v>23006</v>
       </c>
@@ -4726,7 +5239,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="102" s="10" customFormat="1" ht="16.5" spans="1:10">
       <c r="A102" s="55">
         <v>23007</v>
       </c>
@@ -4759,7 +5272,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="103" ht="16.5" spans="1:10">
       <c r="A103" s="23">
         <v>24001</v>
       </c>
@@ -4789,7 +5302,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="104" ht="16.5" spans="1:10">
       <c r="A104" s="23">
         <v>24002</v>
       </c>
@@ -4820,7 +5333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="105" ht="16.5" spans="1:10">
       <c r="A105" s="23">
         <v>24003</v>
       </c>
@@ -4851,7 +5364,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="106" ht="16.5" spans="1:10">
       <c r="A106" s="23">
         <v>24004</v>
       </c>
@@ -4882,7 +5395,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="107" ht="16.5" spans="1:10">
       <c r="A107" s="23">
         <v>24005</v>
       </c>
@@ -4913,7 +5426,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="108" ht="16.5" spans="1:10">
       <c r="A108" s="23">
         <v>24006</v>
       </c>
@@ -4944,7 +5457,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="109" ht="16.5" spans="1:10">
       <c r="A109" s="23">
         <v>24007</v>
       </c>
@@ -4975,7 +5488,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="110" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A110" s="58">
         <v>25001</v>
       </c>
@@ -5007,7 +5520,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="111" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A111" s="58">
         <v>25002</v>
       </c>
@@ -5040,7 +5553,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="112" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A112" s="58">
         <v>25003</v>
       </c>
@@ -5073,7 +5586,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="113" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="113" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A113" s="58">
         <v>25004</v>
       </c>
@@ -5106,7 +5619,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="114" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A114" s="58">
         <v>25005</v>
       </c>
@@ -5139,7 +5652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="115" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A115" s="58">
         <v>25006</v>
       </c>
@@ -5172,7 +5685,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="116" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="116" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A116" s="58">
         <v>25007</v>
       </c>
@@ -5205,7 +5718,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="117" s="12" customFormat="1" ht="16.5" spans="1:10">
       <c r="A117" s="61">
         <v>26001</v>
       </c>
@@ -5235,7 +5748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="118" s="12" customFormat="1" ht="16.5" spans="1:10">
       <c r="A118" s="61">
         <v>26002</v>
       </c>
@@ -5266,7 +5779,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="119" s="12" customFormat="1" ht="16.5" spans="1:10">
       <c r="A119" s="61">
         <v>26003</v>
       </c>
@@ -5297,7 +5810,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="120" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="120" s="12" customFormat="1" ht="16.5" spans="1:10">
       <c r="A120" s="61">
         <v>26004</v>
       </c>
@@ -5328,7 +5841,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="121" s="12" customFormat="1" ht="16.5" spans="1:10">
       <c r="A121" s="61">
         <v>26005</v>
       </c>
@@ -5359,7 +5872,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="122" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="122" s="12" customFormat="1" ht="16.5" spans="1:10">
       <c r="A122" s="61">
         <v>26006</v>
       </c>
@@ -5390,7 +5903,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="123" s="12" customFormat="1" ht="16.5" spans="1:10">
       <c r="A123" s="61">
         <v>26007</v>
       </c>
@@ -5421,7 +5934,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="124" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A124" s="58">
         <v>27001</v>
       </c>
@@ -5451,7 +5964,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="125" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="125" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A125" s="58">
         <v>27002</v>
       </c>
@@ -5482,7 +5995,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="126" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A126" s="58">
         <v>27003</v>
       </c>
@@ -5513,7 +6026,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="127" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="127" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A127" s="58">
         <v>27004</v>
       </c>
@@ -5544,7 +6057,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="128" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A128" s="58">
         <v>27005</v>
       </c>
@@ -5575,7 +6088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="129" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A129" s="58">
         <v>27006</v>
       </c>
@@ -5606,7 +6119,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="130" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="130" s="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A130" s="58">
         <v>27007</v>
       </c>
@@ -5637,7 +6150,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="131" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A131" s="43">
         <v>28001</v>
       </c>
@@ -5667,7 +6180,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="132" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A132" s="43">
         <v>28002</v>
       </c>
@@ -5698,7 +6211,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="133" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A133" s="43">
         <v>28003</v>
       </c>
@@ -5729,7 +6242,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="134" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="134" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A134" s="43">
         <v>28004</v>
       </c>
@@ -5760,7 +6273,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="135" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A135" s="43">
         <v>28005</v>
       </c>
@@ -5791,7 +6304,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="136" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A136" s="43">
         <v>28006</v>
       </c>
@@ -5822,7 +6335,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="137" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="137" s="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A137" s="43">
         <v>28007</v>
       </c>
@@ -5853,7 +6366,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="138" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="138" s="13" customFormat="1" ht="16.5" spans="1:10">
       <c r="A138" s="64">
         <v>31001</v>
       </c>
@@ -5883,7 +6396,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="139" s="13" customFormat="1" ht="16.5" spans="1:10">
       <c r="A139" s="64">
         <v>31002</v>
       </c>
@@ -5914,7 +6427,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="140" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="140" s="13" customFormat="1" ht="16.5" spans="1:10">
       <c r="A140" s="64">
         <v>31003</v>
       </c>
@@ -5945,7 +6458,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="141" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="141" s="13" customFormat="1" ht="16.5" spans="1:10">
       <c r="A141" s="64">
         <v>31004</v>
       </c>
@@ -5976,7 +6489,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="142" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="142" s="13" customFormat="1" ht="16.5" spans="1:10">
       <c r="A142" s="64">
         <v>31005</v>
       </c>
@@ -6007,7 +6520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="143" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="143" s="13" customFormat="1" ht="16.5" spans="1:10">
       <c r="A143" s="64">
         <v>31006</v>
       </c>
@@ -6038,7 +6551,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="144" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="144" s="13" customFormat="1" ht="16.5" spans="1:10">
       <c r="A144" s="64">
         <v>31007</v>
       </c>
@@ -6069,7 +6582,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="145" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="145" s="14" customFormat="1" ht="16.5" spans="1:10">
       <c r="A145" s="68">
         <v>34001</v>
       </c>
@@ -6099,7 +6612,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="146" s="14" customFormat="1" ht="16.5" spans="1:10">
       <c r="A146" s="68">
         <v>34002</v>
       </c>
@@ -6130,7 +6643,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="147" s="14" customFormat="1" ht="16.5" spans="1:10">
       <c r="A147" s="68">
         <v>34003</v>
       </c>
@@ -6161,7 +6674,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="148" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="148" s="14" customFormat="1" ht="16.5" spans="1:10">
       <c r="A148" s="68">
         <v>34004</v>
       </c>
@@ -6192,7 +6705,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="149" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="149" s="14" customFormat="1" ht="16.5" spans="1:10">
       <c r="A149" s="68">
         <v>34005</v>
       </c>
@@ -6223,7 +6736,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="150" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="150" s="14" customFormat="1" ht="16.5" spans="1:10">
       <c r="A150" s="68">
         <v>34006</v>
       </c>
@@ -6254,7 +6767,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="151" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="151" s="14" customFormat="1" ht="16.5" spans="1:10">
       <c r="A151" s="68">
         <v>34007</v>
       </c>
@@ -6285,7 +6798,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="152" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="152" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A152" s="71">
         <v>34011</v>
       </c>
@@ -6315,7 +6828,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="153" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="153" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A153" s="71">
         <v>34012</v>
       </c>
@@ -6346,7 +6859,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="154" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A154" s="71">
         <v>34013</v>
       </c>
@@ -6377,7 +6890,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="155" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="155" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A155" s="71">
         <v>34014</v>
       </c>
@@ -6408,7 +6921,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="156" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="156" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A156" s="71">
         <v>34015</v>
       </c>
@@ -6439,7 +6952,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="157" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A157" s="71">
         <v>34016</v>
       </c>
@@ -6470,7 +6983,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="158" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="158" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A158" s="71">
         <v>34017</v>
       </c>
@@ -6501,7 +7014,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="159" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="159" s="16" customFormat="1" ht="16.5" spans="1:10">
       <c r="A159" s="75">
         <v>35001</v>
       </c>
@@ -6531,7 +7044,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="160" s="16" customFormat="1" ht="16.5" spans="1:10">
       <c r="A160" s="75">
         <v>35002</v>
       </c>
@@ -6562,7 +7075,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="161" s="16" customFormat="1" ht="16.5" spans="1:10">
       <c r="A161" s="75">
         <v>35003</v>
       </c>
@@ -6593,7 +7106,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="162" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="162" s="16" customFormat="1" ht="16.5" spans="1:10">
       <c r="A162" s="75">
         <v>35004</v>
       </c>
@@ -6624,7 +7137,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="163" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="163" s="16" customFormat="1" ht="16.5" spans="1:10">
       <c r="A163" s="75">
         <v>35005</v>
       </c>
@@ -6655,7 +7168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="164" s="16" customFormat="1" ht="16.5" spans="1:10">
       <c r="A164" s="75">
         <v>35006</v>
       </c>
@@ -6686,7 +7199,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="165" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="165" s="16" customFormat="1" ht="16.5" spans="1:10">
       <c r="A165" s="75">
         <v>35007</v>
       </c>
@@ -6717,7 +7230,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="166" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="166" s="17" customFormat="1" ht="16.5" spans="1:10">
       <c r="A166" s="78">
         <v>35011</v>
       </c>
@@ -6747,7 +7260,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="167" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="167" s="17" customFormat="1" ht="16.5" spans="1:10">
       <c r="A167" s="78">
         <v>35012</v>
       </c>
@@ -6778,7 +7291,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="168" s="17" customFormat="1" ht="16.5" spans="1:10">
       <c r="A168" s="78">
         <v>35013</v>
       </c>
@@ -6809,7 +7322,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="169" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="169" s="17" customFormat="1" ht="16.5" spans="1:10">
       <c r="A169" s="78">
         <v>35014</v>
       </c>
@@ -6840,7 +7353,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="170" s="17" customFormat="1" ht="16.5" spans="1:10">
       <c r="A170" s="78">
         <v>35015</v>
       </c>
@@ -6871,7 +7384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="171" s="17" customFormat="1" ht="16.5" spans="1:10">
       <c r="A171" s="78">
         <v>35016</v>
       </c>
@@ -6902,7 +7415,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="172" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="172" s="17" customFormat="1" ht="16.5" spans="1:10">
       <c r="A172" s="78">
         <v>35017</v>
       </c>
@@ -6933,7 +7446,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="173" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A173" s="80">
         <v>36001</v>
       </c>
@@ -6963,7 +7476,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="174" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A174" s="80">
         <v>36002</v>
       </c>
@@ -6994,7 +7507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="175" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A175" s="80">
         <v>36003</v>
       </c>
@@ -7025,7 +7538,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="176" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="176" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A176" s="80">
         <v>36004</v>
       </c>
@@ -7056,7 +7569,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="177" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A177" s="80">
         <v>36005</v>
       </c>
@@ -7087,7 +7600,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="178" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A178" s="80">
         <v>36006</v>
       </c>
@@ -7118,7 +7631,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="179" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="179" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A179" s="80">
         <v>36007</v>
       </c>
@@ -7149,7 +7662,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="180" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="180" s="19" customFormat="1" ht="16.5" spans="1:10">
       <c r="A180" s="84">
         <v>38001</v>
       </c>
@@ -7179,7 +7692,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="181" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="181" s="19" customFormat="1" ht="16.5" spans="1:10">
       <c r="A181" s="84">
         <v>38002</v>
       </c>
@@ -7210,7 +7723,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="182" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="182" s="19" customFormat="1" ht="16.5" spans="1:10">
       <c r="A182" s="84">
         <v>38003</v>
       </c>
@@ -7241,7 +7754,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="183" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="183" s="19" customFormat="1" ht="16.5" spans="1:10">
       <c r="A183" s="84">
         <v>38004</v>
       </c>
@@ -7272,7 +7785,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="184" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="184" s="19" customFormat="1" ht="16.5" spans="1:10">
       <c r="A184" s="84">
         <v>38005</v>
       </c>
@@ -7303,7 +7816,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="185" s="19" customFormat="1" ht="16.5" spans="1:10">
       <c r="A185" s="84">
         <v>38006</v>
       </c>
@@ -7334,7 +7847,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="186" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="186" s="19" customFormat="1" ht="16.5" spans="1:10">
       <c r="A186" s="84">
         <v>38007</v>
       </c>
@@ -7365,7 +7878,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="187" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="187" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A187" s="80">
         <v>37001</v>
       </c>
@@ -7395,7 +7908,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="188" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A188" s="80">
         <v>37002</v>
       </c>
@@ -7426,7 +7939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="189" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="189" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A189" s="80">
         <v>37003</v>
       </c>
@@ -7457,7 +7970,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="190" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="190" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A190" s="80">
         <v>37004</v>
       </c>
@@ -7488,7 +8001,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="191" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="191" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A191" s="80">
         <v>37005</v>
       </c>
@@ -7519,7 +8032,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="192" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="192" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A192" s="80">
         <v>37006</v>
       </c>
@@ -7550,7 +8063,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="193" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="193" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A193" s="80">
         <v>37007</v>
       </c>
@@ -7581,7 +8094,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="194" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="194" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A194" s="88">
         <v>39001</v>
       </c>
@@ -7611,7 +8124,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="195" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A195" s="88">
         <v>39002</v>
       </c>
@@ -7642,7 +8155,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="196" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A196" s="88">
         <v>39003</v>
       </c>
@@ -7673,7 +8186,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="197" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="197" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A197" s="88">
         <v>39004</v>
       </c>
@@ -7704,7 +8217,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="198" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="198" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A198" s="88">
         <v>39005</v>
       </c>
@@ -7735,7 +8248,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="199" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="199" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A199" s="88">
         <v>39006</v>
       </c>
@@ -7766,7 +8279,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="200" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="200" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A200" s="88">
         <v>39007</v>
       </c>
@@ -7797,7 +8310,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="201" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="201" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A201" s="71">
         <v>40001</v>
       </c>
@@ -7827,7 +8340,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="202" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="202" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A202" s="71">
         <v>40002</v>
       </c>
@@ -7858,7 +8371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="203" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="203" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A203" s="71">
         <v>40003</v>
       </c>
@@ -7889,7 +8402,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="204" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="204" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A204" s="71">
         <v>40004</v>
       </c>
@@ -7920,7 +8433,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="205" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="205" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A205" s="71">
         <v>40005</v>
       </c>
@@ -7951,7 +8464,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="206" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="206" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A206" s="71">
         <v>40006</v>
       </c>
@@ -7982,7 +8495,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="207" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="207" s="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A207" s="71">
         <v>40007</v>
       </c>
@@ -8013,7 +8526,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="208" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="208" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A208" s="88">
         <v>48001</v>
       </c>
@@ -8043,7 +8556,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="209" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A209" s="88">
         <v>48002</v>
       </c>
@@ -8073,7 +8586,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="210" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A210" s="88">
         <v>48003</v>
       </c>
@@ -8103,7 +8616,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="211" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="211" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A211" s="88">
         <v>48004</v>
       </c>
@@ -8133,7 +8646,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="212" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="212" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A212" s="88">
         <v>48005</v>
       </c>
@@ -8163,7 +8676,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="213" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A213" s="88">
         <v>48006</v>
       </c>
@@ -8193,7 +8706,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="214" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="214" s="3" customFormat="1" ht="16.5" spans="1:10">
       <c r="A214" s="88">
         <v>48007</v>
       </c>
@@ -8223,7 +8736,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="215" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="215" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A215" s="80">
         <v>50001</v>
       </c>
@@ -8253,7 +8766,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="216" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A216" s="80">
         <v>50002</v>
       </c>
@@ -8283,7 +8796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="217" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="217" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A217" s="80">
         <v>50003</v>
       </c>
@@ -8313,7 +8826,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="218" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="218" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A218" s="80">
         <v>50004</v>
       </c>
@@ -8343,7 +8856,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="219" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="219" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A219" s="80">
         <v>50005</v>
       </c>
@@ -8373,7 +8886,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="220" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="220" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A220" s="80">
         <v>50006</v>
       </c>
@@ -8403,7 +8916,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="221" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="221" s="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A221" s="80">
         <v>50007</v>
       </c>
@@ -8433,7 +8946,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="222" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="222" s="20" customFormat="1" ht="16.5" spans="1:10">
       <c r="A222" s="89">
         <v>51001</v>
       </c>
@@ -8447,11 +8960,11 @@
         <v>1</v>
       </c>
       <c r="E222" s="90" t="s">
-        <v>54</v>
+        <v>189</v>
       </c>
       <c r="F222" s="25"/>
       <c r="G222" s="91" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="H222" s="28">
         <v>8000</v>
@@ -8463,7 +8976,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="223" s="20" customFormat="1" ht="16.5" spans="1:10">
       <c r="A223" s="89">
         <v>51002</v>
       </c>
@@ -8477,11 +8990,11 @@
         <v>2</v>
       </c>
       <c r="E223" s="90" t="s">
-        <v>56</v>
+        <v>189</v>
       </c>
       <c r="F223" s="25"/>
       <c r="G223" s="91" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="H223" s="28">
         <v>6000</v>
@@ -8493,7 +9006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="224" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="224" s="20" customFormat="1" ht="16.5" spans="1:10">
       <c r="A224" s="89">
         <v>51003</v>
       </c>
@@ -8507,11 +9020,11 @@
         <v>3</v>
       </c>
       <c r="E224" s="90" t="s">
-        <v>57</v>
+        <v>189</v>
       </c>
       <c r="F224" s="25"/>
       <c r="G224" s="91" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="H224" s="28">
         <v>4000</v>
@@ -8523,7 +9036,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="225" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="225" s="20" customFormat="1" ht="16.5" spans="1:10">
       <c r="A225" s="89">
         <v>51004</v>
       </c>
@@ -8537,11 +9050,11 @@
         <v>4</v>
       </c>
       <c r="E225" s="90" t="s">
-        <v>58</v>
+        <v>189</v>
       </c>
       <c r="F225" s="25"/>
       <c r="G225" s="91" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="H225" s="28">
         <v>2000</v>
@@ -8553,7 +9066,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="226" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="226" s="20" customFormat="1" ht="16.5" spans="1:10">
       <c r="A226" s="89">
         <v>51005</v>
       </c>
@@ -8567,11 +9080,11 @@
         <v>5</v>
       </c>
       <c r="E226" s="90" t="s">
-        <v>59</v>
+        <v>189</v>
       </c>
       <c r="F226" s="25"/>
       <c r="G226" s="91" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="H226" s="28">
         <v>0</v>
@@ -8583,7 +9096,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="227" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="227" s="20" customFormat="1" ht="16.5" spans="1:10">
       <c r="A227" s="89">
         <v>51006</v>
       </c>
@@ -8597,11 +9110,11 @@
         <v>6</v>
       </c>
       <c r="E227" s="90" t="s">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="F227" s="25"/>
       <c r="G227" s="91" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="H227" s="28">
         <v>-1000</v>
@@ -8613,7 +9126,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="228" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="228" s="20" customFormat="1" ht="16.5" spans="1:10">
       <c r="A228" s="89">
         <v>51007</v>
       </c>
@@ -8627,11 +9140,11 @@
         <v>7</v>
       </c>
       <c r="E228" s="90" t="s">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="F228" s="25"/>
       <c r="G228" s="91" t="s">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="H228" s="28">
         <v>-999999</v>
@@ -8643,7 +9156,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="229" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="229" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A229" s="8">
         <v>53001</v>
       </c>
@@ -8651,17 +9164,17 @@
         <v>105300</v>
       </c>
       <c r="C229" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D229" s="30">
         <v>1</v>
       </c>
       <c r="E229" s="31" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F229" s="51"/>
       <c r="G229" s="93" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H229" s="30">
         <v>2000</v>
@@ -8673,7 +9186,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="230" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="230" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A230" s="8">
         <v>53002</v>
       </c>
@@ -8681,17 +9194,17 @@
         <v>105300</v>
       </c>
       <c r="C230" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D230" s="30">
         <v>2</v>
       </c>
       <c r="E230" s="31" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F230" s="51"/>
       <c r="G230" s="31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H230" s="30">
         <v>1000</v>
@@ -8703,7 +9216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="231" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A231" s="8">
         <v>53003</v>
       </c>
@@ -8711,17 +9224,17 @@
         <v>105300</v>
       </c>
       <c r="C231" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D231" s="30">
         <v>3</v>
       </c>
       <c r="E231" s="31" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F231" s="51"/>
       <c r="G231" s="31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H231" s="30">
         <v>500</v>
@@ -8733,7 +9246,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="232" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="232" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A232" s="8">
         <v>53004</v>
       </c>
@@ -8741,17 +9254,17 @@
         <v>105300</v>
       </c>
       <c r="C232" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D232" s="30">
         <v>4</v>
       </c>
       <c r="E232" s="31" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F232" s="51"/>
       <c r="G232" s="31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H232" s="30">
         <v>-500</v>
@@ -8763,7 +9276,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="233" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="233" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A233" s="8">
         <v>53005</v>
       </c>
@@ -8771,17 +9284,17 @@
         <v>105300</v>
       </c>
       <c r="C233" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D233" s="30">
         <v>5</v>
       </c>
       <c r="E233" s="31" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F233" s="51"/>
       <c r="G233" s="31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H233" s="30">
         <v>-1000</v>
@@ -8793,7 +9306,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="234" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="234" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A234" s="8">
         <v>53006</v>
       </c>
@@ -8801,17 +9314,17 @@
         <v>105300</v>
       </c>
       <c r="C234" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D234" s="30">
         <v>6</v>
       </c>
       <c r="E234" s="31" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F234" s="51"/>
       <c r="G234" s="31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H234" s="30">
         <v>-2000</v>
@@ -8823,7 +9336,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="235" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="235" s="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A235" s="8">
         <v>53007</v>
       </c>
@@ -8831,17 +9344,17 @@
         <v>105300</v>
       </c>
       <c r="C235" s="50" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D235" s="30">
         <v>7</v>
       </c>
       <c r="E235" s="31" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F235" s="51"/>
       <c r="G235" s="31" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H235" s="30">
         <v>-999999</v>
@@ -8853,7 +9366,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="236" ht="16.5" spans="1:10">
       <c r="A236" s="88">
         <v>54001</v>
       </c>
@@ -8861,7 +9374,7 @@
         <v>105400</v>
       </c>
       <c r="C236" s="88" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D236" s="88">
         <v>1</v>
@@ -8882,7 +9395,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="237" ht="16.5" spans="1:10">
       <c r="A237" s="88">
         <v>54002</v>
       </c>
@@ -8890,7 +9403,7 @@
         <v>105400</v>
       </c>
       <c r="C237" s="88" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D237" s="88">
         <v>2</v>
@@ -8911,7 +9424,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="238" ht="16.5" spans="1:10">
       <c r="A238" s="88">
         <v>54003</v>
       </c>
@@ -8919,7 +9432,7 @@
         <v>105400</v>
       </c>
       <c r="C238" s="88" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D238" s="88">
         <v>3</v>
@@ -8940,7 +9453,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="239" ht="16.5" spans="1:10">
       <c r="A239" s="88">
         <v>54004</v>
       </c>
@@ -8948,7 +9461,7 @@
         <v>105400</v>
       </c>
       <c r="C239" s="88" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D239" s="88">
         <v>4</v>
@@ -8969,7 +9482,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="240" ht="16.5" spans="1:10">
       <c r="A240" s="88">
         <v>54005</v>
       </c>
@@ -8977,7 +9490,7 @@
         <v>105400</v>
       </c>
       <c r="C240" s="88" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D240" s="88">
         <v>5</v>
@@ -8998,7 +9511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="241" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="241" ht="16.5" spans="1:10">
       <c r="A241" s="88">
         <v>54006</v>
       </c>
@@ -9006,7 +9519,7 @@
         <v>105400</v>
       </c>
       <c r="C241" s="88" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D241" s="88">
         <v>6</v>
@@ -9027,7 +9540,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="242" ht="16.5" spans="1:10">
       <c r="A242" s="88">
         <v>54007</v>
       </c>
@@ -9035,7 +9548,7 @@
         <v>105400</v>
       </c>
       <c r="C242" s="88" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D242" s="88">
         <v>7</v>
@@ -9056,7 +9569,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="243" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="243" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A243" s="94">
         <v>57001</v>
       </c>
@@ -9064,7 +9577,7 @@
         <v>105700</v>
       </c>
       <c r="C243" s="95" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D243" s="96">
         <v>1</v>
@@ -9086,7 +9599,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="244" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="244" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A244" s="94">
         <v>57002</v>
       </c>
@@ -9094,7 +9607,7 @@
         <v>105700</v>
       </c>
       <c r="C244" s="95" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D244" s="96">
         <v>2</v>
@@ -9116,7 +9629,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="245" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A245" s="94">
         <v>57003</v>
       </c>
@@ -9124,7 +9637,7 @@
         <v>105700</v>
       </c>
       <c r="C245" s="95" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D245" s="96">
         <v>3</v>
@@ -9146,7 +9659,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="246" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="246" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A246" s="94">
         <v>57004</v>
       </c>
@@ -9154,7 +9667,7 @@
         <v>105700</v>
       </c>
       <c r="C246" s="95" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D246" s="96">
         <v>4</v>
@@ -9176,7 +9689,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="247" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="247" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A247" s="94">
         <v>57005</v>
       </c>
@@ -9184,7 +9697,7 @@
         <v>105700</v>
       </c>
       <c r="C247" s="95" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D247" s="96">
         <v>5</v>
@@ -9206,7 +9719,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="248" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A248" s="94">
         <v>57006</v>
       </c>
@@ -9214,7 +9727,7 @@
         <v>105700</v>
       </c>
       <c r="C248" s="95" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D248" s="96">
         <v>6</v>
@@ -9236,7 +9749,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="249" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="249" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A249" s="94">
         <v>57007</v>
       </c>
@@ -9244,7 +9757,7 @@
         <v>105700</v>
       </c>
       <c r="C249" s="95" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D249" s="96">
         <v>7</v>
@@ -9266,7 +9779,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="250" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="250" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A250" s="21">
         <v>58001</v>
       </c>
@@ -9274,20 +9787,20 @@
         <v>105800</v>
       </c>
       <c r="C250" s="100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D250" s="100">
         <v>1</v>
       </c>
       <c r="E250" s="25" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F250" s="98"/>
       <c r="G250" s="27" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="251" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="251" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A251" s="21">
         <v>58002</v>
       </c>
@@ -9295,20 +9808,20 @@
         <v>105800</v>
       </c>
       <c r="C251" s="100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D251" s="100">
         <v>2</v>
       </c>
       <c r="E251" s="25" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F251" s="98"/>
       <c r="G251" s="25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="252" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="252" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A252" s="21">
         <v>58003</v>
       </c>
@@ -9316,20 +9829,20 @@
         <v>105800</v>
       </c>
       <c r="C252" s="100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D252" s="100">
         <v>3</v>
       </c>
       <c r="E252" s="25" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F252" s="98"/>
       <c r="G252" s="25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="253" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="253" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A253" s="21">
         <v>58004</v>
       </c>
@@ -9337,20 +9850,20 @@
         <v>105800</v>
       </c>
       <c r="C253" s="100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D253" s="100">
         <v>4</v>
       </c>
       <c r="E253" s="25" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F253" s="98"/>
       <c r="G253" s="25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="254" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="254" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A254" s="21">
         <v>58005</v>
       </c>
@@ -9358,20 +9871,20 @@
         <v>105800</v>
       </c>
       <c r="C254" s="100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D254" s="100">
         <v>5</v>
       </c>
       <c r="E254" s="25" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F254" s="98"/>
       <c r="G254" s="25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="255" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="255" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A255" s="21">
         <v>58006</v>
       </c>
@@ -9379,20 +9892,20 @@
         <v>105800</v>
       </c>
       <c r="C255" s="100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D255" s="100">
         <v>6</v>
       </c>
       <c r="E255" s="25" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F255" s="98"/>
       <c r="G255" s="25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="256" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="256" s="21" customFormat="1" ht="16.5" spans="1:10">
       <c r="A256" s="21">
         <v>58007</v>
       </c>
@@ -9400,20 +9913,20 @@
         <v>105800</v>
       </c>
       <c r="C256" s="100" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D256" s="100">
         <v>7</v>
       </c>
       <c r="E256" s="25" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F256" s="98"/>
       <c r="G256" s="25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="257" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="257" ht="16.5" spans="1:10">
       <c r="A257" s="101">
         <v>55001</v>
       </c>
@@ -9421,17 +9934,17 @@
         <v>105500</v>
       </c>
       <c r="C257" s="102" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D257" s="68">
         <v>1</v>
       </c>
       <c r="E257" s="69" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F257" s="98"/>
       <c r="G257" s="82" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H257" s="28">
         <v>8000</v>
@@ -9443,7 +9956,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="258" ht="16.5" spans="1:10">
       <c r="A258" s="101">
         <v>55002</v>
       </c>
@@ -9451,13 +9964,13 @@
         <v>105500</v>
       </c>
       <c r="C258" s="102" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D258" s="68">
         <v>2</v>
       </c>
       <c r="E258" s="69" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F258" s="98"/>
       <c r="G258" s="82" t="str">
@@ -9474,7 +9987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="259" ht="16.5" spans="1:10">
       <c r="A259" s="101">
         <v>55003</v>
       </c>
@@ -9482,13 +9995,13 @@
         <v>105500</v>
       </c>
       <c r="C259" s="102" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D259" s="68">
         <v>3</v>
       </c>
       <c r="E259" s="69" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F259" s="98"/>
       <c r="G259" s="82" t="str">
@@ -9505,7 +10018,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="260" ht="16.5" spans="1:10">
       <c r="A260" s="101">
         <v>55004</v>
       </c>
@@ -9513,13 +10026,13 @@
         <v>105500</v>
       </c>
       <c r="C260" s="102" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D260" s="68">
         <v>4</v>
       </c>
       <c r="E260" s="69" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F260" s="98"/>
       <c r="G260" s="82" t="str">
@@ -9536,7 +10049,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="261" ht="16.5" spans="1:10">
       <c r="A261" s="101">
         <v>55005</v>
       </c>
@@ -9544,13 +10057,13 @@
         <v>105500</v>
       </c>
       <c r="C261" s="102" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D261" s="68">
         <v>5</v>
       </c>
       <c r="E261" s="69" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F261" s="98"/>
       <c r="G261" s="82" t="str">
@@ -9567,7 +10080,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="262" ht="16.5" spans="1:10">
       <c r="A262" s="101">
         <v>55006</v>
       </c>
@@ -9575,7 +10088,7 @@
         <v>105500</v>
       </c>
       <c r="C262" s="102" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D262" s="68">
         <v>6</v>
@@ -9598,7 +10111,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="263" ht="16.5" spans="1:10">
       <c r="A263" s="101">
         <v>55007</v>
       </c>
@@ -9606,7 +10119,7 @@
         <v>105500</v>
       </c>
       <c r="C263" s="102" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D263" s="68">
         <v>7</v>
@@ -9629,7 +10142,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="264" ht="16.5" spans="1:10">
       <c r="A264" s="101">
         <v>55011</v>
       </c>
@@ -9637,7 +10150,7 @@
         <v>105501</v>
       </c>
       <c r="C264" s="102" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D264" s="68">
         <v>1</v>
@@ -9647,7 +10160,7 @@
       </c>
       <c r="F264" s="98"/>
       <c r="G264" s="82" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H264" s="28">
         <v>8000</v>
@@ -9659,7 +10172,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="265" ht="16.5" spans="1:10">
       <c r="A265" s="101">
         <v>55012</v>
       </c>
@@ -9667,7 +10180,7 @@
         <v>105501</v>
       </c>
       <c r="C265" s="102" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D265" s="68">
         <v>2</v>
@@ -9689,7 +10202,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="266" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="266" ht="16.5" spans="1:10">
       <c r="A266" s="101">
         <v>55013</v>
       </c>
@@ -9697,7 +10210,7 @@
         <v>105501</v>
       </c>
       <c r="C266" s="102" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D266" s="68">
         <v>3</v>
@@ -9719,7 +10232,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="267" ht="16.5" spans="1:10">
       <c r="A267" s="101">
         <v>55014</v>
       </c>
@@ -9727,7 +10240,7 @@
         <v>105501</v>
       </c>
       <c r="C267" s="102" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D267" s="68">
         <v>4</v>
@@ -9749,7 +10262,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="268" ht="16.5" spans="1:10">
       <c r="A268" s="101">
         <v>55015</v>
       </c>
@@ -9757,7 +10270,7 @@
         <v>105501</v>
       </c>
       <c r="C268" s="102" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D268" s="68">
         <v>5</v>
@@ -9779,7 +10292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="269" ht="16.5" spans="1:10">
       <c r="A269" s="101">
         <v>55016</v>
       </c>
@@ -9787,7 +10300,7 @@
         <v>105501</v>
       </c>
       <c r="C269" s="102" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D269" s="68">
         <v>6</v>
@@ -9809,7 +10322,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="270" ht="16.5" spans="1:10">
       <c r="A270" s="101">
         <v>55017</v>
       </c>
@@ -9817,7 +10330,7 @@
         <v>105501</v>
       </c>
       <c r="C270" s="102" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D270" s="68">
         <v>7</v>
@@ -9840,8 +10353,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C034994-2FEB-44E3-9253-050DAA89361A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -27,13 +33,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -57,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -83,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -95,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -108,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -121,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -141,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0">
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -171,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="212">
   <si>
     <t>id</t>
   </si>
@@ -740,10 +746,10 @@
     <t>糖果派对</t>
   </si>
   <si>
-    <t>1_9850|2_140|3_10|4_9850|5_140|6_10|7_9850|8_140|9_10</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+    <t>1_9850|4_140|7_10|2_9850|5_140|8_10|3_9850|6_140|9_10</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
   </si>
   <si>
     <t>麻将胡了2</t>
@@ -804,19 +810,16 @@
   </si>
   <si>
     <t>伽罗宝石1</t>
+  </si>
+  <si>
+    <t>伽罗宝石2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -837,147 +840,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -991,8 +857,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1001,25 +880,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1037,13 +916,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1055,7 +934,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1067,13 +946,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1103,108 +982,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1212,254 +1007,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1488,7 +1041,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1724,63 +1277,33 @@
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 73" xfId="49"/>
+    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2038,14 +1561,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J270"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J277"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="3" width="15.25" customWidth="1"/>
@@ -2058,7 +1581,7 @@
     <col min="10" max="10" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -2088,7 +1611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:10">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
@@ -2116,7 +1639,7 @@
       </c>
       <c r="J2" s="23"/>
     </row>
-    <row r="3" ht="16.5" spans="1:10">
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
         <v>0</v>
       </c>
@@ -2144,7 +1667,7 @@
       </c>
       <c r="J3" s="23"/>
     </row>
-    <row r="4" ht="16.5" spans="1:10">
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -2156,7 +1679,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="23"/>
     </row>
-    <row r="5" ht="16.5" spans="1:10">
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="23">
         <v>1001</v>
       </c>
@@ -2186,7 +1709,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:10">
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="23">
         <v>1002</v>
       </c>
@@ -2217,7 +1740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:10">
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="23">
         <v>1003</v>
       </c>
@@ -2248,7 +1771,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:10">
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="23">
         <v>1004</v>
       </c>
@@ -2279,7 +1802,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:10">
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="23">
         <v>1005</v>
       </c>
@@ -2310,7 +1833,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:10">
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="23">
         <v>1006</v>
       </c>
@@ -2341,7 +1864,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:10">
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="23">
         <v>1007</v>
       </c>
@@ -2372,7 +1895,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="29">
         <v>3001</v>
       </c>
@@ -2402,7 +1925,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="13" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="29">
         <v>3002</v>
       </c>
@@ -2433,7 +1956,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="29">
         <v>3003</v>
       </c>
@@ -2464,7 +1987,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="29">
         <v>3004</v>
       </c>
@@ -2495,7 +2018,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="16" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="29">
         <v>3005</v>
       </c>
@@ -2526,7 +2049,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="17" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="29">
         <v>3006</v>
       </c>
@@ -2557,7 +2080,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="18" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="29">
         <v>3007</v>
       </c>
@@ -2588,7 +2111,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="19" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="23">
         <v>7001</v>
       </c>
@@ -2620,7 +2143,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="23">
         <v>7002</v>
       </c>
@@ -2653,7 +2176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="23">
         <v>7003</v>
       </c>
@@ -2686,7 +2209,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="23">
         <v>7004</v>
       </c>
@@ -2719,7 +2242,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="23">
         <v>7005</v>
       </c>
@@ -2752,7 +2275,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="23">
         <v>7006</v>
       </c>
@@ -2785,7 +2308,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="25" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="23">
         <v>7007</v>
       </c>
@@ -2818,7 +2341,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="26" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="33">
         <v>8001</v>
       </c>
@@ -2848,7 +2371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="27" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>8002</v>
       </c>
@@ -2878,7 +2401,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="28" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="33">
         <v>8003</v>
       </c>
@@ -2908,7 +2431,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="29" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>8004</v>
       </c>
@@ -2938,7 +2461,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="30" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="33">
         <v>8005</v>
       </c>
@@ -2968,7 +2491,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="31" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>8006</v>
       </c>
@@ -2998,7 +2521,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="32" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="33">
         <v>8007</v>
       </c>
@@ -3028,7 +2551,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="33" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A33" s="29">
         <v>12001</v>
       </c>
@@ -3060,7 +2583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="34" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A34" s="29">
         <v>12002</v>
       </c>
@@ -3093,7 +2616,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="35" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A35" s="29">
         <v>12003</v>
       </c>
@@ -3126,7 +2649,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="36" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A36" s="29">
         <v>12004</v>
       </c>
@@ -3159,7 +2682,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="37" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A37" s="29">
         <v>12005</v>
       </c>
@@ -3192,7 +2715,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="38" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A38" s="29">
         <v>12006</v>
       </c>
@@ -3225,7 +2748,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="39" spans="1:10" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A39" s="29">
         <v>12007</v>
       </c>
@@ -3258,7 +2781,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="40" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A40" s="23">
         <v>14001</v>
       </c>
@@ -3288,7 +2811,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="41" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A41" s="23">
         <v>14002</v>
       </c>
@@ -3319,7 +2842,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="42" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A42" s="23">
         <v>14003</v>
       </c>
@@ -3350,7 +2873,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="43" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A43" s="23">
         <v>14004</v>
       </c>
@@ -3381,7 +2904,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="44" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A44" s="23">
         <v>14005</v>
       </c>
@@ -3412,7 +2935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="45" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A45" s="23">
         <v>14006</v>
       </c>
@@ -3443,7 +2966,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" s="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="46" spans="1:10" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A46" s="23">
         <v>14007</v>
       </c>
@@ -3474,7 +2997,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="47" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>15001</v>
       </c>
@@ -3504,7 +3027,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="48" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" s="39">
         <v>15002</v>
       </c>
@@ -3535,7 +3058,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="49" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>15003</v>
       </c>
@@ -3566,7 +3089,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="50" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="39">
         <v>15004</v>
       </c>
@@ -3597,7 +3120,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="51" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>15005</v>
       </c>
@@ -3628,7 +3151,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="52" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="39">
         <v>15006</v>
       </c>
@@ -3659,7 +3182,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="53" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="53" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="39">
         <v>15007</v>
       </c>
@@ -3690,7 +3213,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="54" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="43">
         <v>16001</v>
       </c>
@@ -3720,7 +3243,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="55" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="43">
         <v>16002</v>
       </c>
@@ -3751,7 +3274,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="56" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="43">
         <v>16003</v>
       </c>
@@ -3782,7 +3305,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="57" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="57" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="43">
         <v>16004</v>
       </c>
@@ -3813,7 +3336,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="58" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="43">
         <v>16005</v>
       </c>
@@ -3844,7 +3367,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="59" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" s="43">
         <v>16006</v>
       </c>
@@ -3875,7 +3398,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="60" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="60" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="43">
         <v>16007</v>
       </c>
@@ -3906,7 +3429,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="61" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A61" s="23">
         <v>17001</v>
       </c>
@@ -3938,7 +3461,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="62" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A62" s="23">
         <v>17002</v>
       </c>
@@ -3971,7 +3494,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="63" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A63" s="23">
         <v>17003</v>
       </c>
@@ -4004,7 +3527,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="64" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A64" s="23">
         <v>17004</v>
       </c>
@@ -4037,7 +3560,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="65" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A65" s="23">
         <v>17005</v>
       </c>
@@ -4070,7 +3593,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="66" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A66" s="23">
         <v>17006</v>
       </c>
@@ -4103,7 +3626,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="67" spans="1:10" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A67" s="23">
         <v>17007</v>
       </c>
@@ -4136,7 +3659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" s="7" customFormat="1" ht="16.5" spans="1:10">
+    <row r="68" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A68" s="47">
         <v>18001</v>
       </c>
@@ -4168,7 +3691,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:10">
+    <row r="69" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A69" s="47">
         <v>18002</v>
       </c>
@@ -4201,7 +3724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" s="7" customFormat="1" ht="16.5" spans="1:10">
+    <row r="70" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A70" s="47">
         <v>18003</v>
       </c>
@@ -4234,7 +3757,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="71" s="7" customFormat="1" ht="16.5" spans="1:10">
+    <row r="71" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A71" s="47">
         <v>18004</v>
       </c>
@@ -4267,7 +3790,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="72" s="7" customFormat="1" ht="16.5" spans="1:10">
+    <row r="72" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A72" s="47">
         <v>18005</v>
       </c>
@@ -4300,7 +3823,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" s="7" customFormat="1" ht="16.5" spans="1:10">
+    <row r="73" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A73" s="47">
         <v>18006</v>
       </c>
@@ -4333,7 +3856,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" s="7" customFormat="1" ht="16.5" spans="1:10">
+    <row r="74" spans="1:10" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A74" s="47">
         <v>18007</v>
       </c>
@@ -4366,7 +3889,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="75" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A75" s="39">
         <v>20001</v>
       </c>
@@ -4396,7 +3919,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="76" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A76" s="39">
         <v>20002</v>
       </c>
@@ -4427,7 +3950,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="77" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A77" s="39">
         <v>20003</v>
       </c>
@@ -4458,7 +3981,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="78" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="78" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A78" s="39">
         <v>20004</v>
       </c>
@@ -4489,7 +4012,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="79" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="79" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A79" s="39">
         <v>20005</v>
       </c>
@@ -4520,7 +4043,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="80" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A80" s="39">
         <v>20006</v>
       </c>
@@ -4551,7 +4074,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" s="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="81" spans="1:10" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A81" s="39">
         <v>20007</v>
       </c>
@@ -4582,7 +4105,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="82" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A82" s="50">
         <v>21001</v>
       </c>
@@ -4614,7 +4137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="83" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A83" s="50">
         <v>21002</v>
       </c>
@@ -4647,7 +4170,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="84" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="84" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A84" s="50">
         <v>21003</v>
       </c>
@@ -4680,7 +4203,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="85" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A85" s="50">
         <v>21004</v>
       </c>
@@ -4713,7 +4236,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="86" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A86" s="50">
         <v>21005</v>
       </c>
@@ -4746,7 +4269,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="87" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A87" s="50">
         <v>21006</v>
       </c>
@@ -4779,7 +4302,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="88" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A88" s="50">
         <v>21007</v>
       </c>
@@ -4812,7 +4335,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" s="9" customFormat="1" ht="16.5" spans="1:10">
+    <row r="89" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A89" s="52">
         <v>22001</v>
       </c>
@@ -4844,7 +4367,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" s="9" customFormat="1" ht="16.5" spans="1:10">
+    <row r="90" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A90" s="52">
         <v>22002</v>
       </c>
@@ -4877,7 +4400,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" s="9" customFormat="1" ht="16.5" spans="1:10">
+    <row r="91" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A91" s="52">
         <v>22003</v>
       </c>
@@ -4910,7 +4433,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="92" s="9" customFormat="1" ht="16.5" spans="1:10">
+    <row r="92" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A92" s="52">
         <v>22004</v>
       </c>
@@ -4943,7 +4466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="93" s="9" customFormat="1" ht="16.5" spans="1:10">
+    <row r="93" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A93" s="52">
         <v>22005</v>
       </c>
@@ -4976,7 +4499,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" s="9" customFormat="1" ht="16.5" spans="1:10">
+    <row r="94" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A94" s="52">
         <v>22006</v>
       </c>
@@ -5009,7 +4532,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" s="9" customFormat="1" ht="16.5" spans="1:10">
+    <row r="95" spans="1:10" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A95" s="52">
         <v>22007</v>
       </c>
@@ -5042,7 +4565,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" s="10" customFormat="1" ht="16.5" spans="1:10">
+    <row r="96" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A96" s="55">
         <v>23001</v>
       </c>
@@ -5074,7 +4597,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="97" s="10" customFormat="1" ht="16.5" spans="1:10">
+    <row r="97" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A97" s="55">
         <v>23002</v>
       </c>
@@ -5107,7 +4630,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="98" s="10" customFormat="1" ht="16.5" spans="1:10">
+    <row r="98" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A98" s="55">
         <v>23003</v>
       </c>
@@ -5140,7 +4663,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="99" s="10" customFormat="1" ht="16.5" spans="1:10">
+    <row r="99" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A99" s="55">
         <v>23004</v>
       </c>
@@ -5173,7 +4696,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="100" s="10" customFormat="1" ht="16.5" spans="1:10">
+    <row r="100" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A100" s="55">
         <v>23005</v>
       </c>
@@ -5206,7 +4729,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" s="10" customFormat="1" ht="16.5" spans="1:10">
+    <row r="101" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A101" s="55">
         <v>23006</v>
       </c>
@@ -5239,7 +4762,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" s="10" customFormat="1" ht="16.5" spans="1:10">
+    <row r="102" spans="1:10" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A102" s="55">
         <v>23007</v>
       </c>
@@ -5272,7 +4795,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" ht="16.5" spans="1:10">
+    <row r="103" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A103" s="23">
         <v>24001</v>
       </c>
@@ -5302,7 +4825,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="104" ht="16.5" spans="1:10">
+    <row r="104" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A104" s="23">
         <v>24002</v>
       </c>
@@ -5333,7 +4856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" ht="16.5" spans="1:10">
+    <row r="105" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A105" s="23">
         <v>24003</v>
       </c>
@@ -5364,7 +4887,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="106" ht="16.5" spans="1:10">
+    <row r="106" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A106" s="23">
         <v>24004</v>
       </c>
@@ -5395,7 +4918,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="107" ht="16.5" spans="1:10">
+    <row r="107" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A107" s="23">
         <v>24005</v>
       </c>
@@ -5426,7 +4949,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" ht="16.5" spans="1:10">
+    <row r="108" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A108" s="23">
         <v>24006</v>
       </c>
@@ -5457,7 +4980,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="109" ht="16.5" spans="1:10">
+    <row r="109" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A109" s="23">
         <v>24007</v>
       </c>
@@ -5488,7 +5011,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="110" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A110" s="58">
         <v>25001</v>
       </c>
@@ -5520,7 +5043,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="111" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A111" s="58">
         <v>25002</v>
       </c>
@@ -5553,7 +5076,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="112" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="112" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A112" s="58">
         <v>25003</v>
       </c>
@@ -5586,7 +5109,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="113" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="113" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A113" s="58">
         <v>25004</v>
       </c>
@@ -5619,7 +5142,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="114" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="114" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A114" s="58">
         <v>25005</v>
       </c>
@@ -5652,7 +5175,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="115" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A115" s="58">
         <v>25006</v>
       </c>
@@ -5685,7 +5208,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="116" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="116" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A116" s="58">
         <v>25007</v>
       </c>
@@ -5718,7 +5241,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" s="12" customFormat="1" ht="16.5" spans="1:10">
+    <row r="117" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A117" s="61">
         <v>26001</v>
       </c>
@@ -5748,7 +5271,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="118" s="12" customFormat="1" ht="16.5" spans="1:10">
+    <row r="118" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A118" s="61">
         <v>26002</v>
       </c>
@@ -5779,7 +5302,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" s="12" customFormat="1" ht="16.5" spans="1:10">
+    <row r="119" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A119" s="61">
         <v>26003</v>
       </c>
@@ -5810,7 +5333,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="120" s="12" customFormat="1" ht="16.5" spans="1:10">
+    <row r="120" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A120" s="61">
         <v>26004</v>
       </c>
@@ -5841,7 +5364,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" s="12" customFormat="1" ht="16.5" spans="1:10">
+    <row r="121" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A121" s="61">
         <v>26005</v>
       </c>
@@ -5872,7 +5395,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="122" s="12" customFormat="1" ht="16.5" spans="1:10">
+    <row r="122" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A122" s="61">
         <v>26006</v>
       </c>
@@ -5903,7 +5426,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="123" s="12" customFormat="1" ht="16.5" spans="1:10">
+    <row r="123" spans="1:10" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A123" s="61">
         <v>26007</v>
       </c>
@@ -5934,7 +5457,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="124" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A124" s="58">
         <v>27001</v>
       </c>
@@ -5964,7 +5487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="125" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="125" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A125" s="58">
         <v>27002</v>
       </c>
@@ -5995,7 +5518,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="126" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A126" s="58">
         <v>27003</v>
       </c>
@@ -6026,7 +5549,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="127" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="127" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A127" s="58">
         <v>27004</v>
       </c>
@@ -6057,7 +5580,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="128" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A128" s="58">
         <v>27005</v>
       </c>
@@ -6088,7 +5611,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="129" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A129" s="58">
         <v>27006</v>
       </c>
@@ -6119,7 +5642,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="130" s="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="130" spans="1:10" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A130" s="58">
         <v>27007</v>
       </c>
@@ -6150,7 +5673,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="131" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A131" s="43">
         <v>28001</v>
       </c>
@@ -6180,7 +5703,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="132" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="132" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A132" s="43">
         <v>28002</v>
       </c>
@@ -6211,7 +5734,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="133" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A133" s="43">
         <v>28003</v>
       </c>
@@ -6242,7 +5765,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="134" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="134" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A134" s="43">
         <v>28004</v>
       </c>
@@ -6273,7 +5796,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="135" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A135" s="43">
         <v>28005</v>
       </c>
@@ -6304,7 +5827,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="136" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="136" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A136" s="43">
         <v>28006</v>
       </c>
@@ -6335,7 +5858,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="137" s="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="137" spans="1:10" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A137" s="43">
         <v>28007</v>
       </c>
@@ -6366,7 +5889,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="138" s="13" customFormat="1" ht="16.5" spans="1:10">
+    <row r="138" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A138" s="64">
         <v>31001</v>
       </c>
@@ -6396,7 +5919,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" s="13" customFormat="1" ht="16.5" spans="1:10">
+    <row r="139" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A139" s="64">
         <v>31002</v>
       </c>
@@ -6427,7 +5950,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="140" s="13" customFormat="1" ht="16.5" spans="1:10">
+    <row r="140" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A140" s="64">
         <v>31003</v>
       </c>
@@ -6458,7 +5981,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="141" s="13" customFormat="1" ht="16.5" spans="1:10">
+    <row r="141" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A141" s="64">
         <v>31004</v>
       </c>
@@ -6489,7 +6012,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="142" s="13" customFormat="1" ht="16.5" spans="1:10">
+    <row r="142" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A142" s="64">
         <v>31005</v>
       </c>
@@ -6520,7 +6043,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="143" s="13" customFormat="1" ht="16.5" spans="1:10">
+    <row r="143" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A143" s="64">
         <v>31006</v>
       </c>
@@ -6551,7 +6074,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="144" s="13" customFormat="1" ht="16.5" spans="1:10">
+    <row r="144" spans="1:10" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A144" s="64">
         <v>31007</v>
       </c>
@@ -6582,7 +6105,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="145" s="14" customFormat="1" ht="16.5" spans="1:10">
+    <row r="145" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A145" s="68">
         <v>34001</v>
       </c>
@@ -6612,7 +6135,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="146" s="14" customFormat="1" ht="16.5" spans="1:10">
+    <row r="146" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A146" s="68">
         <v>34002</v>
       </c>
@@ -6643,7 +6166,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" s="14" customFormat="1" ht="16.5" spans="1:10">
+    <row r="147" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A147" s="68">
         <v>34003</v>
       </c>
@@ -6674,7 +6197,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="148" s="14" customFormat="1" ht="16.5" spans="1:10">
+    <row r="148" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A148" s="68">
         <v>34004</v>
       </c>
@@ -6705,7 +6228,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="149" s="14" customFormat="1" ht="16.5" spans="1:10">
+    <row r="149" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A149" s="68">
         <v>34005</v>
       </c>
@@ -6736,7 +6259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="150" s="14" customFormat="1" ht="16.5" spans="1:10">
+    <row r="150" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A150" s="68">
         <v>34006</v>
       </c>
@@ -6767,7 +6290,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="151" s="14" customFormat="1" ht="16.5" spans="1:10">
+    <row r="151" spans="1:10" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A151" s="68">
         <v>34007</v>
       </c>
@@ -6798,7 +6321,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="152" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="152" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A152" s="71">
         <v>34011</v>
       </c>
@@ -6828,7 +6351,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="153" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="153" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A153" s="71">
         <v>34012</v>
       </c>
@@ -6859,7 +6382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="154" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="154" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A154" s="71">
         <v>34013</v>
       </c>
@@ -6890,7 +6413,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="155" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="155" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A155" s="71">
         <v>34014</v>
       </c>
@@ -6921,7 +6444,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="156" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="156" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A156" s="71">
         <v>34015</v>
       </c>
@@ -6952,7 +6475,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="157" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A157" s="71">
         <v>34016</v>
       </c>
@@ -6983,7 +6506,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="158" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="158" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A158" s="71">
         <v>34017</v>
       </c>
@@ -7014,7 +6537,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="159" s="16" customFormat="1" ht="16.5" spans="1:10">
+    <row r="159" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A159" s="75">
         <v>35001</v>
       </c>
@@ -7044,7 +6567,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" s="16" customFormat="1" ht="16.5" spans="1:10">
+    <row r="160" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A160" s="75">
         <v>35002</v>
       </c>
@@ -7075,7 +6598,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" s="16" customFormat="1" ht="16.5" spans="1:10">
+    <row r="161" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A161" s="75">
         <v>35003</v>
       </c>
@@ -7106,7 +6629,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="162" s="16" customFormat="1" ht="16.5" spans="1:10">
+    <row r="162" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A162" s="75">
         <v>35004</v>
       </c>
@@ -7137,7 +6660,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="163" s="16" customFormat="1" ht="16.5" spans="1:10">
+    <row r="163" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A163" s="75">
         <v>35005</v>
       </c>
@@ -7168,7 +6691,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" s="16" customFormat="1" ht="16.5" spans="1:10">
+    <row r="164" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A164" s="75">
         <v>35006</v>
       </c>
@@ -7199,7 +6722,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="165" s="16" customFormat="1" ht="16.5" spans="1:10">
+    <row r="165" spans="1:10" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A165" s="75">
         <v>35007</v>
       </c>
@@ -7230,7 +6753,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="166" s="17" customFormat="1" ht="16.5" spans="1:10">
+    <row r="166" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A166" s="78">
         <v>35011</v>
       </c>
@@ -7260,7 +6783,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="167" s="17" customFormat="1" ht="16.5" spans="1:10">
+    <row r="167" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A167" s="78">
         <v>35012</v>
       </c>
@@ -7291,7 +6814,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="168" s="17" customFormat="1" ht="16.5" spans="1:10">
+    <row r="168" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A168" s="78">
         <v>35013</v>
       </c>
@@ -7322,7 +6845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="169" s="17" customFormat="1" ht="16.5" spans="1:10">
+    <row r="169" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A169" s="78">
         <v>35014</v>
       </c>
@@ -7353,7 +6876,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" s="17" customFormat="1" ht="16.5" spans="1:10">
+    <row r="170" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A170" s="78">
         <v>35015</v>
       </c>
@@ -7384,7 +6907,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" s="17" customFormat="1" ht="16.5" spans="1:10">
+    <row r="171" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A171" s="78">
         <v>35016</v>
       </c>
@@ -7415,7 +6938,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="172" s="17" customFormat="1" ht="16.5" spans="1:10">
+    <row r="172" spans="1:10" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A172" s="78">
         <v>35017</v>
       </c>
@@ -7446,7 +6969,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="173" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A173" s="80">
         <v>36001</v>
       </c>
@@ -7476,7 +6999,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="174" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A174" s="80">
         <v>36002</v>
       </c>
@@ -7507,7 +7030,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="175" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A175" s="80">
         <v>36003</v>
       </c>
@@ -7538,7 +7061,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="176" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="176" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A176" s="80">
         <v>36004</v>
       </c>
@@ -7569,7 +7092,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="177" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A177" s="80">
         <v>36005</v>
       </c>
@@ -7600,7 +7123,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="178" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="178" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A178" s="80">
         <v>36006</v>
       </c>
@@ -7631,7 +7154,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="179" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="179" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A179" s="80">
         <v>36007</v>
       </c>
@@ -7662,7 +7185,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="180" s="19" customFormat="1" ht="16.5" spans="1:10">
+    <row r="180" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A180" s="84">
         <v>38001</v>
       </c>
@@ -7692,7 +7215,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="181" s="19" customFormat="1" ht="16.5" spans="1:10">
+    <row r="181" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A181" s="84">
         <v>38002</v>
       </c>
@@ -7723,7 +7246,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="182" s="19" customFormat="1" ht="16.5" spans="1:10">
+    <row r="182" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A182" s="84">
         <v>38003</v>
       </c>
@@ -7754,7 +7277,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="183" s="19" customFormat="1" ht="16.5" spans="1:10">
+    <row r="183" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A183" s="84">
         <v>38004</v>
       </c>
@@ -7785,7 +7308,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="184" s="19" customFormat="1" ht="16.5" spans="1:10">
+    <row r="184" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A184" s="84">
         <v>38005</v>
       </c>
@@ -7816,7 +7339,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" s="19" customFormat="1" ht="16.5" spans="1:10">
+    <row r="185" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A185" s="84">
         <v>38006</v>
       </c>
@@ -7847,7 +7370,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="186" s="19" customFormat="1" ht="16.5" spans="1:10">
+    <row r="186" spans="1:10" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A186" s="84">
         <v>38007</v>
       </c>
@@ -7878,7 +7401,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="187" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="187" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A187" s="80">
         <v>37001</v>
       </c>
@@ -7908,7 +7431,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="188" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A188" s="80">
         <v>37002</v>
       </c>
@@ -7939,7 +7462,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="189" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="189" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A189" s="80">
         <v>37003</v>
       </c>
@@ -7970,7 +7493,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="190" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="190" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A190" s="80">
         <v>37004</v>
       </c>
@@ -8001,7 +7524,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="191" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="191" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A191" s="80">
         <v>37005</v>
       </c>
@@ -8032,7 +7555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="192" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="192" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A192" s="80">
         <v>37006</v>
       </c>
@@ -8063,7 +7586,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="193" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="193" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A193" s="80">
         <v>37007</v>
       </c>
@@ -8094,7 +7617,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="194" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="194" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A194" s="88">
         <v>39001</v>
       </c>
@@ -8124,7 +7647,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="195" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A195" s="88">
         <v>39002</v>
       </c>
@@ -8155,7 +7678,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="196" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A196" s="88">
         <v>39003</v>
       </c>
@@ -8186,7 +7709,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="197" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="197" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A197" s="88">
         <v>39004</v>
       </c>
@@ -8217,7 +7740,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="198" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="198" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A198" s="88">
         <v>39005</v>
       </c>
@@ -8248,7 +7771,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="199" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="199" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A199" s="88">
         <v>39006</v>
       </c>
@@ -8279,7 +7802,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="200" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="200" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A200" s="88">
         <v>39007</v>
       </c>
@@ -8310,7 +7833,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="201" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="201" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A201" s="71">
         <v>40001</v>
       </c>
@@ -8340,7 +7863,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="202" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="202" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A202" s="71">
         <v>40002</v>
       </c>
@@ -8371,7 +7894,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="203" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="203" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A203" s="71">
         <v>40003</v>
       </c>
@@ -8402,7 +7925,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="204" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="204" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A204" s="71">
         <v>40004</v>
       </c>
@@ -8433,7 +7956,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="205" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="205" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A205" s="71">
         <v>40005</v>
       </c>
@@ -8464,7 +7987,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="206" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="206" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A206" s="71">
         <v>40006</v>
       </c>
@@ -8495,7 +8018,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="207" s="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="207" spans="1:10" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A207" s="71">
         <v>40007</v>
       </c>
@@ -8526,7 +8049,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="208" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="208" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A208" s="88">
         <v>48001</v>
       </c>
@@ -8556,7 +8079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="209" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="209" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A209" s="88">
         <v>48002</v>
       </c>
@@ -8586,7 +8109,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="210" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A210" s="88">
         <v>48003</v>
       </c>
@@ -8616,7 +8139,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="211" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="211" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A211" s="88">
         <v>48004</v>
       </c>
@@ -8646,7 +8169,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="212" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="212" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A212" s="88">
         <v>48005</v>
       </c>
@@ -8676,7 +8199,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="213" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="213" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A213" s="88">
         <v>48006</v>
       </c>
@@ -8706,7 +8229,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="214" s="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="214" spans="1:10" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A214" s="88">
         <v>48007</v>
       </c>
@@ -8736,7 +8259,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="215" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="215" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A215" s="80">
         <v>50001</v>
       </c>
@@ -8766,7 +8289,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="216" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="216" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A216" s="80">
         <v>50002</v>
       </c>
@@ -8796,7 +8319,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="217" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="217" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A217" s="80">
         <v>50003</v>
       </c>
@@ -8826,7 +8349,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="218" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="218" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A218" s="80">
         <v>50004</v>
       </c>
@@ -8856,7 +8379,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="219" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="219" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A219" s="80">
         <v>50005</v>
       </c>
@@ -8886,7 +8409,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="220" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="220" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A220" s="80">
         <v>50006</v>
       </c>
@@ -8916,7 +8439,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="221" s="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="221" spans="1:10" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A221" s="80">
         <v>50007</v>
       </c>
@@ -8946,7 +8469,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="222" s="20" customFormat="1" ht="16.5" spans="1:10">
+    <row r="222" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A222" s="89">
         <v>51001</v>
       </c>
@@ -8976,7 +8499,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" s="20" customFormat="1" ht="16.5" spans="1:10">
+    <row r="223" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A223" s="89">
         <v>51002</v>
       </c>
@@ -9006,7 +8529,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="224" s="20" customFormat="1" ht="16.5" spans="1:10">
+    <row r="224" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A224" s="89">
         <v>51003</v>
       </c>
@@ -9036,7 +8559,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="225" s="20" customFormat="1" ht="16.5" spans="1:10">
+    <row r="225" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A225" s="89">
         <v>51004</v>
       </c>
@@ -9066,7 +8589,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="226" s="20" customFormat="1" ht="16.5" spans="1:10">
+    <row r="226" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A226" s="89">
         <v>51005</v>
       </c>
@@ -9096,7 +8619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="227" s="20" customFormat="1" ht="16.5" spans="1:10">
+    <row r="227" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A227" s="89">
         <v>51006</v>
       </c>
@@ -9126,7 +8649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="228" s="20" customFormat="1" ht="16.5" spans="1:10">
+    <row r="228" spans="1:10" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A228" s="89">
         <v>51007</v>
       </c>
@@ -9156,7 +8679,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="229" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="229" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A229" s="8">
         <v>53001</v>
       </c>
@@ -9186,7 +8709,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="230" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="230" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A230" s="8">
         <v>53002</v>
       </c>
@@ -9216,7 +8739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="231" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="231" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A231" s="8">
         <v>53003</v>
       </c>
@@ -9246,7 +8769,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="232" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="232" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A232" s="8">
         <v>53004</v>
       </c>
@@ -9276,7 +8799,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="233" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="233" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A233" s="8">
         <v>53005</v>
       </c>
@@ -9306,7 +8829,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="234" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="234" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A234" s="8">
         <v>53006</v>
       </c>
@@ -9336,7 +8859,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="235" s="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="235" spans="1:10" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A235" s="8">
         <v>53007</v>
       </c>
@@ -9366,7 +8889,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="236" ht="16.5" spans="1:10">
+    <row r="236" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A236" s="88">
         <v>54001</v>
       </c>
@@ -9395,7 +8918,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="237" ht="16.5" spans="1:10">
+    <row r="237" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A237" s="88">
         <v>54002</v>
       </c>
@@ -9424,7 +8947,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="238" ht="16.5" spans="1:10">
+    <row r="238" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A238" s="88">
         <v>54003</v>
       </c>
@@ -9453,7 +8976,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="239" ht="16.5" spans="1:10">
+    <row r="239" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A239" s="88">
         <v>54004</v>
       </c>
@@ -9482,7 +9005,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="240" ht="16.5" spans="1:10">
+    <row r="240" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A240" s="88">
         <v>54005</v>
       </c>
@@ -9511,7 +9034,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="241" ht="16.5" spans="1:10">
+    <row r="241" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A241" s="88">
         <v>54006</v>
       </c>
@@ -9540,7 +9063,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="242" ht="16.5" spans="1:10">
+    <row r="242" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A242" s="88">
         <v>54007</v>
       </c>
@@ -9569,7 +9092,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="243" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="243" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A243" s="94">
         <v>57001</v>
       </c>
@@ -9599,7 +9122,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="244" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="244" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A244" s="94">
         <v>57002</v>
       </c>
@@ -9629,7 +9152,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="245" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="245" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A245" s="94">
         <v>57003</v>
       </c>
@@ -9659,7 +9182,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="246" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="246" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A246" s="94">
         <v>57004</v>
       </c>
@@ -9689,7 +9212,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="247" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="247" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A247" s="94">
         <v>57005</v>
       </c>
@@ -9719,7 +9242,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="248" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="248" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A248" s="94">
         <v>57006</v>
       </c>
@@ -9749,7 +9272,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="249" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="249" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A249" s="94">
         <v>57007</v>
       </c>
@@ -9779,7 +9302,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="250" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="250" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A250" s="21">
         <v>58001</v>
       </c>
@@ -9800,7 +9323,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="251" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="251" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A251" s="21">
         <v>58002</v>
       </c>
@@ -9821,7 +9344,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="252" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="252" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A252" s="21">
         <v>58003</v>
       </c>
@@ -9842,7 +9365,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="253" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="253" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A253" s="21">
         <v>58004</v>
       </c>
@@ -9863,7 +9386,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="254" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="254" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A254" s="21">
         <v>58005</v>
       </c>
@@ -9884,7 +9407,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="255" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="255" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A255" s="21">
         <v>58006</v>
       </c>
@@ -9905,7 +9428,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="256" s="21" customFormat="1" ht="16.5" spans="1:10">
+    <row r="256" spans="1:10" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A256" s="21">
         <v>58007</v>
       </c>
@@ -9926,7 +9449,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="257" ht="16.5" spans="1:10">
+    <row r="257" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A257" s="101">
         <v>55001</v>
       </c>
@@ -9956,7 +9479,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="258" ht="16.5" spans="1:10">
+    <row r="258" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A258" s="101">
         <v>55002</v>
       </c>
@@ -9987,7 +9510,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="259" ht="16.5" spans="1:10">
+    <row r="259" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A259" s="101">
         <v>55003</v>
       </c>
@@ -10018,7 +9541,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="260" ht="16.5" spans="1:10">
+    <row r="260" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A260" s="101">
         <v>55004</v>
       </c>
@@ -10049,7 +9572,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="261" ht="16.5" spans="1:10">
+    <row r="261" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A261" s="101">
         <v>55005</v>
       </c>
@@ -10080,7 +9603,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="262" ht="16.5" spans="1:10">
+    <row r="262" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A262" s="101">
         <v>55006</v>
       </c>
@@ -10111,7 +9634,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="263" ht="16.5" spans="1:10">
+    <row r="263" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A263" s="101">
         <v>55007</v>
       </c>
@@ -10142,7 +9665,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="264" ht="16.5" spans="1:10">
+    <row r="264" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A264" s="101">
         <v>55011</v>
       </c>
@@ -10172,7 +9695,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="265" ht="16.5" spans="1:10">
+    <row r="265" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A265" s="101">
         <v>55012</v>
       </c>
@@ -10202,7 +9725,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="266" ht="16.5" spans="1:10">
+    <row r="266" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A266" s="101">
         <v>55013</v>
       </c>
@@ -10232,7 +9755,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="267" ht="16.5" spans="1:10">
+    <row r="267" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A267" s="101">
         <v>55014</v>
       </c>
@@ -10262,7 +9785,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="268" ht="16.5" spans="1:10">
+    <row r="268" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A268" s="101">
         <v>55015</v>
       </c>
@@ -10292,7 +9815,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="269" ht="16.5" spans="1:10">
+    <row r="269" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A269" s="101">
         <v>55016</v>
       </c>
@@ -10322,7 +9845,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="270" ht="16.5" spans="1:10">
+    <row r="270" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A270" s="101">
         <v>55017</v>
       </c>
@@ -10352,9 +9875,219 @@
         <v>35</v>
       </c>
     </row>
+    <row r="271" spans="1:10" s="109" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A271" s="104">
+        <v>55021</v>
+      </c>
+      <c r="B271" s="105">
+        <v>105502</v>
+      </c>
+      <c r="C271" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="D271" s="105">
+        <v>1</v>
+      </c>
+      <c r="E271" s="106" t="s">
+        <v>54</v>
+      </c>
+      <c r="F271" s="106"/>
+      <c r="G271" s="107" t="s">
+        <v>205</v>
+      </c>
+      <c r="H271" s="108">
+        <v>8000</v>
+      </c>
+      <c r="I271" s="108">
+        <v>999999</v>
+      </c>
+      <c r="J271" s="107" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" s="109" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A272" s="104">
+        <v>55022</v>
+      </c>
+      <c r="B272" s="105">
+        <v>105502</v>
+      </c>
+      <c r="C272" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="D272" s="105">
+        <v>2</v>
+      </c>
+      <c r="E272" s="106" t="s">
+        <v>56</v>
+      </c>
+      <c r="F272" s="106"/>
+      <c r="G272" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="H272" s="108">
+        <v>6000</v>
+      </c>
+      <c r="I272" s="108">
+        <v>8000</v>
+      </c>
+      <c r="J272" s="107" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" s="109" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A273" s="104">
+        <v>55023</v>
+      </c>
+      <c r="B273" s="105">
+        <v>105502</v>
+      </c>
+      <c r="C273" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="D273" s="105">
+        <v>3</v>
+      </c>
+      <c r="E273" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="F273" s="106"/>
+      <c r="G273" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="H273" s="108">
+        <v>4000</v>
+      </c>
+      <c r="I273" s="108">
+        <v>6000</v>
+      </c>
+      <c r="J273" s="107" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" s="109" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A274" s="104">
+        <v>55024</v>
+      </c>
+      <c r="B274" s="105">
+        <v>105502</v>
+      </c>
+      <c r="C274" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="D274" s="105">
+        <v>4</v>
+      </c>
+      <c r="E274" s="106" t="s">
+        <v>58</v>
+      </c>
+      <c r="F274" s="106"/>
+      <c r="G274" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="H274" s="108">
+        <v>2000</v>
+      </c>
+      <c r="I274" s="108">
+        <v>4000</v>
+      </c>
+      <c r="J274" s="107" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" s="109" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A275" s="104">
+        <v>55025</v>
+      </c>
+      <c r="B275" s="105">
+        <v>105502</v>
+      </c>
+      <c r="C275" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="D275" s="105">
+        <v>5</v>
+      </c>
+      <c r="E275" s="106" t="s">
+        <v>59</v>
+      </c>
+      <c r="F275" s="106"/>
+      <c r="G275" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="H275" s="108">
+        <v>0</v>
+      </c>
+      <c r="I275" s="108">
+        <v>2000</v>
+      </c>
+      <c r="J275" s="107" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" s="109" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A276" s="104">
+        <v>55026</v>
+      </c>
+      <c r="B276" s="105">
+        <v>105502</v>
+      </c>
+      <c r="C276" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="D276" s="105">
+        <v>6</v>
+      </c>
+      <c r="E276" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="F276" s="106"/>
+      <c r="G276" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="H276" s="108">
+        <v>-1000</v>
+      </c>
+      <c r="I276" s="108">
+        <v>0</v>
+      </c>
+      <c r="J276" s="107" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" s="109" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A277" s="104">
+        <v>55027</v>
+      </c>
+      <c r="B277" s="105">
+        <v>105502</v>
+      </c>
+      <c r="C277" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="D277" s="105">
+        <v>7</v>
+      </c>
+      <c r="E277" s="106" t="s">
+        <v>61</v>
+      </c>
+      <c r="F277" s="106"/>
+      <c r="G277" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="H277" s="108">
+        <v>-999999</v>
+      </c>
+      <c r="I277" s="108">
+        <v>-1000</v>
+      </c>
+      <c r="J277" s="107" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\特殊用户标记\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31361EF-5DED-41F0-977A-79480DF293CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6F5903-44E9-4992-94D3-FE96A869E2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -273,7 +273,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="253">
   <si>
     <t>id</t>
   </si>
@@ -1058,6 +1058,34 @@
   </si>
   <si>
     <t>5,1&amp;0-30000|2-4000|3-0|4-0|5-0|6-0|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0#8,1&amp;0-10000|2-4000|3-0|4-0|5-0|6-0|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0#10,1&amp;0-0|2-4000|3-0|4-0|5-0|6-0|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1&amp;0-8000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1&amp;0-10000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1&amp;0-20000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1&amp;0-16000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1&amp;0-15000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1&amp;0-17500</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,1&amp;0-17000</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1948,7 +1976,9 @@
       <c r="E5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="24"/>
+      <c r="F5" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G5" s="24" t="s">
         <v>213</v>
       </c>
@@ -1985,7 +2015,9 @@
       <c r="E6" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="24"/>
+      <c r="F6" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G6" s="24" t="s">
         <v>213</v>
       </c>
@@ -2023,7 +2055,9 @@
       <c r="E7" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="24"/>
+      <c r="F7" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G7" s="24" t="s">
         <v>213</v>
       </c>
@@ -2061,7 +2095,9 @@
       <c r="E8" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="24"/>
+      <c r="F8" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G8" s="24" t="s">
         <v>213</v>
       </c>
@@ -2099,7 +2135,9 @@
       <c r="E9" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="24"/>
+      <c r="F9" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G9" s="24" t="s">
         <v>213</v>
       </c>
@@ -2137,7 +2175,9 @@
       <c r="E10" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="24"/>
+      <c r="F10" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G10" s="24" t="s">
         <v>213</v>
       </c>
@@ -2175,7 +2215,9 @@
       <c r="E11" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="24"/>
+      <c r="F11" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G11" s="24" t="s">
         <v>213</v>
       </c>
@@ -2213,7 +2255,9 @@
       <c r="E12" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="24"/>
+      <c r="F12" s="24" t="s">
+        <v>248</v>
+      </c>
       <c r="G12" s="24" t="s">
         <v>215</v>
       </c>
@@ -2250,7 +2294,9 @@
       <c r="E13" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="24"/>
+      <c r="F13" s="24" t="s">
+        <v>248</v>
+      </c>
       <c r="G13" s="24" t="s">
         <v>215</v>
       </c>
@@ -2288,7 +2334,9 @@
       <c r="E14" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="24"/>
+      <c r="F14" s="24" t="s">
+        <v>248</v>
+      </c>
       <c r="G14" s="24" t="s">
         <v>215</v>
       </c>
@@ -2326,7 +2374,9 @@
       <c r="E15" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="F15" s="24"/>
+      <c r="F15" s="24" t="s">
+        <v>248</v>
+      </c>
       <c r="G15" s="24" t="s">
         <v>215</v>
       </c>
@@ -2364,7 +2414,9 @@
       <c r="E16" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="24"/>
+      <c r="F16" s="24" t="s">
+        <v>248</v>
+      </c>
       <c r="G16" s="24" t="s">
         <v>215</v>
       </c>
@@ -2402,7 +2454,9 @@
       <c r="E17" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="24"/>
+      <c r="F17" s="24" t="s">
+        <v>248</v>
+      </c>
       <c r="G17" s="24" t="s">
         <v>215</v>
       </c>
@@ -2440,7 +2494,9 @@
       <c r="E18" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="24"/>
+      <c r="F18" s="24" t="s">
+        <v>248</v>
+      </c>
       <c r="G18" s="24" t="s">
         <v>215</v>
       </c>
@@ -2478,7 +2534,9 @@
       <c r="E19" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="93"/>
+      <c r="F19" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G19" s="30" t="s">
         <v>217</v>
       </c>
@@ -2517,7 +2575,9 @@
       <c r="E20" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="93"/>
+      <c r="F20" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G20" s="30" t="s">
         <v>217</v>
       </c>
@@ -2557,7 +2617,9 @@
       <c r="E21" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="93"/>
+      <c r="F21" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G21" s="30" t="s">
         <v>217</v>
       </c>
@@ -2597,7 +2659,9 @@
       <c r="E22" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="93"/>
+      <c r="F22" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G22" s="30" t="s">
         <v>217</v>
       </c>
@@ -2637,7 +2701,9 @@
       <c r="E23" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="93"/>
+      <c r="F23" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G23" s="30" t="s">
         <v>217</v>
       </c>
@@ -2677,7 +2743,9 @@
       <c r="E24" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="93"/>
+      <c r="F24" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G24" s="30" t="s">
         <v>217</v>
       </c>
@@ -2717,7 +2785,9 @@
       <c r="E25" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="93"/>
+      <c r="F25" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G25" s="30" t="s">
         <v>217</v>
       </c>
@@ -2757,7 +2827,9 @@
       <c r="E26" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="F26" s="24"/>
+      <c r="F26" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G26" s="24" t="s">
         <v>218</v>
       </c>
@@ -2796,7 +2868,9 @@
       <c r="E27" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="24"/>
+      <c r="F27" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G27" s="24" t="s">
         <v>218</v>
       </c>
@@ -2836,7 +2910,9 @@
       <c r="E28" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="24"/>
+      <c r="F28" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G28" s="24" t="s">
         <v>218</v>
       </c>
@@ -2876,7 +2952,9 @@
       <c r="E29" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F29" s="24"/>
+      <c r="F29" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G29" s="24" t="s">
         <v>218</v>
       </c>
@@ -2916,7 +2994,9 @@
       <c r="E30" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="24"/>
+      <c r="F30" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G30" s="24" t="s">
         <v>218</v>
       </c>
@@ -2956,7 +3036,9 @@
       <c r="E31" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F31" s="24"/>
+      <c r="F31" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G31" s="24" t="s">
         <v>218</v>
       </c>
@@ -2996,7 +3078,9 @@
       <c r="E32" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="F32" s="24"/>
+      <c r="F32" s="24" t="s">
+        <v>247</v>
+      </c>
       <c r="G32" s="24" t="s">
         <v>218</v>
       </c>
@@ -3036,7 +3120,9 @@
       <c r="E33" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="F33" s="34"/>
+      <c r="F33" s="24" t="s">
+        <v>249</v>
+      </c>
       <c r="G33" s="34" t="s">
         <v>220</v>
       </c>
@@ -3073,7 +3159,9 @@
       <c r="E34" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="34"/>
+      <c r="F34" s="24" t="s">
+        <v>249</v>
+      </c>
       <c r="G34" s="34" t="s">
         <v>220</v>
       </c>
@@ -3111,7 +3199,9 @@
       <c r="E35" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="34"/>
+      <c r="F35" s="24" t="s">
+        <v>249</v>
+      </c>
       <c r="G35" s="34" t="s">
         <v>220</v>
       </c>
@@ -3149,7 +3239,9 @@
       <c r="E36" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F36" s="34"/>
+      <c r="F36" s="24" t="s">
+        <v>249</v>
+      </c>
       <c r="G36" s="34" t="s">
         <v>220</v>
       </c>
@@ -3187,7 +3279,9 @@
       <c r="E37" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F37" s="34"/>
+      <c r="F37" s="24" t="s">
+        <v>249</v>
+      </c>
       <c r="G37" s="34" t="s">
         <v>220</v>
       </c>
@@ -3225,7 +3319,9 @@
       <c r="E38" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="F38" s="34"/>
+      <c r="F38" s="24" t="s">
+        <v>249</v>
+      </c>
       <c r="G38" s="34" t="s">
         <v>220</v>
       </c>
@@ -3263,7 +3359,9 @@
       <c r="E39" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="F39" s="34"/>
+      <c r="F39" s="24" t="s">
+        <v>249</v>
+      </c>
       <c r="G39" s="34" t="s">
         <v>220</v>
       </c>
@@ -3775,7 +3873,9 @@
       <c r="E54" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="F54" s="30"/>
+      <c r="F54" s="30" t="s">
+        <v>250</v>
+      </c>
       <c r="G54" s="30" t="s">
         <v>221</v>
       </c>
@@ -3814,7 +3914,9 @@
       <c r="E55" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="F55" s="30"/>
+      <c r="F55" s="30" t="s">
+        <v>250</v>
+      </c>
       <c r="G55" s="30" t="s">
         <v>207</v>
       </c>
@@ -3854,7 +3956,9 @@
       <c r="E56" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="F56" s="30"/>
+      <c r="F56" s="30" t="s">
+        <v>250</v>
+      </c>
       <c r="G56" s="30" t="s">
         <v>207</v>
       </c>
@@ -3894,7 +3998,9 @@
       <c r="E57" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="F57" s="30"/>
+      <c r="F57" s="30" t="s">
+        <v>250</v>
+      </c>
       <c r="G57" s="30" t="s">
         <v>207</v>
       </c>
@@ -3934,7 +4040,9 @@
       <c r="E58" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="F58" s="30"/>
+      <c r="F58" s="30" t="s">
+        <v>250</v>
+      </c>
       <c r="G58" s="30" t="s">
         <v>207</v>
       </c>
@@ -3974,7 +4082,9 @@
       <c r="E59" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="F59" s="30"/>
+      <c r="F59" s="30" t="s">
+        <v>250</v>
+      </c>
       <c r="G59" s="30" t="s">
         <v>207</v>
       </c>
@@ -4014,7 +4124,9 @@
       <c r="E60" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="F60" s="30"/>
+      <c r="F60" s="30" t="s">
+        <v>250</v>
+      </c>
       <c r="G60" s="30" t="s">
         <v>207</v>
       </c>
@@ -4054,7 +4166,9 @@
       <c r="E61" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="F61" s="44"/>
+      <c r="F61" s="30" t="s">
+        <v>248</v>
+      </c>
       <c r="G61" s="44" t="s">
         <v>222</v>
       </c>
@@ -4093,7 +4207,9 @@
       <c r="E62" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="F62" s="44"/>
+      <c r="F62" s="30" t="s">
+        <v>248</v>
+      </c>
       <c r="G62" s="44" t="s">
         <v>222</v>
       </c>
@@ -4133,7 +4249,9 @@
       <c r="E63" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="F63" s="44"/>
+      <c r="F63" s="30" t="s">
+        <v>248</v>
+      </c>
       <c r="G63" s="44" t="s">
         <v>222</v>
       </c>
@@ -4173,7 +4291,9 @@
       <c r="E64" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="F64" s="44"/>
+      <c r="F64" s="30" t="s">
+        <v>248</v>
+      </c>
       <c r="G64" s="44" t="s">
         <v>222</v>
       </c>
@@ -4213,7 +4333,9 @@
       <c r="E65" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="F65" s="44"/>
+      <c r="F65" s="30" t="s">
+        <v>248</v>
+      </c>
       <c r="G65" s="44" t="s">
         <v>222</v>
       </c>
@@ -4253,7 +4375,9 @@
       <c r="E66" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="F66" s="44"/>
+      <c r="F66" s="30" t="s">
+        <v>248</v>
+      </c>
       <c r="G66" s="44" t="s">
         <v>222</v>
       </c>
@@ -4293,7 +4417,9 @@
       <c r="E67" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="F67" s="44"/>
+      <c r="F67" s="30" t="s">
+        <v>248</v>
+      </c>
       <c r="G67" s="44" t="s">
         <v>222</v>
       </c>
@@ -4333,7 +4459,9 @@
       <c r="E68" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="F68" s="36"/>
+      <c r="F68" s="36" t="s">
+        <v>247</v>
+      </c>
       <c r="G68" s="36" t="s">
         <v>226</v>
       </c>
@@ -4372,7 +4500,9 @@
       <c r="E69" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="F69" s="36"/>
+      <c r="F69" s="36" t="s">
+        <v>247</v>
+      </c>
       <c r="G69" s="36" t="s">
         <v>226</v>
       </c>
@@ -4413,7 +4543,9 @@
       <c r="E70" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="F70" s="36"/>
+      <c r="F70" s="36" t="s">
+        <v>247</v>
+      </c>
       <c r="G70" s="36" t="s">
         <v>226</v>
       </c>
@@ -4454,7 +4586,9 @@
       <c r="E71" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="F71" s="36"/>
+      <c r="F71" s="36" t="s">
+        <v>247</v>
+      </c>
       <c r="G71" s="36" t="s">
         <v>226</v>
       </c>
@@ -4495,7 +4629,9 @@
       <c r="E72" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F72" s="36"/>
+      <c r="F72" s="36" t="s">
+        <v>247</v>
+      </c>
       <c r="G72" s="36" t="s">
         <v>226</v>
       </c>
@@ -4536,7 +4672,9 @@
       <c r="E73" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="F73" s="36"/>
+      <c r="F73" s="36" t="s">
+        <v>247</v>
+      </c>
       <c r="G73" s="36" t="s">
         <v>226</v>
       </c>
@@ -4577,7 +4715,9 @@
       <c r="E74" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="F74" s="36"/>
+      <c r="F74" s="36" t="s">
+        <v>247</v>
+      </c>
       <c r="G74" s="36" t="s">
         <v>226</v>
       </c>
@@ -4618,7 +4758,9 @@
       <c r="E75" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="F75" s="47"/>
+      <c r="F75" s="47" t="s">
+        <v>247</v>
+      </c>
       <c r="G75" s="47" t="s">
         <v>227</v>
       </c>
@@ -4657,7 +4799,9 @@
       <c r="E76" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="F76" s="47"/>
+      <c r="F76" s="47" t="s">
+        <v>247</v>
+      </c>
       <c r="G76" s="47" t="s">
         <v>227</v>
       </c>
@@ -4697,7 +4841,9 @@
       <c r="E77" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="F77" s="47"/>
+      <c r="F77" s="47" t="s">
+        <v>247</v>
+      </c>
       <c r="G77" s="47" t="s">
         <v>227</v>
       </c>
@@ -4737,7 +4883,9 @@
       <c r="E78" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="F78" s="47"/>
+      <c r="F78" s="47" t="s">
+        <v>247</v>
+      </c>
       <c r="G78" s="47" t="s">
         <v>227</v>
       </c>
@@ -4777,7 +4925,9 @@
       <c r="E79" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="F79" s="47"/>
+      <c r="F79" s="47" t="s">
+        <v>247</v>
+      </c>
       <c r="G79" s="47" t="s">
         <v>227</v>
       </c>
@@ -4817,7 +4967,9 @@
       <c r="E80" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="F80" s="47"/>
+      <c r="F80" s="47" t="s">
+        <v>247</v>
+      </c>
       <c r="G80" s="47" t="s">
         <v>227</v>
       </c>
@@ -4857,7 +5009,9 @@
       <c r="E81" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="F81" s="47"/>
+      <c r="F81" s="47" t="s">
+        <v>247</v>
+      </c>
       <c r="G81" s="47" t="s">
         <v>227</v>
       </c>
@@ -4897,7 +5051,9 @@
       <c r="E82" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="F82" s="49"/>
+      <c r="F82" s="49" t="s">
+        <v>248</v>
+      </c>
       <c r="G82" s="49" t="s">
         <v>228</v>
       </c>
@@ -4936,7 +5092,9 @@
       <c r="E83" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="F83" s="49"/>
+      <c r="F83" s="49" t="s">
+        <v>248</v>
+      </c>
       <c r="G83" s="49" t="s">
         <v>228</v>
       </c>
@@ -4976,7 +5134,9 @@
       <c r="E84" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="F84" s="49"/>
+      <c r="F84" s="49" t="s">
+        <v>248</v>
+      </c>
       <c r="G84" s="49" t="s">
         <v>228</v>
       </c>
@@ -5016,7 +5176,9 @@
       <c r="E85" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="F85" s="49"/>
+      <c r="F85" s="49" t="s">
+        <v>248</v>
+      </c>
       <c r="G85" s="49" t="s">
         <v>228</v>
       </c>
@@ -5056,7 +5218,9 @@
       <c r="E86" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="F86" s="49"/>
+      <c r="F86" s="49" t="s">
+        <v>248</v>
+      </c>
       <c r="G86" s="49" t="s">
         <v>228</v>
       </c>
@@ -5096,7 +5260,9 @@
       <c r="E87" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="F87" s="49"/>
+      <c r="F87" s="49" t="s">
+        <v>248</v>
+      </c>
       <c r="G87" s="49" t="s">
         <v>228</v>
       </c>
@@ -5136,7 +5302,9 @@
       <c r="E88" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="F88" s="49"/>
+      <c r="F88" s="49" t="s">
+        <v>248</v>
+      </c>
       <c r="G88" s="49" t="s">
         <v>228</v>
       </c>
@@ -5176,7 +5344,9 @@
       <c r="E89" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="F89" s="52"/>
+      <c r="F89" s="52" t="s">
+        <v>250</v>
+      </c>
       <c r="G89" s="52" t="s">
         <v>230</v>
       </c>
@@ -5215,7 +5385,9 @@
       <c r="E90" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="F90" s="52"/>
+      <c r="F90" s="52" t="s">
+        <v>250</v>
+      </c>
       <c r="G90" s="52" t="s">
         <v>230</v>
       </c>
@@ -5255,7 +5427,9 @@
       <c r="E91" s="52" t="s">
         <v>120</v>
       </c>
-      <c r="F91" s="52"/>
+      <c r="F91" s="52" t="s">
+        <v>250</v>
+      </c>
       <c r="G91" s="52" t="s">
         <v>230</v>
       </c>
@@ -5295,7 +5469,9 @@
       <c r="E92" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="F92" s="52"/>
+      <c r="F92" s="52" t="s">
+        <v>250</v>
+      </c>
       <c r="G92" s="52" t="s">
         <v>230</v>
       </c>
@@ -5335,7 +5511,9 @@
       <c r="E93" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="F93" s="52"/>
+      <c r="F93" s="52" t="s">
+        <v>250</v>
+      </c>
       <c r="G93" s="52" t="s">
         <v>230</v>
       </c>
@@ -5375,7 +5553,9 @@
       <c r="E94" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="F94" s="52"/>
+      <c r="F94" s="52" t="s">
+        <v>250</v>
+      </c>
       <c r="G94" s="52" t="s">
         <v>230</v>
       </c>
@@ -5415,7 +5595,9 @@
       <c r="E95" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="F95" s="52"/>
+      <c r="F95" s="52" t="s">
+        <v>250</v>
+      </c>
       <c r="G95" s="52" t="s">
         <v>230</v>
       </c>
@@ -5455,7 +5637,9 @@
       <c r="E96" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F96" s="24"/>
+      <c r="F96" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G96" s="24" t="s">
         <v>213</v>
       </c>
@@ -5492,7 +5676,9 @@
       <c r="E97" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F97" s="24"/>
+      <c r="F97" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G97" s="24" t="s">
         <v>213</v>
       </c>
@@ -5530,7 +5716,9 @@
       <c r="E98" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="F98" s="24"/>
+      <c r="F98" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G98" s="24" t="s">
         <v>213</v>
       </c>
@@ -5568,7 +5756,9 @@
       <c r="E99" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F99" s="24"/>
+      <c r="F99" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G99" s="24" t="s">
         <v>213</v>
       </c>
@@ -5606,7 +5796,9 @@
       <c r="E100" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F100" s="24"/>
+      <c r="F100" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G100" s="24" t="s">
         <v>213</v>
       </c>
@@ -5644,7 +5836,9 @@
       <c r="E101" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="F101" s="24"/>
+      <c r="F101" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G101" s="24" t="s">
         <v>213</v>
       </c>
@@ -5682,7 +5876,9 @@
       <c r="E102" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="F102" s="24"/>
+      <c r="F102" s="24" t="s">
+        <v>246</v>
+      </c>
       <c r="G102" s="24" t="s">
         <v>213</v>
       </c>
@@ -5720,7 +5916,9 @@
       <c r="E103" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="F103" s="55"/>
+      <c r="F103" s="55" t="s">
+        <v>250</v>
+      </c>
       <c r="G103" s="55" t="s">
         <v>231</v>
       </c>
@@ -5759,7 +5957,9 @@
       <c r="E104" s="55" t="s">
         <v>96</v>
       </c>
-      <c r="F104" s="55"/>
+      <c r="F104" s="55" t="s">
+        <v>250</v>
+      </c>
       <c r="G104" s="55" t="s">
         <v>231</v>
       </c>
@@ -5799,7 +5999,9 @@
       <c r="E105" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="F105" s="55"/>
+      <c r="F105" s="55" t="s">
+        <v>250</v>
+      </c>
       <c r="G105" s="55" t="s">
         <v>231</v>
       </c>
@@ -5839,7 +6041,9 @@
       <c r="E106" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="F106" s="55"/>
+      <c r="F106" s="55" t="s">
+        <v>250</v>
+      </c>
       <c r="G106" s="55" t="s">
         <v>231</v>
       </c>
@@ -5879,7 +6083,9 @@
       <c r="E107" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="F107" s="55"/>
+      <c r="F107" s="55" t="s">
+        <v>250</v>
+      </c>
       <c r="G107" s="55" t="s">
         <v>231</v>
       </c>
@@ -5919,7 +6125,9 @@
       <c r="E108" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="F108" s="55"/>
+      <c r="F108" s="55" t="s">
+        <v>250</v>
+      </c>
       <c r="G108" s="55" t="s">
         <v>231</v>
       </c>
@@ -5959,7 +6167,9 @@
       <c r="E109" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="F109" s="55"/>
+      <c r="F109" s="55" t="s">
+        <v>250</v>
+      </c>
       <c r="G109" s="55" t="s">
         <v>231</v>
       </c>
@@ -6947,7 +7157,9 @@
       <c r="E138" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="F138" s="66"/>
+      <c r="F138" s="66" t="s">
+        <v>251</v>
+      </c>
       <c r="G138" s="66" t="s">
         <v>236</v>
       </c>
@@ -6984,7 +7196,9 @@
       <c r="E139" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="F139" s="66"/>
+      <c r="F139" s="66" t="s">
+        <v>251</v>
+      </c>
       <c r="G139" s="66" t="s">
         <v>236</v>
       </c>
@@ -7022,7 +7236,9 @@
       <c r="E140" s="66" t="s">
         <v>152</v>
       </c>
-      <c r="F140" s="66"/>
+      <c r="F140" s="66" t="s">
+        <v>251</v>
+      </c>
       <c r="G140" s="66" t="s">
         <v>236</v>
       </c>
@@ -7060,7 +7276,9 @@
       <c r="E141" s="66" t="s">
         <v>140</v>
       </c>
-      <c r="F141" s="66"/>
+      <c r="F141" s="66" t="s">
+        <v>251</v>
+      </c>
       <c r="G141" s="66" t="s">
         <v>236</v>
       </c>
@@ -7098,7 +7316,9 @@
       <c r="E142" s="66" t="s">
         <v>233</v>
       </c>
-      <c r="F142" s="66"/>
+      <c r="F142" s="66" t="s">
+        <v>251</v>
+      </c>
       <c r="G142" s="66" t="s">
         <v>236</v>
       </c>
@@ -7136,7 +7356,9 @@
       <c r="E143" s="66" t="s">
         <v>234</v>
       </c>
-      <c r="F143" s="66"/>
+      <c r="F143" s="66" t="s">
+        <v>251</v>
+      </c>
       <c r="G143" s="66" t="s">
         <v>236</v>
       </c>
@@ -7174,7 +7396,9 @@
       <c r="E144" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="F144" s="66"/>
+      <c r="F144" s="66" t="s">
+        <v>251</v>
+      </c>
       <c r="G144" s="66" t="s">
         <v>236</v>
       </c>
@@ -7212,7 +7436,9 @@
       <c r="E145" s="69" t="s">
         <v>150</v>
       </c>
-      <c r="F145" s="69"/>
+      <c r="F145" s="69" t="s">
+        <v>251</v>
+      </c>
       <c r="G145" s="66" t="s">
         <v>236</v>
       </c>
@@ -7249,7 +7475,9 @@
       <c r="E146" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="F146" s="69"/>
+      <c r="F146" s="69" t="s">
+        <v>251</v>
+      </c>
       <c r="G146" s="66" t="s">
         <v>236</v>
       </c>
@@ -7287,7 +7515,9 @@
       <c r="E147" s="69" t="s">
         <v>235</v>
       </c>
-      <c r="F147" s="69"/>
+      <c r="F147" s="69" t="s">
+        <v>251</v>
+      </c>
       <c r="G147" s="66" t="s">
         <v>236</v>
       </c>
@@ -7325,7 +7555,9 @@
       <c r="E148" s="69" t="s">
         <v>140</v>
       </c>
-      <c r="F148" s="69"/>
+      <c r="F148" s="69" t="s">
+        <v>251</v>
+      </c>
       <c r="G148" s="66" t="s">
         <v>236</v>
       </c>
@@ -7363,7 +7595,9 @@
       <c r="E149" s="69" t="s">
         <v>233</v>
       </c>
-      <c r="F149" s="69"/>
+      <c r="F149" s="69" t="s">
+        <v>251</v>
+      </c>
       <c r="G149" s="66" t="s">
         <v>236</v>
       </c>
@@ -7401,7 +7635,9 @@
       <c r="E150" s="69" t="s">
         <v>234</v>
       </c>
-      <c r="F150" s="69"/>
+      <c r="F150" s="69" t="s">
+        <v>251</v>
+      </c>
       <c r="G150" s="66" t="s">
         <v>236</v>
       </c>
@@ -7439,7 +7675,9 @@
       <c r="E151" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="F151" s="69"/>
+      <c r="F151" s="69" t="s">
+        <v>251</v>
+      </c>
       <c r="G151" s="66" t="s">
         <v>236</v>
       </c>
@@ -7477,7 +7715,9 @@
       <c r="E152" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="F152" s="73"/>
+      <c r="F152" s="73" t="s">
+        <v>252</v>
+      </c>
       <c r="G152" s="73" t="s">
         <v>238</v>
       </c>
@@ -7514,7 +7754,9 @@
       <c r="E153" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="F153" s="73"/>
+      <c r="F153" s="73" t="s">
+        <v>252</v>
+      </c>
       <c r="G153" s="73" t="s">
         <v>238</v>
       </c>
@@ -7552,7 +7794,9 @@
       <c r="E154" s="73" t="s">
         <v>145</v>
       </c>
-      <c r="F154" s="73"/>
+      <c r="F154" s="73" t="s">
+        <v>252</v>
+      </c>
       <c r="G154" s="73" t="s">
         <v>238</v>
       </c>
@@ -7590,7 +7834,9 @@
       <c r="E155" s="73" t="s">
         <v>146</v>
       </c>
-      <c r="F155" s="73"/>
+      <c r="F155" s="73" t="s">
+        <v>252</v>
+      </c>
       <c r="G155" s="73" t="s">
         <v>238</v>
       </c>
@@ -7628,7 +7874,9 @@
       <c r="E156" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="F156" s="73"/>
+      <c r="F156" s="73" t="s">
+        <v>252</v>
+      </c>
       <c r="G156" s="73" t="s">
         <v>238</v>
       </c>
@@ -7666,7 +7914,9 @@
       <c r="E157" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="F157" s="73"/>
+      <c r="F157" s="73" t="s">
+        <v>252</v>
+      </c>
       <c r="G157" s="73" t="s">
         <v>238</v>
       </c>
@@ -7704,7 +7954,9 @@
       <c r="E158" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="F158" s="73"/>
+      <c r="F158" s="73" t="s">
+        <v>252</v>
+      </c>
       <c r="G158" s="73" t="s">
         <v>238</v>
       </c>
@@ -7742,7 +7994,9 @@
       <c r="E159" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="F159" s="76"/>
+      <c r="F159" s="76" t="s">
+        <v>252</v>
+      </c>
       <c r="G159" s="76" t="s">
         <v>238</v>
       </c>
@@ -7779,7 +8033,9 @@
       <c r="E160" s="76" t="s">
         <v>144</v>
       </c>
-      <c r="F160" s="76"/>
+      <c r="F160" s="76" t="s">
+        <v>252</v>
+      </c>
       <c r="G160" s="76" t="s">
         <v>238</v>
       </c>
@@ -7817,7 +8073,9 @@
       <c r="E161" s="76" t="s">
         <v>145</v>
       </c>
-      <c r="F161" s="76"/>
+      <c r="F161" s="76" t="s">
+        <v>252</v>
+      </c>
       <c r="G161" s="76" t="s">
         <v>238</v>
       </c>
@@ -7855,7 +8113,9 @@
       <c r="E162" s="76" t="s">
         <v>146</v>
       </c>
-      <c r="F162" s="76"/>
+      <c r="F162" s="76" t="s">
+        <v>252</v>
+      </c>
       <c r="G162" s="76" t="s">
         <v>238</v>
       </c>
@@ -7893,7 +8153,9 @@
       <c r="E163" s="76" t="s">
         <v>147</v>
       </c>
-      <c r="F163" s="76"/>
+      <c r="F163" s="76" t="s">
+        <v>252</v>
+      </c>
       <c r="G163" s="76" t="s">
         <v>238</v>
       </c>
@@ -7931,7 +8193,9 @@
       <c r="E164" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="F164" s="76"/>
+      <c r="F164" s="76" t="s">
+        <v>252</v>
+      </c>
       <c r="G164" s="76" t="s">
         <v>238</v>
       </c>
@@ -7969,7 +8233,9 @@
       <c r="E165" s="76" t="s">
         <v>42</v>
       </c>
-      <c r="F165" s="76"/>
+      <c r="F165" s="76" t="s">
+        <v>252</v>
+      </c>
       <c r="G165" s="76" t="s">
         <v>238</v>
       </c>
@@ -8007,7 +8273,9 @@
       <c r="E166" s="78" t="s">
         <v>150</v>
       </c>
-      <c r="F166" s="78"/>
+      <c r="F166" s="78" t="s">
+        <v>248</v>
+      </c>
       <c r="G166" s="78" t="s">
         <v>239</v>
       </c>
@@ -8044,7 +8312,9 @@
       <c r="E167" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="F167" s="78"/>
+      <c r="F167" s="78" t="s">
+        <v>248</v>
+      </c>
       <c r="G167" s="78" t="s">
         <v>239</v>
       </c>
@@ -8082,7 +8352,9 @@
       <c r="E168" s="78" t="s">
         <v>152</v>
       </c>
-      <c r="F168" s="78"/>
+      <c r="F168" s="78" t="s">
+        <v>248</v>
+      </c>
       <c r="G168" s="78" t="s">
         <v>239</v>
       </c>
@@ -8120,7 +8392,9 @@
       <c r="E169" s="78" t="s">
         <v>153</v>
       </c>
-      <c r="F169" s="78"/>
+      <c r="F169" s="78" t="s">
+        <v>248</v>
+      </c>
       <c r="G169" s="78" t="s">
         <v>239</v>
       </c>
@@ -8158,7 +8432,9 @@
       <c r="E170" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="F170" s="78"/>
+      <c r="F170" s="78" t="s">
+        <v>248</v>
+      </c>
       <c r="G170" s="78" t="s">
         <v>239</v>
       </c>
@@ -8196,7 +8472,9 @@
       <c r="E171" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="F171" s="78"/>
+      <c r="F171" s="78" t="s">
+        <v>248</v>
+      </c>
       <c r="G171" s="78" t="s">
         <v>239</v>
       </c>
@@ -8234,7 +8512,9 @@
       <c r="E172" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="F172" s="78"/>
+      <c r="F172" s="78" t="s">
+        <v>248</v>
+      </c>
       <c r="G172" s="78" t="s">
         <v>239</v>
       </c>
@@ -8272,7 +8552,9 @@
       <c r="E173" s="82" t="s">
         <v>155</v>
       </c>
-      <c r="F173" s="82"/>
+      <c r="F173" s="82" t="s">
+        <v>248</v>
+      </c>
       <c r="G173" s="82" t="s">
         <v>241</v>
       </c>
@@ -8309,7 +8591,9 @@
       <c r="E174" s="82" t="s">
         <v>156</v>
       </c>
-      <c r="F174" s="82"/>
+      <c r="F174" s="82" t="s">
+        <v>248</v>
+      </c>
       <c r="G174" s="82" t="s">
         <v>241</v>
       </c>
@@ -8347,7 +8631,9 @@
       <c r="E175" s="82" t="s">
         <v>157</v>
       </c>
-      <c r="F175" s="82"/>
+      <c r="F175" s="82" t="s">
+        <v>248</v>
+      </c>
       <c r="G175" s="82" t="s">
         <v>241</v>
       </c>
@@ -8385,7 +8671,9 @@
       <c r="E176" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="F176" s="82"/>
+      <c r="F176" s="82" t="s">
+        <v>248</v>
+      </c>
       <c r="G176" s="82" t="s">
         <v>241</v>
       </c>
@@ -8423,7 +8711,9 @@
       <c r="E177" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="F177" s="82"/>
+      <c r="F177" s="82" t="s">
+        <v>248</v>
+      </c>
       <c r="G177" s="82" t="s">
         <v>241</v>
       </c>
@@ -8461,7 +8751,9 @@
       <c r="E178" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="F178" s="82"/>
+      <c r="F178" s="82" t="s">
+        <v>248</v>
+      </c>
       <c r="G178" s="82" t="s">
         <v>241</v>
       </c>
@@ -8499,7 +8791,9 @@
       <c r="E179" s="82" t="s">
         <v>111</v>
       </c>
-      <c r="F179" s="82"/>
+      <c r="F179" s="82" t="s">
+        <v>248</v>
+      </c>
       <c r="G179" s="82" t="s">
         <v>241</v>
       </c>
@@ -9010,7 +9304,9 @@
       <c r="E194" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="F194" s="69"/>
+      <c r="F194" s="69" t="s">
+        <v>248</v>
+      </c>
       <c r="G194" s="69" t="s">
         <v>244</v>
       </c>
@@ -9049,7 +9345,9 @@
       <c r="E195" s="69" t="s">
         <v>177</v>
       </c>
-      <c r="F195" s="69"/>
+      <c r="F195" s="69" t="s">
+        <v>248</v>
+      </c>
       <c r="G195" s="69" t="s">
         <v>244</v>
       </c>
@@ -9090,7 +9388,9 @@
       <c r="E196" s="69" t="s">
         <v>178</v>
       </c>
-      <c r="F196" s="69"/>
+      <c r="F196" s="69" t="s">
+        <v>248</v>
+      </c>
       <c r="G196" s="69" t="s">
         <v>244</v>
       </c>
@@ -9131,7 +9431,9 @@
       <c r="E197" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="F197" s="69"/>
+      <c r="F197" s="69" t="s">
+        <v>248</v>
+      </c>
       <c r="G197" s="69" t="s">
         <v>244</v>
       </c>
@@ -9172,7 +9474,9 @@
       <c r="E198" s="69" t="s">
         <v>179</v>
       </c>
-      <c r="F198" s="69"/>
+      <c r="F198" s="69" t="s">
+        <v>248</v>
+      </c>
       <c r="G198" s="69" t="s">
         <v>244</v>
       </c>
@@ -9213,7 +9517,9 @@
       <c r="E199" s="69" t="s">
         <v>180</v>
       </c>
-      <c r="F199" s="69"/>
+      <c r="F199" s="69" t="s">
+        <v>248</v>
+      </c>
       <c r="G199" s="69" t="s">
         <v>244</v>
       </c>
@@ -9254,7 +9560,9 @@
       <c r="E200" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="F200" s="69"/>
+      <c r="F200" s="69" t="s">
+        <v>248</v>
+      </c>
       <c r="G200" s="69" t="s">
         <v>244</v>
       </c>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -246,7 +246,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="263">
   <si>
     <t>id</t>
   </si>
@@ -761,7 +761,7 @@
     <t>1_9590|2_200|3_200|4_10</t>
   </si>
   <si>
-    <t>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-3700|1200&amp;1400-3700|1400&amp;1600-3700|1600&amp;1800-3700|1800&amp;2000-3700|2000&amp;2400-3700|2400&amp;2800-3700|2800&amp;3200-3700|3200&amp;3600-3700|3600&amp;4000-3700|4000&amp;4800-3700|4800&amp;5600-3700|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-100|1400&amp;1600-100|1600&amp;1800-100|1800&amp;2000-100|2000&amp;2400-100|2400&amp;2800-100|2800&amp;3200-100|3200&amp;3600-100|3600&amp;4000-100|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-100|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
+    <t>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
   </si>
   <si>
     <t>1_9660|2_170|3_170|4_10</t>
@@ -951,6 +951,12 @@
   </si>
   <si>
     <t>1_9930|2_20|3_50</t>
+  </si>
+  <si>
+    <t>嗨到底</t>
+  </si>
+  <si>
+    <t>狂野沙滩</t>
   </si>
   <si>
     <t>超级高尔夫</t>
@@ -1218,18 +1224,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="56">
+  <fills count="58">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1359,6 +1365,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1691,7 +1709,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1715,16 +1733,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1733,90 +1751,90 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2092,6 +2110,30 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2107,30 +2149,30 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2463,7 +2505,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M277"/>
+  <dimension ref="A1:M291"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
@@ -7633,7 +7675,7 @@
       <c r="I139" s="26"/>
       <c r="J139" s="77" t="str">
         <f t="shared" ref="J139:J144" si="18">J138</f>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-3700|1200&amp;1400-3700|1400&amp;1600-3700|1600&amp;1800-3700|1800&amp;2000-3700|2000&amp;2400-3700|2400&amp;2800-3700|2800&amp;3200-3700|3200&amp;3600-3700|3600&amp;4000-3700|4000&amp;4800-3700|4800&amp;5600-3700|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-100|1400&amp;1600-100|1600&amp;1800-100|1800&amp;2000-100|2000&amp;2400-100|2400&amp;2800-100|2800&amp;3200-100|3200&amp;3600-100|3600&amp;4000-100|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-100|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K139" s="31">
         <v>6000</v>
@@ -7667,7 +7709,7 @@
       <c r="I140" s="26"/>
       <c r="J140" s="77" t="str">
         <f t="shared" si="18"/>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-3700|1200&amp;1400-3700|1400&amp;1600-3700|1600&amp;1800-3700|1800&amp;2000-3700|2000&amp;2400-3700|2400&amp;2800-3700|2800&amp;3200-3700|3200&amp;3600-3700|3600&amp;4000-3700|4000&amp;4800-3700|4800&amp;5600-3700|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-100|1400&amp;1600-100|1600&amp;1800-100|1800&amp;2000-100|2000&amp;2400-100|2400&amp;2800-100|2800&amp;3200-100|3200&amp;3600-100|3600&amp;4000-100|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-100|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K140" s="31">
         <v>4000</v>
@@ -7701,7 +7743,7 @@
       <c r="I141" s="26"/>
       <c r="J141" s="77" t="str">
         <f t="shared" si="18"/>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-3700|1200&amp;1400-3700|1400&amp;1600-3700|1600&amp;1800-3700|1800&amp;2000-3700|2000&amp;2400-3700|2400&amp;2800-3700|2800&amp;3200-3700|3200&amp;3600-3700|3600&amp;4000-3700|4000&amp;4800-3700|4800&amp;5600-3700|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-100|1400&amp;1600-100|1600&amp;1800-100|1800&amp;2000-100|2000&amp;2400-100|2400&amp;2800-100|2800&amp;3200-100|3200&amp;3600-100|3600&amp;4000-100|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-100|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K141" s="31">
         <v>2000</v>
@@ -7735,7 +7777,7 @@
       <c r="I142" s="26"/>
       <c r="J142" s="77" t="str">
         <f t="shared" si="18"/>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-3700|1200&amp;1400-3700|1400&amp;1600-3700|1600&amp;1800-3700|1800&amp;2000-3700|2000&amp;2400-3700|2400&amp;2800-3700|2800&amp;3200-3700|3200&amp;3600-3700|3600&amp;4000-3700|4000&amp;4800-3700|4800&amp;5600-3700|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-100|1400&amp;1600-100|1600&amp;1800-100|1800&amp;2000-100|2000&amp;2400-100|2400&amp;2800-100|2800&amp;3200-100|3200&amp;3600-100|3600&amp;4000-100|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-100|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K142" s="31">
         <v>0</v>
@@ -7769,7 +7811,7 @@
       <c r="I143" s="26"/>
       <c r="J143" s="77" t="str">
         <f t="shared" si="18"/>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-3700|1200&amp;1400-3700|1400&amp;1600-3700|1600&amp;1800-3700|1800&amp;2000-3700|2000&amp;2400-3700|2400&amp;2800-3700|2800&amp;3200-3700|3200&amp;3600-3700|3600&amp;4000-3700|4000&amp;4800-3700|4800&amp;5600-3700|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-100|1400&amp;1600-100|1600&amp;1800-100|1800&amp;2000-100|2000&amp;2400-100|2400&amp;2800-100|2800&amp;3200-100|3200&amp;3600-100|3600&amp;4000-100|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-100|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K143" s="31">
         <v>-1000</v>
@@ -7803,7 +7845,7 @@
       <c r="I144" s="26"/>
       <c r="J144" s="77" t="str">
         <f t="shared" si="18"/>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-3700|1200&amp;1400-3700|1400&amp;1600-3700|1600&amp;1800-3700|1800&amp;2000-3700|2000&amp;2400-3700|2400&amp;2800-3700|2800&amp;3200-3700|3200&amp;3600-3700|3600&amp;4000-3700|4000&amp;4800-3700|4800&amp;5600-3700|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-100|1400&amp;1600-100|1600&amp;1800-100|1800&amp;2000-100|2000&amp;2400-100|2400&amp;2800-100|2800&amp;3200-100|3200&amp;3600-100|3600&amp;4000-100|4000&amp;4800-100|4800&amp;5600-100|5600&amp;6400-100|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K144" s="31">
         <v>-999999</v>
@@ -10165,489 +10207,489 @@
       </c>
     </row>
     <row r="208" s="3" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A208" s="106">
+      <c r="A208" s="107">
+        <v>41001</v>
+      </c>
+      <c r="B208" s="107">
+        <v>104100</v>
+      </c>
+      <c r="C208" s="107" t="s">
+        <v>235</v>
+      </c>
+      <c r="D208" s="107">
+        <v>1</v>
+      </c>
+      <c r="E208" s="108" t="s">
+        <v>67</v>
+      </c>
+      <c r="F208" s="108"/>
+      <c r="G208" s="108"/>
+      <c r="H208" s="108"/>
+      <c r="I208" s="26"/>
+      <c r="J208" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="K208" s="110">
+        <v>8000</v>
+      </c>
+      <c r="L208" s="110">
+        <v>999999</v>
+      </c>
+      <c r="M208" s="110" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="209" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A209" s="107">
+        <v>41002</v>
+      </c>
+      <c r="B209" s="107">
+        <v>104100</v>
+      </c>
+      <c r="C209" s="107" t="s">
+        <v>235</v>
+      </c>
+      <c r="D209" s="107">
+        <v>2</v>
+      </c>
+      <c r="E209" s="108" t="s">
+        <v>69</v>
+      </c>
+      <c r="F209" s="108"/>
+      <c r="G209" s="108"/>
+      <c r="H209" s="108"/>
+      <c r="I209" s="26"/>
+      <c r="J209" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="K209" s="110">
+        <v>6000</v>
+      </c>
+      <c r="L209" s="110">
+        <v>8000</v>
+      </c>
+      <c r="M209" s="110" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="210" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A210" s="107">
+        <v>41003</v>
+      </c>
+      <c r="B210" s="107">
+        <v>104100</v>
+      </c>
+      <c r="C210" s="107" t="s">
+        <v>235</v>
+      </c>
+      <c r="D210" s="107">
+        <v>3</v>
+      </c>
+      <c r="E210" s="108" t="s">
+        <v>70</v>
+      </c>
+      <c r="F210" s="108"/>
+      <c r="G210" s="108"/>
+      <c r="H210" s="108"/>
+      <c r="I210" s="26"/>
+      <c r="J210" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="K210" s="110">
+        <v>4000</v>
+      </c>
+      <c r="L210" s="110">
+        <v>6000</v>
+      </c>
+      <c r="M210" s="110" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="211" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A211" s="107">
+        <v>41004</v>
+      </c>
+      <c r="B211" s="107">
+        <v>104100</v>
+      </c>
+      <c r="C211" s="107" t="s">
+        <v>235</v>
+      </c>
+      <c r="D211" s="107">
+        <v>4</v>
+      </c>
+      <c r="E211" s="108" t="s">
+        <v>71</v>
+      </c>
+      <c r="F211" s="108"/>
+      <c r="G211" s="108"/>
+      <c r="H211" s="108"/>
+      <c r="I211" s="26"/>
+      <c r="J211" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="K211" s="110">
+        <v>2000</v>
+      </c>
+      <c r="L211" s="110">
+        <v>4000</v>
+      </c>
+      <c r="M211" s="110" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="212" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A212" s="107">
+        <v>41005</v>
+      </c>
+      <c r="B212" s="107">
+        <v>104100</v>
+      </c>
+      <c r="C212" s="107" t="s">
+        <v>235</v>
+      </c>
+      <c r="D212" s="107">
+        <v>5</v>
+      </c>
+      <c r="E212" s="108" t="s">
+        <v>72</v>
+      </c>
+      <c r="F212" s="108"/>
+      <c r="G212" s="108"/>
+      <c r="H212" s="108"/>
+      <c r="I212" s="26"/>
+      <c r="J212" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="K212" s="110">
+        <v>0</v>
+      </c>
+      <c r="L212" s="110">
+        <v>2000</v>
+      </c>
+      <c r="M212" s="110" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="213" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A213" s="107">
+        <v>41006</v>
+      </c>
+      <c r="B213" s="107">
+        <v>104100</v>
+      </c>
+      <c r="C213" s="107" t="s">
+        <v>235</v>
+      </c>
+      <c r="D213" s="107">
+        <v>6</v>
+      </c>
+      <c r="E213" s="108" t="s">
+        <v>73</v>
+      </c>
+      <c r="F213" s="108"/>
+      <c r="G213" s="108"/>
+      <c r="H213" s="108"/>
+      <c r="I213" s="26"/>
+      <c r="J213" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="K213" s="110">
+        <v>-1000</v>
+      </c>
+      <c r="L213" s="110">
+        <v>0</v>
+      </c>
+      <c r="M213" s="110" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="214" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A214" s="107">
+        <v>41007</v>
+      </c>
+      <c r="B214" s="107">
+        <v>104100</v>
+      </c>
+      <c r="C214" s="107" t="s">
+        <v>235</v>
+      </c>
+      <c r="D214" s="107">
+        <v>7</v>
+      </c>
+      <c r="E214" s="108" t="s">
+        <v>74</v>
+      </c>
+      <c r="F214" s="108"/>
+      <c r="G214" s="108"/>
+      <c r="H214" s="108"/>
+      <c r="I214" s="26"/>
+      <c r="J214" s="109" t="s">
+        <v>68</v>
+      </c>
+      <c r="K214" s="110">
+        <v>-999999</v>
+      </c>
+      <c r="L214" s="110">
+        <v>-1000</v>
+      </c>
+      <c r="M214" s="110" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="215" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A215" s="111">
+        <v>42001</v>
+      </c>
+      <c r="B215" s="111">
+        <v>104200</v>
+      </c>
+      <c r="C215" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D215" s="111">
+        <v>1</v>
+      </c>
+      <c r="E215" s="112" t="s">
+        <v>67</v>
+      </c>
+      <c r="F215" s="112"/>
+      <c r="G215" s="112"/>
+      <c r="H215" s="112"/>
+      <c r="I215" s="26"/>
+      <c r="J215" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="K215" s="110">
+        <v>8000</v>
+      </c>
+      <c r="L215" s="110">
+        <v>999999</v>
+      </c>
+      <c r="M215" s="114" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="216" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A216" s="111">
+        <v>42002</v>
+      </c>
+      <c r="B216" s="111">
+        <v>104200</v>
+      </c>
+      <c r="C216" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D216" s="111">
+        <v>2</v>
+      </c>
+      <c r="E216" s="112" t="s">
+        <v>69</v>
+      </c>
+      <c r="F216" s="112"/>
+      <c r="G216" s="112"/>
+      <c r="H216" s="112"/>
+      <c r="I216" s="26"/>
+      <c r="J216" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="K216" s="110">
+        <v>6000</v>
+      </c>
+      <c r="L216" s="110">
+        <v>8000</v>
+      </c>
+      <c r="M216" s="114" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="217" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A217" s="111">
+        <v>42003</v>
+      </c>
+      <c r="B217" s="111">
+        <v>104200</v>
+      </c>
+      <c r="C217" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D217" s="111">
+        <v>3</v>
+      </c>
+      <c r="E217" s="112" t="s">
+        <v>70</v>
+      </c>
+      <c r="F217" s="112"/>
+      <c r="G217" s="112"/>
+      <c r="H217" s="112"/>
+      <c r="I217" s="26"/>
+      <c r="J217" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="K217" s="110">
+        <v>4000</v>
+      </c>
+      <c r="L217" s="110">
+        <v>6000</v>
+      </c>
+      <c r="M217" s="114" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="218" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A218" s="111">
+        <v>42004</v>
+      </c>
+      <c r="B218" s="111">
+        <v>104200</v>
+      </c>
+      <c r="C218" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D218" s="111">
+        <v>4</v>
+      </c>
+      <c r="E218" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="F218" s="112"/>
+      <c r="G218" s="112"/>
+      <c r="H218" s="112"/>
+      <c r="I218" s="26"/>
+      <c r="J218" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="K218" s="110">
+        <v>2000</v>
+      </c>
+      <c r="L218" s="110">
+        <v>4000</v>
+      </c>
+      <c r="M218" s="114" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="219" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A219" s="111">
+        <v>42005</v>
+      </c>
+      <c r="B219" s="111">
+        <v>104200</v>
+      </c>
+      <c r="C219" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D219" s="111">
+        <v>5</v>
+      </c>
+      <c r="E219" s="112" t="s">
+        <v>72</v>
+      </c>
+      <c r="F219" s="112"/>
+      <c r="G219" s="112"/>
+      <c r="H219" s="112"/>
+      <c r="I219" s="26"/>
+      <c r="J219" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="K219" s="110">
+        <v>0</v>
+      </c>
+      <c r="L219" s="110">
+        <v>2000</v>
+      </c>
+      <c r="M219" s="114" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="220" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A220" s="111">
+        <v>42006</v>
+      </c>
+      <c r="B220" s="111">
+        <v>104200</v>
+      </c>
+      <c r="C220" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D220" s="111">
+        <v>6</v>
+      </c>
+      <c r="E220" s="112" t="s">
+        <v>73</v>
+      </c>
+      <c r="F220" s="112"/>
+      <c r="G220" s="112"/>
+      <c r="H220" s="112"/>
+      <c r="I220" s="26"/>
+      <c r="J220" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="K220" s="110">
+        <v>-1000</v>
+      </c>
+      <c r="L220" s="110">
+        <v>0</v>
+      </c>
+      <c r="M220" s="114" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="221" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A221" s="111">
+        <v>42007</v>
+      </c>
+      <c r="B221" s="111">
+        <v>104200</v>
+      </c>
+      <c r="C221" s="111" t="s">
+        <v>236</v>
+      </c>
+      <c r="D221" s="111">
+        <v>7</v>
+      </c>
+      <c r="E221" s="112" t="s">
+        <v>74</v>
+      </c>
+      <c r="F221" s="112"/>
+      <c r="G221" s="112"/>
+      <c r="H221" s="112"/>
+      <c r="I221" s="26"/>
+      <c r="J221" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="K221" s="110">
+        <v>-999999</v>
+      </c>
+      <c r="L221" s="110">
+        <v>-1000</v>
+      </c>
+      <c r="M221" s="114" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="222" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A222" s="106">
         <v>48001</v>
       </c>
-      <c r="B208" s="106">
+      <c r="B222" s="106">
         <v>104800</v>
       </c>
-      <c r="C208" s="106" t="s">
-        <v>235</v>
-      </c>
-      <c r="D208" s="106">
+      <c r="C222" s="106" t="s">
+        <v>237</v>
+      </c>
+      <c r="D222" s="106">
         <v>1</v>
       </c>
-      <c r="E208" s="38" t="s">
+      <c r="E222" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="F208" s="38"/>
-      <c r="G208" s="38"/>
-      <c r="H208" s="38"/>
-      <c r="I208" s="26"/>
-      <c r="J208" s="40" t="s">
+      <c r="F222" s="38"/>
+      <c r="G222" s="38"/>
+      <c r="H222" s="38"/>
+      <c r="I222" s="26"/>
+      <c r="J222" s="40" t="s">
         <v>68</v>
-      </c>
-      <c r="K208" s="31">
-        <v>8000</v>
-      </c>
-      <c r="L208" s="31">
-        <v>999999</v>
-      </c>
-      <c r="M208" s="37" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="209" s="3" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A209" s="106">
-        <v>48002</v>
-      </c>
-      <c r="B209" s="106">
-        <v>104800</v>
-      </c>
-      <c r="C209" s="106" t="s">
-        <v>235</v>
-      </c>
-      <c r="D209" s="106">
-        <v>2</v>
-      </c>
-      <c r="E209" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="F209" s="38"/>
-      <c r="G209" s="38"/>
-      <c r="H209" s="38"/>
-      <c r="I209" s="26"/>
-      <c r="J209" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K209" s="31">
-        <v>6000</v>
-      </c>
-      <c r="L209" s="31">
-        <v>8000</v>
-      </c>
-      <c r="M209" s="37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="210" s="3" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A210" s="106">
-        <v>48003</v>
-      </c>
-      <c r="B210" s="106">
-        <v>104800</v>
-      </c>
-      <c r="C210" s="106" t="s">
-        <v>235</v>
-      </c>
-      <c r="D210" s="106">
-        <v>3</v>
-      </c>
-      <c r="E210" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="F210" s="38"/>
-      <c r="G210" s="38"/>
-      <c r="H210" s="38"/>
-      <c r="I210" s="26"/>
-      <c r="J210" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K210" s="31">
-        <v>4000</v>
-      </c>
-      <c r="L210" s="31">
-        <v>6000</v>
-      </c>
-      <c r="M210" s="37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="211" s="3" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A211" s="106">
-        <v>48004</v>
-      </c>
-      <c r="B211" s="106">
-        <v>104800</v>
-      </c>
-      <c r="C211" s="106" t="s">
-        <v>235</v>
-      </c>
-      <c r="D211" s="106">
-        <v>4</v>
-      </c>
-      <c r="E211" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="F211" s="38"/>
-      <c r="G211" s="38"/>
-      <c r="H211" s="38"/>
-      <c r="I211" s="26"/>
-      <c r="J211" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K211" s="31">
-        <v>2000</v>
-      </c>
-      <c r="L211" s="31">
-        <v>4000</v>
-      </c>
-      <c r="M211" s="37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="212" s="3" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A212" s="106">
-        <v>48005</v>
-      </c>
-      <c r="B212" s="106">
-        <v>104800</v>
-      </c>
-      <c r="C212" s="106" t="s">
-        <v>235</v>
-      </c>
-      <c r="D212" s="106">
-        <v>5</v>
-      </c>
-      <c r="E212" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="F212" s="38"/>
-      <c r="G212" s="38"/>
-      <c r="H212" s="38"/>
-      <c r="I212" s="26"/>
-      <c r="J212" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K212" s="31">
-        <v>0</v>
-      </c>
-      <c r="L212" s="31">
-        <v>2000</v>
-      </c>
-      <c r="M212" s="37" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="213" s="3" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A213" s="106">
-        <v>48006</v>
-      </c>
-      <c r="B213" s="106">
-        <v>104800</v>
-      </c>
-      <c r="C213" s="106" t="s">
-        <v>235</v>
-      </c>
-      <c r="D213" s="106">
-        <v>6</v>
-      </c>
-      <c r="E213" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="F213" s="38"/>
-      <c r="G213" s="38"/>
-      <c r="H213" s="38"/>
-      <c r="I213" s="26"/>
-      <c r="J213" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K213" s="31">
-        <v>-1000</v>
-      </c>
-      <c r="L213" s="31">
-        <v>0</v>
-      </c>
-      <c r="M213" s="37" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="214" s="3" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A214" s="106">
-        <v>48007</v>
-      </c>
-      <c r="B214" s="106">
-        <v>104800</v>
-      </c>
-      <c r="C214" s="106" t="s">
-        <v>235</v>
-      </c>
-      <c r="D214" s="106">
-        <v>7</v>
-      </c>
-      <c r="E214" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="F214" s="38"/>
-      <c r="G214" s="38"/>
-      <c r="H214" s="38"/>
-      <c r="I214" s="26"/>
-      <c r="J214" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K214" s="31">
-        <v>-999999</v>
-      </c>
-      <c r="L214" s="31">
-        <v>-1000</v>
-      </c>
-      <c r="M214" s="37" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="215" s="18" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A215" s="96">
-        <v>50001</v>
-      </c>
-      <c r="B215" s="96">
-        <v>105000</v>
-      </c>
-      <c r="C215" s="96" t="s">
-        <v>236</v>
-      </c>
-      <c r="D215" s="96">
-        <v>1</v>
-      </c>
-      <c r="E215" s="98" t="s">
-        <v>67</v>
-      </c>
-      <c r="F215" s="98"/>
-      <c r="G215" s="98"/>
-      <c r="H215" s="98"/>
-      <c r="I215" s="26"/>
-      <c r="J215" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="K215" s="31">
-        <v>8000</v>
-      </c>
-      <c r="L215" s="31">
-        <v>999999</v>
-      </c>
-      <c r="M215" s="100" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="216" s="18" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A216" s="96">
-        <v>50002</v>
-      </c>
-      <c r="B216" s="96">
-        <v>105000</v>
-      </c>
-      <c r="C216" s="96" t="s">
-        <v>236</v>
-      </c>
-      <c r="D216" s="96">
-        <v>2</v>
-      </c>
-      <c r="E216" s="98" t="s">
-        <v>69</v>
-      </c>
-      <c r="F216" s="98"/>
-      <c r="G216" s="98"/>
-      <c r="H216" s="98"/>
-      <c r="I216" s="26"/>
-      <c r="J216" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="K216" s="31">
-        <v>6000</v>
-      </c>
-      <c r="L216" s="31">
-        <v>8000</v>
-      </c>
-      <c r="M216" s="100" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="217" s="18" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A217" s="96">
-        <v>50003</v>
-      </c>
-      <c r="B217" s="96">
-        <v>105000</v>
-      </c>
-      <c r="C217" s="96" t="s">
-        <v>236</v>
-      </c>
-      <c r="D217" s="96">
-        <v>3</v>
-      </c>
-      <c r="E217" s="98" t="s">
-        <v>70</v>
-      </c>
-      <c r="F217" s="98"/>
-      <c r="G217" s="98"/>
-      <c r="H217" s="98"/>
-      <c r="I217" s="26"/>
-      <c r="J217" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="K217" s="31">
-        <v>4000</v>
-      </c>
-      <c r="L217" s="31">
-        <v>6000</v>
-      </c>
-      <c r="M217" s="100" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="218" s="18" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A218" s="96">
-        <v>50004</v>
-      </c>
-      <c r="B218" s="96">
-        <v>105000</v>
-      </c>
-      <c r="C218" s="96" t="s">
-        <v>236</v>
-      </c>
-      <c r="D218" s="96">
-        <v>4</v>
-      </c>
-      <c r="E218" s="98" t="s">
-        <v>71</v>
-      </c>
-      <c r="F218" s="98"/>
-      <c r="G218" s="98"/>
-      <c r="H218" s="98"/>
-      <c r="I218" s="26"/>
-      <c r="J218" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="K218" s="31">
-        <v>2000</v>
-      </c>
-      <c r="L218" s="31">
-        <v>4000</v>
-      </c>
-      <c r="M218" s="100" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="219" s="18" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A219" s="96">
-        <v>50005</v>
-      </c>
-      <c r="B219" s="96">
-        <v>105000</v>
-      </c>
-      <c r="C219" s="96" t="s">
-        <v>236</v>
-      </c>
-      <c r="D219" s="96">
-        <v>5</v>
-      </c>
-      <c r="E219" s="98" t="s">
-        <v>72</v>
-      </c>
-      <c r="F219" s="98"/>
-      <c r="G219" s="98"/>
-      <c r="H219" s="98"/>
-      <c r="I219" s="26"/>
-      <c r="J219" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="K219" s="31">
-        <v>0</v>
-      </c>
-      <c r="L219" s="31">
-        <v>2000</v>
-      </c>
-      <c r="M219" s="100" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="220" s="18" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A220" s="96">
-        <v>50006</v>
-      </c>
-      <c r="B220" s="96">
-        <v>105000</v>
-      </c>
-      <c r="C220" s="96" t="s">
-        <v>236</v>
-      </c>
-      <c r="D220" s="96">
-        <v>6</v>
-      </c>
-      <c r="E220" s="98" t="s">
-        <v>73</v>
-      </c>
-      <c r="F220" s="98"/>
-      <c r="G220" s="98"/>
-      <c r="H220" s="98"/>
-      <c r="I220" s="26"/>
-      <c r="J220" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="K220" s="31">
-        <v>-1000</v>
-      </c>
-      <c r="L220" s="31">
-        <v>0</v>
-      </c>
-      <c r="M220" s="100" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="221" s="18" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A221" s="96">
-        <v>50007</v>
-      </c>
-      <c r="B221" s="96">
-        <v>105000</v>
-      </c>
-      <c r="C221" s="96" t="s">
-        <v>236</v>
-      </c>
-      <c r="D221" s="96">
-        <v>7</v>
-      </c>
-      <c r="E221" s="98" t="s">
-        <v>74</v>
-      </c>
-      <c r="F221" s="98"/>
-      <c r="G221" s="98"/>
-      <c r="H221" s="98"/>
-      <c r="I221" s="26"/>
-      <c r="J221" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="K221" s="31">
-        <v>-999999</v>
-      </c>
-      <c r="L221" s="31">
-        <v>-1000</v>
-      </c>
-      <c r="M221" s="100" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="222" s="20" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A222" s="107">
-        <v>51001</v>
-      </c>
-      <c r="B222" s="107">
-        <v>105100</v>
-      </c>
-      <c r="C222" s="107" t="s">
-        <v>237</v>
-      </c>
-      <c r="D222" s="107">
-        <v>1</v>
-      </c>
-      <c r="E222" s="108" t="s">
-        <v>238</v>
-      </c>
-      <c r="F222" s="108"/>
-      <c r="G222" s="108"/>
-      <c r="H222" s="108"/>
-      <c r="I222" s="26"/>
-      <c r="J222" s="109" t="s">
-        <v>239</v>
       </c>
       <c r="K222" s="31">
         <v>8000</v>
@@ -10655,32 +10697,32 @@
       <c r="L222" s="31">
         <v>999999</v>
       </c>
-      <c r="M222" s="110" t="s">
+      <c r="M222" s="37" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="223" s="20" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A223" s="107">
-        <v>51002</v>
-      </c>
-      <c r="B223" s="107">
-        <v>105100</v>
-      </c>
-      <c r="C223" s="107" t="s">
+    <row r="223" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A223" s="106">
+        <v>48002</v>
+      </c>
+      <c r="B223" s="106">
+        <v>104800</v>
+      </c>
+      <c r="C223" s="106" t="s">
         <v>237</v>
       </c>
-      <c r="D223" s="107">
+      <c r="D223" s="106">
         <v>2</v>
       </c>
-      <c r="E223" s="108" t="s">
-        <v>238</v>
-      </c>
-      <c r="F223" s="108"/>
-      <c r="G223" s="108"/>
-      <c r="H223" s="108"/>
+      <c r="E223" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="F223" s="38"/>
+      <c r="G223" s="38"/>
+      <c r="H223" s="38"/>
       <c r="I223" s="26"/>
-      <c r="J223" s="109" t="s">
-        <v>239</v>
+      <c r="J223" s="40" t="s">
+        <v>68</v>
       </c>
       <c r="K223" s="31">
         <v>6000</v>
@@ -10688,32 +10730,32 @@
       <c r="L223" s="31">
         <v>8000</v>
       </c>
-      <c r="M223" s="110" t="s">
+      <c r="M223" s="37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="224" s="20" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A224" s="107">
-        <v>51003</v>
-      </c>
-      <c r="B224" s="107">
-        <v>105100</v>
-      </c>
-      <c r="C224" s="107" t="s">
+    <row r="224" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A224" s="106">
+        <v>48003</v>
+      </c>
+      <c r="B224" s="106">
+        <v>104800</v>
+      </c>
+      <c r="C224" s="106" t="s">
         <v>237</v>
       </c>
-      <c r="D224" s="107">
+      <c r="D224" s="106">
         <v>3</v>
       </c>
-      <c r="E224" s="108" t="s">
-        <v>238</v>
-      </c>
-      <c r="F224" s="108"/>
-      <c r="G224" s="108"/>
-      <c r="H224" s="108"/>
+      <c r="E224" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="F224" s="38"/>
+      <c r="G224" s="38"/>
+      <c r="H224" s="38"/>
       <c r="I224" s="26"/>
-      <c r="J224" s="109" t="s">
-        <v>239</v>
+      <c r="J224" s="40" t="s">
+        <v>68</v>
       </c>
       <c r="K224" s="31">
         <v>4000</v>
@@ -10721,32 +10763,32 @@
       <c r="L224" s="31">
         <v>6000</v>
       </c>
-      <c r="M224" s="110" t="s">
+      <c r="M224" s="37" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="225" s="20" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A225" s="107">
-        <v>51004</v>
-      </c>
-      <c r="B225" s="107">
-        <v>105100</v>
-      </c>
-      <c r="C225" s="107" t="s">
+    <row r="225" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A225" s="106">
+        <v>48004</v>
+      </c>
+      <c r="B225" s="106">
+        <v>104800</v>
+      </c>
+      <c r="C225" s="106" t="s">
         <v>237</v>
       </c>
-      <c r="D225" s="107">
+      <c r="D225" s="106">
         <v>4</v>
       </c>
-      <c r="E225" s="108" t="s">
-        <v>238</v>
-      </c>
-      <c r="F225" s="108"/>
-      <c r="G225" s="108"/>
-      <c r="H225" s="108"/>
+      <c r="E225" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="F225" s="38"/>
+      <c r="G225" s="38"/>
+      <c r="H225" s="38"/>
       <c r="I225" s="26"/>
-      <c r="J225" s="109" t="s">
-        <v>239</v>
+      <c r="J225" s="40" t="s">
+        <v>68</v>
       </c>
       <c r="K225" s="31">
         <v>2000</v>
@@ -10754,32 +10796,32 @@
       <c r="L225" s="31">
         <v>4000</v>
       </c>
-      <c r="M225" s="110" t="s">
+      <c r="M225" s="37" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="226" s="20" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A226" s="107">
-        <v>51005</v>
-      </c>
-      <c r="B226" s="107">
-        <v>105100</v>
-      </c>
-      <c r="C226" s="107" t="s">
+    <row r="226" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A226" s="106">
+        <v>48005</v>
+      </c>
+      <c r="B226" s="106">
+        <v>104800</v>
+      </c>
+      <c r="C226" s="106" t="s">
         <v>237</v>
       </c>
-      <c r="D226" s="107">
+      <c r="D226" s="106">
         <v>5</v>
       </c>
-      <c r="E226" s="108" t="s">
-        <v>238</v>
-      </c>
-      <c r="F226" s="108"/>
-      <c r="G226" s="108"/>
-      <c r="H226" s="108"/>
+      <c r="E226" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="F226" s="38"/>
+      <c r="G226" s="38"/>
+      <c r="H226" s="38"/>
       <c r="I226" s="26"/>
-      <c r="J226" s="109" t="s">
-        <v>239</v>
+      <c r="J226" s="40" t="s">
+        <v>68</v>
       </c>
       <c r="K226" s="31">
         <v>0</v>
@@ -10787,32 +10829,32 @@
       <c r="L226" s="31">
         <v>2000</v>
       </c>
-      <c r="M226" s="110" t="s">
+      <c r="M226" s="37" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="227" s="20" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A227" s="107">
-        <v>51006</v>
-      </c>
-      <c r="B227" s="107">
-        <v>105100</v>
-      </c>
-      <c r="C227" s="107" t="s">
+    <row r="227" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A227" s="106">
+        <v>48006</v>
+      </c>
+      <c r="B227" s="106">
+        <v>104800</v>
+      </c>
+      <c r="C227" s="106" t="s">
         <v>237</v>
       </c>
-      <c r="D227" s="107">
+      <c r="D227" s="106">
         <v>6</v>
       </c>
-      <c r="E227" s="108" t="s">
-        <v>238</v>
-      </c>
-      <c r="F227" s="108"/>
-      <c r="G227" s="108"/>
-      <c r="H227" s="108"/>
+      <c r="E227" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F227" s="38"/>
+      <c r="G227" s="38"/>
+      <c r="H227" s="38"/>
       <c r="I227" s="26"/>
-      <c r="J227" s="109" t="s">
-        <v>239</v>
+      <c r="J227" s="40" t="s">
+        <v>68</v>
       </c>
       <c r="K227" s="31">
         <v>-1000</v>
@@ -10820,32 +10862,32 @@
       <c r="L227" s="31">
         <v>0</v>
       </c>
-      <c r="M227" s="110" t="s">
+      <c r="M227" s="37" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="228" s="20" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A228" s="107">
-        <v>51007</v>
-      </c>
-      <c r="B228" s="107">
-        <v>105100</v>
-      </c>
-      <c r="C228" s="107" t="s">
+    <row r="228" s="3" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A228" s="106">
+        <v>48007</v>
+      </c>
+      <c r="B228" s="106">
+        <v>104800</v>
+      </c>
+      <c r="C228" s="106" t="s">
         <v>237</v>
       </c>
-      <c r="D228" s="107">
+      <c r="D228" s="106">
         <v>7</v>
       </c>
-      <c r="E228" s="108" t="s">
-        <v>238</v>
-      </c>
-      <c r="F228" s="108"/>
-      <c r="G228" s="108"/>
-      <c r="H228" s="108"/>
+      <c r="E228" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="F228" s="38"/>
+      <c r="G228" s="38"/>
+      <c r="H228" s="38"/>
       <c r="I228" s="26"/>
-      <c r="J228" s="109" t="s">
-        <v>239</v>
+      <c r="J228" s="40" t="s">
+        <v>68</v>
       </c>
       <c r="K228" s="31">
         <v>-999999</v>
@@ -10853,1560 +10895,2022 @@
       <c r="L228" s="31">
         <v>-1000</v>
       </c>
-      <c r="M228" s="110" t="s">
+      <c r="M228" s="37" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="229" s="8" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A229" s="8">
+    <row r="229" s="18" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A229" s="96">
+        <v>50001</v>
+      </c>
+      <c r="B229" s="96">
+        <v>105000</v>
+      </c>
+      <c r="C229" s="96" t="s">
+        <v>238</v>
+      </c>
+      <c r="D229" s="96">
+        <v>1</v>
+      </c>
+      <c r="E229" s="98" t="s">
+        <v>67</v>
+      </c>
+      <c r="F229" s="98"/>
+      <c r="G229" s="98"/>
+      <c r="H229" s="98"/>
+      <c r="I229" s="26"/>
+      <c r="J229" s="99" t="s">
+        <v>68</v>
+      </c>
+      <c r="K229" s="31">
+        <v>8000</v>
+      </c>
+      <c r="L229" s="31">
+        <v>999999</v>
+      </c>
+      <c r="M229" s="100" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="230" s="18" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A230" s="96">
+        <v>50002</v>
+      </c>
+      <c r="B230" s="96">
+        <v>105000</v>
+      </c>
+      <c r="C230" s="96" t="s">
+        <v>238</v>
+      </c>
+      <c r="D230" s="96">
+        <v>2</v>
+      </c>
+      <c r="E230" s="98" t="s">
+        <v>69</v>
+      </c>
+      <c r="F230" s="98"/>
+      <c r="G230" s="98"/>
+      <c r="H230" s="98"/>
+      <c r="I230" s="26"/>
+      <c r="J230" s="99" t="s">
+        <v>68</v>
+      </c>
+      <c r="K230" s="31">
+        <v>6000</v>
+      </c>
+      <c r="L230" s="31">
+        <v>8000</v>
+      </c>
+      <c r="M230" s="100" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="231" s="18" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A231" s="96">
+        <v>50003</v>
+      </c>
+      <c r="B231" s="96">
+        <v>105000</v>
+      </c>
+      <c r="C231" s="96" t="s">
+        <v>238</v>
+      </c>
+      <c r="D231" s="96">
+        <v>3</v>
+      </c>
+      <c r="E231" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="F231" s="98"/>
+      <c r="G231" s="98"/>
+      <c r="H231" s="98"/>
+      <c r="I231" s="26"/>
+      <c r="J231" s="99" t="s">
+        <v>68</v>
+      </c>
+      <c r="K231" s="31">
+        <v>4000</v>
+      </c>
+      <c r="L231" s="31">
+        <v>6000</v>
+      </c>
+      <c r="M231" s="100" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="232" s="18" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A232" s="96">
+        <v>50004</v>
+      </c>
+      <c r="B232" s="96">
+        <v>105000</v>
+      </c>
+      <c r="C232" s="96" t="s">
+        <v>238</v>
+      </c>
+      <c r="D232" s="96">
+        <v>4</v>
+      </c>
+      <c r="E232" s="98" t="s">
+        <v>71</v>
+      </c>
+      <c r="F232" s="98"/>
+      <c r="G232" s="98"/>
+      <c r="H232" s="98"/>
+      <c r="I232" s="26"/>
+      <c r="J232" s="99" t="s">
+        <v>68</v>
+      </c>
+      <c r="K232" s="31">
+        <v>2000</v>
+      </c>
+      <c r="L232" s="31">
+        <v>4000</v>
+      </c>
+      <c r="M232" s="100" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="233" s="18" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A233" s="96">
+        <v>50005</v>
+      </c>
+      <c r="B233" s="96">
+        <v>105000</v>
+      </c>
+      <c r="C233" s="96" t="s">
+        <v>238</v>
+      </c>
+      <c r="D233" s="96">
+        <v>5</v>
+      </c>
+      <c r="E233" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="F233" s="98"/>
+      <c r="G233" s="98"/>
+      <c r="H233" s="98"/>
+      <c r="I233" s="26"/>
+      <c r="J233" s="99" t="s">
+        <v>68</v>
+      </c>
+      <c r="K233" s="31">
+        <v>0</v>
+      </c>
+      <c r="L233" s="31">
+        <v>2000</v>
+      </c>
+      <c r="M233" s="100" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="234" s="18" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A234" s="96">
+        <v>50006</v>
+      </c>
+      <c r="B234" s="96">
+        <v>105000</v>
+      </c>
+      <c r="C234" s="96" t="s">
+        <v>238</v>
+      </c>
+      <c r="D234" s="96">
+        <v>6</v>
+      </c>
+      <c r="E234" s="98" t="s">
+        <v>73</v>
+      </c>
+      <c r="F234" s="98"/>
+      <c r="G234" s="98"/>
+      <c r="H234" s="98"/>
+      <c r="I234" s="26"/>
+      <c r="J234" s="99" t="s">
+        <v>68</v>
+      </c>
+      <c r="K234" s="31">
+        <v>-1000</v>
+      </c>
+      <c r="L234" s="31">
+        <v>0</v>
+      </c>
+      <c r="M234" s="100" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="235" s="18" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A235" s="96">
+        <v>50007</v>
+      </c>
+      <c r="B235" s="96">
+        <v>105000</v>
+      </c>
+      <c r="C235" s="96" t="s">
+        <v>238</v>
+      </c>
+      <c r="D235" s="96">
+        <v>7</v>
+      </c>
+      <c r="E235" s="98" t="s">
+        <v>74</v>
+      </c>
+      <c r="F235" s="98"/>
+      <c r="G235" s="98"/>
+      <c r="H235" s="98"/>
+      <c r="I235" s="26"/>
+      <c r="J235" s="99" t="s">
+        <v>68</v>
+      </c>
+      <c r="K235" s="31">
+        <v>-999999</v>
+      </c>
+      <c r="L235" s="31">
+        <v>-1000</v>
+      </c>
+      <c r="M235" s="100" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="236" s="20" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A236" s="115">
+        <v>51001</v>
+      </c>
+      <c r="B236" s="115">
+        <v>105100</v>
+      </c>
+      <c r="C236" s="115" t="s">
+        <v>239</v>
+      </c>
+      <c r="D236" s="115">
+        <v>1</v>
+      </c>
+      <c r="E236" s="116" t="s">
+        <v>240</v>
+      </c>
+      <c r="F236" s="116"/>
+      <c r="G236" s="116"/>
+      <c r="H236" s="116"/>
+      <c r="I236" s="26"/>
+      <c r="J236" s="117" t="s">
+        <v>241</v>
+      </c>
+      <c r="K236" s="31">
+        <v>8000</v>
+      </c>
+      <c r="L236" s="31">
+        <v>999999</v>
+      </c>
+      <c r="M236" s="118" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="237" s="20" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A237" s="115">
+        <v>51002</v>
+      </c>
+      <c r="B237" s="115">
+        <v>105100</v>
+      </c>
+      <c r="C237" s="115" t="s">
+        <v>239</v>
+      </c>
+      <c r="D237" s="115">
+        <v>2</v>
+      </c>
+      <c r="E237" s="116" t="s">
+        <v>240</v>
+      </c>
+      <c r="F237" s="116"/>
+      <c r="G237" s="116"/>
+      <c r="H237" s="116"/>
+      <c r="I237" s="26"/>
+      <c r="J237" s="117" t="s">
+        <v>241</v>
+      </c>
+      <c r="K237" s="31">
+        <v>6000</v>
+      </c>
+      <c r="L237" s="31">
+        <v>8000</v>
+      </c>
+      <c r="M237" s="118" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="238" s="20" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A238" s="115">
+        <v>51003</v>
+      </c>
+      <c r="B238" s="115">
+        <v>105100</v>
+      </c>
+      <c r="C238" s="115" t="s">
+        <v>239</v>
+      </c>
+      <c r="D238" s="115">
+        <v>3</v>
+      </c>
+      <c r="E238" s="116" t="s">
+        <v>240</v>
+      </c>
+      <c r="F238" s="116"/>
+      <c r="G238" s="116"/>
+      <c r="H238" s="116"/>
+      <c r="I238" s="26"/>
+      <c r="J238" s="117" t="s">
+        <v>241</v>
+      </c>
+      <c r="K238" s="31">
+        <v>4000</v>
+      </c>
+      <c r="L238" s="31">
+        <v>6000</v>
+      </c>
+      <c r="M238" s="118" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="239" s="20" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A239" s="115">
+        <v>51004</v>
+      </c>
+      <c r="B239" s="115">
+        <v>105100</v>
+      </c>
+      <c r="C239" s="115" t="s">
+        <v>239</v>
+      </c>
+      <c r="D239" s="115">
+        <v>4</v>
+      </c>
+      <c r="E239" s="116" t="s">
+        <v>240</v>
+      </c>
+      <c r="F239" s="116"/>
+      <c r="G239" s="116"/>
+      <c r="H239" s="116"/>
+      <c r="I239" s="26"/>
+      <c r="J239" s="117" t="s">
+        <v>241</v>
+      </c>
+      <c r="K239" s="31">
+        <v>2000</v>
+      </c>
+      <c r="L239" s="31">
+        <v>4000</v>
+      </c>
+      <c r="M239" s="118" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="240" s="20" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A240" s="115">
+        <v>51005</v>
+      </c>
+      <c r="B240" s="115">
+        <v>105100</v>
+      </c>
+      <c r="C240" s="115" t="s">
+        <v>239</v>
+      </c>
+      <c r="D240" s="115">
+        <v>5</v>
+      </c>
+      <c r="E240" s="116" t="s">
+        <v>240</v>
+      </c>
+      <c r="F240" s="116"/>
+      <c r="G240" s="116"/>
+      <c r="H240" s="116"/>
+      <c r="I240" s="26"/>
+      <c r="J240" s="117" t="s">
+        <v>241</v>
+      </c>
+      <c r="K240" s="31">
+        <v>0</v>
+      </c>
+      <c r="L240" s="31">
+        <v>2000</v>
+      </c>
+      <c r="M240" s="118" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="241" s="20" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A241" s="115">
+        <v>51006</v>
+      </c>
+      <c r="B241" s="115">
+        <v>105100</v>
+      </c>
+      <c r="C241" s="115" t="s">
+        <v>239</v>
+      </c>
+      <c r="D241" s="115">
+        <v>6</v>
+      </c>
+      <c r="E241" s="116" t="s">
+        <v>240</v>
+      </c>
+      <c r="F241" s="116"/>
+      <c r="G241" s="116"/>
+      <c r="H241" s="116"/>
+      <c r="I241" s="26"/>
+      <c r="J241" s="117" t="s">
+        <v>241</v>
+      </c>
+      <c r="K241" s="31">
+        <v>-1000</v>
+      </c>
+      <c r="L241" s="31">
+        <v>0</v>
+      </c>
+      <c r="M241" s="118" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="242" s="20" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A242" s="115">
+        <v>51007</v>
+      </c>
+      <c r="B242" s="115">
+        <v>105100</v>
+      </c>
+      <c r="C242" s="115" t="s">
+        <v>239</v>
+      </c>
+      <c r="D242" s="115">
+        <v>7</v>
+      </c>
+      <c r="E242" s="116" t="s">
+        <v>240</v>
+      </c>
+      <c r="F242" s="116"/>
+      <c r="G242" s="116"/>
+      <c r="H242" s="116"/>
+      <c r="I242" s="26"/>
+      <c r="J242" s="117" t="s">
+        <v>241</v>
+      </c>
+      <c r="K242" s="31">
+        <v>-999999</v>
+      </c>
+      <c r="L242" s="31">
+        <v>-1000</v>
+      </c>
+      <c r="M242" s="118" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="243" s="8" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A243" s="8">
         <v>53001</v>
       </c>
-      <c r="B229" s="57">
+      <c r="B243" s="57">
         <v>105300</v>
       </c>
-      <c r="C229" s="57" t="s">
-        <v>240</v>
-      </c>
-      <c r="D229" s="33">
+      <c r="C243" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="D243" s="33">
         <v>1</v>
       </c>
-      <c r="E229" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="F229" s="34"/>
-      <c r="G229" s="34"/>
-      <c r="H229" s="34"/>
-      <c r="I229" s="58"/>
-      <c r="J229" s="111" t="s">
+      <c r="E243" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="F243" s="34"/>
+      <c r="G243" s="34"/>
+      <c r="H243" s="34"/>
+      <c r="I243" s="58"/>
+      <c r="J243" s="119" t="s">
+        <v>244</v>
+      </c>
+      <c r="K243" s="33">
+        <v>2000</v>
+      </c>
+      <c r="L243" s="33">
+        <v>999999</v>
+      </c>
+      <c r="M243" s="33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="244" s="8" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A244" s="8">
+        <v>53002</v>
+      </c>
+      <c r="B244" s="57">
+        <v>105300</v>
+      </c>
+      <c r="C244" s="57" t="s">
         <v>242</v>
       </c>
-      <c r="K229" s="33">
+      <c r="D244" s="33">
+        <v>2</v>
+      </c>
+      <c r="E244" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="F244" s="34"/>
+      <c r="G244" s="34"/>
+      <c r="H244" s="34"/>
+      <c r="I244" s="58"/>
+      <c r="J244" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="K244" s="33">
+        <v>1000</v>
+      </c>
+      <c r="L244" s="33">
         <v>2000</v>
       </c>
-      <c r="L229" s="33">
+      <c r="M244" s="33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="245" s="8" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A245" s="8">
+        <v>53003</v>
+      </c>
+      <c r="B245" s="57">
+        <v>105300</v>
+      </c>
+      <c r="C245" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="D245" s="33">
+        <v>3</v>
+      </c>
+      <c r="E245" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="F245" s="34"/>
+      <c r="G245" s="34"/>
+      <c r="H245" s="34"/>
+      <c r="I245" s="58"/>
+      <c r="J245" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="K245" s="33">
+        <v>500</v>
+      </c>
+      <c r="L245" s="33">
+        <v>1000</v>
+      </c>
+      <c r="M245" s="33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="246" s="8" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A246" s="8">
+        <v>53004</v>
+      </c>
+      <c r="B246" s="57">
+        <v>105300</v>
+      </c>
+      <c r="C246" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="D246" s="33">
+        <v>4</v>
+      </c>
+      <c r="E246" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="F246" s="34"/>
+      <c r="G246" s="34"/>
+      <c r="H246" s="34"/>
+      <c r="I246" s="58"/>
+      <c r="J246" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="K246" s="33">
+        <v>-500</v>
+      </c>
+      <c r="L246" s="33">
+        <v>500</v>
+      </c>
+      <c r="M246" s="33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="247" s="8" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A247" s="8">
+        <v>53005</v>
+      </c>
+      <c r="B247" s="57">
+        <v>105300</v>
+      </c>
+      <c r="C247" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="D247" s="33">
+        <v>5</v>
+      </c>
+      <c r="E247" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="F247" s="34"/>
+      <c r="G247" s="34"/>
+      <c r="H247" s="34"/>
+      <c r="I247" s="58"/>
+      <c r="J247" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="K247" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="L247" s="33">
+        <v>-500</v>
+      </c>
+      <c r="M247" s="33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="248" s="8" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A248" s="8">
+        <v>53006</v>
+      </c>
+      <c r="B248" s="57">
+        <v>105300</v>
+      </c>
+      <c r="C248" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="D248" s="33">
+        <v>6</v>
+      </c>
+      <c r="E248" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="F248" s="34"/>
+      <c r="G248" s="34"/>
+      <c r="H248" s="34"/>
+      <c r="I248" s="58"/>
+      <c r="J248" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="K248" s="33">
+        <v>-2000</v>
+      </c>
+      <c r="L248" s="33">
+        <v>-1000</v>
+      </c>
+      <c r="M248" s="33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="249" s="8" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A249" s="8">
+        <v>53007</v>
+      </c>
+      <c r="B249" s="57">
+        <v>105300</v>
+      </c>
+      <c r="C249" s="57" t="s">
+        <v>242</v>
+      </c>
+      <c r="D249" s="33">
+        <v>7</v>
+      </c>
+      <c r="E249" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="F249" s="34"/>
+      <c r="G249" s="34"/>
+      <c r="H249" s="34"/>
+      <c r="I249" s="58"/>
+      <c r="J249" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="K249" s="33">
+        <v>-999999</v>
+      </c>
+      <c r="L249" s="33">
+        <v>-2000</v>
+      </c>
+      <c r="M249" s="33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="250" ht="16.5" spans="1:13">
+      <c r="A250" s="106">
+        <v>54001</v>
+      </c>
+      <c r="B250" s="106">
+        <v>105400</v>
+      </c>
+      <c r="C250" s="106" t="s">
+        <v>251</v>
+      </c>
+      <c r="D250" s="106">
+        <v>1</v>
+      </c>
+      <c r="E250" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="F250" s="38"/>
+      <c r="G250" s="38"/>
+      <c r="H250" s="38"/>
+      <c r="J250" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="K250" s="37">
+        <v>2000</v>
+      </c>
+      <c r="L250" s="37">
         <v>999999</v>
       </c>
-      <c r="M229" s="33" t="s">
+      <c r="M250" s="37" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="230" s="8" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A230" s="8">
-        <v>53002</v>
-      </c>
-      <c r="B230" s="57">
-        <v>105300</v>
-      </c>
-      <c r="C230" s="57" t="s">
-        <v>240</v>
-      </c>
-      <c r="D230" s="33">
+    <row r="251" ht="16.5" spans="1:13">
+      <c r="A251" s="106">
+        <v>54002</v>
+      </c>
+      <c r="B251" s="106">
+        <v>105400</v>
+      </c>
+      <c r="C251" s="106" t="s">
+        <v>251</v>
+      </c>
+      <c r="D251" s="106">
         <v>2</v>
       </c>
-      <c r="E230" s="34" t="s">
+      <c r="E251" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="F251" s="38"/>
+      <c r="G251" s="38"/>
+      <c r="H251" s="38"/>
+      <c r="J251" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="K251" s="37">
+        <v>1000</v>
+      </c>
+      <c r="L251" s="37">
+        <v>2000</v>
+      </c>
+      <c r="M251" s="37" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="252" ht="16.5" spans="1:13">
+      <c r="A252" s="106">
+        <v>54003</v>
+      </c>
+      <c r="B252" s="106">
+        <v>105400</v>
+      </c>
+      <c r="C252" s="106" t="s">
+        <v>251</v>
+      </c>
+      <c r="D252" s="106">
+        <v>3</v>
+      </c>
+      <c r="E252" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="F252" s="38"/>
+      <c r="G252" s="38"/>
+      <c r="H252" s="38"/>
+      <c r="J252" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="K252" s="37">
+        <v>500</v>
+      </c>
+      <c r="L252" s="37">
+        <v>1000</v>
+      </c>
+      <c r="M252" s="37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="253" ht="16.5" spans="1:13">
+      <c r="A253" s="106">
+        <v>54004</v>
+      </c>
+      <c r="B253" s="106">
+        <v>105400</v>
+      </c>
+      <c r="C253" s="106" t="s">
+        <v>251</v>
+      </c>
+      <c r="D253" s="106">
+        <v>4</v>
+      </c>
+      <c r="E253" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="F253" s="38"/>
+      <c r="G253" s="38"/>
+      <c r="H253" s="38"/>
+      <c r="J253" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="K253" s="37">
+        <v>-500</v>
+      </c>
+      <c r="L253" s="37">
+        <v>500</v>
+      </c>
+      <c r="M253" s="37" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="254" ht="16.5" spans="1:13">
+      <c r="A254" s="106">
+        <v>54005</v>
+      </c>
+      <c r="B254" s="106">
+        <v>105400</v>
+      </c>
+      <c r="C254" s="106" t="s">
+        <v>251</v>
+      </c>
+      <c r="D254" s="106">
+        <v>5</v>
+      </c>
+      <c r="E254" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="F254" s="38"/>
+      <c r="G254" s="38"/>
+      <c r="H254" s="38"/>
+      <c r="J254" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="K254" s="37">
+        <v>-1000</v>
+      </c>
+      <c r="L254" s="37">
+        <v>-500</v>
+      </c>
+      <c r="M254" s="37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="255" ht="16.5" spans="1:13">
+      <c r="A255" s="106">
+        <v>54006</v>
+      </c>
+      <c r="B255" s="106">
+        <v>105400</v>
+      </c>
+      <c r="C255" s="106" t="s">
+        <v>251</v>
+      </c>
+      <c r="D255" s="106">
+        <v>6</v>
+      </c>
+      <c r="E255" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F255" s="38"/>
+      <c r="G255" s="38"/>
+      <c r="H255" s="38"/>
+      <c r="J255" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="K255" s="37">
+        <v>-2000</v>
+      </c>
+      <c r="L255" s="37">
+        <v>-1000</v>
+      </c>
+      <c r="M255" s="37" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="256" ht="16.5" spans="1:13">
+      <c r="A256" s="106">
+        <v>54007</v>
+      </c>
+      <c r="B256" s="106">
+        <v>105400</v>
+      </c>
+      <c r="C256" s="106" t="s">
+        <v>251</v>
+      </c>
+      <c r="D256" s="106">
+        <v>7</v>
+      </c>
+      <c r="E256" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="F256" s="38"/>
+      <c r="G256" s="38"/>
+      <c r="H256" s="38"/>
+      <c r="J256" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="K256" s="37">
+        <v>-999999</v>
+      </c>
+      <c r="L256" s="37">
+        <v>-2000</v>
+      </c>
+      <c r="M256" s="37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="257" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A257" s="120">
+        <v>57001</v>
+      </c>
+      <c r="B257" s="121">
+        <v>105700</v>
+      </c>
+      <c r="C257" s="121" t="s">
+        <v>252</v>
+      </c>
+      <c r="D257" s="122">
+        <v>1</v>
+      </c>
+      <c r="E257" s="123" t="s">
+        <v>67</v>
+      </c>
+      <c r="F257" s="123"/>
+      <c r="G257" s="123"/>
+      <c r="H257" s="123"/>
+      <c r="I257" s="124"/>
+      <c r="J257" s="125" t="s">
+        <v>68</v>
+      </c>
+      <c r="K257" s="118">
+        <v>2000</v>
+      </c>
+      <c r="L257" s="118">
+        <v>999999</v>
+      </c>
+      <c r="M257" s="125" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="258" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A258" s="120">
+        <v>57002</v>
+      </c>
+      <c r="B258" s="121">
+        <v>105700</v>
+      </c>
+      <c r="C258" s="121" t="s">
+        <v>252</v>
+      </c>
+      <c r="D258" s="122">
+        <v>2</v>
+      </c>
+      <c r="E258" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="F258" s="123"/>
+      <c r="G258" s="123"/>
+      <c r="H258" s="123"/>
+      <c r="I258" s="124"/>
+      <c r="J258" s="125" t="s">
+        <v>68</v>
+      </c>
+      <c r="K258" s="118">
+        <v>1000</v>
+      </c>
+      <c r="L258" s="118">
+        <v>2000</v>
+      </c>
+      <c r="M258" s="125" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="259" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A259" s="120">
+        <v>57003</v>
+      </c>
+      <c r="B259" s="121">
+        <v>105700</v>
+      </c>
+      <c r="C259" s="121" t="s">
+        <v>252</v>
+      </c>
+      <c r="D259" s="122">
+        <v>3</v>
+      </c>
+      <c r="E259" s="123" t="s">
+        <v>70</v>
+      </c>
+      <c r="F259" s="123"/>
+      <c r="G259" s="123"/>
+      <c r="H259" s="123"/>
+      <c r="I259" s="124"/>
+      <c r="J259" s="125" t="s">
+        <v>68</v>
+      </c>
+      <c r="K259" s="118">
+        <v>500</v>
+      </c>
+      <c r="L259" s="118">
+        <v>1000</v>
+      </c>
+      <c r="M259" s="125" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="260" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A260" s="120">
+        <v>57004</v>
+      </c>
+      <c r="B260" s="121">
+        <v>105700</v>
+      </c>
+      <c r="C260" s="121" t="s">
+        <v>252</v>
+      </c>
+      <c r="D260" s="122">
+        <v>4</v>
+      </c>
+      <c r="E260" s="123" t="s">
+        <v>71</v>
+      </c>
+      <c r="F260" s="123"/>
+      <c r="G260" s="123"/>
+      <c r="H260" s="123"/>
+      <c r="I260" s="124"/>
+      <c r="J260" s="125" t="s">
+        <v>68</v>
+      </c>
+      <c r="K260" s="118">
+        <v>-500</v>
+      </c>
+      <c r="L260" s="118">
+        <v>500</v>
+      </c>
+      <c r="M260" s="125" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="261" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A261" s="120">
+        <v>57005</v>
+      </c>
+      <c r="B261" s="121">
+        <v>105700</v>
+      </c>
+      <c r="C261" s="121" t="s">
+        <v>252</v>
+      </c>
+      <c r="D261" s="122">
+        <v>5</v>
+      </c>
+      <c r="E261" s="123" t="s">
+        <v>72</v>
+      </c>
+      <c r="F261" s="123"/>
+      <c r="G261" s="123"/>
+      <c r="H261" s="123"/>
+      <c r="I261" s="124"/>
+      <c r="J261" s="125" t="s">
+        <v>68</v>
+      </c>
+      <c r="K261" s="118">
+        <v>-1000</v>
+      </c>
+      <c r="L261" s="118">
+        <v>-500</v>
+      </c>
+      <c r="M261" s="125" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="262" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A262" s="120">
+        <v>57006</v>
+      </c>
+      <c r="B262" s="121">
+        <v>105700</v>
+      </c>
+      <c r="C262" s="121" t="s">
+        <v>252</v>
+      </c>
+      <c r="D262" s="122">
+        <v>6</v>
+      </c>
+      <c r="E262" s="123" t="s">
+        <v>73</v>
+      </c>
+      <c r="F262" s="123"/>
+      <c r="G262" s="123"/>
+      <c r="H262" s="123"/>
+      <c r="I262" s="124"/>
+      <c r="J262" s="125" t="s">
+        <v>68</v>
+      </c>
+      <c r="K262" s="118">
+        <v>-2000</v>
+      </c>
+      <c r="L262" s="118">
+        <v>-1000</v>
+      </c>
+      <c r="M262" s="125" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="263" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A263" s="120">
+        <v>57007</v>
+      </c>
+      <c r="B263" s="121">
+        <v>105700</v>
+      </c>
+      <c r="C263" s="121" t="s">
+        <v>252</v>
+      </c>
+      <c r="D263" s="122">
+        <v>7</v>
+      </c>
+      <c r="E263" s="123" t="s">
+        <v>74</v>
+      </c>
+      <c r="F263" s="123"/>
+      <c r="G263" s="123"/>
+      <c r="H263" s="123"/>
+      <c r="I263" s="124"/>
+      <c r="J263" s="125" t="s">
+        <v>68</v>
+      </c>
+      <c r="K263" s="118">
+        <v>-999999</v>
+      </c>
+      <c r="L263" s="118">
+        <v>-2000</v>
+      </c>
+      <c r="M263" s="125" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="264" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A264" s="21">
+        <v>58001</v>
+      </c>
+      <c r="B264" s="126">
+        <v>105800</v>
+      </c>
+      <c r="C264" s="126" t="s">
+        <v>253</v>
+      </c>
+      <c r="D264" s="126">
+        <v>1</v>
+      </c>
+      <c r="E264" s="26" t="s">
         <v>243</v>
       </c>
-      <c r="F230" s="34"/>
-      <c r="G230" s="34"/>
-      <c r="H230" s="34"/>
-      <c r="I230" s="58"/>
-      <c r="J230" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="K230" s="33">
-        <v>1000</v>
-      </c>
-      <c r="L230" s="33">
-        <v>2000</v>
-      </c>
-      <c r="M230" s="33" t="s">
+      <c r="F264" s="26"/>
+      <c r="G264" s="26"/>
+      <c r="H264" s="26"/>
+      <c r="I264" s="124"/>
+      <c r="J264" s="30" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="265" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A265" s="21">
+        <v>58002</v>
+      </c>
+      <c r="B265" s="126">
+        <v>105800</v>
+      </c>
+      <c r="C265" s="126" t="s">
+        <v>253</v>
+      </c>
+      <c r="D265" s="126">
+        <v>2</v>
+      </c>
+      <c r="E265" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="F265" s="26"/>
+      <c r="G265" s="26"/>
+      <c r="H265" s="26"/>
+      <c r="I265" s="124"/>
+      <c r="J265" s="26" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="266" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A266" s="21">
+        <v>58003</v>
+      </c>
+      <c r="B266" s="126">
+        <v>105800</v>
+      </c>
+      <c r="C266" s="126" t="s">
+        <v>253</v>
+      </c>
+      <c r="D266" s="126">
+        <v>3</v>
+      </c>
+      <c r="E266" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="F266" s="26"/>
+      <c r="G266" s="26"/>
+      <c r="H266" s="26"/>
+      <c r="I266" s="124"/>
+      <c r="J266" s="26" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="267" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A267" s="21">
+        <v>58004</v>
+      </c>
+      <c r="B267" s="126">
+        <v>105800</v>
+      </c>
+      <c r="C267" s="126" t="s">
+        <v>253</v>
+      </c>
+      <c r="D267" s="126">
+        <v>4</v>
+      </c>
+      <c r="E267" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="F267" s="26"/>
+      <c r="G267" s="26"/>
+      <c r="H267" s="26"/>
+      <c r="I267" s="124"/>
+      <c r="J267" s="26" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="268" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A268" s="21">
+        <v>58005</v>
+      </c>
+      <c r="B268" s="126">
+        <v>105800</v>
+      </c>
+      <c r="C268" s="126" t="s">
+        <v>253</v>
+      </c>
+      <c r="D268" s="126">
+        <v>5</v>
+      </c>
+      <c r="E268" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="F268" s="26"/>
+      <c r="G268" s="26"/>
+      <c r="H268" s="26"/>
+      <c r="I268" s="124"/>
+      <c r="J268" s="26" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="269" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A269" s="21">
+        <v>58006</v>
+      </c>
+      <c r="B269" s="126">
+        <v>105800</v>
+      </c>
+      <c r="C269" s="126" t="s">
+        <v>253</v>
+      </c>
+      <c r="D269" s="126">
+        <v>6</v>
+      </c>
+      <c r="E269" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="F269" s="26"/>
+      <c r="G269" s="26"/>
+      <c r="H269" s="26"/>
+      <c r="I269" s="124"/>
+      <c r="J269" s="26" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="270" s="21" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A270" s="21">
+        <v>58007</v>
+      </c>
+      <c r="B270" s="126">
+        <v>105800</v>
+      </c>
+      <c r="C270" s="126" t="s">
+        <v>253</v>
+      </c>
+      <c r="D270" s="126">
+        <v>7</v>
+      </c>
+      <c r="E270" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="F270" s="26"/>
+      <c r="G270" s="26"/>
+      <c r="H270" s="26"/>
+      <c r="I270" s="124"/>
+      <c r="J270" s="26" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="271" ht="16.5" spans="1:13">
+      <c r="A271" s="127">
+        <v>55001</v>
+      </c>
+      <c r="B271" s="128">
+        <v>105500</v>
+      </c>
+      <c r="C271" s="128" t="s">
+        <v>254</v>
+      </c>
+      <c r="D271" s="79">
+        <v>1</v>
+      </c>
+      <c r="E271" s="81" t="s">
+        <v>255</v>
+      </c>
+      <c r="F271" s="81"/>
+      <c r="G271" s="81"/>
+      <c r="H271" s="81"/>
+      <c r="I271" s="124"/>
+      <c r="J271" s="99" t="s">
+        <v>256</v>
+      </c>
+      <c r="K271" s="31">
+        <v>8000</v>
+      </c>
+      <c r="L271" s="31">
+        <v>999999</v>
+      </c>
+      <c r="M271" s="129" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="272" ht="16.5" spans="1:13">
+      <c r="A272" s="127">
+        <v>55002</v>
+      </c>
+      <c r="B272" s="128">
+        <v>105500</v>
+      </c>
+      <c r="C272" s="128" t="s">
+        <v>254</v>
+      </c>
+      <c r="D272" s="79">
+        <v>2</v>
+      </c>
+      <c r="E272" s="81" t="s">
+        <v>257</v>
+      </c>
+      <c r="F272" s="81"/>
+      <c r="G272" s="81"/>
+      <c r="H272" s="81"/>
+      <c r="I272" s="124"/>
+      <c r="J272" s="99" t="str">
+        <f t="shared" ref="J272:J277" si="28">J271</f>
+        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
+      </c>
+      <c r="K272" s="31">
+        <v>6000</v>
+      </c>
+      <c r="L272" s="31">
+        <v>8000</v>
+      </c>
+      <c r="M272" s="129" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="231" s="8" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A231" s="8">
-        <v>53003</v>
-      </c>
-      <c r="B231" s="57">
-        <v>105300</v>
-      </c>
-      <c r="C231" s="57" t="s">
-        <v>240</v>
-      </c>
-      <c r="D231" s="33">
+    <row r="273" ht="16.5" spans="1:13">
+      <c r="A273" s="127">
+        <v>55003</v>
+      </c>
+      <c r="B273" s="128">
+        <v>105500</v>
+      </c>
+      <c r="C273" s="128" t="s">
+        <v>254</v>
+      </c>
+      <c r="D273" s="79">
         <v>3</v>
       </c>
-      <c r="E231" s="34" t="s">
-        <v>244</v>
-      </c>
-      <c r="F231" s="34"/>
-      <c r="G231" s="34"/>
-      <c r="H231" s="34"/>
-      <c r="I231" s="58"/>
-      <c r="J231" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="K231" s="33">
-        <v>500</v>
-      </c>
-      <c r="L231" s="33">
-        <v>1000</v>
-      </c>
-      <c r="M231" s="33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="232" s="8" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A232" s="8">
-        <v>53004</v>
-      </c>
-      <c r="B232" s="57">
-        <v>105300</v>
-      </c>
-      <c r="C232" s="57" t="s">
-        <v>240</v>
-      </c>
-      <c r="D232" s="33">
-        <v>4</v>
-      </c>
-      <c r="E232" s="34" t="s">
-        <v>245</v>
-      </c>
-      <c r="F232" s="34"/>
-      <c r="G232" s="34"/>
-      <c r="H232" s="34"/>
-      <c r="I232" s="58"/>
-      <c r="J232" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="K232" s="33">
-        <v>-500</v>
-      </c>
-      <c r="L232" s="33">
-        <v>500</v>
-      </c>
-      <c r="M232" s="33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="233" s="8" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A233" s="8">
-        <v>53005</v>
-      </c>
-      <c r="B233" s="57">
-        <v>105300</v>
-      </c>
-      <c r="C233" s="57" t="s">
-        <v>240</v>
-      </c>
-      <c r="D233" s="33">
-        <v>5</v>
-      </c>
-      <c r="E233" s="34" t="s">
-        <v>246</v>
-      </c>
-      <c r="F233" s="34"/>
-      <c r="G233" s="34"/>
-      <c r="H233" s="34"/>
-      <c r="I233" s="58"/>
-      <c r="J233" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="K233" s="33">
-        <v>-1000</v>
-      </c>
-      <c r="L233" s="33">
-        <v>-500</v>
-      </c>
-      <c r="M233" s="33" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="234" s="8" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A234" s="8">
-        <v>53006</v>
-      </c>
-      <c r="B234" s="57">
-        <v>105300</v>
-      </c>
-      <c r="C234" s="57" t="s">
-        <v>240</v>
-      </c>
-      <c r="D234" s="33">
-        <v>6</v>
-      </c>
-      <c r="E234" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="F234" s="34"/>
-      <c r="G234" s="34"/>
-      <c r="H234" s="34"/>
-      <c r="I234" s="58"/>
-      <c r="J234" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="K234" s="33">
-        <v>-2000</v>
-      </c>
-      <c r="L234" s="33">
-        <v>-1000</v>
-      </c>
-      <c r="M234" s="33" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="235" s="8" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A235" s="8">
-        <v>53007</v>
-      </c>
-      <c r="B235" s="57">
-        <v>105300</v>
-      </c>
-      <c r="C235" s="57" t="s">
-        <v>240</v>
-      </c>
-      <c r="D235" s="33">
-        <v>7</v>
-      </c>
-      <c r="E235" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="F235" s="34"/>
-      <c r="G235" s="34"/>
-      <c r="H235" s="34"/>
-      <c r="I235" s="58"/>
-      <c r="J235" s="34" t="s">
-        <v>242</v>
-      </c>
-      <c r="K235" s="33">
-        <v>-999999</v>
-      </c>
-      <c r="L235" s="33">
-        <v>-2000</v>
-      </c>
-      <c r="M235" s="33" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="236" ht="16.5" spans="1:13">
-      <c r="A236" s="106">
-        <v>54001</v>
-      </c>
-      <c r="B236" s="106">
-        <v>105400</v>
-      </c>
-      <c r="C236" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="D236" s="106">
-        <v>1</v>
-      </c>
-      <c r="E236" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="F236" s="38"/>
-      <c r="G236" s="38"/>
-      <c r="H236" s="38"/>
-      <c r="J236" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K236" s="37">
-        <v>2000</v>
-      </c>
-      <c r="L236" s="37">
-        <v>999999</v>
-      </c>
-      <c r="M236" s="37" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="237" ht="16.5" spans="1:13">
-      <c r="A237" s="106">
-        <v>54002</v>
-      </c>
-      <c r="B237" s="106">
-        <v>105400</v>
-      </c>
-      <c r="C237" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="D237" s="106">
-        <v>2</v>
-      </c>
-      <c r="E237" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="F237" s="38"/>
-      <c r="G237" s="38"/>
-      <c r="H237" s="38"/>
-      <c r="J237" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K237" s="37">
-        <v>1000</v>
-      </c>
-      <c r="L237" s="37">
-        <v>2000</v>
-      </c>
-      <c r="M237" s="37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="238" ht="16.5" spans="1:13">
-      <c r="A238" s="106">
-        <v>54003</v>
-      </c>
-      <c r="B238" s="106">
-        <v>105400</v>
-      </c>
-      <c r="C238" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="D238" s="106">
-        <v>3</v>
-      </c>
-      <c r="E238" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="F238" s="38"/>
-      <c r="G238" s="38"/>
-      <c r="H238" s="38"/>
-      <c r="J238" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K238" s="37">
-        <v>500</v>
-      </c>
-      <c r="L238" s="37">
-        <v>1000</v>
-      </c>
-      <c r="M238" s="37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="239" ht="16.5" spans="1:13">
-      <c r="A239" s="106">
-        <v>54004</v>
-      </c>
-      <c r="B239" s="106">
-        <v>105400</v>
-      </c>
-      <c r="C239" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="D239" s="106">
-        <v>4</v>
-      </c>
-      <c r="E239" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="F239" s="38"/>
-      <c r="G239" s="38"/>
-      <c r="H239" s="38"/>
-      <c r="J239" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K239" s="37">
-        <v>-500</v>
-      </c>
-      <c r="L239" s="37">
-        <v>500</v>
-      </c>
-      <c r="M239" s="37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="240" ht="16.5" spans="1:13">
-      <c r="A240" s="106">
-        <v>54005</v>
-      </c>
-      <c r="B240" s="106">
-        <v>105400</v>
-      </c>
-      <c r="C240" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="D240" s="106">
-        <v>5</v>
-      </c>
-      <c r="E240" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="F240" s="38"/>
-      <c r="G240" s="38"/>
-      <c r="H240" s="38"/>
-      <c r="J240" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K240" s="37">
-        <v>-1000</v>
-      </c>
-      <c r="L240" s="37">
-        <v>-500</v>
-      </c>
-      <c r="M240" s="37" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="241" ht="16.5" spans="1:13">
-      <c r="A241" s="106">
-        <v>54006</v>
-      </c>
-      <c r="B241" s="106">
-        <v>105400</v>
-      </c>
-      <c r="C241" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="D241" s="106">
-        <v>6</v>
-      </c>
-      <c r="E241" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="F241" s="38"/>
-      <c r="G241" s="38"/>
-      <c r="H241" s="38"/>
-      <c r="J241" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K241" s="37">
-        <v>-2000</v>
-      </c>
-      <c r="L241" s="37">
-        <v>-1000</v>
-      </c>
-      <c r="M241" s="37" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="242" ht="16.5" spans="1:13">
-      <c r="A242" s="106">
-        <v>54007</v>
-      </c>
-      <c r="B242" s="106">
-        <v>105400</v>
-      </c>
-      <c r="C242" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="D242" s="106">
-        <v>7</v>
-      </c>
-      <c r="E242" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="F242" s="38"/>
-      <c r="G242" s="38"/>
-      <c r="H242" s="38"/>
-      <c r="J242" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="K242" s="37">
-        <v>-999999</v>
-      </c>
-      <c r="L242" s="37">
-        <v>-2000</v>
-      </c>
-      <c r="M242" s="37" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="243" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A243" s="112">
-        <v>57001</v>
-      </c>
-      <c r="B243" s="113">
-        <v>105700</v>
-      </c>
-      <c r="C243" s="113" t="s">
-        <v>250</v>
-      </c>
-      <c r="D243" s="114">
-        <v>1</v>
-      </c>
-      <c r="E243" s="115" t="s">
-        <v>67</v>
-      </c>
-      <c r="F243" s="115"/>
-      <c r="G243" s="115"/>
-      <c r="H243" s="115"/>
-      <c r="I243" s="116"/>
-      <c r="J243" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="K243" s="110">
-        <v>2000</v>
-      </c>
-      <c r="L243" s="110">
-        <v>999999</v>
-      </c>
-      <c r="M243" s="117" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="244" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A244" s="112">
-        <v>57002</v>
-      </c>
-      <c r="B244" s="113">
-        <v>105700</v>
-      </c>
-      <c r="C244" s="113" t="s">
-        <v>250</v>
-      </c>
-      <c r="D244" s="114">
-        <v>2</v>
-      </c>
-      <c r="E244" s="115" t="s">
-        <v>69</v>
-      </c>
-      <c r="F244" s="115"/>
-      <c r="G244" s="115"/>
-      <c r="H244" s="115"/>
-      <c r="I244" s="116"/>
-      <c r="J244" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="K244" s="110">
-        <v>1000</v>
-      </c>
-      <c r="L244" s="110">
-        <v>2000</v>
-      </c>
-      <c r="M244" s="117" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="245" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A245" s="112">
-        <v>57003</v>
-      </c>
-      <c r="B245" s="113">
-        <v>105700</v>
-      </c>
-      <c r="C245" s="113" t="s">
-        <v>250</v>
-      </c>
-      <c r="D245" s="114">
-        <v>3</v>
-      </c>
-      <c r="E245" s="115" t="s">
-        <v>70</v>
-      </c>
-      <c r="F245" s="115"/>
-      <c r="G245" s="115"/>
-      <c r="H245" s="115"/>
-      <c r="I245" s="116"/>
-      <c r="J245" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="K245" s="110">
-        <v>500</v>
-      </c>
-      <c r="L245" s="110">
-        <v>1000</v>
-      </c>
-      <c r="M245" s="117" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="246" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A246" s="112">
-        <v>57004</v>
-      </c>
-      <c r="B246" s="113">
-        <v>105700</v>
-      </c>
-      <c r="C246" s="113" t="s">
-        <v>250</v>
-      </c>
-      <c r="D246" s="114">
-        <v>4</v>
-      </c>
-      <c r="E246" s="115" t="s">
-        <v>71</v>
-      </c>
-      <c r="F246" s="115"/>
-      <c r="G246" s="115"/>
-      <c r="H246" s="115"/>
-      <c r="I246" s="116"/>
-      <c r="J246" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="K246" s="110">
-        <v>-500</v>
-      </c>
-      <c r="L246" s="110">
-        <v>500</v>
-      </c>
-      <c r="M246" s="117" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="247" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A247" s="112">
-        <v>57005</v>
-      </c>
-      <c r="B247" s="113">
-        <v>105700</v>
-      </c>
-      <c r="C247" s="113" t="s">
-        <v>250</v>
-      </c>
-      <c r="D247" s="114">
-        <v>5</v>
-      </c>
-      <c r="E247" s="115" t="s">
-        <v>72</v>
-      </c>
-      <c r="F247" s="115"/>
-      <c r="G247" s="115"/>
-      <c r="H247" s="115"/>
-      <c r="I247" s="116"/>
-      <c r="J247" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="K247" s="110">
-        <v>-1000</v>
-      </c>
-      <c r="L247" s="110">
-        <v>-500</v>
-      </c>
-      <c r="M247" s="117" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="248" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A248" s="112">
-        <v>57006</v>
-      </c>
-      <c r="B248" s="113">
-        <v>105700</v>
-      </c>
-      <c r="C248" s="113" t="s">
-        <v>250</v>
-      </c>
-      <c r="D248" s="114">
-        <v>6</v>
-      </c>
-      <c r="E248" s="115" t="s">
-        <v>73</v>
-      </c>
-      <c r="F248" s="115"/>
-      <c r="G248" s="115"/>
-      <c r="H248" s="115"/>
-      <c r="I248" s="116"/>
-      <c r="J248" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="K248" s="110">
-        <v>-2000</v>
-      </c>
-      <c r="L248" s="110">
-        <v>-1000</v>
-      </c>
-      <c r="M248" s="117" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="249" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A249" s="112">
-        <v>57007</v>
-      </c>
-      <c r="B249" s="113">
-        <v>105700</v>
-      </c>
-      <c r="C249" s="113" t="s">
-        <v>250</v>
-      </c>
-      <c r="D249" s="114">
-        <v>7</v>
-      </c>
-      <c r="E249" s="115" t="s">
-        <v>74</v>
-      </c>
-      <c r="F249" s="115"/>
-      <c r="G249" s="115"/>
-      <c r="H249" s="115"/>
-      <c r="I249" s="116"/>
-      <c r="J249" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="K249" s="110">
-        <v>-999999</v>
-      </c>
-      <c r="L249" s="110">
-        <v>-2000</v>
-      </c>
-      <c r="M249" s="117" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="250" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A250" s="21">
-        <v>58001</v>
-      </c>
-      <c r="B250" s="118">
-        <v>105800</v>
-      </c>
-      <c r="C250" s="118" t="s">
-        <v>251</v>
-      </c>
-      <c r="D250" s="118">
-        <v>1</v>
-      </c>
-      <c r="E250" s="26" t="s">
-        <v>241</v>
-      </c>
-      <c r="F250" s="26"/>
-      <c r="G250" s="26"/>
-      <c r="H250" s="26"/>
-      <c r="I250" s="116"/>
-      <c r="J250" s="30" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="251" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A251" s="21">
-        <v>58002</v>
-      </c>
-      <c r="B251" s="118">
-        <v>105800</v>
-      </c>
-      <c r="C251" s="118" t="s">
-        <v>251</v>
-      </c>
-      <c r="D251" s="118">
-        <v>2</v>
-      </c>
-      <c r="E251" s="26" t="s">
-        <v>243</v>
-      </c>
-      <c r="F251" s="26"/>
-      <c r="G251" s="26"/>
-      <c r="H251" s="26"/>
-      <c r="I251" s="116"/>
-      <c r="J251" s="26" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="252" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A252" s="21">
-        <v>58003</v>
-      </c>
-      <c r="B252" s="118">
-        <v>105800</v>
-      </c>
-      <c r="C252" s="118" t="s">
-        <v>251</v>
-      </c>
-      <c r="D252" s="118">
-        <v>3</v>
-      </c>
-      <c r="E252" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="F252" s="26"/>
-      <c r="G252" s="26"/>
-      <c r="H252" s="26"/>
-      <c r="I252" s="116"/>
-      <c r="J252" s="26" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="253" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A253" s="21">
-        <v>58004</v>
-      </c>
-      <c r="B253" s="118">
-        <v>105800</v>
-      </c>
-      <c r="C253" s="118" t="s">
-        <v>251</v>
-      </c>
-      <c r="D253" s="118">
-        <v>4</v>
-      </c>
-      <c r="E253" s="26" t="s">
-        <v>245</v>
-      </c>
-      <c r="F253" s="26"/>
-      <c r="G253" s="26"/>
-      <c r="H253" s="26"/>
-      <c r="I253" s="116"/>
-      <c r="J253" s="26" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="254" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A254" s="21">
-        <v>58005</v>
-      </c>
-      <c r="B254" s="118">
-        <v>105800</v>
-      </c>
-      <c r="C254" s="118" t="s">
-        <v>251</v>
-      </c>
-      <c r="D254" s="118">
-        <v>5</v>
-      </c>
-      <c r="E254" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="F254" s="26"/>
-      <c r="G254" s="26"/>
-      <c r="H254" s="26"/>
-      <c r="I254" s="116"/>
-      <c r="J254" s="26" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="255" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A255" s="21">
-        <v>58006</v>
-      </c>
-      <c r="B255" s="118">
-        <v>105800</v>
-      </c>
-      <c r="C255" s="118" t="s">
-        <v>251</v>
-      </c>
-      <c r="D255" s="118">
-        <v>6</v>
-      </c>
-      <c r="E255" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="F255" s="26"/>
-      <c r="G255" s="26"/>
-      <c r="H255" s="26"/>
-      <c r="I255" s="116"/>
-      <c r="J255" s="26" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="256" s="21" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A256" s="21">
-        <v>58007</v>
-      </c>
-      <c r="B256" s="118">
-        <v>105800</v>
-      </c>
-      <c r="C256" s="118" t="s">
-        <v>251</v>
-      </c>
-      <c r="D256" s="118">
-        <v>7</v>
-      </c>
-      <c r="E256" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="F256" s="26"/>
-      <c r="G256" s="26"/>
-      <c r="H256" s="26"/>
-      <c r="I256" s="116"/>
-      <c r="J256" s="26" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="257" ht="16.5" spans="1:13">
-      <c r="A257" s="119">
-        <v>55001</v>
-      </c>
-      <c r="B257" s="120">
-        <v>105500</v>
-      </c>
-      <c r="C257" s="120" t="s">
-        <v>252</v>
-      </c>
-      <c r="D257" s="79">
-        <v>1</v>
-      </c>
-      <c r="E257" s="81" t="s">
-        <v>253</v>
-      </c>
-      <c r="F257" s="81"/>
-      <c r="G257" s="81"/>
-      <c r="H257" s="81"/>
-      <c r="I257" s="116"/>
-      <c r="J257" s="99" t="s">
-        <v>254</v>
-      </c>
-      <c r="K257" s="31">
-        <v>8000</v>
-      </c>
-      <c r="L257" s="31">
-        <v>999999</v>
-      </c>
-      <c r="M257" s="121" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="258" ht="16.5" spans="1:13">
-      <c r="A258" s="119">
-        <v>55002</v>
-      </c>
-      <c r="B258" s="120">
-        <v>105500</v>
-      </c>
-      <c r="C258" s="120" t="s">
-        <v>252</v>
-      </c>
-      <c r="D258" s="79">
-        <v>2</v>
-      </c>
-      <c r="E258" s="81" t="s">
-        <v>255</v>
-      </c>
-      <c r="F258" s="81"/>
-      <c r="G258" s="81"/>
-      <c r="H258" s="81"/>
-      <c r="I258" s="116"/>
-      <c r="J258" s="99" t="str">
-        <f t="shared" ref="J258:J263" si="28">J257</f>
-        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
-      </c>
-      <c r="K258" s="31">
-        <v>6000</v>
-      </c>
-      <c r="L258" s="31">
-        <v>8000</v>
-      </c>
-      <c r="M258" s="121" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="259" ht="16.5" spans="1:13">
-      <c r="A259" s="119">
-        <v>55003</v>
-      </c>
-      <c r="B259" s="120">
-        <v>105500</v>
-      </c>
-      <c r="C259" s="120" t="s">
-        <v>252</v>
-      </c>
-      <c r="D259" s="79">
-        <v>3</v>
-      </c>
-      <c r="E259" s="81" t="s">
-        <v>256</v>
-      </c>
-      <c r="F259" s="81"/>
-      <c r="G259" s="81"/>
-      <c r="H259" s="81"/>
-      <c r="I259" s="116"/>
-      <c r="J259" s="99" t="str">
+      <c r="E273" s="81" t="s">
+        <v>258</v>
+      </c>
+      <c r="F273" s="81"/>
+      <c r="G273" s="81"/>
+      <c r="H273" s="81"/>
+      <c r="I273" s="124"/>
+      <c r="J273" s="99" t="str">
         <f t="shared" si="28"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
-      <c r="K259" s="31">
+      <c r="K273" s="31">
         <v>4000</v>
       </c>
-      <c r="L259" s="31">
+      <c r="L273" s="31">
         <v>6000</v>
       </c>
-      <c r="M259" s="121" t="s">
+      <c r="M273" s="129" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="260" ht="16.5" spans="1:13">
-      <c r="A260" s="119">
+    <row r="274" ht="16.5" spans="1:13">
+      <c r="A274" s="127">
         <v>55004</v>
       </c>
-      <c r="B260" s="120">
+      <c r="B274" s="128">
         <v>105500</v>
       </c>
-      <c r="C260" s="120" t="s">
-        <v>252</v>
-      </c>
-      <c r="D260" s="79">
+      <c r="C274" s="128" t="s">
+        <v>254</v>
+      </c>
+      <c r="D274" s="79">
         <v>4</v>
       </c>
-      <c r="E260" s="81" t="s">
-        <v>257</v>
-      </c>
-      <c r="F260" s="81"/>
-      <c r="G260" s="81"/>
-      <c r="H260" s="81"/>
-      <c r="I260" s="116"/>
-      <c r="J260" s="99" t="str">
+      <c r="E274" s="81" t="s">
+        <v>259</v>
+      </c>
+      <c r="F274" s="81"/>
+      <c r="G274" s="81"/>
+      <c r="H274" s="81"/>
+      <c r="I274" s="124"/>
+      <c r="J274" s="99" t="str">
         <f t="shared" si="28"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
-      <c r="K260" s="31">
+      <c r="K274" s="31">
         <v>2000</v>
       </c>
-      <c r="L260" s="31">
+      <c r="L274" s="31">
         <v>4000</v>
       </c>
-      <c r="M260" s="121" t="s">
+      <c r="M274" s="129" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="261" ht="16.5" spans="1:13">
-      <c r="A261" s="119">
+    <row r="275" ht="16.5" spans="1:13">
+      <c r="A275" s="127">
         <v>55005</v>
       </c>
-      <c r="B261" s="120">
+      <c r="B275" s="128">
         <v>105500</v>
       </c>
-      <c r="C261" s="120" t="s">
-        <v>252</v>
-      </c>
-      <c r="D261" s="79">
+      <c r="C275" s="128" t="s">
+        <v>254</v>
+      </c>
+      <c r="D275" s="79">
         <v>5</v>
       </c>
-      <c r="E261" s="81" t="s">
-        <v>258</v>
-      </c>
-      <c r="F261" s="81"/>
-      <c r="G261" s="81"/>
-      <c r="H261" s="81"/>
-      <c r="I261" s="116"/>
-      <c r="J261" s="99" t="str">
+      <c r="E275" s="81" t="s">
+        <v>260</v>
+      </c>
+      <c r="F275" s="81"/>
+      <c r="G275" s="81"/>
+      <c r="H275" s="81"/>
+      <c r="I275" s="124"/>
+      <c r="J275" s="99" t="str">
         <f t="shared" si="28"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
-      <c r="K261" s="31">
+      <c r="K275" s="31">
         <v>0</v>
       </c>
-      <c r="L261" s="31">
+      <c r="L275" s="31">
         <v>2000</v>
       </c>
-      <c r="M261" s="121" t="s">
+      <c r="M275" s="129" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="262" ht="16.5" spans="1:13">
-      <c r="A262" s="119">
+    <row r="276" ht="16.5" spans="1:13">
+      <c r="A276" s="127">
         <v>55006</v>
       </c>
-      <c r="B262" s="120">
+      <c r="B276" s="128">
         <v>105500</v>
       </c>
-      <c r="C262" s="120" t="s">
-        <v>252</v>
-      </c>
-      <c r="D262" s="79">
+      <c r="C276" s="128" t="s">
+        <v>254</v>
+      </c>
+      <c r="D276" s="79">
         <v>6</v>
       </c>
-      <c r="E262" s="81" t="s">
+      <c r="E276" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="F262" s="81"/>
-      <c r="G262" s="81"/>
-      <c r="H262" s="81"/>
-      <c r="I262" s="116"/>
-      <c r="J262" s="99" t="str">
+      <c r="F276" s="81"/>
+      <c r="G276" s="81"/>
+      <c r="H276" s="81"/>
+      <c r="I276" s="124"/>
+      <c r="J276" s="99" t="str">
         <f t="shared" si="28"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
-      <c r="K262" s="31">
+      <c r="K276" s="31">
         <v>-1000</v>
       </c>
-      <c r="L262" s="31">
+      <c r="L276" s="31">
         <v>0</v>
       </c>
-      <c r="M262" s="121" t="s">
+      <c r="M276" s="129" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="263" ht="16.5" spans="1:13">
-      <c r="A263" s="119">
+    <row r="277" ht="16.5" spans="1:13">
+      <c r="A277" s="127">
         <v>55007</v>
       </c>
-      <c r="B263" s="120">
+      <c r="B277" s="128">
         <v>105500</v>
       </c>
-      <c r="C263" s="120" t="s">
-        <v>252</v>
-      </c>
-      <c r="D263" s="79">
+      <c r="C277" s="128" t="s">
+        <v>254</v>
+      </c>
+      <c r="D277" s="79">
         <v>7</v>
       </c>
-      <c r="E263" s="81" t="s">
+      <c r="E277" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="F263" s="81"/>
-      <c r="G263" s="81"/>
-      <c r="H263" s="81"/>
-      <c r="I263" s="116"/>
-      <c r="J263" s="99" t="str">
+      <c r="F277" s="81"/>
+      <c r="G277" s="81"/>
+      <c r="H277" s="81"/>
+      <c r="I277" s="124"/>
+      <c r="J277" s="99" t="str">
         <f t="shared" si="28"/>
         <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</v>
       </c>
-      <c r="K263" s="31">
+      <c r="K277" s="31">
         <v>-999999</v>
       </c>
-      <c r="L263" s="31">
+      <c r="L277" s="31">
         <v>-1000</v>
       </c>
-      <c r="M263" s="121" t="s">
+      <c r="M277" s="129" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="264" ht="16.5" spans="1:13">
-      <c r="A264" s="119">
+    <row r="278" ht="16.5" spans="1:13">
+      <c r="A278" s="127">
         <v>55011</v>
       </c>
-      <c r="B264" s="120">
+      <c r="B278" s="128">
         <v>105501</v>
       </c>
-      <c r="C264" s="120" t="s">
-        <v>259</v>
-      </c>
-      <c r="D264" s="79">
+      <c r="C278" s="128" t="s">
+        <v>261</v>
+      </c>
+      <c r="D278" s="79">
         <v>1</v>
       </c>
-      <c r="E264" s="115" t="s">
+      <c r="E278" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="F264" s="115"/>
-      <c r="G264" s="115"/>
-      <c r="H264" s="115"/>
-      <c r="I264" s="116"/>
-      <c r="J264" s="99" t="s">
-        <v>254</v>
-      </c>
-      <c r="K264" s="31">
+      <c r="F278" s="123"/>
+      <c r="G278" s="123"/>
+      <c r="H278" s="123"/>
+      <c r="I278" s="124"/>
+      <c r="J278" s="99" t="s">
+        <v>256</v>
+      </c>
+      <c r="K278" s="31">
         <v>8000</v>
       </c>
-      <c r="L264" s="31">
+      <c r="L278" s="31">
         <v>999999</v>
       </c>
-      <c r="M264" s="121" t="s">
+      <c r="M278" s="129" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="265" ht="16.5" spans="1:13">
-      <c r="A265" s="119">
+    <row r="279" ht="16.5" spans="1:13">
+      <c r="A279" s="127">
         <v>55012</v>
       </c>
-      <c r="B265" s="120">
+      <c r="B279" s="128">
         <v>105501</v>
       </c>
-      <c r="C265" s="120" t="s">
-        <v>259</v>
-      </c>
-      <c r="D265" s="79">
+      <c r="C279" s="128" t="s">
+        <v>261</v>
+      </c>
+      <c r="D279" s="79">
         <v>2</v>
       </c>
-      <c r="E265" s="115" t="s">
+      <c r="E279" s="123" t="s">
         <v>69</v>
       </c>
-      <c r="F265" s="115"/>
-      <c r="G265" s="115"/>
-      <c r="H265" s="115"/>
-      <c r="I265" s="116"/>
-      <c r="J265" s="99" t="s">
+      <c r="F279" s="123"/>
+      <c r="G279" s="123"/>
+      <c r="H279" s="123"/>
+      <c r="I279" s="124"/>
+      <c r="J279" s="99" t="s">
         <v>200</v>
       </c>
-      <c r="K265" s="31">
+      <c r="K279" s="31">
         <v>6000</v>
       </c>
-      <c r="L265" s="31">
+      <c r="L279" s="31">
         <v>8000</v>
       </c>
-      <c r="M265" s="121" t="s">
+      <c r="M279" s="129" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="266" ht="16.5" spans="1:13">
-      <c r="A266" s="119">
+    <row r="280" ht="16.5" spans="1:13">
+      <c r="A280" s="127">
         <v>55013</v>
       </c>
-      <c r="B266" s="120">
+      <c r="B280" s="128">
         <v>105501</v>
       </c>
-      <c r="C266" s="120" t="s">
-        <v>259</v>
-      </c>
-      <c r="D266" s="79">
+      <c r="C280" s="128" t="s">
+        <v>261</v>
+      </c>
+      <c r="D280" s="79">
         <v>3</v>
       </c>
-      <c r="E266" s="115" t="s">
+      <c r="E280" s="123" t="s">
         <v>70</v>
       </c>
-      <c r="F266" s="115"/>
-      <c r="G266" s="115"/>
-      <c r="H266" s="115"/>
-      <c r="I266" s="116"/>
-      <c r="J266" s="99" t="s">
+      <c r="F280" s="123"/>
+      <c r="G280" s="123"/>
+      <c r="H280" s="123"/>
+      <c r="I280" s="124"/>
+      <c r="J280" s="99" t="s">
         <v>200</v>
       </c>
-      <c r="K266" s="31">
+      <c r="K280" s="31">
         <v>4000</v>
       </c>
-      <c r="L266" s="31">
+      <c r="L280" s="31">
         <v>6000</v>
       </c>
-      <c r="M266" s="121" t="s">
+      <c r="M280" s="129" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="267" ht="16.5" spans="1:13">
-      <c r="A267" s="119">
+    <row r="281" ht="16.5" spans="1:13">
+      <c r="A281" s="127">
         <v>55014</v>
       </c>
-      <c r="B267" s="120">
+      <c r="B281" s="128">
         <v>105501</v>
       </c>
-      <c r="C267" s="120" t="s">
-        <v>259</v>
-      </c>
-      <c r="D267" s="79">
+      <c r="C281" s="128" t="s">
+        <v>261</v>
+      </c>
+      <c r="D281" s="79">
         <v>4</v>
       </c>
-      <c r="E267" s="115" t="s">
+      <c r="E281" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="F267" s="115"/>
-      <c r="G267" s="115"/>
-      <c r="H267" s="115"/>
-      <c r="I267" s="116"/>
-      <c r="J267" s="99" t="s">
+      <c r="F281" s="123"/>
+      <c r="G281" s="123"/>
+      <c r="H281" s="123"/>
+      <c r="I281" s="124"/>
+      <c r="J281" s="99" t="s">
         <v>200</v>
       </c>
-      <c r="K267" s="31">
+      <c r="K281" s="31">
         <v>2000</v>
       </c>
-      <c r="L267" s="31">
+      <c r="L281" s="31">
         <v>4000</v>
       </c>
-      <c r="M267" s="121" t="s">
+      <c r="M281" s="129" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="268" ht="16.5" spans="1:13">
-      <c r="A268" s="119">
+    <row r="282" ht="16.5" spans="1:13">
+      <c r="A282" s="127">
         <v>55015</v>
       </c>
-      <c r="B268" s="120">
+      <c r="B282" s="128">
         <v>105501</v>
       </c>
-      <c r="C268" s="120" t="s">
-        <v>259</v>
-      </c>
-      <c r="D268" s="79">
+      <c r="C282" s="128" t="s">
+        <v>261</v>
+      </c>
+      <c r="D282" s="79">
         <v>5</v>
       </c>
-      <c r="E268" s="115" t="s">
+      <c r="E282" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="F268" s="115"/>
-      <c r="G268" s="115"/>
-      <c r="H268" s="115"/>
-      <c r="I268" s="116"/>
-      <c r="J268" s="99" t="s">
+      <c r="F282" s="123"/>
+      <c r="G282" s="123"/>
+      <c r="H282" s="123"/>
+      <c r="I282" s="124"/>
+      <c r="J282" s="99" t="s">
         <v>200</v>
       </c>
-      <c r="K268" s="31">
+      <c r="K282" s="31">
         <v>0</v>
       </c>
-      <c r="L268" s="31">
+      <c r="L282" s="31">
         <v>2000</v>
       </c>
-      <c r="M268" s="121" t="s">
+      <c r="M282" s="129" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="269" ht="16.5" spans="1:13">
-      <c r="A269" s="119">
+    <row r="283" ht="16.5" spans="1:13">
+      <c r="A283" s="127">
         <v>55016</v>
       </c>
-      <c r="B269" s="120">
+      <c r="B283" s="128">
         <v>105501</v>
       </c>
-      <c r="C269" s="120" t="s">
-        <v>259</v>
-      </c>
-      <c r="D269" s="79">
+      <c r="C283" s="128" t="s">
+        <v>261</v>
+      </c>
+      <c r="D283" s="79">
         <v>6</v>
       </c>
-      <c r="E269" s="115" t="s">
+      <c r="E283" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="F269" s="115"/>
-      <c r="G269" s="115"/>
-      <c r="H269" s="115"/>
-      <c r="I269" s="116"/>
-      <c r="J269" s="99" t="s">
+      <c r="F283" s="123"/>
+      <c r="G283" s="123"/>
+      <c r="H283" s="123"/>
+      <c r="I283" s="124"/>
+      <c r="J283" s="99" t="s">
         <v>200</v>
       </c>
-      <c r="K269" s="31">
+      <c r="K283" s="31">
         <v>-1000</v>
       </c>
-      <c r="L269" s="31">
+      <c r="L283" s="31">
         <v>0</v>
       </c>
-      <c r="M269" s="121" t="s">
+      <c r="M283" s="129" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="270" ht="16.5" spans="1:13">
-      <c r="A270" s="119">
+    <row r="284" ht="16.5" spans="1:13">
+      <c r="A284" s="127">
         <v>55017</v>
       </c>
-      <c r="B270" s="120">
+      <c r="B284" s="128">
         <v>105501</v>
       </c>
-      <c r="C270" s="120" t="s">
-        <v>259</v>
-      </c>
-      <c r="D270" s="79">
+      <c r="C284" s="128" t="s">
+        <v>261</v>
+      </c>
+      <c r="D284" s="79">
         <v>7</v>
       </c>
-      <c r="E270" s="115" t="s">
+      <c r="E284" s="123" t="s">
         <v>74</v>
       </c>
-      <c r="F270" s="115"/>
-      <c r="G270" s="115"/>
-      <c r="H270" s="115"/>
-      <c r="I270" s="116"/>
-      <c r="J270" s="99" t="s">
+      <c r="F284" s="123"/>
+      <c r="G284" s="123"/>
+      <c r="H284" s="123"/>
+      <c r="I284" s="124"/>
+      <c r="J284" s="99" t="s">
         <v>200</v>
       </c>
-      <c r="K270" s="31">
+      <c r="K284" s="31">
         <v>-999999</v>
       </c>
-      <c r="L270" s="31">
+      <c r="L284" s="31">
         <v>-1000</v>
       </c>
-      <c r="M270" s="121" t="s">
+      <c r="M284" s="129" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="271" s="22" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A271" s="122">
+    <row r="285" s="22" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A285" s="130">
         <v>55021</v>
       </c>
-      <c r="B271" s="123">
+      <c r="B285" s="131">
         <v>105502</v>
       </c>
-      <c r="C271" s="123" t="s">
-        <v>260</v>
-      </c>
-      <c r="D271" s="123">
+      <c r="C285" s="131" t="s">
+        <v>262</v>
+      </c>
+      <c r="D285" s="131">
         <v>1</v>
       </c>
-      <c r="E271" s="94" t="s">
+      <c r="E285" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="F271" s="94"/>
-      <c r="G271" s="94"/>
-      <c r="H271" s="94"/>
-      <c r="I271" s="94"/>
-      <c r="J271" s="124" t="s">
-        <v>254</v>
-      </c>
-      <c r="K271" s="125">
+      <c r="F285" s="94"/>
+      <c r="G285" s="94"/>
+      <c r="H285" s="94"/>
+      <c r="I285" s="94"/>
+      <c r="J285" s="132" t="s">
+        <v>256</v>
+      </c>
+      <c r="K285" s="133">
         <v>8000</v>
       </c>
-      <c r="L271" s="125">
+      <c r="L285" s="133">
         <v>999999</v>
       </c>
-      <c r="M271" s="124" t="s">
+      <c r="M285" s="132" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="272" s="22" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A272" s="122">
+    <row r="286" s="22" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A286" s="130">
         <v>55022</v>
       </c>
-      <c r="B272" s="123">
+      <c r="B286" s="131">
         <v>105502</v>
       </c>
-      <c r="C272" s="123" t="s">
-        <v>260</v>
-      </c>
-      <c r="D272" s="123">
+      <c r="C286" s="131" t="s">
+        <v>262</v>
+      </c>
+      <c r="D286" s="131">
         <v>2</v>
       </c>
-      <c r="E272" s="94" t="s">
+      <c r="E286" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="F272" s="94"/>
-      <c r="G272" s="94"/>
-      <c r="H272" s="94"/>
-      <c r="I272" s="94"/>
-      <c r="J272" s="124" t="s">
+      <c r="F286" s="94"/>
+      <c r="G286" s="94"/>
+      <c r="H286" s="94"/>
+      <c r="I286" s="94"/>
+      <c r="J286" s="132" t="s">
         <v>200</v>
       </c>
-      <c r="K272" s="125">
+      <c r="K286" s="133">
         <v>6000</v>
       </c>
-      <c r="L272" s="125">
+      <c r="L286" s="133">
         <v>8000</v>
       </c>
-      <c r="M272" s="124" t="s">
+      <c r="M286" s="132" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="273" s="22" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A273" s="122">
+    <row r="287" s="22" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A287" s="130">
         <v>55023</v>
       </c>
-      <c r="B273" s="123">
+      <c r="B287" s="131">
         <v>105502</v>
       </c>
-      <c r="C273" s="123" t="s">
-        <v>260</v>
-      </c>
-      <c r="D273" s="123">
+      <c r="C287" s="131" t="s">
+        <v>262</v>
+      </c>
+      <c r="D287" s="131">
         <v>3</v>
       </c>
-      <c r="E273" s="94" t="s">
+      <c r="E287" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="F273" s="94"/>
-      <c r="G273" s="94"/>
-      <c r="H273" s="94"/>
-      <c r="I273" s="94"/>
-      <c r="J273" s="124" t="s">
+      <c r="F287" s="94"/>
+      <c r="G287" s="94"/>
+      <c r="H287" s="94"/>
+      <c r="I287" s="94"/>
+      <c r="J287" s="132" t="s">
         <v>200</v>
       </c>
-      <c r="K273" s="125">
+      <c r="K287" s="133">
         <v>4000</v>
       </c>
-      <c r="L273" s="125">
+      <c r="L287" s="133">
         <v>6000</v>
       </c>
-      <c r="M273" s="124" t="s">
+      <c r="M287" s="132" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="274" s="22" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A274" s="122">
+    <row r="288" s="22" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A288" s="130">
         <v>55024</v>
       </c>
-      <c r="B274" s="123">
+      <c r="B288" s="131">
         <v>105502</v>
       </c>
-      <c r="C274" s="123" t="s">
-        <v>260</v>
-      </c>
-      <c r="D274" s="123">
+      <c r="C288" s="131" t="s">
+        <v>262</v>
+      </c>
+      <c r="D288" s="131">
         <v>4</v>
       </c>
-      <c r="E274" s="94" t="s">
+      <c r="E288" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="F274" s="94"/>
-      <c r="G274" s="94"/>
-      <c r="H274" s="94"/>
-      <c r="I274" s="94"/>
-      <c r="J274" s="124" t="s">
+      <c r="F288" s="94"/>
+      <c r="G288" s="94"/>
+      <c r="H288" s="94"/>
+      <c r="I288" s="94"/>
+      <c r="J288" s="132" t="s">
         <v>200</v>
       </c>
-      <c r="K274" s="125">
+      <c r="K288" s="133">
         <v>2000</v>
       </c>
-      <c r="L274" s="125">
+      <c r="L288" s="133">
         <v>4000</v>
       </c>
-      <c r="M274" s="124" t="s">
+      <c r="M288" s="132" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="275" s="22" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A275" s="122">
+    <row r="289" s="22" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A289" s="130">
         <v>55025</v>
       </c>
-      <c r="B275" s="123">
+      <c r="B289" s="131">
         <v>105502</v>
       </c>
-      <c r="C275" s="123" t="s">
-        <v>260</v>
-      </c>
-      <c r="D275" s="123">
+      <c r="C289" s="131" t="s">
+        <v>262</v>
+      </c>
+      <c r="D289" s="131">
         <v>5</v>
       </c>
-      <c r="E275" s="94" t="s">
+      <c r="E289" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="F275" s="94"/>
-      <c r="G275" s="94"/>
-      <c r="H275" s="94"/>
-      <c r="I275" s="94"/>
-      <c r="J275" s="124" t="s">
+      <c r="F289" s="94"/>
+      <c r="G289" s="94"/>
+      <c r="H289" s="94"/>
+      <c r="I289" s="94"/>
+      <c r="J289" s="132" t="s">
         <v>200</v>
       </c>
-      <c r="K275" s="125">
+      <c r="K289" s="133">
         <v>0</v>
       </c>
-      <c r="L275" s="125">
+      <c r="L289" s="133">
         <v>2000</v>
       </c>
-      <c r="M275" s="124" t="s">
+      <c r="M289" s="132" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="276" s="22" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A276" s="122">
+    <row r="290" s="22" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A290" s="130">
         <v>55026</v>
       </c>
-      <c r="B276" s="123">
+      <c r="B290" s="131">
         <v>105502</v>
       </c>
-      <c r="C276" s="123" t="s">
-        <v>260</v>
-      </c>
-      <c r="D276" s="123">
+      <c r="C290" s="131" t="s">
+        <v>262</v>
+      </c>
+      <c r="D290" s="131">
         <v>6</v>
       </c>
-      <c r="E276" s="94" t="s">
+      <c r="E290" s="94" t="s">
         <v>73</v>
       </c>
-      <c r="F276" s="94"/>
-      <c r="G276" s="94"/>
-      <c r="H276" s="94"/>
-      <c r="I276" s="94"/>
-      <c r="J276" s="124" t="s">
+      <c r="F290" s="94"/>
+      <c r="G290" s="94"/>
+      <c r="H290" s="94"/>
+      <c r="I290" s="94"/>
+      <c r="J290" s="132" t="s">
         <v>200</v>
       </c>
-      <c r="K276" s="125">
+      <c r="K290" s="133">
         <v>-1000</v>
       </c>
-      <c r="L276" s="125">
+      <c r="L290" s="133">
         <v>0</v>
       </c>
-      <c r="M276" s="124" t="s">
+      <c r="M290" s="132" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="277" s="22" customFormat="1" ht="16.5" spans="1:13">
-      <c r="A277" s="122">
+    <row r="291" s="22" customFormat="1" ht="16.5" spans="1:13">
+      <c r="A291" s="130">
         <v>55027</v>
       </c>
-      <c r="B277" s="123">
+      <c r="B291" s="131">
         <v>105502</v>
       </c>
-      <c r="C277" s="123" t="s">
-        <v>260</v>
-      </c>
-      <c r="D277" s="123">
+      <c r="C291" s="131" t="s">
+        <v>262</v>
+      </c>
+      <c r="D291" s="131">
         <v>7</v>
       </c>
-      <c r="E277" s="94" t="s">
+      <c r="E291" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="F277" s="94"/>
-      <c r="G277" s="94"/>
-      <c r="H277" s="94"/>
-      <c r="I277" s="94"/>
-      <c r="J277" s="124" t="s">
+      <c r="F291" s="94"/>
+      <c r="G291" s="94"/>
+      <c r="H291" s="94"/>
+      <c r="I291" s="94"/>
+      <c r="J291" s="132" t="s">
         <v>200</v>
       </c>
-      <c r="K277" s="125">
+      <c r="K291" s="133">
         <v>-999999</v>
       </c>
-      <c r="L277" s="125">
+      <c r="L291" s="133">
         <v>-1000</v>
       </c>
-      <c r="M277" s="124" t="s">
+      <c r="M291" s="132" t="s">
         <v>44</v>
       </c>
     </row>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -246,7 +246,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="299">
   <si>
     <t>id</t>
   </si>
@@ -800,7 +800,25 @@
     <t>象财神</t>
   </si>
   <si>
-    <t>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+    <t>1_8830|2_1120|3_50</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9010|2_940|3_50</t>
+  </si>
+  <si>
+    <t>1_9190|2_760|3_50</t>
+  </si>
+  <si>
+    <t>1_9340|2_560|3_100</t>
+  </si>
+  <si>
+    <t>1_9640|2_360|3_0</t>
+  </si>
+  <si>
+    <t>1_9820|2_180|3_0</t>
   </si>
   <si>
     <t>王牌dj</t>
@@ -971,154 +989,157 @@
     <t>10倍金牛</t>
   </si>
   <si>
-    <t>1_9290|2_700|3_10</t>
+    <t>1_8650|2_1300|3_50</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_8870|2_1080|3_50</t>
+  </si>
+  <si>
+    <t>1_9090|2_860|3_50</t>
+  </si>
+  <si>
+    <t>1_9580|2_420|3_0</t>
+  </si>
+  <si>
+    <t>1_9790|2_210|3_0</t>
+  </si>
+  <si>
+    <t>愤怒的小鸡</t>
+  </si>
+  <si>
+    <t>1_9590|2_400|3_10</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-59200|1&amp;25-7500|25&amp;50-6700|50&amp;75-5700|75&amp;100-3200|100&amp;125-3000|125&amp;150-1800|150&amp;175-1800|175&amp;200-1200|200&amp;225-1300|225&amp;250-900|250&amp;300-1400|300&amp;350-1300|350&amp;400-800|400&amp;450-600|450&amp;500-400|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-6900|1200&amp;1400-6100|1400&amp;1600-5900|1600&amp;1800-5300|1800&amp;2000-4700|2000&amp;2400-7700|2400&amp;2800-6100|2800&amp;3200-5000|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9670|2_320|3_10</t>
+  </si>
+  <si>
+    <t>1_9710|2_280|3_10</t>
+  </si>
+  <si>
+    <t>1_9759|2_231|3_10</t>
+  </si>
+  <si>
+    <t>1_9820|2_170|3_10</t>
+  </si>
+  <si>
+    <t>1_9890|2_100|3_10</t>
+  </si>
+  <si>
+    <t>1_9940|2_50|3_10</t>
+  </si>
+  <si>
+    <t>潘金莲</t>
+  </si>
+  <si>
+    <t>1_9610|2_340|3_50</t>
+  </si>
+  <si>
+    <t>30,1&amp;0-20000|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0#30,1&amp;0-35000|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0</t>
+  </si>
+  <si>
+    <t>5,1&amp;0-30000|2-4000|3-0|4-0|5-0|6-0|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0#8,1&amp;0-10000|2-4000|3-0|4-0|5-0|6-0|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0#10,1&amp;0-0|2-4000|3-0|4-0|5-0|6-0|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0</t>
+  </si>
+  <si>
+    <t>1000000&amp;999999999_2,17-0|18-0</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-54800|1&amp;40-20000|40&amp;80-8100|80&amp;120-2000|120&amp;160-2800|160&amp;200-2100|200&amp;240-1600|240&amp;280-1200|280&amp;320-200|320&amp;360-800|360&amp;400-100|400&amp;480-100|480&amp;560-100|560&amp;640-100|640&amp;720-100|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-200|40&amp;80-400|80&amp;120-500|120&amp;160-500|160&amp;200-700|200&amp;240-700|240&amp;280-800|280&amp;320-900|320&amp;360-900|360&amp;400-1000|400&amp;480-2100|480&amp;560-2300|560&amp;640-2400|640&amp;720-2500|720&amp;800-2600|800&amp;960-5200|960&amp;1120-2000|1120&amp;1280-1000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;3,0&amp;1-84600|1&amp;40-13400|40&amp;80-1400|80&amp;120-300|120&amp;160-100|160&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9690|2_260|3_50</t>
+  </si>
+  <si>
+    <t>嗨到底</t>
+  </si>
+  <si>
+    <t>狂野沙滩</t>
+  </si>
+  <si>
+    <t>超级高尔夫</t>
+  </si>
+  <si>
+    <t>澳门壕梦</t>
+  </si>
+  <si>
+    <t>糖果派对</t>
+  </si>
+  <si>
+    <t>1_9850|4_140|7_10|2_9850|5_140|8_10|3_9850|6_140|9_10</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>麻将胡了2</t>
+  </si>
+  <si>
+    <t>1_9640|2_360</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9690|2_310</t>
+  </si>
+  <si>
+    <t>1_9740|2_260</t>
+  </si>
+  <si>
+    <t>1_9790|2_210</t>
+  </si>
+  <si>
+    <t>1_9820|2_180</t>
+  </si>
+  <si>
+    <t>1_9860|2_140</t>
+  </si>
+  <si>
+    <t>1_9900|2_100</t>
+  </si>
+  <si>
+    <t>黄金帝国</t>
+  </si>
+  <si>
+    <t>赏金大对决</t>
+  </si>
+  <si>
+    <t>极速糖果1000</t>
+  </si>
+  <si>
+    <t>伽罗宝石</t>
+  </si>
+  <si>
+    <t>1_8650|2_1300</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</t>
+  </si>
+  <si>
+    <t>1_8850|2_1100</t>
+  </si>
+  <si>
+    <t>1_9150|2_800</t>
+  </si>
+  <si>
+    <t>1_9500|2_500</t>
+  </si>
+  <si>
+    <t>1_9800|2_200</t>
+  </si>
+  <si>
+    <t>1_10000|2_0</t>
+  </si>
+  <si>
+    <t>伽罗宝石2</t>
   </si>
   <si>
     <t>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_9390|2_600|3_10</t>
-  </si>
-  <si>
-    <t>1_9490|2_500|3_10</t>
-  </si>
-  <si>
-    <t>1_9546|2_444|3_10</t>
-  </si>
-  <si>
-    <t>1_9690|2_300|3_10</t>
-  </si>
-  <si>
-    <t>1_9890|2_100|3_10</t>
-  </si>
-  <si>
-    <t>愤怒的小鸡</t>
-  </si>
-  <si>
-    <t>1_9590|2_400|3_10</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-59200|1&amp;25-7500|25&amp;50-6700|50&amp;75-5700|75&amp;100-3200|100&amp;125-3000|125&amp;150-1800|150&amp;175-1800|175&amp;200-1200|200&amp;225-1300|225&amp;250-900|250&amp;300-1400|300&amp;350-1300|350&amp;400-800|400&amp;450-600|450&amp;500-400|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-3700|1000&amp;1200-6900|1200&amp;1400-6100|1400&amp;1600-5900|1600&amp;1800-5300|1800&amp;2000-4700|2000&amp;2400-7700|2400&amp;2800-6100|2800&amp;3200-5000|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_9670|2_320|3_10</t>
-  </si>
-  <si>
-    <t>1_9710|2_280|3_10</t>
-  </si>
-  <si>
-    <t>1_9759|2_231|3_10</t>
-  </si>
-  <si>
-    <t>1_9820|2_170|3_10</t>
-  </si>
-  <si>
-    <t>1_9940|2_50|3_10</t>
-  </si>
-  <si>
-    <t>潘金莲</t>
-  </si>
-  <si>
-    <t>1_9610|2_340|3_50</t>
-  </si>
-  <si>
-    <t>30,1&amp;0-20000|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0#30,1&amp;0-35000|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0</t>
-  </si>
-  <si>
-    <t>5,1&amp;0-30000|2-4000|3-0|4-0|5-0|6-0|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0#8,1&amp;0-10000|2-4000|3-0|4-0|5-0|6-0|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0#10,1&amp;0-0|2-4000|3-0|4-0|5-0|6-0|7-0|8-0|9-0|10-0|11-0|12-0|13-0|14-0</t>
-  </si>
-  <si>
-    <t>1000000&amp;999999999_2,17-0|18-0</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-54800|1&amp;40-20000|40&amp;80-8100|80&amp;120-2000|120&amp;160-2800|160&amp;200-2100|200&amp;240-1600|240&amp;280-1200|280&amp;320-200|320&amp;360-800|360&amp;400-100|400&amp;480-100|480&amp;560-100|560&amp;640-100|640&amp;720-100|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;2,0&amp;1-100|1&amp;40-200|40&amp;80-400|80&amp;120-500|120&amp;160-500|160&amp;200-700|200&amp;240-700|240&amp;280-800|280&amp;320-900|320&amp;360-900|360&amp;400-1000|400&amp;480-2100|480&amp;560-2300|560&amp;640-2400|640&amp;720-2500|720&amp;800-2600|800&amp;960-5200|960&amp;1120-2000|1120&amp;1280-1000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0;3,0&amp;1-84600|1&amp;40-13400|40&amp;80-1400|80&amp;120-300|120&amp;160-100|160&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7680-0|7680&amp;8960-0|8960&amp;10240-0|10240&amp;11520-0|11520&amp;12800-0|12800&amp;14800-0|14800&amp;16800-0|16800&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_9690|2_260|3_50</t>
-  </si>
-  <si>
-    <t>嗨到底</t>
-  </si>
-  <si>
-    <t>狂野沙滩</t>
-  </si>
-  <si>
-    <t>超级高尔夫</t>
-  </si>
-  <si>
-    <t>澳门壕梦</t>
-  </si>
-  <si>
-    <t>糖果派对</t>
-  </si>
-  <si>
-    <t>1_9850|4_140|7_10|2_9850|5_140|8_10|3_9850|6_140|9_10</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;7,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;5,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;8,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;6,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;9,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>麻将胡了2</t>
-  </si>
-  <si>
-    <t>1_9640|2_360</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-70000|1&amp;20-18000|20&amp;40-6000|40&amp;60-2000|60&amp;80-1300|80&amp;100-800|100&amp;120-800|120&amp;140-500|140&amp;160-300|160&amp;180-200|180&amp;200-100|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-2000|240&amp;280-2000|280&amp;320-2000|320&amp;360-2000|360&amp;400-2000|400&amp;480-4000|480&amp;560-4000|560&amp;640-4000|640&amp;720-4000|720&amp;800-3600|800&amp;960-4000|960&amp;1120-4000|1120&amp;1280-4000|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_9690|2_310</t>
-  </si>
-  <si>
-    <t>1_9740|2_260</t>
-  </si>
-  <si>
-    <t>1_9790|2_210</t>
-  </si>
-  <si>
-    <t>1_9820|2_180</t>
-  </si>
-  <si>
-    <t>1_9860|2_140</t>
-  </si>
-  <si>
-    <t>1_9900|2_100</t>
-  </si>
-  <si>
-    <t>黄金帝国</t>
-  </si>
-  <si>
-    <t>赏金大对决</t>
-  </si>
-  <si>
-    <t>极速糖果1000</t>
-  </si>
-  <si>
-    <t>伽罗宝石</t>
-  </si>
-  <si>
-    <t>1_8650|2_1300</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;</t>
-  </si>
-  <si>
-    <t>1_8850|2_1100</t>
-  </si>
-  <si>
-    <t>1_9150|2_800</t>
-  </si>
-  <si>
-    <t>1_9500|2_500</t>
-  </si>
-  <si>
-    <t>1_9800|2_200</t>
-  </si>
-  <si>
-    <t>1_10000|2_0</t>
-  </si>
-  <si>
-    <t>伽罗宝石2</t>
   </si>
   <si>
     <t>伽罗宝石3</t>
@@ -7227,14 +7248,14 @@
         <v>1</v>
       </c>
       <c r="E124" s="64" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="F124" s="64"/>
       <c r="G124" s="64"/>
       <c r="H124" s="64"/>
       <c r="I124" s="26"/>
       <c r="J124" s="66" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K124" s="29">
         <v>1000</v>
@@ -7260,7 +7281,7 @@
         <v>2</v>
       </c>
       <c r="E125" s="64" t="s">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="F125" s="64"/>
       <c r="G125" s="64"/>
@@ -7268,7 +7289,7 @@
       <c r="I125" s="26"/>
       <c r="J125" s="66" t="str">
         <f t="shared" ref="J125:J130" si="1">J124</f>
-        <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K125" s="29">
         <v>600</v>
@@ -7294,7 +7315,7 @@
         <v>3</v>
       </c>
       <c r="E126" s="64" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="F126" s="64"/>
       <c r="G126" s="64"/>
@@ -7302,7 +7323,7 @@
       <c r="I126" s="26"/>
       <c r="J126" s="66" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K126" s="29">
         <v>250</v>
@@ -7328,7 +7349,7 @@
         <v>4</v>
       </c>
       <c r="E127" s="64" t="s">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="F127" s="64"/>
       <c r="G127" s="64"/>
@@ -7336,7 +7357,7 @@
       <c r="I127" s="26"/>
       <c r="J127" s="66" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K127" s="29">
         <v>-250</v>
@@ -7362,7 +7383,7 @@
         <v>5</v>
       </c>
       <c r="E128" s="64" t="s">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="F128" s="64"/>
       <c r="G128" s="64"/>
@@ -7370,7 +7391,7 @@
       <c r="I128" s="26"/>
       <c r="J128" s="66" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K128" s="29">
         <v>-600</v>
@@ -7396,7 +7417,7 @@
         <v>6</v>
       </c>
       <c r="E129" s="64" t="s">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="F129" s="64"/>
       <c r="G129" s="64"/>
@@ -7404,7 +7425,7 @@
       <c r="I129" s="26"/>
       <c r="J129" s="66" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K129" s="29">
         <v>-1000</v>
@@ -7430,7 +7451,7 @@
         <v>7</v>
       </c>
       <c r="E130" s="64" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F130" s="64"/>
       <c r="G130" s="64"/>
@@ -7438,7 +7459,7 @@
       <c r="I130" s="26"/>
       <c r="J130" s="66" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-60000|1&amp;20-30000|20&amp;40-4000|40&amp;60-3000|60&amp;80-2000|80&amp;100-1500|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-700|180&amp;200-600|200&amp;240-500|240&amp;280-300|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-300|60&amp;80-400|80&amp;100-400|100&amp;120-500|120&amp;140-400|140&amp;160-600|160&amp;180-500|180&amp;200-1200|200&amp;240-1400|240&amp;280-1500|280&amp;320-1800|320&amp;360-1700|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-500|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-0|20&amp;40-4700|40&amp;60-2800|60&amp;80-1500|80&amp;100-1300|100&amp;120-700|120&amp;140-600|140&amp;160-300|160&amp;180-400|180&amp;200-200|200&amp;240-300|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K130" s="29">
         <v>-999999</v>
@@ -7458,7 +7479,7 @@
         <v>102800</v>
       </c>
       <c r="C131" s="46" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D131" s="46">
         <v>1</v>
@@ -7491,7 +7512,7 @@
         <v>102800</v>
       </c>
       <c r="C132" s="46" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D132" s="46">
         <v>2</v>
@@ -7525,7 +7546,7 @@
         <v>102800</v>
       </c>
       <c r="C133" s="46" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D133" s="46">
         <v>3</v>
@@ -7559,7 +7580,7 @@
         <v>102800</v>
       </c>
       <c r="C134" s="46" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D134" s="46">
         <v>4</v>
@@ -7593,7 +7614,7 @@
         <v>102800</v>
       </c>
       <c r="C135" s="46" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D135" s="46">
         <v>5</v>
@@ -7627,7 +7648,7 @@
         <v>102800</v>
       </c>
       <c r="C136" s="46" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D136" s="46">
         <v>6</v>
@@ -7661,7 +7682,7 @@
         <v>102800</v>
       </c>
       <c r="C137" s="46" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D137" s="46">
         <v>7</v>
@@ -7695,20 +7716,20 @@
         <v>103100</v>
       </c>
       <c r="C138" s="70" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D138" s="70">
         <v>1</v>
       </c>
       <c r="E138" s="71" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F138" s="71"/>
       <c r="G138" s="71"/>
       <c r="H138" s="71"/>
       <c r="I138" s="26"/>
       <c r="J138" s="72" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K138" s="29">
         <v>1000</v>
@@ -7728,13 +7749,13 @@
         <v>103100</v>
       </c>
       <c r="C139" s="70" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D139" s="70">
         <v>2</v>
       </c>
       <c r="E139" s="71" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F139" s="71"/>
       <c r="G139" s="71"/>
@@ -7762,13 +7783,13 @@
         <v>103100</v>
       </c>
       <c r="C140" s="70" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D140" s="70">
         <v>3</v>
       </c>
       <c r="E140" s="71" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F140" s="71"/>
       <c r="G140" s="71"/>
@@ -7796,13 +7817,13 @@
         <v>103100</v>
       </c>
       <c r="C141" s="70" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D141" s="70">
         <v>4</v>
       </c>
       <c r="E141" s="71" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F141" s="71"/>
       <c r="G141" s="71"/>
@@ -7830,13 +7851,13 @@
         <v>103100</v>
       </c>
       <c r="C142" s="70" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D142" s="70">
         <v>5</v>
       </c>
       <c r="E142" s="71" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F142" s="71"/>
       <c r="G142" s="71"/>
@@ -7864,13 +7885,13 @@
         <v>103100</v>
       </c>
       <c r="C143" s="70" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D143" s="70">
         <v>6</v>
       </c>
       <c r="E143" s="71" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F143" s="71"/>
       <c r="G143" s="71"/>
@@ -7898,13 +7919,13 @@
         <v>103100</v>
       </c>
       <c r="C144" s="70" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D144" s="70">
         <v>7</v>
       </c>
       <c r="E144" s="71" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F144" s="71"/>
       <c r="G144" s="71"/>
@@ -7932,26 +7953,26 @@
         <v>103400</v>
       </c>
       <c r="C145" s="74" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D145" s="74">
         <v>1</v>
       </c>
       <c r="E145" s="75" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F145" s="75" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G145" s="75" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H145" s="75" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I145" s="26"/>
       <c r="J145" s="28" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K145" s="29">
         <v>1000</v>
@@ -7971,7 +7992,7 @@
         <v>103400</v>
       </c>
       <c r="C146" s="74" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D146" s="74">
         <v>2</v>
@@ -7980,17 +8001,17 @@
         <v>93</v>
       </c>
       <c r="F146" s="75" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G146" s="75" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H146" s="75" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I146" s="26"/>
       <c r="J146" s="76" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K146" s="29">
         <v>600</v>
@@ -8010,26 +8031,26 @@
         <v>103400</v>
       </c>
       <c r="C147" s="74" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D147" s="74">
         <v>3</v>
       </c>
       <c r="E147" s="75" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F147" s="75" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G147" s="75" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H147" s="75" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I147" s="26"/>
       <c r="J147" s="76" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K147" s="29">
         <v>250</v>
@@ -8049,26 +8070,26 @@
         <v>103400</v>
       </c>
       <c r="C148" s="74" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D148" s="74">
         <v>4</v>
       </c>
       <c r="E148" s="75" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F148" s="75" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G148" s="75" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H148" s="75" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I148" s="26"/>
       <c r="J148" s="76" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K148" s="29">
         <v>-250</v>
@@ -8088,26 +8109,26 @@
         <v>103400</v>
       </c>
       <c r="C149" s="74" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D149" s="74">
         <v>5</v>
       </c>
       <c r="E149" s="75" t="s">
+        <v>209</v>
+      </c>
+      <c r="F149" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="F149" s="75" t="s">
-        <v>197</v>
-      </c>
       <c r="G149" s="75" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H149" s="75" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I149" s="26"/>
       <c r="J149" s="76" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K149" s="29">
         <v>-600</v>
@@ -8127,26 +8148,26 @@
         <v>103400</v>
       </c>
       <c r="C150" s="74" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D150" s="74">
         <v>6</v>
       </c>
       <c r="E150" s="75" t="s">
+        <v>210</v>
+      </c>
+      <c r="F150" s="75" t="s">
+        <v>203</v>
+      </c>
+      <c r="G150" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="F150" s="75" t="s">
-        <v>197</v>
-      </c>
-      <c r="G150" s="75" t="s">
-        <v>198</v>
-      </c>
       <c r="H150" s="75" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I150" s="26"/>
       <c r="J150" s="76" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K150" s="29">
         <v>-1000</v>
@@ -8166,7 +8187,7 @@
         <v>103400</v>
       </c>
       <c r="C151" s="74" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D151" s="74">
         <v>7</v>
@@ -8175,17 +8196,17 @@
         <v>57</v>
       </c>
       <c r="F151" s="75" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G151" s="75" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="H151" s="75" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="I151" s="26"/>
       <c r="J151" s="76" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K151" s="29">
         <v>-999999</v>
@@ -8205,26 +8226,26 @@
         <v>103401</v>
       </c>
       <c r="C152" s="77" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D152" s="77">
         <v>1</v>
       </c>
       <c r="E152" s="78" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F152" s="78" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G152" s="75" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H152" s="75" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I152" s="26"/>
       <c r="J152" s="79" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K152" s="29">
         <v>1000</v>
@@ -8244,26 +8265,26 @@
         <v>103401</v>
       </c>
       <c r="C153" s="77" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D153" s="77">
         <v>2</v>
       </c>
       <c r="E153" s="78" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F153" s="78" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G153" s="75" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H153" s="75" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I153" s="26"/>
       <c r="J153" s="79" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K153" s="29">
         <v>600</v>
@@ -8283,26 +8304,26 @@
         <v>103401</v>
       </c>
       <c r="C154" s="77" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D154" s="77">
         <v>3</v>
       </c>
       <c r="E154" s="78" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F154" s="78" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G154" s="75" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H154" s="75" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I154" s="26"/>
       <c r="J154" s="79" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K154" s="29">
         <v>250</v>
@@ -8322,26 +8343,26 @@
         <v>103401</v>
       </c>
       <c r="C155" s="77" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D155" s="77">
         <v>4</v>
       </c>
       <c r="E155" s="78" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F155" s="78" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G155" s="75" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H155" s="75" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I155" s="26"/>
       <c r="J155" s="79" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K155" s="29">
         <v>-250</v>
@@ -8361,26 +8382,26 @@
         <v>103401</v>
       </c>
       <c r="C156" s="77" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D156" s="77">
         <v>5</v>
       </c>
       <c r="E156" s="78" t="s">
+        <v>219</v>
+      </c>
+      <c r="F156" s="78" t="s">
+        <v>203</v>
+      </c>
+      <c r="G156" s="75" t="s">
         <v>213</v>
       </c>
-      <c r="F156" s="78" t="s">
-        <v>197</v>
-      </c>
-      <c r="G156" s="75" t="s">
-        <v>207</v>
-      </c>
       <c r="H156" s="75" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I156" s="26"/>
       <c r="J156" s="79" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K156" s="29">
         <v>-600</v>
@@ -8400,26 +8421,26 @@
         <v>103401</v>
       </c>
       <c r="C157" s="77" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D157" s="77">
         <v>6</v>
       </c>
       <c r="E157" s="78" t="s">
+        <v>220</v>
+      </c>
+      <c r="F157" s="78" t="s">
+        <v>203</v>
+      </c>
+      <c r="G157" s="75" t="s">
+        <v>213</v>
+      </c>
+      <c r="H157" s="75" t="s">
         <v>214</v>
-      </c>
-      <c r="F157" s="78" t="s">
-        <v>197</v>
-      </c>
-      <c r="G157" s="75" t="s">
-        <v>207</v>
-      </c>
-      <c r="H157" s="75" t="s">
-        <v>208</v>
       </c>
       <c r="I157" s="26"/>
       <c r="J157" s="79" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K157" s="29">
         <v>-1000</v>
@@ -8439,7 +8460,7 @@
         <v>103401</v>
       </c>
       <c r="C158" s="77" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D158" s="77">
         <v>7</v>
@@ -8448,17 +8469,17 @@
         <v>57</v>
       </c>
       <c r="F158" s="78" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G158" s="75" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H158" s="75" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I158" s="26"/>
       <c r="J158" s="79" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="K158" s="29">
         <v>-999999</v>
@@ -8478,7 +8499,7 @@
         <v>103500</v>
       </c>
       <c r="C159" s="81" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D159" s="81">
         <v>1</v>
@@ -8487,17 +8508,17 @@
         <v>176</v>
       </c>
       <c r="F159" s="82" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G159" s="82" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H159" s="82" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I159" s="26"/>
       <c r="J159" s="28" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K159" s="29">
         <v>1000</v>
@@ -8517,7 +8538,7 @@
         <v>103500</v>
       </c>
       <c r="C160" s="81" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D160" s="81">
         <v>2</v>
@@ -8526,17 +8547,17 @@
         <v>180</v>
       </c>
       <c r="F160" s="82" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G160" s="82" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H160" s="82" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I160" s="26"/>
       <c r="J160" s="83" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K160" s="29">
         <v>600</v>
@@ -8556,7 +8577,7 @@
         <v>103500</v>
       </c>
       <c r="C161" s="81" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D161" s="81">
         <v>3</v>
@@ -8565,17 +8586,17 @@
         <v>127</v>
       </c>
       <c r="F161" s="82" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G161" s="82" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H161" s="82" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I161" s="26"/>
       <c r="J161" s="83" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K161" s="29">
         <v>250</v>
@@ -8595,26 +8616,26 @@
         <v>103500</v>
       </c>
       <c r="C162" s="81" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D162" s="81">
         <v>4</v>
       </c>
       <c r="E162" s="82" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F162" s="82" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G162" s="82" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H162" s="82" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I162" s="26"/>
       <c r="J162" s="83" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K162" s="29">
         <v>-250</v>
@@ -8634,26 +8655,26 @@
         <v>103500</v>
       </c>
       <c r="C163" s="81" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D163" s="81">
         <v>5</v>
       </c>
       <c r="E163" s="82" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F163" s="82" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G163" s="82" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H163" s="82" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I163" s="26"/>
       <c r="J163" s="83" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K163" s="29">
         <v>-600</v>
@@ -8673,26 +8694,26 @@
         <v>103500</v>
       </c>
       <c r="C164" s="81" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D164" s="81">
         <v>6</v>
       </c>
       <c r="E164" s="82" t="s">
+        <v>228</v>
+      </c>
+      <c r="F164" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="F164" s="82" t="s">
-        <v>216</v>
-      </c>
       <c r="G164" s="82" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H164" s="82" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I164" s="26"/>
       <c r="J164" s="83" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K164" s="29">
         <v>-1000</v>
@@ -8712,7 +8733,7 @@
         <v>103500</v>
       </c>
       <c r="C165" s="81" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D165" s="81">
         <v>7</v>
@@ -8721,17 +8742,17 @@
         <v>57</v>
       </c>
       <c r="F165" s="82" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G165" s="82" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H165" s="82" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I165" s="26"/>
       <c r="J165" s="83" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K165" s="29">
         <v>-999999</v>
@@ -8751,7 +8772,7 @@
         <v>103501</v>
       </c>
       <c r="C166" s="84" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D166" s="84">
         <v>1</v>
@@ -8760,17 +8781,17 @@
         <v>176</v>
       </c>
       <c r="F166" s="86" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G166" s="85" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H166" s="85" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I166" s="26"/>
       <c r="J166" s="28" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K166" s="29">
         <v>1000</v>
@@ -8790,7 +8811,7 @@
         <v>103501</v>
       </c>
       <c r="C167" s="84" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D167" s="84">
         <v>2</v>
@@ -8799,17 +8820,17 @@
         <v>180</v>
       </c>
       <c r="F167" s="86" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G167" s="85" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H167" s="85" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I167" s="26"/>
       <c r="J167" s="34" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K167" s="29">
         <v>600</v>
@@ -8829,7 +8850,7 @@
         <v>103501</v>
       </c>
       <c r="C168" s="84" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D168" s="84">
         <v>3</v>
@@ -8838,17 +8859,17 @@
         <v>127</v>
       </c>
       <c r="F168" s="86" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G168" s="85" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H168" s="85" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I168" s="26"/>
       <c r="J168" s="34" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K168" s="29">
         <v>250</v>
@@ -8868,26 +8889,26 @@
         <v>103501</v>
       </c>
       <c r="C169" s="84" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D169" s="84">
         <v>4</v>
       </c>
       <c r="E169" s="85" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F169" s="86" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G169" s="85" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H169" s="85" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I169" s="26"/>
       <c r="J169" s="34" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K169" s="29">
         <v>-250</v>
@@ -8907,26 +8928,26 @@
         <v>103501</v>
       </c>
       <c r="C170" s="84" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D170" s="84">
         <v>5</v>
       </c>
       <c r="E170" s="85" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F170" s="86" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G170" s="85" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H170" s="85" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I170" s="26"/>
       <c r="J170" s="34" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K170" s="29">
         <v>-600</v>
@@ -8946,26 +8967,26 @@
         <v>103501</v>
       </c>
       <c r="C171" s="84" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D171" s="84">
         <v>6</v>
       </c>
       <c r="E171" s="85" t="s">
+        <v>228</v>
+      </c>
+      <c r="F171" s="86" t="s">
         <v>222</v>
       </c>
-      <c r="F171" s="86" t="s">
-        <v>216</v>
-      </c>
       <c r="G171" s="85" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H171" s="85" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I171" s="26"/>
       <c r="J171" s="34" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K171" s="29">
         <v>-1000</v>
@@ -8985,7 +9006,7 @@
         <v>103501</v>
       </c>
       <c r="C172" s="84" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D172" s="84">
         <v>7</v>
@@ -8994,17 +9015,17 @@
         <v>57</v>
       </c>
       <c r="F172" s="86" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G172" s="85" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H172" s="85" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="I172" s="26"/>
       <c r="J172" s="34" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="K172" s="29">
         <v>-999999</v>
@@ -9024,26 +9045,26 @@
         <v>103600</v>
       </c>
       <c r="C173" s="87" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D173" s="87">
         <v>1</v>
       </c>
       <c r="E173" s="88" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F173" s="88" t="s">
         <v>48</v>
       </c>
       <c r="G173" s="88" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H173" s="88" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I173" s="26"/>
       <c r="J173" s="89" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="K173" s="29">
         <v>1000</v>
@@ -9063,7 +9084,7 @@
         <v>103600</v>
       </c>
       <c r="C174" s="87" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D174" s="87">
         <v>2</v>
@@ -9075,14 +9096,14 @@
         <v>48</v>
       </c>
       <c r="G174" s="88" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H174" s="88" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I174" s="26"/>
       <c r="J174" s="89" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="K174" s="29">
         <v>600</v>
@@ -9102,26 +9123,26 @@
         <v>103600</v>
       </c>
       <c r="C175" s="87" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D175" s="87">
         <v>3</v>
       </c>
       <c r="E175" s="88" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F175" s="88" t="s">
         <v>48</v>
       </c>
       <c r="G175" s="88" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H175" s="88" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I175" s="26"/>
       <c r="J175" s="89" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="K175" s="29">
         <v>250</v>
@@ -9141,26 +9162,26 @@
         <v>103600</v>
       </c>
       <c r="C176" s="87" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D176" s="87">
         <v>4</v>
       </c>
       <c r="E176" s="88" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F176" s="88" t="s">
         <v>48</v>
       </c>
       <c r="G176" s="88" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H176" s="88" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I176" s="26"/>
       <c r="J176" s="89" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="K176" s="29">
         <v>-250</v>
@@ -9180,7 +9201,7 @@
         <v>103600</v>
       </c>
       <c r="C177" s="87" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D177" s="87">
         <v>5</v>
@@ -9192,14 +9213,14 @@
         <v>48</v>
       </c>
       <c r="G177" s="88" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H177" s="88" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I177" s="26"/>
       <c r="J177" s="89" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="K177" s="29">
         <v>-600</v>
@@ -9219,7 +9240,7 @@
         <v>103600</v>
       </c>
       <c r="C178" s="87" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D178" s="87">
         <v>6</v>
@@ -9231,14 +9252,14 @@
         <v>48</v>
       </c>
       <c r="G178" s="88" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H178" s="88" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I178" s="26"/>
       <c r="J178" s="89" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="K178" s="29">
         <v>-1000</v>
@@ -9258,7 +9279,7 @@
         <v>103600</v>
       </c>
       <c r="C179" s="87" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D179" s="87">
         <v>7</v>
@@ -9270,14 +9291,14 @@
         <v>48</v>
       </c>
       <c r="G179" s="88" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H179" s="88" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="I179" s="26"/>
       <c r="J179" s="89" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="K179" s="29">
         <v>-999999</v>
@@ -9297,26 +9318,26 @@
         <v>103800</v>
       </c>
       <c r="C180" s="91" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D180" s="91">
         <v>1</v>
       </c>
       <c r="E180" s="92" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F180" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G180" s="92" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H180" s="92" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I180" s="26"/>
       <c r="J180" s="93" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K180" s="29">
         <v>1000</v>
@@ -9336,26 +9357,26 @@
         <v>103800</v>
       </c>
       <c r="C181" s="91" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D181" s="91">
         <v>2</v>
       </c>
       <c r="E181" s="92" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="F181" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G181" s="92" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H181" s="92" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I181" s="26"/>
       <c r="J181" s="93" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K181" s="29">
         <v>600</v>
@@ -9375,26 +9396,26 @@
         <v>103800</v>
       </c>
       <c r="C182" s="91" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D182" s="91">
         <v>3</v>
       </c>
       <c r="E182" s="92" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F182" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G182" s="92" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H182" s="92" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I182" s="26"/>
       <c r="J182" s="93" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K182" s="29">
         <v>250</v>
@@ -9414,26 +9435,26 @@
         <v>103800</v>
       </c>
       <c r="C183" s="91" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D183" s="91">
         <v>4</v>
       </c>
       <c r="E183" s="92" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F183" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G183" s="92" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H183" s="92" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I183" s="26"/>
       <c r="J183" s="93" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K183" s="29">
         <v>-250</v>
@@ -9453,26 +9474,26 @@
         <v>103800</v>
       </c>
       <c r="C184" s="91" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D184" s="91">
         <v>5</v>
       </c>
       <c r="E184" s="92" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F184" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G184" s="92" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H184" s="92" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I184" s="26"/>
       <c r="J184" s="93" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K184" s="29">
         <v>-600</v>
@@ -9492,26 +9513,26 @@
         <v>103800</v>
       </c>
       <c r="C185" s="91" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D185" s="91">
         <v>6</v>
       </c>
       <c r="E185" s="92" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F185" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G185" s="92" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H185" s="92" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I185" s="26"/>
       <c r="J185" s="93" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K185" s="29">
         <v>-1000</v>
@@ -9531,7 +9552,7 @@
         <v>103800</v>
       </c>
       <c r="C186" s="91" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D186" s="91">
         <v>7</v>
@@ -9543,14 +9564,14 @@
         <v>48</v>
       </c>
       <c r="G186" s="92" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H186" s="92" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I186" s="26"/>
       <c r="J186" s="93" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="K186" s="29">
         <v>-999999</v>
@@ -9570,20 +9591,20 @@
         <v>103700</v>
       </c>
       <c r="C187" s="87" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D187" s="87">
         <v>1</v>
       </c>
       <c r="E187" s="88" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F187" s="88"/>
       <c r="G187" s="88"/>
       <c r="H187" s="88"/>
       <c r="I187" s="26"/>
       <c r="J187" s="89" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="K187" s="29">
         <v>1000</v>
@@ -9603,13 +9624,13 @@
         <v>103700</v>
       </c>
       <c r="C188" s="87" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D188" s="87">
         <v>2</v>
       </c>
       <c r="E188" s="88" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="F188" s="88"/>
       <c r="G188" s="88"/>
@@ -9617,7 +9638,7 @@
       <c r="I188" s="26"/>
       <c r="J188" s="89" t="str">
         <f t="shared" ref="J188:J193" si="4">J187</f>
-        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K188" s="29">
         <v>600</v>
@@ -9637,13 +9658,13 @@
         <v>103700</v>
       </c>
       <c r="C189" s="87" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D189" s="87">
         <v>3</v>
       </c>
       <c r="E189" s="88" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F189" s="88"/>
       <c r="G189" s="88"/>
@@ -9651,7 +9672,7 @@
       <c r="I189" s="26"/>
       <c r="J189" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K189" s="29">
         <v>250</v>
@@ -9671,13 +9692,13 @@
         <v>103700</v>
       </c>
       <c r="C190" s="87" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D190" s="87">
         <v>4</v>
       </c>
       <c r="E190" s="88" t="s">
-        <v>245</v>
+        <v>99</v>
       </c>
       <c r="F190" s="88"/>
       <c r="G190" s="88"/>
@@ -9685,7 +9706,7 @@
       <c r="I190" s="26"/>
       <c r="J190" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K190" s="29">
         <v>-250</v>
@@ -9705,13 +9726,13 @@
         <v>103700</v>
       </c>
       <c r="C191" s="87" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D191" s="87">
         <v>5</v>
       </c>
       <c r="E191" s="88" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F191" s="88"/>
       <c r="G191" s="88"/>
@@ -9719,7 +9740,7 @@
       <c r="I191" s="26"/>
       <c r="J191" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K191" s="29">
         <v>-600</v>
@@ -9739,13 +9760,13 @@
         <v>103700</v>
       </c>
       <c r="C192" s="87" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D192" s="87">
         <v>6</v>
       </c>
       <c r="E192" s="88" t="s">
-        <v>76</v>
+        <v>252</v>
       </c>
       <c r="F192" s="88"/>
       <c r="G192" s="88"/>
@@ -9753,7 +9774,7 @@
       <c r="I192" s="26"/>
       <c r="J192" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K192" s="29">
         <v>-1000</v>
@@ -9773,13 +9794,13 @@
         <v>103700</v>
       </c>
       <c r="C193" s="87" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D193" s="87">
         <v>7</v>
       </c>
       <c r="E193" s="88" t="s">
-        <v>247</v>
+        <v>57</v>
       </c>
       <c r="F193" s="88"/>
       <c r="G193" s="88"/>
@@ -9787,7 +9808,7 @@
       <c r="I193" s="26"/>
       <c r="J193" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-13000|1&amp;5-17100|5&amp;10-2800|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-200|35&amp;40-200|40&amp;45-300|45&amp;50-300|50&amp;60-600|60&amp;70-300|70&amp;80-200|80&amp;90-100|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;2,0&amp;1-25000|1&amp;5-0|5&amp;10-0|10&amp;15-0|15&amp;20-0|20&amp;25-0|25&amp;30-0|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-300|60&amp;70-1000|70&amp;80-1700|80&amp;90-0|90&amp;100-2100|100&amp;120-2000|120&amp;140-500|140&amp;160-200|160&amp;180-0|180&amp;200-200|200&amp;240-0|240&amp;280-100|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0;3,0&amp;1-0|1&amp;5-0|5&amp;10-2600|10&amp;15-400|15&amp;20-100|20&amp;25-0|25&amp;30-400|30&amp;35-0|35&amp;40-0|40&amp;45-0|45&amp;50-0|50&amp;60-200|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1850-0|1850&amp;2100-0|2100&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K193" s="29">
         <v>-999999</v>
@@ -9807,20 +9828,20 @@
         <v>103900</v>
       </c>
       <c r="C194" s="95" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D194" s="95">
         <v>1</v>
       </c>
       <c r="E194" s="36" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F194" s="36"/>
       <c r="G194" s="36"/>
       <c r="H194" s="36"/>
       <c r="I194" s="26"/>
       <c r="J194" s="38" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K194" s="29">
         <v>1000</v>
@@ -9840,13 +9861,13 @@
         <v>103900</v>
       </c>
       <c r="C195" s="95" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D195" s="95">
         <v>2</v>
       </c>
       <c r="E195" s="36" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="F195" s="36"/>
       <c r="G195" s="36"/>
@@ -9874,13 +9895,13 @@
         <v>103900</v>
       </c>
       <c r="C196" s="95" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D196" s="95">
         <v>3</v>
       </c>
       <c r="E196" s="36" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F196" s="36"/>
       <c r="G196" s="36"/>
@@ -9908,13 +9929,13 @@
         <v>103900</v>
       </c>
       <c r="C197" s="95" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D197" s="95">
         <v>4</v>
       </c>
       <c r="E197" s="36" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F197" s="36"/>
       <c r="G197" s="36"/>
@@ -9942,13 +9963,13 @@
         <v>103900</v>
       </c>
       <c r="C198" s="95" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D198" s="95">
         <v>5</v>
       </c>
       <c r="E198" s="36" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F198" s="36"/>
       <c r="G198" s="36"/>
@@ -9976,13 +9997,13 @@
         <v>103900</v>
       </c>
       <c r="C199" s="95" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D199" s="95">
         <v>6</v>
       </c>
       <c r="E199" s="36" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="F199" s="36"/>
       <c r="G199" s="36"/>
@@ -10010,13 +10031,13 @@
         <v>103900</v>
       </c>
       <c r="C200" s="95" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D200" s="95">
         <v>7</v>
       </c>
       <c r="E200" s="36" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F200" s="36"/>
       <c r="G200" s="36"/>
@@ -10044,28 +10065,28 @@
         <v>104000</v>
       </c>
       <c r="C201" s="77" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D201" s="77">
         <v>1</v>
       </c>
       <c r="E201" s="78" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F201" s="78" t="s">
         <v>48</v>
       </c>
       <c r="G201" s="78" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="H201" s="78" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I201" s="26" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J201" s="79" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K201" s="29">
         <v>1000</v>
@@ -10085,28 +10106,28 @@
         <v>104000</v>
       </c>
       <c r="C202" s="77" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D202" s="77">
         <v>2</v>
       </c>
       <c r="E202" s="78" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F202" s="78" t="s">
         <v>48</v>
       </c>
       <c r="G202" s="78" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="H202" s="78" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I202" s="26" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J202" s="79" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K202" s="29">
         <v>600</v>
@@ -10126,7 +10147,7 @@
         <v>104000</v>
       </c>
       <c r="C203" s="77" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D203" s="77">
         <v>3</v>
@@ -10138,16 +10159,16 @@
         <v>48</v>
       </c>
       <c r="G203" s="78" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="H203" s="78" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I203" s="26" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J203" s="79" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K203" s="29">
         <v>250</v>
@@ -10167,7 +10188,7 @@
         <v>104000</v>
       </c>
       <c r="C204" s="77" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D204" s="77">
         <v>4</v>
@@ -10179,16 +10200,16 @@
         <v>48</v>
       </c>
       <c r="G204" s="78" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="H204" s="78" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I204" s="26" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J204" s="79" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K204" s="29">
         <v>-250</v>
@@ -10208,7 +10229,7 @@
         <v>104000</v>
       </c>
       <c r="C205" s="77" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D205" s="77">
         <v>5</v>
@@ -10220,16 +10241,16 @@
         <v>48</v>
       </c>
       <c r="G205" s="78" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="H205" s="78" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I205" s="26" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J205" s="79" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K205" s="29">
         <v>-600</v>
@@ -10249,7 +10270,7 @@
         <v>104000</v>
       </c>
       <c r="C206" s="77" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D206" s="77">
         <v>6</v>
@@ -10261,16 +10282,16 @@
         <v>48</v>
       </c>
       <c r="G206" s="78" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="H206" s="78" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I206" s="26" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J206" s="79" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K206" s="29">
         <v>-1000</v>
@@ -10290,7 +10311,7 @@
         <v>104000</v>
       </c>
       <c r="C207" s="77" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="D207" s="77">
         <v>7</v>
@@ -10302,16 +10323,16 @@
         <v>48</v>
       </c>
       <c r="G207" s="78" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="H207" s="78" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="I207" s="26" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="J207" s="79" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="K207" s="29">
         <v>-999999</v>
@@ -10331,7 +10352,7 @@
         <v>104100</v>
       </c>
       <c r="C208" s="96" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D208" s="96">
         <v>1</v>
@@ -10364,7 +10385,7 @@
         <v>104100</v>
       </c>
       <c r="C209" s="96" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D209" s="96">
         <v>2</v>
@@ -10397,7 +10418,7 @@
         <v>104100</v>
       </c>
       <c r="C210" s="96" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D210" s="96">
         <v>3</v>
@@ -10430,7 +10451,7 @@
         <v>104100</v>
       </c>
       <c r="C211" s="96" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D211" s="96">
         <v>4</v>
@@ -10463,7 +10484,7 @@
         <v>104100</v>
       </c>
       <c r="C212" s="96" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D212" s="96">
         <v>5</v>
@@ -10496,7 +10517,7 @@
         <v>104100</v>
       </c>
       <c r="C213" s="96" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D213" s="96">
         <v>6</v>
@@ -10529,7 +10550,7 @@
         <v>104100</v>
       </c>
       <c r="C214" s="96" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D214" s="96">
         <v>7</v>
@@ -10562,7 +10583,7 @@
         <v>104200</v>
       </c>
       <c r="C215" s="100" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D215" s="100">
         <v>1</v>
@@ -10595,7 +10616,7 @@
         <v>104200</v>
       </c>
       <c r="C216" s="100" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D216" s="100">
         <v>2</v>
@@ -10628,7 +10649,7 @@
         <v>104200</v>
       </c>
       <c r="C217" s="100" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D217" s="100">
         <v>3</v>
@@ -10661,7 +10682,7 @@
         <v>104200</v>
       </c>
       <c r="C218" s="100" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D218" s="100">
         <v>4</v>
@@ -10694,7 +10715,7 @@
         <v>104200</v>
       </c>
       <c r="C219" s="100" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D219" s="100">
         <v>5</v>
@@ -10727,7 +10748,7 @@
         <v>104200</v>
       </c>
       <c r="C220" s="100" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D220" s="100">
         <v>6</v>
@@ -10760,7 +10781,7 @@
         <v>104200</v>
       </c>
       <c r="C221" s="100" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D221" s="100">
         <v>7</v>
@@ -10793,7 +10814,7 @@
         <v>104800</v>
       </c>
       <c r="C222" s="95" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D222" s="95">
         <v>1</v>
@@ -10826,7 +10847,7 @@
         <v>104800</v>
       </c>
       <c r="C223" s="95" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D223" s="95">
         <v>2</v>
@@ -10859,7 +10880,7 @@
         <v>104800</v>
       </c>
       <c r="C224" s="95" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D224" s="95">
         <v>3</v>
@@ -10892,7 +10913,7 @@
         <v>104800</v>
       </c>
       <c r="C225" s="95" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D225" s="95">
         <v>4</v>
@@ -10925,7 +10946,7 @@
         <v>104800</v>
       </c>
       <c r="C226" s="95" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D226" s="95">
         <v>5</v>
@@ -10958,7 +10979,7 @@
         <v>104800</v>
       </c>
       <c r="C227" s="95" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D227" s="95">
         <v>6</v>
@@ -10991,7 +11012,7 @@
         <v>104800</v>
       </c>
       <c r="C228" s="95" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D228" s="95">
         <v>7</v>
@@ -11024,7 +11045,7 @@
         <v>105000</v>
       </c>
       <c r="C229" s="87" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D229" s="87">
         <v>1</v>
@@ -11057,7 +11078,7 @@
         <v>105000</v>
       </c>
       <c r="C230" s="87" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D230" s="87">
         <v>2</v>
@@ -11090,7 +11111,7 @@
         <v>105000</v>
       </c>
       <c r="C231" s="87" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D231" s="87">
         <v>3</v>
@@ -11123,7 +11144,7 @@
         <v>105000</v>
       </c>
       <c r="C232" s="87" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D232" s="87">
         <v>4</v>
@@ -11156,7 +11177,7 @@
         <v>105000</v>
       </c>
       <c r="C233" s="87" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D233" s="87">
         <v>5</v>
@@ -11189,7 +11210,7 @@
         <v>105000</v>
       </c>
       <c r="C234" s="87" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D234" s="87">
         <v>6</v>
@@ -11222,7 +11243,7 @@
         <v>105000</v>
       </c>
       <c r="C235" s="87" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D235" s="87">
         <v>7</v>
@@ -11255,20 +11276,20 @@
         <v>105100</v>
       </c>
       <c r="C236" s="104" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D236" s="104">
         <v>1</v>
       </c>
       <c r="E236" s="105" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F236" s="105"/>
       <c r="G236" s="105"/>
       <c r="H236" s="105"/>
       <c r="I236" s="26"/>
       <c r="J236" s="106" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K236" s="29">
         <v>1000</v>
@@ -11288,20 +11309,20 @@
         <v>105100</v>
       </c>
       <c r="C237" s="104" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D237" s="104">
         <v>2</v>
       </c>
       <c r="E237" s="105" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F237" s="105"/>
       <c r="G237" s="105"/>
       <c r="H237" s="105"/>
       <c r="I237" s="26"/>
       <c r="J237" s="106" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K237" s="29">
         <v>600</v>
@@ -11321,20 +11342,20 @@
         <v>105100</v>
       </c>
       <c r="C238" s="104" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D238" s="104">
         <v>3</v>
       </c>
       <c r="E238" s="105" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F238" s="105"/>
       <c r="G238" s="105"/>
       <c r="H238" s="105"/>
       <c r="I238" s="26"/>
       <c r="J238" s="106" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K238" s="29">
         <v>250</v>
@@ -11354,20 +11375,20 @@
         <v>105100</v>
       </c>
       <c r="C239" s="104" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D239" s="104">
         <v>4</v>
       </c>
       <c r="E239" s="105" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F239" s="105"/>
       <c r="G239" s="105"/>
       <c r="H239" s="105"/>
       <c r="I239" s="26"/>
       <c r="J239" s="106" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K239" s="29">
         <v>-250</v>
@@ -11387,20 +11408,20 @@
         <v>105100</v>
       </c>
       <c r="C240" s="104" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D240" s="104">
         <v>5</v>
       </c>
       <c r="E240" s="105" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F240" s="105"/>
       <c r="G240" s="105"/>
       <c r="H240" s="105"/>
       <c r="I240" s="26"/>
       <c r="J240" s="106" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K240" s="29">
         <v>-600</v>
@@ -11420,20 +11441,20 @@
         <v>105100</v>
       </c>
       <c r="C241" s="104" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D241" s="104">
         <v>6</v>
       </c>
       <c r="E241" s="105" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F241" s="105"/>
       <c r="G241" s="105"/>
       <c r="H241" s="105"/>
       <c r="I241" s="26"/>
       <c r="J241" s="106" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K241" s="29">
         <v>-1000</v>
@@ -11453,20 +11474,20 @@
         <v>105100</v>
       </c>
       <c r="C242" s="104" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D242" s="104">
         <v>7</v>
       </c>
       <c r="E242" s="105" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="F242" s="105"/>
       <c r="G242" s="105"/>
       <c r="H242" s="105"/>
       <c r="I242" s="26"/>
       <c r="J242" s="106" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K242" s="29">
         <v>-999999</v>
@@ -11486,20 +11507,20 @@
         <v>105300</v>
       </c>
       <c r="C243" s="53" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D243" s="31">
         <v>1</v>
       </c>
       <c r="E243" s="32" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F243" s="32"/>
       <c r="G243" s="32"/>
       <c r="H243" s="32"/>
       <c r="I243" s="54"/>
       <c r="J243" s="108" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K243" s="29">
         <v>1000</v>
@@ -11519,20 +11540,20 @@
         <v>105300</v>
       </c>
       <c r="C244" s="53" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D244" s="31">
         <v>2</v>
       </c>
       <c r="E244" s="32" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F244" s="32"/>
       <c r="G244" s="32"/>
       <c r="H244" s="32"/>
       <c r="I244" s="54"/>
       <c r="J244" s="32" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K244" s="29">
         <v>600</v>
@@ -11552,20 +11573,20 @@
         <v>105300</v>
       </c>
       <c r="C245" s="53" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D245" s="31">
         <v>3</v>
       </c>
       <c r="E245" s="32" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F245" s="32"/>
       <c r="G245" s="32"/>
       <c r="H245" s="32"/>
       <c r="I245" s="54"/>
       <c r="J245" s="32" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K245" s="29">
         <v>250</v>
@@ -11585,20 +11606,20 @@
         <v>105300</v>
       </c>
       <c r="C246" s="53" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D246" s="31">
         <v>4</v>
       </c>
       <c r="E246" s="32" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F246" s="32"/>
       <c r="G246" s="32"/>
       <c r="H246" s="32"/>
       <c r="I246" s="54"/>
       <c r="J246" s="32" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K246" s="29">
         <v>-250</v>
@@ -11618,20 +11639,20 @@
         <v>105300</v>
       </c>
       <c r="C247" s="53" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D247" s="31">
         <v>5</v>
       </c>
       <c r="E247" s="32" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F247" s="32"/>
       <c r="G247" s="32"/>
       <c r="H247" s="32"/>
       <c r="I247" s="54"/>
       <c r="J247" s="32" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K247" s="29">
         <v>-600</v>
@@ -11651,20 +11672,20 @@
         <v>105300</v>
       </c>
       <c r="C248" s="53" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D248" s="31">
         <v>6</v>
       </c>
       <c r="E248" s="32" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F248" s="32"/>
       <c r="G248" s="32"/>
       <c r="H248" s="32"/>
       <c r="I248" s="54"/>
       <c r="J248" s="32" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K248" s="29">
         <v>-1000</v>
@@ -11684,20 +11705,20 @@
         <v>105300</v>
       </c>
       <c r="C249" s="53" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D249" s="31">
         <v>7</v>
       </c>
       <c r="E249" s="32" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F249" s="32"/>
       <c r="G249" s="32"/>
       <c r="H249" s="32"/>
       <c r="I249" s="54"/>
       <c r="J249" s="32" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K249" s="29">
         <v>-999999</v>
@@ -11717,7 +11738,7 @@
         <v>105400</v>
       </c>
       <c r="C250" s="95" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D250" s="95">
         <v>1</v>
@@ -11749,7 +11770,7 @@
         <v>105400</v>
       </c>
       <c r="C251" s="95" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D251" s="95">
         <v>2</v>
@@ -11781,7 +11802,7 @@
         <v>105400</v>
       </c>
       <c r="C252" s="95" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D252" s="95">
         <v>3</v>
@@ -11813,7 +11834,7 @@
         <v>105400</v>
       </c>
       <c r="C253" s="95" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D253" s="95">
         <v>4</v>
@@ -11845,7 +11866,7 @@
         <v>105400</v>
       </c>
       <c r="C254" s="95" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D254" s="95">
         <v>5</v>
@@ -11877,7 +11898,7 @@
         <v>105400</v>
       </c>
       <c r="C255" s="95" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D255" s="95">
         <v>6</v>
@@ -11909,7 +11930,7 @@
         <v>105400</v>
       </c>
       <c r="C256" s="95" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D256" s="95">
         <v>7</v>
@@ -11941,7 +11962,7 @@
         <v>105700</v>
       </c>
       <c r="C257" s="110" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D257" s="111">
         <v>1</v>
@@ -11974,7 +11995,7 @@
         <v>105700</v>
       </c>
       <c r="C258" s="110" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D258" s="111">
         <v>2</v>
@@ -12007,7 +12028,7 @@
         <v>105700</v>
       </c>
       <c r="C259" s="110" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D259" s="111">
         <v>3</v>
@@ -12040,7 +12061,7 @@
         <v>105700</v>
       </c>
       <c r="C260" s="110" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D260" s="111">
         <v>4</v>
@@ -12073,7 +12094,7 @@
         <v>105700</v>
       </c>
       <c r="C261" s="110" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D261" s="111">
         <v>5</v>
@@ -12106,7 +12127,7 @@
         <v>105700</v>
       </c>
       <c r="C262" s="110" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D262" s="111">
         <v>6</v>
@@ -12139,7 +12160,7 @@
         <v>105700</v>
       </c>
       <c r="C263" s="110" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D263" s="111">
         <v>7</v>
@@ -12172,20 +12193,20 @@
         <v>105800</v>
       </c>
       <c r="C264" s="115" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D264" s="115">
         <v>1</v>
       </c>
       <c r="E264" s="26" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F264" s="26"/>
       <c r="G264" s="26"/>
       <c r="H264" s="26"/>
       <c r="I264" s="113"/>
       <c r="J264" s="28" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K264" s="29">
         <v>1000</v>
@@ -12202,20 +12223,20 @@
         <v>105800</v>
       </c>
       <c r="C265" s="115" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D265" s="115">
         <v>2</v>
       </c>
       <c r="E265" s="26" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F265" s="26"/>
       <c r="G265" s="26"/>
       <c r="H265" s="26"/>
       <c r="I265" s="113"/>
       <c r="J265" s="26" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K265" s="29">
         <v>600</v>
@@ -12232,20 +12253,20 @@
         <v>105800</v>
       </c>
       <c r="C266" s="115" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D266" s="115">
         <v>3</v>
       </c>
       <c r="E266" s="26" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="F266" s="26"/>
       <c r="G266" s="26"/>
       <c r="H266" s="26"/>
       <c r="I266" s="113"/>
       <c r="J266" s="26" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K266" s="29">
         <v>250</v>
@@ -12262,20 +12283,20 @@
         <v>105800</v>
       </c>
       <c r="C267" s="115" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D267" s="115">
         <v>4</v>
       </c>
       <c r="E267" s="26" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F267" s="26"/>
       <c r="G267" s="26"/>
       <c r="H267" s="26"/>
       <c r="I267" s="113"/>
       <c r="J267" s="26" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K267" s="29">
         <v>-250</v>
@@ -12292,20 +12313,20 @@
         <v>105800</v>
       </c>
       <c r="C268" s="115" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D268" s="115">
         <v>5</v>
       </c>
       <c r="E268" s="26" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F268" s="26"/>
       <c r="G268" s="26"/>
       <c r="H268" s="26"/>
       <c r="I268" s="113"/>
       <c r="J268" s="26" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K268" s="29">
         <v>-600</v>
@@ -12322,20 +12343,20 @@
         <v>105800</v>
       </c>
       <c r="C269" s="115" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D269" s="115">
         <v>6</v>
       </c>
       <c r="E269" s="26" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F269" s="26"/>
       <c r="G269" s="26"/>
       <c r="H269" s="26"/>
       <c r="I269" s="113"/>
       <c r="J269" s="26" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K269" s="29">
         <v>-1000</v>
@@ -12352,20 +12373,20 @@
         <v>105800</v>
       </c>
       <c r="C270" s="115" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D270" s="115">
         <v>7</v>
       </c>
       <c r="E270" s="26" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F270" s="26"/>
       <c r="G270" s="26"/>
       <c r="H270" s="26"/>
       <c r="I270" s="113"/>
       <c r="J270" s="26" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K270" s="29">
         <v>-999999</v>
@@ -12382,20 +12403,20 @@
         <v>105500</v>
       </c>
       <c r="C271" s="117" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D271" s="74">
         <v>1</v>
       </c>
       <c r="E271" s="75" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="F271" s="75"/>
       <c r="G271" s="75"/>
       <c r="H271" s="75"/>
       <c r="I271" s="113"/>
       <c r="J271" s="89" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="K271" s="29">
         <v>1000</v>
@@ -12415,13 +12436,13 @@
         <v>105500</v>
       </c>
       <c r="C272" s="117" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D272" s="74">
         <v>2</v>
       </c>
       <c r="E272" s="75" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F272" s="75"/>
       <c r="G272" s="75"/>
@@ -12449,13 +12470,13 @@
         <v>105500</v>
       </c>
       <c r="C273" s="117" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D273" s="74">
         <v>3</v>
       </c>
       <c r="E273" s="75" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F273" s="75"/>
       <c r="G273" s="75"/>
@@ -12483,13 +12504,13 @@
         <v>105500</v>
       </c>
       <c r="C274" s="117" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D274" s="74">
         <v>4</v>
       </c>
       <c r="E274" s="75" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F274" s="75"/>
       <c r="G274" s="75"/>
@@ -12517,13 +12538,13 @@
         <v>105500</v>
       </c>
       <c r="C275" s="117" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D275" s="74">
         <v>5</v>
       </c>
       <c r="E275" s="75" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="F275" s="75"/>
       <c r="G275" s="75"/>
@@ -12551,13 +12572,13 @@
         <v>105500</v>
       </c>
       <c r="C276" s="117" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D276" s="74">
         <v>6</v>
       </c>
       <c r="E276" s="75" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F276" s="75"/>
       <c r="G276" s="75"/>
@@ -12585,13 +12606,13 @@
         <v>105500</v>
       </c>
       <c r="C277" s="117" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D277" s="74">
         <v>7</v>
       </c>
       <c r="E277" s="75" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="F277" s="75"/>
       <c r="G277" s="75"/>
@@ -12619,7 +12640,7 @@
         <v>105501</v>
       </c>
       <c r="C278" s="117" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D278" s="74">
         <v>1</v>
@@ -12632,7 +12653,7 @@
       <c r="H278" s="112"/>
       <c r="I278" s="113"/>
       <c r="J278" s="89" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="K278" s="29">
         <v>1000</v>
@@ -12652,7 +12673,7 @@
         <v>105501</v>
       </c>
       <c r="C279" s="117" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D279" s="74">
         <v>2</v>
@@ -12665,7 +12686,7 @@
       <c r="H279" s="112"/>
       <c r="I279" s="113"/>
       <c r="J279" s="89" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K279" s="29">
         <v>600</v>
@@ -12685,7 +12706,7 @@
         <v>105501</v>
       </c>
       <c r="C280" s="117" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D280" s="74">
         <v>3</v>
@@ -12698,7 +12719,7 @@
       <c r="H280" s="112"/>
       <c r="I280" s="113"/>
       <c r="J280" s="89" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K280" s="29">
         <v>250</v>
@@ -12718,7 +12739,7 @@
         <v>105501</v>
       </c>
       <c r="C281" s="117" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D281" s="74">
         <v>4</v>
@@ -12731,7 +12752,7 @@
       <c r="H281" s="112"/>
       <c r="I281" s="113"/>
       <c r="J281" s="89" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K281" s="29">
         <v>-250</v>
@@ -12751,7 +12772,7 @@
         <v>105501</v>
       </c>
       <c r="C282" s="117" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D282" s="74">
         <v>5</v>
@@ -12764,7 +12785,7 @@
       <c r="H282" s="112"/>
       <c r="I282" s="113"/>
       <c r="J282" s="89" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K282" s="29">
         <v>-600</v>
@@ -12784,7 +12805,7 @@
         <v>105501</v>
       </c>
       <c r="C283" s="117" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D283" s="74">
         <v>6</v>
@@ -12797,7 +12818,7 @@
       <c r="H283" s="112"/>
       <c r="I283" s="113"/>
       <c r="J283" s="89" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K283" s="29">
         <v>-1000</v>
@@ -12817,7 +12838,7 @@
         <v>105501</v>
       </c>
       <c r="C284" s="117" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D284" s="74">
         <v>7</v>
@@ -12830,7 +12851,7 @@
       <c r="H284" s="112"/>
       <c r="I284" s="113"/>
       <c r="J284" s="89" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K284" s="29">
         <v>-999999</v>
@@ -12850,7 +12871,7 @@
         <v>105502</v>
       </c>
       <c r="C285" s="120" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D285" s="120">
         <v>1</v>
@@ -12863,7 +12884,7 @@
       <c r="H285" s="85"/>
       <c r="I285" s="85"/>
       <c r="J285" s="121" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="K285" s="29">
         <v>1000</v>
@@ -12883,7 +12904,7 @@
         <v>105502</v>
       </c>
       <c r="C286" s="120" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D286" s="120">
         <v>2</v>
@@ -12896,7 +12917,7 @@
       <c r="H286" s="85"/>
       <c r="I286" s="85"/>
       <c r="J286" s="121" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K286" s="29">
         <v>600</v>
@@ -12916,7 +12937,7 @@
         <v>105502</v>
       </c>
       <c r="C287" s="120" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D287" s="120">
         <v>3</v>
@@ -12929,7 +12950,7 @@
       <c r="H287" s="85"/>
       <c r="I287" s="85"/>
       <c r="J287" s="121" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K287" s="29">
         <v>250</v>
@@ -12949,7 +12970,7 @@
         <v>105502</v>
       </c>
       <c r="C288" s="120" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D288" s="120">
         <v>4</v>
@@ -12962,7 +12983,7 @@
       <c r="H288" s="85"/>
       <c r="I288" s="85"/>
       <c r="J288" s="121" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K288" s="29">
         <v>-250</v>
@@ -12982,7 +13003,7 @@
         <v>105502</v>
       </c>
       <c r="C289" s="120" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D289" s="120">
         <v>5</v>
@@ -12995,7 +13016,7 @@
       <c r="H289" s="85"/>
       <c r="I289" s="85"/>
       <c r="J289" s="121" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K289" s="29">
         <v>-600</v>
@@ -13015,7 +13036,7 @@
         <v>105502</v>
       </c>
       <c r="C290" s="120" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D290" s="120">
         <v>6</v>
@@ -13028,7 +13049,7 @@
       <c r="H290" s="85"/>
       <c r="I290" s="85"/>
       <c r="J290" s="121" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K290" s="29">
         <v>-1000</v>
@@ -13048,7 +13069,7 @@
         <v>105502</v>
       </c>
       <c r="C291" s="120" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D291" s="120">
         <v>7</v>
@@ -13061,7 +13082,7 @@
       <c r="H291" s="85"/>
       <c r="I291" s="85"/>
       <c r="J291" s="121" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="K291" s="29">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java\project\slots\resources\sample\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D974A9-0F52-4006-92B6-1302B0E4E39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -22,18 +28,21 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -57,7 +66,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -82,7 +91,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -107,7 +116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -132,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -158,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -170,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -183,7 +192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -196,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -216,7 +225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -803,9 +812,6 @@
     <t>1_8830|2_1120|3_50</t>
   </si>
   <si>
-    <t>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
-  </si>
-  <si>
     <t>1_9010|2_940|3_50</t>
   </si>
   <si>
@@ -992,9 +998,6 @@
     <t>1_8650|2_1300|3_50</t>
   </si>
   <si>
-    <t>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
-  </si>
-  <si>
     <t>1_8870|2_1080|3_50</t>
   </si>
   <si>
@@ -1143,19 +1146,21 @@
   </si>
   <si>
     <t>伽罗宝石3</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1176,147 +1181,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1330,8 +1198,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1340,25 +1221,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799951170384838"/>
+        <fgColor theme="5" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799951170384838"/>
+        <fgColor theme="7" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799951170384838"/>
+        <fgColor theme="8" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799951170384838"/>
+        <fgColor theme="9" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1376,13 +1257,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399945066682943"/>
+        <fgColor theme="9" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1394,7 +1275,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1406,13 +1287,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1442,162 +1323,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.4"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399945066682943"/>
+        <fgColor theme="7" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399945066682943"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1605,254 +1378,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1882,7 +1413,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2167,63 +1698,25 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 73" xfId="49"/>
+    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2481,14 +1974,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M291"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="3" width="15.25" customWidth="1"/>
@@ -2501,7 +1994,7 @@
     <col min="13" max="13" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:13">
+    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -2540,7 +2033,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:13">
+    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
         <v>12</v>
       </c>
@@ -2577,7 +2070,7 @@
       </c>
       <c r="M2" s="24"/>
     </row>
-    <row r="3" ht="16.5" spans="1:13">
+    <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="24" t="s">
         <v>0</v>
       </c>
@@ -2614,7 +2107,7 @@
       </c>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" ht="16.5" spans="1:13">
+    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
@@ -2629,7 +2122,7 @@
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
     </row>
-    <row r="5" ht="16.5" spans="1:13">
+    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="24">
         <v>1001</v>
       </c>
@@ -2668,7 +2161,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:13">
+    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="24">
         <v>1002</v>
       </c>
@@ -2707,7 +2200,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:13">
+    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A7" s="24">
         <v>1003</v>
       </c>
@@ -2746,7 +2239,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:13">
+    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A8" s="24">
         <v>1004</v>
       </c>
@@ -2785,7 +2278,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:13">
+    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A9" s="24">
         <v>1005</v>
       </c>
@@ -2824,7 +2317,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:13">
+    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A10" s="24">
         <v>1006</v>
       </c>
@@ -2863,7 +2356,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:13">
+    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A11" s="24">
         <v>1007</v>
       </c>
@@ -2902,7 +2395,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="12" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="30">
         <v>3001</v>
       </c>
@@ -2941,7 +2434,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="13" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="30">
         <v>3002</v>
       </c>
@@ -2980,7 +2473,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="14" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="30">
         <v>3003</v>
       </c>
@@ -3019,7 +2512,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="15" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="30">
         <v>3004</v>
       </c>
@@ -3058,7 +2551,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="16" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="30">
         <v>3005</v>
       </c>
@@ -3097,7 +2590,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="17" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="30">
         <v>3006</v>
       </c>
@@ -3136,7 +2629,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="18" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="30">
         <v>3007</v>
       </c>
@@ -3175,7 +2668,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="19" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="24">
         <v>7001</v>
       </c>
@@ -3216,7 +2709,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="20" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="24">
         <v>7002</v>
       </c>
@@ -3257,7 +2750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="21" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="24">
         <v>7003</v>
       </c>
@@ -3298,7 +2791,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="22" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="24">
         <v>7004</v>
       </c>
@@ -3339,7 +2832,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="23" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="24">
         <v>7005</v>
       </c>
@@ -3380,7 +2873,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="24" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="24">
         <v>7006</v>
       </c>
@@ -3421,7 +2914,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="25" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="24">
         <v>7007</v>
       </c>
@@ -3462,7 +2955,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="26" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>8001</v>
       </c>
@@ -3495,7 +2988,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="27" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>8002</v>
       </c>
@@ -3528,7 +3021,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="28" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>8003</v>
       </c>
@@ -3561,7 +3054,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="29" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>8004</v>
       </c>
@@ -3594,7 +3087,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="30" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>8005</v>
       </c>
@@ -3627,7 +3120,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="31" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>8006</v>
       </c>
@@ -3660,7 +3153,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="32" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>8007</v>
       </c>
@@ -3693,7 +3186,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="33" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A33" s="30">
         <v>12001</v>
       </c>
@@ -3734,7 +3227,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="34" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A34" s="30">
         <v>12002</v>
       </c>
@@ -3775,7 +3268,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="35" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A35" s="30">
         <v>12003</v>
       </c>
@@ -3816,7 +3309,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="36" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A36" s="30">
         <v>12004</v>
       </c>
@@ -3857,7 +3350,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="37" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A37" s="30">
         <v>12005</v>
       </c>
@@ -3898,7 +3391,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="38" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A38" s="30">
         <v>12006</v>
       </c>
@@ -3939,7 +3432,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:13">
+    <row r="39" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A39" s="30">
         <v>12007</v>
       </c>
@@ -3980,7 +3473,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" s="4" customFormat="1" ht="16.5" spans="1:13">
+    <row r="40" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A40" s="24">
         <v>14001</v>
       </c>
@@ -4019,7 +3512,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:13">
+    <row r="41" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A41" s="24">
         <v>14002</v>
       </c>
@@ -4058,7 +3551,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:13">
+    <row r="42" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A42" s="24">
         <v>14003</v>
       </c>
@@ -4097,7 +3590,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:13">
+    <row r="43" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A43" s="24">
         <v>14004</v>
       </c>
@@ -4136,7 +3629,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" s="4" customFormat="1" ht="16.5" spans="1:13">
+    <row r="44" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A44" s="24">
         <v>14005</v>
       </c>
@@ -4175,7 +3668,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" s="4" customFormat="1" ht="16.5" spans="1:13">
+    <row r="45" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A45" s="24">
         <v>14006</v>
       </c>
@@ -4214,7 +3707,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" s="4" customFormat="1" ht="16.5" spans="1:13">
+    <row r="46" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A46" s="24">
         <v>14007</v>
       </c>
@@ -4253,7 +3746,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="47" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" s="42">
         <v>15001</v>
       </c>
@@ -4286,7 +3779,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="48" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" s="42">
         <v>15002</v>
       </c>
@@ -4319,7 +3812,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="49" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" s="42">
         <v>15003</v>
       </c>
@@ -4352,7 +3845,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="50" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" s="42">
         <v>15004</v>
       </c>
@@ -4385,7 +3878,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="51" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" s="42">
         <v>15005</v>
       </c>
@@ -4418,7 +3911,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="52" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" s="42">
         <v>15006</v>
       </c>
@@ -4451,7 +3944,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="53" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="53" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" s="42">
         <v>15007</v>
       </c>
@@ -4484,7 +3977,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="54" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" s="46">
         <v>16001</v>
       </c>
@@ -4517,7 +4010,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="55" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" s="46">
         <v>16002</v>
       </c>
@@ -4550,7 +4043,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="56" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" s="46">
         <v>16003</v>
       </c>
@@ -4583,7 +4076,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="57" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" s="46">
         <v>16004</v>
       </c>
@@ -4616,7 +4109,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="58" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" s="46">
         <v>16005</v>
       </c>
@@ -4649,7 +4142,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="59" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" s="46">
         <v>16006</v>
       </c>
@@ -4682,7 +4175,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="60" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" s="46">
         <v>16007</v>
       </c>
@@ -4715,7 +4208,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="61" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A61" s="24">
         <v>17001</v>
       </c>
@@ -4756,7 +4249,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="62" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A62" s="24">
         <v>17002</v>
       </c>
@@ -4797,7 +4290,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="63" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A63" s="24">
         <v>17003</v>
       </c>
@@ -4838,7 +4331,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="64" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A64" s="24">
         <v>17004</v>
       </c>
@@ -4879,7 +4372,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="65" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A65" s="24">
         <v>17005</v>
       </c>
@@ -4920,7 +4413,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="66" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A66" s="24">
         <v>17006</v>
       </c>
@@ -4961,7 +4454,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" ht="16.5" spans="1:13">
+    <row r="67" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A67" s="24">
         <v>17007</v>
       </c>
@@ -5002,7 +4495,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="68" s="7" customFormat="1" ht="16.5" spans="1:13">
+    <row r="68" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A68" s="50">
         <v>18001</v>
       </c>
@@ -5043,7 +4536,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:13">
+    <row r="69" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A69" s="50">
         <v>18002</v>
       </c>
@@ -5084,7 +4577,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" s="7" customFormat="1" ht="16.5" spans="1:13">
+    <row r="70" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A70" s="50">
         <v>18003</v>
       </c>
@@ -5125,7 +4618,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" s="7" customFormat="1" ht="16.5" spans="1:13">
+    <row r="71" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A71" s="50">
         <v>18004</v>
       </c>
@@ -5166,7 +4659,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="72" s="7" customFormat="1" ht="16.5" spans="1:13">
+    <row r="72" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A72" s="50">
         <v>18005</v>
       </c>
@@ -5207,7 +4700,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="73" s="7" customFormat="1" ht="16.5" spans="1:13">
+    <row r="73" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A73" s="50">
         <v>18006</v>
       </c>
@@ -5248,7 +4741,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" s="7" customFormat="1" ht="16.5" spans="1:13">
+    <row r="74" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A74" s="50">
         <v>18007</v>
       </c>
@@ -5289,7 +4782,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="75" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="75" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A75" s="42">
         <v>20001</v>
       </c>
@@ -5330,7 +4823,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="76" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A76" s="42">
         <v>20002</v>
       </c>
@@ -5371,7 +4864,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="77" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A77" s="42">
         <v>20003</v>
       </c>
@@ -5412,7 +4905,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="78" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="78" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A78" s="42">
         <v>20004</v>
       </c>
@@ -5453,7 +4946,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="79" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="79" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A79" s="42">
         <v>20005</v>
       </c>
@@ -5494,7 +4987,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="80" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="80" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A80" s="42">
         <v>20006</v>
       </c>
@@ -5535,7 +5028,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" s="5" customFormat="1" ht="16.5" spans="1:13">
+    <row r="81" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A81" s="42">
         <v>20007</v>
       </c>
@@ -5576,7 +5069,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="82" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A82" s="53">
         <v>21001</v>
       </c>
@@ -5617,7 +5110,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="83" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="83" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A83" s="53">
         <v>21002</v>
       </c>
@@ -5658,7 +5151,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="84" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A84" s="53">
         <v>21003</v>
       </c>
@@ -5699,7 +5192,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="85" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="85" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A85" s="53">
         <v>21004</v>
       </c>
@@ -5740,7 +5233,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="86" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="86" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A86" s="53">
         <v>21005</v>
       </c>
@@ -5781,7 +5274,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="87" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="87" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A87" s="53">
         <v>21006</v>
       </c>
@@ -5822,7 +5315,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="88" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A88" s="53">
         <v>21007</v>
       </c>
@@ -5863,7 +5356,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="89" s="9" customFormat="1" ht="16.5" spans="1:13">
+    <row r="89" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A89" s="56">
         <v>22001</v>
       </c>
@@ -5904,7 +5397,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90" s="9" customFormat="1" ht="16.5" spans="1:13">
+    <row r="90" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A90" s="56">
         <v>22002</v>
       </c>
@@ -5945,7 +5438,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" s="9" customFormat="1" ht="16.5" spans="1:13">
+    <row r="91" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A91" s="56">
         <v>22003</v>
       </c>
@@ -5986,7 +5479,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="92" s="9" customFormat="1" ht="16.5" spans="1:13">
+    <row r="92" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A92" s="56">
         <v>22004</v>
       </c>
@@ -6027,7 +5520,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="93" s="9" customFormat="1" ht="16.5" spans="1:13">
+    <row r="93" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A93" s="56">
         <v>22005</v>
       </c>
@@ -6068,7 +5561,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="94" s="9" customFormat="1" ht="16.5" spans="1:13">
+    <row r="94" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A94" s="56">
         <v>22006</v>
       </c>
@@ -6109,7 +5602,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" s="9" customFormat="1" ht="16.5" spans="1:13">
+    <row r="95" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A95" s="56">
         <v>22007</v>
       </c>
@@ -6150,7 +5643,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="96" s="10" customFormat="1" ht="16.5" spans="1:13">
+    <row r="96" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A96" s="60">
         <v>23001</v>
       </c>
@@ -6191,7 +5684,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="97" s="10" customFormat="1" ht="16.5" spans="1:13">
+    <row r="97" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A97" s="60">
         <v>23002</v>
       </c>
@@ -6232,7 +5725,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" s="10" customFormat="1" ht="16.5" spans="1:13">
+    <row r="98" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A98" s="60">
         <v>23003</v>
       </c>
@@ -6273,7 +5766,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="99" s="10" customFormat="1" ht="16.5" spans="1:13">
+    <row r="99" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A99" s="60">
         <v>23004</v>
       </c>
@@ -6314,7 +5807,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="100" s="10" customFormat="1" ht="16.5" spans="1:13">
+    <row r="100" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A100" s="60">
         <v>23005</v>
       </c>
@@ -6355,7 +5848,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="101" s="10" customFormat="1" ht="16.5" spans="1:13">
+    <row r="101" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A101" s="60">
         <v>23006</v>
       </c>
@@ -6396,7 +5889,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="102" s="10" customFormat="1" ht="16.5" spans="1:13">
+    <row r="102" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A102" s="60">
         <v>23007</v>
       </c>
@@ -6437,7 +5930,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" ht="16.5" spans="1:13">
+    <row r="103" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A103" s="24">
         <v>24001</v>
       </c>
@@ -6476,7 +5969,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="104" ht="16.5" spans="1:13">
+    <row r="104" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A104" s="24">
         <v>24002</v>
       </c>
@@ -6515,7 +6008,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" ht="16.5" spans="1:13">
+    <row r="105" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A105" s="24">
         <v>24003</v>
       </c>
@@ -6554,7 +6047,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="106" ht="16.5" spans="1:13">
+    <row r="106" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A106" s="24">
         <v>24004</v>
       </c>
@@ -6593,7 +6086,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="107" ht="16.5" spans="1:13">
+    <row r="107" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A107" s="24">
         <v>24005</v>
       </c>
@@ -6632,7 +6125,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="108" ht="16.5" spans="1:13">
+    <row r="108" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A108" s="24">
         <v>24006</v>
       </c>
@@ -6671,7 +6164,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" ht="16.5" spans="1:13">
+    <row r="109" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A109" s="24">
         <v>24007</v>
       </c>
@@ -6710,7 +6203,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="110" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A110" s="63">
         <v>25001</v>
       </c>
@@ -6751,7 +6244,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="111" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="111" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A111" s="63">
         <v>25002</v>
       </c>
@@ -6792,7 +6285,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="112" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A112" s="63">
         <v>25003</v>
       </c>
@@ -6833,7 +6326,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="113" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="113" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A113" s="63">
         <v>25004</v>
       </c>
@@ -6874,7 +6367,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="114" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A114" s="63">
         <v>25005</v>
       </c>
@@ -6915,7 +6408,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="115" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="115" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A115" s="63">
         <v>25006</v>
       </c>
@@ -6956,7 +6449,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="116" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="116" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A116" s="63">
         <v>25007</v>
       </c>
@@ -6997,7 +6490,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="117" s="12" customFormat="1" ht="16.5" spans="1:13">
+    <row r="117" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A117" s="67">
         <v>26001</v>
       </c>
@@ -7030,7 +6523,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" s="12" customFormat="1" ht="16.5" spans="1:13">
+    <row r="118" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A118" s="67">
         <v>26002</v>
       </c>
@@ -7064,7 +6557,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" s="12" customFormat="1" ht="16.5" spans="1:13">
+    <row r="119" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A119" s="67">
         <v>26003</v>
       </c>
@@ -7098,7 +6591,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="120" s="12" customFormat="1" ht="16.5" spans="1:13">
+    <row r="120" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A120" s="67">
         <v>26004</v>
       </c>
@@ -7132,7 +6625,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="121" s="12" customFormat="1" ht="16.5" spans="1:13">
+    <row r="121" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A121" s="67">
         <v>26005</v>
       </c>
@@ -7166,7 +6659,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="122" s="12" customFormat="1" ht="16.5" spans="1:13">
+    <row r="122" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A122" s="67">
         <v>26006</v>
       </c>
@@ -7200,7 +6693,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="123" s="12" customFormat="1" ht="16.5" spans="1:13">
+    <row r="123" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A123" s="67">
         <v>26007</v>
       </c>
@@ -7234,7 +6727,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="124" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="124" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A124" s="63">
         <v>27001</v>
       </c>
@@ -7254,8 +6747,8 @@
       <c r="G124" s="64"/>
       <c r="H124" s="64"/>
       <c r="I124" s="26"/>
-      <c r="J124" s="66" t="s">
-        <v>185</v>
+      <c r="J124" s="122" t="s">
+        <v>297</v>
       </c>
       <c r="K124" s="29">
         <v>1000</v>
@@ -7267,7 +6760,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="125" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="125" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A125" s="63">
         <v>27002</v>
       </c>
@@ -7281,7 +6774,7 @@
         <v>2</v>
       </c>
       <c r="E125" s="64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F125" s="64"/>
       <c r="G125" s="64"/>
@@ -7289,7 +6782,7 @@
       <c r="I125" s="26"/>
       <c r="J125" s="66" t="str">
         <f t="shared" ref="J125:J130" si="1">J124</f>
-        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K125" s="29">
         <v>600</v>
@@ -7301,7 +6794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="126" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="126" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A126" s="63">
         <v>27003</v>
       </c>
@@ -7315,7 +6808,7 @@
         <v>3</v>
       </c>
       <c r="E126" s="64" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F126" s="64"/>
       <c r="G126" s="64"/>
@@ -7323,7 +6816,7 @@
       <c r="I126" s="26"/>
       <c r="J126" s="66" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K126" s="29">
         <v>250</v>
@@ -7335,7 +6828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="127" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="127" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A127" s="63">
         <v>27004</v>
       </c>
@@ -7349,7 +6842,7 @@
         <v>4</v>
       </c>
       <c r="E127" s="64" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F127" s="64"/>
       <c r="G127" s="64"/>
@@ -7357,7 +6850,7 @@
       <c r="I127" s="26"/>
       <c r="J127" s="66" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K127" s="29">
         <v>-250</v>
@@ -7369,7 +6862,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="128" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="128" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A128" s="63">
         <v>27005</v>
       </c>
@@ -7383,7 +6876,7 @@
         <v>5</v>
       </c>
       <c r="E128" s="64" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F128" s="64"/>
       <c r="G128" s="64"/>
@@ -7391,7 +6884,7 @@
       <c r="I128" s="26"/>
       <c r="J128" s="66" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K128" s="29">
         <v>-600</v>
@@ -7403,7 +6896,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="129" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="129" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A129" s="63">
         <v>27006</v>
       </c>
@@ -7417,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="E129" s="64" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F129" s="64"/>
       <c r="G129" s="64"/>
@@ -7425,7 +6918,7 @@
       <c r="I129" s="26"/>
       <c r="J129" s="66" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K129" s="29">
         <v>-1000</v>
@@ -7437,7 +6930,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="130" s="11" customFormat="1" ht="16.5" spans="1:13">
+    <row r="130" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A130" s="63">
         <v>27007</v>
       </c>
@@ -7459,7 +6952,7 @@
       <c r="I130" s="26"/>
       <c r="J130" s="66" t="str">
         <f t="shared" si="1"/>
-        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K130" s="29">
         <v>-999999</v>
@@ -7471,7 +6964,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="131" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="131" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A131" s="46">
         <v>28001</v>
       </c>
@@ -7479,7 +6972,7 @@
         <v>102800</v>
       </c>
       <c r="C131" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D131" s="46">
         <v>1</v>
@@ -7504,7 +6997,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="132" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="132" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A132" s="46">
         <v>28002</v>
       </c>
@@ -7512,7 +7005,7 @@
         <v>102800</v>
       </c>
       <c r="C132" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D132" s="46">
         <v>2</v>
@@ -7538,7 +7031,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="133" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A133" s="46">
         <v>28003</v>
       </c>
@@ -7546,7 +7039,7 @@
         <v>102800</v>
       </c>
       <c r="C133" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D133" s="46">
         <v>3</v>
@@ -7572,7 +7065,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="134" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="134" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A134" s="46">
         <v>28004</v>
       </c>
@@ -7580,7 +7073,7 @@
         <v>102800</v>
       </c>
       <c r="C134" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D134" s="46">
         <v>4</v>
@@ -7606,7 +7099,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="135" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="135" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A135" s="46">
         <v>28005</v>
       </c>
@@ -7614,7 +7107,7 @@
         <v>102800</v>
       </c>
       <c r="C135" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D135" s="46">
         <v>5</v>
@@ -7640,7 +7133,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="136" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="136" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A136" s="46">
         <v>28006</v>
       </c>
@@ -7648,7 +7141,7 @@
         <v>102800</v>
       </c>
       <c r="C136" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D136" s="46">
         <v>6</v>
@@ -7674,7 +7167,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="137" s="6" customFormat="1" ht="16.5" spans="1:13">
+    <row r="137" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A137" s="46">
         <v>28007</v>
       </c>
@@ -7682,7 +7175,7 @@
         <v>102800</v>
       </c>
       <c r="C137" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D137" s="46">
         <v>7</v>
@@ -7708,7 +7201,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="138" s="13" customFormat="1" ht="16.5" spans="1:13">
+    <row r="138" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A138" s="70">
         <v>31001</v>
       </c>
@@ -7716,20 +7209,20 @@
         <v>103100</v>
       </c>
       <c r="C138" s="70" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D138" s="70">
         <v>1</v>
       </c>
       <c r="E138" s="71" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F138" s="71"/>
       <c r="G138" s="71"/>
       <c r="H138" s="71"/>
       <c r="I138" s="26"/>
       <c r="J138" s="72" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K138" s="29">
         <v>1000</v>
@@ -7741,7 +7234,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="139" s="13" customFormat="1" ht="16.5" spans="1:13">
+    <row r="139" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A139" s="70">
         <v>31002</v>
       </c>
@@ -7749,13 +7242,13 @@
         <v>103100</v>
       </c>
       <c r="C139" s="70" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D139" s="70">
         <v>2</v>
       </c>
       <c r="E139" s="71" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F139" s="71"/>
       <c r="G139" s="71"/>
@@ -7775,7 +7268,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" s="13" customFormat="1" ht="16.5" spans="1:13">
+    <row r="140" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A140" s="70">
         <v>31003</v>
       </c>
@@ -7783,13 +7276,13 @@
         <v>103100</v>
       </c>
       <c r="C140" s="70" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D140" s="70">
         <v>3</v>
       </c>
       <c r="E140" s="71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F140" s="71"/>
       <c r="G140" s="71"/>
@@ -7809,7 +7302,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="141" s="13" customFormat="1" ht="16.5" spans="1:13">
+    <row r="141" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A141" s="70">
         <v>31004</v>
       </c>
@@ -7817,13 +7310,13 @@
         <v>103100</v>
       </c>
       <c r="C141" s="70" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D141" s="70">
         <v>4</v>
       </c>
       <c r="E141" s="71" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F141" s="71"/>
       <c r="G141" s="71"/>
@@ -7843,7 +7336,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="142" s="13" customFormat="1" ht="16.5" spans="1:13">
+    <row r="142" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A142" s="70">
         <v>31005</v>
       </c>
@@ -7851,13 +7344,13 @@
         <v>103100</v>
       </c>
       <c r="C142" s="70" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D142" s="70">
         <v>5</v>
       </c>
       <c r="E142" s="71" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F142" s="71"/>
       <c r="G142" s="71"/>
@@ -7877,7 +7370,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="143" s="13" customFormat="1" ht="16.5" spans="1:13">
+    <row r="143" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A143" s="70">
         <v>31006</v>
       </c>
@@ -7885,13 +7378,13 @@
         <v>103100</v>
       </c>
       <c r="C143" s="70" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D143" s="70">
         <v>6</v>
       </c>
       <c r="E143" s="71" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F143" s="71"/>
       <c r="G143" s="71"/>
@@ -7911,7 +7404,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="144" s="13" customFormat="1" ht="16.5" spans="1:13">
+    <row r="144" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A144" s="70">
         <v>31007</v>
       </c>
@@ -7919,13 +7412,13 @@
         <v>103100</v>
       </c>
       <c r="C144" s="70" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D144" s="70">
         <v>7</v>
       </c>
       <c r="E144" s="71" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F144" s="71"/>
       <c r="G144" s="71"/>
@@ -7945,7 +7438,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="145" s="14" customFormat="1" ht="16.5" spans="1:13">
+    <row r="145" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A145" s="74">
         <v>34001</v>
       </c>
@@ -7953,26 +7446,26 @@
         <v>103400</v>
       </c>
       <c r="C145" s="74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D145" s="74">
         <v>1</v>
       </c>
       <c r="E145" s="75" t="s">
+        <v>201</v>
+      </c>
+      <c r="F145" s="75" t="s">
         <v>202</v>
       </c>
-      <c r="F145" s="75" t="s">
+      <c r="G145" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="G145" s="75" t="s">
+      <c r="H145" s="75" t="s">
         <v>204</v>
-      </c>
-      <c r="H145" s="75" t="s">
-        <v>205</v>
       </c>
       <c r="I145" s="26"/>
       <c r="J145" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K145" s="29">
         <v>1000</v>
@@ -7984,7 +7477,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="146" s="14" customFormat="1" ht="16.5" spans="1:13">
+    <row r="146" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A146" s="74">
         <v>34002</v>
       </c>
@@ -7992,7 +7485,7 @@
         <v>103400</v>
       </c>
       <c r="C146" s="74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D146" s="74">
         <v>2</v>
@@ -8001,17 +7494,17 @@
         <v>93</v>
       </c>
       <c r="F146" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="G146" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="G146" s="75" t="s">
+      <c r="H146" s="75" t="s">
         <v>204</v>
-      </c>
-      <c r="H146" s="75" t="s">
-        <v>205</v>
       </c>
       <c r="I146" s="26"/>
       <c r="J146" s="76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K146" s="29">
         <v>600</v>
@@ -8023,7 +7516,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="147" s="14" customFormat="1" ht="16.5" spans="1:13">
+    <row r="147" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A147" s="74">
         <v>34003</v>
       </c>
@@ -8031,26 +7524,26 @@
         <v>103400</v>
       </c>
       <c r="C147" s="74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D147" s="74">
         <v>3</v>
       </c>
       <c r="E147" s="75" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F147" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="G147" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="G147" s="75" t="s">
+      <c r="H147" s="75" t="s">
         <v>204</v>
-      </c>
-      <c r="H147" s="75" t="s">
-        <v>205</v>
       </c>
       <c r="I147" s="26"/>
       <c r="J147" s="76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K147" s="29">
         <v>250</v>
@@ -8062,7 +7555,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" s="14" customFormat="1" ht="16.5" spans="1:13">
+    <row r="148" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A148" s="74">
         <v>34004</v>
       </c>
@@ -8070,26 +7563,26 @@
         <v>103400</v>
       </c>
       <c r="C148" s="74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D148" s="74">
         <v>4</v>
       </c>
       <c r="E148" s="75" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F148" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="G148" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="G148" s="75" t="s">
+      <c r="H148" s="75" t="s">
         <v>204</v>
-      </c>
-      <c r="H148" s="75" t="s">
-        <v>205</v>
       </c>
       <c r="I148" s="26"/>
       <c r="J148" s="76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K148" s="29">
         <v>-250</v>
@@ -8101,7 +7594,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="149" s="14" customFormat="1" ht="16.5" spans="1:13">
+    <row r="149" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A149" s="74">
         <v>34005</v>
       </c>
@@ -8109,26 +7602,26 @@
         <v>103400</v>
       </c>
       <c r="C149" s="74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D149" s="74">
         <v>5</v>
       </c>
       <c r="E149" s="75" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F149" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="G149" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="G149" s="75" t="s">
+      <c r="H149" s="75" t="s">
         <v>204</v>
-      </c>
-      <c r="H149" s="75" t="s">
-        <v>205</v>
       </c>
       <c r="I149" s="26"/>
       <c r="J149" s="76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K149" s="29">
         <v>-600</v>
@@ -8140,7 +7633,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="150" s="14" customFormat="1" ht="16.5" spans="1:13">
+    <row r="150" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A150" s="74">
         <v>34006</v>
       </c>
@@ -8148,26 +7641,26 @@
         <v>103400</v>
       </c>
       <c r="C150" s="74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D150" s="74">
         <v>6</v>
       </c>
       <c r="E150" s="75" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F150" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="G150" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="G150" s="75" t="s">
+      <c r="H150" s="75" t="s">
         <v>204</v>
-      </c>
-      <c r="H150" s="75" t="s">
-        <v>205</v>
       </c>
       <c r="I150" s="26"/>
       <c r="J150" s="76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K150" s="29">
         <v>-1000</v>
@@ -8179,7 +7672,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" s="14" customFormat="1" ht="16.5" spans="1:13">
+    <row r="151" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A151" s="74">
         <v>34007</v>
       </c>
@@ -8187,7 +7680,7 @@
         <v>103400</v>
       </c>
       <c r="C151" s="74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D151" s="74">
         <v>7</v>
@@ -8196,17 +7689,17 @@
         <v>57</v>
       </c>
       <c r="F151" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="G151" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="G151" s="75" t="s">
+      <c r="H151" s="75" t="s">
         <v>204</v>
-      </c>
-      <c r="H151" s="75" t="s">
-        <v>205</v>
       </c>
       <c r="I151" s="26"/>
       <c r="J151" s="76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K151" s="29">
         <v>-999999</v>
@@ -8218,7 +7711,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="152" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="152" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A152" s="77">
         <v>34011</v>
       </c>
@@ -8226,26 +7719,26 @@
         <v>103401</v>
       </c>
       <c r="C152" s="77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D152" s="77">
         <v>1</v>
       </c>
       <c r="E152" s="78" t="s">
+        <v>211</v>
+      </c>
+      <c r="F152" s="78" t="s">
+        <v>202</v>
+      </c>
+      <c r="G152" s="75" t="s">
         <v>212</v>
       </c>
-      <c r="F152" s="78" t="s">
-        <v>203</v>
-      </c>
-      <c r="G152" s="75" t="s">
+      <c r="H152" s="75" t="s">
         <v>213</v>
-      </c>
-      <c r="H152" s="75" t="s">
-        <v>214</v>
       </c>
       <c r="I152" s="26"/>
       <c r="J152" s="79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K152" s="29">
         <v>1000</v>
@@ -8257,7 +7750,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="153" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="153" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A153" s="77">
         <v>34012</v>
       </c>
@@ -8265,26 +7758,26 @@
         <v>103401</v>
       </c>
       <c r="C153" s="77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D153" s="77">
         <v>2</v>
       </c>
       <c r="E153" s="78" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F153" s="78" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G153" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="H153" s="75" t="s">
         <v>213</v>
-      </c>
-      <c r="H153" s="75" t="s">
-        <v>214</v>
       </c>
       <c r="I153" s="26"/>
       <c r="J153" s="79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K153" s="29">
         <v>600</v>
@@ -8296,7 +7789,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="154" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="154" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A154" s="77">
         <v>34013</v>
       </c>
@@ -8304,26 +7797,26 @@
         <v>103401</v>
       </c>
       <c r="C154" s="77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D154" s="77">
         <v>3</v>
       </c>
       <c r="E154" s="78" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F154" s="78" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G154" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="H154" s="75" t="s">
         <v>213</v>
-      </c>
-      <c r="H154" s="75" t="s">
-        <v>214</v>
       </c>
       <c r="I154" s="26"/>
       <c r="J154" s="79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K154" s="29">
         <v>250</v>
@@ -8335,7 +7828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="155" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="155" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A155" s="77">
         <v>34014</v>
       </c>
@@ -8343,26 +7836,26 @@
         <v>103401</v>
       </c>
       <c r="C155" s="77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D155" s="77">
         <v>4</v>
       </c>
       <c r="E155" s="78" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F155" s="78" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G155" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="H155" s="75" t="s">
         <v>213</v>
-      </c>
-      <c r="H155" s="75" t="s">
-        <v>214</v>
       </c>
       <c r="I155" s="26"/>
       <c r="J155" s="79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K155" s="29">
         <v>-250</v>
@@ -8374,7 +7867,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="156" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="156" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A156" s="77">
         <v>34015</v>
       </c>
@@ -8382,26 +7875,26 @@
         <v>103401</v>
       </c>
       <c r="C156" s="77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D156" s="77">
         <v>5</v>
       </c>
       <c r="E156" s="78" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F156" s="78" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G156" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="H156" s="75" t="s">
         <v>213</v>
-      </c>
-      <c r="H156" s="75" t="s">
-        <v>214</v>
       </c>
       <c r="I156" s="26"/>
       <c r="J156" s="79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K156" s="29">
         <v>-600</v>
@@ -8413,7 +7906,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="157" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="157" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A157" s="77">
         <v>34016</v>
       </c>
@@ -8421,26 +7914,26 @@
         <v>103401</v>
       </c>
       <c r="C157" s="77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D157" s="77">
         <v>6</v>
       </c>
       <c r="E157" s="78" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F157" s="78" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G157" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="H157" s="75" t="s">
         <v>213</v>
-      </c>
-      <c r="H157" s="75" t="s">
-        <v>214</v>
       </c>
       <c r="I157" s="26"/>
       <c r="J157" s="79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K157" s="29">
         <v>-1000</v>
@@ -8452,7 +7945,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="158" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="158" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A158" s="77">
         <v>34017</v>
       </c>
@@ -8460,7 +7953,7 @@
         <v>103401</v>
       </c>
       <c r="C158" s="77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D158" s="77">
         <v>7</v>
@@ -8469,17 +7962,17 @@
         <v>57</v>
       </c>
       <c r="F158" s="78" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G158" s="75" t="s">
+        <v>212</v>
+      </c>
+      <c r="H158" s="75" t="s">
         <v>213</v>
-      </c>
-      <c r="H158" s="75" t="s">
-        <v>214</v>
       </c>
       <c r="I158" s="26"/>
       <c r="J158" s="79" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K158" s="29">
         <v>-999999</v>
@@ -8491,7 +7984,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="159" s="16" customFormat="1" ht="16.5" spans="1:13">
+    <row r="159" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A159" s="81">
         <v>35001</v>
       </c>
@@ -8499,7 +7992,7 @@
         <v>103500</v>
       </c>
       <c r="C159" s="81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D159" s="81">
         <v>1</v>
@@ -8508,17 +8001,17 @@
         <v>176</v>
       </c>
       <c r="F159" s="82" t="s">
+        <v>221</v>
+      </c>
+      <c r="G159" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="G159" s="82" t="s">
+      <c r="H159" s="82" t="s">
         <v>223</v>
-      </c>
-      <c r="H159" s="82" t="s">
-        <v>224</v>
       </c>
       <c r="I159" s="26"/>
       <c r="J159" s="28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K159" s="29">
         <v>1000</v>
@@ -8530,7 +8023,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="160" s="16" customFormat="1" ht="16.5" spans="1:13">
+    <row r="160" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A160" s="81">
         <v>35002</v>
       </c>
@@ -8538,7 +8031,7 @@
         <v>103500</v>
       </c>
       <c r="C160" s="81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D160" s="81">
         <v>2</v>
@@ -8547,17 +8040,17 @@
         <v>180</v>
       </c>
       <c r="F160" s="82" t="s">
+        <v>221</v>
+      </c>
+      <c r="G160" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="G160" s="82" t="s">
+      <c r="H160" s="82" t="s">
         <v>223</v>
-      </c>
-      <c r="H160" s="82" t="s">
-        <v>224</v>
       </c>
       <c r="I160" s="26"/>
       <c r="J160" s="83" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K160" s="29">
         <v>600</v>
@@ -8569,7 +8062,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="161" s="16" customFormat="1" ht="16.5" spans="1:13">
+    <row r="161" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A161" s="81">
         <v>35003</v>
       </c>
@@ -8577,7 +8070,7 @@
         <v>103500</v>
       </c>
       <c r="C161" s="81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D161" s="81">
         <v>3</v>
@@ -8586,17 +8079,17 @@
         <v>127</v>
       </c>
       <c r="F161" s="82" t="s">
+        <v>221</v>
+      </c>
+      <c r="G161" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="G161" s="82" t="s">
+      <c r="H161" s="82" t="s">
         <v>223</v>
-      </c>
-      <c r="H161" s="82" t="s">
-        <v>224</v>
       </c>
       <c r="I161" s="26"/>
       <c r="J161" s="83" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K161" s="29">
         <v>250</v>
@@ -8608,7 +8101,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="162" s="16" customFormat="1" ht="16.5" spans="1:13">
+    <row r="162" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A162" s="81">
         <v>35004</v>
       </c>
@@ -8616,26 +8109,26 @@
         <v>103500</v>
       </c>
       <c r="C162" s="81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D162" s="81">
         <v>4</v>
       </c>
       <c r="E162" s="82" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F162" s="82" t="s">
+        <v>221</v>
+      </c>
+      <c r="G162" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="G162" s="82" t="s">
+      <c r="H162" s="82" t="s">
         <v>223</v>
-      </c>
-      <c r="H162" s="82" t="s">
-        <v>224</v>
       </c>
       <c r="I162" s="26"/>
       <c r="J162" s="83" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K162" s="29">
         <v>-250</v>
@@ -8647,7 +8140,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="163" s="16" customFormat="1" ht="16.5" spans="1:13">
+    <row r="163" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A163" s="81">
         <v>35005</v>
       </c>
@@ -8655,26 +8148,26 @@
         <v>103500</v>
       </c>
       <c r="C163" s="81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D163" s="81">
         <v>5</v>
       </c>
       <c r="E163" s="82" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F163" s="82" t="s">
+        <v>221</v>
+      </c>
+      <c r="G163" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="G163" s="82" t="s">
+      <c r="H163" s="82" t="s">
         <v>223</v>
-      </c>
-      <c r="H163" s="82" t="s">
-        <v>224</v>
       </c>
       <c r="I163" s="26"/>
       <c r="J163" s="83" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K163" s="29">
         <v>-600</v>
@@ -8686,7 +8179,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="164" s="16" customFormat="1" ht="16.5" spans="1:13">
+    <row r="164" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A164" s="81">
         <v>35006</v>
       </c>
@@ -8694,26 +8187,26 @@
         <v>103500</v>
       </c>
       <c r="C164" s="81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D164" s="81">
         <v>6</v>
       </c>
       <c r="E164" s="82" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F164" s="82" t="s">
+        <v>221</v>
+      </c>
+      <c r="G164" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="G164" s="82" t="s">
+      <c r="H164" s="82" t="s">
         <v>223</v>
-      </c>
-      <c r="H164" s="82" t="s">
-        <v>224</v>
       </c>
       <c r="I164" s="26"/>
       <c r="J164" s="83" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K164" s="29">
         <v>-1000</v>
@@ -8725,7 +8218,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="165" s="16" customFormat="1" ht="16.5" spans="1:13">
+    <row r="165" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A165" s="81">
         <v>35007</v>
       </c>
@@ -8733,7 +8226,7 @@
         <v>103500</v>
       </c>
       <c r="C165" s="81" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D165" s="81">
         <v>7</v>
@@ -8742,17 +8235,17 @@
         <v>57</v>
       </c>
       <c r="F165" s="82" t="s">
+        <v>221</v>
+      </c>
+      <c r="G165" s="82" t="s">
         <v>222</v>
       </c>
-      <c r="G165" s="82" t="s">
+      <c r="H165" s="82" t="s">
         <v>223</v>
-      </c>
-      <c r="H165" s="82" t="s">
-        <v>224</v>
       </c>
       <c r="I165" s="26"/>
       <c r="J165" s="83" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K165" s="29">
         <v>-999999</v>
@@ -8764,7 +8257,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="166" s="17" customFormat="1" ht="16.5" spans="1:13">
+    <row r="166" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A166" s="84">
         <v>35011</v>
       </c>
@@ -8772,7 +8265,7 @@
         <v>103501</v>
       </c>
       <c r="C166" s="84" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D166" s="84">
         <v>1</v>
@@ -8781,17 +8274,17 @@
         <v>176</v>
       </c>
       <c r="F166" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="G166" s="85" t="s">
         <v>222</v>
       </c>
-      <c r="G166" s="85" t="s">
+      <c r="H166" s="85" t="s">
         <v>223</v>
-      </c>
-      <c r="H166" s="85" t="s">
-        <v>224</v>
       </c>
       <c r="I166" s="26"/>
       <c r="J166" s="28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K166" s="29">
         <v>1000</v>
@@ -8803,7 +8296,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="167" s="17" customFormat="1" ht="16.5" spans="1:13">
+    <row r="167" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A167" s="84">
         <v>35012</v>
       </c>
@@ -8811,7 +8304,7 @@
         <v>103501</v>
       </c>
       <c r="C167" s="84" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D167" s="84">
         <v>2</v>
@@ -8820,17 +8313,17 @@
         <v>180</v>
       </c>
       <c r="F167" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="G167" s="85" t="s">
         <v>222</v>
       </c>
-      <c r="G167" s="85" t="s">
+      <c r="H167" s="85" t="s">
         <v>223</v>
-      </c>
-      <c r="H167" s="85" t="s">
-        <v>224</v>
       </c>
       <c r="I167" s="26"/>
       <c r="J167" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K167" s="29">
         <v>600</v>
@@ -8842,7 +8335,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="168" s="17" customFormat="1" ht="16.5" spans="1:13">
+    <row r="168" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A168" s="84">
         <v>35013</v>
       </c>
@@ -8850,7 +8343,7 @@
         <v>103501</v>
       </c>
       <c r="C168" s="84" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D168" s="84">
         <v>3</v>
@@ -8859,17 +8352,17 @@
         <v>127</v>
       </c>
       <c r="F168" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="G168" s="85" t="s">
         <v>222</v>
       </c>
-      <c r="G168" s="85" t="s">
+      <c r="H168" s="85" t="s">
         <v>223</v>
-      </c>
-      <c r="H168" s="85" t="s">
-        <v>224</v>
       </c>
       <c r="I168" s="26"/>
       <c r="J168" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K168" s="29">
         <v>250</v>
@@ -8881,7 +8374,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="169" s="17" customFormat="1" ht="16.5" spans="1:13">
+    <row r="169" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A169" s="84">
         <v>35014</v>
       </c>
@@ -8889,26 +8382,26 @@
         <v>103501</v>
       </c>
       <c r="C169" s="84" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D169" s="84">
         <v>4</v>
       </c>
       <c r="E169" s="85" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F169" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="G169" s="85" t="s">
         <v>222</v>
       </c>
-      <c r="G169" s="85" t="s">
+      <c r="H169" s="85" t="s">
         <v>223</v>
-      </c>
-      <c r="H169" s="85" t="s">
-        <v>224</v>
       </c>
       <c r="I169" s="26"/>
       <c r="J169" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K169" s="29">
         <v>-250</v>
@@ -8920,7 +8413,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="170" s="17" customFormat="1" ht="16.5" spans="1:13">
+    <row r="170" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A170" s="84">
         <v>35015</v>
       </c>
@@ -8928,26 +8421,26 @@
         <v>103501</v>
       </c>
       <c r="C170" s="84" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D170" s="84">
         <v>5</v>
       </c>
       <c r="E170" s="85" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F170" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="G170" s="85" t="s">
         <v>222</v>
       </c>
-      <c r="G170" s="85" t="s">
+      <c r="H170" s="85" t="s">
         <v>223</v>
-      </c>
-      <c r="H170" s="85" t="s">
-        <v>224</v>
       </c>
       <c r="I170" s="26"/>
       <c r="J170" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K170" s="29">
         <v>-600</v>
@@ -8959,7 +8452,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="171" s="17" customFormat="1" ht="16.5" spans="1:13">
+    <row r="171" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A171" s="84">
         <v>35016</v>
       </c>
@@ -8967,26 +8460,26 @@
         <v>103501</v>
       </c>
       <c r="C171" s="84" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D171" s="84">
         <v>6</v>
       </c>
       <c r="E171" s="85" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F171" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="G171" s="85" t="s">
         <v>222</v>
       </c>
-      <c r="G171" s="85" t="s">
+      <c r="H171" s="85" t="s">
         <v>223</v>
-      </c>
-      <c r="H171" s="85" t="s">
-        <v>224</v>
       </c>
       <c r="I171" s="26"/>
       <c r="J171" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K171" s="29">
         <v>-1000</v>
@@ -8998,7 +8491,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="172" s="17" customFormat="1" ht="16.5" spans="1:13">
+    <row r="172" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A172" s="84">
         <v>35017</v>
       </c>
@@ -9006,7 +8499,7 @@
         <v>103501</v>
       </c>
       <c r="C172" s="84" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D172" s="84">
         <v>7</v>
@@ -9015,17 +8508,17 @@
         <v>57</v>
       </c>
       <c r="F172" s="86" t="s">
+        <v>221</v>
+      </c>
+      <c r="G172" s="85" t="s">
         <v>222</v>
       </c>
-      <c r="G172" s="85" t="s">
+      <c r="H172" s="85" t="s">
         <v>223</v>
-      </c>
-      <c r="H172" s="85" t="s">
-        <v>224</v>
       </c>
       <c r="I172" s="26"/>
       <c r="J172" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K172" s="29">
         <v>-999999</v>
@@ -9037,7 +8530,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="173" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="173" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A173" s="87">
         <v>36001</v>
       </c>
@@ -9045,26 +8538,26 @@
         <v>103600</v>
       </c>
       <c r="C173" s="87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D173" s="87">
         <v>1</v>
       </c>
       <c r="E173" s="88" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F173" s="88" t="s">
         <v>48</v>
       </c>
       <c r="G173" s="88" t="s">
+        <v>230</v>
+      </c>
+      <c r="H173" s="88" t="s">
         <v>231</v>
-      </c>
-      <c r="H173" s="88" t="s">
-        <v>232</v>
       </c>
       <c r="I173" s="26"/>
       <c r="J173" s="89" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K173" s="29">
         <v>1000</v>
@@ -9076,7 +8569,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="174" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="174" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A174" s="87">
         <v>36002</v>
       </c>
@@ -9084,7 +8577,7 @@
         <v>103600</v>
       </c>
       <c r="C174" s="87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D174" s="87">
         <v>2</v>
@@ -9096,14 +8589,14 @@
         <v>48</v>
       </c>
       <c r="G174" s="88" t="s">
+        <v>230</v>
+      </c>
+      <c r="H174" s="88" t="s">
         <v>231</v>
-      </c>
-      <c r="H174" s="88" t="s">
-        <v>232</v>
       </c>
       <c r="I174" s="26"/>
       <c r="J174" s="89" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K174" s="29">
         <v>600</v>
@@ -9115,7 +8608,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="175" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="175" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A175" s="87">
         <v>36003</v>
       </c>
@@ -9123,26 +8616,26 @@
         <v>103600</v>
       </c>
       <c r="C175" s="87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D175" s="87">
         <v>3</v>
       </c>
       <c r="E175" s="88" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F175" s="88" t="s">
         <v>48</v>
       </c>
       <c r="G175" s="88" t="s">
+        <v>230</v>
+      </c>
+      <c r="H175" s="88" t="s">
         <v>231</v>
-      </c>
-      <c r="H175" s="88" t="s">
-        <v>232</v>
       </c>
       <c r="I175" s="26"/>
       <c r="J175" s="89" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K175" s="29">
         <v>250</v>
@@ -9154,7 +8647,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="176" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="176" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A176" s="87">
         <v>36004</v>
       </c>
@@ -9162,26 +8655,26 @@
         <v>103600</v>
       </c>
       <c r="C176" s="87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D176" s="87">
         <v>4</v>
       </c>
       <c r="E176" s="88" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F176" s="88" t="s">
         <v>48</v>
       </c>
       <c r="G176" s="88" t="s">
+        <v>230</v>
+      </c>
+      <c r="H176" s="88" t="s">
         <v>231</v>
-      </c>
-      <c r="H176" s="88" t="s">
-        <v>232</v>
       </c>
       <c r="I176" s="26"/>
       <c r="J176" s="89" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K176" s="29">
         <v>-250</v>
@@ -9193,7 +8686,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="177" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="177" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A177" s="87">
         <v>36005</v>
       </c>
@@ -9201,7 +8694,7 @@
         <v>103600</v>
       </c>
       <c r="C177" s="87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D177" s="87">
         <v>5</v>
@@ -9213,14 +8706,14 @@
         <v>48</v>
       </c>
       <c r="G177" s="88" t="s">
+        <v>230</v>
+      </c>
+      <c r="H177" s="88" t="s">
         <v>231</v>
-      </c>
-      <c r="H177" s="88" t="s">
-        <v>232</v>
       </c>
       <c r="I177" s="26"/>
       <c r="J177" s="89" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K177" s="29">
         <v>-600</v>
@@ -9232,7 +8725,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="178" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="178" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A178" s="87">
         <v>36006</v>
       </c>
@@ -9240,7 +8733,7 @@
         <v>103600</v>
       </c>
       <c r="C178" s="87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D178" s="87">
         <v>6</v>
@@ -9252,14 +8745,14 @@
         <v>48</v>
       </c>
       <c r="G178" s="88" t="s">
+        <v>230</v>
+      </c>
+      <c r="H178" s="88" t="s">
         <v>231</v>
-      </c>
-      <c r="H178" s="88" t="s">
-        <v>232</v>
       </c>
       <c r="I178" s="26"/>
       <c r="J178" s="89" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K178" s="29">
         <v>-1000</v>
@@ -9271,7 +8764,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="179" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="179" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A179" s="87">
         <v>36007</v>
       </c>
@@ -9279,7 +8772,7 @@
         <v>103600</v>
       </c>
       <c r="C179" s="87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D179" s="87">
         <v>7</v>
@@ -9291,14 +8784,14 @@
         <v>48</v>
       </c>
       <c r="G179" s="88" t="s">
+        <v>230</v>
+      </c>
+      <c r="H179" s="88" t="s">
         <v>231</v>
-      </c>
-      <c r="H179" s="88" t="s">
-        <v>232</v>
       </c>
       <c r="I179" s="26"/>
       <c r="J179" s="89" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K179" s="29">
         <v>-999999</v>
@@ -9310,7 +8803,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="180" s="19" customFormat="1" ht="16.5" spans="1:13">
+    <row r="180" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A180" s="91">
         <v>38001</v>
       </c>
@@ -9318,26 +8811,26 @@
         <v>103800</v>
       </c>
       <c r="C180" s="91" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D180" s="91">
         <v>1</v>
       </c>
       <c r="E180" s="92" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F180" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G180" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="H180" s="92" t="s">
         <v>238</v>
-      </c>
-      <c r="H180" s="92" t="s">
-        <v>239</v>
       </c>
       <c r="I180" s="26"/>
       <c r="J180" s="93" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K180" s="29">
         <v>1000</v>
@@ -9349,7 +8842,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="181" s="19" customFormat="1" ht="16.5" spans="1:13">
+    <row r="181" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A181" s="91">
         <v>38002</v>
       </c>
@@ -9357,26 +8850,26 @@
         <v>103800</v>
       </c>
       <c r="C181" s="91" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D181" s="91">
         <v>2</v>
       </c>
       <c r="E181" s="92" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F181" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G181" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="H181" s="92" t="s">
         <v>238</v>
-      </c>
-      <c r="H181" s="92" t="s">
-        <v>239</v>
       </c>
       <c r="I181" s="26"/>
       <c r="J181" s="93" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K181" s="29">
         <v>600</v>
@@ -9388,7 +8881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" s="19" customFormat="1" ht="16.5" spans="1:13">
+    <row r="182" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A182" s="91">
         <v>38003</v>
       </c>
@@ -9396,26 +8889,26 @@
         <v>103800</v>
       </c>
       <c r="C182" s="91" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D182" s="91">
         <v>3</v>
       </c>
       <c r="E182" s="92" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F182" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G182" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="H182" s="92" t="s">
         <v>238</v>
-      </c>
-      <c r="H182" s="92" t="s">
-        <v>239</v>
       </c>
       <c r="I182" s="26"/>
       <c r="J182" s="93" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K182" s="29">
         <v>250</v>
@@ -9427,7 +8920,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="183" s="19" customFormat="1" ht="16.5" spans="1:13">
+    <row r="183" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A183" s="91">
         <v>38004</v>
       </c>
@@ -9435,26 +8928,26 @@
         <v>103800</v>
       </c>
       <c r="C183" s="91" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D183" s="91">
         <v>4</v>
       </c>
       <c r="E183" s="92" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F183" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G183" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="H183" s="92" t="s">
         <v>238</v>
-      </c>
-      <c r="H183" s="92" t="s">
-        <v>239</v>
       </c>
       <c r="I183" s="26"/>
       <c r="J183" s="93" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K183" s="29">
         <v>-250</v>
@@ -9466,7 +8959,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="184" s="19" customFormat="1" ht="16.5" spans="1:13">
+    <row r="184" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A184" s="91">
         <v>38005</v>
       </c>
@@ -9474,26 +8967,26 @@
         <v>103800</v>
       </c>
       <c r="C184" s="91" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D184" s="91">
         <v>5</v>
       </c>
       <c r="E184" s="92" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F184" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G184" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="H184" s="92" t="s">
         <v>238</v>
-      </c>
-      <c r="H184" s="92" t="s">
-        <v>239</v>
       </c>
       <c r="I184" s="26"/>
       <c r="J184" s="93" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K184" s="29">
         <v>-600</v>
@@ -9505,7 +8998,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="185" s="19" customFormat="1" ht="16.5" spans="1:13">
+    <row r="185" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A185" s="91">
         <v>38006</v>
       </c>
@@ -9513,26 +9006,26 @@
         <v>103800</v>
       </c>
       <c r="C185" s="91" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D185" s="91">
         <v>6</v>
       </c>
       <c r="E185" s="92" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F185" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G185" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="H185" s="92" t="s">
         <v>238</v>
-      </c>
-      <c r="H185" s="92" t="s">
-        <v>239</v>
       </c>
       <c r="I185" s="26"/>
       <c r="J185" s="93" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K185" s="29">
         <v>-1000</v>
@@ -9544,7 +9037,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="186" s="19" customFormat="1" ht="16.5" spans="1:13">
+    <row r="186" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A186" s="91">
         <v>38007</v>
       </c>
@@ -9552,7 +9045,7 @@
         <v>103800</v>
       </c>
       <c r="C186" s="91" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D186" s="91">
         <v>7</v>
@@ -9564,14 +9057,14 @@
         <v>48</v>
       </c>
       <c r="G186" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="H186" s="92" t="s">
         <v>238</v>
-      </c>
-      <c r="H186" s="92" t="s">
-        <v>239</v>
       </c>
       <c r="I186" s="26"/>
       <c r="J186" s="93" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K186" s="29">
         <v>-999999</v>
@@ -9583,7 +9076,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="187" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="187" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A187" s="87">
         <v>37001</v>
       </c>
@@ -9591,20 +9084,20 @@
         <v>103700</v>
       </c>
       <c r="C187" s="87" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D187" s="87">
         <v>1</v>
       </c>
       <c r="E187" s="88" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F187" s="88"/>
       <c r="G187" s="88"/>
       <c r="H187" s="88"/>
       <c r="I187" s="26"/>
-      <c r="J187" s="89" t="s">
-        <v>248</v>
+      <c r="J187" s="123" t="s">
+        <v>298</v>
       </c>
       <c r="K187" s="29">
         <v>1000</v>
@@ -9616,7 +9109,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="188" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="188" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A188" s="87">
         <v>37002</v>
       </c>
@@ -9624,13 +9117,13 @@
         <v>103700</v>
       </c>
       <c r="C188" s="87" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D188" s="87">
         <v>2</v>
       </c>
       <c r="E188" s="88" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F188" s="88"/>
       <c r="G188" s="88"/>
@@ -9638,7 +9131,7 @@
       <c r="I188" s="26"/>
       <c r="J188" s="89" t="str">
         <f t="shared" ref="J188:J193" si="4">J187</f>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K188" s="29">
         <v>600</v>
@@ -9650,7 +9143,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="189" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="189" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A189" s="87">
         <v>37003</v>
       </c>
@@ -9658,13 +9151,13 @@
         <v>103700</v>
       </c>
       <c r="C189" s="87" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D189" s="87">
         <v>3</v>
       </c>
       <c r="E189" s="88" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F189" s="88"/>
       <c r="G189" s="88"/>
@@ -9672,7 +9165,7 @@
       <c r="I189" s="26"/>
       <c r="J189" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K189" s="29">
         <v>250</v>
@@ -9684,7 +9177,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="190" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="190" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A190" s="87">
         <v>37004</v>
       </c>
@@ -9692,7 +9185,7 @@
         <v>103700</v>
       </c>
       <c r="C190" s="87" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D190" s="87">
         <v>4</v>
@@ -9706,7 +9199,7 @@
       <c r="I190" s="26"/>
       <c r="J190" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K190" s="29">
         <v>-250</v>
@@ -9718,7 +9211,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="191" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="191" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A191" s="87">
         <v>37005</v>
       </c>
@@ -9726,13 +9219,13 @@
         <v>103700</v>
       </c>
       <c r="C191" s="87" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D191" s="87">
         <v>5</v>
       </c>
       <c r="E191" s="88" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F191" s="88"/>
       <c r="G191" s="88"/>
@@ -9740,7 +9233,7 @@
       <c r="I191" s="26"/>
       <c r="J191" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K191" s="29">
         <v>-600</v>
@@ -9752,7 +9245,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="192" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="192" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A192" s="87">
         <v>37006</v>
       </c>
@@ -9760,13 +9253,13 @@
         <v>103700</v>
       </c>
       <c r="C192" s="87" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D192" s="87">
         <v>6</v>
       </c>
       <c r="E192" s="88" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F192" s="88"/>
       <c r="G192" s="88"/>
@@ -9774,7 +9267,7 @@
       <c r="I192" s="26"/>
       <c r="J192" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K192" s="29">
         <v>-1000</v>
@@ -9786,7 +9279,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="193" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="193" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A193" s="87">
         <v>37007</v>
       </c>
@@ -9794,7 +9287,7 @@
         <v>103700</v>
       </c>
       <c r="C193" s="87" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D193" s="87">
         <v>7</v>
@@ -9808,7 +9301,7 @@
       <c r="I193" s="26"/>
       <c r="J193" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K193" s="29">
         <v>-999999</v>
@@ -9820,7 +9313,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="194" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="194" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A194" s="95">
         <v>39001</v>
       </c>
@@ -9828,20 +9321,20 @@
         <v>103900</v>
       </c>
       <c r="C194" s="95" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D194" s="95">
         <v>1</v>
       </c>
       <c r="E194" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F194" s="36"/>
       <c r="G194" s="36"/>
       <c r="H194" s="36"/>
       <c r="I194" s="26"/>
       <c r="J194" s="38" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K194" s="29">
         <v>1000</v>
@@ -9853,7 +9346,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="195" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="195" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A195" s="95">
         <v>39002</v>
       </c>
@@ -9861,13 +9354,13 @@
         <v>103900</v>
       </c>
       <c r="C195" s="95" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D195" s="95">
         <v>2</v>
       </c>
       <c r="E195" s="36" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F195" s="36"/>
       <c r="G195" s="36"/>
@@ -9887,7 +9380,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="196" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="196" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A196" s="95">
         <v>39003</v>
       </c>
@@ -9895,13 +9388,13 @@
         <v>103900</v>
       </c>
       <c r="C196" s="95" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D196" s="95">
         <v>3</v>
       </c>
       <c r="E196" s="36" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F196" s="36"/>
       <c r="G196" s="36"/>
@@ -9921,7 +9414,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="197" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A197" s="95">
         <v>39004</v>
       </c>
@@ -9929,13 +9422,13 @@
         <v>103900</v>
       </c>
       <c r="C197" s="95" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D197" s="95">
         <v>4</v>
       </c>
       <c r="E197" s="36" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F197" s="36"/>
       <c r="G197" s="36"/>
@@ -9955,7 +9448,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="198" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="198" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A198" s="95">
         <v>39005</v>
       </c>
@@ -9963,13 +9456,13 @@
         <v>103900</v>
       </c>
       <c r="C198" s="95" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D198" s="95">
         <v>5</v>
       </c>
       <c r="E198" s="36" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F198" s="36"/>
       <c r="G198" s="36"/>
@@ -9989,7 +9482,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="199" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="199" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A199" s="95">
         <v>39006</v>
       </c>
@@ -9997,13 +9490,13 @@
         <v>103900</v>
       </c>
       <c r="C199" s="95" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D199" s="95">
         <v>6</v>
       </c>
       <c r="E199" s="36" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F199" s="36"/>
       <c r="G199" s="36"/>
@@ -10023,7 +9516,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="200" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="200" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A200" s="95">
         <v>39007</v>
       </c>
@@ -10031,13 +9524,13 @@
         <v>103900</v>
       </c>
       <c r="C200" s="95" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D200" s="95">
         <v>7</v>
       </c>
       <c r="E200" s="36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F200" s="36"/>
       <c r="G200" s="36"/>
@@ -10057,7 +9550,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="201" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="201" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A201" s="77">
         <v>40001</v>
       </c>
@@ -10065,28 +9558,28 @@
         <v>104000</v>
       </c>
       <c r="C201" s="77" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D201" s="77">
         <v>1</v>
       </c>
       <c r="E201" s="78" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F201" s="78" t="s">
         <v>48</v>
       </c>
       <c r="G201" s="78" t="s">
+        <v>262</v>
+      </c>
+      <c r="H201" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="I201" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="H201" s="78" t="s">
+      <c r="J201" s="79" t="s">
         <v>265</v>
-      </c>
-      <c r="I201" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="J201" s="79" t="s">
-        <v>267</v>
       </c>
       <c r="K201" s="29">
         <v>1000</v>
@@ -10098,7 +9591,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="202" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="202" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A202" s="77">
         <v>40002</v>
       </c>
@@ -10106,28 +9599,28 @@
         <v>104000</v>
       </c>
       <c r="C202" s="77" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D202" s="77">
         <v>2</v>
       </c>
       <c r="E202" s="78" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F202" s="78" t="s">
         <v>48</v>
       </c>
       <c r="G202" s="78" t="s">
+        <v>262</v>
+      </c>
+      <c r="H202" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="I202" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="H202" s="78" t="s">
+      <c r="J202" s="79" t="s">
         <v>265</v>
-      </c>
-      <c r="I202" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="J202" s="79" t="s">
-        <v>267</v>
       </c>
       <c r="K202" s="29">
         <v>600</v>
@@ -10139,7 +9632,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="203" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="203" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A203" s="77">
         <v>40003</v>
       </c>
@@ -10147,7 +9640,7 @@
         <v>104000</v>
       </c>
       <c r="C203" s="77" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D203" s="77">
         <v>3</v>
@@ -10159,16 +9652,16 @@
         <v>48</v>
       </c>
       <c r="G203" s="78" t="s">
+        <v>262</v>
+      </c>
+      <c r="H203" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="I203" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="H203" s="78" t="s">
+      <c r="J203" s="79" t="s">
         <v>265</v>
-      </c>
-      <c r="I203" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="J203" s="79" t="s">
-        <v>267</v>
       </c>
       <c r="K203" s="29">
         <v>250</v>
@@ -10180,7 +9673,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="204" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="204" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A204" s="77">
         <v>40004</v>
       </c>
@@ -10188,7 +9681,7 @@
         <v>104000</v>
       </c>
       <c r="C204" s="77" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D204" s="77">
         <v>4</v>
@@ -10200,16 +9693,16 @@
         <v>48</v>
       </c>
       <c r="G204" s="78" t="s">
+        <v>262</v>
+      </c>
+      <c r="H204" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="I204" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="H204" s="78" t="s">
+      <c r="J204" s="79" t="s">
         <v>265</v>
-      </c>
-      <c r="I204" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="J204" s="79" t="s">
-        <v>267</v>
       </c>
       <c r="K204" s="29">
         <v>-250</v>
@@ -10221,7 +9714,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="205" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="205" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A205" s="77">
         <v>40005</v>
       </c>
@@ -10229,7 +9722,7 @@
         <v>104000</v>
       </c>
       <c r="C205" s="77" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D205" s="77">
         <v>5</v>
@@ -10241,16 +9734,16 @@
         <v>48</v>
       </c>
       <c r="G205" s="78" t="s">
+        <v>262</v>
+      </c>
+      <c r="H205" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="I205" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="H205" s="78" t="s">
+      <c r="J205" s="79" t="s">
         <v>265</v>
-      </c>
-      <c r="I205" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="J205" s="79" t="s">
-        <v>267</v>
       </c>
       <c r="K205" s="29">
         <v>-600</v>
@@ -10262,7 +9755,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="206" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="206" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A206" s="77">
         <v>40006</v>
       </c>
@@ -10270,7 +9763,7 @@
         <v>104000</v>
       </c>
       <c r="C206" s="77" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D206" s="77">
         <v>6</v>
@@ -10282,16 +9775,16 @@
         <v>48</v>
       </c>
       <c r="G206" s="78" t="s">
+        <v>262</v>
+      </c>
+      <c r="H206" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="I206" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="H206" s="78" t="s">
+      <c r="J206" s="79" t="s">
         <v>265</v>
-      </c>
-      <c r="I206" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="J206" s="79" t="s">
-        <v>267</v>
       </c>
       <c r="K206" s="29">
         <v>-1000</v>
@@ -10303,7 +9796,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="207" s="15" customFormat="1" ht="16.5" spans="1:13">
+    <row r="207" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A207" s="77">
         <v>40007</v>
       </c>
@@ -10311,7 +9804,7 @@
         <v>104000</v>
       </c>
       <c r="C207" s="77" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D207" s="77">
         <v>7</v>
@@ -10323,16 +9816,16 @@
         <v>48</v>
       </c>
       <c r="G207" s="78" t="s">
+        <v>262</v>
+      </c>
+      <c r="H207" s="78" t="s">
+        <v>263</v>
+      </c>
+      <c r="I207" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="H207" s="78" t="s">
+      <c r="J207" s="79" t="s">
         <v>265</v>
-      </c>
-      <c r="I207" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="J207" s="79" t="s">
-        <v>267</v>
       </c>
       <c r="K207" s="29">
         <v>-999999</v>
@@ -10344,7 +9837,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="208" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="208" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A208" s="96">
         <v>41001</v>
       </c>
@@ -10352,7 +9845,7 @@
         <v>104100</v>
       </c>
       <c r="C208" s="96" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D208" s="96">
         <v>1</v>
@@ -10377,7 +9870,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="209" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="209" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A209" s="96">
         <v>41002</v>
       </c>
@@ -10385,7 +9878,7 @@
         <v>104100</v>
       </c>
       <c r="C209" s="96" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D209" s="96">
         <v>2</v>
@@ -10410,7 +9903,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="210" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="210" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A210" s="96">
         <v>41003</v>
       </c>
@@ -10418,7 +9911,7 @@
         <v>104100</v>
       </c>
       <c r="C210" s="96" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D210" s="96">
         <v>3</v>
@@ -10443,7 +9936,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="211" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="211" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A211" s="96">
         <v>41004</v>
       </c>
@@ -10451,7 +9944,7 @@
         <v>104100</v>
       </c>
       <c r="C211" s="96" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D211" s="96">
         <v>4</v>
@@ -10476,7 +9969,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="212" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="212" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A212" s="96">
         <v>41005</v>
       </c>
@@ -10484,7 +9977,7 @@
         <v>104100</v>
       </c>
       <c r="C212" s="96" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D212" s="96">
         <v>5</v>
@@ -10509,7 +10002,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="213" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="213" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A213" s="96">
         <v>41006</v>
       </c>
@@ -10517,7 +10010,7 @@
         <v>104100</v>
       </c>
       <c r="C213" s="96" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D213" s="96">
         <v>6</v>
@@ -10542,7 +10035,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="214" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="214" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A214" s="96">
         <v>41007</v>
       </c>
@@ -10550,7 +10043,7 @@
         <v>104100</v>
       </c>
       <c r="C214" s="96" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D214" s="96">
         <v>7</v>
@@ -10575,7 +10068,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="215" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="215" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A215" s="100">
         <v>42001</v>
       </c>
@@ -10583,7 +10076,7 @@
         <v>104200</v>
       </c>
       <c r="C215" s="100" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D215" s="100">
         <v>1</v>
@@ -10608,7 +10101,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="216" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="216" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A216" s="100">
         <v>42002</v>
       </c>
@@ -10616,7 +10109,7 @@
         <v>104200</v>
       </c>
       <c r="C216" s="100" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D216" s="100">
         <v>2</v>
@@ -10641,7 +10134,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="217" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="217" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A217" s="100">
         <v>42003</v>
       </c>
@@ -10649,7 +10142,7 @@
         <v>104200</v>
       </c>
       <c r="C217" s="100" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D217" s="100">
         <v>3</v>
@@ -10674,7 +10167,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="218" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="218" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A218" s="100">
         <v>42004</v>
       </c>
@@ -10682,7 +10175,7 @@
         <v>104200</v>
       </c>
       <c r="C218" s="100" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D218" s="100">
         <v>4</v>
@@ -10707,7 +10200,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="219" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="219" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A219" s="100">
         <v>42005</v>
       </c>
@@ -10715,7 +10208,7 @@
         <v>104200</v>
       </c>
       <c r="C219" s="100" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D219" s="100">
         <v>5</v>
@@ -10740,7 +10233,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="220" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="220" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A220" s="100">
         <v>42006</v>
       </c>
@@ -10748,7 +10241,7 @@
         <v>104200</v>
       </c>
       <c r="C220" s="100" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D220" s="100">
         <v>6</v>
@@ -10773,7 +10266,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="221" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="221" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A221" s="100">
         <v>42007</v>
       </c>
@@ -10781,7 +10274,7 @@
         <v>104200</v>
       </c>
       <c r="C221" s="100" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D221" s="100">
         <v>7</v>
@@ -10806,7 +10299,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="222" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="222" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A222" s="95">
         <v>48001</v>
       </c>
@@ -10814,7 +10307,7 @@
         <v>104800</v>
       </c>
       <c r="C222" s="95" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D222" s="95">
         <v>1</v>
@@ -10839,7 +10332,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="223" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="223" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A223" s="95">
         <v>48002</v>
       </c>
@@ -10847,7 +10340,7 @@
         <v>104800</v>
       </c>
       <c r="C223" s="95" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D223" s="95">
         <v>2</v>
@@ -10872,7 +10365,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="224" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="224" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A224" s="95">
         <v>48003</v>
       </c>
@@ -10880,7 +10373,7 @@
         <v>104800</v>
       </c>
       <c r="C224" s="95" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D224" s="95">
         <v>3</v>
@@ -10905,7 +10398,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="225" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="225" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A225" s="95">
         <v>48004</v>
       </c>
@@ -10913,7 +10406,7 @@
         <v>104800</v>
       </c>
       <c r="C225" s="95" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D225" s="95">
         <v>4</v>
@@ -10938,7 +10431,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="226" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="226" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A226" s="95">
         <v>48005</v>
       </c>
@@ -10946,7 +10439,7 @@
         <v>104800</v>
       </c>
       <c r="C226" s="95" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D226" s="95">
         <v>5</v>
@@ -10971,7 +10464,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="227" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="227" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A227" s="95">
         <v>48006</v>
       </c>
@@ -10979,7 +10472,7 @@
         <v>104800</v>
       </c>
       <c r="C227" s="95" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D227" s="95">
         <v>6</v>
@@ -11004,7 +10497,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="228" s="3" customFormat="1" ht="16.5" spans="1:13">
+    <row r="228" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A228" s="95">
         <v>48007</v>
       </c>
@@ -11012,7 +10505,7 @@
         <v>104800</v>
       </c>
       <c r="C228" s="95" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D228" s="95">
         <v>7</v>
@@ -11037,7 +10530,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="229" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="229" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A229" s="87">
         <v>50001</v>
       </c>
@@ -11045,7 +10538,7 @@
         <v>105000</v>
       </c>
       <c r="C229" s="87" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D229" s="87">
         <v>1</v>
@@ -11070,7 +10563,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="230" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="230" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A230" s="87">
         <v>50002</v>
       </c>
@@ -11078,7 +10571,7 @@
         <v>105000</v>
       </c>
       <c r="C230" s="87" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D230" s="87">
         <v>2</v>
@@ -11103,7 +10596,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="231" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="231" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A231" s="87">
         <v>50003</v>
       </c>
@@ -11111,7 +10604,7 @@
         <v>105000</v>
       </c>
       <c r="C231" s="87" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D231" s="87">
         <v>3</v>
@@ -11136,7 +10629,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="232" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="232" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A232" s="87">
         <v>50004</v>
       </c>
@@ -11144,7 +10637,7 @@
         <v>105000</v>
       </c>
       <c r="C232" s="87" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D232" s="87">
         <v>4</v>
@@ -11169,7 +10662,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="233" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="233" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A233" s="87">
         <v>50005</v>
       </c>
@@ -11177,7 +10670,7 @@
         <v>105000</v>
       </c>
       <c r="C233" s="87" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D233" s="87">
         <v>5</v>
@@ -11202,7 +10695,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="234" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="234" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A234" s="87">
         <v>50006</v>
       </c>
@@ -11210,7 +10703,7 @@
         <v>105000</v>
       </c>
       <c r="C234" s="87" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D234" s="87">
         <v>6</v>
@@ -11235,7 +10728,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="235" s="18" customFormat="1" ht="16.5" spans="1:13">
+    <row r="235" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A235" s="87">
         <v>50007</v>
       </c>
@@ -11243,7 +10736,7 @@
         <v>105000</v>
       </c>
       <c r="C235" s="87" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D235" s="87">
         <v>7</v>
@@ -11268,7 +10761,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="236" s="20" customFormat="1" ht="16.5" spans="1:13">
+    <row r="236" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A236" s="104">
         <v>51001</v>
       </c>
@@ -11276,20 +10769,20 @@
         <v>105100</v>
       </c>
       <c r="C236" s="104" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D236" s="104">
         <v>1</v>
       </c>
       <c r="E236" s="105" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F236" s="105"/>
       <c r="G236" s="105"/>
       <c r="H236" s="105"/>
       <c r="I236" s="26"/>
       <c r="J236" s="106" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K236" s="29">
         <v>1000</v>
@@ -11301,7 +10794,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="237" s="20" customFormat="1" ht="16.5" spans="1:13">
+    <row r="237" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A237" s="104">
         <v>51002</v>
       </c>
@@ -11309,20 +10802,20 @@
         <v>105100</v>
       </c>
       <c r="C237" s="104" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D237" s="104">
         <v>2</v>
       </c>
       <c r="E237" s="105" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F237" s="105"/>
       <c r="G237" s="105"/>
       <c r="H237" s="105"/>
       <c r="I237" s="26"/>
       <c r="J237" s="106" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K237" s="29">
         <v>600</v>
@@ -11334,7 +10827,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="238" s="20" customFormat="1" ht="16.5" spans="1:13">
+    <row r="238" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A238" s="104">
         <v>51003</v>
       </c>
@@ -11342,20 +10835,20 @@
         <v>105100</v>
       </c>
       <c r="C238" s="104" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D238" s="104">
         <v>3</v>
       </c>
       <c r="E238" s="105" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F238" s="105"/>
       <c r="G238" s="105"/>
       <c r="H238" s="105"/>
       <c r="I238" s="26"/>
       <c r="J238" s="106" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K238" s="29">
         <v>250</v>
@@ -11367,7 +10860,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="239" s="20" customFormat="1" ht="16.5" spans="1:13">
+    <row r="239" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A239" s="104">
         <v>51004</v>
       </c>
@@ -11375,20 +10868,20 @@
         <v>105100</v>
       </c>
       <c r="C239" s="104" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D239" s="104">
         <v>4</v>
       </c>
       <c r="E239" s="105" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F239" s="105"/>
       <c r="G239" s="105"/>
       <c r="H239" s="105"/>
       <c r="I239" s="26"/>
       <c r="J239" s="106" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K239" s="29">
         <v>-250</v>
@@ -11400,7 +10893,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="240" s="20" customFormat="1" ht="16.5" spans="1:13">
+    <row r="240" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A240" s="104">
         <v>51005</v>
       </c>
@@ -11408,20 +10901,20 @@
         <v>105100</v>
       </c>
       <c r="C240" s="104" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D240" s="104">
         <v>5</v>
       </c>
       <c r="E240" s="105" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F240" s="105"/>
       <c r="G240" s="105"/>
       <c r="H240" s="105"/>
       <c r="I240" s="26"/>
       <c r="J240" s="106" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K240" s="29">
         <v>-600</v>
@@ -11433,7 +10926,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="241" s="20" customFormat="1" ht="16.5" spans="1:13">
+    <row r="241" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A241" s="104">
         <v>51006</v>
       </c>
@@ -11441,20 +10934,20 @@
         <v>105100</v>
       </c>
       <c r="C241" s="104" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D241" s="104">
         <v>6</v>
       </c>
       <c r="E241" s="105" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F241" s="105"/>
       <c r="G241" s="105"/>
       <c r="H241" s="105"/>
       <c r="I241" s="26"/>
       <c r="J241" s="106" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K241" s="29">
         <v>-1000</v>
@@ -11466,7 +10959,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="242" s="20" customFormat="1" ht="16.5" spans="1:13">
+    <row r="242" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A242" s="104">
         <v>51007</v>
       </c>
@@ -11474,20 +10967,20 @@
         <v>105100</v>
       </c>
       <c r="C242" s="104" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D242" s="104">
         <v>7</v>
       </c>
       <c r="E242" s="105" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F242" s="105"/>
       <c r="G242" s="105"/>
       <c r="H242" s="105"/>
       <c r="I242" s="26"/>
       <c r="J242" s="106" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K242" s="29">
         <v>-999999</v>
@@ -11499,7 +10992,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="243" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="243" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A243" s="8">
         <v>53001</v>
       </c>
@@ -11507,20 +11000,20 @@
         <v>105300</v>
       </c>
       <c r="C243" s="53" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D243" s="31">
         <v>1</v>
       </c>
       <c r="E243" s="32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F243" s="32"/>
       <c r="G243" s="32"/>
       <c r="H243" s="32"/>
       <c r="I243" s="54"/>
       <c r="J243" s="108" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K243" s="29">
         <v>1000</v>
@@ -11532,7 +11025,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="244" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="244" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A244" s="8">
         <v>53002</v>
       </c>
@@ -11540,20 +11033,20 @@
         <v>105300</v>
       </c>
       <c r="C244" s="53" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D244" s="31">
         <v>2</v>
       </c>
       <c r="E244" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F244" s="32"/>
       <c r="G244" s="32"/>
       <c r="H244" s="32"/>
       <c r="I244" s="54"/>
       <c r="J244" s="32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K244" s="29">
         <v>600</v>
@@ -11565,7 +11058,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="245" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="245" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A245" s="8">
         <v>53003</v>
       </c>
@@ -11573,20 +11066,20 @@
         <v>105300</v>
       </c>
       <c r="C245" s="53" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D245" s="31">
         <v>3</v>
       </c>
       <c r="E245" s="32" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F245" s="32"/>
       <c r="G245" s="32"/>
       <c r="H245" s="32"/>
       <c r="I245" s="54"/>
       <c r="J245" s="32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K245" s="29">
         <v>250</v>
@@ -11598,7 +11091,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="246" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="246" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A246" s="8">
         <v>53004</v>
       </c>
@@ -11606,20 +11099,20 @@
         <v>105300</v>
       </c>
       <c r="C246" s="53" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D246" s="31">
         <v>4</v>
       </c>
       <c r="E246" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F246" s="32"/>
       <c r="G246" s="32"/>
       <c r="H246" s="32"/>
       <c r="I246" s="54"/>
       <c r="J246" s="32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K246" s="29">
         <v>-250</v>
@@ -11631,7 +11124,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="247" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="247" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A247" s="8">
         <v>53005</v>
       </c>
@@ -11639,20 +11132,20 @@
         <v>105300</v>
       </c>
       <c r="C247" s="53" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D247" s="31">
         <v>5</v>
       </c>
       <c r="E247" s="32" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F247" s="32"/>
       <c r="G247" s="32"/>
       <c r="H247" s="32"/>
       <c r="I247" s="54"/>
       <c r="J247" s="32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K247" s="29">
         <v>-600</v>
@@ -11664,7 +11157,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="248" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="248" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A248" s="8">
         <v>53006</v>
       </c>
@@ -11672,20 +11165,20 @@
         <v>105300</v>
       </c>
       <c r="C248" s="53" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D248" s="31">
         <v>6</v>
       </c>
       <c r="E248" s="32" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F248" s="32"/>
       <c r="G248" s="32"/>
       <c r="H248" s="32"/>
       <c r="I248" s="54"/>
       <c r="J248" s="32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K248" s="29">
         <v>-1000</v>
@@ -11697,7 +11190,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="249" s="8" customFormat="1" ht="16.5" spans="1:13">
+    <row r="249" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A249" s="8">
         <v>53007</v>
       </c>
@@ -11705,20 +11198,20 @@
         <v>105300</v>
       </c>
       <c r="C249" s="53" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D249" s="31">
         <v>7</v>
       </c>
       <c r="E249" s="32" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F249" s="32"/>
       <c r="G249" s="32"/>
       <c r="H249" s="32"/>
       <c r="I249" s="54"/>
       <c r="J249" s="32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K249" s="29">
         <v>-999999</v>
@@ -11730,7 +11223,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="250" ht="16.5" spans="1:13">
+    <row r="250" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A250" s="95">
         <v>54001</v>
       </c>
@@ -11738,7 +11231,7 @@
         <v>105400</v>
       </c>
       <c r="C250" s="95" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D250" s="95">
         <v>1</v>
@@ -11762,7 +11255,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="251" ht="16.5" spans="1:13">
+    <row r="251" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A251" s="95">
         <v>54002</v>
       </c>
@@ -11770,7 +11263,7 @@
         <v>105400</v>
       </c>
       <c r="C251" s="95" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D251" s="95">
         <v>2</v>
@@ -11794,7 +11287,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="252" ht="16.5" spans="1:13">
+    <row r="252" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A252" s="95">
         <v>54003</v>
       </c>
@@ -11802,7 +11295,7 @@
         <v>105400</v>
       </c>
       <c r="C252" s="95" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D252" s="95">
         <v>3</v>
@@ -11826,7 +11319,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="253" ht="16.5" spans="1:13">
+    <row r="253" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A253" s="95">
         <v>54004</v>
       </c>
@@ -11834,7 +11327,7 @@
         <v>105400</v>
       </c>
       <c r="C253" s="95" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D253" s="95">
         <v>4</v>
@@ -11858,7 +11351,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="254" ht="16.5" spans="1:13">
+    <row r="254" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A254" s="95">
         <v>54005</v>
       </c>
@@ -11866,7 +11359,7 @@
         <v>105400</v>
       </c>
       <c r="C254" s="95" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D254" s="95">
         <v>5</v>
@@ -11890,7 +11383,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="255" ht="16.5" spans="1:13">
+    <row r="255" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A255" s="95">
         <v>54006</v>
       </c>
@@ -11898,7 +11391,7 @@
         <v>105400</v>
       </c>
       <c r="C255" s="95" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D255" s="95">
         <v>6</v>
@@ -11922,7 +11415,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="256" ht="16.5" spans="1:13">
+    <row r="256" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A256" s="95">
         <v>54007</v>
       </c>
@@ -11930,7 +11423,7 @@
         <v>105400</v>
       </c>
       <c r="C256" s="95" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D256" s="95">
         <v>7</v>
@@ -11954,7 +11447,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="257" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="257" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A257" s="109">
         <v>57001</v>
       </c>
@@ -11962,7 +11455,7 @@
         <v>105700</v>
       </c>
       <c r="C257" s="110" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D257" s="111">
         <v>1</v>
@@ -11987,7 +11480,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="258" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="258" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A258" s="109">
         <v>57002</v>
       </c>
@@ -11995,7 +11488,7 @@
         <v>105700</v>
       </c>
       <c r="C258" s="110" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D258" s="111">
         <v>2</v>
@@ -12020,7 +11513,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="259" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="259" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A259" s="109">
         <v>57003</v>
       </c>
@@ -12028,7 +11521,7 @@
         <v>105700</v>
       </c>
       <c r="C259" s="110" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D259" s="111">
         <v>3</v>
@@ -12053,7 +11546,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="260" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="260" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A260" s="109">
         <v>57004</v>
       </c>
@@ -12061,7 +11554,7 @@
         <v>105700</v>
       </c>
       <c r="C260" s="110" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D260" s="111">
         <v>4</v>
@@ -12086,7 +11579,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="261" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="261" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A261" s="109">
         <v>57005</v>
       </c>
@@ -12094,7 +11587,7 @@
         <v>105700</v>
       </c>
       <c r="C261" s="110" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D261" s="111">
         <v>5</v>
@@ -12119,7 +11612,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="262" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="262" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A262" s="109">
         <v>57006</v>
       </c>
@@ -12127,7 +11620,7 @@
         <v>105700</v>
       </c>
       <c r="C262" s="110" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D262" s="111">
         <v>6</v>
@@ -12152,7 +11645,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="263" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="263" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A263" s="109">
         <v>57007</v>
       </c>
@@ -12160,7 +11653,7 @@
         <v>105700</v>
       </c>
       <c r="C263" s="110" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D263" s="111">
         <v>7</v>
@@ -12185,7 +11678,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="264" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="264" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A264" s="21">
         <v>58001</v>
       </c>
@@ -12193,20 +11686,20 @@
         <v>105800</v>
       </c>
       <c r="C264" s="115" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D264" s="115">
         <v>1</v>
       </c>
       <c r="E264" s="26" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F264" s="26"/>
       <c r="G264" s="26"/>
       <c r="H264" s="26"/>
       <c r="I264" s="113"/>
       <c r="J264" s="28" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K264" s="29">
         <v>1000</v>
@@ -12215,7 +11708,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="265" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="265" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A265" s="21">
         <v>58002</v>
       </c>
@@ -12223,20 +11716,20 @@
         <v>105800</v>
       </c>
       <c r="C265" s="115" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D265" s="115">
         <v>2</v>
       </c>
       <c r="E265" s="26" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F265" s="26"/>
       <c r="G265" s="26"/>
       <c r="H265" s="26"/>
       <c r="I265" s="113"/>
       <c r="J265" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K265" s="29">
         <v>600</v>
@@ -12245,7 +11738,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="266" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="266" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A266" s="21">
         <v>58003</v>
       </c>
@@ -12253,20 +11746,20 @@
         <v>105800</v>
       </c>
       <c r="C266" s="115" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D266" s="115">
         <v>3</v>
       </c>
       <c r="E266" s="26" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F266" s="26"/>
       <c r="G266" s="26"/>
       <c r="H266" s="26"/>
       <c r="I266" s="113"/>
       <c r="J266" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K266" s="29">
         <v>250</v>
@@ -12275,7 +11768,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="267" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="267" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A267" s="21">
         <v>58004</v>
       </c>
@@ -12283,20 +11776,20 @@
         <v>105800</v>
       </c>
       <c r="C267" s="115" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D267" s="115">
         <v>4</v>
       </c>
       <c r="E267" s="26" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F267" s="26"/>
       <c r="G267" s="26"/>
       <c r="H267" s="26"/>
       <c r="I267" s="113"/>
       <c r="J267" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K267" s="29">
         <v>-250</v>
@@ -12305,7 +11798,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="268" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="268" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A268" s="21">
         <v>58005</v>
       </c>
@@ -12313,20 +11806,20 @@
         <v>105800</v>
       </c>
       <c r="C268" s="115" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D268" s="115">
         <v>5</v>
       </c>
       <c r="E268" s="26" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F268" s="26"/>
       <c r="G268" s="26"/>
       <c r="H268" s="26"/>
       <c r="I268" s="113"/>
       <c r="J268" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K268" s="29">
         <v>-600</v>
@@ -12335,7 +11828,7 @@
         <v>-250</v>
       </c>
     </row>
-    <row r="269" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="269" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A269" s="21">
         <v>58006</v>
       </c>
@@ -12343,20 +11836,20 @@
         <v>105800</v>
       </c>
       <c r="C269" s="115" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D269" s="115">
         <v>6</v>
       </c>
       <c r="E269" s="26" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F269" s="26"/>
       <c r="G269" s="26"/>
       <c r="H269" s="26"/>
       <c r="I269" s="113"/>
       <c r="J269" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K269" s="29">
         <v>-1000</v>
@@ -12365,7 +11858,7 @@
         <v>-600</v>
       </c>
     </row>
-    <row r="270" s="21" customFormat="1" ht="16.5" spans="1:13">
+    <row r="270" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A270" s="21">
         <v>58007</v>
       </c>
@@ -12373,20 +11866,20 @@
         <v>105800</v>
       </c>
       <c r="C270" s="115" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D270" s="115">
         <v>7</v>
       </c>
       <c r="E270" s="26" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F270" s="26"/>
       <c r="G270" s="26"/>
       <c r="H270" s="26"/>
       <c r="I270" s="113"/>
       <c r="J270" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K270" s="29">
         <v>-999999</v>
@@ -12395,7 +11888,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="271" ht="16.5" spans="1:13">
+    <row r="271" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A271" s="116">
         <v>55001</v>
       </c>
@@ -12403,20 +11896,20 @@
         <v>105500</v>
       </c>
       <c r="C271" s="117" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D271" s="74">
         <v>1</v>
       </c>
       <c r="E271" s="75" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F271" s="75"/>
       <c r="G271" s="75"/>
       <c r="H271" s="75"/>
       <c r="I271" s="113"/>
       <c r="J271" s="89" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K271" s="29">
         <v>1000</v>
@@ -12428,7 +11921,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="272" ht="16.5" spans="1:13">
+    <row r="272" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A272" s="116">
         <v>55002</v>
       </c>
@@ -12436,13 +11929,13 @@
         <v>105500</v>
       </c>
       <c r="C272" s="117" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D272" s="74">
         <v>2</v>
       </c>
       <c r="E272" s="75" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F272" s="75"/>
       <c r="G272" s="75"/>
@@ -12462,7 +11955,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="273" ht="16.5" spans="1:13">
+    <row r="273" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A273" s="116">
         <v>55003</v>
       </c>
@@ -12470,13 +11963,13 @@
         <v>105500</v>
       </c>
       <c r="C273" s="117" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D273" s="74">
         <v>3</v>
       </c>
       <c r="E273" s="75" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F273" s="75"/>
       <c r="G273" s="75"/>
@@ -12496,7 +11989,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="274" ht="16.5" spans="1:13">
+    <row r="274" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A274" s="116">
         <v>55004</v>
       </c>
@@ -12504,13 +11997,13 @@
         <v>105500</v>
       </c>
       <c r="C274" s="117" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D274" s="74">
         <v>4</v>
       </c>
       <c r="E274" s="75" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F274" s="75"/>
       <c r="G274" s="75"/>
@@ -12530,7 +12023,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="275" ht="16.5" spans="1:13">
+    <row r="275" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A275" s="116">
         <v>55005</v>
       </c>
@@ -12538,13 +12031,13 @@
         <v>105500</v>
       </c>
       <c r="C275" s="117" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D275" s="74">
         <v>5</v>
       </c>
       <c r="E275" s="75" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F275" s="75"/>
       <c r="G275" s="75"/>
@@ -12564,7 +12057,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="276" ht="16.5" spans="1:13">
+    <row r="276" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A276" s="116">
         <v>55006</v>
       </c>
@@ -12572,13 +12065,13 @@
         <v>105500</v>
       </c>
       <c r="C276" s="117" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D276" s="74">
         <v>6</v>
       </c>
       <c r="E276" s="75" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F276" s="75"/>
       <c r="G276" s="75"/>
@@ -12598,7 +12091,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="277" ht="16.5" spans="1:13">
+    <row r="277" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A277" s="116">
         <v>55007</v>
       </c>
@@ -12606,13 +12099,13 @@
         <v>105500</v>
       </c>
       <c r="C277" s="117" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D277" s="74">
         <v>7</v>
       </c>
       <c r="E277" s="75" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F277" s="75"/>
       <c r="G277" s="75"/>
@@ -12632,7 +12125,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="278" ht="16.5" spans="1:13">
+    <row r="278" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A278" s="116">
         <v>55011</v>
       </c>
@@ -12640,7 +12133,7 @@
         <v>105501</v>
       </c>
       <c r="C278" s="117" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D278" s="74">
         <v>1</v>
@@ -12653,7 +12146,7 @@
       <c r="H278" s="112"/>
       <c r="I278" s="113"/>
       <c r="J278" s="89" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K278" s="29">
         <v>1000</v>
@@ -12665,7 +12158,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="279" ht="16.5" spans="1:13">
+    <row r="279" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A279" s="116">
         <v>55012</v>
       </c>
@@ -12673,7 +12166,7 @@
         <v>105501</v>
       </c>
       <c r="C279" s="117" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D279" s="74">
         <v>2</v>
@@ -12686,7 +12179,7 @@
       <c r="H279" s="112"/>
       <c r="I279" s="113"/>
       <c r="J279" s="89" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K279" s="29">
         <v>600</v>
@@ -12698,7 +12191,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="280" ht="16.5" spans="1:13">
+    <row r="280" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A280" s="116">
         <v>55013</v>
       </c>
@@ -12706,7 +12199,7 @@
         <v>105501</v>
       </c>
       <c r="C280" s="117" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D280" s="74">
         <v>3</v>
@@ -12719,7 +12212,7 @@
       <c r="H280" s="112"/>
       <c r="I280" s="113"/>
       <c r="J280" s="89" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K280" s="29">
         <v>250</v>
@@ -12731,7 +12224,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="281" ht="16.5" spans="1:13">
+    <row r="281" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A281" s="116">
         <v>55014</v>
       </c>
@@ -12739,7 +12232,7 @@
         <v>105501</v>
       </c>
       <c r="C281" s="117" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D281" s="74">
         <v>4</v>
@@ -12752,7 +12245,7 @@
       <c r="H281" s="112"/>
       <c r="I281" s="113"/>
       <c r="J281" s="89" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K281" s="29">
         <v>-250</v>
@@ -12764,7 +12257,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="282" ht="16.5" spans="1:13">
+    <row r="282" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A282" s="116">
         <v>55015</v>
       </c>
@@ -12772,7 +12265,7 @@
         <v>105501</v>
       </c>
       <c r="C282" s="117" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D282" s="74">
         <v>5</v>
@@ -12785,7 +12278,7 @@
       <c r="H282" s="112"/>
       <c r="I282" s="113"/>
       <c r="J282" s="89" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K282" s="29">
         <v>-600</v>
@@ -12797,7 +12290,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="283" ht="16.5" spans="1:13">
+    <row r="283" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A283" s="116">
         <v>55016</v>
       </c>
@@ -12805,7 +12298,7 @@
         <v>105501</v>
       </c>
       <c r="C283" s="117" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D283" s="74">
         <v>6</v>
@@ -12818,7 +12311,7 @@
       <c r="H283" s="112"/>
       <c r="I283" s="113"/>
       <c r="J283" s="89" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K283" s="29">
         <v>-1000</v>
@@ -12830,7 +12323,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="284" ht="16.5" spans="1:13">
+    <row r="284" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A284" s="116">
         <v>55017</v>
       </c>
@@ -12838,7 +12331,7 @@
         <v>105501</v>
       </c>
       <c r="C284" s="117" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D284" s="74">
         <v>7</v>
@@ -12851,7 +12344,7 @@
       <c r="H284" s="112"/>
       <c r="I284" s="113"/>
       <c r="J284" s="89" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K284" s="29">
         <v>-999999</v>
@@ -12863,7 +12356,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="285" s="22" customFormat="1" ht="16.5" spans="1:13">
+    <row r="285" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A285" s="119">
         <v>55021</v>
       </c>
@@ -12871,7 +12364,7 @@
         <v>105502</v>
       </c>
       <c r="C285" s="120" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D285" s="120">
         <v>1</v>
@@ -12884,7 +12377,7 @@
       <c r="H285" s="85"/>
       <c r="I285" s="85"/>
       <c r="J285" s="121" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K285" s="29">
         <v>1000</v>
@@ -12896,7 +12389,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="286" s="22" customFormat="1" ht="16.5" spans="1:13">
+    <row r="286" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A286" s="119">
         <v>55022</v>
       </c>
@@ -12904,7 +12397,7 @@
         <v>105502</v>
       </c>
       <c r="C286" s="120" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D286" s="120">
         <v>2</v>
@@ -12917,7 +12410,7 @@
       <c r="H286" s="85"/>
       <c r="I286" s="85"/>
       <c r="J286" s="121" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K286" s="29">
         <v>600</v>
@@ -12929,7 +12422,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="287" s="22" customFormat="1" ht="16.5" spans="1:13">
+    <row r="287" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A287" s="119">
         <v>55023</v>
       </c>
@@ -12937,7 +12430,7 @@
         <v>105502</v>
       </c>
       <c r="C287" s="120" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D287" s="120">
         <v>3</v>
@@ -12950,7 +12443,7 @@
       <c r="H287" s="85"/>
       <c r="I287" s="85"/>
       <c r="J287" s="121" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K287" s="29">
         <v>250</v>
@@ -12962,7 +12455,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="288" s="22" customFormat="1" ht="16.5" spans="1:13">
+    <row r="288" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A288" s="119">
         <v>55024</v>
       </c>
@@ -12970,7 +12463,7 @@
         <v>105502</v>
       </c>
       <c r="C288" s="120" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D288" s="120">
         <v>4</v>
@@ -12983,7 +12476,7 @@
       <c r="H288" s="85"/>
       <c r="I288" s="85"/>
       <c r="J288" s="121" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K288" s="29">
         <v>-250</v>
@@ -12995,7 +12488,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="289" s="22" customFormat="1" ht="16.5" spans="1:13">
+    <row r="289" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A289" s="119">
         <v>55025</v>
       </c>
@@ -13003,7 +12496,7 @@
         <v>105502</v>
       </c>
       <c r="C289" s="120" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D289" s="120">
         <v>5</v>
@@ -13016,7 +12509,7 @@
       <c r="H289" s="85"/>
       <c r="I289" s="85"/>
       <c r="J289" s="121" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K289" s="29">
         <v>-600</v>
@@ -13028,7 +12521,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="290" s="22" customFormat="1" ht="16.5" spans="1:13">
+    <row r="290" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A290" s="119">
         <v>55026</v>
       </c>
@@ -13036,7 +12529,7 @@
         <v>105502</v>
       </c>
       <c r="C290" s="120" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D290" s="120">
         <v>6</v>
@@ -13049,7 +12542,7 @@
       <c r="H290" s="85"/>
       <c r="I290" s="85"/>
       <c r="J290" s="121" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K290" s="29">
         <v>-1000</v>
@@ -13061,7 +12554,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="291" s="22" customFormat="1" ht="16.5" spans="1:13">
+    <row r="291" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A291" s="119">
         <v>55027</v>
       </c>
@@ -13069,7 +12562,7 @@
         <v>105502</v>
       </c>
       <c r="C291" s="120" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D291" s="120">
         <v>7</v>
@@ -13082,7 +12575,7 @@
       <c r="H291" s="85"/>
       <c r="I291" s="85"/>
       <c r="J291" s="121" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K291" s="29">
         <v>-999999</v>
@@ -13095,8 +12588,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java\project\slots\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D974A9-0F52-4006-92B6-1302B0E4E39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -28,21 +22,18 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>chuge</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -66,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -91,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -116,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -141,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -167,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="J1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -179,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -192,7 +183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="L1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -205,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -225,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="I12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -255,7 +246,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="297">
   <si>
     <t>id</t>
   </si>
@@ -812,6 +803,9 @@
     <t>1_8830|2_1120|3_50</t>
   </si>
   <si>
+    <t>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
+  </si>
+  <si>
     <t>1_9010|2_940|3_50</t>
   </si>
   <si>
@@ -995,19 +989,16 @@
     <t>10倍金牛</t>
   </si>
   <si>
-    <t>1_8650|2_1300|3_50</t>
-  </si>
-  <si>
-    <t>1_8870|2_1080|3_50</t>
-  </si>
-  <si>
-    <t>1_9090|2_860|3_50</t>
-  </si>
-  <si>
-    <t>1_9580|2_420|3_0</t>
-  </si>
-  <si>
-    <t>1_9790|2_210|3_0</t>
+    <t>1_9320|2_630|3_50</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9425|2_525|3_50</t>
+  </si>
+  <si>
+    <t>1_9530|2_420|3_50</t>
   </si>
   <si>
     <t>愤怒的小鸡</t>
@@ -1146,21 +1137,19 @@
   </si>
   <si>
     <t>伽罗宝石3</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-100000|1&amp;25-50000|25&amp;50-15000|50&amp;75-12000|75&amp;100-7000|100&amp;125-4000|125&amp;150-2000|150&amp;175-1000|175&amp;200-900|200&amp;225-400|225&amp;250-1100|250&amp;300-500|300&amp;350-1100|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-83700|200&amp;225-11700|225&amp;250-3200|250&amp;300-0|300&amp;350-600|350&amp;400-100|400&amp;450-0|450&amp;500-600|500&amp;600-100|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-80900|1&amp;25-13300|25&amp;50-4100|50&amp;75-600|75&amp;100-700|100&amp;125-200|125&amp;150-200|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1181,11 +1170,153 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1193,26 +1324,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="27">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1221,25 +1334,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79992065187536243"/>
+        <fgColor theme="5" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79992065187536243"/>
+        <fgColor theme="7" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79992065187536243"/>
+        <fgColor theme="8" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79992065187536243"/>
+        <fgColor theme="9" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1257,13 +1370,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39991454817346722"/>
+        <fgColor theme="9" tint="0.399945066682943"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1275,7 +1388,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1287,13 +1400,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1323,54 +1436,162 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79995117038483843"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39994506668294322"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79995117038483843"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39991454817346722"/>
+        <fgColor theme="7" tint="0.399945066682943"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39991454817346722"/>
+        <fgColor theme="4" tint="0.399945066682943"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1378,12 +1599,254 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1413,7 +1876,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1698,25 +2161,63 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 73" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 73" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1974,14 +2475,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M291"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="3" width="15.25" customWidth="1"/>
@@ -1994,7 +2495,7 @@
     <col min="13" max="13" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" spans="1:13">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -2033,7 +2534,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" ht="16.5" spans="1:13">
       <c r="A2" s="24" t="s">
         <v>12</v>
       </c>
@@ -2070,7 +2571,7 @@
       </c>
       <c r="M2" s="24"/>
     </row>
-    <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" ht="16.5" spans="1:13">
       <c r="A3" s="24" t="s">
         <v>0</v>
       </c>
@@ -2107,7 +2608,7 @@
       </c>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" spans="1:13">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
@@ -2122,7 +2623,7 @@
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
     </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" ht="16.5" spans="1:13">
       <c r="A5" s="24">
         <v>1001</v>
       </c>
@@ -2161,7 +2662,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" ht="16.5" spans="1:13">
       <c r="A6" s="24">
         <v>1002</v>
       </c>
@@ -2200,7 +2701,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="7" ht="16.5" spans="1:13">
       <c r="A7" s="24">
         <v>1003</v>
       </c>
@@ -2239,7 +2740,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="8" ht="16.5" spans="1:13">
       <c r="A8" s="24">
         <v>1004</v>
       </c>
@@ -2278,7 +2779,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="9" ht="16.5" spans="1:13">
       <c r="A9" s="24">
         <v>1005</v>
       </c>
@@ -2317,7 +2818,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="10" ht="16.5" spans="1:13">
       <c r="A10" s="24">
         <v>1006</v>
       </c>
@@ -2356,7 +2857,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="11" ht="16.5" spans="1:13">
       <c r="A11" s="24">
         <v>1007</v>
       </c>
@@ -2395,7 +2896,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="12" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A12" s="30">
         <v>3001</v>
       </c>
@@ -2434,7 +2935,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A13" s="30">
         <v>3002</v>
       </c>
@@ -2473,7 +2974,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="14" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A14" s="30">
         <v>3003</v>
       </c>
@@ -2512,7 +3013,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="15" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A15" s="30">
         <v>3004</v>
       </c>
@@ -2551,7 +3052,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="16" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A16" s="30">
         <v>3005</v>
       </c>
@@ -2590,7 +3091,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="17" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A17" s="30">
         <v>3006</v>
       </c>
@@ -2629,7 +3130,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="18" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A18" s="30">
         <v>3007</v>
       </c>
@@ -2668,7 +3169,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="19" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A19" s="24">
         <v>7001</v>
       </c>
@@ -2709,7 +3210,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="20" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A20" s="24">
         <v>7002</v>
       </c>
@@ -2750,7 +3251,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="21" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A21" s="24">
         <v>7003</v>
       </c>
@@ -2791,7 +3292,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="22" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A22" s="24">
         <v>7004</v>
       </c>
@@ -2832,7 +3333,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="23" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A23" s="24">
         <v>7005</v>
       </c>
@@ -2873,7 +3374,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="24" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A24" s="24">
         <v>7006</v>
       </c>
@@ -2914,7 +3415,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="25" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A25" s="24">
         <v>7007</v>
       </c>
@@ -2955,7 +3456,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A26" s="35">
         <v>8001</v>
       </c>
@@ -2988,7 +3489,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A27" s="35">
         <v>8002</v>
       </c>
@@ -3021,7 +3522,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A28" s="35">
         <v>8003</v>
       </c>
@@ -3054,7 +3555,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A29" s="35">
         <v>8004</v>
       </c>
@@ -3087,7 +3588,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A30" s="35">
         <v>8005</v>
       </c>
@@ -3120,7 +3621,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A31" s="35">
         <v>8006</v>
       </c>
@@ -3153,7 +3654,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A32" s="35">
         <v>8007</v>
       </c>
@@ -3186,7 +3687,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="33" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A33" s="30">
         <v>12001</v>
       </c>
@@ -3227,7 +3728,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="34" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A34" s="30">
         <v>12002</v>
       </c>
@@ -3268,7 +3769,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="35" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A35" s="30">
         <v>12003</v>
       </c>
@@ -3309,7 +3810,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="36" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A36" s="30">
         <v>12004</v>
       </c>
@@ -3350,7 +3851,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="37" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A37" s="30">
         <v>12005</v>
       </c>
@@ -3391,7 +3892,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="38" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A38" s="30">
         <v>12006</v>
       </c>
@@ -3432,7 +3933,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="39" s="1" customFormat="1" ht="16.5" spans="1:13">
       <c r="A39" s="30">
         <v>12007</v>
       </c>
@@ -3473,7 +3974,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="40" s="4" customFormat="1" ht="16.5" spans="1:13">
       <c r="A40" s="24">
         <v>14001</v>
       </c>
@@ -3512,7 +4013,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="41" s="4" customFormat="1" ht="16.5" spans="1:13">
       <c r="A41" s="24">
         <v>14002</v>
       </c>
@@ -3551,7 +4052,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="42" s="4" customFormat="1" ht="16.5" spans="1:13">
       <c r="A42" s="24">
         <v>14003</v>
       </c>
@@ -3590,7 +4091,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="43" s="4" customFormat="1" ht="16.5" spans="1:13">
       <c r="A43" s="24">
         <v>14004</v>
       </c>
@@ -3629,7 +4130,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="44" s="4" customFormat="1" ht="16.5" spans="1:13">
       <c r="A44" s="24">
         <v>14005</v>
       </c>
@@ -3668,7 +4169,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="45" s="4" customFormat="1" ht="16.5" spans="1:13">
       <c r="A45" s="24">
         <v>14006</v>
       </c>
@@ -3707,7 +4208,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="46" s="4" customFormat="1" ht="16.5" spans="1:13">
       <c r="A46" s="24">
         <v>14007</v>
       </c>
@@ -3746,7 +4247,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="47" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A47" s="42">
         <v>15001</v>
       </c>
@@ -3779,7 +4280,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="48" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A48" s="42">
         <v>15002</v>
       </c>
@@ -3812,7 +4313,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="49" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A49" s="42">
         <v>15003</v>
       </c>
@@ -3845,7 +4346,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="50" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A50" s="42">
         <v>15004</v>
       </c>
@@ -3878,7 +4379,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="51" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A51" s="42">
         <v>15005</v>
       </c>
@@ -3911,7 +4412,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="52" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A52" s="42">
         <v>15006</v>
       </c>
@@ -3944,7 +4445,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="53" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A53" s="42">
         <v>15007</v>
       </c>
@@ -3977,7 +4478,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="54" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A54" s="46">
         <v>16001</v>
       </c>
@@ -4010,7 +4511,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="55" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A55" s="46">
         <v>16002</v>
       </c>
@@ -4043,7 +4544,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="56" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A56" s="46">
         <v>16003</v>
       </c>
@@ -4076,7 +4577,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="57" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A57" s="46">
         <v>16004</v>
       </c>
@@ -4109,7 +4610,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="58" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A58" s="46">
         <v>16005</v>
       </c>
@@ -4142,7 +4643,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="59" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A59" s="46">
         <v>16006</v>
       </c>
@@ -4175,7 +4676,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="60" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A60" s="46">
         <v>16007</v>
       </c>
@@ -4208,7 +4709,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="61" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A61" s="24">
         <v>17001</v>
       </c>
@@ -4249,7 +4750,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="62" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A62" s="24">
         <v>17002</v>
       </c>
@@ -4290,7 +4791,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="63" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A63" s="24">
         <v>17003</v>
       </c>
@@ -4331,7 +4832,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="64" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A64" s="24">
         <v>17004</v>
       </c>
@@ -4372,7 +4873,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="65" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A65" s="24">
         <v>17005</v>
       </c>
@@ -4413,7 +4914,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="66" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="66" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A66" s="24">
         <v>17006</v>
       </c>
@@ -4454,7 +4955,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" spans="1:13" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="67" s="2" customFormat="1" ht="16.5" spans="1:13">
       <c r="A67" s="24">
         <v>17007</v>
       </c>
@@ -4495,7 +4996,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="68" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="68" s="7" customFormat="1" ht="16.5" spans="1:13">
       <c r="A68" s="50">
         <v>18001</v>
       </c>
@@ -4536,7 +5037,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:13">
       <c r="A69" s="50">
         <v>18002</v>
       </c>
@@ -4577,7 +5078,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="70" s="7" customFormat="1" ht="16.5" spans="1:13">
       <c r="A70" s="50">
         <v>18003</v>
       </c>
@@ -4618,7 +5119,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="71" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="71" s="7" customFormat="1" ht="16.5" spans="1:13">
       <c r="A71" s="50">
         <v>18004</v>
       </c>
@@ -4659,7 +5160,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="72" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="72" s="7" customFormat="1" ht="16.5" spans="1:13">
       <c r="A72" s="50">
         <v>18005</v>
       </c>
@@ -4700,7 +5201,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="73" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="73" s="7" customFormat="1" ht="16.5" spans="1:13">
       <c r="A73" s="50">
         <v>18006</v>
       </c>
@@ -4741,7 +5242,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:13" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="74" s="7" customFormat="1" ht="16.5" spans="1:13">
       <c r="A74" s="50">
         <v>18007</v>
       </c>
@@ -4782,7 +5283,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="75" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="75" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A75" s="42">
         <v>20001</v>
       </c>
@@ -4823,7 +5324,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="76" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A76" s="42">
         <v>20002</v>
       </c>
@@ -4864,7 +5365,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="77" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A77" s="42">
         <v>20003</v>
       </c>
@@ -4905,7 +5406,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="78" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="78" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A78" s="42">
         <v>20004</v>
       </c>
@@ -4946,7 +5447,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="79" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A79" s="42">
         <v>20005</v>
       </c>
@@ -4987,7 +5488,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="80" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="80" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A80" s="42">
         <v>20006</v>
       </c>
@@ -5028,7 +5529,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" spans="1:13" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="81" s="5" customFormat="1" ht="16.5" spans="1:13">
       <c r="A81" s="42">
         <v>20007</v>
       </c>
@@ -5069,7 +5570,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="82" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A82" s="53">
         <v>21001</v>
       </c>
@@ -5110,7 +5611,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="83" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="83" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A83" s="53">
         <v>21002</v>
       </c>
@@ -5151,7 +5652,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="84" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A84" s="53">
         <v>21003</v>
       </c>
@@ -5192,7 +5693,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="85" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="85" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A85" s="53">
         <v>21004</v>
       </c>
@@ -5233,7 +5734,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="86" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="86" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A86" s="53">
         <v>21005</v>
       </c>
@@ -5274,7 +5775,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="87" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="87" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A87" s="53">
         <v>21006</v>
       </c>
@@ -5315,7 +5816,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="88" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A88" s="53">
         <v>21007</v>
       </c>
@@ -5356,7 +5857,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="89" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="89" s="9" customFormat="1" ht="16.5" spans="1:13">
       <c r="A89" s="56">
         <v>22001</v>
       </c>
@@ -5397,7 +5898,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="90" s="9" customFormat="1" ht="16.5" spans="1:13">
       <c r="A90" s="56">
         <v>22002</v>
       </c>
@@ -5438,7 +5939,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="91" s="9" customFormat="1" ht="16.5" spans="1:13">
       <c r="A91" s="56">
         <v>22003</v>
       </c>
@@ -5479,7 +5980,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="92" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="92" s="9" customFormat="1" ht="16.5" spans="1:13">
       <c r="A92" s="56">
         <v>22004</v>
       </c>
@@ -5520,7 +6021,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="93" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="93" s="9" customFormat="1" ht="16.5" spans="1:13">
       <c r="A93" s="56">
         <v>22005</v>
       </c>
@@ -5561,7 +6062,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="94" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="94" s="9" customFormat="1" ht="16.5" spans="1:13">
       <c r="A94" s="56">
         <v>22006</v>
       </c>
@@ -5602,7 +6103,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" spans="1:13" s="9" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="95" s="9" customFormat="1" ht="16.5" spans="1:13">
       <c r="A95" s="56">
         <v>22007</v>
       </c>
@@ -5643,7 +6144,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="96" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="96" s="10" customFormat="1" ht="16.5" spans="1:13">
       <c r="A96" s="60">
         <v>23001</v>
       </c>
@@ -5684,7 +6185,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="97" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="97" s="10" customFormat="1" ht="16.5" spans="1:13">
       <c r="A97" s="60">
         <v>23002</v>
       </c>
@@ -5725,7 +6226,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="98" s="10" customFormat="1" ht="16.5" spans="1:13">
       <c r="A98" s="60">
         <v>23003</v>
       </c>
@@ -5766,7 +6267,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="99" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="99" s="10" customFormat="1" ht="16.5" spans="1:13">
       <c r="A99" s="60">
         <v>23004</v>
       </c>
@@ -5807,7 +6308,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="100" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="100" s="10" customFormat="1" ht="16.5" spans="1:13">
       <c r="A100" s="60">
         <v>23005</v>
       </c>
@@ -5848,7 +6349,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="101" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="101" s="10" customFormat="1" ht="16.5" spans="1:13">
       <c r="A101" s="60">
         <v>23006</v>
       </c>
@@ -5889,7 +6390,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="102" spans="1:13" s="10" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="102" s="10" customFormat="1" ht="16.5" spans="1:13">
       <c r="A102" s="60">
         <v>23007</v>
       </c>
@@ -5930,7 +6431,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="103" ht="16.5" spans="1:13">
       <c r="A103" s="24">
         <v>24001</v>
       </c>
@@ -5969,7 +6470,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="104" ht="16.5" spans="1:13">
       <c r="A104" s="24">
         <v>24002</v>
       </c>
@@ -6008,7 +6509,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="105" ht="16.5" spans="1:13">
       <c r="A105" s="24">
         <v>24003</v>
       </c>
@@ -6047,7 +6548,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="106" ht="16.5" spans="1:13">
       <c r="A106" s="24">
         <v>24004</v>
       </c>
@@ -6086,7 +6587,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="107" ht="16.5" spans="1:13">
       <c r="A107" s="24">
         <v>24005</v>
       </c>
@@ -6125,7 +6626,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="108" ht="16.5" spans="1:13">
       <c r="A108" s="24">
         <v>24006</v>
       </c>
@@ -6164,7 +6665,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="109" ht="16.5" spans="1:13">
       <c r="A109" s="24">
         <v>24007</v>
       </c>
@@ -6203,7 +6704,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="110" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A110" s="63">
         <v>25001</v>
       </c>
@@ -6244,7 +6745,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="111" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="111" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A111" s="63">
         <v>25002</v>
       </c>
@@ -6285,7 +6786,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="112" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A112" s="63">
         <v>25003</v>
       </c>
@@ -6326,7 +6827,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="113" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="113" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A113" s="63">
         <v>25004</v>
       </c>
@@ -6367,7 +6868,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="114" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="114" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A114" s="63">
         <v>25005</v>
       </c>
@@ -6408,7 +6909,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="115" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="115" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A115" s="63">
         <v>25006</v>
       </c>
@@ -6449,7 +6950,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="116" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="116" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A116" s="63">
         <v>25007</v>
       </c>
@@ -6490,7 +6991,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="117" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="117" s="12" customFormat="1" ht="16.5" spans="1:13">
       <c r="A117" s="67">
         <v>26001</v>
       </c>
@@ -6523,7 +7024,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="118" s="12" customFormat="1" ht="16.5" spans="1:13">
       <c r="A118" s="67">
         <v>26002</v>
       </c>
@@ -6557,7 +7058,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="119" s="12" customFormat="1" ht="16.5" spans="1:13">
       <c r="A119" s="67">
         <v>26003</v>
       </c>
@@ -6591,7 +7092,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="120" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="120" s="12" customFormat="1" ht="16.5" spans="1:13">
       <c r="A120" s="67">
         <v>26004</v>
       </c>
@@ -6625,7 +7126,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="121" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="121" s="12" customFormat="1" ht="16.5" spans="1:13">
       <c r="A121" s="67">
         <v>26005</v>
       </c>
@@ -6659,7 +7160,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="122" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="122" s="12" customFormat="1" ht="16.5" spans="1:13">
       <c r="A122" s="67">
         <v>26006</v>
       </c>
@@ -6693,7 +7194,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="123" spans="1:13" s="12" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="123" s="12" customFormat="1" ht="16.5" spans="1:13">
       <c r="A123" s="67">
         <v>26007</v>
       </c>
@@ -6727,7 +7228,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="124" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="124" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A124" s="63">
         <v>27001</v>
       </c>
@@ -6747,8 +7248,8 @@
       <c r="G124" s="64"/>
       <c r="H124" s="64"/>
       <c r="I124" s="26"/>
-      <c r="J124" s="122" t="s">
-        <v>297</v>
+      <c r="J124" s="66" t="s">
+        <v>185</v>
       </c>
       <c r="K124" s="29">
         <v>1000</v>
@@ -6760,7 +7261,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="125" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="125" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A125" s="63">
         <v>27002</v>
       </c>
@@ -6774,7 +7275,7 @@
         <v>2</v>
       </c>
       <c r="E125" s="64" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F125" s="64"/>
       <c r="G125" s="64"/>
@@ -6794,7 +7295,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="126" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="126" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A126" s="63">
         <v>27003</v>
       </c>
@@ -6808,7 +7309,7 @@
         <v>3</v>
       </c>
       <c r="E126" s="64" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F126" s="64"/>
       <c r="G126" s="64"/>
@@ -6828,7 +7329,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="127" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="127" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A127" s="63">
         <v>27004</v>
       </c>
@@ -6842,7 +7343,7 @@
         <v>4</v>
       </c>
       <c r="E127" s="64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F127" s="64"/>
       <c r="G127" s="64"/>
@@ -6862,7 +7363,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="128" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="128" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A128" s="63">
         <v>27005</v>
       </c>
@@ -6876,7 +7377,7 @@
         <v>5</v>
       </c>
       <c r="E128" s="64" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F128" s="64"/>
       <c r="G128" s="64"/>
@@ -6896,7 +7397,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="129" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="129" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A129" s="63">
         <v>27006</v>
       </c>
@@ -6910,7 +7411,7 @@
         <v>6</v>
       </c>
       <c r="E129" s="64" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F129" s="64"/>
       <c r="G129" s="64"/>
@@ -6930,7 +7431,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="130" spans="1:13" s="11" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="130" s="11" customFormat="1" ht="16.5" spans="1:13">
       <c r="A130" s="63">
         <v>27007</v>
       </c>
@@ -6964,7 +7465,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="131" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="131" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A131" s="46">
         <v>28001</v>
       </c>
@@ -6972,7 +7473,7 @@
         <v>102800</v>
       </c>
       <c r="C131" s="46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D131" s="46">
         <v>1</v>
@@ -6997,7 +7498,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="132" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="132" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A132" s="46">
         <v>28002</v>
       </c>
@@ -7005,7 +7506,7 @@
         <v>102800</v>
       </c>
       <c r="C132" s="46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D132" s="46">
         <v>2</v>
@@ -7031,7 +7532,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="133" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A133" s="46">
         <v>28003</v>
       </c>
@@ -7039,7 +7540,7 @@
         <v>102800</v>
       </c>
       <c r="C133" s="46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D133" s="46">
         <v>3</v>
@@ -7065,7 +7566,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="134" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="134" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A134" s="46">
         <v>28004</v>
       </c>
@@ -7073,7 +7574,7 @@
         <v>102800</v>
       </c>
       <c r="C134" s="46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D134" s="46">
         <v>4</v>
@@ -7099,7 +7600,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="135" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="135" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A135" s="46">
         <v>28005</v>
       </c>
@@ -7107,7 +7608,7 @@
         <v>102800</v>
       </c>
       <c r="C135" s="46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D135" s="46">
         <v>5</v>
@@ -7133,7 +7634,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="136" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="136" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A136" s="46">
         <v>28006</v>
       </c>
@@ -7141,7 +7642,7 @@
         <v>102800</v>
       </c>
       <c r="C136" s="46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D136" s="46">
         <v>6</v>
@@ -7167,7 +7668,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="137" spans="1:13" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="137" s="6" customFormat="1" ht="16.5" spans="1:13">
       <c r="A137" s="46">
         <v>28007</v>
       </c>
@@ -7175,7 +7676,7 @@
         <v>102800</v>
       </c>
       <c r="C137" s="46" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D137" s="46">
         <v>7</v>
@@ -7201,7 +7702,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="138" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="138" s="13" customFormat="1" ht="16.5" spans="1:13">
       <c r="A138" s="70">
         <v>31001</v>
       </c>
@@ -7209,20 +7710,20 @@
         <v>103100</v>
       </c>
       <c r="C138" s="70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D138" s="70">
         <v>1</v>
       </c>
       <c r="E138" s="71" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F138" s="71"/>
       <c r="G138" s="71"/>
       <c r="H138" s="71"/>
       <c r="I138" s="26"/>
       <c r="J138" s="72" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K138" s="29">
         <v>1000</v>
@@ -7234,7 +7735,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="139" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="139" s="13" customFormat="1" ht="16.5" spans="1:13">
       <c r="A139" s="70">
         <v>31002</v>
       </c>
@@ -7242,13 +7743,13 @@
         <v>103100</v>
       </c>
       <c r="C139" s="70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D139" s="70">
         <v>2</v>
       </c>
       <c r="E139" s="71" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F139" s="71"/>
       <c r="G139" s="71"/>
@@ -7268,7 +7769,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="140" s="13" customFormat="1" ht="16.5" spans="1:13">
       <c r="A140" s="70">
         <v>31003</v>
       </c>
@@ -7276,13 +7777,13 @@
         <v>103100</v>
       </c>
       <c r="C140" s="70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D140" s="70">
         <v>3</v>
       </c>
       <c r="E140" s="71" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F140" s="71"/>
       <c r="G140" s="71"/>
@@ -7302,7 +7803,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="141" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="141" s="13" customFormat="1" ht="16.5" spans="1:13">
       <c r="A141" s="70">
         <v>31004</v>
       </c>
@@ -7310,13 +7811,13 @@
         <v>103100</v>
       </c>
       <c r="C141" s="70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D141" s="70">
         <v>4</v>
       </c>
       <c r="E141" s="71" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F141" s="71"/>
       <c r="G141" s="71"/>
@@ -7336,7 +7837,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="142" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="142" s="13" customFormat="1" ht="16.5" spans="1:13">
       <c r="A142" s="70">
         <v>31005</v>
       </c>
@@ -7344,13 +7845,13 @@
         <v>103100</v>
       </c>
       <c r="C142" s="70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D142" s="70">
         <v>5</v>
       </c>
       <c r="E142" s="71" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F142" s="71"/>
       <c r="G142" s="71"/>
@@ -7370,7 +7871,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="143" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="143" s="13" customFormat="1" ht="16.5" spans="1:13">
       <c r="A143" s="70">
         <v>31006</v>
       </c>
@@ -7378,13 +7879,13 @@
         <v>103100</v>
       </c>
       <c r="C143" s="70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D143" s="70">
         <v>6</v>
       </c>
       <c r="E143" s="71" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F143" s="71"/>
       <c r="G143" s="71"/>
@@ -7404,7 +7905,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="144" spans="1:13" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="144" s="13" customFormat="1" ht="16.5" spans="1:13">
       <c r="A144" s="70">
         <v>31007</v>
       </c>
@@ -7412,13 +7913,13 @@
         <v>103100</v>
       </c>
       <c r="C144" s="70" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D144" s="70">
         <v>7</v>
       </c>
       <c r="E144" s="71" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F144" s="71"/>
       <c r="G144" s="71"/>
@@ -7438,7 +7939,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="145" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="145" s="14" customFormat="1" ht="16.5" spans="1:13">
       <c r="A145" s="74">
         <v>34001</v>
       </c>
@@ -7446,26 +7947,26 @@
         <v>103400</v>
       </c>
       <c r="C145" s="74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D145" s="74">
         <v>1</v>
       </c>
       <c r="E145" s="75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F145" s="75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G145" s="75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H145" s="75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I145" s="26"/>
       <c r="J145" s="28" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K145" s="29">
         <v>1000</v>
@@ -7477,7 +7978,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="146" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="146" s="14" customFormat="1" ht="16.5" spans="1:13">
       <c r="A146" s="74">
         <v>34002</v>
       </c>
@@ -7485,7 +7986,7 @@
         <v>103400</v>
       </c>
       <c r="C146" s="74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D146" s="74">
         <v>2</v>
@@ -7494,17 +7995,17 @@
         <v>93</v>
       </c>
       <c r="F146" s="75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G146" s="75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H146" s="75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I146" s="26"/>
       <c r="J146" s="76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K146" s="29">
         <v>600</v>
@@ -7516,7 +8017,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="147" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="147" s="14" customFormat="1" ht="16.5" spans="1:13">
       <c r="A147" s="74">
         <v>34003</v>
       </c>
@@ -7524,26 +8025,26 @@
         <v>103400</v>
       </c>
       <c r="C147" s="74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D147" s="74">
         <v>3</v>
       </c>
       <c r="E147" s="75" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F147" s="75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G147" s="75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H147" s="75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I147" s="26"/>
       <c r="J147" s="76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K147" s="29">
         <v>250</v>
@@ -7555,7 +8056,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="148" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="148" s="14" customFormat="1" ht="16.5" spans="1:13">
       <c r="A148" s="74">
         <v>34004</v>
       </c>
@@ -7563,26 +8064,26 @@
         <v>103400</v>
       </c>
       <c r="C148" s="74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D148" s="74">
         <v>4</v>
       </c>
       <c r="E148" s="75" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F148" s="75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G148" s="75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H148" s="75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I148" s="26"/>
       <c r="J148" s="76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K148" s="29">
         <v>-250</v>
@@ -7594,7 +8095,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="149" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="149" s="14" customFormat="1" ht="16.5" spans="1:13">
       <c r="A149" s="74">
         <v>34005</v>
       </c>
@@ -7602,26 +8103,26 @@
         <v>103400</v>
       </c>
       <c r="C149" s="74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D149" s="74">
         <v>5</v>
       </c>
       <c r="E149" s="75" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F149" s="75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G149" s="75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H149" s="75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I149" s="26"/>
       <c r="J149" s="76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K149" s="29">
         <v>-600</v>
@@ -7633,7 +8134,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="150" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="150" s="14" customFormat="1" ht="16.5" spans="1:13">
       <c r="A150" s="74">
         <v>34006</v>
       </c>
@@ -7641,26 +8142,26 @@
         <v>103400</v>
       </c>
       <c r="C150" s="74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D150" s="74">
         <v>6</v>
       </c>
       <c r="E150" s="75" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F150" s="75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G150" s="75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H150" s="75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I150" s="26"/>
       <c r="J150" s="76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K150" s="29">
         <v>-1000</v>
@@ -7672,7 +8173,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" spans="1:13" s="14" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="151" s="14" customFormat="1" ht="16.5" spans="1:13">
       <c r="A151" s="74">
         <v>34007</v>
       </c>
@@ -7680,7 +8181,7 @@
         <v>103400</v>
       </c>
       <c r="C151" s="74" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D151" s="74">
         <v>7</v>
@@ -7689,17 +8190,17 @@
         <v>57</v>
       </c>
       <c r="F151" s="75" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G151" s="75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H151" s="75" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I151" s="26"/>
       <c r="J151" s="76" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K151" s="29">
         <v>-999999</v>
@@ -7711,7 +8212,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="152" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="152" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A152" s="77">
         <v>34011</v>
       </c>
@@ -7719,26 +8220,26 @@
         <v>103401</v>
       </c>
       <c r="C152" s="77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D152" s="77">
         <v>1</v>
       </c>
       <c r="E152" s="78" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F152" s="78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G152" s="75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H152" s="75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I152" s="26"/>
       <c r="J152" s="79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K152" s="29">
         <v>1000</v>
@@ -7750,7 +8251,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="153" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="153" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A153" s="77">
         <v>34012</v>
       </c>
@@ -7758,26 +8259,26 @@
         <v>103401</v>
       </c>
       <c r="C153" s="77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D153" s="77">
         <v>2</v>
       </c>
       <c r="E153" s="78" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F153" s="78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G153" s="75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H153" s="75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I153" s="26"/>
       <c r="J153" s="79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K153" s="29">
         <v>600</v>
@@ -7789,7 +8290,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="154" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="154" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A154" s="77">
         <v>34013</v>
       </c>
@@ -7797,26 +8298,26 @@
         <v>103401</v>
       </c>
       <c r="C154" s="77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D154" s="77">
         <v>3</v>
       </c>
       <c r="E154" s="78" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F154" s="78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G154" s="75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H154" s="75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I154" s="26"/>
       <c r="J154" s="79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K154" s="29">
         <v>250</v>
@@ -7828,7 +8329,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="155" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="155" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A155" s="77">
         <v>34014</v>
       </c>
@@ -7836,26 +8337,26 @@
         <v>103401</v>
       </c>
       <c r="C155" s="77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D155" s="77">
         <v>4</v>
       </c>
       <c r="E155" s="78" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F155" s="78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G155" s="75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H155" s="75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I155" s="26"/>
       <c r="J155" s="79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K155" s="29">
         <v>-250</v>
@@ -7867,7 +8368,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="156" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="156" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A156" s="77">
         <v>34015</v>
       </c>
@@ -7875,26 +8376,26 @@
         <v>103401</v>
       </c>
       <c r="C156" s="77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D156" s="77">
         <v>5</v>
       </c>
       <c r="E156" s="78" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F156" s="78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G156" s="75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H156" s="75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I156" s="26"/>
       <c r="J156" s="79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K156" s="29">
         <v>-600</v>
@@ -7906,7 +8407,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="157" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="157" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A157" s="77">
         <v>34016</v>
       </c>
@@ -7914,26 +8415,26 @@
         <v>103401</v>
       </c>
       <c r="C157" s="77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D157" s="77">
         <v>6</v>
       </c>
       <c r="E157" s="78" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F157" s="78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G157" s="75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H157" s="75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I157" s="26"/>
       <c r="J157" s="79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K157" s="29">
         <v>-1000</v>
@@ -7945,7 +8446,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="158" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="158" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A158" s="77">
         <v>34017</v>
       </c>
@@ -7953,7 +8454,7 @@
         <v>103401</v>
       </c>
       <c r="C158" s="77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D158" s="77">
         <v>7</v>
@@ -7962,17 +8463,17 @@
         <v>57</v>
       </c>
       <c r="F158" s="78" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G158" s="75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H158" s="75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I158" s="26"/>
       <c r="J158" s="79" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K158" s="29">
         <v>-999999</v>
@@ -7984,7 +8485,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="159" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="159" s="16" customFormat="1" ht="16.5" spans="1:13">
       <c r="A159" s="81">
         <v>35001</v>
       </c>
@@ -7992,7 +8493,7 @@
         <v>103500</v>
       </c>
       <c r="C159" s="81" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D159" s="81">
         <v>1</v>
@@ -8001,17 +8502,17 @@
         <v>176</v>
       </c>
       <c r="F159" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G159" s="82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H159" s="82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I159" s="26"/>
       <c r="J159" s="28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K159" s="29">
         <v>1000</v>
@@ -8023,7 +8524,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="160" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="160" s="16" customFormat="1" ht="16.5" spans="1:13">
       <c r="A160" s="81">
         <v>35002</v>
       </c>
@@ -8031,7 +8532,7 @@
         <v>103500</v>
       </c>
       <c r="C160" s="81" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D160" s="81">
         <v>2</v>
@@ -8040,17 +8541,17 @@
         <v>180</v>
       </c>
       <c r="F160" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G160" s="82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H160" s="82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I160" s="26"/>
       <c r="J160" s="83" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K160" s="29">
         <v>600</v>
@@ -8062,7 +8563,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="161" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="161" s="16" customFormat="1" ht="16.5" spans="1:13">
       <c r="A161" s="81">
         <v>35003</v>
       </c>
@@ -8070,7 +8571,7 @@
         <v>103500</v>
       </c>
       <c r="C161" s="81" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D161" s="81">
         <v>3</v>
@@ -8079,17 +8580,17 @@
         <v>127</v>
       </c>
       <c r="F161" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G161" s="82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H161" s="82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I161" s="26"/>
       <c r="J161" s="83" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K161" s="29">
         <v>250</v>
@@ -8101,7 +8602,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="162" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="162" s="16" customFormat="1" ht="16.5" spans="1:13">
       <c r="A162" s="81">
         <v>35004</v>
       </c>
@@ -8109,26 +8610,26 @@
         <v>103500</v>
       </c>
       <c r="C162" s="81" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D162" s="81">
         <v>4</v>
       </c>
       <c r="E162" s="82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F162" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G162" s="82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H162" s="82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I162" s="26"/>
       <c r="J162" s="83" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K162" s="29">
         <v>-250</v>
@@ -8140,7 +8641,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="163" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="163" s="16" customFormat="1" ht="16.5" spans="1:13">
       <c r="A163" s="81">
         <v>35005</v>
       </c>
@@ -8148,26 +8649,26 @@
         <v>103500</v>
       </c>
       <c r="C163" s="81" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D163" s="81">
         <v>5</v>
       </c>
       <c r="E163" s="82" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F163" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G163" s="82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H163" s="82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I163" s="26"/>
       <c r="J163" s="83" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K163" s="29">
         <v>-600</v>
@@ -8179,7 +8680,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="164" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="164" s="16" customFormat="1" ht="16.5" spans="1:13">
       <c r="A164" s="81">
         <v>35006</v>
       </c>
@@ -8187,26 +8688,26 @@
         <v>103500</v>
       </c>
       <c r="C164" s="81" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D164" s="81">
         <v>6</v>
       </c>
       <c r="E164" s="82" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F164" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G164" s="82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H164" s="82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I164" s="26"/>
       <c r="J164" s="83" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K164" s="29">
         <v>-1000</v>
@@ -8218,7 +8719,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="165" spans="1:13" s="16" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="165" s="16" customFormat="1" ht="16.5" spans="1:13">
       <c r="A165" s="81">
         <v>35007</v>
       </c>
@@ -8226,7 +8727,7 @@
         <v>103500</v>
       </c>
       <c r="C165" s="81" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D165" s="81">
         <v>7</v>
@@ -8235,17 +8736,17 @@
         <v>57</v>
       </c>
       <c r="F165" s="82" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G165" s="82" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H165" s="82" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I165" s="26"/>
       <c r="J165" s="83" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K165" s="29">
         <v>-999999</v>
@@ -8257,7 +8758,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="166" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="166" s="17" customFormat="1" ht="16.5" spans="1:13">
       <c r="A166" s="84">
         <v>35011</v>
       </c>
@@ -8265,7 +8766,7 @@
         <v>103501</v>
       </c>
       <c r="C166" s="84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D166" s="84">
         <v>1</v>
@@ -8274,17 +8775,17 @@
         <v>176</v>
       </c>
       <c r="F166" s="86" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G166" s="85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H166" s="85" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I166" s="26"/>
       <c r="J166" s="28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K166" s="29">
         <v>1000</v>
@@ -8296,7 +8797,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="167" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="167" s="17" customFormat="1" ht="16.5" spans="1:13">
       <c r="A167" s="84">
         <v>35012</v>
       </c>
@@ -8304,7 +8805,7 @@
         <v>103501</v>
       </c>
       <c r="C167" s="84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D167" s="84">
         <v>2</v>
@@ -8313,17 +8814,17 @@
         <v>180</v>
       </c>
       <c r="F167" s="86" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G167" s="85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H167" s="85" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I167" s="26"/>
       <c r="J167" s="34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K167" s="29">
         <v>600</v>
@@ -8335,7 +8836,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="168" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="168" s="17" customFormat="1" ht="16.5" spans="1:13">
       <c r="A168" s="84">
         <v>35013</v>
       </c>
@@ -8343,7 +8844,7 @@
         <v>103501</v>
       </c>
       <c r="C168" s="84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D168" s="84">
         <v>3</v>
@@ -8352,17 +8853,17 @@
         <v>127</v>
       </c>
       <c r="F168" s="86" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G168" s="85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H168" s="85" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I168" s="26"/>
       <c r="J168" s="34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K168" s="29">
         <v>250</v>
@@ -8374,7 +8875,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="169" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="169" s="17" customFormat="1" ht="16.5" spans="1:13">
       <c r="A169" s="84">
         <v>35014</v>
       </c>
@@ -8382,26 +8883,26 @@
         <v>103501</v>
       </c>
       <c r="C169" s="84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D169" s="84">
         <v>4</v>
       </c>
       <c r="E169" s="85" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F169" s="86" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G169" s="85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H169" s="85" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I169" s="26"/>
       <c r="J169" s="34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K169" s="29">
         <v>-250</v>
@@ -8413,7 +8914,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="170" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="170" s="17" customFormat="1" ht="16.5" spans="1:13">
       <c r="A170" s="84">
         <v>35015</v>
       </c>
@@ -8421,26 +8922,26 @@
         <v>103501</v>
       </c>
       <c r="C170" s="84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D170" s="84">
         <v>5</v>
       </c>
       <c r="E170" s="85" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F170" s="86" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G170" s="85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H170" s="85" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I170" s="26"/>
       <c r="J170" s="34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K170" s="29">
         <v>-600</v>
@@ -8452,7 +8953,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="171" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="171" s="17" customFormat="1" ht="16.5" spans="1:13">
       <c r="A171" s="84">
         <v>35016</v>
       </c>
@@ -8460,26 +8961,26 @@
         <v>103501</v>
       </c>
       <c r="C171" s="84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D171" s="84">
         <v>6</v>
       </c>
       <c r="E171" s="85" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F171" s="86" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G171" s="85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H171" s="85" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I171" s="26"/>
       <c r="J171" s="34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K171" s="29">
         <v>-1000</v>
@@ -8491,7 +8992,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="172" spans="1:13" s="17" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="172" s="17" customFormat="1" ht="16.5" spans="1:13">
       <c r="A172" s="84">
         <v>35017</v>
       </c>
@@ -8499,7 +9000,7 @@
         <v>103501</v>
       </c>
       <c r="C172" s="84" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D172" s="84">
         <v>7</v>
@@ -8508,17 +9009,17 @@
         <v>57</v>
       </c>
       <c r="F172" s="86" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G172" s="85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H172" s="85" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I172" s="26"/>
       <c r="J172" s="34" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K172" s="29">
         <v>-999999</v>
@@ -8530,7 +9031,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="173" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="173" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A173" s="87">
         <v>36001</v>
       </c>
@@ -8538,26 +9039,26 @@
         <v>103600</v>
       </c>
       <c r="C173" s="87" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D173" s="87">
         <v>1</v>
       </c>
       <c r="E173" s="88" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F173" s="88" t="s">
         <v>48</v>
       </c>
       <c r="G173" s="88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H173" s="88" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I173" s="26"/>
       <c r="J173" s="89" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K173" s="29">
         <v>1000</v>
@@ -8569,7 +9070,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="174" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="174" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A174" s="87">
         <v>36002</v>
       </c>
@@ -8577,7 +9078,7 @@
         <v>103600</v>
       </c>
       <c r="C174" s="87" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D174" s="87">
         <v>2</v>
@@ -8589,14 +9090,14 @@
         <v>48</v>
       </c>
       <c r="G174" s="88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H174" s="88" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I174" s="26"/>
       <c r="J174" s="89" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K174" s="29">
         <v>600</v>
@@ -8608,7 +9109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="175" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="175" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A175" s="87">
         <v>36003</v>
       </c>
@@ -8616,26 +9117,26 @@
         <v>103600</v>
       </c>
       <c r="C175" s="87" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D175" s="87">
         <v>3</v>
       </c>
       <c r="E175" s="88" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F175" s="88" t="s">
         <v>48</v>
       </c>
       <c r="G175" s="88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H175" s="88" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I175" s="26"/>
       <c r="J175" s="89" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K175" s="29">
         <v>250</v>
@@ -8647,7 +9148,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="176" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="176" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A176" s="87">
         <v>36004</v>
       </c>
@@ -8655,26 +9156,26 @@
         <v>103600</v>
       </c>
       <c r="C176" s="87" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D176" s="87">
         <v>4</v>
       </c>
       <c r="E176" s="88" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F176" s="88" t="s">
         <v>48</v>
       </c>
       <c r="G176" s="88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H176" s="88" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I176" s="26"/>
       <c r="J176" s="89" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K176" s="29">
         <v>-250</v>
@@ -8686,7 +9187,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="177" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="177" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A177" s="87">
         <v>36005</v>
       </c>
@@ -8694,7 +9195,7 @@
         <v>103600</v>
       </c>
       <c r="C177" s="87" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D177" s="87">
         <v>5</v>
@@ -8706,14 +9207,14 @@
         <v>48</v>
       </c>
       <c r="G177" s="88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H177" s="88" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I177" s="26"/>
       <c r="J177" s="89" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K177" s="29">
         <v>-600</v>
@@ -8725,7 +9226,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="178" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="178" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A178" s="87">
         <v>36006</v>
       </c>
@@ -8733,7 +9234,7 @@
         <v>103600</v>
       </c>
       <c r="C178" s="87" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D178" s="87">
         <v>6</v>
@@ -8745,14 +9246,14 @@
         <v>48</v>
       </c>
       <c r="G178" s="88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H178" s="88" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I178" s="26"/>
       <c r="J178" s="89" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K178" s="29">
         <v>-1000</v>
@@ -8764,7 +9265,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="179" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="179" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A179" s="87">
         <v>36007</v>
       </c>
@@ -8772,7 +9273,7 @@
         <v>103600</v>
       </c>
       <c r="C179" s="87" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D179" s="87">
         <v>7</v>
@@ -8784,14 +9285,14 @@
         <v>48</v>
       </c>
       <c r="G179" s="88" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H179" s="88" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I179" s="26"/>
       <c r="J179" s="89" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K179" s="29">
         <v>-999999</v>
@@ -8803,7 +9304,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="180" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="180" s="19" customFormat="1" ht="16.5" spans="1:13">
       <c r="A180" s="91">
         <v>38001</v>
       </c>
@@ -8811,26 +9312,26 @@
         <v>103800</v>
       </c>
       <c r="C180" s="91" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D180" s="91">
         <v>1</v>
       </c>
       <c r="E180" s="92" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F180" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G180" s="92" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H180" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I180" s="26"/>
       <c r="J180" s="93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K180" s="29">
         <v>1000</v>
@@ -8842,7 +9343,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="181" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="181" s="19" customFormat="1" ht="16.5" spans="1:13">
       <c r="A181" s="91">
         <v>38002</v>
       </c>
@@ -8850,26 +9351,26 @@
         <v>103800</v>
       </c>
       <c r="C181" s="91" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D181" s="91">
         <v>2</v>
       </c>
       <c r="E181" s="92" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F181" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G181" s="92" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H181" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I181" s="26"/>
       <c r="J181" s="93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K181" s="29">
         <v>600</v>
@@ -8881,7 +9382,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="182" s="19" customFormat="1" ht="16.5" spans="1:13">
       <c r="A182" s="91">
         <v>38003</v>
       </c>
@@ -8889,26 +9390,26 @@
         <v>103800</v>
       </c>
       <c r="C182" s="91" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D182" s="91">
         <v>3</v>
       </c>
       <c r="E182" s="92" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F182" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G182" s="92" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H182" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I182" s="26"/>
       <c r="J182" s="93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K182" s="29">
         <v>250</v>
@@ -8920,7 +9421,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="183" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="183" s="19" customFormat="1" ht="16.5" spans="1:13">
       <c r="A183" s="91">
         <v>38004</v>
       </c>
@@ -8928,26 +9429,26 @@
         <v>103800</v>
       </c>
       <c r="C183" s="91" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D183" s="91">
         <v>4</v>
       </c>
       <c r="E183" s="92" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F183" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G183" s="92" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H183" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I183" s="26"/>
       <c r="J183" s="93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K183" s="29">
         <v>-250</v>
@@ -8959,7 +9460,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="184" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="184" s="19" customFormat="1" ht="16.5" spans="1:13">
       <c r="A184" s="91">
         <v>38005</v>
       </c>
@@ -8967,26 +9468,26 @@
         <v>103800</v>
       </c>
       <c r="C184" s="91" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D184" s="91">
         <v>5</v>
       </c>
       <c r="E184" s="92" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F184" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G184" s="92" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H184" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I184" s="26"/>
       <c r="J184" s="93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K184" s="29">
         <v>-600</v>
@@ -8998,7 +9499,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="185" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="185" s="19" customFormat="1" ht="16.5" spans="1:13">
       <c r="A185" s="91">
         <v>38006</v>
       </c>
@@ -9006,26 +9507,26 @@
         <v>103800</v>
       </c>
       <c r="C185" s="91" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D185" s="91">
         <v>6</v>
       </c>
       <c r="E185" s="92" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F185" s="92" t="s">
         <v>48</v>
       </c>
       <c r="G185" s="92" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H185" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I185" s="26"/>
       <c r="J185" s="93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K185" s="29">
         <v>-1000</v>
@@ -9037,7 +9538,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="186" spans="1:13" s="19" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="186" s="19" customFormat="1" ht="16.5" spans="1:13">
       <c r="A186" s="91">
         <v>38007</v>
       </c>
@@ -9045,7 +9546,7 @@
         <v>103800</v>
       </c>
       <c r="C186" s="91" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D186" s="91">
         <v>7</v>
@@ -9057,14 +9558,14 @@
         <v>48</v>
       </c>
       <c r="G186" s="92" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H186" s="92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I186" s="26"/>
       <c r="J186" s="93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K186" s="29">
         <v>-999999</v>
@@ -9076,7 +9577,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="187" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="187" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A187" s="87">
         <v>37001</v>
       </c>
@@ -9084,20 +9585,20 @@
         <v>103700</v>
       </c>
       <c r="C187" s="87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D187" s="87">
         <v>1</v>
       </c>
       <c r="E187" s="88" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F187" s="88"/>
       <c r="G187" s="88"/>
       <c r="H187" s="88"/>
       <c r="I187" s="26"/>
-      <c r="J187" s="123" t="s">
-        <v>298</v>
+      <c r="J187" s="89" t="s">
+        <v>248</v>
       </c>
       <c r="K187" s="29">
         <v>1000</v>
@@ -9109,7 +9610,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="188" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="188" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A188" s="87">
         <v>37002</v>
       </c>
@@ -9117,13 +9618,13 @@
         <v>103700</v>
       </c>
       <c r="C188" s="87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D188" s="87">
         <v>2</v>
       </c>
       <c r="E188" s="88" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F188" s="88"/>
       <c r="G188" s="88"/>
@@ -9131,7 +9632,7 @@
       <c r="I188" s="26"/>
       <c r="J188" s="89" t="str">
         <f t="shared" ref="J188:J193" si="4">J187</f>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K188" s="29">
         <v>600</v>
@@ -9143,7 +9644,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="189" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="189" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A189" s="87">
         <v>37003</v>
       </c>
@@ -9151,13 +9652,13 @@
         <v>103700</v>
       </c>
       <c r="C189" s="87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D189" s="87">
         <v>3</v>
       </c>
       <c r="E189" s="88" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F189" s="88"/>
       <c r="G189" s="88"/>
@@ -9165,7 +9666,7 @@
       <c r="I189" s="26"/>
       <c r="J189" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K189" s="29">
         <v>250</v>
@@ -9177,7 +9678,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="190" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="190" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A190" s="87">
         <v>37004</v>
       </c>
@@ -9185,13 +9686,13 @@
         <v>103700</v>
       </c>
       <c r="C190" s="87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D190" s="87">
         <v>4</v>
       </c>
       <c r="E190" s="88" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="F190" s="88"/>
       <c r="G190" s="88"/>
@@ -9199,7 +9700,7 @@
       <c r="I190" s="26"/>
       <c r="J190" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K190" s="29">
         <v>-250</v>
@@ -9211,7 +9712,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="191" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="191" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A191" s="87">
         <v>37005</v>
       </c>
@@ -9219,13 +9720,13 @@
         <v>103700</v>
       </c>
       <c r="C191" s="87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D191" s="87">
         <v>5</v>
       </c>
       <c r="E191" s="88" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="F191" s="88"/>
       <c r="G191" s="88"/>
@@ -9233,7 +9734,7 @@
       <c r="I191" s="26"/>
       <c r="J191" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K191" s="29">
         <v>-600</v>
@@ -9245,7 +9746,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="192" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="192" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A192" s="87">
         <v>37006</v>
       </c>
@@ -9253,13 +9754,13 @@
         <v>103700</v>
       </c>
       <c r="C192" s="87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D192" s="87">
         <v>6</v>
       </c>
       <c r="E192" s="88" t="s">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="F192" s="88"/>
       <c r="G192" s="88"/>
@@ -9267,7 +9768,7 @@
       <c r="I192" s="26"/>
       <c r="J192" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K192" s="29">
         <v>-1000</v>
@@ -9279,7 +9780,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="193" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="193" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A193" s="87">
         <v>37007</v>
       </c>
@@ -9287,7 +9788,7 @@
         <v>103700</v>
       </c>
       <c r="C193" s="87" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D193" s="87">
         <v>7</v>
@@ -9301,7 +9802,7 @@
       <c r="I193" s="26"/>
       <c r="J193" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-10000|1&amp;25-20000|25&amp;50-30000|50&amp;75-30000|75&amp;100-30000|100&amp;125-20000|125&amp;150-9000|150&amp;175-8000|175&amp;200-7000|200&amp;225-6000|225&amp;250-5000|250&amp;300-4000|300&amp;350-3000|350&amp;400-2000|400&amp;450-1000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-30000|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-20000|800&amp;900-10000|900&amp;1000-6000|1000&amp;1200-4000|1200&amp;1400-2000|1400&amp;1600-1000|1600&amp;1800-500|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
       </c>
       <c r="K193" s="29">
         <v>-999999</v>
@@ -9313,7 +9814,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="194" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="194" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A194" s="95">
         <v>39001</v>
       </c>
@@ -9346,7 +9847,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="195" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="195" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A195" s="95">
         <v>39002</v>
       </c>
@@ -9380,7 +9881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="196" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="196" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A196" s="95">
         <v>39003</v>
       </c>
@@ -9414,7 +9915,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="197" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="197" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A197" s="95">
         <v>39004</v>
       </c>
@@ -9448,7 +9949,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="198" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="198" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A198" s="95">
         <v>39005</v>
       </c>
@@ -9482,7 +9983,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="199" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="199" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A199" s="95">
         <v>39006</v>
       </c>
@@ -9516,7 +10017,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="200" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="200" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A200" s="95">
         <v>39007</v>
       </c>
@@ -9550,7 +10051,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="201" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="201" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A201" s="77">
         <v>40001</v>
       </c>
@@ -9591,7 +10092,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="202" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="202" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A202" s="77">
         <v>40002</v>
       </c>
@@ -9632,7 +10133,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="203" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="203" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A203" s="77">
         <v>40003</v>
       </c>
@@ -9673,7 +10174,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="204" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="204" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A204" s="77">
         <v>40004</v>
       </c>
@@ -9714,7 +10215,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="205" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="205" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A205" s="77">
         <v>40005</v>
       </c>
@@ -9755,7 +10256,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="206" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="206" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A206" s="77">
         <v>40006</v>
       </c>
@@ -9796,7 +10297,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="207" spans="1:13" s="15" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="207" s="15" customFormat="1" ht="16.5" spans="1:13">
       <c r="A207" s="77">
         <v>40007</v>
       </c>
@@ -9837,7 +10338,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="208" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="208" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A208" s="96">
         <v>41001</v>
       </c>
@@ -9870,7 +10371,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="209" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="209" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A209" s="96">
         <v>41002</v>
       </c>
@@ -9903,7 +10404,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="210" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="210" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A210" s="96">
         <v>41003</v>
       </c>
@@ -9936,7 +10437,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="211" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="211" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A211" s="96">
         <v>41004</v>
       </c>
@@ -9969,7 +10470,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="212" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="212" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A212" s="96">
         <v>41005</v>
       </c>
@@ -10002,7 +10503,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="213" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="213" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A213" s="96">
         <v>41006</v>
       </c>
@@ -10035,7 +10536,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="214" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="214" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A214" s="96">
         <v>41007</v>
       </c>
@@ -10068,7 +10569,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="215" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="215" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A215" s="100">
         <v>42001</v>
       </c>
@@ -10101,7 +10602,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="216" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="216" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A216" s="100">
         <v>42002</v>
       </c>
@@ -10134,7 +10635,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="217" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="217" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A217" s="100">
         <v>42003</v>
       </c>
@@ -10167,7 +10668,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="218" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="218" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A218" s="100">
         <v>42004</v>
       </c>
@@ -10200,7 +10701,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="219" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="219" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A219" s="100">
         <v>42005</v>
       </c>
@@ -10233,7 +10734,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="220" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="220" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A220" s="100">
         <v>42006</v>
       </c>
@@ -10266,7 +10767,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="221" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="221" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A221" s="100">
         <v>42007</v>
       </c>
@@ -10299,7 +10800,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="222" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="222" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A222" s="95">
         <v>48001</v>
       </c>
@@ -10332,7 +10833,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="223" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="223" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A223" s="95">
         <v>48002</v>
       </c>
@@ -10365,7 +10866,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="224" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="224" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A224" s="95">
         <v>48003</v>
       </c>
@@ -10398,7 +10899,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="225" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="225" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A225" s="95">
         <v>48004</v>
       </c>
@@ -10431,7 +10932,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="226" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="226" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A226" s="95">
         <v>48005</v>
       </c>
@@ -10464,7 +10965,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="227" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="227" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A227" s="95">
         <v>48006</v>
       </c>
@@ -10497,7 +10998,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="228" spans="1:13" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="228" s="3" customFormat="1" ht="16.5" spans="1:13">
       <c r="A228" s="95">
         <v>48007</v>
       </c>
@@ -10530,7 +11031,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="229" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="229" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A229" s="87">
         <v>50001</v>
       </c>
@@ -10563,7 +11064,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="230" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="230" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A230" s="87">
         <v>50002</v>
       </c>
@@ -10596,7 +11097,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="231" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="231" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A231" s="87">
         <v>50003</v>
       </c>
@@ -10629,7 +11130,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="232" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="232" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A232" s="87">
         <v>50004</v>
       </c>
@@ -10662,7 +11163,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="233" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="233" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A233" s="87">
         <v>50005</v>
       </c>
@@ -10695,7 +11196,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="234" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="234" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A234" s="87">
         <v>50006</v>
       </c>
@@ -10728,7 +11229,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="235" spans="1:13" s="18" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="235" s="18" customFormat="1" ht="16.5" spans="1:13">
       <c r="A235" s="87">
         <v>50007</v>
       </c>
@@ -10761,7 +11262,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="236" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="236" s="20" customFormat="1" ht="16.5" spans="1:13">
       <c r="A236" s="104">
         <v>51001</v>
       </c>
@@ -10794,7 +11295,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="237" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="237" s="20" customFormat="1" ht="16.5" spans="1:13">
       <c r="A237" s="104">
         <v>51002</v>
       </c>
@@ -10827,7 +11328,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="238" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="238" s="20" customFormat="1" ht="16.5" spans="1:13">
       <c r="A238" s="104">
         <v>51003</v>
       </c>
@@ -10860,7 +11361,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="239" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="239" s="20" customFormat="1" ht="16.5" spans="1:13">
       <c r="A239" s="104">
         <v>51004</v>
       </c>
@@ -10893,7 +11394,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="240" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="240" s="20" customFormat="1" ht="16.5" spans="1:13">
       <c r="A240" s="104">
         <v>51005</v>
       </c>
@@ -10926,7 +11427,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="241" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="241" s="20" customFormat="1" ht="16.5" spans="1:13">
       <c r="A241" s="104">
         <v>51006</v>
       </c>
@@ -10959,7 +11460,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="242" spans="1:13" s="20" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="242" s="20" customFormat="1" ht="16.5" spans="1:13">
       <c r="A242" s="104">
         <v>51007</v>
       </c>
@@ -10992,7 +11493,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="243" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="243" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A243" s="8">
         <v>53001</v>
       </c>
@@ -11025,7 +11526,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="244" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="244" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A244" s="8">
         <v>53002</v>
       </c>
@@ -11058,7 +11559,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="245" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="245" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A245" s="8">
         <v>53003</v>
       </c>
@@ -11091,7 +11592,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="246" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="246" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A246" s="8">
         <v>53004</v>
       </c>
@@ -11124,7 +11625,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="247" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="247" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A247" s="8">
         <v>53005</v>
       </c>
@@ -11157,7 +11658,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="248" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="248" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A248" s="8">
         <v>53006</v>
       </c>
@@ -11190,7 +11691,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="249" spans="1:13" s="8" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="249" s="8" customFormat="1" ht="16.5" spans="1:13">
       <c r="A249" s="8">
         <v>53007</v>
       </c>
@@ -11223,7 +11724,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="250" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="250" ht="16.5" spans="1:13">
       <c r="A250" s="95">
         <v>54001</v>
       </c>
@@ -11255,7 +11756,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="251" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="251" ht="16.5" spans="1:13">
       <c r="A251" s="95">
         <v>54002</v>
       </c>
@@ -11287,7 +11788,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="252" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="252" ht="16.5" spans="1:13">
       <c r="A252" s="95">
         <v>54003</v>
       </c>
@@ -11319,7 +11820,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="253" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="253" ht="16.5" spans="1:13">
       <c r="A253" s="95">
         <v>54004</v>
       </c>
@@ -11351,7 +11852,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="254" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="254" ht="16.5" spans="1:13">
       <c r="A254" s="95">
         <v>54005</v>
       </c>
@@ -11383,7 +11884,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="255" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="255" ht="16.5" spans="1:13">
       <c r="A255" s="95">
         <v>54006</v>
       </c>
@@ -11415,7 +11916,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="256" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="256" ht="16.5" spans="1:13">
       <c r="A256" s="95">
         <v>54007</v>
       </c>
@@ -11447,7 +11948,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="257" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="257" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A257" s="109">
         <v>57001</v>
       </c>
@@ -11480,7 +11981,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="258" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="258" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A258" s="109">
         <v>57002</v>
       </c>
@@ -11513,7 +12014,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="259" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="259" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A259" s="109">
         <v>57003</v>
       </c>
@@ -11546,7 +12047,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="260" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="260" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A260" s="109">
         <v>57004</v>
       </c>
@@ -11579,7 +12080,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="261" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="261" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A261" s="109">
         <v>57005</v>
       </c>
@@ -11612,7 +12113,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="262" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="262" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A262" s="109">
         <v>57006</v>
       </c>
@@ -11645,7 +12146,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="263" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="263" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A263" s="109">
         <v>57007</v>
       </c>
@@ -11678,7 +12179,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="264" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="264" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A264" s="21">
         <v>58001</v>
       </c>
@@ -11708,7 +12209,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="265" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="265" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A265" s="21">
         <v>58002</v>
       </c>
@@ -11738,7 +12239,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="266" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="266" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A266" s="21">
         <v>58003</v>
       </c>
@@ -11768,7 +12269,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="267" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="267" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A267" s="21">
         <v>58004</v>
       </c>
@@ -11798,7 +12299,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="268" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="268" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A268" s="21">
         <v>58005</v>
       </c>
@@ -11828,7 +12329,7 @@
         <v>-250</v>
       </c>
     </row>
-    <row r="269" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="269" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A269" s="21">
         <v>58006</v>
       </c>
@@ -11858,7 +12359,7 @@
         <v>-600</v>
       </c>
     </row>
-    <row r="270" spans="1:13" s="21" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="270" s="21" customFormat="1" ht="16.5" spans="1:13">
       <c r="A270" s="21">
         <v>58007</v>
       </c>
@@ -11888,7 +12389,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="271" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="271" ht="16.5" spans="1:13">
       <c r="A271" s="116">
         <v>55001</v>
       </c>
@@ -11921,7 +12422,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="272" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="272" ht="16.5" spans="1:13">
       <c r="A272" s="116">
         <v>55002</v>
       </c>
@@ -11955,7 +12456,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="273" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="273" ht="16.5" spans="1:13">
       <c r="A273" s="116">
         <v>55003</v>
       </c>
@@ -11989,7 +12490,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="274" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="274" ht="16.5" spans="1:13">
       <c r="A274" s="116">
         <v>55004</v>
       </c>
@@ -12023,7 +12524,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="275" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="275" ht="16.5" spans="1:13">
       <c r="A275" s="116">
         <v>55005</v>
       </c>
@@ -12057,7 +12558,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="276" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="276" ht="16.5" spans="1:13">
       <c r="A276" s="116">
         <v>55006</v>
       </c>
@@ -12091,7 +12592,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="277" ht="16.5" spans="1:13">
       <c r="A277" s="116">
         <v>55007</v>
       </c>
@@ -12125,7 +12626,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="278" ht="16.5" spans="1:13">
       <c r="A278" s="116">
         <v>55011</v>
       </c>
@@ -12158,7 +12659,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="279" ht="16.5" spans="1:13">
       <c r="A279" s="116">
         <v>55012</v>
       </c>
@@ -12191,7 +12692,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="280" ht="16.5" spans="1:13">
       <c r="A280" s="116">
         <v>55013</v>
       </c>
@@ -12224,7 +12725,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="281" ht="16.5" spans="1:13">
       <c r="A281" s="116">
         <v>55014</v>
       </c>
@@ -12257,7 +12758,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="282" ht="16.5" spans="1:13">
       <c r="A282" s="116">
         <v>55015</v>
       </c>
@@ -12290,7 +12791,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="283" ht="16.5" spans="1:13">
       <c r="A283" s="116">
         <v>55016</v>
       </c>
@@ -12323,7 +12824,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="284" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="284" ht="16.5" spans="1:13">
       <c r="A284" s="116">
         <v>55017</v>
       </c>
@@ -12356,7 +12857,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="285" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="285" s="22" customFormat="1" ht="16.5" spans="1:13">
       <c r="A285" s="119">
         <v>55021</v>
       </c>
@@ -12389,7 +12890,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="286" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="286" s="22" customFormat="1" ht="16.5" spans="1:13">
       <c r="A286" s="119">
         <v>55022</v>
       </c>
@@ -12422,7 +12923,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="287" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="287" s="22" customFormat="1" ht="16.5" spans="1:13">
       <c r="A287" s="119">
         <v>55023</v>
       </c>
@@ -12455,7 +12956,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="288" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="288" s="22" customFormat="1" ht="16.5" spans="1:13">
       <c r="A288" s="119">
         <v>55024</v>
       </c>
@@ -12488,7 +12989,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="289" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="289" s="22" customFormat="1" ht="16.5" spans="1:13">
       <c r="A289" s="119">
         <v>55025</v>
       </c>
@@ -12521,7 +13022,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="290" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="290" s="22" customFormat="1" ht="16.5" spans="1:13">
       <c r="A290" s="119">
         <v>55026</v>
       </c>
@@ -12554,7 +13055,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="291" spans="1:13" s="22" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="291" s="22" customFormat="1" ht="16.5" spans="1:13">
       <c r="A291" s="119">
         <v>55027</v>
       </c>
@@ -12588,8 +13089,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -246,7 +246,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="295">
   <si>
     <t>id</t>
   </si>
@@ -989,16 +989,10 @@
     <t>10倍金牛</t>
   </si>
   <si>
-    <t>1_9320|2_630|3_50</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_9425|2_525|3_50</t>
-  </si>
-  <si>
-    <t>1_9530|2_420|3_50</t>
+    <t>1,0&amp;1-48900|1&amp;10-19700|10&amp;20-12100|20&amp;30-7600|30&amp;40-2000|40&amp;50-2000|50&amp;60-2400|60&amp;70-1000|70&amp;80-400|80&amp;90-200|90&amp;100-100|100&amp;120-100|120&amp;140-300|140&amp;160-300|160&amp;180-100|180&amp;200-0|200&amp;240-900|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-21500|10&amp;20-20200|20&amp;30-22000|30&amp;40-8800|40&amp;50-4500|50&amp;60-4400|60&amp;70-3600|70&amp;80-3500|80&amp;90-1000|90&amp;100-1200|100&amp;120-3300|120&amp;140-1000|140&amp;160-2000|160&amp;180-200|180&amp;200-400|200&amp;240-800|240&amp;280-600|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-38300|40&amp;50-0|50&amp;60-38600|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-19300|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-3800|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9830|2_120|3_50</t>
   </si>
   <si>
     <t>愤怒的小鸡</t>
@@ -9591,14 +9585,14 @@
         <v>1</v>
       </c>
       <c r="E187" s="88" t="s">
-        <v>247</v>
+        <v>141</v>
       </c>
       <c r="F187" s="88"/>
       <c r="G187" s="88"/>
       <c r="H187" s="88"/>
       <c r="I187" s="26"/>
-      <c r="J187" s="89" t="s">
-        <v>248</v>
+      <c r="J187" s="28" t="s">
+        <v>247</v>
       </c>
       <c r="K187" s="29">
         <v>1000</v>
@@ -9624,7 +9618,7 @@
         <v>2</v>
       </c>
       <c r="E188" s="88" t="s">
-        <v>249</v>
+        <v>180</v>
       </c>
       <c r="F188" s="88"/>
       <c r="G188" s="88"/>
@@ -9632,7 +9626,7 @@
       <c r="I188" s="26"/>
       <c r="J188" s="89" t="str">
         <f t="shared" ref="J188:J193" si="4">J187</f>
-        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-48900|1&amp;10-19700|10&amp;20-12100|20&amp;30-7600|30&amp;40-2000|40&amp;50-2000|50&amp;60-2400|60&amp;70-1000|70&amp;80-400|80&amp;90-200|90&amp;100-100|100&amp;120-100|120&amp;140-300|140&amp;160-300|160&amp;180-100|180&amp;200-0|200&amp;240-900|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-21500|10&amp;20-20200|20&amp;30-22000|30&amp;40-8800|40&amp;50-4500|50&amp;60-4400|60&amp;70-3600|70&amp;80-3500|80&amp;90-1000|90&amp;100-1200|100&amp;120-3300|120&amp;140-1000|140&amp;160-2000|160&amp;180-200|180&amp;200-400|200&amp;240-800|240&amp;280-600|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-38300|40&amp;50-0|50&amp;60-38600|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-19300|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-3800|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="K188" s="29">
         <v>600</v>
@@ -9658,7 +9652,7 @@
         <v>3</v>
       </c>
       <c r="E189" s="88" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
       <c r="F189" s="88"/>
       <c r="G189" s="88"/>
@@ -9666,7 +9660,7 @@
       <c r="I189" s="26"/>
       <c r="J189" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-48900|1&amp;10-19700|10&amp;20-12100|20&amp;30-7600|30&amp;40-2000|40&amp;50-2000|50&amp;60-2400|60&amp;70-1000|70&amp;80-400|80&amp;90-200|90&amp;100-100|100&amp;120-100|120&amp;140-300|140&amp;160-300|160&amp;180-100|180&amp;200-0|200&amp;240-900|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-21500|10&amp;20-20200|20&amp;30-22000|30&amp;40-8800|40&amp;50-4500|50&amp;60-4400|60&amp;70-3600|70&amp;80-3500|80&amp;90-1000|90&amp;100-1200|100&amp;120-3300|120&amp;140-1000|140&amp;160-2000|160&amp;180-200|180&amp;200-400|200&amp;240-800|240&amp;280-600|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-38300|40&amp;50-0|50&amp;60-38600|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-19300|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-3800|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="K189" s="29">
         <v>250</v>
@@ -9692,7 +9686,7 @@
         <v>4</v>
       </c>
       <c r="E190" s="88" t="s">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="F190" s="88"/>
       <c r="G190" s="88"/>
@@ -9700,7 +9694,7 @@
       <c r="I190" s="26"/>
       <c r="J190" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-48900|1&amp;10-19700|10&amp;20-12100|20&amp;30-7600|30&amp;40-2000|40&amp;50-2000|50&amp;60-2400|60&amp;70-1000|70&amp;80-400|80&amp;90-200|90&amp;100-100|100&amp;120-100|120&amp;140-300|140&amp;160-300|160&amp;180-100|180&amp;200-0|200&amp;240-900|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-21500|10&amp;20-20200|20&amp;30-22000|30&amp;40-8800|40&amp;50-4500|50&amp;60-4400|60&amp;70-3600|70&amp;80-3500|80&amp;90-1000|90&amp;100-1200|100&amp;120-3300|120&amp;140-1000|140&amp;160-2000|160&amp;180-200|180&amp;200-400|200&amp;240-800|240&amp;280-600|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-38300|40&amp;50-0|50&amp;60-38600|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-19300|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-3800|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="K190" s="29">
         <v>-250</v>
@@ -9726,7 +9720,7 @@
         <v>5</v>
       </c>
       <c r="E191" s="88" t="s">
-        <v>219</v>
+        <v>102</v>
       </c>
       <c r="F191" s="88"/>
       <c r="G191" s="88"/>
@@ -9734,7 +9728,7 @@
       <c r="I191" s="26"/>
       <c r="J191" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-48900|1&amp;10-19700|10&amp;20-12100|20&amp;30-7600|30&amp;40-2000|40&amp;50-2000|50&amp;60-2400|60&amp;70-1000|70&amp;80-400|80&amp;90-200|90&amp;100-100|100&amp;120-100|120&amp;140-300|140&amp;160-300|160&amp;180-100|180&amp;200-0|200&amp;240-900|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-21500|10&amp;20-20200|20&amp;30-22000|30&amp;40-8800|40&amp;50-4500|50&amp;60-4400|60&amp;70-3600|70&amp;80-3500|80&amp;90-1000|90&amp;100-1200|100&amp;120-3300|120&amp;140-1000|140&amp;160-2000|160&amp;180-200|180&amp;200-400|200&amp;240-800|240&amp;280-600|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-38300|40&amp;50-0|50&amp;60-38600|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-19300|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-3800|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="K191" s="29">
         <v>-600</v>
@@ -9760,7 +9754,7 @@
         <v>6</v>
       </c>
       <c r="E192" s="88" t="s">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="F192" s="88"/>
       <c r="G192" s="88"/>
@@ -9768,7 +9762,7 @@
       <c r="I192" s="26"/>
       <c r="J192" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-48900|1&amp;10-19700|10&amp;20-12100|20&amp;30-7600|30&amp;40-2000|40&amp;50-2000|50&amp;60-2400|60&amp;70-1000|70&amp;80-400|80&amp;90-200|90&amp;100-100|100&amp;120-100|120&amp;140-300|140&amp;160-300|160&amp;180-100|180&amp;200-0|200&amp;240-900|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-21500|10&amp;20-20200|20&amp;30-22000|30&amp;40-8800|40&amp;50-4500|50&amp;60-4400|60&amp;70-3600|70&amp;80-3500|80&amp;90-1000|90&amp;100-1200|100&amp;120-3300|120&amp;140-1000|140&amp;160-2000|160&amp;180-200|180&amp;200-400|200&amp;240-800|240&amp;280-600|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-38300|40&amp;50-0|50&amp;60-38600|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-19300|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-3800|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="K192" s="29">
         <v>-1000</v>
@@ -9802,7 +9796,7 @@
       <c r="I193" s="26"/>
       <c r="J193" s="89" t="str">
         <f t="shared" si="4"/>
-        <v>1,0&amp;1-24000|1&amp;25-11000|25&amp;50-8000|50&amp;75-8000|75&amp;100-8000|100&amp;125-8000|125&amp;150-6000|150&amp;175-6000|175&amp;200-5000|200&amp;225-5000|225&amp;250-4000|250&amp;300-4000|300&amp;350-3000|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-60000|1000&amp;1200-40000|1200&amp;1400-10000|1400&amp;1600-20000|1600&amp;1800-60000|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-10300|1&amp;25-800|25&amp;50-1600|50&amp;75-800|75&amp;100-1000|100&amp;125-1200|125&amp;150-600|150&amp;175-1200|175&amp;200-300|200&amp;225-200|225&amp;250-100|250&amp;300-500|300&amp;350-300|350&amp;400-300|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</v>
+        <v>1,0&amp;1-48900|1&amp;10-19700|10&amp;20-12100|20&amp;30-7600|30&amp;40-2000|40&amp;50-2000|50&amp;60-2400|60&amp;70-1000|70&amp;80-400|80&amp;90-200|90&amp;100-100|100&amp;120-100|120&amp;140-300|140&amp;160-300|160&amp;180-100|180&amp;200-0|200&amp;240-900|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-21500|10&amp;20-20200|20&amp;30-22000|30&amp;40-8800|40&amp;50-4500|50&amp;60-4400|60&amp;70-3600|70&amp;80-3500|80&amp;90-1000|90&amp;100-1200|100&amp;120-3300|120&amp;140-1000|140&amp;160-2000|160&amp;180-200|180&amp;200-400|200&amp;240-800|240&amp;280-600|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-38300|40&amp;50-0|50&amp;60-38600|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-19300|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-3800|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</v>
       </c>
       <c r="K193" s="29">
         <v>-999999</v>
@@ -9822,20 +9816,20 @@
         <v>103900</v>
       </c>
       <c r="C194" s="95" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D194" s="95">
         <v>1</v>
       </c>
       <c r="E194" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F194" s="36"/>
       <c r="G194" s="36"/>
       <c r="H194" s="36"/>
       <c r="I194" s="26"/>
       <c r="J194" s="38" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="K194" s="29">
         <v>1000</v>
@@ -9855,13 +9849,13 @@
         <v>103900</v>
       </c>
       <c r="C195" s="95" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D195" s="95">
         <v>2</v>
       </c>
       <c r="E195" s="36" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F195" s="36"/>
       <c r="G195" s="36"/>
@@ -9889,13 +9883,13 @@
         <v>103900</v>
       </c>
       <c r="C196" s="95" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D196" s="95">
         <v>3</v>
       </c>
       <c r="E196" s="36" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F196" s="36"/>
       <c r="G196" s="36"/>
@@ -9923,13 +9917,13 @@
         <v>103900</v>
       </c>
       <c r="C197" s="95" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D197" s="95">
         <v>4</v>
       </c>
       <c r="E197" s="36" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F197" s="36"/>
       <c r="G197" s="36"/>
@@ -9957,13 +9951,13 @@
         <v>103900</v>
       </c>
       <c r="C198" s="95" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D198" s="95">
         <v>5</v>
       </c>
       <c r="E198" s="36" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F198" s="36"/>
       <c r="G198" s="36"/>
@@ -9991,13 +9985,13 @@
         <v>103900</v>
       </c>
       <c r="C199" s="95" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D199" s="95">
         <v>6</v>
       </c>
       <c r="E199" s="36" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F199" s="36"/>
       <c r="G199" s="36"/>
@@ -10025,13 +10019,13 @@
         <v>103900</v>
       </c>
       <c r="C200" s="95" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D200" s="95">
         <v>7</v>
       </c>
       <c r="E200" s="36" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F200" s="36"/>
       <c r="G200" s="36"/>
@@ -10059,28 +10053,28 @@
         <v>104000</v>
       </c>
       <c r="C201" s="77" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D201" s="77">
         <v>1</v>
       </c>
       <c r="E201" s="78" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F201" s="78" t="s">
         <v>48</v>
       </c>
       <c r="G201" s="78" t="s">
+        <v>260</v>
+      </c>
+      <c r="H201" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="I201" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="H201" s="78" t="s">
+      <c r="J201" s="79" t="s">
         <v>263</v>
-      </c>
-      <c r="I201" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="J201" s="79" t="s">
-        <v>265</v>
       </c>
       <c r="K201" s="29">
         <v>1000</v>
@@ -10100,28 +10094,28 @@
         <v>104000</v>
       </c>
       <c r="C202" s="77" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D202" s="77">
         <v>2</v>
       </c>
       <c r="E202" s="78" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F202" s="78" t="s">
         <v>48</v>
       </c>
       <c r="G202" s="78" t="s">
+        <v>260</v>
+      </c>
+      <c r="H202" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="I202" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="H202" s="78" t="s">
+      <c r="J202" s="79" t="s">
         <v>263</v>
-      </c>
-      <c r="I202" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="J202" s="79" t="s">
-        <v>265</v>
       </c>
       <c r="K202" s="29">
         <v>600</v>
@@ -10141,7 +10135,7 @@
         <v>104000</v>
       </c>
       <c r="C203" s="77" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D203" s="77">
         <v>3</v>
@@ -10153,16 +10147,16 @@
         <v>48</v>
       </c>
       <c r="G203" s="78" t="s">
+        <v>260</v>
+      </c>
+      <c r="H203" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="I203" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="H203" s="78" t="s">
+      <c r="J203" s="79" t="s">
         <v>263</v>
-      </c>
-      <c r="I203" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="J203" s="79" t="s">
-        <v>265</v>
       </c>
       <c r="K203" s="29">
         <v>250</v>
@@ -10182,7 +10176,7 @@
         <v>104000</v>
       </c>
       <c r="C204" s="77" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D204" s="77">
         <v>4</v>
@@ -10194,16 +10188,16 @@
         <v>48</v>
       </c>
       <c r="G204" s="78" t="s">
+        <v>260</v>
+      </c>
+      <c r="H204" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="I204" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="H204" s="78" t="s">
+      <c r="J204" s="79" t="s">
         <v>263</v>
-      </c>
-      <c r="I204" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="J204" s="79" t="s">
-        <v>265</v>
       </c>
       <c r="K204" s="29">
         <v>-250</v>
@@ -10223,7 +10217,7 @@
         <v>104000</v>
       </c>
       <c r="C205" s="77" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D205" s="77">
         <v>5</v>
@@ -10235,16 +10229,16 @@
         <v>48</v>
       </c>
       <c r="G205" s="78" t="s">
+        <v>260</v>
+      </c>
+      <c r="H205" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="I205" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="H205" s="78" t="s">
+      <c r="J205" s="79" t="s">
         <v>263</v>
-      </c>
-      <c r="I205" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="J205" s="79" t="s">
-        <v>265</v>
       </c>
       <c r="K205" s="29">
         <v>-600</v>
@@ -10264,7 +10258,7 @@
         <v>104000</v>
       </c>
       <c r="C206" s="77" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D206" s="77">
         <v>6</v>
@@ -10276,16 +10270,16 @@
         <v>48</v>
       </c>
       <c r="G206" s="78" t="s">
+        <v>260</v>
+      </c>
+      <c r="H206" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="I206" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="H206" s="78" t="s">
+      <c r="J206" s="79" t="s">
         <v>263</v>
-      </c>
-      <c r="I206" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="J206" s="79" t="s">
-        <v>265</v>
       </c>
       <c r="K206" s="29">
         <v>-1000</v>
@@ -10305,7 +10299,7 @@
         <v>104000</v>
       </c>
       <c r="C207" s="77" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D207" s="77">
         <v>7</v>
@@ -10317,16 +10311,16 @@
         <v>48</v>
       </c>
       <c r="G207" s="78" t="s">
+        <v>260</v>
+      </c>
+      <c r="H207" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="I207" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="H207" s="78" t="s">
+      <c r="J207" s="79" t="s">
         <v>263</v>
-      </c>
-      <c r="I207" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="J207" s="79" t="s">
-        <v>265</v>
       </c>
       <c r="K207" s="29">
         <v>-999999</v>
@@ -10346,7 +10340,7 @@
         <v>104100</v>
       </c>
       <c r="C208" s="96" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D208" s="96">
         <v>1</v>
@@ -10379,7 +10373,7 @@
         <v>104100</v>
       </c>
       <c r="C209" s="96" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D209" s="96">
         <v>2</v>
@@ -10412,7 +10406,7 @@
         <v>104100</v>
       </c>
       <c r="C210" s="96" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D210" s="96">
         <v>3</v>
@@ -10445,7 +10439,7 @@
         <v>104100</v>
       </c>
       <c r="C211" s="96" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D211" s="96">
         <v>4</v>
@@ -10478,7 +10472,7 @@
         <v>104100</v>
       </c>
       <c r="C212" s="96" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D212" s="96">
         <v>5</v>
@@ -10511,7 +10505,7 @@
         <v>104100</v>
       </c>
       <c r="C213" s="96" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D213" s="96">
         <v>6</v>
@@ -10544,7 +10538,7 @@
         <v>104100</v>
       </c>
       <c r="C214" s="96" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D214" s="96">
         <v>7</v>
@@ -10577,7 +10571,7 @@
         <v>104200</v>
       </c>
       <c r="C215" s="100" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D215" s="100">
         <v>1</v>
@@ -10610,7 +10604,7 @@
         <v>104200</v>
       </c>
       <c r="C216" s="100" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D216" s="100">
         <v>2</v>
@@ -10643,7 +10637,7 @@
         <v>104200</v>
       </c>
       <c r="C217" s="100" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D217" s="100">
         <v>3</v>
@@ -10676,7 +10670,7 @@
         <v>104200</v>
       </c>
       <c r="C218" s="100" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D218" s="100">
         <v>4</v>
@@ -10709,7 +10703,7 @@
         <v>104200</v>
       </c>
       <c r="C219" s="100" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D219" s="100">
         <v>5</v>
@@ -10742,7 +10736,7 @@
         <v>104200</v>
       </c>
       <c r="C220" s="100" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D220" s="100">
         <v>6</v>
@@ -10775,7 +10769,7 @@
         <v>104200</v>
       </c>
       <c r="C221" s="100" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D221" s="100">
         <v>7</v>
@@ -10808,7 +10802,7 @@
         <v>104800</v>
       </c>
       <c r="C222" s="95" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D222" s="95">
         <v>1</v>
@@ -10841,7 +10835,7 @@
         <v>104800</v>
       </c>
       <c r="C223" s="95" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D223" s="95">
         <v>2</v>
@@ -10874,7 +10868,7 @@
         <v>104800</v>
       </c>
       <c r="C224" s="95" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D224" s="95">
         <v>3</v>
@@ -10907,7 +10901,7 @@
         <v>104800</v>
       </c>
       <c r="C225" s="95" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D225" s="95">
         <v>4</v>
@@ -10940,7 +10934,7 @@
         <v>104800</v>
       </c>
       <c r="C226" s="95" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D226" s="95">
         <v>5</v>
@@ -10973,7 +10967,7 @@
         <v>104800</v>
       </c>
       <c r="C227" s="95" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D227" s="95">
         <v>6</v>
@@ -11006,7 +11000,7 @@
         <v>104800</v>
       </c>
       <c r="C228" s="95" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D228" s="95">
         <v>7</v>
@@ -11039,7 +11033,7 @@
         <v>105000</v>
       </c>
       <c r="C229" s="87" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D229" s="87">
         <v>1</v>
@@ -11072,7 +11066,7 @@
         <v>105000</v>
       </c>
       <c r="C230" s="87" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D230" s="87">
         <v>2</v>
@@ -11105,7 +11099,7 @@
         <v>105000</v>
       </c>
       <c r="C231" s="87" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D231" s="87">
         <v>3</v>
@@ -11138,7 +11132,7 @@
         <v>105000</v>
       </c>
       <c r="C232" s="87" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D232" s="87">
         <v>4</v>
@@ -11171,7 +11165,7 @@
         <v>105000</v>
       </c>
       <c r="C233" s="87" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D233" s="87">
         <v>5</v>
@@ -11204,7 +11198,7 @@
         <v>105000</v>
       </c>
       <c r="C234" s="87" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D234" s="87">
         <v>6</v>
@@ -11237,7 +11231,7 @@
         <v>105000</v>
       </c>
       <c r="C235" s="87" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D235" s="87">
         <v>7</v>
@@ -11270,20 +11264,20 @@
         <v>105100</v>
       </c>
       <c r="C236" s="104" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D236" s="104">
         <v>1</v>
       </c>
       <c r="E236" s="105" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F236" s="105"/>
       <c r="G236" s="105"/>
       <c r="H236" s="105"/>
       <c r="I236" s="26"/>
       <c r="J236" s="106" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K236" s="29">
         <v>1000</v>
@@ -11303,20 +11297,20 @@
         <v>105100</v>
       </c>
       <c r="C237" s="104" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D237" s="104">
         <v>2</v>
       </c>
       <c r="E237" s="105" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F237" s="105"/>
       <c r="G237" s="105"/>
       <c r="H237" s="105"/>
       <c r="I237" s="26"/>
       <c r="J237" s="106" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K237" s="29">
         <v>600</v>
@@ -11336,20 +11330,20 @@
         <v>105100</v>
       </c>
       <c r="C238" s="104" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D238" s="104">
         <v>3</v>
       </c>
       <c r="E238" s="105" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F238" s="105"/>
       <c r="G238" s="105"/>
       <c r="H238" s="105"/>
       <c r="I238" s="26"/>
       <c r="J238" s="106" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K238" s="29">
         <v>250</v>
@@ -11369,20 +11363,20 @@
         <v>105100</v>
       </c>
       <c r="C239" s="104" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D239" s="104">
         <v>4</v>
       </c>
       <c r="E239" s="105" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F239" s="105"/>
       <c r="G239" s="105"/>
       <c r="H239" s="105"/>
       <c r="I239" s="26"/>
       <c r="J239" s="106" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K239" s="29">
         <v>-250</v>
@@ -11402,20 +11396,20 @@
         <v>105100</v>
       </c>
       <c r="C240" s="104" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D240" s="104">
         <v>5</v>
       </c>
       <c r="E240" s="105" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F240" s="105"/>
       <c r="G240" s="105"/>
       <c r="H240" s="105"/>
       <c r="I240" s="26"/>
       <c r="J240" s="106" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K240" s="29">
         <v>-600</v>
@@ -11435,20 +11429,20 @@
         <v>105100</v>
       </c>
       <c r="C241" s="104" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D241" s="104">
         <v>6</v>
       </c>
       <c r="E241" s="105" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F241" s="105"/>
       <c r="G241" s="105"/>
       <c r="H241" s="105"/>
       <c r="I241" s="26"/>
       <c r="J241" s="106" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K241" s="29">
         <v>-1000</v>
@@ -11468,20 +11462,20 @@
         <v>105100</v>
       </c>
       <c r="C242" s="104" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D242" s="104">
         <v>7</v>
       </c>
       <c r="E242" s="105" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F242" s="105"/>
       <c r="G242" s="105"/>
       <c r="H242" s="105"/>
       <c r="I242" s="26"/>
       <c r="J242" s="106" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K242" s="29">
         <v>-999999</v>
@@ -11501,20 +11495,20 @@
         <v>105300</v>
       </c>
       <c r="C243" s="53" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D243" s="31">
         <v>1</v>
       </c>
       <c r="E243" s="32" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F243" s="32"/>
       <c r="G243" s="32"/>
       <c r="H243" s="32"/>
       <c r="I243" s="54"/>
       <c r="J243" s="108" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K243" s="29">
         <v>1000</v>
@@ -11534,20 +11528,20 @@
         <v>105300</v>
       </c>
       <c r="C244" s="53" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D244" s="31">
         <v>2</v>
       </c>
       <c r="E244" s="32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F244" s="32"/>
       <c r="G244" s="32"/>
       <c r="H244" s="32"/>
       <c r="I244" s="54"/>
       <c r="J244" s="32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K244" s="29">
         <v>600</v>
@@ -11567,20 +11561,20 @@
         <v>105300</v>
       </c>
       <c r="C245" s="53" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D245" s="31">
         <v>3</v>
       </c>
       <c r="E245" s="32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F245" s="32"/>
       <c r="G245" s="32"/>
       <c r="H245" s="32"/>
       <c r="I245" s="54"/>
       <c r="J245" s="32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K245" s="29">
         <v>250</v>
@@ -11600,20 +11594,20 @@
         <v>105300</v>
       </c>
       <c r="C246" s="53" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D246" s="31">
         <v>4</v>
       </c>
       <c r="E246" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F246" s="32"/>
       <c r="G246" s="32"/>
       <c r="H246" s="32"/>
       <c r="I246" s="54"/>
       <c r="J246" s="32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K246" s="29">
         <v>-250</v>
@@ -11633,20 +11627,20 @@
         <v>105300</v>
       </c>
       <c r="C247" s="53" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D247" s="31">
         <v>5</v>
       </c>
       <c r="E247" s="32" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F247" s="32"/>
       <c r="G247" s="32"/>
       <c r="H247" s="32"/>
       <c r="I247" s="54"/>
       <c r="J247" s="32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K247" s="29">
         <v>-600</v>
@@ -11666,20 +11660,20 @@
         <v>105300</v>
       </c>
       <c r="C248" s="53" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D248" s="31">
         <v>6</v>
       </c>
       <c r="E248" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F248" s="32"/>
       <c r="G248" s="32"/>
       <c r="H248" s="32"/>
       <c r="I248" s="54"/>
       <c r="J248" s="32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K248" s="29">
         <v>-1000</v>
@@ -11699,20 +11693,20 @@
         <v>105300</v>
       </c>
       <c r="C249" s="53" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D249" s="31">
         <v>7</v>
       </c>
       <c r="E249" s="32" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F249" s="32"/>
       <c r="G249" s="32"/>
       <c r="H249" s="32"/>
       <c r="I249" s="54"/>
       <c r="J249" s="32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K249" s="29">
         <v>-999999</v>
@@ -11732,7 +11726,7 @@
         <v>105400</v>
       </c>
       <c r="C250" s="95" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D250" s="95">
         <v>1</v>
@@ -11764,7 +11758,7 @@
         <v>105400</v>
       </c>
       <c r="C251" s="95" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D251" s="95">
         <v>2</v>
@@ -11796,7 +11790,7 @@
         <v>105400</v>
       </c>
       <c r="C252" s="95" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D252" s="95">
         <v>3</v>
@@ -11828,7 +11822,7 @@
         <v>105400</v>
       </c>
       <c r="C253" s="95" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D253" s="95">
         <v>4</v>
@@ -11860,7 +11854,7 @@
         <v>105400</v>
       </c>
       <c r="C254" s="95" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D254" s="95">
         <v>5</v>
@@ -11892,7 +11886,7 @@
         <v>105400</v>
       </c>
       <c r="C255" s="95" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D255" s="95">
         <v>6</v>
@@ -11924,7 +11918,7 @@
         <v>105400</v>
       </c>
       <c r="C256" s="95" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D256" s="95">
         <v>7</v>
@@ -11956,7 +11950,7 @@
         <v>105700</v>
       </c>
       <c r="C257" s="110" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D257" s="111">
         <v>1</v>
@@ -11989,7 +11983,7 @@
         <v>105700</v>
       </c>
       <c r="C258" s="110" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D258" s="111">
         <v>2</v>
@@ -12022,7 +12016,7 @@
         <v>105700</v>
       </c>
       <c r="C259" s="110" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D259" s="111">
         <v>3</v>
@@ -12055,7 +12049,7 @@
         <v>105700</v>
       </c>
       <c r="C260" s="110" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D260" s="111">
         <v>4</v>
@@ -12088,7 +12082,7 @@
         <v>105700</v>
       </c>
       <c r="C261" s="110" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D261" s="111">
         <v>5</v>
@@ -12121,7 +12115,7 @@
         <v>105700</v>
       </c>
       <c r="C262" s="110" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D262" s="111">
         <v>6</v>
@@ -12154,7 +12148,7 @@
         <v>105700</v>
       </c>
       <c r="C263" s="110" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D263" s="111">
         <v>7</v>
@@ -12187,20 +12181,20 @@
         <v>105800</v>
       </c>
       <c r="C264" s="115" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D264" s="115">
         <v>1</v>
       </c>
       <c r="E264" s="26" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F264" s="26"/>
       <c r="G264" s="26"/>
       <c r="H264" s="26"/>
       <c r="I264" s="113"/>
       <c r="J264" s="28" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K264" s="29">
         <v>1000</v>
@@ -12217,20 +12211,20 @@
         <v>105800</v>
       </c>
       <c r="C265" s="115" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D265" s="115">
         <v>2</v>
       </c>
       <c r="E265" s="26" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F265" s="26"/>
       <c r="G265" s="26"/>
       <c r="H265" s="26"/>
       <c r="I265" s="113"/>
       <c r="J265" s="26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K265" s="29">
         <v>600</v>
@@ -12247,20 +12241,20 @@
         <v>105800</v>
       </c>
       <c r="C266" s="115" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D266" s="115">
         <v>3</v>
       </c>
       <c r="E266" s="26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F266" s="26"/>
       <c r="G266" s="26"/>
       <c r="H266" s="26"/>
       <c r="I266" s="113"/>
       <c r="J266" s="26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K266" s="29">
         <v>250</v>
@@ -12277,20 +12271,20 @@
         <v>105800</v>
       </c>
       <c r="C267" s="115" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D267" s="115">
         <v>4</v>
       </c>
       <c r="E267" s="26" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F267" s="26"/>
       <c r="G267" s="26"/>
       <c r="H267" s="26"/>
       <c r="I267" s="113"/>
       <c r="J267" s="26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K267" s="29">
         <v>-250</v>
@@ -12307,20 +12301,20 @@
         <v>105800</v>
       </c>
       <c r="C268" s="115" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D268" s="115">
         <v>5</v>
       </c>
       <c r="E268" s="26" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F268" s="26"/>
       <c r="G268" s="26"/>
       <c r="H268" s="26"/>
       <c r="I268" s="113"/>
       <c r="J268" s="26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K268" s="29">
         <v>-600</v>
@@ -12337,20 +12331,20 @@
         <v>105800</v>
       </c>
       <c r="C269" s="115" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D269" s="115">
         <v>6</v>
       </c>
       <c r="E269" s="26" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F269" s="26"/>
       <c r="G269" s="26"/>
       <c r="H269" s="26"/>
       <c r="I269" s="113"/>
       <c r="J269" s="26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K269" s="29">
         <v>-1000</v>
@@ -12367,20 +12361,20 @@
         <v>105800</v>
       </c>
       <c r="C270" s="115" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D270" s="115">
         <v>7</v>
       </c>
       <c r="E270" s="26" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F270" s="26"/>
       <c r="G270" s="26"/>
       <c r="H270" s="26"/>
       <c r="I270" s="113"/>
       <c r="J270" s="26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K270" s="29">
         <v>-999999</v>
@@ -12397,20 +12391,20 @@
         <v>105500</v>
       </c>
       <c r="C271" s="117" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D271" s="74">
         <v>1</v>
       </c>
       <c r="E271" s="75" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F271" s="75"/>
       <c r="G271" s="75"/>
       <c r="H271" s="75"/>
       <c r="I271" s="113"/>
       <c r="J271" s="89" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K271" s="29">
         <v>1000</v>
@@ -12430,13 +12424,13 @@
         <v>105500</v>
       </c>
       <c r="C272" s="117" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D272" s="74">
         <v>2</v>
       </c>
       <c r="E272" s="75" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F272" s="75"/>
       <c r="G272" s="75"/>
@@ -12464,13 +12458,13 @@
         <v>105500</v>
       </c>
       <c r="C273" s="117" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D273" s="74">
         <v>3</v>
       </c>
       <c r="E273" s="75" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F273" s="75"/>
       <c r="G273" s="75"/>
@@ -12498,13 +12492,13 @@
         <v>105500</v>
       </c>
       <c r="C274" s="117" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D274" s="74">
         <v>4</v>
       </c>
       <c r="E274" s="75" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F274" s="75"/>
       <c r="G274" s="75"/>
@@ -12532,13 +12526,13 @@
         <v>105500</v>
       </c>
       <c r="C275" s="117" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D275" s="74">
         <v>5</v>
       </c>
       <c r="E275" s="75" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F275" s="75"/>
       <c r="G275" s="75"/>
@@ -12566,13 +12560,13 @@
         <v>105500</v>
       </c>
       <c r="C276" s="117" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D276" s="74">
         <v>6</v>
       </c>
       <c r="E276" s="75" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F276" s="75"/>
       <c r="G276" s="75"/>
@@ -12600,13 +12594,13 @@
         <v>105500</v>
       </c>
       <c r="C277" s="117" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D277" s="74">
         <v>7</v>
       </c>
       <c r="E277" s="75" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F277" s="75"/>
       <c r="G277" s="75"/>
@@ -12634,7 +12628,7 @@
         <v>105501</v>
       </c>
       <c r="C278" s="117" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D278" s="74">
         <v>1</v>
@@ -12647,7 +12641,7 @@
       <c r="H278" s="112"/>
       <c r="I278" s="113"/>
       <c r="J278" s="89" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K278" s="29">
         <v>1000</v>
@@ -12667,7 +12661,7 @@
         <v>105501</v>
       </c>
       <c r="C279" s="117" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D279" s="74">
         <v>2</v>
@@ -12680,7 +12674,7 @@
       <c r="H279" s="112"/>
       <c r="I279" s="113"/>
       <c r="J279" s="89" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K279" s="29">
         <v>600</v>
@@ -12700,7 +12694,7 @@
         <v>105501</v>
       </c>
       <c r="C280" s="117" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D280" s="74">
         <v>3</v>
@@ -12713,7 +12707,7 @@
       <c r="H280" s="112"/>
       <c r="I280" s="113"/>
       <c r="J280" s="89" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K280" s="29">
         <v>250</v>
@@ -12733,7 +12727,7 @@
         <v>105501</v>
       </c>
       <c r="C281" s="117" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D281" s="74">
         <v>4</v>
@@ -12746,7 +12740,7 @@
       <c r="H281" s="112"/>
       <c r="I281" s="113"/>
       <c r="J281" s="89" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K281" s="29">
         <v>-250</v>
@@ -12766,7 +12760,7 @@
         <v>105501</v>
       </c>
       <c r="C282" s="117" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D282" s="74">
         <v>5</v>
@@ -12779,7 +12773,7 @@
       <c r="H282" s="112"/>
       <c r="I282" s="113"/>
       <c r="J282" s="89" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K282" s="29">
         <v>-600</v>
@@ -12799,7 +12793,7 @@
         <v>105501</v>
       </c>
       <c r="C283" s="117" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D283" s="74">
         <v>6</v>
@@ -12812,7 +12806,7 @@
       <c r="H283" s="112"/>
       <c r="I283" s="113"/>
       <c r="J283" s="89" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K283" s="29">
         <v>-1000</v>
@@ -12832,7 +12826,7 @@
         <v>105501</v>
       </c>
       <c r="C284" s="117" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D284" s="74">
         <v>7</v>
@@ -12845,7 +12839,7 @@
       <c r="H284" s="112"/>
       <c r="I284" s="113"/>
       <c r="J284" s="89" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K284" s="29">
         <v>-999999</v>
@@ -12865,7 +12859,7 @@
         <v>105502</v>
       </c>
       <c r="C285" s="120" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D285" s="120">
         <v>1</v>
@@ -12878,7 +12872,7 @@
       <c r="H285" s="85"/>
       <c r="I285" s="85"/>
       <c r="J285" s="121" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K285" s="29">
         <v>1000</v>
@@ -12898,7 +12892,7 @@
         <v>105502</v>
       </c>
       <c r="C286" s="120" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D286" s="120">
         <v>2</v>
@@ -12911,7 +12905,7 @@
       <c r="H286" s="85"/>
       <c r="I286" s="85"/>
       <c r="J286" s="121" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K286" s="29">
         <v>600</v>
@@ -12931,7 +12925,7 @@
         <v>105502</v>
       </c>
       <c r="C287" s="120" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D287" s="120">
         <v>3</v>
@@ -12944,7 +12938,7 @@
       <c r="H287" s="85"/>
       <c r="I287" s="85"/>
       <c r="J287" s="121" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K287" s="29">
         <v>250</v>
@@ -12964,7 +12958,7 @@
         <v>105502</v>
       </c>
       <c r="C288" s="120" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D288" s="120">
         <v>4</v>
@@ -12977,7 +12971,7 @@
       <c r="H288" s="85"/>
       <c r="I288" s="85"/>
       <c r="J288" s="121" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K288" s="29">
         <v>-250</v>
@@ -12997,7 +12991,7 @@
         <v>105502</v>
       </c>
       <c r="C289" s="120" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D289" s="120">
         <v>5</v>
@@ -13010,7 +13004,7 @@
       <c r="H289" s="85"/>
       <c r="I289" s="85"/>
       <c r="J289" s="121" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K289" s="29">
         <v>-600</v>
@@ -13030,7 +13024,7 @@
         <v>105502</v>
       </c>
       <c r="C290" s="120" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D290" s="120">
         <v>6</v>
@@ -13043,7 +13037,7 @@
       <c r="H290" s="85"/>
       <c r="I290" s="85"/>
       <c r="J290" s="121" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K290" s="29">
         <v>-1000</v>
@@ -13063,7 +13057,7 @@
         <v>105502</v>
       </c>
       <c r="C291" s="120" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D291" s="120">
         <v>7</v>
@@ -13076,7 +13070,7 @@
       <c r="H291" s="85"/>
       <c r="I291" s="85"/>
       <c r="J291" s="121" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K291" s="29">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -12641,7 +12641,7 @@
       <c r="H278" s="112"/>
       <c r="I278" s="113"/>
       <c r="J278" s="89" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="K278" s="29">
         <v>1000</v>
@@ -12872,7 +12872,7 @@
       <c r="H285" s="85"/>
       <c r="I285" s="85"/>
       <c r="J285" s="121" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="K285" s="29">
         <v>1000</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SpecialResultLib" sheetId="1" r:id="rId1"/>
@@ -395,7 +395,7 @@
     <t>1,1&amp;0-20000</t>
   </si>
   <si>
-    <t>30,1&amp;0-20000|2-7000|3-1800|4-0|5-0#70,1&amp;0-40000|3-3000|4-500|5-0</t>
+    <t>4,1&amp;0-69999#5,1&amp;0-0|1-0|2-0|4-0|5-0</t>
   </si>
   <si>
     <t>5,1&amp;0-20000|2-0|3-0|4-0|5-0#8,1&amp;0-8000|2-0|3-0|4-0|5-0#10,1&amp;0-0|2-0|3-0|4-0|5-0</t>
@@ -1308,12 +1308,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -395,7 +395,7 @@
     <t>1,1&amp;0-20000</t>
   </si>
   <si>
-    <t>30,1&amp;0-20000|2-7000|3-1800|4-0|5-0#70,1&amp;0-40000|3-3000|4-500|5-0</t>
+    <t>4,1&amp;0-69999#5,1&amp;0-0|1-0|2-0|4-0|5-0</t>
   </si>
   <si>
     <t>5,1&amp;0-20000|2-0|3-0|4-0|5-0#8,1&amp;0-8000|2-0|3-0|4-0|5-0#10,1&amp;0-0|2-0|3-0|4-0|5-0</t>
@@ -1308,12 +1308,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -12641,7 +12641,7 @@
       <c r="H278" s="112"/>
       <c r="I278" s="113"/>
       <c r="J278" s="89" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="K278" s="29">
         <v>1000</v>
@@ -12872,7 +12872,7 @@
       <c r="H285" s="85"/>
       <c r="I285" s="85"/>
       <c r="J285" s="121" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="K285" s="29">
         <v>1000</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -830,7 +830,7 @@
     <t>1_9590|2_200|3_200|4_10</t>
   </si>
   <si>
-    <t>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</t>
+    <t>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-1000|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</t>
   </si>
   <si>
     <t>1_9660|2_170|3_170|4_10</t>
@@ -1308,12 +1308,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -7751,7 +7751,7 @@
       <c r="I139" s="26"/>
       <c r="J139" s="72" t="str">
         <f t="shared" ref="J139:J144" si="3">J138</f>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-1000|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
       </c>
       <c r="K139" s="29">
         <v>600</v>
@@ -7785,7 +7785,7 @@
       <c r="I140" s="26"/>
       <c r="J140" s="72" t="str">
         <f t="shared" si="3"/>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-1000|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
       </c>
       <c r="K140" s="29">
         <v>250</v>
@@ -7819,7 +7819,7 @@
       <c r="I141" s="26"/>
       <c r="J141" s="72" t="str">
         <f t="shared" si="3"/>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-1000|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
       </c>
       <c r="K141" s="29">
         <v>-250</v>
@@ -7853,7 +7853,7 @@
       <c r="I142" s="26"/>
       <c r="J142" s="72" t="str">
         <f t="shared" si="3"/>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-1000|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
       </c>
       <c r="K142" s="29">
         <v>-600</v>
@@ -7887,7 +7887,7 @@
       <c r="I143" s="26"/>
       <c r="J143" s="72" t="str">
         <f t="shared" si="3"/>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-1000|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
       </c>
       <c r="K143" s="29">
         <v>-1000</v>
@@ -7921,7 +7921,7 @@
       <c r="I144" s="26"/>
       <c r="J144" s="72" t="str">
         <f t="shared" si="3"/>
-        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
+        <v>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-1000|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</v>
       </c>
       <c r="K144" s="29">
         <v>-999999</v>

--- a/slots/resources/sample/SpecialResultLib.xlsx
+++ b/slots/resources/sample/SpecialResultLib.xlsx
@@ -246,7 +246,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="304">
   <si>
     <t>id</t>
   </si>
@@ -587,6 +587,9 @@
     <t>热血足球</t>
   </si>
   <si>
+    <t>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-1000|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-0|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-1000|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
     <t>圣诞狂欢夜</t>
   </si>
   <si>
@@ -827,28 +830,28 @@
     <t>绿巨人</t>
   </si>
   <si>
-    <t>1_9590|2_200|3_200|4_10</t>
-  </si>
-  <si>
-    <t>1,0&amp;1-74400|1&amp;25-8800|25&amp;50-6800|50&amp;75-3500|75&amp;100-1800|100&amp;125-900|125&amp;150-800|150&amp;175-500|175&amp;200-500|200&amp;225-300|225&amp;250-200|250&amp;300-500|300&amp;350-200|350&amp;400-200|400&amp;450-100|450&amp;500-100|500&amp;600-200|600&amp;700-100|700&amp;800-100|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-3700|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-100|1&amp;25-100|25&amp;50-100|50&amp;75-300|75&amp;100-300|100&amp;125-400|125&amp;150-400|150&amp;175-500|175&amp;200-400|200&amp;225-600|225&amp;250-500|250&amp;300-1200|300&amp;350-1400|350&amp;400-1500|400&amp;450-1800|450&amp;500-1700|500&amp;600-3600|600&amp;700-3700|700&amp;800-3800|800&amp;900-1000|900&amp;1000-1000|1000&amp;1200-1000|1200&amp;1400-1000|1400&amp;1600-1000|1600&amp;1800-1000|1800&amp;2000-1000|2000&amp;2400-1000|2400&amp;2800-1000|2800&amp;3200-1000|3200&amp;3600-1000|3600&amp;4000-1000|4000&amp;4800-1000|4800&amp;5600-1000|5600&amp;6400-100|6400&amp;7200-1000|7200&amp;8000-1000|8000&amp;9250-1000|9250&amp;10500-1000|10500&amp;99999999-1000</t>
-  </si>
-  <si>
-    <t>1_9660|2_170|3_170|4_10</t>
-  </si>
-  <si>
-    <t>1_9740|2_130|3_130|4_10</t>
-  </si>
-  <si>
-    <t>1_9810|2_95|3_95|4_10</t>
-  </si>
-  <si>
-    <t>1_9860|2_70|3_70|4_10</t>
-  </si>
-  <si>
-    <t>1_9910|2_45|3_45|4_10</t>
-  </si>
-  <si>
-    <t>1_9960|2_20|3_20|4_10</t>
+    <t>1_9630|2_100|3_100|4_10|5_150|6_10</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-57600|1&amp;25-26200|25&amp;50-9100|50&amp;75-3600|75&amp;100-1500|100&amp;125-1000|125&amp;150-300|150&amp;175-200|175&amp;200-100|200&amp;225-100|225&amp;250-100|250&amp;300-100|300&amp;350-0|350&amp;400-0|400&amp;450-100|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;2,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-400|350&amp;400-900|400&amp;450-1600|450&amp;500-2200|500&amp;600-6100|600&amp;700-7600|700&amp;800-8500|800&amp;900-800|900&amp;1000-700|1000&amp;1200-300|1200&amp;1400-200|1400&amp;1600-100|1600&amp;1800-100|1800&amp;2000-50|2000&amp;2400-50|2400&amp;2800-30|2800&amp;3200-30|3200&amp;3600-20|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;3,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-900|125&amp;150-1800|150&amp;175-3000|175&amp;200-2600|200&amp;225-4900|225&amp;250-2800|250&amp;300-8000|300&amp;350-9600|350&amp;400-10200|400&amp;450-6900|450&amp;500-9300|500&amp;600-12600|600&amp;700-11900|700&amp;800-5600|800&amp;900-400|900&amp;1000-300|1000&amp;1200-200|1200&amp;1400-100|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;4,0&amp;1-81100|1&amp;25-16200|25&amp;50-2000|50&amp;75-400|75&amp;100-100|100&amp;125-100|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-0|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;5,0&amp;1-6600|1&amp;25-6800|25&amp;50-11000|50&amp;75-14200|75&amp;100-12300|100&amp;125-11500|125&amp;150-8400|150&amp;175-7100|175&amp;200-5100|200&amp;225-4100|225&amp;250-2800|250&amp;300-3900|300&amp;350-2300|350&amp;400-1300|400&amp;450-800|450&amp;500-500|500&amp;600-500|600&amp;700-300|700&amp;800-0|800&amp;900-0|900&amp;1000-0|1000&amp;1200-0|1200&amp;1400-0|1400&amp;1600-0|1600&amp;1800-0|1800&amp;2000-0|2000&amp;2400-0|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0;6,0&amp;1-0|1&amp;25-0|25&amp;50-0|50&amp;75-0|75&amp;100-0|100&amp;125-0|125&amp;150-0|150&amp;175-0|175&amp;200-0|200&amp;225-0|225&amp;250-0|250&amp;300-0|300&amp;350-0|350&amp;400-0|400&amp;450-0|450&amp;500-0|500&amp;600-0|600&amp;700-3000|700&amp;800-2700|800&amp;900-6500|900&amp;1000-2000|1000&amp;1200-3000|1200&amp;1400-2000|1400&amp;1600-100|1600&amp;1800-20|1800&amp;2000-20|2000&amp;2400-10|2400&amp;2800-0|2800&amp;3200-0|3200&amp;3600-0|3600&amp;4000-0|4000&amp;4800-0|4800&amp;5600-0|5600&amp;6400-0|6400&amp;7200-0|7200&amp;8000-0|8000&amp;9250-0|9250&amp;10500-0|10500&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9682|2_90|3_90|4_10|5_120|6_8</t>
+  </si>
+  <si>
+    <t>1_9744|2_70|3_70|4_10|5_100|6_6</t>
+  </si>
+  <si>
+    <t>1_9822|2_45|3_50|4_10|5_70|6_3</t>
+  </si>
+  <si>
+    <t>1_9868|2_30|3_30|4_10|5_60|6_2</t>
+  </si>
+  <si>
+    <t>1_9939|2_20|3_20|4_10|5_10|6_1</t>
+  </si>
+  <si>
+    <t>1_9970|2_10|3_10|4_0|5_10|6_0</t>
   </si>
   <si>
     <t>神马飞扬</t>
@@ -989,10 +992,10 @@
     <t>10倍金牛</t>
   </si>
   <si>
-    <t>1,0&amp;1-48900|1&amp;10-19700|10&amp;20-12100|20&amp;30-7600|30&amp;40-2000|40&amp;50-2000|50&amp;60-2400|60&amp;70-1000|70&amp;80-400|80&amp;90-200|90&amp;100-100|100&amp;120-100|120&amp;140-300|140&amp;160-300|160&amp;180-100|180&amp;200-0|200&amp;240-900|240&amp;280-200|280&amp;320-100|320&amp;360-100|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-21500|10&amp;20-20200|20&amp;30-22000|30&amp;40-8800|40&amp;50-4500|50&amp;60-4400|60&amp;70-3600|70&amp;80-3500|80&amp;90-1000|90&amp;100-1200|100&amp;120-3300|120&amp;140-1000|140&amp;160-2000|160&amp;180-200|180&amp;200-400|200&amp;240-800|240&amp;280-600|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-38300|40&amp;50-0|50&amp;60-38600|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-19300|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-3800|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</t>
-  </si>
-  <si>
-    <t>1_9830|2_120|3_50</t>
+    <t>1_9550|2_400|3_50</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-49000|1&amp;10-19700|10&amp;20-12000|20&amp;30-7600|30&amp;40-2000|40&amp;50-2000|50&amp;60-1500|60&amp;70-500|70&amp;80-400|80&amp;90-200|90&amp;100-100|100&amp;120-500|120&amp;140-200|140&amp;160-200|160&amp;180-100|180&amp;200-0|200&amp;240-50|240&amp;280-20|280&amp;320-10|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;2,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-8500|40&amp;50-4400|50&amp;60-4300|60&amp;70-3600|70&amp;80-3400|80&amp;90-1000|90&amp;100-1300|100&amp;120-3200|120&amp;140-900|140&amp;160-1000|160&amp;180-100|180&amp;200-200|200&amp;240-400|240&amp;280-300|280&amp;320-200|320&amp;360-100|360&amp;400-0|400&amp;480-20|480&amp;560-10|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0;3,0&amp;1-0|1&amp;10-0|10&amp;20-0|20&amp;30-0|30&amp;40-38100|40&amp;50-0|50&amp;60-38400|60&amp;70-0|70&amp;80-0|80&amp;90-0|90&amp;100-0|100&amp;120-19600|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-3900|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3700-0|3700&amp;4200-0|4200&amp;99999999-0</t>
   </si>
   <si>
     <t>愤怒的小鸡</t>
@@ -1131,6 +1134,30 @@
   </si>
   <si>
     <t>伽罗宝石3</t>
+  </si>
+  <si>
+    <t>德古拉</t>
+  </si>
+  <si>
+    <t>1_9650|2_150|3_150|4_50</t>
+  </si>
+  <si>
+    <t>1,0&amp;1-55600|1&amp;20-27600|20&amp;40-4900|40&amp;60-2700|60&amp;80-600|80&amp;100-2500|100&amp;120-500|120&amp;140-400|140&amp;160-100|160&amp;180-1500|180&amp;200-200|200&amp;240-600|240&amp;280-400|280&amp;320-100|320&amp;360-600|360&amp;400-100|400&amp;480-600|480&amp;560-200|560&amp;640-100|640&amp;720-100|720&amp;800-0|800&amp;960-300|960&amp;1120-100|1120&amp;1280-100|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-100|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-200|1&amp;20-4900|20&amp;40-6400|40&amp;60-6100|60&amp;80-5000|80&amp;100-4700|100&amp;120-4100|120&amp;140-3500|140&amp;160-2900|160&amp;180-2900|180&amp;200-2900|200&amp;240-4800|240&amp;280-4100|280&amp;320-3300|320&amp;360-3100|360&amp;400-2500|400&amp;480-4900|480&amp;560-4300|560&amp;640-3600|640&amp;720-3300|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-1000|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-0|1&amp;20-1000|20&amp;40-1000|40&amp;60-1000|60&amp;80-1000|80&amp;100-1000|100&amp;120-1000|120&amp;140-1000|140&amp;160-1000|160&amp;180-1000|180&amp;200-1000|200&amp;240-1000|240&amp;280-200|280&amp;320-600|320&amp;360-1400|360&amp;400-2600|400&amp;480-10200|480&amp;560-17000|560&amp;640-20100|640&amp;720-18000|720&amp;800-12900|800&amp;960-12700|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;4,0&amp;1-0|1&amp;20-90000|20&amp;40-0|40&amp;60-7000|60&amp;80-0|80&amp;100-2000|100&amp;120-0|120&amp;140-0|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-1000|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</t>
+  </si>
+  <si>
+    <t>1_9710|2_120|3_120|4_50</t>
+  </si>
+  <si>
+    <t>1_9750|2_100|3_100|4_50</t>
+  </si>
+  <si>
+    <t>1_9790|2_80|3_80|4_50</t>
+  </si>
+  <si>
+    <t>1_9880|2_60|3_60|4_0</t>
+  </si>
+  <si>
+    <t>1_9900|2_50|3_50|4_0</t>
   </si>
 </sst>
 </file>
@@ -1308,12 +1335,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2475,7 +2502,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M291"/>
+  <dimension ref="A1:M304"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
@@ -4493,7 +4520,7 @@
       <c r="H54" s="47"/>
       <c r="I54" s="26"/>
       <c r="J54" s="48" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="K54" s="29">
         <v>1000</v>
@@ -4525,8 +4552,9 @@
       <c r="G55" s="47"/>
       <c r="H55" s="47"/>
       <c r="I55" s="26"/>
-      <c r="J55" s="48" t="s">
-        <v>73</v>
+      <c r="J55" s="48" t="str">
+        <f t="shared" ref="J55:J60" si="0">J54</f>
+        <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-1000|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-0|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-1000|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="K55" s="29">
         <v>600</v>
@@ -4558,8 +4586,9 @@
       <c r="G56" s="47"/>
       <c r="H56" s="47"/>
       <c r="I56" s="26"/>
-      <c r="J56" s="48" t="s">
-        <v>73</v>
+      <c r="J56" s="48" t="str">
+        <f t="shared" si="0"/>
+        <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-1000|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-0|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-1000|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="K56" s="29">
         <v>250</v>
@@ -4591,8 +4620,9 @@
       <c r="G57" s="47"/>
       <c r="H57" s="47"/>
       <c r="I57" s="26"/>
-      <c r="J57" s="48" t="s">
-        <v>73</v>
+      <c r="J57" s="48" t="str">
+        <f t="shared" si="0"/>
+        <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-1000|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-0|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-1000|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="K57" s="29">
         <v>-250</v>
@@ -4624,8 +4654,9 @@
       <c r="G58" s="47"/>
       <c r="H58" s="47"/>
       <c r="I58" s="26"/>
-      <c r="J58" s="48" t="s">
-        <v>73</v>
+      <c r="J58" s="48" t="str">
+        <f t="shared" si="0"/>
+        <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-1000|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-0|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-1000|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="K58" s="29">
         <v>-600</v>
@@ -4657,8 +4688,9 @@
       <c r="G59" s="47"/>
       <c r="H59" s="47"/>
       <c r="I59" s="26"/>
-      <c r="J59" s="48" t="s">
-        <v>73</v>
+      <c r="J59" s="48" t="str">
+        <f t="shared" si="0"/>
+        <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-1000|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-0|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-1000|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="K59" s="29">
         <v>-1000</v>
@@ -4690,8 +4722,9 @@
       <c r="G60" s="47"/>
       <c r="H60" s="47"/>
       <c r="I60" s="26"/>
-      <c r="J60" s="48" t="s">
-        <v>73</v>
+      <c r="J60" s="48" t="str">
+        <f t="shared" si="0"/>
+        <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-1000|360&amp;400-1000|400&amp;480-1000|480&amp;560-1000|560&amp;640-1000|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-0|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-1000|800&amp;960-1000|960&amp;1120-1000|1120&amp;1280-1000|1280&amp;1440-1000|1440&amp;1600-1000|1600&amp;1920-1000|1920&amp;2240-1000|2240&amp;2560-1000|2560&amp;2880-1000|2880&amp;3200-1000|3200&amp;3840-1000|3840&amp;4480-1000|4480&amp;5120-1000|5120&amp;5760-1000|5760&amp;6400-1000|6400&amp;7400-1000|7400&amp;8400-1000|8400&amp;99999999-1000;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="K60" s="29">
         <v>-999999</v>
@@ -4711,28 +4744,28 @@
         <v>101700</v>
       </c>
       <c r="C61" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D61" s="31">
         <v>1</v>
       </c>
       <c r="E61" s="32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F61" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G61" s="33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H61" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I61" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J61" s="28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K61" s="29">
         <v>1000</v>
@@ -4752,28 +4785,28 @@
         <v>101700</v>
       </c>
       <c r="C62" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D62" s="31">
         <v>2</v>
       </c>
       <c r="E62" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="F62" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="G62" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="H62" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="I62" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="J62" s="34" t="s">
         <v>120</v>
-      </c>
-      <c r="F62" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="G62" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="H62" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="I62" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="J62" s="34" t="s">
-        <v>119</v>
       </c>
       <c r="K62" s="29">
         <v>600</v>
@@ -4793,28 +4826,28 @@
         <v>101700</v>
       </c>
       <c r="C63" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D63" s="31">
         <v>3</v>
       </c>
       <c r="E63" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F63" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="G63" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F63" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="G63" s="33" t="s">
-        <v>121</v>
-      </c>
       <c r="H63" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I63" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J63" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K63" s="29">
         <v>250</v>
@@ -4834,28 +4867,28 @@
         <v>101700</v>
       </c>
       <c r="C64" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D64" s="31">
         <v>4</v>
       </c>
       <c r="E64" s="32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F64" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G64" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H64" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I64" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J64" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K64" s="29">
         <v>-250</v>
@@ -4875,28 +4908,28 @@
         <v>101700</v>
       </c>
       <c r="C65" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D65" s="31">
         <v>5</v>
       </c>
       <c r="E65" s="32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F65" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G65" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H65" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I65" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J65" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K65" s="29">
         <v>-600</v>
@@ -4916,28 +4949,28 @@
         <v>101700</v>
       </c>
       <c r="C66" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D66" s="31">
         <v>6</v>
       </c>
       <c r="E66" s="32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F66" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G66" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H66" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I66" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J66" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K66" s="29">
         <v>-1000</v>
@@ -4957,7 +4990,7 @@
         <v>101700</v>
       </c>
       <c r="C67" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D67" s="31">
         <v>7</v>
@@ -4966,19 +4999,19 @@
         <v>57</v>
       </c>
       <c r="F67" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G67" s="33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H67" s="33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I67" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J67" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K67" s="29">
         <v>-999999</v>
@@ -4998,28 +5031,28 @@
         <v>101800</v>
       </c>
       <c r="C68" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D68" s="50">
         <v>1</v>
       </c>
       <c r="E68" s="51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F68" s="51" t="s">
         <v>48</v>
       </c>
       <c r="G68" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H68" s="51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I68" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J68" s="28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K68" s="29">
         <v>1000</v>
@@ -5039,28 +5072,28 @@
         <v>101800</v>
       </c>
       <c r="C69" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D69" s="50">
         <v>2</v>
       </c>
       <c r="E69" s="51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F69" s="51" t="s">
         <v>48</v>
       </c>
       <c r="G69" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H69" s="51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I69" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J69" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K69" s="29">
         <v>600</v>
@@ -5080,28 +5113,28 @@
         <v>101800</v>
       </c>
       <c r="C70" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D70" s="50">
         <v>3</v>
       </c>
       <c r="E70" s="51" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F70" s="51" t="s">
         <v>48</v>
       </c>
       <c r="G70" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H70" s="51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I70" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J70" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K70" s="29">
         <v>250</v>
@@ -5121,28 +5154,28 @@
         <v>101800</v>
       </c>
       <c r="C71" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D71" s="50">
         <v>4</v>
       </c>
       <c r="E71" s="51" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F71" s="51" t="s">
         <v>48</v>
       </c>
       <c r="G71" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H71" s="51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I71" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J71" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K71" s="29">
         <v>-250</v>
@@ -5162,28 +5195,28 @@
         <v>101800</v>
       </c>
       <c r="C72" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D72" s="50">
         <v>5</v>
       </c>
       <c r="E72" s="51" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F72" s="51" t="s">
         <v>48</v>
       </c>
       <c r="G72" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H72" s="51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I72" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J72" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K72" s="29">
         <v>-600</v>
@@ -5203,28 +5236,28 @@
         <v>101800</v>
       </c>
       <c r="C73" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D73" s="50">
         <v>6</v>
       </c>
       <c r="E73" s="51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F73" s="51" t="s">
         <v>48</v>
       </c>
       <c r="G73" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H73" s="51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I73" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J73" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K73" s="29">
         <v>-1000</v>
@@ -5244,7 +5277,7 @@
         <v>101800</v>
       </c>
       <c r="C74" s="50" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D74" s="50">
         <v>7</v>
@@ -5256,16 +5289,16 @@
         <v>48</v>
       </c>
       <c r="G74" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H74" s="51" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I74" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J74" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K74" s="29">
         <v>-999999</v>
@@ -5285,28 +5318,28 @@
         <v>102000</v>
       </c>
       <c r="C75" s="42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D75" s="42">
         <v>1</v>
       </c>
       <c r="E75" s="43" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F75" s="43" t="s">
         <v>60</v>
       </c>
       <c r="G75" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H75" s="43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I75" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J75" s="44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K75" s="29">
         <v>1000</v>
@@ -5326,28 +5359,28 @@
         <v>102000</v>
       </c>
       <c r="C76" s="42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D76" s="42">
         <v>2</v>
       </c>
       <c r="E76" s="43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F76" s="43" t="s">
         <v>60</v>
       </c>
       <c r="G76" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H76" s="43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I76" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J76" s="44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K76" s="29">
         <v>600</v>
@@ -5367,28 +5400,28 @@
         <v>102000</v>
       </c>
       <c r="C77" s="42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D77" s="42">
         <v>3</v>
       </c>
       <c r="E77" s="43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F77" s="43" t="s">
         <v>60</v>
       </c>
       <c r="G77" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H77" s="43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I77" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J77" s="44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K77" s="29">
         <v>250</v>
@@ -5408,28 +5441,28 @@
         <v>102000</v>
       </c>
       <c r="C78" s="42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D78" s="42">
         <v>4</v>
       </c>
       <c r="E78" s="43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F78" s="43" t="s">
         <v>60</v>
       </c>
       <c r="G78" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H78" s="43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I78" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J78" s="44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K78" s="29">
         <v>-250</v>
@@ -5449,28 +5482,28 @@
         <v>102000</v>
       </c>
       <c r="C79" s="42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D79" s="42">
         <v>5</v>
       </c>
       <c r="E79" s="43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F79" s="43" t="s">
         <v>60</v>
       </c>
       <c r="G79" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H79" s="43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I79" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J79" s="44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K79" s="29">
         <v>-600</v>
@@ -5490,28 +5523,28 @@
         <v>102000</v>
       </c>
       <c r="C80" s="42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D80" s="42">
         <v>6</v>
       </c>
       <c r="E80" s="43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F80" s="43" t="s">
         <v>60</v>
       </c>
       <c r="G80" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H80" s="43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I80" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J80" s="44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K80" s="29">
         <v>-1000</v>
@@ -5531,7 +5564,7 @@
         <v>102000</v>
       </c>
       <c r="C81" s="42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D81" s="42">
         <v>7</v>
@@ -5543,16 +5576,16 @@
         <v>60</v>
       </c>
       <c r="G81" s="43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H81" s="43" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I81" s="26" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J81" s="44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K81" s="29">
         <v>-999999</v>
@@ -5572,28 +5605,28 @@
         <v>102100</v>
       </c>
       <c r="C82" s="53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D82" s="53">
         <v>1</v>
       </c>
       <c r="E82" s="54" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F82" s="54" t="s">
         <v>60</v>
       </c>
       <c r="G82" s="55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H82" s="55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I82" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J82" s="28" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K82" s="29">
         <v>1000</v>
@@ -5613,28 +5646,28 @@
         <v>102100</v>
       </c>
       <c r="C83" s="53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D83" s="53">
         <v>2</v>
       </c>
       <c r="E83" s="54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F83" s="54" t="s">
         <v>60</v>
       </c>
       <c r="G83" s="55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H83" s="55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J83" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K83" s="29">
         <v>600</v>
@@ -5654,28 +5687,28 @@
         <v>102100</v>
       </c>
       <c r="C84" s="53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D84" s="53">
         <v>3</v>
       </c>
       <c r="E84" s="54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F84" s="54" t="s">
         <v>60</v>
       </c>
       <c r="G84" s="55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H84" s="55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J84" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K84" s="29">
         <v>250</v>
@@ -5695,28 +5728,28 @@
         <v>102100</v>
       </c>
       <c r="C85" s="53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D85" s="53">
         <v>4</v>
       </c>
       <c r="E85" s="54" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F85" s="54" t="s">
         <v>60</v>
       </c>
       <c r="G85" s="55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H85" s="55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I85" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J85" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K85" s="29">
         <v>-250</v>
@@ -5736,28 +5769,28 @@
         <v>102100</v>
       </c>
       <c r="C86" s="53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D86" s="53">
         <v>5</v>
       </c>
       <c r="E86" s="54" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F86" s="54" t="s">
         <v>60</v>
       </c>
       <c r="G86" s="55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H86" s="55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I86" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J86" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K86" s="29">
         <v>-600</v>
@@ -5777,28 +5810,28 @@
         <v>102100</v>
       </c>
       <c r="C87" s="53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D87" s="53">
         <v>6</v>
       </c>
       <c r="E87" s="54" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F87" s="54" t="s">
         <v>60</v>
       </c>
       <c r="G87" s="55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H87" s="55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I87" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J87" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K87" s="29">
         <v>-1000</v>
@@ -5818,28 +5851,28 @@
         <v>102100</v>
       </c>
       <c r="C88" s="53" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D88" s="53">
         <v>7</v>
       </c>
       <c r="E88" s="54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F88" s="54" t="s">
         <v>60</v>
       </c>
       <c r="G88" s="55" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H88" s="55" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I88" s="26" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J88" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K88" s="29">
         <v>-999999</v>
@@ -5859,28 +5892,28 @@
         <v>102200</v>
       </c>
       <c r="C89" s="56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D89" s="56">
         <v>1</v>
       </c>
       <c r="E89" s="57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F89" s="57" t="s">
         <v>48</v>
       </c>
       <c r="G89" s="58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H89" s="58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I89" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J89" s="28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K89" s="29">
         <v>1000</v>
@@ -5900,28 +5933,28 @@
         <v>102200</v>
       </c>
       <c r="C90" s="56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D90" s="56">
         <v>2</v>
       </c>
       <c r="E90" s="57" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F90" s="57" t="s">
         <v>48</v>
       </c>
       <c r="G90" s="58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H90" s="58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I90" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J90" s="59" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K90" s="29">
         <v>600</v>
@@ -5941,28 +5974,28 @@
         <v>102200</v>
       </c>
       <c r="C91" s="56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D91" s="56">
         <v>3</v>
       </c>
       <c r="E91" s="57" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F91" s="57" t="s">
         <v>48</v>
       </c>
       <c r="G91" s="58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H91" s="58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I91" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J91" s="59" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K91" s="29">
         <v>250</v>
@@ -5982,28 +6015,28 @@
         <v>102200</v>
       </c>
       <c r="C92" s="56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D92" s="56">
         <v>4</v>
       </c>
       <c r="E92" s="57" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F92" s="57" t="s">
         <v>48</v>
       </c>
       <c r="G92" s="58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H92" s="58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I92" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J92" s="59" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K92" s="29">
         <v>-250</v>
@@ -6023,28 +6056,28 @@
         <v>102200</v>
       </c>
       <c r="C93" s="56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D93" s="56">
         <v>5</v>
       </c>
       <c r="E93" s="57" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F93" s="57" t="s">
         <v>48</v>
       </c>
       <c r="G93" s="58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H93" s="58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I93" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J93" s="59" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K93" s="29">
         <v>-600</v>
@@ -6064,28 +6097,28 @@
         <v>102200</v>
       </c>
       <c r="C94" s="56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D94" s="56">
         <v>6</v>
       </c>
       <c r="E94" s="57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F94" s="57" t="s">
         <v>48</v>
       </c>
       <c r="G94" s="58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H94" s="58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I94" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J94" s="59" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K94" s="29">
         <v>-1000</v>
@@ -6105,7 +6138,7 @@
         <v>102200</v>
       </c>
       <c r="C95" s="56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D95" s="56">
         <v>7</v>
@@ -6117,16 +6150,16 @@
         <v>48</v>
       </c>
       <c r="G95" s="58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H95" s="58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I95" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J95" s="59" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K95" s="29">
         <v>-999999</v>
@@ -6146,7 +6179,7 @@
         <v>102300</v>
       </c>
       <c r="C96" s="60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D96" s="60">
         <v>1</v>
@@ -6155,19 +6188,19 @@
         <v>102</v>
       </c>
       <c r="F96" s="61" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G96" s="61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H96" s="61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I96" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J96" s="28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K96" s="29">
         <v>1000</v>
@@ -6187,28 +6220,28 @@
         <v>102300</v>
       </c>
       <c r="C97" s="60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D97" s="60">
         <v>2</v>
       </c>
       <c r="E97" s="61" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F97" s="61" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G97" s="61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H97" s="61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I97" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J97" s="62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K97" s="29">
         <v>600</v>
@@ -6228,28 +6261,28 @@
         <v>102300</v>
       </c>
       <c r="C98" s="60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D98" s="60">
         <v>3</v>
       </c>
       <c r="E98" s="61" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F98" s="61" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G98" s="61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H98" s="61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I98" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J98" s="62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K98" s="29">
         <v>250</v>
@@ -6269,28 +6302,28 @@
         <v>102300</v>
       </c>
       <c r="C99" s="60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D99" s="60">
         <v>4</v>
       </c>
       <c r="E99" s="61" t="s">
+        <v>172</v>
+      </c>
+      <c r="F99" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="G99" s="61" t="s">
+        <v>168</v>
+      </c>
+      <c r="H99" s="61" t="s">
+        <v>169</v>
+      </c>
+      <c r="I99" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="J99" s="62" t="s">
         <v>171</v>
-      </c>
-      <c r="F99" s="61" t="s">
-        <v>115</v>
-      </c>
-      <c r="G99" s="61" t="s">
-        <v>167</v>
-      </c>
-      <c r="H99" s="61" t="s">
-        <v>168</v>
-      </c>
-      <c r="I99" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="J99" s="62" t="s">
-        <v>170</v>
       </c>
       <c r="K99" s="29">
         <v>-250</v>
@@ -6310,28 +6343,28 @@
         <v>102300</v>
       </c>
       <c r="C100" s="60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D100" s="60">
         <v>5</v>
       </c>
       <c r="E100" s="61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F100" s="61" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G100" s="61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H100" s="61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I100" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J100" s="62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K100" s="29">
         <v>-600</v>
@@ -6351,28 +6384,28 @@
         <v>102300</v>
       </c>
       <c r="C101" s="60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D101" s="60">
         <v>6</v>
       </c>
       <c r="E101" s="61" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F101" s="61" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G101" s="61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H101" s="61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I101" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J101" s="62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K101" s="29">
         <v>-1000</v>
@@ -6392,28 +6425,28 @@
         <v>102300</v>
       </c>
       <c r="C102" s="60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D102" s="60">
         <v>7</v>
       </c>
       <c r="E102" s="61" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F102" s="61" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G102" s="61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H102" s="61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I102" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J102" s="62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K102" s="29">
         <v>-999999</v>
@@ -6433,7 +6466,7 @@
         <v>102400</v>
       </c>
       <c r="C103" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D103" s="24">
         <v>1</v>
@@ -6448,7 +6481,7 @@
         <v>30</v>
       </c>
       <c r="H103" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I103" s="26"/>
       <c r="J103" s="28" t="s">
@@ -6472,7 +6505,7 @@
         <v>102400</v>
       </c>
       <c r="C104" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D104" s="24">
         <v>2</v>
@@ -6487,7 +6520,7 @@
         <v>30</v>
       </c>
       <c r="H104" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I104" s="26"/>
       <c r="J104" s="26" t="s">
@@ -6511,7 +6544,7 @@
         <v>102400</v>
       </c>
       <c r="C105" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D105" s="24">
         <v>3</v>
@@ -6526,7 +6559,7 @@
         <v>30</v>
       </c>
       <c r="H105" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I105" s="26"/>
       <c r="J105" s="26" t="s">
@@ -6550,7 +6583,7 @@
         <v>102400</v>
       </c>
       <c r="C106" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D106" s="24">
         <v>4</v>
@@ -6565,7 +6598,7 @@
         <v>30</v>
       </c>
       <c r="H106" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I106" s="26"/>
       <c r="J106" s="26" t="s">
@@ -6589,7 +6622,7 @@
         <v>102400</v>
       </c>
       <c r="C107" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D107" s="24">
         <v>5</v>
@@ -6604,7 +6637,7 @@
         <v>30</v>
       </c>
       <c r="H107" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I107" s="26"/>
       <c r="J107" s="26" t="s">
@@ -6628,7 +6661,7 @@
         <v>102400</v>
       </c>
       <c r="C108" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D108" s="24">
         <v>6</v>
@@ -6643,7 +6676,7 @@
         <v>30</v>
       </c>
       <c r="H108" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I108" s="26"/>
       <c r="J108" s="26" t="s">
@@ -6667,7 +6700,7 @@
         <v>102400</v>
       </c>
       <c r="C109" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D109" s="24">
         <v>7</v>
@@ -6682,7 +6715,7 @@
         <v>30</v>
       </c>
       <c r="H109" s="26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I109" s="26"/>
       <c r="J109" s="26" t="s">
@@ -6706,28 +6739,28 @@
         <v>102500</v>
       </c>
       <c r="C110" s="63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D110" s="63">
         <v>1</v>
       </c>
       <c r="E110" s="64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F110" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G110" s="65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H110" s="65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I110" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J110" s="28" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K110" s="29">
         <v>1000</v>
@@ -6747,28 +6780,28 @@
         <v>102500</v>
       </c>
       <c r="C111" s="63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D111" s="63">
         <v>2</v>
       </c>
       <c r="E111" s="64" t="s">
+        <v>181</v>
+      </c>
+      <c r="F111" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="G111" s="65" t="s">
+        <v>178</v>
+      </c>
+      <c r="H111" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="I111" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="J111" s="66" t="s">
         <v>180</v>
-      </c>
-      <c r="F111" s="64" t="s">
-        <v>115</v>
-      </c>
-      <c r="G111" s="65" t="s">
-        <v>177</v>
-      </c>
-      <c r="H111" s="65" t="s">
-        <v>178</v>
-      </c>
-      <c r="I111" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="J111" s="66" t="s">
-        <v>179</v>
       </c>
       <c r="K111" s="29">
         <v>600</v>
@@ -6788,28 +6821,28 @@
         <v>102500</v>
       </c>
       <c r="C112" s="63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D112" s="63">
         <v>3</v>
       </c>
       <c r="E112" s="64" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F112" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G112" s="65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H112" s="65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I112" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J112" s="66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K112" s="29">
         <v>250</v>
@@ -6829,28 +6862,28 @@
         <v>102500</v>
       </c>
       <c r="C113" s="63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D113" s="63">
         <v>4</v>
       </c>
       <c r="E113" s="64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F113" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G113" s="65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H113" s="65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I113" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J113" s="66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K113" s="29">
         <v>-250</v>
@@ -6870,28 +6903,28 @@
         <v>102500</v>
       </c>
       <c r="C114" s="63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D114" s="63">
         <v>5</v>
       </c>
       <c r="E114" s="64" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F114" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G114" s="65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H114" s="65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I114" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J114" s="66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K114" s="29">
         <v>-600</v>
@@ -6911,28 +6944,28 @@
         <v>102500</v>
       </c>
       <c r="C115" s="63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D115" s="63">
         <v>6</v>
       </c>
       <c r="E115" s="64" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F115" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G115" s="65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H115" s="65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I115" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J115" s="66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K115" s="29">
         <v>-1000</v>
@@ -6952,7 +6985,7 @@
         <v>102500</v>
       </c>
       <c r="C116" s="63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D116" s="63">
         <v>7</v>
@@ -6961,19 +6994,19 @@
         <v>57</v>
       </c>
       <c r="F116" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G116" s="65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H116" s="65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I116" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J116" s="66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K116" s="29">
         <v>-999999</v>
@@ -6993,7 +7026,7 @@
         <v>102600</v>
       </c>
       <c r="C117" s="67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D117" s="67">
         <v>1</v>
@@ -7026,7 +7059,7 @@
         <v>102600</v>
       </c>
       <c r="C118" s="67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D118" s="67">
         <v>2</v>
@@ -7039,7 +7072,7 @@
       <c r="H118" s="68"/>
       <c r="I118" s="26"/>
       <c r="J118" s="69" t="str">
-        <f t="shared" ref="J118:J123" si="0">J117</f>
+        <f t="shared" ref="J118:J123" si="1">J117</f>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="K118" s="29">
@@ -7060,7 +7093,7 @@
         <v>102600</v>
       </c>
       <c r="C119" s="67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D119" s="67">
         <v>3</v>
@@ -7073,7 +7106,7 @@
       <c r="H119" s="68"/>
       <c r="I119" s="26"/>
       <c r="J119" s="69" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="K119" s="29">
@@ -7094,7 +7127,7 @@
         <v>102600</v>
       </c>
       <c r="C120" s="67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D120" s="67">
         <v>4</v>
@@ -7107,7 +7140,7 @@
       <c r="H120" s="68"/>
       <c r="I120" s="26"/>
       <c r="J120" s="69" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="K120" s="29">
@@ -7128,7 +7161,7 @@
         <v>102600</v>
       </c>
       <c r="C121" s="67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D121" s="67">
         <v>5</v>
@@ -7141,7 +7174,7 @@
       <c r="H121" s="68"/>
       <c r="I121" s="26"/>
       <c r="J121" s="69" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1,0&amp;1-70000|1&amp;20-25000|20&amp;40-5000|40&amp;60-4900|60&amp;80-3000|80&amp;100-1000|100&amp;120-1200|120&amp;140-1000|140&amp;160-500|160&amp;180-500|180&amp;200-400|200&amp;240-500|240&amp;280-400|280&amp;320-100|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;2,0&amp;1-0|1&amp;20-0|20&amp;40-0|40&amp;60-0|60&amp;80-400|80&amp;100-400|100&amp;120-400|120&amp;140-800|140&amp;160-800|160&amp;180-800|180&amp;200-800|200&amp;240-1000|240&amp;280-1200|280&amp;320-1400|320&amp;360-1600|360&amp;400-1200|400&amp;480-2000|480&amp;560-1000|560&amp;640-1500|640&amp;720-1000|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0;3,0&amp;1-65500|1&amp;20-29400|20&amp;40-3100|40&amp;60-1000|60&amp;80-500|80&amp;100-300|100&amp;120-0|120&amp;140-100|140&amp;160-0|160&amp;180-0|180&amp;200-0|200&amp;240-0|240&amp;280-0|280&amp;320-0|320&amp;360-0|360&amp;400-0|400&amp;480-0|480&amp;560-0|560&amp;640-0|640&amp;720-0|720&amp;800-0|800&amp;960-0|960&amp;1120-0|1120&amp;1280-0|1280&amp;1440-0|1440&amp;1600-0|1600&amp;1920-0|1920&amp;2240-0|2240&amp;2560-0|2560&amp;2880-0|2880&amp;3200-0|3200&amp;3840-0|3840&amp;4480-0|4480&amp;5120-0|5120&amp;5760-0|5760&amp;6400-0|6400&amp;7400-0|7400&amp;8400-0|8400&amp;99999999-0</v>
       </c>
       <c r="K121" s="29">
@@ -7162,7 +7195,7 @@
         <v>102600</v>
       </c>
       <c r="C122" s="67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D122" s="67">
         <v>6</v>
@@ -7175,7 +7208,7 @@
       <c r="H122" s="68"/>
       <c r="I122" s="26"/>
       <c r="J122" s="69" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
    